--- a/bodegas/LJ-101.xlsx
+++ b/bodegas/LJ-101.xlsx
@@ -13069,10 +13069,10 @@
         <v>19</v>
       </c>
       <c r="N291" t="n">
-        <v>4242.3899305556</v>
+        <v>4193.85</v>
       </c>
       <c r="O291" t="n">
-        <v>80605.4086805564</v>
+        <v>79683.15000000001</v>
       </c>
       <c r="P291" t="n">
         <v>7500</v>
@@ -13295,10 +13295,10 @@
         <v>88</v>
       </c>
       <c r="N296" t="n">
-        <v>6470.8036363636</v>
+        <v>6441.03</v>
       </c>
       <c r="O296" t="n">
-        <v>569430.7199999968</v>
+        <v>566810.64</v>
       </c>
       <c r="P296" t="n">
         <v>10500</v>
@@ -24392,10 +24392,10 @@
         <v>31</v>
       </c>
       <c r="N547" t="n">
-        <v>5234.4433367983</v>
+        <v>5218.1704573805</v>
       </c>
       <c r="O547" t="n">
-        <v>162267.7434407473</v>
+        <v>161763.2841787955</v>
       </c>
       <c r="P547" t="n">
         <v>8500</v>
@@ -25186,10 +25186,10 @@
         <v>9</v>
       </c>
       <c r="N564" t="n">
-        <v>15692.208588957</v>
+        <v>15502</v>
       </c>
       <c r="O564" t="n">
-        <v>141229.877300613</v>
+        <v>139518</v>
       </c>
       <c r="P564" t="n">
         <v>25900</v>
@@ -35328,10 +35328,10 @@
         <v>32</v>
       </c>
       <c r="N784" t="n">
-        <v>2861.1357880311</v>
+        <v>2857.22</v>
       </c>
       <c r="O784" t="n">
-        <v>91556.34521699521</v>
+        <v>91431.03999999999</v>
       </c>
       <c r="P784" t="n">
         <v>4900</v>

--- a/bodegas/LJ-101.xlsx
+++ b/bodegas/LJ-101.xlsx
@@ -983,10 +983,10 @@
         <v>12</v>
       </c>
       <c r="N14" t="n">
-        <v>27225.941422594</v>
+        <v>27000</v>
       </c>
       <c r="O14" t="n">
-        <v>326711.297071128</v>
+        <v>324000</v>
       </c>
       <c r="P14" t="n">
         <v>30000</v>
@@ -1139,10 +1139,10 @@
         <v>7</v>
       </c>
       <c r="N18" t="n">
-        <v>5784.4419026549</v>
+        <v>5758.9597787611</v>
       </c>
       <c r="O18" t="n">
-        <v>40491.0933185843</v>
+        <v>40312.7184513277</v>
       </c>
       <c r="P18" t="n">
         <v>16900</v>
@@ -2027,10 +2027,10 @@
         <v>11</v>
       </c>
       <c r="N40" t="n">
-        <v>2421.5176470588</v>
+        <v>2413.0011764706</v>
       </c>
       <c r="O40" t="n">
-        <v>26636.6941176468</v>
+        <v>26543.0129411766</v>
       </c>
       <c r="P40" t="n">
         <v>4700</v>
@@ -2066,10 +2066,10 @@
         <v>7</v>
       </c>
       <c r="N41" t="n">
-        <v>2487.0572046589</v>
+        <v>2474.7042429285</v>
       </c>
       <c r="O41" t="n">
-        <v>17409.4004326123</v>
+        <v>17322.9297004995</v>
       </c>
       <c r="P41" t="n">
         <v>4500</v>
@@ -2339,10 +2339,10 @@
         <v>22</v>
       </c>
       <c r="N48" t="n">
-        <v>21510.733070539</v>
+        <v>21333.69</v>
       </c>
       <c r="O48" t="n">
-        <v>473236.127551858</v>
+        <v>469341.18</v>
       </c>
       <c r="P48" t="n">
         <v>30000</v>
@@ -3629,10 +3629,10 @@
         <v>1</v>
       </c>
       <c r="N77" t="n">
-        <v>20547.289545455</v>
+        <v>18835.016818182</v>
       </c>
       <c r="O77" t="n">
-        <v>20547.289545455</v>
+        <v>18835.016818182</v>
       </c>
       <c r="P77" t="n">
         <v>40500</v>
@@ -3794,10 +3794,10 @@
         <v>7</v>
       </c>
       <c r="N81" t="n">
-        <v>15834.716054688</v>
+        <v>15711.966289063</v>
       </c>
       <c r="O81" t="n">
-        <v>110843.012382816</v>
+        <v>109983.764023441</v>
       </c>
       <c r="P81" t="n">
         <v>28500</v>
@@ -3841,10 +3841,10 @@
         <v>19</v>
       </c>
       <c r="N82" t="n">
-        <v>9642.5297333333</v>
+        <v>9392.0745333333</v>
       </c>
       <c r="O82" t="n">
-        <v>183208.0649333327</v>
+        <v>178449.4161333327</v>
       </c>
       <c r="P82" t="n">
         <v>18500</v>
@@ -5691,10 +5691,10 @@
         <v>17</v>
       </c>
       <c r="N125" t="n">
-        <v>27232.75862069</v>
+        <v>27000</v>
       </c>
       <c r="O125" t="n">
-        <v>462956.89655173</v>
+        <v>459000</v>
       </c>
       <c r="P125" t="n">
         <v>20000</v>
@@ -6031,10 +6031,10 @@
         <v>13</v>
       </c>
       <c r="N133" t="n">
-        <v>8104.9092</v>
+        <v>8046.39</v>
       </c>
       <c r="O133" t="n">
-        <v>105363.8196</v>
+        <v>104603.07</v>
       </c>
       <c r="P133" t="n">
         <v>20900</v>
@@ -6394,10 +6394,10 @@
         <v>7</v>
       </c>
       <c r="N141" t="n">
-        <v>7477.1013333333</v>
+        <v>7394.9354444444</v>
       </c>
       <c r="O141" t="n">
-        <v>52339.7093333331</v>
+        <v>51764.54811111079</v>
       </c>
       <c r="P141" t="n">
         <v>17900</v>
@@ -6988,10 +6988,10 @@
         <v>8</v>
       </c>
       <c r="N155" t="n">
-        <v>2576.9026455026</v>
+        <v>2563.34</v>
       </c>
       <c r="O155" t="n">
-        <v>20615.2211640208</v>
+        <v>20506.72</v>
       </c>
       <c r="P155" t="n">
         <v>4700</v>
@@ -7076,10 +7076,10 @@
         <v>6</v>
       </c>
       <c r="N157" t="n">
-        <v>11705.0765</v>
+        <v>11513.19</v>
       </c>
       <c r="O157" t="n">
-        <v>70230.459</v>
+        <v>69079.14</v>
       </c>
       <c r="P157" t="n">
         <v>17900</v>
@@ -8795,10 +8795,10 @@
         <v>9</v>
       </c>
       <c r="N196" t="n">
-        <v>13624.59908046</v>
+        <v>13593.35</v>
       </c>
       <c r="O196" t="n">
-        <v>122621.39172414</v>
+        <v>122340.15</v>
       </c>
       <c r="P196" t="n">
         <v>25500</v>
@@ -11192,10 +11192,10 @@
         <v>80</v>
       </c>
       <c r="N249" t="n">
-        <v>2289.4664730119</v>
+        <v>2267.0481788216</v>
       </c>
       <c r="O249" t="n">
-        <v>183157.317840952</v>
+        <v>181363.854305728</v>
       </c>
       <c r="P249" t="n">
         <v>3900</v>
@@ -11904,10 +11904,10 @@
         <v>18</v>
       </c>
       <c r="N265" t="n">
-        <v>4898.3218562874</v>
+        <v>4891</v>
       </c>
       <c r="O265" t="n">
-        <v>88169.7934131732</v>
+        <v>88038</v>
       </c>
       <c r="P265" t="n">
         <v>8200</v>
@@ -15961,10 +15961,10 @@
         <v>23</v>
       </c>
       <c r="N355" t="n">
-        <v>11658.147712418</v>
+        <v>11507.72</v>
       </c>
       <c r="O355" t="n">
-        <v>268137.397385614</v>
+        <v>264677.56</v>
       </c>
       <c r="P355" t="n">
         <v>25800</v>
@@ -16515,10 +16515,10 @@
         <v>3</v>
       </c>
       <c r="N367" t="n">
-        <v>19900</v>
+        <v>15920</v>
       </c>
       <c r="O367" t="n">
-        <v>59700</v>
+        <v>47760</v>
       </c>
       <c r="P367" t="n">
         <v>19900</v>
@@ -17272,10 +17272,10 @@
         <v>9</v>
       </c>
       <c r="N384" t="n">
-        <v>9301.333333333299</v>
+        <v>8720</v>
       </c>
       <c r="O384" t="n">
-        <v>83711.99999999969</v>
+        <v>78480</v>
       </c>
       <c r="P384" t="n">
         <v>10900</v>
@@ -18469,10 +18469,10 @@
         <v>2</v>
       </c>
       <c r="N411" t="n">
-        <v>4508.1255605381</v>
+        <v>4488</v>
       </c>
       <c r="O411" t="n">
-        <v>9016.2511210762</v>
+        <v>8976</v>
       </c>
       <c r="P411" t="n">
         <v>6200</v>
@@ -18510,10 +18510,10 @@
         <v>15</v>
       </c>
       <c r="N412" t="n">
-        <v>2613.7446197991</v>
+        <v>2610</v>
       </c>
       <c r="O412" t="n">
-        <v>39206.1692969865</v>
+        <v>39150</v>
       </c>
       <c r="P412" t="n">
         <v>3200</v>
@@ -20554,10 +20554,10 @@
         <v>10</v>
       </c>
       <c r="N460" t="n">
-        <v>13805.304244604</v>
+        <v>13513.64294964</v>
       </c>
       <c r="O460" t="n">
-        <v>138053.04244604</v>
+        <v>135136.4294964</v>
       </c>
       <c r="P460" t="n">
         <v>21900</v>
@@ -21414,10 +21414,10 @@
         <v>9</v>
       </c>
       <c r="N480" t="n">
-        <v>5453.6557676349</v>
+        <v>5431.12</v>
       </c>
       <c r="O480" t="n">
-        <v>49082.90190871411</v>
+        <v>48880.08</v>
       </c>
       <c r="P480" t="n">
         <v>8900</v>
@@ -21598,10 +21598,10 @@
         <v>13</v>
       </c>
       <c r="N484" t="n">
-        <v>27226.972222222</v>
+        <v>26854</v>
       </c>
       <c r="O484" t="n">
-        <v>353950.638888886</v>
+        <v>349102</v>
       </c>
       <c r="P484" t="n">
         <v>43900</v>
@@ -21639,10 +21639,10 @@
         <v>3</v>
       </c>
       <c r="N485" t="n">
-        <v>9777</v>
+        <v>6518</v>
       </c>
       <c r="O485" t="n">
-        <v>29331</v>
+        <v>19554</v>
       </c>
       <c r="P485" t="n">
         <v>10900</v>
@@ -22735,10 +22735,10 @@
         <v>51</v>
       </c>
       <c r="N510" t="n">
-        <v>13971.496466667</v>
+        <v>13878.97</v>
       </c>
       <c r="O510" t="n">
-        <v>712546.3198000171</v>
+        <v>707827.47</v>
       </c>
       <c r="P510" t="n">
         <v>21900</v>
@@ -23096,10 +23096,10 @@
         <v>9</v>
       </c>
       <c r="N518" t="n">
-        <v>7408.8065217391</v>
+        <v>5875.95</v>
       </c>
       <c r="O518" t="n">
-        <v>66679.25869565191</v>
+        <v>52883.55</v>
       </c>
       <c r="P518" t="n">
         <v>5900</v>
@@ -23622,10 +23622,10 @@
         <v>16</v>
       </c>
       <c r="N530" t="n">
-        <v>4692.9807692308</v>
+        <v>4437</v>
       </c>
       <c r="O530" t="n">
-        <v>75087.69230769281</v>
+        <v>70992</v>
       </c>
       <c r="P530" t="n">
         <v>4900</v>
@@ -23939,10 +23939,10 @@
         <v>39</v>
       </c>
       <c r="N537" t="n">
-        <v>3117.5970357143</v>
+        <v>3113.8900238095</v>
       </c>
       <c r="O537" t="n">
-        <v>121586.2843928577</v>
+        <v>121441.7109285705</v>
       </c>
       <c r="P537" t="n">
         <v>5000</v>
@@ -24169,10 +24169,10 @@
         <v>12</v>
       </c>
       <c r="N542" t="n">
-        <v>9099.032608695699</v>
+        <v>8878.450000000001</v>
       </c>
       <c r="O542" t="n">
-        <v>109188.3913043484</v>
+        <v>106541.4</v>
       </c>
       <c r="P542" t="n">
         <v>14100</v>
@@ -24215,10 +24215,10 @@
         <v>1</v>
       </c>
       <c r="N543" t="n">
-        <v>2498.7228351648</v>
+        <v>2495.98</v>
       </c>
       <c r="O543" t="n">
-        <v>2498.7228351648</v>
+        <v>2495.98</v>
       </c>
       <c r="P543" t="n">
         <v>4100</v>
@@ -24779,10 +24779,10 @@
         <v>37</v>
       </c>
       <c r="N555" t="n">
-        <v>3969.9272029703</v>
+        <v>3965.02</v>
       </c>
       <c r="O555" t="n">
-        <v>146887.3065099011</v>
+        <v>146705.74</v>
       </c>
       <c r="P555" t="n">
         <v>6500</v>
@@ -24825,10 +24825,10 @@
         <v>39</v>
       </c>
       <c r="N556" t="n">
-        <v>5844.4237327189</v>
+        <v>5791.05</v>
       </c>
       <c r="O556" t="n">
-        <v>227932.5255760371</v>
+        <v>225850.95</v>
       </c>
       <c r="P556" t="n">
         <v>9300</v>
@@ -24917,10 +24917,10 @@
         <v>3</v>
       </c>
       <c r="N558" t="n">
-        <v>22317.65</v>
+        <v>17358.17</v>
       </c>
       <c r="O558" t="n">
-        <v>66952.95000000001</v>
+        <v>52074.50999999999</v>
       </c>
       <c r="P558" t="n">
         <v>24500</v>
@@ -25622,10 +25622,10 @@
         <v>7</v>
       </c>
       <c r="N573" t="n">
-        <v>44124.685714286</v>
+        <v>42899</v>
       </c>
       <c r="O573" t="n">
-        <v>308872.800000002</v>
+        <v>300293</v>
       </c>
       <c r="P573" t="n">
         <v>70900</v>
@@ -26082,10 +26082,10 @@
         <v>6</v>
       </c>
       <c r="N583" t="n">
-        <v>22795.894912427</v>
+        <v>22739</v>
       </c>
       <c r="O583" t="n">
-        <v>136775.369474562</v>
+        <v>136434</v>
       </c>
       <c r="P583" t="n">
         <v>36900</v>
@@ -26174,10 +26174,10 @@
         <v>15</v>
       </c>
       <c r="N585" t="n">
-        <v>16092.045229682</v>
+        <v>16058</v>
       </c>
       <c r="O585" t="n">
-        <v>241380.67844523</v>
+        <v>240870</v>
       </c>
       <c r="P585" t="n">
         <v>25900</v>
@@ -27703,10 +27703,10 @@
         <v>6</v>
       </c>
       <c r="N618" t="n">
-        <v>9704.4375</v>
+        <v>8508</v>
       </c>
       <c r="O618" t="n">
-        <v>58226.625</v>
+        <v>51048</v>
       </c>
       <c r="P618" t="n">
         <v>14500</v>
@@ -28491,10 +28491,10 @@
         <v>6</v>
       </c>
       <c r="N635" t="n">
-        <v>9368.9914285714</v>
+        <v>7715.64</v>
       </c>
       <c r="O635" t="n">
-        <v>56213.9485714284</v>
+        <v>46293.84</v>
       </c>
       <c r="P635" t="n">
         <v>9900</v>
@@ -28675,10 +28675,10 @@
         <v>42</v>
       </c>
       <c r="N639" t="n">
-        <v>21748.414253898</v>
+        <v>21676</v>
       </c>
       <c r="O639" t="n">
-        <v>913433.398663716</v>
+        <v>910392</v>
       </c>
       <c r="P639" t="n">
         <v>34900</v>
@@ -29227,10 +29227,10 @@
         <v>11</v>
       </c>
       <c r="N651" t="n">
-        <v>18473.630136986</v>
+        <v>17981</v>
       </c>
       <c r="O651" t="n">
-        <v>203209.931506846</v>
+        <v>197791</v>
       </c>
       <c r="P651" t="n">
         <v>29900</v>
@@ -30372,10 +30372,10 @@
         <v>6</v>
       </c>
       <c r="N676" t="n">
-        <v>27422.4</v>
+        <v>27186</v>
       </c>
       <c r="O676" t="n">
-        <v>164534.4</v>
+        <v>163116</v>
       </c>
       <c r="P676" t="n">
         <v>43900</v>
@@ -30464,10 +30464,10 @@
         <v>27</v>
       </c>
       <c r="N678" t="n">
-        <v>3903.9739463602</v>
+        <v>3898</v>
       </c>
       <c r="O678" t="n">
-        <v>105407.2965517254</v>
+        <v>105246</v>
       </c>
       <c r="P678" t="n">
         <v>6900</v>
@@ -30510,10 +30510,10 @@
         <v>6</v>
       </c>
       <c r="N679" t="n">
-        <v>13585.460030166</v>
+        <v>13565</v>
       </c>
       <c r="O679" t="n">
-        <v>81512.760180996</v>
+        <v>81390</v>
       </c>
       <c r="P679" t="n">
         <v>22500</v>
@@ -30740,10 +30740,10 @@
         <v>24</v>
       </c>
       <c r="N684" t="n">
-        <v>8836.1575342466</v>
+        <v>8806</v>
       </c>
       <c r="O684" t="n">
-        <v>212067.7808219184</v>
+        <v>211344</v>
       </c>
       <c r="P684" t="n">
         <v>14900</v>
@@ -32167,10 +32167,10 @@
         <v>33</v>
       </c>
       <c r="N715" t="n">
-        <v>3647.235915493</v>
+        <v>3639.35</v>
       </c>
       <c r="O715" t="n">
-        <v>120358.785211269</v>
+        <v>120098.55</v>
       </c>
       <c r="P715" t="n">
         <v>7500</v>
@@ -32397,10 +32397,10 @@
         <v>17</v>
       </c>
       <c r="N720" t="n">
-        <v>12664.079439252</v>
+        <v>12489</v>
       </c>
       <c r="O720" t="n">
-        <v>215289.350467284</v>
+        <v>212313</v>
       </c>
       <c r="P720" t="n">
         <v>20900</v>
@@ -32443,10 +32443,10 @@
         <v>4</v>
       </c>
       <c r="N721" t="n">
-        <v>21937.5</v>
+        <v>21762</v>
       </c>
       <c r="O721" t="n">
-        <v>87750</v>
+        <v>87048</v>
       </c>
       <c r="P721" t="n">
         <v>35900</v>
@@ -40481,10 +40481,10 @@
         <v>9</v>
       </c>
       <c r="N895" t="n">
-        <v>8330.0435897436</v>
+        <v>7923.7</v>
       </c>
       <c r="O895" t="n">
-        <v>74970.3923076924</v>
+        <v>71313.3</v>
       </c>
       <c r="P895" t="n">
         <v>16600</v>
@@ -41590,10 +41590,10 @@
         <v>4</v>
       </c>
       <c r="N918" t="n">
-        <v>2870.9917808219</v>
+        <v>2832.1946575342</v>
       </c>
       <c r="O918" t="n">
-        <v>11483.9671232876</v>
+        <v>11328.7786301368</v>
       </c>
       <c r="P918" t="n">
         <v>12900</v>
@@ -41781,10 +41781,10 @@
         <v>3</v>
       </c>
       <c r="N922" t="n">
-        <v>29585.206779661</v>
+        <v>28615.2</v>
       </c>
       <c r="O922" t="n">
-        <v>88755.62033898299</v>
+        <v>85845.60000000001</v>
       </c>
       <c r="P922" t="n">
         <v>36500</v>
@@ -41830,10 +41830,10 @@
         <v>8</v>
       </c>
       <c r="N923" t="n">
-        <v>18030.611052632</v>
+        <v>16313.41</v>
       </c>
       <c r="O923" t="n">
-        <v>144244.888421056</v>
+        <v>130507.28</v>
       </c>
       <c r="P923" t="n">
         <v>33500</v>
@@ -42063,10 +42063,10 @@
         <v>10</v>
       </c>
       <c r="N928" t="n">
-        <v>10459.349677419</v>
+        <v>10348.08</v>
       </c>
       <c r="O928" t="n">
-        <v>104593.49677419</v>
+        <v>103480.8</v>
       </c>
       <c r="P928" t="n">
         <v>16900</v>
@@ -42112,10 +42112,10 @@
         <v>8</v>
       </c>
       <c r="N929" t="n">
-        <v>10806.564102564</v>
+        <v>10536.4</v>
       </c>
       <c r="O929" t="n">
-        <v>86452.512820512</v>
+        <v>84291.2</v>
       </c>
       <c r="P929" t="n">
         <v>16900</v>
@@ -42210,10 +42210,10 @@
         <v>8</v>
       </c>
       <c r="N931" t="n">
-        <v>10649.1</v>
+        <v>9874.620000000001</v>
       </c>
       <c r="O931" t="n">
-        <v>85192.8</v>
+        <v>78996.96000000001</v>
       </c>
       <c r="P931" t="n">
         <v>14700</v>
@@ -42746,10 +42746,10 @@
         <v>9</v>
       </c>
       <c r="N942" t="n">
-        <v>10020.157196262</v>
+        <v>9746.8801869159</v>
       </c>
       <c r="O942" t="n">
-        <v>90181.41476635801</v>
+        <v>87721.92168224309</v>
       </c>
       <c r="P942" t="n">
         <v>18500</v>
@@ -43472,10 +43472,10 @@
         <v>4</v>
       </c>
       <c r="N957" t="n">
-        <v>4388.3371764706</v>
+        <v>4337.31</v>
       </c>
       <c r="O957" t="n">
-        <v>17553.3487058824</v>
+        <v>17349.24</v>
       </c>
       <c r="P957" t="n">
         <v>12900</v>
@@ -43992,10 +43992,10 @@
         <v>36</v>
       </c>
       <c r="N968" t="n">
-        <v>4360.6660810811</v>
+        <v>4190.77</v>
       </c>
       <c r="O968" t="n">
-        <v>156983.9789189196</v>
+        <v>150867.72</v>
       </c>
       <c r="P968" t="n">
         <v>5900</v>
@@ -44956,10 +44956,10 @@
         <v>10</v>
       </c>
       <c r="N988" t="n">
-        <v>6053.1143</v>
+        <v>5876.81</v>
       </c>
       <c r="O988" t="n">
-        <v>60531.143</v>
+        <v>58768.10000000001</v>
       </c>
       <c r="P988" t="n">
         <v>22900</v>
@@ -45383,10 +45383,10 @@
         <v>11</v>
       </c>
       <c r="N997" t="n">
-        <v>7984.35</v>
+        <v>7258.5</v>
       </c>
       <c r="O997" t="n">
-        <v>87827.85000000001</v>
+        <v>79843.5</v>
       </c>
       <c r="P997" t="n">
         <v>17500</v>
@@ -45524,10 +45524,10 @@
         <v>5</v>
       </c>
       <c r="N1000" t="n">
-        <v>10018.344827586</v>
+        <v>9372</v>
       </c>
       <c r="O1000" t="n">
-        <v>50091.72413793</v>
+        <v>46860</v>
       </c>
       <c r="P1000" t="n">
         <v>17900</v>
@@ -45671,10 +45671,10 @@
         <v>5</v>
       </c>
       <c r="N1003" t="n">
-        <v>31661.163333333</v>
+        <v>13569.07</v>
       </c>
       <c r="O1003" t="n">
-        <v>158305.816666665</v>
+        <v>67845.35000000001</v>
       </c>
       <c r="P1003" t="n">
         <v>29900</v>
@@ -47098,10 +47098,10 @@
         <v>2</v>
       </c>
       <c r="N1033" t="n">
+        <v>28076.23</v>
+      </c>
+      <c r="O1033" t="n">
         <v>56152.46</v>
-      </c>
-      <c r="O1033" t="n">
-        <v>112304.92</v>
       </c>
       <c r="P1033" t="n">
         <v>36500</v>
@@ -47147,10 +47147,10 @@
         <v>9</v>
       </c>
       <c r="N1034" t="n">
-        <v>16236.522</v>
+        <v>15033.8164</v>
       </c>
       <c r="O1034" t="n">
-        <v>146128.698</v>
+        <v>135304.3476</v>
       </c>
       <c r="P1034" t="n">
         <v>19900</v>
@@ -47343,10 +47343,10 @@
         <v>7</v>
       </c>
       <c r="N1038" t="n">
-        <v>17438.2184</v>
+        <v>16146.4984</v>
       </c>
       <c r="O1038" t="n">
-        <v>122067.5288</v>
+        <v>113025.4888</v>
       </c>
       <c r="P1038" t="n">
         <v>26900</v>
@@ -49632,10 +49632,10 @@
         <v>2</v>
       </c>
       <c r="N1088" t="n">
-        <v>23008.657146402</v>
+        <v>22951.705012407</v>
       </c>
       <c r="O1088" t="n">
-        <v>46017.314292804</v>
+        <v>45903.410024814</v>
       </c>
       <c r="P1088" t="n">
         <v>37900</v>
@@ -53323,10 +53323,10 @@
         <v>35</v>
       </c>
       <c r="N1168" t="n">
-        <v>449.18534246575</v>
+        <v>415.07</v>
       </c>
       <c r="O1168" t="n">
-        <v>15721.48698630125</v>
+        <v>14527.45</v>
       </c>
       <c r="P1168" t="n">
         <v>2900</v>
@@ -53783,10 +53783,10 @@
         <v>9</v>
       </c>
       <c r="N1178" t="n">
-        <v>1039.9621428571</v>
+        <v>970.63142857143</v>
       </c>
       <c r="O1178" t="n">
-        <v>9359.6592857139</v>
+        <v>8735.68285714287</v>
       </c>
       <c r="P1178" t="n">
         <v>7200</v>

--- a/bodegas/LJ-101.xlsx
+++ b/bodegas/LJ-101.xlsx
@@ -944,10 +944,10 @@
         <v>69</v>
       </c>
       <c r="N13" t="n">
-        <v>1815.9962867012</v>
+        <v>1811.3037996546</v>
       </c>
       <c r="O13" t="n">
-        <v>125303.7437823828</v>
+        <v>124979.9621761674</v>
       </c>
       <c r="P13" t="n">
         <v>2600</v>
@@ -5992,10 +5992,10 @@
         <v>13</v>
       </c>
       <c r="N132" t="n">
-        <v>3872.3234767642</v>
+        <v>3865.67</v>
       </c>
       <c r="O132" t="n">
-        <v>50340.2051979346</v>
+        <v>50253.71</v>
       </c>
       <c r="P132" t="n">
         <v>5500</v>
@@ -6169,10 +6169,10 @@
         <v>34</v>
       </c>
       <c r="N136" t="n">
-        <v>2589.9594489247</v>
+        <v>2572.67</v>
       </c>
       <c r="O136" t="n">
-        <v>88058.62126343981</v>
+        <v>87470.78</v>
       </c>
       <c r="P136" t="n">
         <v>4700</v>
@@ -6307,10 +6307,10 @@
         <v>8</v>
       </c>
       <c r="N139" t="n">
-        <v>2597.4440764331</v>
+        <v>2570.16</v>
       </c>
       <c r="O139" t="n">
-        <v>20779.5526114648</v>
+        <v>20561.28</v>
       </c>
       <c r="P139" t="n">
         <v>4700</v>
@@ -6433,10 +6433,10 @@
         <v>4</v>
       </c>
       <c r="N142" t="n">
-        <v>3126.0967950311</v>
+        <v>3114.49</v>
       </c>
       <c r="O142" t="n">
-        <v>12504.3871801244</v>
+        <v>12457.96</v>
       </c>
       <c r="P142" t="n">
         <v>5500</v>
@@ -6988,10 +6988,10 @@
         <v>8</v>
       </c>
       <c r="N155" t="n">
-        <v>2597.7011260054</v>
+        <v>2563.34</v>
       </c>
       <c r="O155" t="n">
-        <v>20781.6090080432</v>
+        <v>20506.72</v>
       </c>
       <c r="P155" t="n">
         <v>4700</v>
@@ -8128,10 +8128,10 @@
         <v>15</v>
       </c>
       <c r="N181" t="n">
-        <v>3489.6196317829</v>
+        <v>3456.13</v>
       </c>
       <c r="O181" t="n">
-        <v>52344.2944767435</v>
+        <v>51841.95</v>
       </c>
       <c r="P181" t="n">
         <v>5700</v>
@@ -9364,10 +9364,10 @@
         <v>25</v>
       </c>
       <c r="N209" t="n">
-        <v>2588.3559055118</v>
+        <v>2582.2560787402</v>
       </c>
       <c r="O209" t="n">
-        <v>64708.89763779499</v>
+        <v>64556.401968505</v>
       </c>
       <c r="P209" t="n">
         <v>4500</v>
@@ -9725,10 +9725,10 @@
         <v>39</v>
       </c>
       <c r="N217" t="n">
-        <v>6816.3581538462</v>
+        <v>6713.08</v>
       </c>
       <c r="O217" t="n">
-        <v>265837.9680000018</v>
+        <v>261810.12</v>
       </c>
       <c r="P217" t="n">
         <v>9900</v>
@@ -10370,10 +10370,10 @@
         <v>40</v>
       </c>
       <c r="N231" t="n">
-        <v>7538.62740638</v>
+        <v>7507.39</v>
       </c>
       <c r="O231" t="n">
-        <v>301545.0962552</v>
+        <v>300295.6</v>
       </c>
       <c r="P231" t="n">
         <v>13500</v>
@@ -10419,10 +10419,10 @@
         <v>56</v>
       </c>
       <c r="N232" t="n">
-        <v>8907.908396946599</v>
+        <v>8796</v>
       </c>
       <c r="O232" t="n">
-        <v>498842.8702290095</v>
+        <v>492576</v>
       </c>
       <c r="P232" t="n">
         <v>14900</v>
@@ -10598,10 +10598,10 @@
         <v>36</v>
       </c>
       <c r="N236" t="n">
-        <v>3801.7317574476</v>
+        <v>3795.7100070509</v>
       </c>
       <c r="O236" t="n">
-        <v>136862.3432681136</v>
+        <v>136645.5602538324</v>
       </c>
       <c r="P236" t="n">
         <v>6200</v>
@@ -10644,10 +10644,10 @@
         <v>42</v>
       </c>
       <c r="N237" t="n">
-        <v>3695.2967632027</v>
+        <v>3684</v>
       </c>
       <c r="O237" t="n">
-        <v>155202.4640545134</v>
+        <v>154728</v>
       </c>
       <c r="P237" t="n">
         <v>6200</v>
@@ -11013,10 +11013,10 @@
         <v>51</v>
       </c>
       <c r="N245" t="n">
-        <v>1213.150338295</v>
+        <v>1203.38</v>
       </c>
       <c r="O245" t="n">
-        <v>61870.667253045</v>
+        <v>61372.38</v>
       </c>
       <c r="P245" t="n">
         <v>1900</v>
@@ -11192,10 +11192,10 @@
         <v>80</v>
       </c>
       <c r="N249" t="n">
-        <v>2286.8353823774</v>
+        <v>2267.048162926</v>
       </c>
       <c r="O249" t="n">
-        <v>182946.830590192</v>
+        <v>181363.85303408</v>
       </c>
       <c r="P249" t="n">
         <v>3900</v>
@@ -11422,10 +11422,10 @@
         <v>10</v>
       </c>
       <c r="N254" t="n">
-        <v>8687.96003996</v>
+        <v>8662</v>
       </c>
       <c r="O254" t="n">
-        <v>86879.60039960001</v>
+        <v>86620</v>
       </c>
       <c r="P254" t="n">
         <v>14200</v>
@@ -11950,10 +11950,10 @@
         <v>18</v>
       </c>
       <c r="N266" t="n">
-        <v>8209.849315068501</v>
+        <v>8154</v>
       </c>
       <c r="O266" t="n">
-        <v>147777.287671233</v>
+        <v>146772</v>
       </c>
       <c r="P266" t="n">
         <v>13500</v>
@@ -13210,10 +13210,10 @@
         <v>56</v>
       </c>
       <c r="N294" t="n">
-        <v>6493.1840890688</v>
+        <v>6441.03</v>
       </c>
       <c r="O294" t="n">
-        <v>363618.3089878528</v>
+        <v>360697.68</v>
       </c>
       <c r="P294" t="n">
         <v>10500</v>
@@ -13425,10 +13425,10 @@
         <v>64</v>
       </c>
       <c r="N299" t="n">
-        <v>3660.708</v>
+        <v>3655.96</v>
       </c>
       <c r="O299" t="n">
-        <v>234285.312</v>
+        <v>233981.44</v>
       </c>
       <c r="P299" t="n">
         <v>5500</v>
@@ -13872,10 +13872,10 @@
         <v>51</v>
       </c>
       <c r="N309" t="n">
-        <v>1535.9702761427</v>
+        <v>1532.6290291403</v>
       </c>
       <c r="O309" t="n">
-        <v>78334.4840832777</v>
+        <v>78164.0804861553</v>
       </c>
       <c r="P309" t="n">
         <v>1200</v>
@@ -14973,10 +14973,10 @@
         <v>9</v>
       </c>
       <c r="N333" t="n">
-        <v>9795.0468</v>
+        <v>9678.9</v>
       </c>
       <c r="O333" t="n">
-        <v>88155.4212</v>
+        <v>87110.09999999999</v>
       </c>
       <c r="P333" t="n">
         <v>15500</v>
@@ -16090,10 +16090,10 @@
         <v>14</v>
       </c>
       <c r="N358" t="n">
-        <v>1303.6380504587</v>
+        <v>1301.3994036697</v>
       </c>
       <c r="O358" t="n">
-        <v>18250.9327064218</v>
+        <v>18219.5916513758</v>
       </c>
       <c r="P358" t="n">
         <v>2000</v>
@@ -16423,10 +16423,10 @@
         <v>63</v>
       </c>
       <c r="N365" t="n">
-        <v>2030.7740585774</v>
+        <v>1965</v>
       </c>
       <c r="O365" t="n">
-        <v>127938.7656903762</v>
+        <v>123795</v>
       </c>
       <c r="P365" t="n">
         <v>3700</v>
@@ -17001,10 +17001,10 @@
         <v>5</v>
       </c>
       <c r="N378" t="n">
-        <v>210.96774011299</v>
+        <v>204.05079096045</v>
       </c>
       <c r="O378" t="n">
-        <v>1054.83870056495</v>
+        <v>1020.25395480225</v>
       </c>
       <c r="P378" t="n">
         <v>500</v>
@@ -18469,10 +18469,10 @@
         <v>2</v>
       </c>
       <c r="N411" t="n">
-        <v>4550.9158878505</v>
+        <v>4488</v>
       </c>
       <c r="O411" t="n">
-        <v>9101.831775701001</v>
+        <v>8976</v>
       </c>
       <c r="P411" t="n">
         <v>6200</v>
@@ -18510,10 +18510,10 @@
         <v>15</v>
       </c>
       <c r="N412" t="n">
-        <v>2621.3808139535</v>
+        <v>2610</v>
       </c>
       <c r="O412" t="n">
-        <v>39320.7122093025</v>
+        <v>39150</v>
       </c>
       <c r="P412" t="n">
         <v>3200</v>
@@ -18592,10 +18592,10 @@
         <v>13</v>
       </c>
       <c r="N414" t="n">
-        <v>1979.2819843342</v>
+        <v>1969</v>
       </c>
       <c r="O414" t="n">
-        <v>25730.6657963446</v>
+        <v>25597</v>
       </c>
       <c r="P414" t="n">
         <v>1500</v>
@@ -18633,10 +18633,10 @@
         <v>19</v>
       </c>
       <c r="N415" t="n">
-        <v>2040.34375</v>
+        <v>1958.73</v>
       </c>
       <c r="O415" t="n">
-        <v>38766.53125</v>
+        <v>37215.87</v>
       </c>
       <c r="P415" t="n">
         <v>3400</v>
@@ -18674,10 +18674,10 @@
         <v>56</v>
       </c>
       <c r="N416" t="n">
-        <v>8818.9498942682</v>
+        <v>8794.48</v>
       </c>
       <c r="O416" t="n">
-        <v>493861.1940790192</v>
+        <v>492490.88</v>
       </c>
       <c r="P416" t="n">
         <v>14500</v>
@@ -18843,10 +18843,10 @@
         <v>97</v>
       </c>
       <c r="N420" t="n">
-        <v>2558.6841592313</v>
+        <v>2517.22</v>
       </c>
       <c r="O420" t="n">
-        <v>248192.3634454361</v>
+        <v>244170.34</v>
       </c>
       <c r="P420" t="n">
         <v>4200</v>
@@ -18884,10 +18884,10 @@
         <v>217</v>
       </c>
       <c r="N421" t="n">
-        <v>2035.7801454898</v>
+        <v>2029.8736372454</v>
       </c>
       <c r="O421" t="n">
-        <v>441764.2915712866</v>
+        <v>440482.5792822518</v>
       </c>
       <c r="P421" t="n">
         <v>3600</v>
@@ -19637,10 +19637,10 @@
         <v>16</v>
       </c>
       <c r="N439" t="n">
-        <v>15639.519117647</v>
+        <v>14371.45</v>
       </c>
       <c r="O439" t="n">
-        <v>250232.305882352</v>
+        <v>229943.2</v>
       </c>
       <c r="P439" t="n">
         <v>23300</v>
@@ -20508,10 +20508,10 @@
         <v>15</v>
       </c>
       <c r="N459" t="n">
-        <v>11652.839895288</v>
+        <v>11562.038534031</v>
       </c>
       <c r="O459" t="n">
-        <v>174792.59842932</v>
+        <v>173430.578010465</v>
       </c>
       <c r="P459" t="n">
         <v>18500</v>
@@ -20600,10 +20600,10 @@
         <v>3</v>
       </c>
       <c r="N461" t="n">
-        <v>12155.852217573</v>
+        <v>12005.159832636</v>
       </c>
       <c r="O461" t="n">
-        <v>36467.55665271899</v>
+        <v>36015.479497908</v>
       </c>
       <c r="P461" t="n">
         <v>19500</v>
@@ -21025,10 +21025,10 @@
         <v>19</v>
       </c>
       <c r="N471" t="n">
-        <v>22817.681329923</v>
+        <v>22730.48</v>
       </c>
       <c r="O471" t="n">
-        <v>433535.945268537</v>
+        <v>431879.12</v>
       </c>
       <c r="P471" t="n">
         <v>36900</v>
@@ -24396,10 +24396,10 @@
         <v>11</v>
       </c>
       <c r="N547" t="n">
-        <v>5220.5451448041</v>
+        <v>5194</v>
       </c>
       <c r="O547" t="n">
-        <v>57425.99659284511</v>
+        <v>57134</v>
       </c>
       <c r="P547" t="n">
         <v>9000</v>
@@ -26355,10 +26355,10 @@
         <v>13</v>
       </c>
       <c r="N589" t="n">
-        <v>1420.3389830508</v>
+        <v>1400</v>
       </c>
       <c r="O589" t="n">
-        <v>18464.4067796604</v>
+        <v>18200</v>
       </c>
       <c r="P589" t="n">
         <v>2300</v>
@@ -26401,10 +26401,10 @@
         <v>18</v>
       </c>
       <c r="N590" t="n">
-        <v>6085.1063829787</v>
+        <v>6000</v>
       </c>
       <c r="O590" t="n">
-        <v>109531.9148936166</v>
+        <v>108000</v>
       </c>
       <c r="P590" t="n">
         <v>10000</v>
@@ -26583,10 +26583,10 @@
         <v>12</v>
       </c>
       <c r="N594" t="n">
-        <v>539.28902627512</v>
+        <v>520</v>
       </c>
       <c r="O594" t="n">
-        <v>6471.46831530144</v>
+        <v>6240</v>
       </c>
       <c r="P594" t="n">
         <v>850</v>
@@ -26678,10 +26678,10 @@
         <v>1</v>
       </c>
       <c r="N596" t="n">
-        <v>1872.4705882353</v>
+        <v>1840</v>
       </c>
       <c r="O596" t="n">
-        <v>1872.4705882353</v>
+        <v>1840</v>
       </c>
       <c r="P596" t="n">
         <v>3000</v>
@@ -27101,10 +27101,10 @@
         <v>37</v>
       </c>
       <c r="N605" t="n">
-        <v>13863.987068966</v>
+        <v>13687</v>
       </c>
       <c r="O605" t="n">
-        <v>512967.521551742</v>
+        <v>506419</v>
       </c>
       <c r="P605" t="n">
         <v>21900</v>
@@ -27976,10 +27976,10 @@
         <v>8</v>
       </c>
       <c r="N624" t="n">
-        <v>6112.6956521739</v>
+        <v>5858</v>
       </c>
       <c r="O624" t="n">
-        <v>48901.5652173912</v>
+        <v>46864</v>
       </c>
       <c r="P624" t="n">
         <v>9500</v>
@@ -28856,10 +28856,10 @@
         <v>10</v>
       </c>
       <c r="N643" t="n">
-        <v>9045.4669811321</v>
+        <v>9003</v>
       </c>
       <c r="O643" t="n">
-        <v>90454.669811321</v>
+        <v>90030</v>
       </c>
       <c r="P643" t="n">
         <v>14900</v>
@@ -29679,10 +29679,10 @@
         <v>3</v>
       </c>
       <c r="N661" t="n">
-        <v>4223.6597938144</v>
+        <v>4202</v>
       </c>
       <c r="O661" t="n">
-        <v>12670.9793814432</v>
+        <v>12606</v>
       </c>
       <c r="P661" t="n">
         <v>7900</v>
@@ -29863,10 +29863,10 @@
         <v>2</v>
       </c>
       <c r="N665" t="n">
-        <v>10095.669565217</v>
+        <v>9839</v>
       </c>
       <c r="O665" t="n">
-        <v>20191.339130434</v>
+        <v>19678</v>
       </c>
       <c r="P665" t="n">
         <v>16900</v>
@@ -32944,10 +32944,10 @@
         <v>153</v>
       </c>
       <c r="N732" t="n">
-        <v>1946.0906677937</v>
+        <v>1907.3944716822</v>
       </c>
       <c r="O732" t="n">
-        <v>297751.8721724361</v>
+        <v>291831.3541673766</v>
       </c>
       <c r="P732" t="n">
         <v>2500</v>
@@ -32990,10 +32990,10 @@
         <v>67</v>
       </c>
       <c r="N733" t="n">
-        <v>1796.7129837251</v>
+        <v>1771.091283906</v>
       </c>
       <c r="O733" t="n">
-        <v>120379.7699095817</v>
+        <v>118663.116021702</v>
       </c>
       <c r="P733" t="n">
         <v>2500</v>
@@ -33036,10 +33036,10 @@
         <v>135</v>
       </c>
       <c r="N734" t="n">
-        <v>2095.5452849741</v>
+        <v>2079.3842227979</v>
       </c>
       <c r="O734" t="n">
-        <v>282898.6134715035</v>
+        <v>280716.8700777165</v>
       </c>
       <c r="P734" t="n">
         <v>2900</v>
@@ -33082,10 +33082,10 @@
         <v>107</v>
       </c>
       <c r="N735" t="n">
-        <v>1828.4692441176</v>
+        <v>1803.0149852941</v>
       </c>
       <c r="O735" t="n">
-        <v>195646.2091205832</v>
+        <v>192922.6034264687</v>
       </c>
       <c r="P735" t="n">
         <v>2500</v>
@@ -33174,10 +33174,10 @@
         <v>70</v>
       </c>
       <c r="N737" t="n">
-        <v>2137.4820360902</v>
+        <v>2122.1641172932</v>
       </c>
       <c r="O737" t="n">
-        <v>149623.742526314</v>
+        <v>148551.488210524</v>
       </c>
       <c r="P737" t="n">
         <v>2900</v>
@@ -33312,10 +33312,10 @@
         <v>109</v>
       </c>
       <c r="N740" t="n">
-        <v>3276.0008772707</v>
+        <v>3224.5679308817</v>
       </c>
       <c r="O740" t="n">
-        <v>357084.0956225063</v>
+        <v>351477.9044661053</v>
       </c>
       <c r="P740" t="n">
         <v>4500</v>
@@ -33768,10 +33768,10 @@
         <v>28</v>
       </c>
       <c r="N750" t="n">
-        <v>5414.576625</v>
+        <v>5347.73</v>
       </c>
       <c r="O750" t="n">
-        <v>151608.1455</v>
+        <v>149736.44</v>
       </c>
       <c r="P750" t="n">
         <v>9500</v>
@@ -35292,10 +35292,10 @@
         <v>8</v>
       </c>
       <c r="N783" t="n">
-        <v>2769.7168108108</v>
+        <v>2682.71</v>
       </c>
       <c r="O783" t="n">
-        <v>22157.7344864864</v>
+        <v>21461.68</v>
       </c>
       <c r="P783" t="n">
         <v>10900</v>
@@ -36031,10 +36031,10 @@
         <v>250</v>
       </c>
       <c r="N799" t="n">
-        <v>577.72789151821</v>
+        <v>574.67194894975</v>
       </c>
       <c r="O799" t="n">
-        <v>144431.9728795525</v>
+        <v>143667.9872374375</v>
       </c>
       <c r="P799" t="n">
         <v>800</v>
@@ -36780,10 +36780,10 @@
         <v>9</v>
       </c>
       <c r="N815" t="n">
-        <v>2483.1635416667</v>
+        <v>2270.3210416667</v>
       </c>
       <c r="O815" t="n">
-        <v>22348.4718750003</v>
+        <v>20432.8893750003</v>
       </c>
       <c r="P815" t="n">
         <v>3900</v>
@@ -37581,10 +37581,10 @@
         <v>14</v>
       </c>
       <c r="N832" t="n">
-        <v>1815.5064655172</v>
+        <v>1684.79</v>
       </c>
       <c r="O832" t="n">
-        <v>25417.0905172408</v>
+        <v>23587.06</v>
       </c>
       <c r="P832" t="n">
         <v>2900</v>
@@ -37625,10 +37625,10 @@
         <v>2</v>
       </c>
       <c r="N833" t="n">
-        <v>6349.5722627737</v>
+        <v>6213.51</v>
       </c>
       <c r="O833" t="n">
-        <v>12699.1445255474</v>
+        <v>12427.02</v>
       </c>
       <c r="P833" t="n">
         <v>10300</v>
@@ -39045,10 +39045,10 @@
         <v>187</v>
       </c>
       <c r="N864" t="n">
-        <v>2047.4600343643</v>
+        <v>2030.02</v>
       </c>
       <c r="O864" t="n">
-        <v>382875.0264261241</v>
+        <v>379613.74</v>
       </c>
       <c r="P864" t="n">
         <v>3600</v>
@@ -39274,10 +39274,10 @@
         <v>309</v>
       </c>
       <c r="N869" t="n">
-        <v>704.1779547101401</v>
+        <v>703.79545471015</v>
       </c>
       <c r="O869" t="n">
-        <v>217590.9880054333</v>
+        <v>217472.7955054363</v>
       </c>
       <c r="P869" t="n">
         <v>900</v>
@@ -39323,10 +39323,10 @@
         <v>24</v>
       </c>
       <c r="N870" t="n">
-        <v>3216.9665454545</v>
+        <v>3182.2510909091</v>
       </c>
       <c r="O870" t="n">
-        <v>77207.19709090801</v>
+        <v>76374.02618181841</v>
       </c>
       <c r="P870" t="n">
         <v>6900</v>
@@ -40198,10 +40198,10 @@
         <v>19</v>
       </c>
       <c r="N889" t="n">
-        <v>3674.9932848233</v>
+        <v>3629.7161122661</v>
       </c>
       <c r="O889" t="n">
-        <v>69824.8724116427</v>
+        <v>68964.6061330559</v>
       </c>
       <c r="P889" t="n">
         <v>4900</v>
@@ -46426,10 +46426,10 @@
         <v>50</v>
       </c>
       <c r="N1019" t="n">
-        <v>713.93197013211</v>
+        <v>711.48</v>
       </c>
       <c r="O1019" t="n">
-        <v>35696.5985066055</v>
+        <v>35574</v>
       </c>
       <c r="P1019" t="n">
         <v>2500</v>
@@ -47925,10 +47925,10 @@
         <v>19</v>
       </c>
       <c r="N1050" t="n">
-        <v>2251.9952</v>
+        <v>2010.71</v>
       </c>
       <c r="O1050" t="n">
-        <v>42787.9088</v>
+        <v>38203.49</v>
       </c>
       <c r="P1050" t="n">
         <v>7200</v>
@@ -48203,10 +48203,10 @@
         <v>56</v>
       </c>
       <c r="N1056" t="n">
-        <v>2851.4129341317</v>
+        <v>2752.52</v>
       </c>
       <c r="O1056" t="n">
-        <v>159679.1243113752</v>
+        <v>154141.12</v>
       </c>
       <c r="P1056" t="n">
         <v>4500</v>
@@ -48332,10 +48332,10 @@
         <v>597</v>
       </c>
       <c r="N1059" t="n">
-        <v>714.37850499616</v>
+        <v>704.8968946963899</v>
       </c>
       <c r="O1059" t="n">
-        <v>426483.9674827075</v>
+        <v>420823.4461337448</v>
       </c>
       <c r="P1059" t="n">
         <v>900</v>
@@ -48780,10 +48780,10 @@
         <v>9</v>
       </c>
       <c r="N1069" t="n">
-        <v>2496.9418200728</v>
+        <v>2489.1752678107</v>
       </c>
       <c r="O1069" t="n">
-        <v>22472.4763806552</v>
+        <v>22402.5774102963</v>
       </c>
       <c r="P1069" t="n">
         <v>3000</v>
@@ -48947,10 +48947,10 @@
         <v>73</v>
       </c>
       <c r="N1073" t="n">
-        <v>3192.6751439214</v>
+        <v>3181.9</v>
       </c>
       <c r="O1073" t="n">
-        <v>233065.2855062622</v>
+        <v>232278.7</v>
       </c>
       <c r="P1073" t="n">
         <v>5100</v>
@@ -49032,10 +49032,10 @@
         <v>50</v>
       </c>
       <c r="N1075" t="n">
-        <v>1803.5408695029</v>
+        <v>1794.2879773671</v>
       </c>
       <c r="O1075" t="n">
-        <v>90177.04347514501</v>
+        <v>89714.398868355</v>
       </c>
       <c r="P1075" t="n">
         <v>1600</v>
@@ -49076,10 +49076,10 @@
         <v>4</v>
       </c>
       <c r="N1076" t="n">
-        <v>3081.4280769231</v>
+        <v>2830.2251183432</v>
       </c>
       <c r="O1076" t="n">
-        <v>12325.7123076924</v>
+        <v>11320.9004733728</v>
       </c>
       <c r="P1076" t="n">
         <v>2400</v>
@@ -49164,10 +49164,10 @@
         <v>9</v>
       </c>
       <c r="N1078" t="n">
-        <v>2540.4017582418</v>
+        <v>2523.3377514793</v>
       </c>
       <c r="O1078" t="n">
-        <v>22863.6158241762</v>
+        <v>22710.0397633137</v>
       </c>
       <c r="P1078" t="n">
         <v>2800</v>
@@ -49537,10 +49537,10 @@
         <v>140</v>
       </c>
       <c r="N1086" t="n">
-        <v>707.12182981928</v>
+        <v>705.52801204819</v>
       </c>
       <c r="O1086" t="n">
-        <v>98997.0561746992</v>
+        <v>98773.9216867466</v>
       </c>
       <c r="P1086" t="n">
         <v>1500</v>
@@ -52029,10 +52029,10 @@
         <v>9</v>
       </c>
       <c r="N1140" t="n">
-        <v>1338.6403076923</v>
+        <v>1160.1556923077</v>
       </c>
       <c r="O1140" t="n">
-        <v>12047.7627692307</v>
+        <v>10441.4012307693</v>
       </c>
       <c r="P1140" t="n">
         <v>1600</v>
@@ -54359,10 +54359,10 @@
         <v>19</v>
       </c>
       <c r="N1190" t="n">
-        <v>229.9076771366</v>
+        <v>227.41596785975</v>
       </c>
       <c r="O1190" t="n">
-        <v>4368.2458655954</v>
+        <v>4320.90338933525</v>
       </c>
       <c r="P1190" t="n">
         <v>1200</v>
@@ -55330,10 +55330,10 @@
         <v>6</v>
       </c>
       <c r="N1211" t="n">
-        <v>2464</v>
+        <v>2200</v>
       </c>
       <c r="O1211" t="n">
-        <v>14784</v>
+        <v>13200</v>
       </c>
       <c r="P1211" t="n">
         <v>2700</v>

--- a/bodegas/LJ-101.xlsx
+++ b/bodegas/LJ-101.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-07</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-08</t>
         </is>
       </c>
     </row>
@@ -7912,22 +7912,22 @@
         <v>0</v>
       </c>
       <c r="L176" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M176" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="N176" t="n">
         <v>1726.32</v>
       </c>
       <c r="O176" t="n">
-        <v>27621.12</v>
+        <v>17263.2</v>
       </c>
       <c r="P176" t="n">
         <v>1500</v>
       </c>
       <c r="Q176" t="n">
-        <v>24000</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="177">
@@ -9542,22 +9542,22 @@
         <v>0</v>
       </c>
       <c r="L213" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M213" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="N213" t="n">
         <v>2033.5763768116</v>
       </c>
       <c r="O213" t="n">
-        <v>65074.4440579712</v>
+        <v>16268.6110144928</v>
       </c>
       <c r="P213" t="n">
         <v>4100</v>
       </c>
       <c r="Q213" t="n">
-        <v>131200</v>
+        <v>32800</v>
       </c>
     </row>
     <row r="214">
@@ -10318,22 +10318,22 @@
         <v>0</v>
       </c>
       <c r="L230" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M230" t="n">
-        <v>1172</v>
+        <v>1072</v>
       </c>
       <c r="N230" t="n">
         <v>156.25</v>
       </c>
       <c r="O230" t="n">
-        <v>183125</v>
+        <v>167500</v>
       </c>
       <c r="P230" t="n">
         <v>250</v>
       </c>
       <c r="Q230" t="n">
-        <v>293000</v>
+        <v>268000</v>
       </c>
     </row>
     <row r="231">
@@ -11503,22 +11503,22 @@
         <v>0</v>
       </c>
       <c r="L256" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M256" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N256" t="n">
         <v>10716.34</v>
       </c>
       <c r="O256" t="n">
-        <v>64298.04</v>
+        <v>42865.36</v>
       </c>
       <c r="P256" t="n">
         <v>39000</v>
       </c>
       <c r="Q256" t="n">
-        <v>234000</v>
+        <v>156000</v>
       </c>
     </row>
     <row r="257">
@@ -12083,22 +12083,22 @@
         <v>0</v>
       </c>
       <c r="L269" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M269" t="n">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="N269" t="n">
         <v>2090.85</v>
       </c>
       <c r="O269" t="n">
-        <v>457896.15</v>
+        <v>420260.85</v>
       </c>
       <c r="P269" t="n">
         <v>2900</v>
       </c>
       <c r="Q269" t="n">
-        <v>635100</v>
+        <v>582900</v>
       </c>
     </row>
     <row r="270">
@@ -12302,22 +12302,22 @@
         <v>0</v>
       </c>
       <c r="L274" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M274" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="N274" t="n">
         <v>2769.98</v>
       </c>
       <c r="O274" t="n">
-        <v>80329.42</v>
+        <v>63709.54</v>
       </c>
       <c r="P274" t="n">
         <v>3500</v>
       </c>
       <c r="Q274" t="n">
-        <v>101500</v>
+        <v>80500</v>
       </c>
     </row>
     <row r="275">
@@ -13245,22 +13245,22 @@
         <v>0</v>
       </c>
       <c r="L295" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M295" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="N295" t="n">
         <v>1121.98</v>
       </c>
       <c r="O295" t="n">
-        <v>10097.82</v>
+        <v>6731.88</v>
       </c>
       <c r="P295" t="n">
         <v>2400</v>
       </c>
       <c r="Q295" t="n">
-        <v>21600</v>
+        <v>14400</v>
       </c>
     </row>
     <row r="296">
@@ -13291,22 +13291,22 @@
         <v>0</v>
       </c>
       <c r="L296" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M296" t="n">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="N296" t="n">
         <v>1592.5677691978</v>
       </c>
       <c r="O296" t="n">
-        <v>136960.8281510108</v>
+        <v>98739.20169026361</v>
       </c>
       <c r="P296" t="n">
         <v>3900</v>
       </c>
       <c r="Q296" t="n">
-        <v>335400</v>
+        <v>241800</v>
       </c>
     </row>
     <row r="297">
@@ -13825,22 +13825,22 @@
         <v>0</v>
       </c>
       <c r="L308" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M308" t="n">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="N308" t="n">
         <v>1770.37</v>
       </c>
       <c r="O308" t="n">
-        <v>157562.93</v>
+        <v>146940.71</v>
       </c>
       <c r="P308" t="n">
         <v>3900</v>
       </c>
       <c r="Q308" t="n">
-        <v>347100</v>
+        <v>323700</v>
       </c>
     </row>
     <row r="309">
@@ -14552,22 +14552,22 @@
         <v>0</v>
       </c>
       <c r="L324" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M324" t="n">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="N324" t="n">
         <v>1200</v>
       </c>
       <c r="O324" t="n">
-        <v>349200</v>
+        <v>342000</v>
       </c>
       <c r="P324" t="n">
         <v>1500</v>
       </c>
       <c r="Q324" t="n">
-        <v>436500</v>
+        <v>427500</v>
       </c>
     </row>
     <row r="325">
@@ -15474,22 +15474,22 @@
         <v>0</v>
       </c>
       <c r="L344" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M344" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="N344" t="n">
         <v>1630.9229788882</v>
       </c>
       <c r="O344" t="n">
-        <v>140259.3761843852</v>
+        <v>130473.838311056</v>
       </c>
       <c r="P344" t="n">
         <v>2500</v>
       </c>
       <c r="Q344" t="n">
-        <v>215000</v>
+        <v>200000</v>
       </c>
     </row>
     <row r="345">
@@ -21454,22 +21454,22 @@
         <v>0</v>
       </c>
       <c r="L481" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M481" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="N481" t="n">
         <v>1560.9985110132</v>
       </c>
       <c r="O481" t="n">
-        <v>84293.9195947128</v>
+        <v>74927.92852863359</v>
       </c>
       <c r="P481" t="n">
         <v>2900</v>
       </c>
       <c r="Q481" t="n">
-        <v>156600</v>
+        <v>139200</v>
       </c>
     </row>
     <row r="482">
@@ -24206,22 +24206,22 @@
         <v>0</v>
       </c>
       <c r="L543" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M543" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="N543" t="n">
         <v>3254.49</v>
       </c>
       <c r="O543" t="n">
-        <v>152961.03</v>
+        <v>136688.58</v>
       </c>
       <c r="P543" t="n">
         <v>5200</v>
       </c>
       <c r="Q543" t="n">
-        <v>244400</v>
+        <v>218400</v>
       </c>
     </row>
     <row r="544">
@@ -26482,22 +26482,22 @@
         <v>0</v>
       </c>
       <c r="L592" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M592" t="n">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="N592" t="n">
         <v>1817</v>
       </c>
       <c r="O592" t="n">
-        <v>205321</v>
+        <v>194419</v>
       </c>
       <c r="P592" t="n">
         <v>3100</v>
       </c>
       <c r="Q592" t="n">
-        <v>350300</v>
+        <v>331700</v>
       </c>
     </row>
     <row r="593">
@@ -27924,22 +27924,22 @@
         <v>0</v>
       </c>
       <c r="L623" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M623" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N623" t="n">
         <v>17644.653166667</v>
       </c>
       <c r="O623" t="n">
-        <v>35289.306333334</v>
+        <v>0</v>
       </c>
       <c r="P623" t="n">
         <v>28200</v>
       </c>
       <c r="Q623" t="n">
-        <v>56400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="624">
@@ -29857,22 +29857,22 @@
         <v>0</v>
       </c>
       <c r="L665" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M665" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N665" t="n">
         <v>9839</v>
       </c>
       <c r="O665" t="n">
-        <v>19678</v>
+        <v>0</v>
       </c>
       <c r="P665" t="n">
         <v>16900</v>
       </c>
       <c r="Q665" t="n">
-        <v>33800</v>
+        <v>0</v>
       </c>
     </row>
     <row r="666">
@@ -30780,22 +30780,22 @@
         <v>0</v>
       </c>
       <c r="L685" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M685" t="n">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="N685" t="n">
         <v>753</v>
       </c>
       <c r="O685" t="n">
-        <v>125751</v>
+        <v>116715</v>
       </c>
       <c r="P685" t="n">
         <v>1600</v>
       </c>
       <c r="Q685" t="n">
-        <v>267200</v>
+        <v>248000</v>
       </c>
     </row>
     <row r="686">
@@ -33076,22 +33076,22 @@
         <v>0</v>
       </c>
       <c r="L735" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M735" t="n">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="N735" t="n">
         <v>1803.0149852941</v>
       </c>
       <c r="O735" t="n">
-        <v>192922.6034264687</v>
+        <v>171286.4236029395</v>
       </c>
       <c r="P735" t="n">
         <v>2500</v>
       </c>
       <c r="Q735" t="n">
-        <v>267500</v>
+        <v>237500</v>
       </c>
     </row>
     <row r="736">
@@ -33168,22 +33168,22 @@
         <v>0</v>
       </c>
       <c r="L737" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M737" t="n">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="N737" t="n">
         <v>2122.1641172932</v>
       </c>
       <c r="O737" t="n">
-        <v>148551.488210524</v>
+        <v>135818.5035067648</v>
       </c>
       <c r="P737" t="n">
         <v>2900</v>
       </c>
       <c r="Q737" t="n">
-        <v>203000</v>
+        <v>185600</v>
       </c>
     </row>
     <row r="738">
@@ -33808,22 +33808,22 @@
         <v>0</v>
       </c>
       <c r="L751" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M751" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="N751" t="n">
         <v>2311.9273755656</v>
       </c>
       <c r="O751" t="n">
-        <v>62422.0391402712</v>
+        <v>48550.4748868776</v>
       </c>
       <c r="P751" t="n">
         <v>3500</v>
       </c>
       <c r="Q751" t="n">
-        <v>94500</v>
+        <v>73500</v>
       </c>
     </row>
     <row r="752">
@@ -33854,22 +33854,22 @@
         <v>0</v>
       </c>
       <c r="L752" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M752" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="N752" t="n">
         <v>1906.1870703125</v>
       </c>
       <c r="O752" t="n">
-        <v>118183.598359375</v>
+        <v>106746.4759375</v>
       </c>
       <c r="P752" t="n">
         <v>2900</v>
       </c>
       <c r="Q752" t="n">
-        <v>179800</v>
+        <v>162400</v>
       </c>
     </row>
     <row r="753">
@@ -34217,22 +34217,22 @@
         <v>0</v>
       </c>
       <c r="L760" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M760" t="n">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="N760" t="n">
         <v>2556.7443828715</v>
       </c>
       <c r="O760" t="n">
-        <v>340047.0029219095</v>
+        <v>324706.5366246805</v>
       </c>
       <c r="P760" t="n">
         <v>3900</v>
       </c>
       <c r="Q760" t="n">
-        <v>518700</v>
+        <v>495300</v>
       </c>
     </row>
     <row r="761">
@@ -35428,22 +35428,22 @@
         <v>0</v>
       </c>
       <c r="L786" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M786" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="N786" t="n">
         <v>1530.4499204455</v>
       </c>
       <c r="O786" t="n">
-        <v>42852.597772474</v>
+        <v>33669.898249801</v>
       </c>
       <c r="P786" t="n">
         <v>2600</v>
       </c>
       <c r="Q786" t="n">
-        <v>72800</v>
+        <v>57200</v>
       </c>
     </row>
     <row r="787">
@@ -36071,22 +36071,22 @@
         <v>0</v>
       </c>
       <c r="L800" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M800" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="N800" t="n">
         <v>2312.96</v>
       </c>
       <c r="O800" t="n">
-        <v>101770.24</v>
+        <v>94831.36</v>
       </c>
       <c r="P800" t="n">
         <v>2500</v>
       </c>
       <c r="Q800" t="n">
-        <v>110000</v>
+        <v>102500</v>
       </c>
     </row>
     <row r="801">
@@ -36581,22 +36581,22 @@
         <v>0</v>
       </c>
       <c r="L811" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M811" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="N811" t="n">
         <v>2296.5708695652</v>
       </c>
       <c r="O811" t="n">
-        <v>119421.6852173904</v>
+        <v>105642.2599999992</v>
       </c>
       <c r="P811" t="n">
         <v>1900</v>
       </c>
       <c r="Q811" t="n">
-        <v>98800</v>
+        <v>87400</v>
       </c>
     </row>
     <row r="812">
@@ -38295,22 +38295,22 @@
         <v>0</v>
       </c>
       <c r="L848" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M848" t="n">
-        <v>1277</v>
+        <v>1229</v>
       </c>
       <c r="N848" t="n">
         <v>517.28747614462</v>
       </c>
       <c r="O848" t="n">
-        <v>660576.1070366798</v>
+        <v>635746.3081817379</v>
       </c>
       <c r="P848" t="n">
         <v>900</v>
       </c>
       <c r="Q848" t="n">
-        <v>1149300</v>
+        <v>1106100</v>
       </c>
     </row>
     <row r="849">
@@ -38995,22 +38995,22 @@
         <v>0</v>
       </c>
       <c r="L863" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M863" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="N863" t="n">
         <v>2000</v>
       </c>
       <c r="O863" t="n">
-        <v>158000</v>
+        <v>146000</v>
       </c>
       <c r="P863" t="n">
         <v>2000</v>
       </c>
       <c r="Q863" t="n">
-        <v>158000</v>
+        <v>146000</v>
       </c>
     </row>
     <row r="864">
@@ -39737,22 +39737,22 @@
         <v>0</v>
       </c>
       <c r="L879" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M879" t="n">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="N879" t="n">
         <v>3006.0208571429</v>
       </c>
       <c r="O879" t="n">
-        <v>414830.8782857202</v>
+        <v>396794.7531428628</v>
       </c>
       <c r="P879" t="n">
         <v>3900</v>
       </c>
       <c r="Q879" t="n">
-        <v>538200</v>
+        <v>514800</v>
       </c>
     </row>
     <row r="880">
@@ -40236,22 +40236,22 @@
         <v>0</v>
       </c>
       <c r="L890" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M890" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="N890" t="n">
         <v>1755.74</v>
       </c>
       <c r="O890" t="n">
-        <v>94809.96000000001</v>
+        <v>84275.52</v>
       </c>
       <c r="P890" t="n">
         <v>1500</v>
       </c>
       <c r="Q890" t="n">
-        <v>81000</v>
+        <v>72000</v>
       </c>
     </row>
     <row r="891">
@@ -43371,22 +43371,22 @@
         <v>0</v>
       </c>
       <c r="L955" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M955" t="n">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="N955" t="n">
         <v>3000.33</v>
       </c>
       <c r="O955" t="n">
-        <v>543059.73</v>
+        <v>525057.75</v>
       </c>
       <c r="P955" t="n">
         <v>2900</v>
       </c>
       <c r="Q955" t="n">
-        <v>524900</v>
+        <v>507500</v>
       </c>
     </row>
     <row r="956">
@@ -48982,22 +48982,22 @@
         <v>0</v>
       </c>
       <c r="L1074" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M1074" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="N1074" t="n">
         <v>1213.6821153846</v>
       </c>
       <c r="O1074" t="n">
-        <v>27914.6886538458</v>
+        <v>20632.5959615382</v>
       </c>
       <c r="P1074" t="n">
         <v>1500</v>
       </c>
       <c r="Q1074" t="n">
-        <v>34500</v>
+        <v>25500</v>
       </c>
     </row>
     <row r="1075">
@@ -49674,22 +49674,22 @@
         <v>0</v>
       </c>
       <c r="L1089" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M1089" t="n">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="N1089" t="n">
         <v>1757.320515873</v>
       </c>
       <c r="O1089" t="n">
-        <v>100167.269404761</v>
+        <v>89623.346309523</v>
       </c>
       <c r="P1089" t="n">
         <v>2000</v>
       </c>
       <c r="Q1089" t="n">
-        <v>114000</v>
+        <v>102000</v>
       </c>
     </row>
     <row r="1090">
@@ -49720,22 +49720,22 @@
         <v>0</v>
       </c>
       <c r="L1090" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M1090" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="N1090" t="n">
         <v>1561.33</v>
       </c>
       <c r="O1090" t="n">
-        <v>56207.88</v>
+        <v>46839.89999999999</v>
       </c>
       <c r="P1090" t="n">
         <v>2000</v>
       </c>
       <c r="Q1090" t="n">
-        <v>72000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="1091">
@@ -55048,22 +55048,22 @@
         <v>0</v>
       </c>
       <c r="L1205" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M1205" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N1205" t="n">
         <v>3306.0098310139</v>
       </c>
       <c r="O1205" t="n">
-        <v>82650.2457753475</v>
+        <v>62814.1867892641</v>
       </c>
       <c r="P1205" t="n">
         <v>4200</v>
       </c>
       <c r="Q1205" t="n">
-        <v>105000</v>
+        <v>79800</v>
       </c>
     </row>
     <row r="1206">
@@ -57709,22 +57709,22 @@
         <v>0</v>
       </c>
       <c r="L1263" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M1263" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="N1263" t="n">
         <v>12720</v>
       </c>
       <c r="O1263" t="n">
-        <v>165360</v>
+        <v>127200</v>
       </c>
       <c r="P1263" t="n">
         <v>15900</v>
       </c>
       <c r="Q1263" t="n">
-        <v>206700</v>
+        <v>159000</v>
       </c>
     </row>
     <row r="1264">

--- a/bodegas/LJ-101.xlsx
+++ b/bodegas/LJ-101.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-09</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-10</t>
         </is>
       </c>
     </row>
@@ -7865,22 +7865,22 @@
         <v>0</v>
       </c>
       <c r="L175" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M175" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="N175" t="n">
         <v>1726.32</v>
       </c>
       <c r="O175" t="n">
-        <v>27621.12</v>
+        <v>17263.2</v>
       </c>
       <c r="P175" t="n">
         <v>1500</v>
       </c>
       <c r="Q175" t="n">
-        <v>24000</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="176">
@@ -8247,22 +8247,22 @@
         <v>0</v>
       </c>
       <c r="L184" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M184" t="n">
-        <v>410</v>
+        <v>398</v>
       </c>
       <c r="N184" t="n">
         <v>1098.0529624405</v>
       </c>
       <c r="O184" t="n">
-        <v>450201.714600605</v>
+        <v>437025.079051319</v>
       </c>
       <c r="P184" t="n">
         <v>1500</v>
       </c>
       <c r="Q184" t="n">
-        <v>615000</v>
+        <v>597000</v>
       </c>
     </row>
     <row r="185">
@@ -9495,22 +9495,22 @@
         <v>0</v>
       </c>
       <c r="L212" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M212" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="N212" t="n">
         <v>2033.5756109726</v>
       </c>
       <c r="O212" t="n">
-        <v>56940.1171072328</v>
+        <v>8134.3024438904</v>
       </c>
       <c r="P212" t="n">
         <v>4100</v>
       </c>
       <c r="Q212" t="n">
-        <v>114800</v>
+        <v>16400</v>
       </c>
     </row>
     <row r="213">
@@ -10087,22 +10087,22 @@
         <v>0</v>
       </c>
       <c r="L225" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M225" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="N225" t="n">
         <v>2341</v>
       </c>
       <c r="O225" t="n">
-        <v>49161</v>
+        <v>39797</v>
       </c>
       <c r="P225" t="n">
         <v>3900</v>
       </c>
       <c r="Q225" t="n">
-        <v>81900</v>
+        <v>66300</v>
       </c>
     </row>
     <row r="226">
@@ -10271,22 +10271,22 @@
         <v>0</v>
       </c>
       <c r="L229" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M229" t="n">
-        <v>1172</v>
+        <v>1072</v>
       </c>
       <c r="N229" t="n">
         <v>156.25</v>
       </c>
       <c r="O229" t="n">
-        <v>183125</v>
+        <v>167500</v>
       </c>
       <c r="P229" t="n">
         <v>250</v>
       </c>
       <c r="Q229" t="n">
-        <v>293000</v>
+        <v>268000</v>
       </c>
     </row>
     <row r="230">
@@ -10317,22 +10317,22 @@
         <v>0</v>
       </c>
       <c r="L230" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M230" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="N230" t="n">
         <v>7507.39</v>
       </c>
       <c r="O230" t="n">
-        <v>300295.6</v>
+        <v>285280.82</v>
       </c>
       <c r="P230" t="n">
         <v>13500</v>
       </c>
       <c r="Q230" t="n">
-        <v>540000</v>
+        <v>513000</v>
       </c>
     </row>
     <row r="231">
@@ -10366,22 +10366,22 @@
         <v>0</v>
       </c>
       <c r="L231" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M231" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="N231" t="n">
         <v>8796</v>
       </c>
       <c r="O231" t="n">
-        <v>466188</v>
+        <v>448596</v>
       </c>
       <c r="P231" t="n">
         <v>14900</v>
       </c>
       <c r="Q231" t="n">
-        <v>789700</v>
+        <v>759900</v>
       </c>
     </row>
     <row r="232">
@@ -11636,22 +11636,22 @@
         <v>0</v>
       </c>
       <c r="L259" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M259" t="n">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="N259" t="n">
         <v>489.88</v>
       </c>
       <c r="O259" t="n">
-        <v>151862.8</v>
+        <v>146964</v>
       </c>
       <c r="P259" t="n">
         <v>700</v>
       </c>
       <c r="Q259" t="n">
-        <v>217000</v>
+        <v>210000</v>
       </c>
     </row>
     <row r="260">
@@ -12036,22 +12036,22 @@
         <v>0</v>
       </c>
       <c r="L268" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M268" t="n">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="N268" t="n">
         <v>2090.85</v>
       </c>
       <c r="O268" t="n">
-        <v>432805.95</v>
+        <v>395170.65</v>
       </c>
       <c r="P268" t="n">
         <v>2900</v>
       </c>
       <c r="Q268" t="n">
-        <v>600300</v>
+        <v>548100</v>
       </c>
     </row>
     <row r="269">
@@ -12255,22 +12255,22 @@
         <v>0</v>
       </c>
       <c r="L273" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M273" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="N273" t="n">
         <v>2769.98</v>
       </c>
       <c r="O273" t="n">
-        <v>80329.42</v>
+        <v>63709.54</v>
       </c>
       <c r="P273" t="n">
         <v>3500</v>
       </c>
       <c r="Q273" t="n">
-        <v>101500</v>
+        <v>80500</v>
       </c>
     </row>
     <row r="274">
@@ -13198,22 +13198,22 @@
         <v>0</v>
       </c>
       <c r="L294" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M294" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="N294" t="n">
         <v>1121.98</v>
       </c>
       <c r="O294" t="n">
-        <v>10097.82</v>
+        <v>6731.88</v>
       </c>
       <c r="P294" t="n">
         <v>2400</v>
       </c>
       <c r="Q294" t="n">
-        <v>21600</v>
+        <v>14400</v>
       </c>
     </row>
     <row r="295">
@@ -13244,22 +13244,22 @@
         <v>0</v>
       </c>
       <c r="L295" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M295" t="n">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="N295" t="n">
         <v>1592.5677332171</v>
       </c>
       <c r="O295" t="n">
-        <v>136960.8250566706</v>
+        <v>98739.1994594602</v>
       </c>
       <c r="P295" t="n">
         <v>3900</v>
       </c>
       <c r="Q295" t="n">
-        <v>335400</v>
+        <v>241800</v>
       </c>
     </row>
     <row r="296">
@@ -13778,22 +13778,22 @@
         <v>0</v>
       </c>
       <c r="L307" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M307" t="n">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="N307" t="n">
         <v>1770.37</v>
       </c>
       <c r="O307" t="n">
-        <v>157562.93</v>
+        <v>146940.71</v>
       </c>
       <c r="P307" t="n">
         <v>3900</v>
       </c>
       <c r="Q307" t="n">
-        <v>347100</v>
+        <v>323700</v>
       </c>
     </row>
     <row r="308">
@@ -14505,22 +14505,22 @@
         <v>0</v>
       </c>
       <c r="L323" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M323" t="n">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="N323" t="n">
         <v>1200</v>
       </c>
       <c r="O323" t="n">
-        <v>349200</v>
+        <v>342000</v>
       </c>
       <c r="P323" t="n">
         <v>1500</v>
       </c>
       <c r="Q323" t="n">
-        <v>436500</v>
+        <v>427500</v>
       </c>
     </row>
     <row r="324">
@@ -15427,22 +15427,22 @@
         <v>0</v>
       </c>
       <c r="L343" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M343" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="N343" t="n">
         <v>1630.9230192383</v>
       </c>
       <c r="O343" t="n">
-        <v>140259.3796544938</v>
+        <v>130473.841539064</v>
       </c>
       <c r="P343" t="n">
         <v>2500</v>
       </c>
       <c r="Q343" t="n">
-        <v>215000</v>
+        <v>200000</v>
       </c>
     </row>
     <row r="344">
@@ -15657,22 +15657,22 @@
         <v>0</v>
       </c>
       <c r="L348" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M348" t="n">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="N348" t="n">
         <v>2403.5100306848</v>
       </c>
       <c r="O348" t="n">
-        <v>870070.6311078975</v>
+        <v>862860.1010158431</v>
       </c>
       <c r="P348" t="n">
         <v>3500</v>
       </c>
       <c r="Q348" t="n">
-        <v>1267000</v>
+        <v>1256500</v>
       </c>
     </row>
     <row r="349">
@@ -15703,22 +15703,22 @@
         <v>0</v>
       </c>
       <c r="L349" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M349" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="N349" t="n">
         <v>2521.5479047619</v>
       </c>
       <c r="O349" t="n">
-        <v>272327.1737142852</v>
+        <v>264762.5299999995</v>
       </c>
       <c r="P349" t="n">
         <v>3900</v>
       </c>
       <c r="Q349" t="n">
-        <v>421200</v>
+        <v>409500</v>
       </c>
     </row>
     <row r="350">
@@ -18162,22 +18162,22 @@
         <v>0</v>
       </c>
       <c r="L404" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M404" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="N404" t="n">
         <v>9338</v>
       </c>
       <c r="O404" t="n">
-        <v>224112</v>
+        <v>205436</v>
       </c>
       <c r="P404" t="n">
         <v>15500</v>
       </c>
       <c r="Q404" t="n">
-        <v>372000</v>
+        <v>341000</v>
       </c>
     </row>
     <row r="405">
@@ -19584,22 +19584,22 @@
         <v>0</v>
       </c>
       <c r="L438" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M438" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N438" t="n">
         <v>14371.45</v>
       </c>
       <c r="O438" t="n">
-        <v>229943.2</v>
+        <v>215571.75</v>
       </c>
       <c r="P438" t="n">
         <v>23300</v>
       </c>
       <c r="Q438" t="n">
-        <v>372800</v>
+        <v>349500</v>
       </c>
     </row>
     <row r="439">
@@ -20752,22 +20752,22 @@
         <v>0</v>
       </c>
       <c r="L465" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M465" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N465" t="n">
         <v>15700</v>
       </c>
       <c r="O465" t="n">
-        <v>78500</v>
+        <v>62800</v>
       </c>
       <c r="P465" t="n">
         <v>29900</v>
       </c>
       <c r="Q465" t="n">
-        <v>149500</v>
+        <v>119600</v>
       </c>
     </row>
     <row r="466">
@@ -20972,22 +20972,22 @@
         <v>0</v>
       </c>
       <c r="L470" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M470" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N470" t="n">
         <v>22730.48</v>
       </c>
       <c r="O470" t="n">
-        <v>386418.16</v>
+        <v>363687.68</v>
       </c>
       <c r="P470" t="n">
         <v>36900</v>
       </c>
       <c r="Q470" t="n">
-        <v>627300</v>
+        <v>590400</v>
       </c>
     </row>
     <row r="471">
@@ -21233,22 +21233,22 @@
         <v>0</v>
       </c>
       <c r="L476" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M476" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="N476" t="n">
         <v>16974.69</v>
       </c>
       <c r="O476" t="n">
-        <v>645038.22</v>
+        <v>611088.84</v>
       </c>
       <c r="P476" t="n">
         <v>26900</v>
       </c>
       <c r="Q476" t="n">
-        <v>1022200</v>
+        <v>968400</v>
       </c>
     </row>
     <row r="477">
@@ -21407,22 +21407,22 @@
         <v>0</v>
       </c>
       <c r="L480" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M480" t="n">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="N480" t="n">
         <v>1560.9988178914</v>
       </c>
       <c r="O480" t="n">
-        <v>121757.9077955292</v>
+        <v>74927.9432587872</v>
       </c>
       <c r="P480" t="n">
         <v>2900</v>
       </c>
       <c r="Q480" t="n">
-        <v>226200</v>
+        <v>139200</v>
       </c>
     </row>
     <row r="481">
@@ -24159,22 +24159,22 @@
         <v>0</v>
       </c>
       <c r="L542" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M542" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="N542" t="n">
         <v>3254.49</v>
       </c>
       <c r="O542" t="n">
-        <v>149706.54</v>
+        <v>133434.09</v>
       </c>
       <c r="P542" t="n">
         <v>5200</v>
       </c>
       <c r="Q542" t="n">
-        <v>239200</v>
+        <v>213200</v>
       </c>
     </row>
     <row r="543">
@@ -26435,22 +26435,22 @@
         <v>0</v>
       </c>
       <c r="L591" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M591" t="n">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="N591" t="n">
         <v>1817</v>
       </c>
       <c r="O591" t="n">
-        <v>205321</v>
+        <v>194419</v>
       </c>
       <c r="P591" t="n">
         <v>3100</v>
       </c>
       <c r="Q591" t="n">
-        <v>350300</v>
+        <v>331700</v>
       </c>
     </row>
     <row r="592">
@@ -27877,22 +27877,22 @@
         <v>0</v>
       </c>
       <c r="L622" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M622" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N622" t="n">
         <v>17644.653166667</v>
       </c>
       <c r="O622" t="n">
-        <v>35289.306333334</v>
+        <v>0</v>
       </c>
       <c r="P622" t="n">
         <v>28200</v>
       </c>
       <c r="Q622" t="n">
-        <v>56400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="623">
@@ -29810,22 +29810,22 @@
         <v>0</v>
       </c>
       <c r="L664" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M664" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N664" t="n">
         <v>9839</v>
       </c>
       <c r="O664" t="n">
-        <v>19678</v>
+        <v>0</v>
       </c>
       <c r="P664" t="n">
         <v>16900</v>
       </c>
       <c r="Q664" t="n">
-        <v>33800</v>
+        <v>0</v>
       </c>
     </row>
     <row r="665">
@@ -30638,22 +30638,22 @@
         <v>0</v>
       </c>
       <c r="L682" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M682" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N682" t="n">
         <v>23439</v>
       </c>
       <c r="O682" t="n">
-        <v>421902</v>
+        <v>398463</v>
       </c>
       <c r="P682" t="n">
         <v>37900</v>
       </c>
       <c r="Q682" t="n">
-        <v>682200</v>
+        <v>644300</v>
       </c>
     </row>
     <row r="683">
@@ -30684,22 +30684,22 @@
         <v>0</v>
       </c>
       <c r="L683" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M683" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="N683" t="n">
         <v>19008</v>
       </c>
       <c r="O683" t="n">
-        <v>608256</v>
+        <v>589248</v>
       </c>
       <c r="P683" t="n">
         <v>30900</v>
       </c>
       <c r="Q683" t="n">
-        <v>988800</v>
+        <v>957900</v>
       </c>
     </row>
     <row r="684">
@@ -30733,22 +30733,22 @@
         <v>0</v>
       </c>
       <c r="L684" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M684" t="n">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="N684" t="n">
         <v>753</v>
       </c>
       <c r="O684" t="n">
-        <v>105420</v>
+        <v>96384</v>
       </c>
       <c r="P684" t="n">
         <v>1600</v>
       </c>
       <c r="Q684" t="n">
-        <v>224000</v>
+        <v>204800</v>
       </c>
     </row>
     <row r="685">
@@ -30871,22 +30871,22 @@
         <v>0</v>
       </c>
       <c r="L687" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M687" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N687" t="n">
         <v>12211</v>
       </c>
       <c r="O687" t="n">
-        <v>36633</v>
+        <v>12211</v>
       </c>
       <c r="P687" t="n">
         <v>19900</v>
       </c>
       <c r="Q687" t="n">
-        <v>59700</v>
+        <v>19900</v>
       </c>
     </row>
     <row r="688">
@@ -32709,22 +32709,22 @@
         <v>0</v>
       </c>
       <c r="L727" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M727" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="N727" t="n">
         <v>1516.0388137227</v>
       </c>
       <c r="O727" t="n">
-        <v>42449.0867842356</v>
+        <v>37900.9703430675</v>
       </c>
       <c r="P727" t="n">
         <v>2300</v>
       </c>
       <c r="Q727" t="n">
-        <v>64400</v>
+        <v>57500</v>
       </c>
     </row>
     <row r="728">
@@ -33029,22 +33029,22 @@
         <v>0</v>
       </c>
       <c r="L734" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M734" t="n">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="N734" t="n">
         <v>1803.0149867608</v>
       </c>
       <c r="O734" t="n">
-        <v>192922.6035834056</v>
+        <v>171286.423742276</v>
       </c>
       <c r="P734" t="n">
         <v>2500</v>
       </c>
       <c r="Q734" t="n">
-        <v>267500</v>
+        <v>237500</v>
       </c>
     </row>
     <row r="735">
@@ -33121,22 +33121,22 @@
         <v>0</v>
       </c>
       <c r="L736" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M736" t="n">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="N736" t="n">
         <v>2122.1641172932</v>
       </c>
       <c r="O736" t="n">
-        <v>148551.488210524</v>
+        <v>135818.5035067648</v>
       </c>
       <c r="P736" t="n">
         <v>2900</v>
       </c>
       <c r="Q736" t="n">
-        <v>203000</v>
+        <v>185600</v>
       </c>
     </row>
     <row r="737">
@@ -33761,22 +33761,22 @@
         <v>0</v>
       </c>
       <c r="L750" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M750" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="N750" t="n">
         <v>2311.9269828927</v>
       </c>
       <c r="O750" t="n">
-        <v>62422.0285381029</v>
+        <v>41614.6856920686</v>
       </c>
       <c r="P750" t="n">
         <v>3500</v>
       </c>
       <c r="Q750" t="n">
-        <v>94500</v>
+        <v>63000</v>
       </c>
     </row>
     <row r="751">
@@ -33807,22 +33807,22 @@
         <v>0</v>
       </c>
       <c r="L751" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M751" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="N751" t="n">
         <v>1906.1869325153</v>
       </c>
       <c r="O751" t="n">
-        <v>118183.5898159486</v>
+        <v>106746.4682208568</v>
       </c>
       <c r="P751" t="n">
         <v>2900</v>
       </c>
       <c r="Q751" t="n">
-        <v>179800</v>
+        <v>162400</v>
       </c>
     </row>
     <row r="752">
@@ -33945,22 +33945,22 @@
         <v>0</v>
       </c>
       <c r="L754" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M754" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="N754" t="n">
         <v>1668.6155910543</v>
       </c>
       <c r="O754" t="n">
-        <v>175204.6370607015</v>
+        <v>170198.7902875386</v>
       </c>
       <c r="P754" t="n">
         <v>2500</v>
       </c>
       <c r="Q754" t="n">
-        <v>262500</v>
+        <v>255000</v>
       </c>
     </row>
     <row r="755">
@@ -34037,22 +34037,22 @@
         <v>0</v>
       </c>
       <c r="L756" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M756" t="n">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="N756" t="n">
         <v>1259.2744102228</v>
       </c>
       <c r="O756" t="n">
-        <v>196446.8079947568</v>
+        <v>188891.16153342</v>
       </c>
       <c r="P756" t="n">
         <v>1900</v>
       </c>
       <c r="Q756" t="n">
-        <v>296400</v>
+        <v>285000</v>
       </c>
     </row>
     <row r="757">
@@ -34216,22 +34216,22 @@
         <v>0</v>
       </c>
       <c r="L760" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M760" t="n">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="N760" t="n">
         <v>2556.7444501279</v>
       </c>
       <c r="O760" t="n">
-        <v>340047.0118670107</v>
+        <v>324706.5451662433</v>
       </c>
       <c r="P760" t="n">
         <v>3900</v>
       </c>
       <c r="Q760" t="n">
-        <v>518700</v>
+        <v>495300</v>
       </c>
     </row>
     <row r="761">
@@ -34353,22 +34353,22 @@
         <v>0</v>
       </c>
       <c r="L763" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M763" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N763" t="n">
         <v>18491</v>
       </c>
       <c r="O763" t="n">
-        <v>55473</v>
+        <v>18491</v>
       </c>
       <c r="P763" t="n">
         <v>13500</v>
       </c>
       <c r="Q763" t="n">
-        <v>40500</v>
+        <v>13500</v>
       </c>
     </row>
     <row r="764">
@@ -35427,22 +35427,22 @@
         <v>0</v>
       </c>
       <c r="L786" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M786" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="N786" t="n">
         <v>1530.4499204455</v>
       </c>
       <c r="O786" t="n">
-        <v>42852.597772474</v>
+        <v>33669.898249801</v>
       </c>
       <c r="P786" t="n">
         <v>2600</v>
       </c>
       <c r="Q786" t="n">
-        <v>72800</v>
+        <v>57200</v>
       </c>
     </row>
     <row r="787">
@@ -36070,22 +36070,22 @@
         <v>0</v>
       </c>
       <c r="L800" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M800" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="N800" t="n">
         <v>2312.96</v>
       </c>
       <c r="O800" t="n">
-        <v>101770.24</v>
+        <v>94831.36</v>
       </c>
       <c r="P800" t="n">
         <v>2500</v>
       </c>
       <c r="Q800" t="n">
-        <v>110000</v>
+        <v>102500</v>
       </c>
     </row>
     <row r="801">
@@ -36580,22 +36580,22 @@
         <v>0</v>
       </c>
       <c r="L811" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M811" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="N811" t="n">
         <v>2296.5708695652</v>
       </c>
       <c r="O811" t="n">
-        <v>119421.6852173904</v>
+        <v>105642.2599999992</v>
       </c>
       <c r="P811" t="n">
         <v>1900</v>
       </c>
       <c r="Q811" t="n">
-        <v>98800</v>
+        <v>87400</v>
       </c>
     </row>
     <row r="812">
@@ -37569,22 +37569,22 @@
         <v>0</v>
       </c>
       <c r="L832" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M832" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N832" t="n">
         <v>6213.51</v>
       </c>
       <c r="O832" t="n">
-        <v>12427.02</v>
+        <v>0</v>
       </c>
       <c r="P832" t="n">
         <v>10300</v>
       </c>
       <c r="Q832" t="n">
-        <v>20600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="833">
@@ -38245,22 +38245,22 @@
         <v>0</v>
       </c>
       <c r="L847" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M847" t="n">
-        <v>1206</v>
+        <v>1146</v>
       </c>
       <c r="N847" t="n">
         <v>517.28760395334</v>
       </c>
       <c r="O847" t="n">
-        <v>623848.850367728</v>
+        <v>592811.5941305276</v>
       </c>
       <c r="P847" t="n">
         <v>900</v>
       </c>
       <c r="Q847" t="n">
-        <v>1085400</v>
+        <v>1031400</v>
       </c>
     </row>
     <row r="848">
@@ -38945,22 +38945,22 @@
         <v>0</v>
       </c>
       <c r="L862" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M862" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="N862" t="n">
         <v>2000</v>
       </c>
       <c r="O862" t="n">
-        <v>158000</v>
+        <v>146000</v>
       </c>
       <c r="P862" t="n">
         <v>2000</v>
       </c>
       <c r="Q862" t="n">
-        <v>158000</v>
+        <v>146000</v>
       </c>
     </row>
     <row r="863">
@@ -39218,22 +39218,22 @@
         <v>0</v>
       </c>
       <c r="L868" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M868" t="n">
-        <v>300</v>
+        <v>276</v>
       </c>
       <c r="N868" t="n">
         <v>703.79543678174</v>
       </c>
       <c r="O868" t="n">
-        <v>211138.631034522</v>
+        <v>194247.5405517602</v>
       </c>
       <c r="P868" t="n">
         <v>900</v>
       </c>
       <c r="Q868" t="n">
-        <v>270000</v>
+        <v>248400</v>
       </c>
     </row>
     <row r="869">
@@ -39687,22 +39687,22 @@
         <v>0</v>
       </c>
       <c r="L878" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M878" t="n">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="N878" t="n">
         <v>3006.0208571429</v>
       </c>
       <c r="O878" t="n">
-        <v>414830.8782857202</v>
+        <v>396794.7531428628</v>
       </c>
       <c r="P878" t="n">
         <v>3900</v>
       </c>
       <c r="Q878" t="n">
-        <v>538200</v>
+        <v>514800</v>
       </c>
     </row>
     <row r="879">
@@ -40186,22 +40186,22 @@
         <v>0</v>
       </c>
       <c r="L889" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M889" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="N889" t="n">
         <v>1755.74</v>
       </c>
       <c r="O889" t="n">
-        <v>94809.96000000001</v>
+        <v>84275.52</v>
       </c>
       <c r="P889" t="n">
         <v>1500</v>
       </c>
       <c r="Q889" t="n">
-        <v>81000</v>
+        <v>72000</v>
       </c>
     </row>
     <row r="890">
@@ -43321,22 +43321,22 @@
         <v>0</v>
       </c>
       <c r="L954" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M954" t="n">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="N954" t="n">
         <v>3000.33</v>
       </c>
       <c r="O954" t="n">
-        <v>543059.73</v>
+        <v>525057.75</v>
       </c>
       <c r="P954" t="n">
         <v>2900</v>
       </c>
       <c r="Q954" t="n">
-        <v>524900</v>
+        <v>507500</v>
       </c>
     </row>
     <row r="955">
@@ -45327,22 +45327,22 @@
         <v>0</v>
       </c>
       <c r="L996" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M996" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N996" t="n">
         <v>9372</v>
       </c>
       <c r="O996" t="n">
-        <v>46860</v>
+        <v>28116</v>
       </c>
       <c r="P996" t="n">
         <v>17900</v>
       </c>
       <c r="Q996" t="n">
-        <v>89500</v>
+        <v>53700</v>
       </c>
     </row>
     <row r="997">
@@ -47339,22 +47339,22 @@
         <v>0</v>
       </c>
       <c r="L1038" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M1038" t="n">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="N1038" t="n">
         <v>665.32330236486</v>
       </c>
       <c r="O1038" t="n">
-        <v>184959.8780574311</v>
+        <v>180967.9382432419</v>
       </c>
       <c r="P1038" t="n">
         <v>2900</v>
       </c>
       <c r="Q1038" t="n">
-        <v>806200</v>
+        <v>788800</v>
       </c>
     </row>
     <row r="1039">
@@ -48932,22 +48932,22 @@
         <v>0</v>
       </c>
       <c r="L1073" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M1073" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="N1073" t="n">
         <v>1213.6821194605</v>
       </c>
       <c r="O1073" t="n">
-        <v>26701.006628131</v>
+        <v>19418.913911368</v>
       </c>
       <c r="P1073" t="n">
         <v>1500</v>
       </c>
       <c r="Q1073" t="n">
-        <v>33000</v>
+        <v>24000</v>
       </c>
     </row>
     <row r="1074">
@@ -49624,22 +49624,22 @@
         <v>0</v>
       </c>
       <c r="L1088" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M1088" t="n">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="N1088" t="n">
         <v>1757.3205179283</v>
       </c>
       <c r="O1088" t="n">
-        <v>100167.2695219131</v>
+        <v>89623.34641434329</v>
       </c>
       <c r="P1088" t="n">
         <v>2000</v>
       </c>
       <c r="Q1088" t="n">
-        <v>114000</v>
+        <v>102000</v>
       </c>
     </row>
     <row r="1089">
@@ -49670,22 +49670,22 @@
         <v>0</v>
       </c>
       <c r="L1089" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M1089" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="N1089" t="n">
         <v>1561.33</v>
       </c>
       <c r="O1089" t="n">
-        <v>56207.88</v>
+        <v>46839.89999999999</v>
       </c>
       <c r="P1089" t="n">
         <v>2000</v>
       </c>
       <c r="Q1089" t="n">
-        <v>72000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="1090">
@@ -52019,22 +52019,22 @@
         <v>0</v>
       </c>
       <c r="L1140" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M1140" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="N1140" t="n">
         <v>7740</v>
       </c>
       <c r="O1140" t="n">
-        <v>472140</v>
+        <v>448920</v>
       </c>
       <c r="P1140" t="n">
         <v>9500</v>
       </c>
       <c r="Q1140" t="n">
-        <v>579500</v>
+        <v>551000</v>
       </c>
     </row>
     <row r="1141">
@@ -52341,22 +52341,22 @@
         <v>0</v>
       </c>
       <c r="L1147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1147" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N1147" t="n">
         <v>25000</v>
       </c>
       <c r="O1147" t="n">
-        <v>250000</v>
+        <v>225000</v>
       </c>
       <c r="P1147" t="n">
         <v>30000</v>
       </c>
       <c r="Q1147" t="n">
-        <v>300000</v>
+        <v>270000</v>
       </c>
     </row>
     <row r="1148">
@@ -54998,22 +54998,22 @@
         <v>0</v>
       </c>
       <c r="L1204" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M1204" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N1204" t="n">
         <v>3306.0098310139</v>
       </c>
       <c r="O1204" t="n">
-        <v>82650.2457753475</v>
+        <v>62814.1867892641</v>
       </c>
       <c r="P1204" t="n">
         <v>4200</v>
       </c>
       <c r="Q1204" t="n">
-        <v>105000</v>
+        <v>79800</v>
       </c>
     </row>
     <row r="1205">
@@ -57659,22 +57659,22 @@
         <v>0</v>
       </c>
       <c r="L1262" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M1262" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="N1262" t="n">
         <v>12720</v>
       </c>
       <c r="O1262" t="n">
-        <v>165360</v>
+        <v>127200</v>
       </c>
       <c r="P1262" t="n">
         <v>15900</v>
       </c>
       <c r="Q1262" t="n">
-        <v>206700</v>
+        <v>159000</v>
       </c>
     </row>
     <row r="1263">

--- a/bodegas/LJ-101.xlsx
+++ b/bodegas/LJ-101.xlsx
@@ -938,22 +938,22 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M13" t="n">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="N13" t="n">
-        <v>1811.3041548631</v>
+        <v>1811.3043052838</v>
       </c>
       <c r="O13" t="n">
-        <v>128602.5949952801</v>
+        <v>101433.0410958928</v>
       </c>
       <c r="P13" t="n">
         <v>2600</v>
       </c>
       <c r="Q13" t="n">
-        <v>184600</v>
+        <v>145600</v>
       </c>
     </row>
     <row r="14">
@@ -1022,10 +1022,10 @@
         <v>50</v>
       </c>
       <c r="N15" t="n">
-        <v>3376.7465109371</v>
+        <v>3376.7465014893</v>
       </c>
       <c r="O15" t="n">
-        <v>168837.325546855</v>
+        <v>168837.325074465</v>
       </c>
       <c r="P15" t="n">
         <v>4500</v>
@@ -1698,22 +1698,22 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N32" t="n">
         <v>2445.67</v>
       </c>
       <c r="O32" t="n">
-        <v>53804.74000000001</v>
+        <v>51359.07</v>
       </c>
       <c r="P32" t="n">
         <v>4600</v>
       </c>
       <c r="Q32" t="n">
-        <v>101200</v>
+        <v>96600</v>
       </c>
     </row>
     <row r="33">
@@ -2027,10 +2027,10 @@
         <v>11</v>
       </c>
       <c r="N40" t="n">
-        <v>2413.0010330579</v>
+        <v>2413.001059322</v>
       </c>
       <c r="O40" t="n">
-        <v>26543.0113636369</v>
+        <v>26543.011652542</v>
       </c>
       <c r="P40" t="n">
         <v>4700</v>
@@ -2456,10 +2456,10 @@
         <v>9</v>
       </c>
       <c r="N51" t="n">
-        <v>14857.623171806</v>
+        <v>14857.623185841</v>
       </c>
       <c r="O51" t="n">
-        <v>133718.608546254</v>
+        <v>133718.608672569</v>
       </c>
       <c r="P51" t="n">
         <v>34900</v>
@@ -3576,22 +3576,22 @@
         <v>0</v>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M76" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="N76" t="n">
-        <v>17085.59</v>
+        <v>17085.54</v>
       </c>
       <c r="O76" t="n">
-        <v>205027.08</v>
+        <v>136684.32</v>
       </c>
       <c r="P76" t="n">
         <v>29200</v>
       </c>
       <c r="Q76" t="n">
-        <v>350400</v>
+        <v>233600</v>
       </c>
     </row>
     <row r="77">
@@ -3618,22 +3618,22 @@
         <v>0</v>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M77" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N77" t="n">
-        <v>5059.5844444444</v>
+        <v>5059.58125</v>
       </c>
       <c r="O77" t="n">
-        <v>20238.3377777776</v>
+        <v>15178.74375</v>
       </c>
       <c r="P77" t="n">
         <v>10000</v>
       </c>
       <c r="Q77" t="n">
-        <v>40000</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="78">
@@ -3699,22 +3699,22 @@
         <v>0</v>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M79" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N79" t="n">
         <v>36762.36</v>
       </c>
       <c r="O79" t="n">
-        <v>698484.84</v>
+        <v>624960.12</v>
       </c>
       <c r="P79" t="n">
         <v>57100</v>
       </c>
       <c r="Q79" t="n">
-        <v>1084900</v>
+        <v>970700</v>
       </c>
     </row>
     <row r="80">
@@ -3741,22 +3741,22 @@
         <v>0</v>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M80" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N80" t="n">
-        <v>15711.966106557</v>
+        <v>15711.966058091</v>
       </c>
       <c r="O80" t="n">
-        <v>188543.593278684</v>
+        <v>157119.66058091</v>
       </c>
       <c r="P80" t="n">
         <v>28500</v>
       </c>
       <c r="Q80" t="n">
-        <v>342000</v>
+        <v>285000</v>
       </c>
     </row>
     <row r="81">
@@ -3788,22 +3788,22 @@
         <v>0</v>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M81" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N81" t="n">
-        <v>9392.0745945946</v>
+        <v>9392.0746575342</v>
       </c>
       <c r="O81" t="n">
-        <v>178449.4172972974</v>
+        <v>169057.3438356156</v>
       </c>
       <c r="P81" t="n">
         <v>18500</v>
       </c>
       <c r="Q81" t="n">
-        <v>351500</v>
+        <v>333000</v>
       </c>
     </row>
     <row r="82">
@@ -4562,10 +4562,10 @@
         <v>3</v>
       </c>
       <c r="N99" t="n">
-        <v>56906.800571429</v>
+        <v>56906.801935484</v>
       </c>
       <c r="O99" t="n">
-        <v>170720.401714287</v>
+        <v>170720.405806452</v>
       </c>
       <c r="P99" t="n">
         <v>95900</v>
@@ -4656,10 +4656,10 @@
         <v>6</v>
       </c>
       <c r="N101" t="n">
-        <v>141416.88453074</v>
+        <v>141416.88454545</v>
       </c>
       <c r="O101" t="n">
-        <v>848501.3071844401</v>
+        <v>848501.3072727001</v>
       </c>
       <c r="P101" t="n">
         <v>251900</v>
@@ -4978,22 +4978,22 @@
         <v>0</v>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M109" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="N109" t="n">
         <v>15780</v>
       </c>
       <c r="O109" t="n">
-        <v>220920</v>
+        <v>94680</v>
       </c>
       <c r="P109" t="n">
         <v>21900</v>
       </c>
       <c r="Q109" t="n">
-        <v>306600</v>
+        <v>131400</v>
       </c>
     </row>
     <row r="110">
@@ -5101,10 +5101,10 @@
         <v>1</v>
       </c>
       <c r="N112" t="n">
-        <v>61666.873861893</v>
+        <v>61666.873932292</v>
       </c>
       <c r="O112" t="n">
-        <v>61666.873861893</v>
+        <v>61666.873932292</v>
       </c>
       <c r="P112" t="n">
         <v>98900</v>
@@ -5185,22 +5185,22 @@
         <v>0</v>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M114" t="n">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="N114" t="n">
-        <v>408.26623529412</v>
+        <v>408.26614457831</v>
       </c>
       <c r="O114" t="n">
-        <v>66547.39635294156</v>
+        <v>64914.31698795129</v>
       </c>
       <c r="P114" t="n">
         <v>1600</v>
       </c>
       <c r="Q114" t="n">
-        <v>260800</v>
+        <v>254400</v>
       </c>
     </row>
     <row r="115">
@@ -5643,10 +5643,10 @@
         <v>6</v>
       </c>
       <c r="N124" t="n">
-        <v>427.91890410959</v>
+        <v>430.87006896552</v>
       </c>
       <c r="O124" t="n">
-        <v>2567.51342465754</v>
+        <v>2585.22041379312</v>
       </c>
       <c r="P124" t="n">
         <v>6800</v>
@@ -5735,10 +5735,10 @@
         <v>20</v>
       </c>
       <c r="N126" t="n">
-        <v>538.40033834586</v>
+        <v>542.47912878788</v>
       </c>
       <c r="O126" t="n">
-        <v>10768.0067669172</v>
+        <v>10849.5825757576</v>
       </c>
       <c r="P126" t="n">
         <v>6800</v>
@@ -5781,10 +5781,10 @@
         <v>25</v>
       </c>
       <c r="N127" t="n">
-        <v>28.165601851852</v>
+        <v>28.165539906103</v>
       </c>
       <c r="O127" t="n">
-        <v>704.1400462962999</v>
+        <v>704.138497652575</v>
       </c>
       <c r="P127" t="n">
         <v>6800</v>
@@ -5931,22 +5931,22 @@
         <v>0</v>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M131" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N131" t="n">
         <v>8046.39</v>
       </c>
       <c r="O131" t="n">
-        <v>88510.29000000001</v>
+        <v>80463.90000000001</v>
       </c>
       <c r="P131" t="n">
         <v>20900</v>
       </c>
       <c r="Q131" t="n">
-        <v>229900</v>
+        <v>209000</v>
       </c>
     </row>
     <row r="132">
@@ -6069,22 +6069,22 @@
         <v>0</v>
       </c>
       <c r="L134" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M134" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="N134" t="n">
         <v>2572.67</v>
       </c>
       <c r="O134" t="n">
-        <v>84898.11</v>
+        <v>79752.77</v>
       </c>
       <c r="P134" t="n">
         <v>4700</v>
       </c>
       <c r="Q134" t="n">
-        <v>155100</v>
+        <v>145700</v>
       </c>
     </row>
     <row r="135">
@@ -7659,22 +7659,22 @@
         <v>0</v>
       </c>
       <c r="L170" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M170" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N170" t="n">
         <v>10752.93</v>
       </c>
       <c r="O170" t="n">
-        <v>21505.86</v>
+        <v>10752.93</v>
       </c>
       <c r="P170" t="n">
         <v>18400</v>
       </c>
       <c r="Q170" t="n">
-        <v>36800</v>
+        <v>18400</v>
       </c>
     </row>
     <row r="171">
@@ -7742,10 +7742,10 @@
         <v>41</v>
       </c>
       <c r="N172" t="n">
-        <v>1950.2152424105</v>
+        <v>1950.2151724138</v>
       </c>
       <c r="O172" t="n">
-        <v>79958.8249388305</v>
+        <v>79958.8220689658</v>
       </c>
       <c r="P172" t="n">
         <v>2900</v>
@@ -7911,10 +7911,10 @@
         <v>108</v>
       </c>
       <c r="N176" t="n">
-        <v>4937.3101603499</v>
+        <v>4937.3101608187</v>
       </c>
       <c r="O176" t="n">
-        <v>533229.4973177892</v>
+        <v>533229.4973684195</v>
       </c>
       <c r="P176" t="n">
         <v>7500</v>
@@ -8200,22 +8200,22 @@
         <v>0</v>
       </c>
       <c r="L183" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="M183" t="n">
-        <v>327</v>
+        <v>308</v>
       </c>
       <c r="N183" t="n">
-        <v>1098.0535004591</v>
+        <v>1098.0541801698</v>
       </c>
       <c r="O183" t="n">
-        <v>359063.4946501257</v>
+        <v>338200.6874922984</v>
       </c>
       <c r="P183" t="n">
         <v>1500</v>
       </c>
       <c r="Q183" t="n">
-        <v>490500</v>
+        <v>462000</v>
       </c>
     </row>
     <row r="184">
@@ -8284,25 +8284,25 @@
         <v>8</v>
       </c>
       <c r="K185" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L185" t="n">
         <v>0</v>
       </c>
       <c r="M185" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N185" t="n">
         <v>6295.2</v>
       </c>
       <c r="O185" t="n">
-        <v>50361.6</v>
+        <v>62952</v>
       </c>
       <c r="P185" t="n">
         <v>10500</v>
       </c>
       <c r="Q185" t="n">
-        <v>84000</v>
+        <v>105000</v>
       </c>
     </row>
     <row r="186">
@@ -8421,22 +8421,22 @@
         <v>0</v>
       </c>
       <c r="L188" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M188" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="N188" t="n">
         <v>1295.12</v>
       </c>
       <c r="O188" t="n">
-        <v>34968.24</v>
+        <v>28492.64</v>
       </c>
       <c r="P188" t="n">
         <v>1500</v>
       </c>
       <c r="Q188" t="n">
-        <v>40500</v>
+        <v>33000</v>
       </c>
     </row>
     <row r="189">
@@ -8692,25 +8692,25 @@
         <v>3</v>
       </c>
       <c r="K194" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="L194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M194" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="N194" t="n">
         <v>13593.35</v>
       </c>
       <c r="O194" t="n">
-        <v>40780.05</v>
+        <v>312647.05</v>
       </c>
       <c r="P194" t="n">
         <v>25500</v>
       </c>
       <c r="Q194" t="n">
-        <v>76500</v>
+        <v>586500</v>
       </c>
     </row>
     <row r="195">
@@ -8908,22 +8908,22 @@
         <v>0</v>
       </c>
       <c r="L199" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M199" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N199" t="n">
         <v>4065.61</v>
       </c>
       <c r="O199" t="n">
-        <v>134165.13</v>
+        <v>130099.52</v>
       </c>
       <c r="P199" t="n">
         <v>5000</v>
       </c>
       <c r="Q199" t="n">
-        <v>165000</v>
+        <v>160000</v>
       </c>
     </row>
     <row r="200">
@@ -9041,22 +9041,22 @@
         <v>0</v>
       </c>
       <c r="L202" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M202" t="n">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="N202" t="n">
         <v>2850.95</v>
       </c>
       <c r="O202" t="n">
-        <v>259436.45</v>
+        <v>222374.1</v>
       </c>
       <c r="P202" t="n">
         <v>4900</v>
       </c>
       <c r="Q202" t="n">
-        <v>445900</v>
+        <v>382200</v>
       </c>
     </row>
     <row r="203">
@@ -9270,10 +9270,10 @@
         <v>65</v>
       </c>
       <c r="N207" t="n">
-        <v>2582.2560562265</v>
+        <v>2582.2560231583</v>
       </c>
       <c r="O207" t="n">
-        <v>167846.6436547225</v>
+        <v>167846.6415052895</v>
       </c>
       <c r="P207" t="n">
         <v>4500</v>
@@ -9356,22 +9356,22 @@
         <v>0</v>
       </c>
       <c r="L209" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M209" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="N209" t="n">
         <v>10600</v>
       </c>
       <c r="O209" t="n">
-        <v>445200</v>
+        <v>392200</v>
       </c>
       <c r="P209" t="n">
         <v>17200</v>
       </c>
       <c r="Q209" t="n">
-        <v>722400</v>
+        <v>636400</v>
       </c>
     </row>
     <row r="210">
@@ -9408,10 +9408,10 @@
         <v>2</v>
       </c>
       <c r="N210" t="n">
-        <v>5216.8959875629</v>
+        <v>5216.8959762435</v>
       </c>
       <c r="O210" t="n">
-        <v>10433.7919751258</v>
+        <v>10433.791952487</v>
       </c>
       <c r="P210" t="n">
         <v>8500</v>
@@ -9448,22 +9448,22 @@
         <v>0</v>
       </c>
       <c r="L211" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="M211" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="N211" t="n">
-        <v>2033.573495935</v>
+        <v>2033.5693416928</v>
       </c>
       <c r="O211" t="n">
-        <v>115913.689268295</v>
+        <v>101678.46708464</v>
       </c>
       <c r="P211" t="n">
         <v>4100</v>
       </c>
       <c r="Q211" t="n">
-        <v>233700</v>
+        <v>205000</v>
       </c>
     </row>
     <row r="212">
@@ -9726,10 +9726,10 @@
         <v>391</v>
       </c>
       <c r="N217" t="n">
-        <v>3158.860813875</v>
+        <v>3158.8608143857</v>
       </c>
       <c r="O217" t="n">
-        <v>1235114.578225125</v>
+        <v>1235114.578424809</v>
       </c>
       <c r="P217" t="n">
         <v>5600</v>
@@ -10040,22 +10040,22 @@
         <v>0</v>
       </c>
       <c r="L224" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M224" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="N224" t="n">
         <v>2341</v>
       </c>
       <c r="O224" t="n">
-        <v>39797</v>
+        <v>30433</v>
       </c>
       <c r="P224" t="n">
         <v>3900</v>
       </c>
       <c r="Q224" t="n">
-        <v>66300</v>
+        <v>50700</v>
       </c>
     </row>
     <row r="225">
@@ -10138,10 +10138,10 @@
         <v>202</v>
       </c>
       <c r="N226" t="n">
-        <v>2694.8234682861</v>
+        <v>2694.8234624043</v>
       </c>
       <c r="O226" t="n">
-        <v>544354.3405937921</v>
+        <v>544354.3394056686</v>
       </c>
       <c r="P226" t="n">
         <v>4900</v>
@@ -10184,10 +10184,10 @@
         <v>13</v>
       </c>
       <c r="N227" t="n">
-        <v>1026.13</v>
+        <v>1037.4476102941</v>
       </c>
       <c r="O227" t="n">
-        <v>13339.69</v>
+        <v>13486.8189338233</v>
       </c>
       <c r="P227" t="n">
         <v>1900</v>
@@ -10224,22 +10224,22 @@
         <v>0</v>
       </c>
       <c r="L228" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="M228" t="n">
-        <v>1072</v>
+        <v>1062</v>
       </c>
       <c r="N228" t="n">
         <v>156.25</v>
       </c>
       <c r="O228" t="n">
-        <v>167500</v>
+        <v>165937.5</v>
       </c>
       <c r="P228" t="n">
         <v>250</v>
       </c>
       <c r="Q228" t="n">
-        <v>268000</v>
+        <v>265500</v>
       </c>
     </row>
     <row r="229">
@@ -10365,22 +10365,22 @@
         <v>0</v>
       </c>
       <c r="L231" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M231" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N231" t="n">
         <v>5002</v>
       </c>
       <c r="O231" t="n">
-        <v>200080</v>
+        <v>195078</v>
       </c>
       <c r="P231" t="n">
         <v>8400</v>
       </c>
       <c r="Q231" t="n">
-        <v>336000</v>
+        <v>327600</v>
       </c>
     </row>
     <row r="232">
@@ -10729,10 +10729,10 @@
         <v>10</v>
       </c>
       <c r="N239" t="n">
-        <v>4890.9300461095</v>
+        <v>4890.9300462963</v>
       </c>
       <c r="O239" t="n">
-        <v>48909.300461095</v>
+        <v>48909.300462963</v>
       </c>
       <c r="P239" t="n">
         <v>8200</v>
@@ -10766,25 +10766,25 @@
         <v>13</v>
       </c>
       <c r="K240" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L240" t="n">
         <v>0</v>
       </c>
       <c r="M240" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="N240" t="n">
         <v>5613.75</v>
       </c>
       <c r="O240" t="n">
-        <v>72978.75</v>
+        <v>89820</v>
       </c>
       <c r="P240" t="n">
         <v>7900</v>
       </c>
       <c r="Q240" t="n">
-        <v>102700</v>
+        <v>126400</v>
       </c>
     </row>
     <row r="241">
@@ -11406,25 +11406,25 @@
         <v>10</v>
       </c>
       <c r="K254" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L254" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M254" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="N254" t="n">
         <v>10716.34</v>
       </c>
       <c r="O254" t="n">
-        <v>107163.4</v>
+        <v>75014.38</v>
       </c>
       <c r="P254" t="n">
         <v>39000</v>
       </c>
       <c r="Q254" t="n">
-        <v>390000</v>
+        <v>273000</v>
       </c>
     </row>
     <row r="255">
@@ -11499,22 +11499,22 @@
         <v>0</v>
       </c>
       <c r="L256" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M256" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N256" t="n">
-        <v>3594.254188862</v>
+        <v>3594.2541747573</v>
       </c>
       <c r="O256" t="n">
-        <v>75479.337966102</v>
+        <v>68290.8293203887</v>
       </c>
       <c r="P256" t="n">
         <v>6500</v>
       </c>
       <c r="Q256" t="n">
-        <v>136500</v>
+        <v>123500</v>
       </c>
     </row>
     <row r="257">
@@ -11586,25 +11586,25 @@
         <v>420</v>
       </c>
       <c r="K258" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="L258" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M258" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="N258" t="n">
         <v>489.88</v>
       </c>
       <c r="O258" t="n">
-        <v>205749.6</v>
+        <v>206239.48</v>
       </c>
       <c r="P258" t="n">
         <v>700</v>
       </c>
       <c r="Q258" t="n">
-        <v>294000</v>
+        <v>294700</v>
       </c>
     </row>
     <row r="259">
@@ -11847,25 +11847,25 @@
         <v>18</v>
       </c>
       <c r="K264" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L264" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M264" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N264" t="n">
         <v>8154</v>
       </c>
       <c r="O264" t="n">
-        <v>146772</v>
+        <v>154926</v>
       </c>
       <c r="P264" t="n">
         <v>13500</v>
       </c>
       <c r="Q264" t="n">
-        <v>243000</v>
+        <v>256500</v>
       </c>
     </row>
     <row r="265">
@@ -11902,10 +11902,10 @@
         <v>9</v>
       </c>
       <c r="N265" t="n">
-        <v>14822.378867257</v>
+        <v>14822.378864577</v>
       </c>
       <c r="O265" t="n">
-        <v>133401.409805313</v>
+        <v>133401.409781193</v>
       </c>
       <c r="P265" t="n">
         <v>24900</v>
@@ -11986,25 +11986,25 @@
         <v>195</v>
       </c>
       <c r="K267" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L267" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="M267" t="n">
-        <v>177</v>
+        <v>265</v>
       </c>
       <c r="N267" t="n">
         <v>2090.85</v>
       </c>
       <c r="O267" t="n">
-        <v>370080.45</v>
+        <v>554075.25</v>
       </c>
       <c r="P267" t="n">
         <v>2900</v>
       </c>
       <c r="Q267" t="n">
-        <v>513300</v>
+        <v>768500</v>
       </c>
     </row>
     <row r="268">
@@ -12486,10 +12486,10 @@
         <v>8</v>
       </c>
       <c r="N278" t="n">
-        <v>12267.650842105</v>
+        <v>12267.650645161</v>
       </c>
       <c r="O278" t="n">
-        <v>98141.20673684</v>
+        <v>98141.205161288</v>
       </c>
       <c r="P278" t="n">
         <v>19900</v>
@@ -12715,10 +12715,10 @@
         <v>5</v>
       </c>
       <c r="N283" t="n">
-        <v>15851.61</v>
+        <v>15957.996644295</v>
       </c>
       <c r="O283" t="n">
-        <v>79258.05</v>
+        <v>79789.98322147501</v>
       </c>
       <c r="P283" t="n">
         <v>23900</v>
@@ -12881,25 +12881,25 @@
         <v>18</v>
       </c>
       <c r="K287" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M287" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="N287" t="n">
         <v>4193.85</v>
       </c>
       <c r="O287" t="n">
-        <v>75489.3</v>
+        <v>113233.95</v>
       </c>
       <c r="P287" t="n">
         <v>7500</v>
       </c>
       <c r="Q287" t="n">
-        <v>135000</v>
+        <v>202500</v>
       </c>
     </row>
     <row r="288">
@@ -12930,25 +12930,25 @@
         <v>16</v>
       </c>
       <c r="K288" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L288" t="n">
         <v>0</v>
       </c>
       <c r="M288" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="N288" t="n">
-        <v>3041.6600125549</v>
+        <v>3041.6600125945</v>
       </c>
       <c r="O288" t="n">
-        <v>48666.5602008784</v>
+        <v>79083.16032745701</v>
       </c>
       <c r="P288" t="n">
         <v>5500</v>
       </c>
       <c r="Q288" t="n">
-        <v>88000</v>
+        <v>143000</v>
       </c>
     </row>
     <row r="289">
@@ -13026,10 +13026,10 @@
         <v>1</v>
       </c>
       <c r="N290" t="n">
-        <v>4372.2107866525</v>
+        <v>4372.2107869318</v>
       </c>
       <c r="O290" t="n">
-        <v>4372.2107866525</v>
+        <v>4372.2107869318</v>
       </c>
       <c r="P290" t="n">
         <v>7500</v>
@@ -13110,22 +13110,22 @@
         <v>0</v>
       </c>
       <c r="L292" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M292" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="N292" t="n">
         <v>6441.03</v>
       </c>
       <c r="O292" t="n">
-        <v>437990.04</v>
+        <v>399343.86</v>
       </c>
       <c r="P292" t="n">
         <v>10500</v>
       </c>
       <c r="Q292" t="n">
-        <v>714000</v>
+        <v>651000</v>
       </c>
     </row>
     <row r="293">
@@ -13151,22 +13151,22 @@
         <v>0</v>
       </c>
       <c r="L293" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M293" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N293" t="n">
         <v>1121.98</v>
       </c>
       <c r="O293" t="n">
-        <v>6731.88</v>
+        <v>10097.82</v>
       </c>
       <c r="P293" t="n">
         <v>2400</v>
       </c>
       <c r="Q293" t="n">
-        <v>14400</v>
+        <v>21600</v>
       </c>
     </row>
     <row r="294">
@@ -13197,22 +13197,22 @@
         <v>0</v>
       </c>
       <c r="L294" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="M294" t="n">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="N294" t="n">
-        <v>1592.5676712942</v>
+        <v>1592.5675881262</v>
       </c>
       <c r="O294" t="n">
-        <v>171997.3084997736</v>
+        <v>154479.0560482414</v>
       </c>
       <c r="P294" t="n">
         <v>3900</v>
       </c>
       <c r="Q294" t="n">
-        <v>421200</v>
+        <v>378300</v>
       </c>
     </row>
     <row r="295">
@@ -13635,25 +13635,25 @@
         <v>45</v>
       </c>
       <c r="K304" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L304" t="n">
         <v>0</v>
       </c>
       <c r="M304" t="n">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="N304" t="n">
         <v>4648.6</v>
       </c>
       <c r="O304" t="n">
-        <v>209187</v>
+        <v>264970.2</v>
       </c>
       <c r="P304" t="n">
         <v>8900</v>
       </c>
       <c r="Q304" t="n">
-        <v>400500</v>
+        <v>507300</v>
       </c>
     </row>
     <row r="305">
@@ -13868,10 +13868,10 @@
         <v>11</v>
       </c>
       <c r="N309" t="n">
-        <v>17472.91</v>
+        <v>17476.031091396</v>
       </c>
       <c r="O309" t="n">
-        <v>192202.01</v>
+        <v>192236.342005356</v>
       </c>
       <c r="P309" t="n">
         <v>2900</v>
@@ -14082,22 +14082,22 @@
         <v>0</v>
       </c>
       <c r="L314" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M314" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="N314" t="n">
         <v>1387.55</v>
       </c>
       <c r="O314" t="n">
-        <v>215070.25</v>
+        <v>213682.7</v>
       </c>
       <c r="P314" t="n">
         <v>2300</v>
       </c>
       <c r="Q314" t="n">
-        <v>356500</v>
+        <v>354200</v>
       </c>
     </row>
     <row r="315">
@@ -14458,22 +14458,22 @@
         <v>0</v>
       </c>
       <c r="L322" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M322" t="n">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="N322" t="n">
         <v>1200</v>
       </c>
       <c r="O322" t="n">
-        <v>342000</v>
+        <v>349200</v>
       </c>
       <c r="P322" t="n">
         <v>1500</v>
       </c>
       <c r="Q322" t="n">
-        <v>427500</v>
+        <v>436500</v>
       </c>
     </row>
     <row r="323">
@@ -14552,10 +14552,10 @@
         <v>4</v>
       </c>
       <c r="N324" t="n">
-        <v>8341.030000000001</v>
+        <v>8367.5094603175</v>
       </c>
       <c r="O324" t="n">
-        <v>33364.12</v>
+        <v>33470.03784127</v>
       </c>
       <c r="P324" t="n">
         <v>13900</v>
@@ -14826,25 +14826,25 @@
         <v>7</v>
       </c>
       <c r="K330" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L330" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M330" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="N330" t="n">
         <v>11921.4</v>
       </c>
       <c r="O330" t="n">
-        <v>83449.8</v>
+        <v>190742.4</v>
       </c>
       <c r="P330" t="n">
         <v>19900</v>
       </c>
       <c r="Q330" t="n">
-        <v>139300</v>
+        <v>318400</v>
       </c>
     </row>
     <row r="331">
@@ -15158,10 +15158,10 @@
         <v>104</v>
       </c>
       <c r="N337" t="n">
-        <v>1151.3923550423</v>
+        <v>1151.3923553227</v>
       </c>
       <c r="O337" t="n">
-        <v>119744.8049243992</v>
+        <v>119744.8049535608</v>
       </c>
       <c r="P337" t="n">
         <v>1500</v>
@@ -15285,25 +15285,25 @@
         <v>6</v>
       </c>
       <c r="K340" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L340" t="n">
         <v>0</v>
       </c>
       <c r="M340" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N340" t="n">
         <v>9903</v>
       </c>
       <c r="O340" t="n">
-        <v>59418</v>
+        <v>69321</v>
       </c>
       <c r="P340" t="n">
         <v>15900</v>
       </c>
       <c r="Q340" t="n">
-        <v>95400</v>
+        <v>111300</v>
       </c>
     </row>
     <row r="341">
@@ -15380,22 +15380,22 @@
         <v>0</v>
       </c>
       <c r="L342" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="M342" t="n">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="N342" t="n">
-        <v>1630.9230521929</v>
+        <v>1630.9231064431</v>
       </c>
       <c r="O342" t="n">
-        <v>194079.8432109551</v>
+        <v>185925.2341345134</v>
       </c>
       <c r="P342" t="n">
         <v>2500</v>
       </c>
       <c r="Q342" t="n">
-        <v>297500</v>
+        <v>285000</v>
       </c>
     </row>
     <row r="343">
@@ -15472,22 +15472,22 @@
         <v>0</v>
       </c>
       <c r="L344" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M344" t="n">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N344" t="n">
-        <v>1690.6034846029</v>
+        <v>1690.6033768352</v>
       </c>
       <c r="O344" t="n">
-        <v>147082.5031604523</v>
+        <v>131867.0633931456</v>
       </c>
       <c r="P344" t="n">
         <v>2900</v>
       </c>
       <c r="Q344" t="n">
-        <v>252300</v>
+        <v>226200</v>
       </c>
     </row>
     <row r="345">
@@ -15518,22 +15518,22 @@
         <v>0</v>
       </c>
       <c r="L345" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="M345" t="n">
-        <v>541</v>
+        <v>509</v>
       </c>
       <c r="N345" t="n">
-        <v>1550.1930031561</v>
+        <v>1550.1930735465</v>
       </c>
       <c r="O345" t="n">
-        <v>838654.4147074502</v>
+        <v>789048.2744351685</v>
       </c>
       <c r="P345" t="n">
         <v>2500</v>
       </c>
       <c r="Q345" t="n">
-        <v>1352500</v>
+        <v>1272500</v>
       </c>
     </row>
     <row r="346">
@@ -15610,22 +15610,22 @@
         <v>0</v>
       </c>
       <c r="L347" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="M347" t="n">
-        <v>344</v>
+        <v>322</v>
       </c>
       <c r="N347" t="n">
-        <v>2403.5101337902</v>
+        <v>2403.5102087442</v>
       </c>
       <c r="O347" t="n">
-        <v>826807.4860238289</v>
+        <v>773930.2872156324</v>
       </c>
       <c r="P347" t="n">
         <v>3500</v>
       </c>
       <c r="Q347" t="n">
-        <v>1204000</v>
+        <v>1127000</v>
       </c>
     </row>
     <row r="348">
@@ -15656,22 +15656,22 @@
         <v>0</v>
       </c>
       <c r="L348" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M348" t="n">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="N348" t="n">
-        <v>2521.5468491124</v>
+        <v>2521.5455211726</v>
       </c>
       <c r="O348" t="n">
-        <v>229460.7632692284</v>
+        <v>219374.4603420162</v>
       </c>
       <c r="P348" t="n">
         <v>3900</v>
       </c>
       <c r="Q348" t="n">
-        <v>354900</v>
+        <v>339300</v>
       </c>
     </row>
     <row r="349">
@@ -15730,25 +15730,25 @@
         <v>52</v>
       </c>
       <c r="K350" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L350" t="n">
         <v>0</v>
       </c>
       <c r="M350" t="n">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="N350" t="n">
         <v>1232.8081659389</v>
       </c>
       <c r="O350" t="n">
-        <v>64106.02462882279</v>
+        <v>78899.7226200896</v>
       </c>
       <c r="P350" t="n">
         <v>2400</v>
       </c>
       <c r="Q350" t="n">
-        <v>124800</v>
+        <v>153600</v>
       </c>
     </row>
     <row r="351">
@@ -15820,22 +15820,22 @@
         <v>0</v>
       </c>
       <c r="L352" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M352" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="N352" t="n">
         <v>14778</v>
       </c>
       <c r="O352" t="n">
-        <v>162558</v>
+        <v>118224</v>
       </c>
       <c r="P352" t="n">
         <v>24900</v>
       </c>
       <c r="Q352" t="n">
-        <v>273900</v>
+        <v>199200</v>
       </c>
     </row>
     <row r="353">
@@ -16640,22 +16640,22 @@
         <v>0</v>
       </c>
       <c r="L370" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M370" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N370" t="n">
         <v>17328</v>
       </c>
       <c r="O370" t="n">
-        <v>467856</v>
+        <v>450528</v>
       </c>
       <c r="P370" t="n">
         <v>32900</v>
       </c>
       <c r="Q370" t="n">
-        <v>888300</v>
+        <v>855400</v>
       </c>
     </row>
     <row r="371">
@@ -18287,22 +18287,22 @@
         <v>0</v>
       </c>
       <c r="L407" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M407" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="N407" t="n">
-        <v>7537.4721167883</v>
+        <v>7537.4721481481</v>
       </c>
       <c r="O407" t="n">
-        <v>82912.1932846713</v>
+        <v>67837.2493333329</v>
       </c>
       <c r="P407" t="n">
         <v>8900</v>
       </c>
       <c r="Q407" t="n">
-        <v>97900</v>
+        <v>80100</v>
       </c>
     </row>
     <row r="408">
@@ -18658,25 +18658,25 @@
         <v>198</v>
       </c>
       <c r="K416" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L416" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M416" t="n">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="N416" t="n">
         <v>2567</v>
       </c>
       <c r="O416" t="n">
-        <v>508266</v>
+        <v>492864</v>
       </c>
       <c r="P416" t="n">
         <v>4500</v>
       </c>
       <c r="Q416" t="n">
-        <v>891000</v>
+        <v>864000</v>
       </c>
     </row>
     <row r="417">
@@ -18790,10 +18790,10 @@
         <v>213</v>
       </c>
       <c r="N419" t="n">
-        <v>2029.8736460865</v>
+        <v>2029.8736549708</v>
       </c>
       <c r="O419" t="n">
-        <v>432363.0866164245</v>
+        <v>432363.0885087804</v>
       </c>
       <c r="P419" t="n">
         <v>3600</v>
@@ -19077,10 +19077,10 @@
         <v>556</v>
       </c>
       <c r="N426" t="n">
-        <v>880.32932278334</v>
+        <v>880.32933581916</v>
       </c>
       <c r="O426" t="n">
-        <v>489463.103467537</v>
+        <v>489463.1107154529</v>
       </c>
       <c r="P426" t="n">
         <v>1200</v>
@@ -19286,22 +19286,22 @@
         <v>0</v>
       </c>
       <c r="L431" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M431" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N431" t="n">
         <v>14060.64</v>
       </c>
       <c r="O431" t="n">
-        <v>281212.8</v>
+        <v>267152.16</v>
       </c>
       <c r="P431" t="n">
         <v>22900</v>
       </c>
       <c r="Q431" t="n">
-        <v>458000</v>
+        <v>435100</v>
       </c>
     </row>
     <row r="432">
@@ -19537,22 +19537,22 @@
         <v>0</v>
       </c>
       <c r="L437" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M437" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="N437" t="n">
         <v>14371.45</v>
       </c>
       <c r="O437" t="n">
-        <v>215571.75</v>
+        <v>114971.6</v>
       </c>
       <c r="P437" t="n">
         <v>23300</v>
       </c>
       <c r="Q437" t="n">
-        <v>349500</v>
+        <v>186400</v>
       </c>
     </row>
     <row r="438">
@@ -19718,25 +19718,25 @@
         <v>26</v>
       </c>
       <c r="K441" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L441" t="n">
         <v>0</v>
       </c>
       <c r="M441" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="N441" t="n">
         <v>3877.89</v>
       </c>
       <c r="O441" t="n">
-        <v>100825.14</v>
+        <v>147359.82</v>
       </c>
       <c r="P441" t="n">
         <v>6500</v>
       </c>
       <c r="Q441" t="n">
-        <v>169000</v>
+        <v>247000</v>
       </c>
     </row>
     <row r="442">
@@ -19858,10 +19858,10 @@
         <v>17</v>
       </c>
       <c r="N444" t="n">
-        <v>4285.1952479339</v>
+        <v>4285.1952751817</v>
       </c>
       <c r="O444" t="n">
-        <v>72848.31921487629</v>
+        <v>72848.3196780889</v>
       </c>
       <c r="P444" t="n">
         <v>6900</v>
@@ -20275,22 +20275,22 @@
         <v>0</v>
       </c>
       <c r="L454" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M454" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N454" t="n">
         <v>8987</v>
       </c>
       <c r="O454" t="n">
-        <v>89870</v>
+        <v>80883</v>
       </c>
       <c r="P454" t="n">
         <v>15200</v>
       </c>
       <c r="Q454" t="n">
-        <v>152000</v>
+        <v>136800</v>
       </c>
     </row>
     <row r="455">
@@ -20318,25 +20318,25 @@
         <v>11</v>
       </c>
       <c r="K455" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L455" t="n">
         <v>0</v>
       </c>
       <c r="M455" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="N455" t="n">
-        <v>4605.2146487985</v>
+        <v>4605.2146574074</v>
       </c>
       <c r="O455" t="n">
-        <v>50657.3611367835</v>
+        <v>69078.21986111101</v>
       </c>
       <c r="P455" t="n">
         <v>7600</v>
       </c>
       <c r="Q455" t="n">
-        <v>83600</v>
+        <v>114000</v>
       </c>
     </row>
     <row r="456">
@@ -20451,25 +20451,25 @@
         <v>10</v>
       </c>
       <c r="K458" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L458" t="n">
         <v>0</v>
       </c>
       <c r="M458" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="N458" t="n">
         <v>13513.642971014</v>
       </c>
       <c r="O458" t="n">
-        <v>135136.42971014</v>
+        <v>175677.358623182</v>
       </c>
       <c r="P458" t="n">
         <v>21900</v>
       </c>
       <c r="Q458" t="n">
-        <v>219000</v>
+        <v>284700</v>
       </c>
     </row>
     <row r="459">
@@ -21064,10 +21064,10 @@
         <v>9</v>
       </c>
       <c r="N472" t="n">
-        <v>27123.765250464</v>
+        <v>27123.765241636</v>
       </c>
       <c r="O472" t="n">
-        <v>244113.887254176</v>
+        <v>244113.887174724</v>
       </c>
       <c r="P472" t="n">
         <v>44500</v>
@@ -21186,22 +21186,22 @@
         <v>0</v>
       </c>
       <c r="L475" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M475" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="N475" t="n">
         <v>16974.69</v>
       </c>
       <c r="O475" t="n">
-        <v>712936.98</v>
+        <v>662012.9099999999</v>
       </c>
       <c r="P475" t="n">
         <v>26900</v>
       </c>
       <c r="Q475" t="n">
-        <v>1129800</v>
+        <v>1049100</v>
       </c>
     </row>
     <row r="476">
@@ -21360,22 +21360,22 @@
         <v>0</v>
       </c>
       <c r="L479" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M479" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="N479" t="n">
-        <v>1560.9989986027</v>
+        <v>1560.9991607397</v>
       </c>
       <c r="O479" t="n">
-        <v>109269.929902189</v>
+        <v>118635.9362162172</v>
       </c>
       <c r="P479" t="n">
         <v>2900</v>
       </c>
       <c r="Q479" t="n">
-        <v>203000</v>
+        <v>220400</v>
       </c>
     </row>
     <row r="480">
@@ -21845,10 +21845,10 @@
         <v>6</v>
       </c>
       <c r="N490" t="n">
-        <v>7969.950164794</v>
+        <v>7969.9501649175</v>
       </c>
       <c r="O490" t="n">
-        <v>47819.700988764</v>
+        <v>47819.700989505</v>
       </c>
       <c r="P490" t="n">
         <v>12900</v>
@@ -23434,25 +23434,25 @@
         <v>6</v>
       </c>
       <c r="K526" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L526" t="n">
         <v>0</v>
       </c>
       <c r="M526" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="N526" t="n">
         <v>8562.18</v>
       </c>
       <c r="O526" t="n">
-        <v>51373.08</v>
+        <v>85621.8</v>
       </c>
       <c r="P526" t="n">
         <v>9900</v>
       </c>
       <c r="Q526" t="n">
-        <v>59400</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="527">
@@ -23882,22 +23882,22 @@
         <v>0</v>
       </c>
       <c r="L536" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M536" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="N536" t="n">
         <v>4690.64</v>
       </c>
       <c r="O536" t="n">
-        <v>145409.84</v>
+        <v>126647.28</v>
       </c>
       <c r="P536" t="n">
         <v>7500</v>
       </c>
       <c r="Q536" t="n">
-        <v>232500</v>
+        <v>202500</v>
       </c>
     </row>
     <row r="537">
@@ -24112,22 +24112,22 @@
         <v>0</v>
       </c>
       <c r="L541" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M541" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="N541" t="n">
         <v>3254.49</v>
       </c>
       <c r="O541" t="n">
-        <v>133434.09</v>
+        <v>149706.54</v>
       </c>
       <c r="P541" t="n">
         <v>5200</v>
       </c>
       <c r="Q541" t="n">
-        <v>213200</v>
+        <v>239200</v>
       </c>
     </row>
     <row r="542">
@@ -24164,10 +24164,10 @@
         <v>14</v>
       </c>
       <c r="N542" t="n">
-        <v>5218.1704988662</v>
+        <v>5218.1705022831</v>
       </c>
       <c r="O542" t="n">
-        <v>73054.3869841268</v>
+        <v>73054.3870319634</v>
       </c>
       <c r="P542" t="n">
         <v>8500</v>
@@ -24210,10 +24210,10 @@
         <v>14</v>
       </c>
       <c r="N543" t="n">
-        <v>1595.0094843962</v>
+        <v>1595.0094808743</v>
       </c>
       <c r="O543" t="n">
-        <v>22330.1327815468</v>
+        <v>22330.1327322402</v>
       </c>
       <c r="P543" t="n">
         <v>2600</v>
@@ -24440,22 +24440,22 @@
         <v>0</v>
       </c>
       <c r="L548" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M548" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N548" t="n">
         <v>3920</v>
       </c>
       <c r="O548" t="n">
-        <v>50960</v>
+        <v>43120</v>
       </c>
       <c r="P548" t="n">
         <v>4900</v>
       </c>
       <c r="Q548" t="n">
-        <v>63700</v>
+        <v>53900</v>
       </c>
     </row>
     <row r="549">
@@ -24906,22 +24906,22 @@
         <v>0</v>
       </c>
       <c r="L558" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M558" t="n">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="N558" t="n">
-        <v>1664.3605954323</v>
+        <v>1664.360187234</v>
       </c>
       <c r="O558" t="n">
-        <v>234674.8439559543</v>
+        <v>213038.103965952</v>
       </c>
       <c r="P558" t="n">
         <v>2900</v>
       </c>
       <c r="Q558" t="n">
-        <v>408900</v>
+        <v>371200</v>
       </c>
     </row>
     <row r="559">
@@ -24952,22 +24952,22 @@
         <v>0</v>
       </c>
       <c r="L559" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M559" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N559" t="n">
         <v>15502</v>
       </c>
       <c r="O559" t="n">
-        <v>108514</v>
+        <v>93012</v>
       </c>
       <c r="P559" t="n">
         <v>25900</v>
       </c>
       <c r="Q559" t="n">
-        <v>181300</v>
+        <v>155400</v>
       </c>
     </row>
     <row r="560">
@@ -25706,10 +25706,10 @@
         <v>29</v>
       </c>
       <c r="N575" t="n">
-        <v>1778.4725400058</v>
+        <v>1778.4725489051</v>
       </c>
       <c r="O575" t="n">
-        <v>51575.7036601682</v>
+        <v>51575.7039182479</v>
       </c>
       <c r="P575" t="n">
         <v>4900</v>
@@ -25746,22 +25746,22 @@
         <v>0</v>
       </c>
       <c r="L576" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M576" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N576" t="n">
         <v>1548</v>
       </c>
       <c r="O576" t="n">
-        <v>12384</v>
+        <v>0</v>
       </c>
       <c r="P576" t="n">
         <v>3900</v>
       </c>
       <c r="Q576" t="n">
-        <v>31200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="577">
@@ -25976,22 +25976,22 @@
         <v>0</v>
       </c>
       <c r="L581" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M581" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="N581" t="n">
         <v>18016</v>
       </c>
       <c r="O581" t="n">
-        <v>162144</v>
+        <v>90080</v>
       </c>
       <c r="P581" t="n">
         <v>29900</v>
       </c>
       <c r="Q581" t="n">
-        <v>269100</v>
+        <v>149500</v>
       </c>
     </row>
     <row r="582">
@@ -26022,22 +26022,22 @@
         <v>0</v>
       </c>
       <c r="L582" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M582" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="N582" t="n">
         <v>16058</v>
       </c>
       <c r="O582" t="n">
-        <v>240870</v>
+        <v>160580</v>
       </c>
       <c r="P582" t="n">
         <v>25900</v>
       </c>
       <c r="Q582" t="n">
-        <v>388500</v>
+        <v>259000</v>
       </c>
     </row>
     <row r="583">
@@ -26160,22 +26160,22 @@
         <v>0</v>
       </c>
       <c r="L585" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M585" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="N585" t="n">
         <v>5148</v>
       </c>
       <c r="O585" t="n">
-        <v>293436</v>
+        <v>283140</v>
       </c>
       <c r="P585" t="n">
         <v>8600</v>
       </c>
       <c r="Q585" t="n">
-        <v>490200</v>
+        <v>473000</v>
       </c>
     </row>
     <row r="586">
@@ -26998,22 +26998,22 @@
         <v>0</v>
       </c>
       <c r="L603" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M603" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="N603" t="n">
         <v>13687</v>
       </c>
       <c r="O603" t="n">
-        <v>479045</v>
+        <v>369549</v>
       </c>
       <c r="P603" t="n">
         <v>21900</v>
       </c>
       <c r="Q603" t="n">
-        <v>766500</v>
+        <v>591300</v>
       </c>
     </row>
     <row r="604">
@@ -27096,10 +27096,10 @@
         <v>32</v>
       </c>
       <c r="N605" t="n">
-        <v>8293</v>
+        <v>8329.056521739099</v>
       </c>
       <c r="O605" t="n">
-        <v>265376</v>
+        <v>266529.8086956512</v>
       </c>
       <c r="P605" t="n">
         <v>13500</v>
@@ -27421,10 +27421,10 @@
         <v>1</v>
       </c>
       <c r="N612" t="n">
-        <v>2821.5820512821</v>
+        <v>2821.5822222222</v>
       </c>
       <c r="O612" t="n">
-        <v>2821.5820512821</v>
+        <v>2821.5822222222</v>
       </c>
       <c r="P612" t="n">
         <v>4500</v>
@@ -27640,10 +27640,10 @@
         <v>22</v>
       </c>
       <c r="K617" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L617" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M617" t="n">
         <v>22</v>
@@ -27824,25 +27824,25 @@
         <v>2</v>
       </c>
       <c r="K621" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L621" t="n">
         <v>2</v>
       </c>
       <c r="M621" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N621" t="n">
-        <v>17644.653166667</v>
+        <v>17644.653275862</v>
       </c>
       <c r="O621" t="n">
-        <v>0</v>
+        <v>35289.306551724</v>
       </c>
       <c r="P621" t="n">
         <v>28200</v>
       </c>
       <c r="Q621" t="n">
-        <v>0</v>
+        <v>56400</v>
       </c>
     </row>
     <row r="622">
@@ -27962,25 +27962,25 @@
         <v>190</v>
       </c>
       <c r="K624" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L624" t="n">
         <v>0</v>
       </c>
       <c r="M624" t="n">
-        <v>190</v>
+        <v>214</v>
       </c>
       <c r="N624" t="n">
-        <v>2252.2963603819</v>
+        <v>2252.2964527845</v>
       </c>
       <c r="O624" t="n">
-        <v>427936.308472561</v>
+        <v>481991.440895883</v>
       </c>
       <c r="P624" t="n">
         <v>3900</v>
       </c>
       <c r="Q624" t="n">
-        <v>741000</v>
+        <v>834600</v>
       </c>
     </row>
     <row r="625">
@@ -28437,10 +28437,10 @@
         <v>125</v>
       </c>
       <c r="N634" t="n">
-        <v>2328.1187525865</v>
+        <v>2328.1187507401</v>
       </c>
       <c r="O634" t="n">
-        <v>291014.8440733125</v>
+        <v>291014.8438425125</v>
       </c>
       <c r="P634" t="n">
         <v>4500</v>
@@ -28707,22 +28707,22 @@
         <v>0</v>
       </c>
       <c r="L640" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M640" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="N640" t="n">
         <v>3519</v>
       </c>
       <c r="O640" t="n">
-        <v>49266</v>
+        <v>0</v>
       </c>
       <c r="P640" t="n">
         <v>5900</v>
       </c>
       <c r="Q640" t="n">
-        <v>82600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="641">
@@ -28888,25 +28888,25 @@
         <v>6</v>
       </c>
       <c r="K644" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L644" t="n">
         <v>0</v>
       </c>
       <c r="M644" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="N644" t="n">
         <v>13922</v>
       </c>
       <c r="O644" t="n">
-        <v>83532</v>
+        <v>167064</v>
       </c>
       <c r="P644" t="n">
         <v>22900</v>
       </c>
       <c r="Q644" t="n">
-        <v>137400</v>
+        <v>274800</v>
       </c>
     </row>
     <row r="645">
@@ -29357,10 +29357,10 @@
         <v>88</v>
       </c>
       <c r="N654" t="n">
-        <v>3903.7359649123</v>
+        <v>3903.7361538462</v>
       </c>
       <c r="O654" t="n">
-        <v>343528.7649122824</v>
+        <v>343528.7815384656</v>
       </c>
       <c r="P654" t="n">
         <v>7500</v>
@@ -29582,10 +29582,10 @@
         <v>3</v>
       </c>
       <c r="N659" t="n">
-        <v>4202</v>
+        <v>4213.1164021164</v>
       </c>
       <c r="O659" t="n">
-        <v>12606</v>
+        <v>12639.3492063492</v>
       </c>
       <c r="P659" t="n">
         <v>7900</v>
@@ -29757,25 +29757,25 @@
         <v>2</v>
       </c>
       <c r="K663" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L663" t="n">
         <v>2</v>
       </c>
       <c r="M663" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N663" t="n">
         <v>9839</v>
       </c>
       <c r="O663" t="n">
-        <v>0</v>
+        <v>19678</v>
       </c>
       <c r="P663" t="n">
         <v>16900</v>
       </c>
       <c r="Q663" t="n">
-        <v>0</v>
+        <v>33800</v>
       </c>
     </row>
     <row r="664">
@@ -29895,25 +29895,25 @@
         <v>26</v>
       </c>
       <c r="K666" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L666" t="n">
         <v>0</v>
       </c>
       <c r="M666" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="N666" t="n">
         <v>6849.2</v>
       </c>
       <c r="O666" t="n">
-        <v>178079.2</v>
+        <v>246571.2</v>
       </c>
       <c r="P666" t="n">
         <v>11500</v>
       </c>
       <c r="Q666" t="n">
-        <v>299000</v>
+        <v>414000</v>
       </c>
     </row>
     <row r="667">
@@ -30125,25 +30125,25 @@
         <v>21</v>
       </c>
       <c r="K671" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L671" t="n">
         <v>0</v>
       </c>
       <c r="M671" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="N671" t="n">
         <v>6645</v>
       </c>
       <c r="O671" t="n">
-        <v>139545</v>
+        <v>219285</v>
       </c>
       <c r="P671" t="n">
         <v>10900</v>
       </c>
       <c r="Q671" t="n">
-        <v>228900</v>
+        <v>359700</v>
       </c>
     </row>
     <row r="672">
@@ -30683,22 +30683,22 @@
         <v>0</v>
       </c>
       <c r="L683" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="M683" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="N683" t="n">
         <v>753</v>
       </c>
       <c r="O683" t="n">
-        <v>96384</v>
+        <v>98643</v>
       </c>
       <c r="P683" t="n">
         <v>1600</v>
       </c>
       <c r="Q683" t="n">
-        <v>204800</v>
+        <v>209600</v>
       </c>
     </row>
     <row r="684">
@@ -30867,22 +30867,22 @@
         <v>0</v>
       </c>
       <c r="L687" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M687" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N687" t="n">
         <v>11348</v>
       </c>
       <c r="O687" t="n">
-        <v>45392</v>
+        <v>34044</v>
       </c>
       <c r="P687" t="n">
         <v>19900</v>
       </c>
       <c r="Q687" t="n">
-        <v>79600</v>
+        <v>59700</v>
       </c>
     </row>
     <row r="688">
@@ -30919,10 +30919,10 @@
         <v>36</v>
       </c>
       <c r="N688" t="n">
-        <v>17075.989524138</v>
+        <v>17075.98952381</v>
       </c>
       <c r="O688" t="n">
-        <v>614735.6228689679</v>
+        <v>614735.6228571599</v>
       </c>
       <c r="P688" t="n">
         <v>27500</v>
@@ -31092,22 +31092,22 @@
         <v>0</v>
       </c>
       <c r="L692" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M692" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N692" t="n">
         <v>11015</v>
       </c>
       <c r="O692" t="n">
-        <v>77105</v>
+        <v>55075</v>
       </c>
       <c r="P692" t="n">
         <v>17900</v>
       </c>
       <c r="Q692" t="n">
-        <v>125300</v>
+        <v>89500</v>
       </c>
     </row>
     <row r="693">
@@ -31368,25 +31368,25 @@
         <v>33</v>
       </c>
       <c r="K698" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L698" t="n">
         <v>0</v>
       </c>
       <c r="M698" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="N698" t="n">
         <v>10755</v>
       </c>
       <c r="O698" t="n">
-        <v>354915</v>
+        <v>483975</v>
       </c>
       <c r="P698" t="n">
         <v>17900</v>
       </c>
       <c r="Q698" t="n">
-        <v>590700</v>
+        <v>805500</v>
       </c>
     </row>
     <row r="699">
@@ -31601,22 +31601,22 @@
         <v>0</v>
       </c>
       <c r="L703" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M703" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="N703" t="n">
-        <v>4268.7037401575</v>
+        <v>4268.7041295547</v>
       </c>
       <c r="O703" t="n">
-        <v>132329.8159448825</v>
+        <v>123792.4197570863</v>
       </c>
       <c r="P703" t="n">
         <v>6900</v>
       </c>
       <c r="Q703" t="n">
-        <v>213900</v>
+        <v>200100</v>
       </c>
     </row>
     <row r="704">
@@ -32015,22 +32015,22 @@
         <v>0</v>
       </c>
       <c r="L712" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M712" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="N712" t="n">
         <v>1326</v>
       </c>
       <c r="O712" t="n">
-        <v>58344</v>
+        <v>55692</v>
       </c>
       <c r="P712" t="n">
         <v>2500</v>
       </c>
       <c r="Q712" t="n">
-        <v>110000</v>
+        <v>105000</v>
       </c>
     </row>
     <row r="713">
@@ -32104,25 +32104,25 @@
         <v>12</v>
       </c>
       <c r="K714" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L714" t="n">
         <v>0</v>
       </c>
       <c r="M714" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="N714" t="n">
         <v>10817</v>
       </c>
       <c r="O714" t="n">
-        <v>129804</v>
+        <v>173072</v>
       </c>
       <c r="P714" t="n">
         <v>17900</v>
       </c>
       <c r="Q714" t="n">
-        <v>214800</v>
+        <v>286400</v>
       </c>
     </row>
     <row r="715">
@@ -32153,22 +32153,22 @@
         <v>0</v>
       </c>
       <c r="L715" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M715" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N715" t="n">
         <v>2458</v>
       </c>
       <c r="O715" t="n">
-        <v>46702</v>
+        <v>41786</v>
       </c>
       <c r="P715" t="n">
         <v>3500</v>
       </c>
       <c r="Q715" t="n">
-        <v>66500</v>
+        <v>59500</v>
       </c>
     </row>
     <row r="716">
@@ -32337,22 +32337,22 @@
         <v>0</v>
       </c>
       <c r="L719" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M719" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N719" t="n">
         <v>15472</v>
       </c>
       <c r="O719" t="n">
-        <v>92832</v>
+        <v>30944</v>
       </c>
       <c r="P719" t="n">
         <v>25900</v>
       </c>
       <c r="Q719" t="n">
-        <v>155400</v>
+        <v>51800</v>
       </c>
     </row>
     <row r="720">
@@ -32755,10 +32755,10 @@
         <v>102</v>
       </c>
       <c r="N728" t="n">
-        <v>4248.6196402878</v>
+        <v>4248.6214117647</v>
       </c>
       <c r="O728" t="n">
-        <v>433359.2033093557</v>
+        <v>433359.3839999994</v>
       </c>
       <c r="P728" t="n">
         <v>5900</v>
@@ -32801,10 +32801,10 @@
         <v>243</v>
       </c>
       <c r="N729" t="n">
-        <v>2458.5134452463</v>
+        <v>2458.5134204724</v>
       </c>
       <c r="O729" t="n">
-        <v>597418.7671948508</v>
+        <v>597418.7611747932</v>
       </c>
       <c r="P729" t="n">
         <v>3500</v>
@@ -32847,10 +32847,10 @@
         <v>153</v>
       </c>
       <c r="N730" t="n">
-        <v>1907.3944387755</v>
+        <v>1907.3944245524</v>
       </c>
       <c r="O730" t="n">
-        <v>291831.3491326515</v>
+        <v>291831.3469565172</v>
       </c>
       <c r="P730" t="n">
         <v>2500</v>
@@ -32939,10 +32939,10 @@
         <v>134</v>
       </c>
       <c r="N732" t="n">
-        <v>2079.3842077922</v>
+        <v>2079.384205911</v>
       </c>
       <c r="O732" t="n">
-        <v>278637.4838441548</v>
+        <v>278637.483592074</v>
       </c>
       <c r="P732" t="n">
         <v>2900</v>
@@ -32979,22 +32979,22 @@
         <v>0</v>
       </c>
       <c r="L733" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M733" t="n">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="N733" t="n">
-        <v>1803.0149882284</v>
+        <v>1803.0150073855</v>
       </c>
       <c r="O733" t="n">
-        <v>301103.5030341428</v>
+        <v>311921.5962776915</v>
       </c>
       <c r="P733" t="n">
         <v>2500</v>
       </c>
       <c r="Q733" t="n">
-        <v>417500</v>
+        <v>432500</v>
       </c>
     </row>
     <row r="734">
@@ -33031,10 +33031,10 @@
         <v>53</v>
       </c>
       <c r="N734" t="n">
-        <v>3306.595443038</v>
+        <v>3306.5954372624</v>
       </c>
       <c r="O734" t="n">
-        <v>175249.558481014</v>
+        <v>175249.5581749072</v>
       </c>
       <c r="P734" t="n">
         <v>4900</v>
@@ -33077,10 +33077,10 @@
         <v>64</v>
       </c>
       <c r="N735" t="n">
-        <v>2122.1641066586</v>
+        <v>2122.1640959855</v>
       </c>
       <c r="O735" t="n">
-        <v>135818.5028261504</v>
+        <v>135818.502143072</v>
       </c>
       <c r="P735" t="n">
         <v>2900</v>
@@ -33123,10 +33123,10 @@
         <v>86</v>
       </c>
       <c r="N736" t="n">
-        <v>2108.7898867497</v>
+        <v>2108.7899091941</v>
       </c>
       <c r="O736" t="n">
-        <v>181355.9302604742</v>
+        <v>181355.9321906926</v>
       </c>
       <c r="P736" t="n">
         <v>2900</v>
@@ -33169,10 +33169,10 @@
         <v>306</v>
       </c>
       <c r="N737" t="n">
-        <v>2056.0838862559</v>
+        <v>2056.083871734</v>
       </c>
       <c r="O737" t="n">
-        <v>629161.6691943053</v>
+        <v>629161.664750604</v>
       </c>
       <c r="P737" t="n">
         <v>2900</v>
@@ -33209,22 +33209,22 @@
         <v>0</v>
       </c>
       <c r="L738" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M738" t="n">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="N738" t="n">
-        <v>3224.5679768271</v>
+        <v>3224.5680666967</v>
       </c>
       <c r="O738" t="n">
-        <v>338579.6375668455</v>
+        <v>322456.80666967</v>
       </c>
       <c r="P738" t="n">
         <v>4500</v>
       </c>
       <c r="Q738" t="n">
-        <v>472500</v>
+        <v>450000</v>
       </c>
     </row>
     <row r="739">
@@ -33261,10 +33261,10 @@
         <v>161</v>
       </c>
       <c r="N739" t="n">
-        <v>1655.9313291536</v>
+        <v>1655.9312964128</v>
       </c>
       <c r="O739" t="n">
-        <v>266604.9439937296</v>
+        <v>266604.9387224608</v>
       </c>
       <c r="P739" t="n">
         <v>2500</v>
@@ -33396,22 +33396,22 @@
         <v>0</v>
       </c>
       <c r="L742" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M742" t="n">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="N742" t="n">
         <v>1662</v>
       </c>
       <c r="O742" t="n">
-        <v>608292</v>
+        <v>601644</v>
       </c>
       <c r="P742" t="n">
         <v>2900</v>
       </c>
       <c r="Q742" t="n">
-        <v>1061400</v>
+        <v>1049800</v>
       </c>
     </row>
     <row r="743">
@@ -33534,22 +33534,22 @@
         <v>0</v>
       </c>
       <c r="L745" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M745" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="N745" t="n">
-        <v>1592.2748727876</v>
+        <v>1592.2752659892</v>
       </c>
       <c r="O745" t="n">
-        <v>125789.7149502204</v>
+        <v>121012.9202151792</v>
       </c>
       <c r="P745" t="n">
         <v>2500</v>
       </c>
       <c r="Q745" t="n">
-        <v>197500</v>
+        <v>190000</v>
       </c>
     </row>
     <row r="746">
@@ -33580,22 +33580,22 @@
         <v>0</v>
       </c>
       <c r="L746" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M746" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="N746" t="n">
         <v>2327.68</v>
       </c>
       <c r="O746" t="n">
-        <v>81468.79999999999</v>
+        <v>74485.75999999999</v>
       </c>
       <c r="P746" t="n">
         <v>3900</v>
       </c>
       <c r="Q746" t="n">
-        <v>136500</v>
+        <v>124800</v>
       </c>
     </row>
     <row r="747">
@@ -33671,10 +33671,10 @@
         <v>28</v>
       </c>
       <c r="N748" t="n">
-        <v>5347.73</v>
+        <v>5370.4862978723</v>
       </c>
       <c r="O748" t="n">
-        <v>149736.44</v>
+        <v>150373.6163404244</v>
       </c>
       <c r="P748" t="n">
         <v>9500</v>
@@ -33711,22 +33711,22 @@
         <v>0</v>
       </c>
       <c r="L749" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="M749" t="n">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="N749" t="n">
-        <v>2311.9264781906</v>
+        <v>2311.9257410562</v>
       </c>
       <c r="O749" t="n">
-        <v>312110.074555731</v>
+        <v>293614.5691141374</v>
       </c>
       <c r="P749" t="n">
         <v>3500</v>
       </c>
       <c r="Q749" t="n">
-        <v>472500</v>
+        <v>444500</v>
       </c>
     </row>
     <row r="750">
@@ -33757,22 +33757,22 @@
         <v>0</v>
       </c>
       <c r="L750" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="M750" t="n">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="N750" t="n">
-        <v>1906.1867105263</v>
+        <v>1906.1864705882</v>
       </c>
       <c r="O750" t="n">
-        <v>91496.9621052624</v>
+        <v>74341.27235293981</v>
       </c>
       <c r="P750" t="n">
         <v>2900</v>
       </c>
       <c r="Q750" t="n">
-        <v>139200</v>
+        <v>113100</v>
       </c>
     </row>
     <row r="751">
@@ -33803,22 +33803,22 @@
         <v>0</v>
       </c>
       <c r="L751" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M751" t="n">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="N751" t="n">
-        <v>3033.7312929293</v>
+        <v>3033.7307083333</v>
       </c>
       <c r="O751" t="n">
-        <v>233597.3095555561</v>
+        <v>188091.3039166646</v>
       </c>
       <c r="P751" t="n">
         <v>4500</v>
       </c>
       <c r="Q751" t="n">
-        <v>346500</v>
+        <v>279000</v>
       </c>
     </row>
     <row r="752">
@@ -33849,22 +33849,22 @@
         <v>0</v>
       </c>
       <c r="L752" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M752" t="n">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="N752" t="n">
-        <v>2060.1607096774</v>
+        <v>2060.1606493506</v>
       </c>
       <c r="O752" t="n">
-        <v>228677.8387741914</v>
+        <v>220437.1894805142</v>
       </c>
       <c r="P752" t="n">
         <v>2900</v>
       </c>
       <c r="Q752" t="n">
-        <v>321900</v>
+        <v>310300</v>
       </c>
     </row>
     <row r="753">
@@ -33895,22 +33895,22 @@
         <v>0</v>
       </c>
       <c r="L753" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M753" t="n">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="N753" t="n">
-        <v>1668.6158441558</v>
+        <v>1668.6165143824</v>
       </c>
       <c r="O753" t="n">
-        <v>161855.7368831126</v>
+        <v>155181.3358375632</v>
       </c>
       <c r="P753" t="n">
         <v>2500</v>
       </c>
       <c r="Q753" t="n">
-        <v>242500</v>
+        <v>232500</v>
       </c>
     </row>
     <row r="754">
@@ -33987,22 +33987,22 @@
         <v>0</v>
       </c>
       <c r="L755" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M755" t="n">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="N755" t="n">
-        <v>1259.2744160105</v>
+        <v>1259.2744247206</v>
       </c>
       <c r="O755" t="n">
-        <v>307262.957506562</v>
+        <v>299707.3130835028</v>
       </c>
       <c r="P755" t="n">
         <v>1900</v>
       </c>
       <c r="Q755" t="n">
-        <v>463600</v>
+        <v>452200</v>
       </c>
     </row>
     <row r="756">
@@ -34166,22 +34166,22 @@
         <v>0</v>
       </c>
       <c r="L759" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M759" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="N759" t="n">
-        <v>2556.7449856734</v>
+        <v>2556.7450581395</v>
       </c>
       <c r="O759" t="n">
-        <v>294025.673352441</v>
+        <v>296582.426744182</v>
       </c>
       <c r="P759" t="n">
         <v>3900</v>
       </c>
       <c r="Q759" t="n">
-        <v>448500</v>
+        <v>452400</v>
       </c>
     </row>
     <row r="760">
@@ -34216,10 +34216,10 @@
         <v>254</v>
       </c>
       <c r="N760" t="n">
-        <v>692.15205253785</v>
+        <v>692.15206356312</v>
       </c>
       <c r="O760" t="n">
-        <v>175806.6213446139</v>
+        <v>175806.6241450325</v>
       </c>
       <c r="P760" t="n">
         <v>1200</v>
@@ -34303,22 +34303,22 @@
         <v>0</v>
       </c>
       <c r="L762" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M762" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="N762" t="n">
         <v>18491</v>
       </c>
       <c r="O762" t="n">
-        <v>166419</v>
+        <v>55473</v>
       </c>
       <c r="P762" t="n">
         <v>13500</v>
       </c>
       <c r="Q762" t="n">
-        <v>121500</v>
+        <v>40500</v>
       </c>
     </row>
     <row r="763">
@@ -34629,22 +34629,22 @@
         <v>0</v>
       </c>
       <c r="L769" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M769" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N769" t="n">
-        <v>1757.9454901961</v>
+        <v>1757.9455445545</v>
       </c>
       <c r="O769" t="n">
-        <v>68559.87411764791</v>
+        <v>66801.930693071</v>
       </c>
       <c r="P769" t="n">
         <v>1800</v>
       </c>
       <c r="Q769" t="n">
-        <v>70200</v>
+        <v>68400</v>
       </c>
     </row>
     <row r="770">
@@ -34765,22 +34765,22 @@
         <v>0</v>
       </c>
       <c r="L772" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M772" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="N772" t="n">
         <v>1337.86</v>
       </c>
       <c r="O772" t="n">
-        <v>48162.96</v>
+        <v>45487.24</v>
       </c>
       <c r="P772" t="n">
         <v>3000</v>
       </c>
       <c r="Q772" t="n">
-        <v>108000</v>
+        <v>102000</v>
       </c>
     </row>
     <row r="773">
@@ -35094,22 +35094,22 @@
         <v>0</v>
       </c>
       <c r="L779" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M779" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N779" t="n">
-        <v>3026.5146568627</v>
+        <v>3026.514679803</v>
       </c>
       <c r="O779" t="n">
-        <v>130140.1302450961</v>
+        <v>127113.616551726</v>
       </c>
       <c r="P779" t="n">
         <v>7000</v>
       </c>
       <c r="Q779" t="n">
-        <v>301000</v>
+        <v>294000</v>
       </c>
     </row>
     <row r="780">
@@ -35377,22 +35377,22 @@
         <v>0</v>
       </c>
       <c r="L785" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M785" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="N785" t="n">
         <v>1530.4499204138</v>
       </c>
       <c r="O785" t="n">
-        <v>33669.8982491036</v>
+        <v>42852.5977715864</v>
       </c>
       <c r="P785" t="n">
         <v>2600</v>
       </c>
       <c r="Q785" t="n">
-        <v>57200</v>
+        <v>72800</v>
       </c>
     </row>
     <row r="786">
@@ -36484,22 +36484,22 @@
         <v>0</v>
       </c>
       <c r="L809" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M809" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="N809" t="n">
         <v>2296.5708695652</v>
       </c>
       <c r="O809" t="n">
-        <v>105642.2599999992</v>
+        <v>119421.6852173904</v>
       </c>
       <c r="P809" t="n">
         <v>1900</v>
       </c>
       <c r="Q809" t="n">
-        <v>87400</v>
+        <v>98800</v>
       </c>
     </row>
     <row r="810">
@@ -37062,10 +37062,10 @@
         <v>3</v>
       </c>
       <c r="N821" t="n">
-        <v>3907.5003212851</v>
+        <v>3907.5003292181</v>
       </c>
       <c r="O821" t="n">
-        <v>11722.5009638553</v>
+        <v>11722.5009876543</v>
       </c>
       <c r="P821" t="n">
         <v>3900</v>
@@ -38149,22 +38149,22 @@
         <v>0</v>
       </c>
       <c r="L845" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="M845" t="n">
-        <v>1353</v>
+        <v>1349</v>
       </c>
       <c r="N845" t="n">
-        <v>517.28774146762</v>
+        <v>517.2878865955601</v>
       </c>
       <c r="O845" t="n">
-        <v>699890.3142056898</v>
+        <v>697821.3590174105</v>
       </c>
       <c r="P845" t="n">
         <v>900</v>
       </c>
       <c r="Q845" t="n">
-        <v>1217700</v>
+        <v>1214100</v>
       </c>
     </row>
     <row r="846">
@@ -38710,22 +38710,22 @@
         <v>0</v>
       </c>
       <c r="L857" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M857" t="n">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="N857" t="n">
-        <v>3110.8430699863</v>
+        <v>3110.8429819337</v>
       </c>
       <c r="O857" t="n">
-        <v>1110570.975985109</v>
+        <v>1098127.572622596</v>
       </c>
       <c r="P857" t="n">
         <v>4500</v>
       </c>
       <c r="Q857" t="n">
-        <v>1606500</v>
+        <v>1588500</v>
       </c>
     </row>
     <row r="858">
@@ -38893,22 +38893,22 @@
         <v>0</v>
       </c>
       <c r="L861" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M861" t="n">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="N861" t="n">
         <v>2030.02</v>
       </c>
       <c r="O861" t="n">
-        <v>381643.76</v>
+        <v>357283.52</v>
       </c>
       <c r="P861" t="n">
         <v>3600</v>
       </c>
       <c r="Q861" t="n">
-        <v>676800</v>
+        <v>633600</v>
       </c>
     </row>
     <row r="862">
@@ -39122,22 +39122,22 @@
         <v>0</v>
       </c>
       <c r="L866" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="M866" t="n">
-        <v>471</v>
+        <v>412</v>
       </c>
       <c r="N866" t="n">
-        <v>703.79541200942</v>
+        <v>703.79538564105</v>
       </c>
       <c r="O866" t="n">
-        <v>331487.6390564368</v>
+        <v>289963.6988841126</v>
       </c>
       <c r="P866" t="n">
         <v>900</v>
       </c>
       <c r="Q866" t="n">
-        <v>423900</v>
+        <v>370800</v>
       </c>
     </row>
     <row r="867">
@@ -39496,22 +39496,22 @@
         <v>0</v>
       </c>
       <c r="L874" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M874" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N874" t="n">
-        <v>2501.385443038</v>
+        <v>2501.3854237288</v>
       </c>
       <c r="O874" t="n">
-        <v>27515.239873418</v>
+        <v>25013.854237288</v>
       </c>
       <c r="P874" t="n">
         <v>4100</v>
       </c>
       <c r="Q874" t="n">
-        <v>45100</v>
+        <v>41000</v>
       </c>
     </row>
     <row r="875">
@@ -39637,22 +39637,22 @@
         <v>0</v>
       </c>
       <c r="L877" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M877" t="n">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="N877" t="n">
         <v>3006.0208571429</v>
       </c>
       <c r="O877" t="n">
-        <v>396794.7531428628</v>
+        <v>414830.8782857202</v>
       </c>
       <c r="P877" t="n">
         <v>3900</v>
       </c>
       <c r="Q877" t="n">
-        <v>514800</v>
+        <v>538200</v>
       </c>
     </row>
     <row r="878">
@@ -39955,22 +39955,22 @@
         <v>0</v>
       </c>
       <c r="L884" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M884" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="N884" t="n">
         <v>1300</v>
       </c>
       <c r="O884" t="n">
-        <v>52000</v>
+        <v>44200</v>
       </c>
       <c r="P884" t="n">
         <v>2200</v>
       </c>
       <c r="Q884" t="n">
-        <v>88000</v>
+        <v>74800</v>
       </c>
     </row>
     <row r="885">
@@ -40191,10 +40191,10 @@
         <v>52</v>
       </c>
       <c r="N889" t="n">
-        <v>1595.5191323094</v>
+        <v>1595.5190941049</v>
       </c>
       <c r="O889" t="n">
-        <v>82966.99488008879</v>
+        <v>82966.99289345479</v>
       </c>
       <c r="P889" t="n">
         <v>2500</v>
@@ -40234,22 +40234,22 @@
         <v>0</v>
       </c>
       <c r="L890" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M890" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N890" t="n">
         <v>7923.7</v>
       </c>
       <c r="O890" t="n">
-        <v>71313.3</v>
+        <v>55465.9</v>
       </c>
       <c r="P890" t="n">
         <v>16600</v>
       </c>
       <c r="Q890" t="n">
-        <v>149400</v>
+        <v>116200</v>
       </c>
     </row>
     <row r="891">
@@ -41248,22 +41248,22 @@
         <v>0</v>
       </c>
       <c r="L911" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M911" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="N911" t="n">
         <v>3057.26</v>
       </c>
       <c r="O911" t="n">
-        <v>122290.4</v>
+        <v>110061.36</v>
       </c>
       <c r="P911" t="n">
         <v>4900</v>
       </c>
       <c r="Q911" t="n">
-        <v>196000</v>
+        <v>176400</v>
       </c>
     </row>
     <row r="912">
@@ -41297,22 +41297,22 @@
         <v>0</v>
       </c>
       <c r="L912" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M912" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N912" t="n">
-        <v>2832.1946575342</v>
+        <v>2832.1948571429</v>
       </c>
       <c r="O912" t="n">
-        <v>16993.1679452052</v>
+        <v>8496.584571428701</v>
       </c>
       <c r="P912" t="n">
         <v>12900</v>
       </c>
       <c r="Q912" t="n">
-        <v>77400</v>
+        <v>38700</v>
       </c>
     </row>
     <row r="913">
@@ -41390,22 +41390,22 @@
         <v>0</v>
       </c>
       <c r="L914" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M914" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N914" t="n">
         <v>26586.06</v>
       </c>
       <c r="O914" t="n">
-        <v>26586.06</v>
+        <v>0</v>
       </c>
       <c r="P914" t="n">
         <v>70900</v>
       </c>
       <c r="Q914" t="n">
-        <v>70900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="915">
@@ -41819,22 +41819,22 @@
         <v>0</v>
       </c>
       <c r="L923" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M923" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N923" t="n">
         <v>10536.4</v>
       </c>
       <c r="O923" t="n">
-        <v>63218.39999999999</v>
+        <v>52682</v>
       </c>
       <c r="P923" t="n">
         <v>16900</v>
       </c>
       <c r="Q923" t="n">
-        <v>101400</v>
+        <v>84500</v>
       </c>
     </row>
     <row r="924">
@@ -42257,22 +42257,22 @@
         <v>0</v>
       </c>
       <c r="L932" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M932" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N932" t="n">
-        <v>23475.658125</v>
+        <v>23475.658064516</v>
       </c>
       <c r="O932" t="n">
-        <v>140853.94875</v>
+        <v>117378.29032258</v>
       </c>
       <c r="P932" t="n">
         <v>31900</v>
       </c>
       <c r="Q932" t="n">
-        <v>191400</v>
+        <v>159500</v>
       </c>
     </row>
     <row r="933">
@@ -42355,22 +42355,22 @@
         <v>0</v>
       </c>
       <c r="L934" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M934" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="N934" t="n">
-        <v>5796.334</v>
+        <v>5796.3343478261</v>
       </c>
       <c r="O934" t="n">
-        <v>127519.348</v>
+        <v>115926.686956522</v>
       </c>
       <c r="P934" t="n">
         <v>15900</v>
       </c>
       <c r="Q934" t="n">
-        <v>349800</v>
+        <v>318000</v>
       </c>
     </row>
     <row r="935">
@@ -42793,22 +42793,22 @@
         <v>0</v>
       </c>
       <c r="L943" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M943" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="N943" t="n">
         <v>11352.65</v>
       </c>
       <c r="O943" t="n">
-        <v>136231.8</v>
+        <v>90821.2</v>
       </c>
       <c r="P943" t="n">
         <v>14900</v>
       </c>
       <c r="Q943" t="n">
-        <v>178800</v>
+        <v>119200</v>
       </c>
     </row>
     <row r="944">
@@ -42894,10 +42894,10 @@
         <v>22</v>
       </c>
       <c r="N945" t="n">
-        <v>875.69015686275</v>
+        <v>875.69016</v>
       </c>
       <c r="O945" t="n">
-        <v>19265.1834509805</v>
+        <v>19265.18352</v>
       </c>
       <c r="P945" t="n">
         <v>4500</v>
@@ -42983,25 +42983,25 @@
         <v>25</v>
       </c>
       <c r="K947" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L947" t="n">
         <v>0</v>
       </c>
       <c r="M947" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N947" t="n">
         <v>6989.34</v>
       </c>
       <c r="O947" t="n">
-        <v>174733.5</v>
+        <v>209680.2</v>
       </c>
       <c r="P947" t="n">
         <v>10900</v>
       </c>
       <c r="Q947" t="n">
-        <v>272500</v>
+        <v>327000</v>
       </c>
     </row>
     <row r="948">
@@ -43127,25 +43127,25 @@
         <v>22</v>
       </c>
       <c r="K950" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L950" t="n">
         <v>0</v>
       </c>
       <c r="M950" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="N950" t="n">
         <v>4568.55</v>
       </c>
       <c r="O950" t="n">
-        <v>100508.1</v>
+        <v>137056.5</v>
       </c>
       <c r="P950" t="n">
         <v>6900</v>
       </c>
       <c r="Q950" t="n">
-        <v>151800</v>
+        <v>207000</v>
       </c>
     </row>
     <row r="951">
@@ -43463,10 +43463,10 @@
         <v>8</v>
       </c>
       <c r="N957" t="n">
-        <v>3067.0905341246</v>
+        <v>3067.0905389222</v>
       </c>
       <c r="O957" t="n">
-        <v>24536.7242729968</v>
+        <v>24536.7243113776</v>
       </c>
       <c r="P957" t="n">
         <v>7200</v>
@@ -43705,10 +43705,10 @@
         <v>36</v>
       </c>
       <c r="N962" t="n">
-        <v>4190.77</v>
+        <v>4205.0243197279</v>
       </c>
       <c r="O962" t="n">
-        <v>150867.72</v>
+        <v>151380.8755102044</v>
       </c>
       <c r="P962" t="n">
         <v>5900</v>
@@ -43754,10 +43754,10 @@
         <v>16</v>
       </c>
       <c r="N963" t="n">
-        <v>3499.72</v>
+        <v>3508.0033609467</v>
       </c>
       <c r="O963" t="n">
-        <v>55995.52</v>
+        <v>56128.0537751472</v>
       </c>
       <c r="P963" t="n">
         <v>6900</v>
@@ -44043,10 +44043,10 @@
         <v>13</v>
       </c>
       <c r="N969" t="n">
-        <v>1783.7988868778</v>
+        <v>1783.7988843537</v>
       </c>
       <c r="O969" t="n">
-        <v>23189.3855294114</v>
+        <v>23189.3854965981</v>
       </c>
       <c r="P969" t="n">
         <v>1500</v>
@@ -44859,10 +44859,10 @@
         <v>11</v>
       </c>
       <c r="N986" t="n">
-        <v>10737.526727273</v>
+        <v>10737.526666667</v>
       </c>
       <c r="O986" t="n">
-        <v>118112.794000003</v>
+        <v>118112.793333337</v>
       </c>
       <c r="P986" t="n">
         <v>18900</v>
@@ -46040,22 +46040,22 @@
         <v>0</v>
       </c>
       <c r="L1011" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1011" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N1011" t="n">
-        <v>14327.781538462</v>
+        <v>14327.781818182</v>
       </c>
       <c r="O1011" t="n">
-        <v>186261.160000006</v>
+        <v>157605.600000002</v>
       </c>
       <c r="P1011" t="n">
         <v>29900</v>
       </c>
       <c r="Q1011" t="n">
-        <v>388700</v>
+        <v>328900</v>
       </c>
     </row>
     <row r="1012">
@@ -46176,22 +46176,22 @@
         <v>0</v>
       </c>
       <c r="L1014" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1014" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N1014" t="n">
         <v>8671.389999999999</v>
       </c>
       <c r="O1014" t="n">
-        <v>8671.389999999999</v>
+        <v>0</v>
       </c>
       <c r="P1014" t="n">
         <v>20500</v>
       </c>
       <c r="Q1014" t="n">
-        <v>20500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1015">
@@ -46225,22 +46225,22 @@
         <v>0</v>
       </c>
       <c r="L1015" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1015" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N1015" t="n">
         <v>1024.29</v>
       </c>
       <c r="O1015" t="n">
-        <v>24582.96</v>
+        <v>23558.67</v>
       </c>
       <c r="P1015" t="n">
         <v>2900</v>
       </c>
       <c r="Q1015" t="n">
-        <v>69600</v>
+        <v>66700</v>
       </c>
     </row>
     <row r="1016">
@@ -46471,10 +46471,10 @@
         <v>24</v>
       </c>
       <c r="N1020" t="n">
-        <v>1934.77</v>
+        <v>1942.8822431866</v>
       </c>
       <c r="O1020" t="n">
-        <v>46434.48</v>
+        <v>46629.1738364784</v>
       </c>
       <c r="P1020" t="n">
         <v>8900</v>
@@ -46609,25 +46609,25 @@
         <v>46</v>
       </c>
       <c r="K1023" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="L1023" t="n">
         <v>0</v>
       </c>
       <c r="M1023" t="n">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="N1023" t="n">
-        <v>7046.9398302567</v>
+        <v>7046.9398299681</v>
       </c>
       <c r="O1023" t="n">
-        <v>324159.2321918082</v>
+        <v>535567.4270775756</v>
       </c>
       <c r="P1023" t="n">
         <v>9900</v>
       </c>
       <c r="Q1023" t="n">
-        <v>455400</v>
+        <v>752400</v>
       </c>
     </row>
     <row r="1024">
@@ -46713,10 +46713,10 @@
         <v>8</v>
       </c>
       <c r="N1025" t="n">
-        <v>26378.027272727</v>
+        <v>26378.027</v>
       </c>
       <c r="O1025" t="n">
-        <v>211024.218181816</v>
+        <v>211024.216</v>
       </c>
       <c r="P1025" t="n">
         <v>36500</v>
@@ -47249,10 +47249,10 @@
         <v>255</v>
       </c>
       <c r="N1036" t="n">
-        <v>665.32333760137</v>
+        <v>665.32334188034</v>
       </c>
       <c r="O1036" t="n">
-        <v>169657.4510883493</v>
+        <v>169657.4521794867</v>
       </c>
       <c r="P1036" t="n">
         <v>2900</v>
@@ -47577,25 +47577,25 @@
         <v>7</v>
       </c>
       <c r="K1043" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L1043" t="n">
         <v>0</v>
       </c>
       <c r="M1043" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="N1043" t="n">
         <v>4581.84</v>
       </c>
       <c r="O1043" t="n">
-        <v>32072.88</v>
+        <v>142037.04</v>
       </c>
       <c r="P1043" t="n">
         <v>7900</v>
       </c>
       <c r="Q1043" t="n">
-        <v>55300</v>
+        <v>244900</v>
       </c>
     </row>
     <row r="1044">
@@ -47724,22 +47724,22 @@
         <v>0</v>
       </c>
       <c r="L1046" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1046" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N1046" t="n">
-        <v>540.4025</v>
+        <v>540.40252525253</v>
       </c>
       <c r="O1046" t="n">
-        <v>20535.295</v>
+        <v>19994.89343434361</v>
       </c>
       <c r="P1046" t="n">
         <v>2500</v>
       </c>
       <c r="Q1046" t="n">
-        <v>95000</v>
+        <v>92500</v>
       </c>
     </row>
     <row r="1047">
@@ -47975,10 +47975,10 @@
         <v>28</v>
       </c>
       <c r="N1051" t="n">
-        <v>315.02678272981</v>
+        <v>315.02679218968</v>
       </c>
       <c r="O1051" t="n">
-        <v>8820.749916434681</v>
+        <v>8820.750181311039</v>
       </c>
       <c r="P1051" t="n">
         <v>2200</v>
@@ -48051,22 +48051,22 @@
         <v>0</v>
       </c>
       <c r="L1053" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1053" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="N1053" t="n">
         <v>2752.52</v>
       </c>
       <c r="O1053" t="n">
-        <v>154141.12</v>
+        <v>148636.08</v>
       </c>
       <c r="P1053" t="n">
         <v>4500</v>
       </c>
       <c r="Q1053" t="n">
-        <v>252000</v>
+        <v>243000</v>
       </c>
     </row>
     <row r="1054">
@@ -48405,10 +48405,10 @@
         <v>19</v>
       </c>
       <c r="N1061" t="n">
-        <v>5577.2680821918</v>
+        <v>5577.2680778032</v>
       </c>
       <c r="O1061" t="n">
-        <v>105968.0935616442</v>
+        <v>105968.0934782608</v>
       </c>
       <c r="P1061" t="n">
         <v>6500</v>
@@ -48748,25 +48748,25 @@
         <v>453</v>
       </c>
       <c r="K1069" t="n">
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="L1069" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M1069" t="n">
-        <v>453</v>
+        <v>663</v>
       </c>
       <c r="N1069" t="n">
         <v>1176.57</v>
       </c>
       <c r="O1069" t="n">
-        <v>532986.21</v>
+        <v>780065.9099999999</v>
       </c>
       <c r="P1069" t="n">
         <v>1900</v>
       </c>
       <c r="Q1069" t="n">
-        <v>860700</v>
+        <v>1259700</v>
       </c>
     </row>
     <row r="1070">
@@ -48795,22 +48795,22 @@
         <v>0</v>
       </c>
       <c r="L1070" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M1070" t="n">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="N1070" t="n">
         <v>3181.9</v>
       </c>
       <c r="O1070" t="n">
-        <v>305462.4</v>
+        <v>289552.9</v>
       </c>
       <c r="P1070" t="n">
         <v>5100</v>
       </c>
       <c r="Q1070" t="n">
-        <v>489600</v>
+        <v>464100</v>
       </c>
     </row>
     <row r="1071">
@@ -48842,10 +48842,10 @@
         <v>16</v>
       </c>
       <c r="N1071" t="n">
-        <v>1213.6821194605</v>
+        <v>1213.6821442495</v>
       </c>
       <c r="O1071" t="n">
-        <v>19418.913911368</v>
+        <v>19418.914307992</v>
       </c>
       <c r="P1071" t="n">
         <v>1500</v>
@@ -48886,10 +48886,10 @@
         <v>50</v>
       </c>
       <c r="N1072" t="n">
-        <v>1794.2879773671</v>
+        <v>1794.2879767875</v>
       </c>
       <c r="O1072" t="n">
-        <v>89714.398868355</v>
+        <v>89714.39883937499</v>
       </c>
       <c r="P1072" t="n">
         <v>1600</v>
@@ -49287,25 +49287,25 @@
         <v>1</v>
       </c>
       <c r="K1081" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L1081" t="n">
         <v>0</v>
       </c>
       <c r="M1081" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="N1081" t="n">
         <v>22951.704968711</v>
       </c>
       <c r="O1081" t="n">
-        <v>22951.704968711</v>
+        <v>160661.934780977</v>
       </c>
       <c r="P1081" t="n">
         <v>37900</v>
       </c>
       <c r="Q1081" t="n">
-        <v>37900</v>
+        <v>265300</v>
       </c>
     </row>
     <row r="1082">
@@ -49534,10 +49534,10 @@
         <v>51</v>
       </c>
       <c r="N1086" t="n">
-        <v>1757.3205295316</v>
+        <v>1757.3205360825</v>
       </c>
       <c r="O1086" t="n">
-        <v>89623.34700611159</v>
+        <v>89623.3473402075</v>
       </c>
       <c r="P1086" t="n">
         <v>2000</v>
@@ -50540,25 +50540,25 @@
         <v>450</v>
       </c>
       <c r="K1108" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="L1108" t="n">
         <v>0</v>
       </c>
       <c r="M1108" t="n">
-        <v>450</v>
+        <v>650</v>
       </c>
       <c r="N1108" t="n">
         <v>220.00820587826</v>
       </c>
       <c r="O1108" t="n">
-        <v>99003.69264521699</v>
+        <v>143005.333820869</v>
       </c>
       <c r="P1108" t="n">
         <v>260</v>
       </c>
       <c r="Q1108" t="n">
-        <v>117000</v>
+        <v>169000</v>
       </c>
     </row>
     <row r="1109">
@@ -50911,22 +50911,22 @@
         <v>0</v>
       </c>
       <c r="L1116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1116" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N1116" t="n">
         <v>3504.16</v>
       </c>
       <c r="O1116" t="n">
-        <v>66579.03999999999</v>
+        <v>63074.88</v>
       </c>
       <c r="P1116" t="n">
         <v>3900</v>
       </c>
       <c r="Q1116" t="n">
-        <v>74100</v>
+        <v>70200</v>
       </c>
     </row>
     <row r="1117">
@@ -50957,22 +50957,22 @@
         <v>0</v>
       </c>
       <c r="L1117" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M1117" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="N1117" t="n">
         <v>12000</v>
       </c>
       <c r="O1117" t="n">
-        <v>120000</v>
+        <v>72000</v>
       </c>
       <c r="P1117" t="n">
         <v>15000</v>
       </c>
       <c r="Q1117" t="n">
-        <v>150000</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="1118">
@@ -51184,25 +51184,25 @@
         <v>40</v>
       </c>
       <c r="K1122" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L1122" t="n">
         <v>0</v>
       </c>
       <c r="M1122" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="N1122" t="n">
         <v>1952.66</v>
       </c>
       <c r="O1122" t="n">
-        <v>78106.40000000001</v>
+        <v>101538.32</v>
       </c>
       <c r="P1122" t="n">
         <v>3500</v>
       </c>
       <c r="Q1122" t="n">
-        <v>140000</v>
+        <v>182000</v>
       </c>
     </row>
     <row r="1123">
@@ -51509,22 +51509,22 @@
         <v>0</v>
       </c>
       <c r="L1129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1129" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N1129" t="n">
         <v>1952.41</v>
       </c>
       <c r="O1129" t="n">
-        <v>66381.94</v>
+        <v>64429.53000000001</v>
       </c>
       <c r="P1129" t="n">
         <v>2700</v>
       </c>
       <c r="Q1129" t="n">
-        <v>91800</v>
+        <v>89100</v>
       </c>
     </row>
     <row r="1130">
@@ -51601,22 +51601,22 @@
         <v>0</v>
       </c>
       <c r="L1131" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1131" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N1131" t="n">
-        <v>9855.0382758621</v>
+        <v>9855.0381481481</v>
       </c>
       <c r="O1131" t="n">
-        <v>59130.2296551726</v>
+        <v>39420.1525925924</v>
       </c>
       <c r="P1131" t="n">
         <v>15500</v>
       </c>
       <c r="Q1131" t="n">
-        <v>93000</v>
+        <v>62000</v>
       </c>
     </row>
     <row r="1132">
@@ -53395,22 +53395,22 @@
         <v>0</v>
       </c>
       <c r="L1170" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1170" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N1170" t="n">
         <v>32.41</v>
       </c>
       <c r="O1170" t="n">
-        <v>324.1</v>
+        <v>259.28</v>
       </c>
       <c r="P1170" t="n">
         <v>13500</v>
       </c>
       <c r="Q1170" t="n">
-        <v>135000</v>
+        <v>108000</v>
       </c>
     </row>
     <row r="1171">
@@ -53441,22 +53441,22 @@
         <v>0</v>
       </c>
       <c r="L1171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1171" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N1171" t="n">
-        <v>970.63142857143</v>
+        <v>970.63153846154</v>
       </c>
       <c r="O1171" t="n">
-        <v>8735.68285714287</v>
+        <v>7765.05230769232</v>
       </c>
       <c r="P1171" t="n">
         <v>7200</v>
       </c>
       <c r="Q1171" t="n">
-        <v>64800</v>
+        <v>57600</v>
       </c>
     </row>
     <row r="1172">
@@ -53641,10 +53641,10 @@
         <v>49</v>
       </c>
       <c r="N1175" t="n">
-        <v>1236.3</v>
+        <v>1242.6076530612</v>
       </c>
       <c r="O1175" t="n">
-        <v>60578.7</v>
+        <v>60887.77499999879</v>
       </c>
       <c r="P1175" t="n">
         <v>2300</v>
@@ -53727,22 +53727,22 @@
         <v>0</v>
       </c>
       <c r="L1177" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1177" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N1177" t="n">
         <v>11433.53</v>
       </c>
       <c r="O1177" t="n">
-        <v>80034.71000000001</v>
+        <v>57167.65</v>
       </c>
       <c r="P1177" t="n">
         <v>15000</v>
       </c>
       <c r="Q1177" t="n">
-        <v>105000</v>
+        <v>75000</v>
       </c>
     </row>
     <row r="1178">
@@ -54207,22 +54207,22 @@
         <v>0</v>
       </c>
       <c r="L1187" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1187" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N1187" t="n">
-        <v>227.41596785975</v>
+        <v>227.41597222222</v>
       </c>
       <c r="O1187" t="n">
-        <v>4320.90338933525</v>
+        <v>4093.48749999996</v>
       </c>
       <c r="P1187" t="n">
         <v>1200</v>
       </c>
       <c r="Q1187" t="n">
-        <v>22800</v>
+        <v>21600</v>
       </c>
     </row>
     <row r="1188">
@@ -54908,10 +54908,10 @@
         <v>34</v>
       </c>
       <c r="N1202" t="n">
-        <v>3306.0098310139</v>
+        <v>3306.00983</v>
       </c>
       <c r="O1202" t="n">
-        <v>112404.3342544726</v>
+        <v>112404.33422</v>
       </c>
       <c r="P1202" t="n">
         <v>4200</v>
@@ -57563,22 +57563,22 @@
         <v>0</v>
       </c>
       <c r="L1260" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M1260" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="N1260" t="n">
         <v>12720</v>
       </c>
       <c r="O1260" t="n">
-        <v>127200</v>
+        <v>165360</v>
       </c>
       <c r="P1260" t="n">
         <v>15900</v>
       </c>
       <c r="Q1260" t="n">
-        <v>159000</v>
+        <v>206700</v>
       </c>
     </row>
     <row r="1261">

--- a/bodegas/LJ-101.xlsx
+++ b/bodegas/LJ-101.xlsx
@@ -938,22 +938,22 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="M13" t="n">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="N13" t="n">
-        <v>1811.3044829343</v>
+        <v>1811.3047800109</v>
       </c>
       <c r="O13" t="n">
-        <v>128602.6182883353</v>
+        <v>86942.6294405232</v>
       </c>
       <c r="P13" t="n">
         <v>2600</v>
       </c>
       <c r="Q13" t="n">
-        <v>184600</v>
+        <v>124800</v>
       </c>
     </row>
     <row r="14">
@@ -1022,10 +1022,10 @@
         <v>50</v>
       </c>
       <c r="N15" t="n">
-        <v>3376.746498645</v>
+        <v>3376.7464976959</v>
       </c>
       <c r="O15" t="n">
-        <v>168837.32493225</v>
+        <v>168837.324884795</v>
       </c>
       <c r="P15" t="n">
         <v>4500</v>
@@ -2027,10 +2027,10 @@
         <v>11</v>
       </c>
       <c r="N40" t="n">
-        <v>2413.0010615711</v>
+        <v>2413.0010626993</v>
       </c>
       <c r="O40" t="n">
-        <v>26543.0116772821</v>
+        <v>26543.0116896923</v>
       </c>
       <c r="P40" t="n">
         <v>4700</v>
@@ -2066,10 +2066,10 @@
         <v>6</v>
       </c>
       <c r="N41" t="n">
-        <v>2474.7042043551</v>
+        <v>2474.7041652614</v>
       </c>
       <c r="O41" t="n">
-        <v>14848.2252261306</v>
+        <v>14848.2249915684</v>
       </c>
       <c r="P41" t="n">
         <v>4500</v>
@@ -2450,22 +2450,22 @@
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M51" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N51" t="n">
-        <v>14857.623185841</v>
+        <v>14857.6232</v>
       </c>
       <c r="O51" t="n">
-        <v>133718.608672569</v>
+        <v>118860.9856</v>
       </c>
       <c r="P51" t="n">
         <v>34900</v>
       </c>
       <c r="Q51" t="n">
-        <v>314100</v>
+        <v>279200</v>
       </c>
     </row>
     <row r="52">
@@ -3275,10 +3275,10 @@
         <v>5</v>
       </c>
       <c r="N69" t="n">
-        <v>28751.742258065</v>
+        <v>28751.742333333</v>
       </c>
       <c r="O69" t="n">
-        <v>143758.711290325</v>
+        <v>143758.711666665</v>
       </c>
       <c r="P69" t="n">
         <v>34800</v>
@@ -3576,22 +3576,22 @@
         <v>0</v>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M76" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N76" t="n">
-        <v>17085.54</v>
+        <v>17085.518571429</v>
       </c>
       <c r="O76" t="n">
-        <v>136684.32</v>
+        <v>119598.630000003</v>
       </c>
       <c r="P76" t="n">
         <v>29200</v>
       </c>
       <c r="Q76" t="n">
-        <v>233600</v>
+        <v>204400</v>
       </c>
     </row>
     <row r="77">
@@ -3699,22 +3699,22 @@
         <v>0</v>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M79" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N79" t="n">
         <v>36762.36</v>
       </c>
       <c r="O79" t="n">
-        <v>588197.76</v>
+        <v>551435.4</v>
       </c>
       <c r="P79" t="n">
         <v>57100</v>
       </c>
       <c r="Q79" t="n">
-        <v>913600</v>
+        <v>856500</v>
       </c>
     </row>
     <row r="80">
@@ -3919,10 +3919,10 @@
         <v>1</v>
       </c>
       <c r="N84" t="n">
-        <v>7407.7300524934</v>
+        <v>7407.7300526316</v>
       </c>
       <c r="O84" t="n">
-        <v>7407.7300524934</v>
+        <v>7407.7300526316</v>
       </c>
       <c r="P84" t="n">
         <v>10900</v>
@@ -4075,10 +4075,10 @@
         <v>4</v>
       </c>
       <c r="N88" t="n">
-        <v>14708.815744681</v>
+        <v>14708.815698925</v>
       </c>
       <c r="O88" t="n">
-        <v>58835.262978724</v>
+        <v>58835.2627957</v>
       </c>
       <c r="P88" t="n">
         <v>16900</v>
@@ -4698,10 +4698,10 @@
         <v>6</v>
       </c>
       <c r="N102" t="n">
-        <v>200072.2</v>
+        <v>200072.20007812</v>
       </c>
       <c r="O102" t="n">
-        <v>1200433.2</v>
+        <v>1200433.20046872</v>
       </c>
       <c r="P102" t="n">
         <v>312000</v>
@@ -4864,22 +4864,22 @@
         <v>0</v>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M106" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="N106" t="n">
         <v>1977.88</v>
       </c>
       <c r="O106" t="n">
-        <v>136473.72</v>
+        <v>134495.84</v>
       </c>
       <c r="P106" t="n">
         <v>2900</v>
       </c>
       <c r="Q106" t="n">
-        <v>200100</v>
+        <v>197200</v>
       </c>
     </row>
     <row r="107">
@@ -5101,10 +5101,10 @@
         <v>1</v>
       </c>
       <c r="N112" t="n">
-        <v>61666.873994709</v>
+        <v>61666.874005305</v>
       </c>
       <c r="O112" t="n">
-        <v>61666.873994709</v>
+        <v>61666.874005305</v>
       </c>
       <c r="P112" t="n">
         <v>98900</v>
@@ -6372,22 +6372,22 @@
         <v>0</v>
       </c>
       <c r="L141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M141" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N141" t="n">
         <v>2791.02</v>
       </c>
       <c r="O141" t="n">
-        <v>86521.62</v>
+        <v>83730.60000000001</v>
       </c>
       <c r="P141" t="n">
         <v>3900</v>
       </c>
       <c r="Q141" t="n">
-        <v>120900</v>
+        <v>117000</v>
       </c>
     </row>
     <row r="142">
@@ -7391,10 +7391,10 @@
         <v>27</v>
       </c>
       <c r="N164" t="n">
-        <v>732.63413793103</v>
+        <v>732.63415224913</v>
       </c>
       <c r="O164" t="n">
-        <v>19781.12172413781</v>
+        <v>19781.12211072651</v>
       </c>
       <c r="P164" t="n">
         <v>6200</v>
@@ -7911,10 +7911,10 @@
         <v>108</v>
       </c>
       <c r="N176" t="n">
-        <v>4937.3101611722</v>
+        <v>4937.3101612903</v>
       </c>
       <c r="O176" t="n">
-        <v>533229.4974065976</v>
+        <v>533229.4974193524</v>
       </c>
       <c r="P176" t="n">
         <v>7500</v>
@@ -8197,25 +8197,25 @@
         <v>296</v>
       </c>
       <c r="K183" t="n">
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="L183" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="M183" t="n">
-        <v>290</v>
+        <v>559</v>
       </c>
       <c r="N183" t="n">
-        <v>1098.0555939754</v>
+        <v>1098.055952691</v>
       </c>
       <c r="O183" t="n">
-        <v>318436.122252866</v>
+        <v>613813.2775542689</v>
       </c>
       <c r="P183" t="n">
         <v>1500</v>
       </c>
       <c r="Q183" t="n">
-        <v>435000</v>
+        <v>838500</v>
       </c>
     </row>
     <row r="184">
@@ -8513,22 +8513,22 @@
         <v>0</v>
       </c>
       <c r="L190" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M190" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="N190" t="n">
         <v>2189</v>
       </c>
       <c r="O190" t="n">
-        <v>63481</v>
+        <v>59103</v>
       </c>
       <c r="P190" t="n">
         <v>4500</v>
       </c>
       <c r="Q190" t="n">
-        <v>130500</v>
+        <v>121500</v>
       </c>
     </row>
     <row r="191">
@@ -9169,22 +9169,22 @@
         <v>0</v>
       </c>
       <c r="L205" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M205" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N205" t="n">
         <v>3247</v>
       </c>
       <c r="O205" t="n">
-        <v>32470</v>
+        <v>29223</v>
       </c>
       <c r="P205" t="n">
         <v>5200</v>
       </c>
       <c r="Q205" t="n">
-        <v>52000</v>
+        <v>46800</v>
       </c>
     </row>
     <row r="206">
@@ -9215,22 +9215,22 @@
         <v>0</v>
       </c>
       <c r="L206" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M206" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="N206" t="n">
-        <v>2582.2560112135</v>
+        <v>2582.2559895309</v>
       </c>
       <c r="O206" t="n">
-        <v>167846.6407288775</v>
+        <v>160099.8713509158</v>
       </c>
       <c r="P206" t="n">
         <v>4500</v>
       </c>
       <c r="Q206" t="n">
-        <v>292500</v>
+        <v>279000</v>
       </c>
     </row>
     <row r="207">
@@ -9258,25 +9258,25 @@
         <v>4</v>
       </c>
       <c r="K207" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="L207" t="n">
         <v>0</v>
       </c>
       <c r="M207" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="N207" t="n">
         <v>8138.14</v>
       </c>
       <c r="O207" t="n">
-        <v>32552.56</v>
+        <v>187177.22</v>
       </c>
       <c r="P207" t="n">
         <v>13500</v>
       </c>
       <c r="Q207" t="n">
-        <v>54000</v>
+        <v>310500</v>
       </c>
     </row>
     <row r="208">
@@ -9359,10 +9359,10 @@
         <v>2</v>
       </c>
       <c r="N209" t="n">
-        <v>5216.8959654608</v>
+        <v>5216.8959618537</v>
       </c>
       <c r="O209" t="n">
-        <v>10433.7919309216</v>
+        <v>10433.7919237074</v>
       </c>
       <c r="P209" t="n">
         <v>8500</v>
@@ -9399,22 +9399,22 @@
         <v>0</v>
       </c>
       <c r="L210" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M210" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="N210" t="n">
-        <v>2033.5670707071</v>
+        <v>2033.5662758621</v>
       </c>
       <c r="O210" t="n">
-        <v>69141.28040404139</v>
+        <v>65074.1208275872</v>
       </c>
       <c r="P210" t="n">
         <v>4100</v>
       </c>
       <c r="Q210" t="n">
-        <v>139400</v>
+        <v>131200</v>
       </c>
     </row>
     <row r="211">
@@ -9671,22 +9671,22 @@
         <v>0</v>
       </c>
       <c r="L216" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M216" t="n">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="N216" t="n">
-        <v>3158.860814779</v>
+        <v>3158.8608154486</v>
       </c>
       <c r="O216" t="n">
-        <v>1228796.856949031</v>
+        <v>1225637.996394057</v>
       </c>
       <c r="P216" t="n">
         <v>5600</v>
       </c>
       <c r="Q216" t="n">
-        <v>2178400</v>
+        <v>2172800</v>
       </c>
     </row>
     <row r="217">
@@ -9899,22 +9899,22 @@
         <v>0</v>
       </c>
       <c r="L221" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M221" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="N221" t="n">
-        <v>3230.0677414075</v>
+        <v>3230.0677302632</v>
       </c>
       <c r="O221" t="n">
-        <v>274555.7580196375</v>
+        <v>268095.6216118456</v>
       </c>
       <c r="P221" t="n">
         <v>6200</v>
       </c>
       <c r="Q221" t="n">
-        <v>527000</v>
+        <v>514600</v>
       </c>
     </row>
     <row r="222">
@@ -10083,22 +10083,22 @@
         <v>0</v>
       </c>
       <c r="L225" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M225" t="n">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="N225" t="n">
-        <v>2694.8234565119</v>
+        <v>2694.8234059946</v>
       </c>
       <c r="O225" t="n">
-        <v>544354.3382154038</v>
+        <v>512016.447138974</v>
       </c>
       <c r="P225" t="n">
         <v>4900</v>
       </c>
       <c r="Q225" t="n">
-        <v>989800</v>
+        <v>931000</v>
       </c>
     </row>
     <row r="226">
@@ -10455,10 +10455,10 @@
         <v>36</v>
       </c>
       <c r="N233" t="n">
-        <v>3795.7100070621</v>
+        <v>3795.7100070671</v>
       </c>
       <c r="O233" t="n">
-        <v>136645.5602542356</v>
+        <v>136645.5602544156</v>
       </c>
       <c r="P233" t="n">
         <v>6200</v>
@@ -10671,19 +10671,19 @@
         <v>10</v>
       </c>
       <c r="K238" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L238" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M238" t="n">
         <v>10</v>
       </c>
       <c r="N238" t="n">
-        <v>4890.9300464306</v>
+        <v>4890.9300465929</v>
       </c>
       <c r="O238" t="n">
-        <v>48909.300464306</v>
+        <v>48909.300465929</v>
       </c>
       <c r="P238" t="n">
         <v>8200</v>
@@ -10720,22 +10720,22 @@
         <v>0</v>
       </c>
       <c r="L239" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M239" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="N239" t="n">
         <v>5613.75</v>
       </c>
       <c r="O239" t="n">
-        <v>89820</v>
+        <v>56137.5</v>
       </c>
       <c r="P239" t="n">
         <v>7900</v>
       </c>
       <c r="Q239" t="n">
-        <v>126400</v>
+        <v>79000</v>
       </c>
     </row>
     <row r="240">
@@ -10864,22 +10864,22 @@
         <v>0</v>
       </c>
       <c r="L242" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M242" t="n">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="N242" t="n">
         <v>1203.38</v>
       </c>
       <c r="O242" t="n">
-        <v>77016.32000000001</v>
+        <v>64982.52</v>
       </c>
       <c r="P242" t="n">
         <v>1900</v>
       </c>
       <c r="Q242" t="n">
-        <v>121600</v>
+        <v>102600</v>
       </c>
     </row>
     <row r="243">
@@ -10910,22 +10910,22 @@
         <v>0</v>
       </c>
       <c r="L243" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M243" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="N243" t="n">
         <v>5888</v>
       </c>
       <c r="O243" t="n">
-        <v>58880</v>
+        <v>11776</v>
       </c>
       <c r="P243" t="n">
         <v>9500</v>
       </c>
       <c r="Q243" t="n">
-        <v>95000</v>
+        <v>19000</v>
       </c>
     </row>
     <row r="244">
@@ -11040,19 +11040,19 @@
         <v>76</v>
       </c>
       <c r="K246" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L246" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M246" t="n">
         <v>76</v>
       </c>
       <c r="N246" t="n">
-        <v>2267.0481598668</v>
+        <v>2267.0481583333</v>
       </c>
       <c r="O246" t="n">
-        <v>172295.6601498768</v>
+        <v>172295.6600333308</v>
       </c>
       <c r="P246" t="n">
         <v>3900</v>
@@ -11227,22 +11227,22 @@
         <v>0</v>
       </c>
       <c r="L250" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M250" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="N250" t="n">
         <v>8012</v>
       </c>
       <c r="O250" t="n">
-        <v>88132</v>
+        <v>72108</v>
       </c>
       <c r="P250" t="n">
         <v>13200</v>
       </c>
       <c r="Q250" t="n">
-        <v>145200</v>
+        <v>118800</v>
       </c>
     </row>
     <row r="251">
@@ -11357,25 +11357,25 @@
         <v>15</v>
       </c>
       <c r="K253" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L253" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M253" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="N253" t="n">
         <v>10716.34</v>
       </c>
       <c r="O253" t="n">
-        <v>117879.74</v>
+        <v>96447.06</v>
       </c>
       <c r="P253" t="n">
         <v>39000</v>
       </c>
       <c r="Q253" t="n">
-        <v>429000</v>
+        <v>351000</v>
       </c>
     </row>
     <row r="254">
@@ -11450,22 +11450,22 @@
         <v>0</v>
       </c>
       <c r="L255" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M255" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="N255" t="n">
-        <v>3594.2541391941</v>
+        <v>3594.254124847</v>
       </c>
       <c r="O255" t="n">
-        <v>68290.82864468789</v>
+        <v>57508.065997552</v>
       </c>
       <c r="P255" t="n">
         <v>6500</v>
       </c>
       <c r="Q255" t="n">
-        <v>123500</v>
+        <v>104000</v>
       </c>
     </row>
     <row r="256">
@@ -11540,22 +11540,22 @@
         <v>0</v>
       </c>
       <c r="L257" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="M257" t="n">
-        <v>404</v>
+        <v>373</v>
       </c>
       <c r="N257" t="n">
         <v>489.88</v>
       </c>
       <c r="O257" t="n">
-        <v>197911.52</v>
+        <v>182725.24</v>
       </c>
       <c r="P257" t="n">
         <v>700</v>
       </c>
       <c r="Q257" t="n">
-        <v>282800</v>
+        <v>261100</v>
       </c>
     </row>
     <row r="258">
@@ -11663,22 +11663,22 @@
         <v>0</v>
       </c>
       <c r="L260" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M260" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="N260" t="n">
-        <v>3240.8500301659</v>
+        <v>3240.8500302572</v>
       </c>
       <c r="O260" t="n">
-        <v>440755.6041025624</v>
+        <v>434273.9040544648</v>
       </c>
       <c r="P260" t="n">
         <v>5200</v>
       </c>
       <c r="Q260" t="n">
-        <v>707200</v>
+        <v>696800</v>
       </c>
     </row>
     <row r="261">
@@ -11801,22 +11801,22 @@
         <v>0</v>
       </c>
       <c r="L263" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M263" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N263" t="n">
         <v>8154</v>
       </c>
       <c r="O263" t="n">
-        <v>154926</v>
+        <v>146772</v>
       </c>
       <c r="P263" t="n">
         <v>13500</v>
       </c>
       <c r="Q263" t="n">
-        <v>256500</v>
+        <v>243000</v>
       </c>
     </row>
     <row r="264">
@@ -11853,10 +11853,10 @@
         <v>12</v>
       </c>
       <c r="N264" t="n">
-        <v>14822.378862559</v>
+        <v>14822.378861885</v>
       </c>
       <c r="O264" t="n">
-        <v>177868.546350708</v>
+        <v>177868.54634262</v>
       </c>
       <c r="P264" t="n">
         <v>24900</v>
@@ -11940,22 +11940,22 @@
         <v>0</v>
       </c>
       <c r="L266" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="M266" t="n">
-        <v>260</v>
+        <v>234</v>
       </c>
       <c r="N266" t="n">
         <v>2090.85</v>
       </c>
       <c r="O266" t="n">
-        <v>543621</v>
+        <v>489258.9</v>
       </c>
       <c r="P266" t="n">
         <v>2900</v>
       </c>
       <c r="Q266" t="n">
-        <v>754000</v>
+        <v>678600</v>
       </c>
     </row>
     <row r="267">
@@ -12480,22 +12480,22 @@
         <v>0</v>
       </c>
       <c r="L278" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M278" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N278" t="n">
         <v>1381.75</v>
       </c>
       <c r="O278" t="n">
-        <v>48361.25</v>
+        <v>46979.5</v>
       </c>
       <c r="P278" t="n">
         <v>2500</v>
       </c>
       <c r="Q278" t="n">
-        <v>87500</v>
+        <v>85000</v>
       </c>
     </row>
     <row r="279">
@@ -12835,22 +12835,22 @@
         <v>0</v>
       </c>
       <c r="L286" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M286" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="N286" t="n">
         <v>4193.85</v>
       </c>
       <c r="O286" t="n">
-        <v>113233.95</v>
+        <v>96458.55</v>
       </c>
       <c r="P286" t="n">
         <v>7500</v>
       </c>
       <c r="Q286" t="n">
-        <v>202500</v>
+        <v>172500</v>
       </c>
     </row>
     <row r="287">
@@ -12884,22 +12884,22 @@
         <v>0</v>
       </c>
       <c r="L287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M287" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N287" t="n">
-        <v>3041.6600126502</v>
+        <v>3041.6600127551</v>
       </c>
       <c r="O287" t="n">
-        <v>79083.1603289052</v>
+        <v>76041.5003188775</v>
       </c>
       <c r="P287" t="n">
         <v>5500</v>
       </c>
       <c r="Q287" t="n">
-        <v>143000</v>
+        <v>137500</v>
       </c>
     </row>
     <row r="288">
@@ -13148,22 +13148,22 @@
         <v>0</v>
       </c>
       <c r="L293" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M293" t="n">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="N293" t="n">
-        <v>1592.5674522293</v>
+        <v>1592.5674</v>
       </c>
       <c r="O293" t="n">
-        <v>146516.2056050956</v>
+        <v>135368.229</v>
       </c>
       <c r="P293" t="n">
         <v>3900</v>
       </c>
       <c r="Q293" t="n">
-        <v>358800</v>
+        <v>331500</v>
       </c>
     </row>
     <row r="294">
@@ -13230,22 +13230,22 @@
         <v>0</v>
       </c>
       <c r="L295" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M295" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N295" t="n">
         <v>2224.56</v>
       </c>
       <c r="O295" t="n">
-        <v>40042.08</v>
+        <v>37817.52</v>
       </c>
       <c r="P295" t="n">
         <v>3900</v>
       </c>
       <c r="Q295" t="n">
-        <v>70200</v>
+        <v>66300</v>
       </c>
     </row>
     <row r="296">
@@ -13363,22 +13363,22 @@
         <v>0</v>
       </c>
       <c r="L298" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M298" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N298" t="n">
         <v>4717</v>
       </c>
       <c r="O298" t="n">
-        <v>89623</v>
+        <v>80189</v>
       </c>
       <c r="P298" t="n">
         <v>7900</v>
       </c>
       <c r="Q298" t="n">
-        <v>150100</v>
+        <v>134300</v>
       </c>
     </row>
     <row r="299">
@@ -13589,22 +13589,22 @@
         <v>0</v>
       </c>
       <c r="L303" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M303" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="N303" t="n">
         <v>4648.6</v>
       </c>
       <c r="O303" t="n">
-        <v>251024.4</v>
+        <v>237078.6</v>
       </c>
       <c r="P303" t="n">
         <v>8900</v>
       </c>
       <c r="Q303" t="n">
-        <v>480600</v>
+        <v>453900</v>
       </c>
     </row>
     <row r="304">
@@ -14033,22 +14033,22 @@
         <v>0</v>
       </c>
       <c r="L313" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M313" t="n">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="N313" t="n">
         <v>1387.55</v>
       </c>
       <c r="O313" t="n">
-        <v>213682.7</v>
+        <v>206744.95</v>
       </c>
       <c r="P313" t="n">
         <v>2300</v>
       </c>
       <c r="Q313" t="n">
-        <v>354200</v>
+        <v>342700</v>
       </c>
     </row>
     <row r="314">
@@ -14174,25 +14174,25 @@
         <v>1</v>
       </c>
       <c r="K316" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L316" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M316" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N316" t="n">
         <v>4635.49</v>
       </c>
       <c r="O316" t="n">
-        <v>4635.49</v>
+        <v>0</v>
       </c>
       <c r="P316" t="n">
         <v>7500</v>
       </c>
       <c r="Q316" t="n">
-        <v>7500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="317">
@@ -14644,22 +14644,22 @@
         <v>0</v>
       </c>
       <c r="L326" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M326" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="N326" t="n">
         <v>3761.6</v>
       </c>
       <c r="O326" t="n">
-        <v>195603.2</v>
+        <v>184318.4</v>
       </c>
       <c r="P326" t="n">
         <v>6900</v>
       </c>
       <c r="Q326" t="n">
-        <v>358800</v>
+        <v>338100</v>
       </c>
     </row>
     <row r="327">
@@ -14777,25 +14777,25 @@
         <v>16</v>
       </c>
       <c r="K329" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L329" t="n">
         <v>0</v>
       </c>
       <c r="M329" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="N329" t="n">
         <v>11921.4</v>
       </c>
       <c r="O329" t="n">
-        <v>190742.4</v>
+        <v>238428</v>
       </c>
       <c r="P329" t="n">
         <v>19900</v>
       </c>
       <c r="Q329" t="n">
-        <v>318400</v>
+        <v>398000</v>
       </c>
     </row>
     <row r="330">
@@ -15144,22 +15144,22 @@
         <v>0</v>
       </c>
       <c r="L337" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M337" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="N337" t="n">
         <v>3751</v>
       </c>
       <c r="O337" t="n">
-        <v>495132</v>
+        <v>487630</v>
       </c>
       <c r="P337" t="n">
         <v>6400</v>
       </c>
       <c r="Q337" t="n">
-        <v>844800</v>
+        <v>832000</v>
       </c>
     </row>
     <row r="338">
@@ -15331,22 +15331,22 @@
         <v>0</v>
       </c>
       <c r="L341" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="M341" t="n">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="N341" t="n">
-        <v>1630.9231587595</v>
+        <v>1630.9231730968</v>
       </c>
       <c r="O341" t="n">
-        <v>177770.6243047855</v>
+        <v>158199.5477903896</v>
       </c>
       <c r="P341" t="n">
         <v>2500</v>
       </c>
       <c r="Q341" t="n">
-        <v>272500</v>
+        <v>242500</v>
       </c>
     </row>
     <row r="342">
@@ -15383,10 +15383,10 @@
         <v>1</v>
       </c>
       <c r="N342" t="n">
-        <v>1467.327254902</v>
+        <v>1467.3264227642</v>
       </c>
       <c r="O342" t="n">
-        <v>1467.327254902</v>
+        <v>1467.3264227642</v>
       </c>
       <c r="P342" t="n">
         <v>2500</v>
@@ -15423,22 +15423,22 @@
         <v>0</v>
       </c>
       <c r="L343" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M343" t="n">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="N343" t="n">
-        <v>1690.6026503973</v>
+        <v>1690.6023498845</v>
       </c>
       <c r="O343" t="n">
-        <v>76077.1192678785</v>
+        <v>49027.4681466505</v>
       </c>
       <c r="P343" t="n">
         <v>2900</v>
       </c>
       <c r="Q343" t="n">
-        <v>130500</v>
+        <v>84100</v>
       </c>
     </row>
     <row r="344">
@@ -15469,22 +15469,22 @@
         <v>0</v>
       </c>
       <c r="L344" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="M344" t="n">
-        <v>450</v>
+        <v>412</v>
       </c>
       <c r="N344" t="n">
-        <v>1550.1931558806</v>
+        <v>1550.193183768</v>
       </c>
       <c r="O344" t="n">
-        <v>697586.92014627</v>
+        <v>638679.5917124159</v>
       </c>
       <c r="P344" t="n">
         <v>2500</v>
       </c>
       <c r="Q344" t="n">
-        <v>1125000</v>
+        <v>1030000</v>
       </c>
     </row>
     <row r="345">
@@ -15521,10 +15521,10 @@
         <v>1</v>
       </c>
       <c r="N345" t="n">
-        <v>1579.391025</v>
+        <v>1579.3909343434</v>
       </c>
       <c r="O345" t="n">
-        <v>1579.391025</v>
+        <v>1579.3909343434</v>
       </c>
       <c r="P345" t="n">
         <v>2900</v>
@@ -15561,22 +15561,22 @@
         <v>0</v>
       </c>
       <c r="L346" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="M346" t="n">
-        <v>280</v>
+        <v>267</v>
       </c>
       <c r="N346" t="n">
-        <v>2403.5103724115</v>
+        <v>2403.5104597508</v>
       </c>
       <c r="O346" t="n">
-        <v>672982.90427522</v>
+        <v>641737.2927534635</v>
       </c>
       <c r="P346" t="n">
         <v>3500</v>
       </c>
       <c r="Q346" t="n">
-        <v>980000</v>
+        <v>934500</v>
       </c>
     </row>
     <row r="347">
@@ -15607,22 +15607,22 @@
         <v>0</v>
       </c>
       <c r="L347" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M347" t="n">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="N347" t="n">
-        <v>2521.5439240506</v>
+        <v>2521.5426705653</v>
       </c>
       <c r="O347" t="n">
-        <v>103383.3008860746</v>
+        <v>70603.19477582839</v>
       </c>
       <c r="P347" t="n">
         <v>3900</v>
       </c>
       <c r="Q347" t="n">
-        <v>159900</v>
+        <v>109200</v>
       </c>
     </row>
     <row r="348">
@@ -16366,22 +16366,22 @@
         <v>0</v>
       </c>
       <c r="L364" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M364" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N364" t="n">
         <v>15920</v>
       </c>
       <c r="O364" t="n">
-        <v>47760</v>
+        <v>31840</v>
       </c>
       <c r="P364" t="n">
         <v>19900</v>
       </c>
       <c r="Q364" t="n">
-        <v>59700</v>
+        <v>39800</v>
       </c>
     </row>
     <row r="365">
@@ -17077,22 +17077,22 @@
         <v>0</v>
       </c>
       <c r="L380" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M380" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N380" t="n">
         <v>14118.32</v>
       </c>
       <c r="O380" t="n">
-        <v>127064.88</v>
+        <v>112946.56</v>
       </c>
       <c r="P380" t="n">
         <v>17900</v>
       </c>
       <c r="Q380" t="n">
-        <v>161100</v>
+        <v>143200</v>
       </c>
     </row>
     <row r="381">
@@ -17123,22 +17123,22 @@
         <v>0</v>
       </c>
       <c r="L381" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M381" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N381" t="n">
         <v>8720</v>
       </c>
       <c r="O381" t="n">
-        <v>122080</v>
+        <v>113360</v>
       </c>
       <c r="P381" t="n">
         <v>10900</v>
       </c>
       <c r="Q381" t="n">
-        <v>152600</v>
+        <v>141700</v>
       </c>
     </row>
     <row r="382">
@@ -18022,22 +18022,22 @@
         <v>0</v>
       </c>
       <c r="L401" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M401" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="N401" t="n">
         <v>9338</v>
       </c>
       <c r="O401" t="n">
-        <v>205436</v>
+        <v>186760</v>
       </c>
       <c r="P401" t="n">
         <v>15500</v>
       </c>
       <c r="Q401" t="n">
-        <v>341000</v>
+        <v>310000</v>
       </c>
     </row>
     <row r="402">
@@ -18358,22 +18358,22 @@
         <v>0</v>
       </c>
       <c r="L409" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M409" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N409" t="n">
         <v>2081</v>
       </c>
       <c r="O409" t="n">
-        <v>79078</v>
+        <v>76997</v>
       </c>
       <c r="P409" t="n">
         <v>3200</v>
       </c>
       <c r="Q409" t="n">
-        <v>121600</v>
+        <v>118400</v>
       </c>
     </row>
     <row r="410">
@@ -18481,22 +18481,22 @@
         <v>0</v>
       </c>
       <c r="L412" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M412" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N412" t="n">
         <v>8794.48</v>
       </c>
       <c r="O412" t="n">
-        <v>492490.88</v>
+        <v>483696.4</v>
       </c>
       <c r="P412" t="n">
         <v>14500</v>
       </c>
       <c r="Q412" t="n">
-        <v>812000</v>
+        <v>797500</v>
       </c>
     </row>
     <row r="413">
@@ -18568,22 +18568,22 @@
         <v>0</v>
       </c>
       <c r="L414" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M414" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="N414" t="n">
         <v>2567</v>
       </c>
       <c r="O414" t="n">
-        <v>492864</v>
+        <v>487730</v>
       </c>
       <c r="P414" t="n">
         <v>4500</v>
       </c>
       <c r="Q414" t="n">
-        <v>864000</v>
+        <v>855000</v>
       </c>
     </row>
     <row r="415">
@@ -18697,10 +18697,10 @@
         <v>201</v>
       </c>
       <c r="N417" t="n">
-        <v>2029.8737073653</v>
+        <v>2029.8737091988</v>
       </c>
       <c r="O417" t="n">
-        <v>408004.6151804253</v>
+        <v>408004.6155489588</v>
       </c>
       <c r="P417" t="n">
         <v>3600</v>
@@ -18732,22 +18732,22 @@
         <v>0</v>
       </c>
       <c r="L418" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M418" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="N418" t="n">
         <v>2673</v>
       </c>
       <c r="O418" t="n">
-        <v>133650</v>
+        <v>122958</v>
       </c>
       <c r="P418" t="n">
         <v>2500</v>
       </c>
       <c r="Q418" t="n">
-        <v>125000</v>
+        <v>115000</v>
       </c>
     </row>
     <row r="419">
@@ -18896,22 +18896,22 @@
         <v>0</v>
       </c>
       <c r="L422" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M422" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N422" t="n">
         <v>3473</v>
       </c>
       <c r="O422" t="n">
-        <v>3473</v>
+        <v>0</v>
       </c>
       <c r="P422" t="n">
         <v>5300</v>
       </c>
       <c r="Q422" t="n">
-        <v>5300</v>
+        <v>0</v>
       </c>
     </row>
     <row r="423">
@@ -18984,10 +18984,10 @@
         <v>543</v>
       </c>
       <c r="N424" t="n">
-        <v>880.3293685687599</v>
+        <v>880.32937295274</v>
       </c>
       <c r="O424" t="n">
-        <v>478018.8471328366</v>
+        <v>478018.8495133378</v>
       </c>
       <c r="P424" t="n">
         <v>1200</v>
@@ -19536,22 +19536,22 @@
         <v>0</v>
       </c>
       <c r="L437" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M437" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="N437" t="n">
-        <v>998.76125988546</v>
+        <v>998.76126091703</v>
       </c>
       <c r="O437" t="n">
-        <v>90887.27464957687</v>
+        <v>87890.99096069863</v>
       </c>
       <c r="P437" t="n">
         <v>1600</v>
       </c>
       <c r="Q437" t="n">
-        <v>145600</v>
+        <v>140800</v>
       </c>
     </row>
     <row r="438">
@@ -19713,22 +19713,22 @@
         <v>0</v>
       </c>
       <c r="L441" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M441" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N441" t="n">
-        <v>4285.1952751817</v>
+        <v>4285.1952806653</v>
       </c>
       <c r="O441" t="n">
-        <v>72848.3196780889</v>
+        <v>68563.1244906448</v>
       </c>
       <c r="P441" t="n">
         <v>6900</v>
       </c>
       <c r="Q441" t="n">
-        <v>117300</v>
+        <v>110400</v>
       </c>
     </row>
     <row r="442">
@@ -20367,10 +20367,10 @@
         <v>3</v>
       </c>
       <c r="N456" t="n">
-        <v>12005.159831933</v>
+        <v>12005.159831224</v>
       </c>
       <c r="O456" t="n">
-        <v>36015.479495799</v>
+        <v>36015.479493672</v>
       </c>
       <c r="P456" t="n">
         <v>19500</v>
@@ -21044,25 +21044,25 @@
         <v>39</v>
       </c>
       <c r="K472" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L472" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M472" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N472" t="n">
         <v>16974.69</v>
       </c>
       <c r="O472" t="n">
-        <v>628063.5299999999</v>
+        <v>645038.22</v>
       </c>
       <c r="P472" t="n">
         <v>26900</v>
       </c>
       <c r="Q472" t="n">
-        <v>995300</v>
+        <v>1022200</v>
       </c>
     </row>
     <row r="473">
@@ -21227,10 +21227,10 @@
         <v>76</v>
       </c>
       <c r="N476" t="n">
-        <v>1560.9993877551</v>
+        <v>1560.9994428152</v>
       </c>
       <c r="O476" t="n">
-        <v>118635.9534693876</v>
+        <v>118635.9576539552</v>
       </c>
       <c r="P476" t="n">
         <v>2900</v>
@@ -21967,22 +21967,22 @@
         <v>0</v>
       </c>
       <c r="L493" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="M493" t="n">
-        <v>377</v>
+        <v>346</v>
       </c>
       <c r="N493" t="n">
         <v>1200</v>
       </c>
       <c r="O493" t="n">
-        <v>452400</v>
+        <v>415200</v>
       </c>
       <c r="P493" t="n">
         <v>1500</v>
       </c>
       <c r="Q493" t="n">
-        <v>565500</v>
+        <v>519000</v>
       </c>
     </row>
     <row r="494">
@@ -22320,10 +22320,10 @@
         <v>121</v>
       </c>
       <c r="N501" t="n">
-        <v>548.14725212465</v>
+        <v>548.14724692526</v>
       </c>
       <c r="O501" t="n">
-        <v>66325.81750708265</v>
+        <v>66325.81687795646</v>
       </c>
       <c r="P501" t="n">
         <v>2000</v>
@@ -22583,22 +22583,22 @@
         <v>0</v>
       </c>
       <c r="L507" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M507" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N507" t="n">
         <v>4679.92</v>
       </c>
       <c r="O507" t="n">
-        <v>74878.72</v>
+        <v>65518.88</v>
       </c>
       <c r="P507" t="n">
         <v>2500</v>
       </c>
       <c r="Q507" t="n">
-        <v>40000</v>
+        <v>35000</v>
       </c>
     </row>
     <row r="508">
@@ -22716,22 +22716,22 @@
         <v>0</v>
       </c>
       <c r="L510" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M510" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N510" t="n">
         <v>20907</v>
       </c>
       <c r="O510" t="n">
-        <v>41814</v>
+        <v>20907</v>
       </c>
       <c r="P510" t="n">
         <v>35600</v>
       </c>
       <c r="Q510" t="n">
-        <v>71200</v>
+        <v>35600</v>
       </c>
     </row>
     <row r="511">
@@ -22854,25 +22854,25 @@
         <v>9</v>
       </c>
       <c r="K513" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L513" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M513" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="N513" t="n">
         <v>5875.95</v>
       </c>
       <c r="O513" t="n">
-        <v>52883.55</v>
+        <v>82263.3</v>
       </c>
       <c r="P513" t="n">
         <v>5900</v>
       </c>
       <c r="Q513" t="n">
-        <v>53100</v>
+        <v>82600</v>
       </c>
     </row>
     <row r="514">
@@ -22947,22 +22947,22 @@
         <v>0</v>
       </c>
       <c r="L515" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M515" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N515" t="n">
         <v>5470.94</v>
       </c>
       <c r="O515" t="n">
-        <v>71122.22</v>
+        <v>65651.28</v>
       </c>
       <c r="P515" t="n">
         <v>6900</v>
       </c>
       <c r="Q515" t="n">
-        <v>89700</v>
+        <v>82800</v>
       </c>
     </row>
     <row r="516">
@@ -23295,10 +23295,10 @@
         <v>10</v>
       </c>
       <c r="K523" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L523" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M523" t="n">
         <v>10</v>
@@ -23605,22 +23605,22 @@
         <v>0</v>
       </c>
       <c r="L530" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M530" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="N530" t="n">
         <v>2634.61</v>
       </c>
       <c r="O530" t="n">
-        <v>126461.28</v>
+        <v>118557.45</v>
       </c>
       <c r="P530" t="n">
         <v>4200</v>
       </c>
       <c r="Q530" t="n">
-        <v>201600</v>
+        <v>189000</v>
       </c>
     </row>
     <row r="531">
@@ -23697,22 +23697,22 @@
         <v>0</v>
       </c>
       <c r="L532" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M532" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N532" t="n">
         <v>5569.98</v>
       </c>
       <c r="O532" t="n">
-        <v>200519.28</v>
+        <v>194949.3</v>
       </c>
       <c r="P532" t="n">
         <v>8900</v>
       </c>
       <c r="Q532" t="n">
-        <v>320400</v>
+        <v>311500</v>
       </c>
     </row>
     <row r="533">
@@ -23881,22 +23881,22 @@
         <v>0</v>
       </c>
       <c r="L536" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M536" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N536" t="n">
         <v>8878.450000000001</v>
       </c>
       <c r="O536" t="n">
-        <v>106541.4</v>
+        <v>88784.5</v>
       </c>
       <c r="P536" t="n">
         <v>14100</v>
       </c>
       <c r="Q536" t="n">
-        <v>169200</v>
+        <v>141000</v>
       </c>
     </row>
     <row r="537">
@@ -24025,10 +24025,10 @@
         <v>13</v>
       </c>
       <c r="N539" t="n">
-        <v>5218.1705164319</v>
+        <v>5218.170521327</v>
       </c>
       <c r="O539" t="n">
-        <v>67836.2167136147</v>
+        <v>67836.216777251</v>
       </c>
       <c r="P539" t="n">
         <v>8500</v>
@@ -24065,22 +24065,22 @@
         <v>0</v>
       </c>
       <c r="L540" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M540" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N540" t="n">
-        <v>3610.6500248756</v>
+        <v>3610.6500249688</v>
       </c>
       <c r="O540" t="n">
-        <v>86655.6005970144</v>
+        <v>75823.6505243448</v>
       </c>
       <c r="P540" t="n">
         <v>5800</v>
       </c>
       <c r="Q540" t="n">
-        <v>139200</v>
+        <v>121800</v>
       </c>
     </row>
     <row r="541">
@@ -24255,22 +24255,22 @@
         <v>0</v>
       </c>
       <c r="L544" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M544" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N544" t="n">
         <v>3920</v>
       </c>
       <c r="O544" t="n">
-        <v>54880</v>
+        <v>50960</v>
       </c>
       <c r="P544" t="n">
         <v>4900</v>
       </c>
       <c r="Q544" t="n">
-        <v>68600</v>
+        <v>63700</v>
       </c>
     </row>
     <row r="545">
@@ -24350,22 +24350,22 @@
         <v>0</v>
       </c>
       <c r="L546" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M546" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N546" t="n">
         <v>4227.77</v>
       </c>
       <c r="O546" t="n">
-        <v>198705.19</v>
+        <v>194477.42</v>
       </c>
       <c r="P546" t="n">
         <v>6900</v>
       </c>
       <c r="Q546" t="n">
-        <v>324300</v>
+        <v>317400</v>
       </c>
     </row>
     <row r="547">
@@ -24491,22 +24491,22 @@
         <v>0</v>
       </c>
       <c r="L549" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M549" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N549" t="n">
         <v>5791.05</v>
       </c>
       <c r="O549" t="n">
-        <v>133194.15</v>
+        <v>121612.05</v>
       </c>
       <c r="P549" t="n">
         <v>9300</v>
       </c>
       <c r="Q549" t="n">
-        <v>213900</v>
+        <v>195300</v>
       </c>
     </row>
     <row r="550">
@@ -24721,22 +24721,22 @@
         <v>0</v>
       </c>
       <c r="L554" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M554" t="n">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="N554" t="n">
-        <v>1664.3592041199</v>
+        <v>1664.3590294957</v>
       </c>
       <c r="O554" t="n">
-        <v>188072.5900655487</v>
+        <v>173093.3390675528</v>
       </c>
       <c r="P554" t="n">
         <v>2900</v>
       </c>
       <c r="Q554" t="n">
-        <v>327700</v>
+        <v>301600</v>
       </c>
     </row>
     <row r="555">
@@ -25791,22 +25791,22 @@
         <v>0</v>
       </c>
       <c r="L577" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M577" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N577" t="n">
         <v>18016</v>
       </c>
       <c r="O577" t="n">
-        <v>54048</v>
+        <v>36032</v>
       </c>
       <c r="P577" t="n">
         <v>29900</v>
       </c>
       <c r="Q577" t="n">
-        <v>89700</v>
+        <v>59800</v>
       </c>
     </row>
     <row r="578">
@@ -25837,22 +25837,22 @@
         <v>0</v>
       </c>
       <c r="L578" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M578" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N578" t="n">
         <v>16058</v>
       </c>
       <c r="O578" t="n">
-        <v>160580</v>
+        <v>128464</v>
       </c>
       <c r="P578" t="n">
         <v>25900</v>
       </c>
       <c r="Q578" t="n">
-        <v>259000</v>
+        <v>207200</v>
       </c>
     </row>
     <row r="579">
@@ -25975,22 +25975,22 @@
         <v>0</v>
       </c>
       <c r="L581" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M581" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N581" t="n">
         <v>5148</v>
       </c>
       <c r="O581" t="n">
-        <v>283140</v>
+        <v>277992</v>
       </c>
       <c r="P581" t="n">
         <v>8600</v>
       </c>
       <c r="Q581" t="n">
-        <v>473000</v>
+        <v>464400</v>
       </c>
     </row>
     <row r="582">
@@ -26997,22 +26997,22 @@
         <v>0</v>
       </c>
       <c r="L603" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M603" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N603" t="n">
         <v>3938.66</v>
       </c>
       <c r="O603" t="n">
-        <v>47263.92</v>
+        <v>43325.25999999999</v>
       </c>
       <c r="P603" t="n">
         <v>4500</v>
       </c>
       <c r="Q603" t="n">
-        <v>54000</v>
+        <v>49500</v>
       </c>
     </row>
     <row r="604">
@@ -27458,22 +27458,22 @@
         <v>0</v>
       </c>
       <c r="L613" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M613" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="N613" t="n">
         <v>8858.16</v>
       </c>
       <c r="O613" t="n">
-        <v>194879.52</v>
+        <v>177163.2</v>
       </c>
       <c r="P613" t="n">
         <v>15500</v>
       </c>
       <c r="Q613" t="n">
-        <v>341000</v>
+        <v>310000</v>
       </c>
     </row>
     <row r="614">
@@ -27777,25 +27777,25 @@
         <v>202</v>
       </c>
       <c r="K620" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L620" t="n">
         <v>0</v>
       </c>
       <c r="M620" t="n">
-        <v>202</v>
+        <v>226</v>
       </c>
       <c r="N620" t="n">
-        <v>2252.2965479115</v>
+        <v>2252.2965559656</v>
       </c>
       <c r="O620" t="n">
-        <v>454963.902678123</v>
+        <v>509019.0216482256</v>
       </c>
       <c r="P620" t="n">
         <v>3900</v>
       </c>
       <c r="Q620" t="n">
-        <v>787800</v>
+        <v>881400</v>
       </c>
     </row>
     <row r="621">
@@ -28335,10 +28335,10 @@
         <v>5</v>
       </c>
       <c r="K632" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L632" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M632" t="n">
         <v>5</v>
@@ -28841,25 +28841,25 @@
         <v>33</v>
       </c>
       <c r="K643" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="L643" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M643" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="N643" t="n">
-        <v>4907.8219448698</v>
+        <v>4907.8219751166</v>
       </c>
       <c r="O643" t="n">
-        <v>161958.1241807034</v>
+        <v>201220.7009797806</v>
       </c>
       <c r="P643" t="n">
         <v>8200</v>
       </c>
       <c r="Q643" t="n">
-        <v>270600</v>
+        <v>336200</v>
       </c>
     </row>
     <row r="644">
@@ -29529,22 +29529,22 @@
         <v>0</v>
       </c>
       <c r="L658" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M658" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N658" t="n">
         <v>9839</v>
       </c>
       <c r="O658" t="n">
-        <v>88551</v>
+        <v>78712</v>
       </c>
       <c r="P658" t="n">
         <v>16900</v>
       </c>
       <c r="Q658" t="n">
-        <v>152100</v>
+        <v>135200</v>
       </c>
     </row>
     <row r="659">
@@ -29667,22 +29667,22 @@
         <v>0</v>
       </c>
       <c r="L661" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M661" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="N661" t="n">
         <v>6849.2</v>
       </c>
       <c r="O661" t="n">
-        <v>246571.2</v>
+        <v>226023.6</v>
       </c>
       <c r="P661" t="n">
         <v>11500</v>
       </c>
       <c r="Q661" t="n">
-        <v>414000</v>
+        <v>379500</v>
       </c>
     </row>
     <row r="662">
@@ -29759,22 +29759,22 @@
         <v>0</v>
       </c>
       <c r="L663" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M663" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="N663" t="n">
         <v>5772</v>
       </c>
       <c r="O663" t="n">
-        <v>294372</v>
+        <v>277056</v>
       </c>
       <c r="P663" t="n">
         <v>9900</v>
       </c>
       <c r="Q663" t="n">
-        <v>504900</v>
+        <v>475200</v>
       </c>
     </row>
     <row r="664">
@@ -29851,22 +29851,22 @@
         <v>0</v>
       </c>
       <c r="L665" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M665" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N665" t="n">
         <v>8637</v>
       </c>
       <c r="O665" t="n">
-        <v>86370</v>
+        <v>69096</v>
       </c>
       <c r="P665" t="n">
         <v>14500</v>
       </c>
       <c r="Q665" t="n">
-        <v>145000</v>
+        <v>116000</v>
       </c>
     </row>
     <row r="666">
@@ -29943,22 +29943,22 @@
         <v>0</v>
       </c>
       <c r="L667" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M667" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N667" t="n">
         <v>27186</v>
       </c>
       <c r="O667" t="n">
-        <v>244674</v>
+        <v>217488</v>
       </c>
       <c r="P667" t="n">
         <v>43900</v>
       </c>
       <c r="Q667" t="n">
-        <v>395100</v>
+        <v>351200</v>
       </c>
     </row>
     <row r="668">
@@ -30124,25 +30124,25 @@
         <v>15</v>
       </c>
       <c r="K671" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L671" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M671" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N671" t="n">
         <v>7635</v>
       </c>
       <c r="O671" t="n">
-        <v>114525</v>
+        <v>122160</v>
       </c>
       <c r="P671" t="n">
         <v>13900</v>
       </c>
       <c r="Q671" t="n">
-        <v>208500</v>
+        <v>222400</v>
       </c>
     </row>
     <row r="672">
@@ -30219,22 +30219,22 @@
         <v>0</v>
       </c>
       <c r="L673" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M673" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N673" t="n">
         <v>5438</v>
       </c>
       <c r="O673" t="n">
-        <v>81570</v>
+        <v>70694</v>
       </c>
       <c r="P673" t="n">
         <v>8900</v>
       </c>
       <c r="Q673" t="n">
-        <v>133500</v>
+        <v>115700</v>
       </c>
     </row>
     <row r="674">
@@ -30907,22 +30907,22 @@
         <v>0</v>
       </c>
       <c r="L688" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M688" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="N688" t="n">
         <v>59834</v>
       </c>
       <c r="O688" t="n">
-        <v>8316926</v>
+        <v>8257092</v>
       </c>
       <c r="P688" t="n">
         <v>7900</v>
       </c>
       <c r="Q688" t="n">
-        <v>1098100</v>
+        <v>1090200</v>
       </c>
     </row>
     <row r="689">
@@ -31692,22 +31692,22 @@
         <v>0</v>
       </c>
       <c r="L705" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M705" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N705" t="n">
         <v>8700</v>
       </c>
       <c r="O705" t="n">
-        <v>200100</v>
+        <v>191400</v>
       </c>
       <c r="P705" t="n">
         <v>14900</v>
       </c>
       <c r="Q705" t="n">
-        <v>342700</v>
+        <v>327800</v>
       </c>
     </row>
     <row r="706">
@@ -31784,22 +31784,22 @@
         <v>0</v>
       </c>
       <c r="L707" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M707" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="N707" t="n">
         <v>1326</v>
       </c>
       <c r="O707" t="n">
-        <v>58344</v>
+        <v>54366</v>
       </c>
       <c r="P707" t="n">
         <v>2500</v>
       </c>
       <c r="Q707" t="n">
-        <v>110000</v>
+        <v>102500</v>
       </c>
     </row>
     <row r="708">
@@ -32382,22 +32382,22 @@
         <v>0</v>
       </c>
       <c r="L720" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M720" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="N720" t="n">
         <v>1803</v>
       </c>
       <c r="O720" t="n">
-        <v>108180</v>
+        <v>100968</v>
       </c>
       <c r="P720" t="n">
         <v>3900</v>
       </c>
       <c r="Q720" t="n">
-        <v>234000</v>
+        <v>218400</v>
       </c>
     </row>
     <row r="721">
@@ -32480,10 +32480,10 @@
         <v>18</v>
       </c>
       <c r="N722" t="n">
-        <v>1516.0388110875</v>
+        <v>1516.0388102832</v>
       </c>
       <c r="O722" t="n">
-        <v>27288.698599575</v>
+        <v>27288.6985850976</v>
       </c>
       <c r="P722" t="n">
         <v>2300</v>
@@ -32564,22 +32564,22 @@
         <v>0</v>
       </c>
       <c r="L724" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="M724" t="n">
-        <v>102</v>
+        <v>46</v>
       </c>
       <c r="N724" t="n">
-        <v>4248.6238427948</v>
+        <v>4248.635</v>
       </c>
       <c r="O724" t="n">
-        <v>433359.6319650696</v>
+        <v>195437.21</v>
       </c>
       <c r="P724" t="n">
         <v>5900</v>
       </c>
       <c r="Q724" t="n">
-        <v>601800</v>
+        <v>271400</v>
       </c>
     </row>
     <row r="725">
@@ -32610,22 +32610,22 @@
         <v>0</v>
       </c>
       <c r="L725" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="M725" t="n">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="N725" t="n">
-        <v>2458.5133829585</v>
+        <v>2458.5133724619</v>
       </c>
       <c r="O725" t="n">
-        <v>572833.6182293305</v>
+        <v>565458.075666237</v>
       </c>
       <c r="P725" t="n">
         <v>3500</v>
       </c>
       <c r="Q725" t="n">
-        <v>815500</v>
+        <v>805000</v>
       </c>
     </row>
     <row r="726">
@@ -32656,22 +32656,22 @@
         <v>0</v>
       </c>
       <c r="L726" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M726" t="n">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="N726" t="n">
-        <v>1907.3941918295</v>
+        <v>1907.3940437158</v>
       </c>
       <c r="O726" t="n">
-        <v>291831.3113499135</v>
+        <v>286109.10655737</v>
       </c>
       <c r="P726" t="n">
         <v>2500</v>
       </c>
       <c r="Q726" t="n">
-        <v>382500</v>
+        <v>375000</v>
       </c>
     </row>
     <row r="727">
@@ -32708,10 +32708,10 @@
         <v>67</v>
       </c>
       <c r="N727" t="n">
-        <v>1771.0911342735</v>
+        <v>1771.0911179361</v>
       </c>
       <c r="O727" t="n">
-        <v>118663.1059963245</v>
+        <v>118663.1049017187</v>
       </c>
       <c r="P727" t="n">
         <v>2500</v>
@@ -32748,22 +32748,22 @@
         <v>0</v>
       </c>
       <c r="L728" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M728" t="n">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="N728" t="n">
-        <v>2079.3841889251</v>
+        <v>2079.3841813438</v>
       </c>
       <c r="O728" t="n">
-        <v>266161.1761824128</v>
+        <v>257843.6384866312</v>
       </c>
       <c r="P728" t="n">
         <v>2900</v>
       </c>
       <c r="Q728" t="n">
-        <v>371200</v>
+        <v>359600</v>
       </c>
     </row>
     <row r="729">
@@ -32794,22 +32794,22 @@
         <v>0</v>
       </c>
       <c r="L729" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M729" t="n">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="N729" t="n">
-        <v>1803.0151566778</v>
+        <v>1803.0151724138</v>
       </c>
       <c r="O729" t="n">
-        <v>311921.6221052594</v>
+        <v>306512.579310346</v>
       </c>
       <c r="P729" t="n">
         <v>2500</v>
       </c>
       <c r="Q729" t="n">
-        <v>432500</v>
+        <v>425000</v>
       </c>
     </row>
     <row r="730">
@@ -32892,10 +32892,10 @@
         <v>64</v>
       </c>
       <c r="N731" t="n">
-        <v>2122.1640073529</v>
+        <v>2122.1640036787</v>
       </c>
       <c r="O731" t="n">
-        <v>135818.4964705856</v>
+        <v>135818.4962354368</v>
       </c>
       <c r="P731" t="n">
         <v>2900</v>
@@ -32938,10 +32938,10 @@
         <v>86</v>
       </c>
       <c r="N732" t="n">
-        <v>2108.7899885584</v>
+        <v>2108.7900518135</v>
       </c>
       <c r="O732" t="n">
-        <v>181355.9390160224</v>
+        <v>181355.944455961</v>
       </c>
       <c r="P732" t="n">
         <v>2900</v>
@@ -32978,22 +32978,22 @@
         <v>0</v>
       </c>
       <c r="L733" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="M733" t="n">
-        <v>304</v>
+        <v>269</v>
       </c>
       <c r="N733" t="n">
-        <v>2056.0838222089</v>
+        <v>2056.0837188071</v>
       </c>
       <c r="O733" t="n">
-        <v>625049.4819515056</v>
+        <v>553086.5203591099</v>
       </c>
       <c r="P733" t="n">
         <v>2900</v>
       </c>
       <c r="Q733" t="n">
-        <v>881600</v>
+        <v>780100</v>
       </c>
     </row>
     <row r="734">
@@ -33024,22 +33024,22 @@
         <v>0</v>
       </c>
       <c r="L734" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M734" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="N734" t="n">
-        <v>3224.568287037</v>
+        <v>3224.5683024119</v>
       </c>
       <c r="O734" t="n">
-        <v>322456.8287037</v>
+        <v>319232.2619387781</v>
       </c>
       <c r="P734" t="n">
         <v>4500</v>
       </c>
       <c r="Q734" t="n">
-        <v>450000</v>
+        <v>445500</v>
       </c>
     </row>
     <row r="735">
@@ -33076,10 +33076,10 @@
         <v>157</v>
       </c>
       <c r="N735" t="n">
-        <v>1655.931057226</v>
+        <v>1655.9310223953</v>
       </c>
       <c r="O735" t="n">
-        <v>259981.175984482</v>
+        <v>259981.1705160621</v>
       </c>
       <c r="P735" t="n">
         <v>2500</v>
@@ -33349,22 +33349,22 @@
         <v>0</v>
       </c>
       <c r="L741" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M741" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="N741" t="n">
-        <v>1592.2755269762</v>
+        <v>1592.2756948933</v>
       </c>
       <c r="O741" t="n">
-        <v>97128.8071455482</v>
+        <v>89167.43891402479</v>
       </c>
       <c r="P741" t="n">
         <v>2500</v>
       </c>
       <c r="Q741" t="n">
-        <v>152500</v>
+        <v>140000</v>
       </c>
     </row>
     <row r="742">
@@ -33526,22 +33526,22 @@
         <v>0</v>
       </c>
       <c r="L745" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M745" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="N745" t="n">
-        <v>2311.9247818182</v>
+        <v>2311.9246983547</v>
       </c>
       <c r="O745" t="n">
-        <v>224256.7038363654</v>
+        <v>217320.9216453418</v>
       </c>
       <c r="P745" t="n">
         <v>3500</v>
       </c>
       <c r="Q745" t="n">
-        <v>339500</v>
+        <v>329000</v>
       </c>
     </row>
     <row r="746">
@@ -33618,22 +33618,22 @@
         <v>0</v>
       </c>
       <c r="L747" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="M747" t="n">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="N747" t="n">
-        <v>3033.7290022676</v>
+        <v>3033.7273039216</v>
       </c>
       <c r="O747" t="n">
-        <v>100113.0570748308</v>
+        <v>9101.181911764801</v>
       </c>
       <c r="P747" t="n">
         <v>4500</v>
       </c>
       <c r="Q747" t="n">
-        <v>148500</v>
+        <v>13500</v>
       </c>
     </row>
     <row r="748">
@@ -33670,10 +33670,10 @@
         <v>107</v>
       </c>
       <c r="N748" t="n">
-        <v>2060.160557377</v>
+        <v>2060.1604635762</v>
       </c>
       <c r="O748" t="n">
-        <v>220437.179639339</v>
+        <v>220437.1696026534</v>
       </c>
       <c r="P748" t="n">
         <v>2900</v>
@@ -33710,22 +33710,22 @@
         <v>0</v>
       </c>
       <c r="L749" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M749" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="N749" t="n">
-        <v>1668.6190998043</v>
+        <v>1668.6199591002</v>
       </c>
       <c r="O749" t="n">
-        <v>116803.336986301</v>
+        <v>88436.8578323106</v>
       </c>
       <c r="P749" t="n">
         <v>2500</v>
       </c>
       <c r="Q749" t="n">
-        <v>175000</v>
+        <v>132500</v>
       </c>
     </row>
     <row r="750">
@@ -33762,10 +33762,10 @@
         <v>123</v>
       </c>
       <c r="N750" t="n">
-        <v>2546.9850949914</v>
+        <v>2546.985</v>
       </c>
       <c r="O750" t="n">
-        <v>313279.1666839422</v>
+        <v>313279.155</v>
       </c>
       <c r="P750" t="n">
         <v>3900</v>
@@ -33802,22 +33802,22 @@
         <v>0</v>
       </c>
       <c r="L751" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="M751" t="n">
-        <v>228</v>
+        <v>206</v>
       </c>
       <c r="N751" t="n">
-        <v>1259.2744422442</v>
+        <v>1259.2744638514</v>
       </c>
       <c r="O751" t="n">
-        <v>287114.5728316776</v>
+        <v>259410.5395533884</v>
       </c>
       <c r="P751" t="n">
         <v>1900</v>
       </c>
       <c r="Q751" t="n">
-        <v>433200</v>
+        <v>391400</v>
       </c>
     </row>
     <row r="752">
@@ -33981,22 +33981,22 @@
         <v>0</v>
       </c>
       <c r="L755" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M755" t="n">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="N755" t="n">
-        <v>2556.7452252252</v>
+        <v>2556.7453211009</v>
       </c>
       <c r="O755" t="n">
-        <v>263344.7581981956</v>
+        <v>250561.0414678882</v>
       </c>
       <c r="P755" t="n">
         <v>3900</v>
       </c>
       <c r="Q755" t="n">
-        <v>401700</v>
+        <v>382200</v>
       </c>
     </row>
     <row r="756">
@@ -34025,22 +34025,22 @@
         <v>0</v>
       </c>
       <c r="L756" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M756" t="n">
-        <v>362</v>
+        <v>350</v>
       </c>
       <c r="N756" t="n">
-        <v>692.15208975521</v>
+        <v>692.15209736124</v>
       </c>
       <c r="O756" t="n">
-        <v>250559.056491386</v>
+        <v>242253.234076434</v>
       </c>
       <c r="P756" t="n">
         <v>1200</v>
       </c>
       <c r="Q756" t="n">
-        <v>434400</v>
+        <v>420000</v>
       </c>
     </row>
     <row r="757">
@@ -34534,22 +34534,22 @@
         <v>0</v>
       </c>
       <c r="L767" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M767" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="N767" t="n">
         <v>1337.86</v>
       </c>
       <c r="O767" t="n">
-        <v>45487.24</v>
+        <v>41473.66</v>
       </c>
       <c r="P767" t="n">
         <v>3000</v>
       </c>
       <c r="Q767" t="n">
-        <v>102000</v>
+        <v>93000</v>
       </c>
     </row>
     <row r="768">
@@ -35468,25 +35468,25 @@
         <v>13</v>
       </c>
       <c r="K787" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L787" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M787" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="N787" t="n">
         <v>3629.36</v>
       </c>
       <c r="O787" t="n">
-        <v>47181.68</v>
+        <v>58069.76</v>
       </c>
       <c r="P787" t="n">
         <v>3900</v>
       </c>
       <c r="Q787" t="n">
-        <v>50700</v>
+        <v>62400</v>
       </c>
     </row>
     <row r="788">
@@ -35936,10 +35936,10 @@
         <v>16</v>
       </c>
       <c r="N797" t="n">
-        <v>10732.241860465</v>
+        <v>10732.241904762</v>
       </c>
       <c r="O797" t="n">
-        <v>171715.86976744</v>
+        <v>171715.870476192</v>
       </c>
       <c r="P797" t="n">
         <v>25900</v>
@@ -36305,10 +36305,10 @@
         <v>52</v>
       </c>
       <c r="N805" t="n">
-        <v>1690.8700089526</v>
+        <v>1690.8700089606</v>
       </c>
       <c r="O805" t="n">
-        <v>87925.2404655352</v>
+        <v>87925.2404659512</v>
       </c>
       <c r="P805" t="n">
         <v>3000</v>
@@ -37826,10 +37826,10 @@
         <v>22</v>
       </c>
       <c r="N838" t="n">
-        <v>4032.3968542199</v>
+        <v>4032.3968461538</v>
       </c>
       <c r="O838" t="n">
-        <v>88712.7307928378</v>
+        <v>88712.73061538361</v>
       </c>
       <c r="P838" t="n">
         <v>4200</v>
@@ -37918,22 +37918,22 @@
         <v>0</v>
       </c>
       <c r="L840" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="M840" t="n">
-        <v>1259</v>
+        <v>1160</v>
       </c>
       <c r="N840" t="n">
-        <v>517.28815469086</v>
+        <v>517.28824762181</v>
       </c>
       <c r="O840" t="n">
-        <v>651265.7867557927</v>
+        <v>600054.3672412996</v>
       </c>
       <c r="P840" t="n">
         <v>900</v>
       </c>
       <c r="Q840" t="n">
-        <v>1133100</v>
+        <v>1044000</v>
       </c>
     </row>
     <row r="841">
@@ -38338,22 +38338,22 @@
         <v>0</v>
       </c>
       <c r="L849" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M849" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N849" t="n">
-        <v>3259.1342205323</v>
+        <v>3259.1342528736</v>
       </c>
       <c r="O849" t="n">
-        <v>68441.81863117829</v>
+        <v>61923.5508045984</v>
       </c>
       <c r="P849" t="n">
         <v>3600</v>
       </c>
       <c r="Q849" t="n">
-        <v>75600</v>
+        <v>68400</v>
       </c>
     </row>
     <row r="850">
@@ -38433,22 +38433,22 @@
         <v>0</v>
       </c>
       <c r="L851" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M851" t="n">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="N851" t="n">
-        <v>3110.8427709611</v>
+        <v>3110.8426932617</v>
       </c>
       <c r="O851" t="n">
-        <v>1085684.127065424</v>
+        <v>1057686.515708978</v>
       </c>
       <c r="P851" t="n">
         <v>4500</v>
       </c>
       <c r="Q851" t="n">
-        <v>1570500</v>
+        <v>1530000</v>
       </c>
     </row>
     <row r="852">
@@ -38616,22 +38616,22 @@
         <v>0</v>
       </c>
       <c r="L855" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M855" t="n">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="N855" t="n">
         <v>2030.02</v>
       </c>
       <c r="O855" t="n">
-        <v>353223.48</v>
+        <v>332923.28</v>
       </c>
       <c r="P855" t="n">
         <v>3600</v>
       </c>
       <c r="Q855" t="n">
-        <v>626400</v>
+        <v>590400</v>
       </c>
     </row>
     <row r="856">
@@ -38845,22 +38845,22 @@
         <v>0</v>
       </c>
       <c r="L860" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="M860" t="n">
-        <v>279</v>
+        <v>216</v>
       </c>
       <c r="N860" t="n">
-        <v>703.79533220158</v>
+        <v>703.7953201758</v>
       </c>
       <c r="O860" t="n">
-        <v>196358.8976842408</v>
+        <v>152019.7891579728</v>
       </c>
       <c r="P860" t="n">
         <v>900</v>
       </c>
       <c r="Q860" t="n">
-        <v>251100</v>
+        <v>194400</v>
       </c>
     </row>
     <row r="861">
@@ -39219,22 +39219,22 @@
         <v>0</v>
       </c>
       <c r="L868" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M868" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="N868" t="n">
-        <v>2501.3852212389</v>
+        <v>2501.3851351351</v>
       </c>
       <c r="O868" t="n">
-        <v>25013.852212389</v>
+        <v>15008.3108108106</v>
       </c>
       <c r="P868" t="n">
         <v>4100</v>
       </c>
       <c r="Q868" t="n">
-        <v>41000</v>
+        <v>24600</v>
       </c>
     </row>
     <row r="869">
@@ -39366,10 +39366,10 @@
         <v>133</v>
       </c>
       <c r="N871" t="n">
-        <v>3006.0208530806</v>
+        <v>3006.0208653846</v>
       </c>
       <c r="O871" t="n">
-        <v>399800.7734597198</v>
+        <v>399800.7750961517</v>
       </c>
       <c r="P871" t="n">
         <v>3900</v>
@@ -39409,22 +39409,22 @@
         <v>0</v>
       </c>
       <c r="L872" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M872" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N872" t="n">
         <v>14260.14</v>
       </c>
       <c r="O872" t="n">
-        <v>356503.5</v>
+        <v>342243.36</v>
       </c>
       <c r="P872" t="n">
         <v>15900</v>
       </c>
       <c r="Q872" t="n">
-        <v>397500</v>
+        <v>381600</v>
       </c>
     </row>
     <row r="873">
@@ -39914,10 +39914,10 @@
         <v>52</v>
       </c>
       <c r="N883" t="n">
-        <v>1595.5155551576</v>
+        <v>1595.5155292429</v>
       </c>
       <c r="O883" t="n">
-        <v>82966.80886819519</v>
+        <v>82966.8075206308</v>
       </c>
       <c r="P883" t="n">
         <v>2500</v>
@@ -40346,22 +40346,22 @@
         <v>0</v>
       </c>
       <c r="L892" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M892" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N892" t="n">
         <v>11606.87</v>
       </c>
       <c r="O892" t="n">
-        <v>69641.22</v>
+        <v>58034.35000000001</v>
       </c>
       <c r="P892" t="n">
         <v>14900</v>
       </c>
       <c r="Q892" t="n">
-        <v>89400</v>
+        <v>74500</v>
       </c>
     </row>
     <row r="893">
@@ -41588,25 +41588,25 @@
         <v>4</v>
       </c>
       <c r="K918" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L918" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M918" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N918" t="n">
         <v>9874.620000000001</v>
       </c>
       <c r="O918" t="n">
-        <v>39498.48</v>
+        <v>59247.72</v>
       </c>
       <c r="P918" t="n">
         <v>14700</v>
       </c>
       <c r="Q918" t="n">
-        <v>58800</v>
+        <v>88200</v>
       </c>
     </row>
     <row r="919">
@@ -42225,22 +42225,22 @@
         <v>0</v>
       </c>
       <c r="L931" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M931" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N931" t="n">
         <v>10296.29</v>
       </c>
       <c r="O931" t="n">
-        <v>133851.77</v>
+        <v>113259.19</v>
       </c>
       <c r="P931" t="n">
         <v>16900</v>
       </c>
       <c r="Q931" t="n">
-        <v>219700</v>
+        <v>185900</v>
       </c>
     </row>
     <row r="932">
@@ -42271,22 +42271,22 @@
         <v>0</v>
       </c>
       <c r="L932" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M932" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N932" t="n">
-        <v>3879.9761538462</v>
+        <v>3879.9772727273</v>
       </c>
       <c r="O932" t="n">
-        <v>23279.8569230772</v>
+        <v>15519.9090909092</v>
       </c>
       <c r="P932" t="n">
         <v>12500</v>
       </c>
       <c r="Q932" t="n">
-        <v>75000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="933">
@@ -42369,22 +42369,22 @@
         <v>0</v>
       </c>
       <c r="L934" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M934" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N934" t="n">
         <v>4795.69</v>
       </c>
       <c r="O934" t="n">
-        <v>38365.52</v>
+        <v>23978.45</v>
       </c>
       <c r="P934" t="n">
         <v>10200</v>
       </c>
       <c r="Q934" t="n">
-        <v>81600</v>
+        <v>51000</v>
       </c>
     </row>
     <row r="935">
@@ -42611,22 +42611,22 @@
         <v>0</v>
       </c>
       <c r="L939" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M939" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="N939" t="n">
         <v>5430.86</v>
       </c>
       <c r="O939" t="n">
-        <v>168356.66</v>
+        <v>157494.94</v>
       </c>
       <c r="P939" t="n">
         <v>13900</v>
       </c>
       <c r="Q939" t="n">
-        <v>430900</v>
+        <v>403100</v>
       </c>
     </row>
     <row r="940">
@@ -42660,22 +42660,22 @@
         <v>0</v>
       </c>
       <c r="L940" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M940" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="N940" t="n">
         <v>6989.34</v>
       </c>
       <c r="O940" t="n">
-        <v>209680.2</v>
+        <v>195701.52</v>
       </c>
       <c r="P940" t="n">
         <v>10900</v>
       </c>
       <c r="Q940" t="n">
-        <v>327000</v>
+        <v>305200</v>
       </c>
     </row>
     <row r="941">
@@ -42801,25 +42801,25 @@
         <v>30</v>
       </c>
       <c r="K943" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L943" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M943" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N943" t="n">
         <v>4568.55</v>
       </c>
       <c r="O943" t="n">
-        <v>137056.5</v>
+        <v>132487.95</v>
       </c>
       <c r="P943" t="n">
         <v>6900</v>
       </c>
       <c r="Q943" t="n">
-        <v>207000</v>
+        <v>200100</v>
       </c>
     </row>
     <row r="944">
@@ -43041,22 +43041,22 @@
         <v>0</v>
       </c>
       <c r="L948" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M948" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="N948" t="n">
         <v>4286.16</v>
       </c>
       <c r="O948" t="n">
-        <v>137157.12</v>
+        <v>120012.48</v>
       </c>
       <c r="P948" t="n">
         <v>8900</v>
       </c>
       <c r="Q948" t="n">
-        <v>284800</v>
+        <v>249200</v>
       </c>
     </row>
     <row r="949">
@@ -43131,22 +43131,22 @@
         <v>0</v>
       </c>
       <c r="L950" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M950" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N950" t="n">
-        <v>3067.0905389222</v>
+        <v>3067.0905454545</v>
       </c>
       <c r="O950" t="n">
-        <v>24536.7243113776</v>
+        <v>12268.362181818</v>
       </c>
       <c r="P950" t="n">
         <v>7200</v>
       </c>
       <c r="Q950" t="n">
-        <v>57600</v>
+        <v>28800</v>
       </c>
     </row>
     <row r="951">
@@ -43180,22 +43180,22 @@
         <v>0</v>
       </c>
       <c r="L951" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M951" t="n">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="N951" t="n">
         <v>507.37</v>
       </c>
       <c r="O951" t="n">
-        <v>102996.11</v>
+        <v>100966.63</v>
       </c>
       <c r="P951" t="n">
         <v>2500</v>
       </c>
       <c r="Q951" t="n">
-        <v>507500</v>
+        <v>497500</v>
       </c>
     </row>
     <row r="952">
@@ -44478,22 +44478,22 @@
         <v>0</v>
       </c>
       <c r="L978" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M978" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N978" t="n">
         <v>23283.47</v>
       </c>
       <c r="O978" t="n">
-        <v>139700.82</v>
+        <v>116417.35</v>
       </c>
       <c r="P978" t="n">
         <v>52900</v>
       </c>
       <c r="Q978" t="n">
-        <v>317400</v>
+        <v>264500</v>
       </c>
     </row>
     <row r="979">
@@ -44533,10 +44533,10 @@
         <v>11</v>
       </c>
       <c r="N979" t="n">
-        <v>10737.526470588</v>
+        <v>10737.5264</v>
       </c>
       <c r="O979" t="n">
-        <v>118112.791176468</v>
+        <v>118112.7904</v>
       </c>
       <c r="P979" t="n">
         <v>18900</v>
@@ -46246,10 +46246,10 @@
         <v>75</v>
       </c>
       <c r="N1015" t="n">
-        <v>7046.939829932</v>
+        <v>7046.9398298958</v>
       </c>
       <c r="O1015" t="n">
-        <v>528520.4872449</v>
+        <v>528520.487242185</v>
       </c>
       <c r="P1015" t="n">
         <v>9900</v>
@@ -46871,22 +46871,22 @@
         <v>0</v>
       </c>
       <c r="L1028" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M1028" t="n">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="N1028" t="n">
-        <v>665.32343283582</v>
+        <v>665.3234571176</v>
       </c>
       <c r="O1028" t="n">
-        <v>163004.2410447759</v>
+        <v>157016.3358797536</v>
       </c>
       <c r="P1028" t="n">
         <v>2900</v>
       </c>
       <c r="Q1028" t="n">
-        <v>710500</v>
+        <v>684400</v>
       </c>
     </row>
     <row r="1029">
@@ -47505,10 +47505,10 @@
         <v>64</v>
       </c>
       <c r="N1041" t="n">
-        <v>430.60997670355</v>
+        <v>430.60997668998</v>
       </c>
       <c r="O1041" t="n">
-        <v>27559.0385090272</v>
+        <v>27559.03850815872</v>
       </c>
       <c r="P1041" t="n">
         <v>2200</v>
@@ -47554,10 +47554,10 @@
         <v>128</v>
       </c>
       <c r="N1042" t="n">
-        <v>465.8709360519</v>
+        <v>465.87093953488</v>
       </c>
       <c r="O1042" t="n">
-        <v>59631.4798146432</v>
+        <v>59631.48026046464</v>
       </c>
       <c r="P1042" t="n">
         <v>2500</v>
@@ -48379,22 +48379,22 @@
         <v>0</v>
       </c>
       <c r="L1061" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M1061" t="n">
-        <v>649</v>
+        <v>637</v>
       </c>
       <c r="N1061" t="n">
         <v>1176.57</v>
       </c>
       <c r="O1061" t="n">
-        <v>763593.9299999999</v>
+        <v>749475.09</v>
       </c>
       <c r="P1061" t="n">
         <v>1900</v>
       </c>
       <c r="Q1061" t="n">
-        <v>1233100</v>
+        <v>1210300</v>
       </c>
     </row>
     <row r="1062">
@@ -48558,10 +48558,10 @@
         <v>4</v>
       </c>
       <c r="N1065" t="n">
-        <v>2830.2251183432</v>
+        <v>2830.2251488095</v>
       </c>
       <c r="O1065" t="n">
-        <v>11320.9004733728</v>
+        <v>11320.900595238</v>
       </c>
       <c r="P1065" t="n">
         <v>2400</v>
@@ -48602,10 +48602,10 @@
         <v>12</v>
       </c>
       <c r="N1066" t="n">
-        <v>15219.155340909</v>
+        <v>15219.155287356</v>
       </c>
       <c r="O1066" t="n">
-        <v>182629.864090908</v>
+        <v>182629.863448272</v>
       </c>
       <c r="P1066" t="n">
         <v>16000</v>
@@ -48730,25 +48730,25 @@
         <v>10</v>
       </c>
       <c r="K1069" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L1069" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M1069" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N1069" t="n">
-        <v>8922.214777777799</v>
+        <v>8922.214942528701</v>
       </c>
       <c r="O1069" t="n">
-        <v>89222.14777777799</v>
+        <v>98144.36436781571</v>
       </c>
       <c r="P1069" t="n">
         <v>8200</v>
       </c>
       <c r="Q1069" t="n">
-        <v>82000</v>
+        <v>90200</v>
       </c>
     </row>
     <row r="1070">
@@ -49054,22 +49054,22 @@
         <v>0</v>
       </c>
       <c r="L1076" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1076" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N1076" t="n">
-        <v>4985.4046511628</v>
+        <v>4985.4047058824</v>
       </c>
       <c r="O1076" t="n">
-        <v>189445.3767441864</v>
+        <v>184459.9741176488</v>
       </c>
       <c r="P1076" t="n">
         <v>7900</v>
       </c>
       <c r="Q1076" t="n">
-        <v>300200</v>
+        <v>292300</v>
       </c>
     </row>
     <row r="1077">
@@ -49156,22 +49156,22 @@
         <v>0</v>
       </c>
       <c r="L1078" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M1078" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="N1078" t="n">
-        <v>1757.3205360825</v>
+        <v>1757.3205416667</v>
       </c>
       <c r="O1078" t="n">
-        <v>96652.62948453749</v>
+        <v>91380.6681666684</v>
       </c>
       <c r="P1078" t="n">
         <v>2000</v>
       </c>
       <c r="Q1078" t="n">
-        <v>110000</v>
+        <v>104000</v>
       </c>
     </row>
     <row r="1079">
@@ -50171,22 +50171,22 @@
         <v>0</v>
       </c>
       <c r="L1100" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="M1100" t="n">
-        <v>550</v>
+        <v>350</v>
       </c>
       <c r="N1100" t="n">
-        <v>220.00769152493</v>
+        <v>220.00713026296</v>
       </c>
       <c r="O1100" t="n">
-        <v>121004.2303387115</v>
+        <v>77002.49559203601</v>
       </c>
       <c r="P1100" t="n">
         <v>260</v>
       </c>
       <c r="Q1100" t="n">
-        <v>143000</v>
+        <v>91000</v>
       </c>
     </row>
     <row r="1101">
@@ -50539,22 +50539,22 @@
         <v>0</v>
       </c>
       <c r="L1108" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1108" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N1108" t="n">
         <v>3504.16</v>
       </c>
       <c r="O1108" t="n">
-        <v>63074.88</v>
+        <v>56066.56</v>
       </c>
       <c r="P1108" t="n">
         <v>3900</v>
       </c>
       <c r="Q1108" t="n">
-        <v>70200</v>
+        <v>62400</v>
       </c>
     </row>
     <row r="1109">
@@ -50585,22 +50585,22 @@
         <v>0</v>
       </c>
       <c r="L1109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1109" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N1109" t="n">
         <v>12000</v>
       </c>
       <c r="O1109" t="n">
-        <v>72000</v>
+        <v>60000</v>
       </c>
       <c r="P1109" t="n">
         <v>15000</v>
       </c>
       <c r="Q1109" t="n">
-        <v>90000</v>
+        <v>75000</v>
       </c>
     </row>
     <row r="1110">
@@ -50861,22 +50861,22 @@
         <v>0</v>
       </c>
       <c r="L1115" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M1115" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="N1115" t="n">
         <v>9708.190000000001</v>
       </c>
       <c r="O1115" t="n">
-        <v>106790.09</v>
+        <v>77665.52</v>
       </c>
       <c r="P1115" t="n">
         <v>10200</v>
       </c>
       <c r="Q1115" t="n">
-        <v>112200</v>
+        <v>81600</v>
       </c>
     </row>
     <row r="1116">
@@ -50999,22 +50999,22 @@
         <v>0</v>
       </c>
       <c r="L1118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1118" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N1118" t="n">
         <v>6270.21</v>
       </c>
       <c r="O1118" t="n">
-        <v>62702.1</v>
+        <v>56431.89</v>
       </c>
       <c r="P1118" t="n">
         <v>8900</v>
       </c>
       <c r="Q1118" t="n">
-        <v>89000</v>
+        <v>80100</v>
       </c>
     </row>
     <row r="1119">
@@ -51551,22 +51551,22 @@
         <v>0</v>
       </c>
       <c r="L1130" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M1130" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="N1130" t="n">
         <v>7740</v>
       </c>
       <c r="O1130" t="n">
-        <v>379260</v>
+        <v>356040</v>
       </c>
       <c r="P1130" t="n">
         <v>9500</v>
       </c>
       <c r="Q1130" t="n">
-        <v>465500</v>
+        <v>437000</v>
       </c>
     </row>
     <row r="1131">
@@ -51597,22 +51597,22 @@
         <v>0</v>
       </c>
       <c r="L1131" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1131" t="n">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="N1131" t="n">
-        <v>788.1365841161401</v>
+        <v>7480</v>
       </c>
       <c r="O1131" t="n">
-        <v>226983.3362254484</v>
+        <v>2139280</v>
       </c>
       <c r="P1131" t="n">
         <v>9500</v>
       </c>
       <c r="Q1131" t="n">
-        <v>2736000</v>
+        <v>2717000</v>
       </c>
     </row>
     <row r="1132">
@@ -51735,22 +51735,22 @@
         <v>0</v>
       </c>
       <c r="L1134" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M1134" t="n">
-        <v>598</v>
+        <v>580</v>
       </c>
       <c r="N1134" t="n">
         <v>9240</v>
       </c>
       <c r="O1134" t="n">
-        <v>5525520</v>
+        <v>5359200</v>
       </c>
       <c r="P1134" t="n">
         <v>11500</v>
       </c>
       <c r="Q1134" t="n">
-        <v>6877000</v>
+        <v>6670000</v>
       </c>
     </row>
     <row r="1135">
@@ -52747,22 +52747,22 @@
         <v>0</v>
       </c>
       <c r="L1156" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1156" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N1156" t="n">
         <v>6500</v>
       </c>
       <c r="O1156" t="n">
-        <v>65000</v>
+        <v>52000</v>
       </c>
       <c r="P1156" t="n">
         <v>7800</v>
       </c>
       <c r="Q1156" t="n">
-        <v>78000</v>
+        <v>62400</v>
       </c>
     </row>
     <row r="1157">
@@ -53115,22 +53115,22 @@
         <v>0</v>
       </c>
       <c r="L1164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1164" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N1164" t="n">
         <v>32.41</v>
       </c>
       <c r="O1164" t="n">
-        <v>259.28</v>
+        <v>226.87</v>
       </c>
       <c r="P1164" t="n">
         <v>13500</v>
       </c>
       <c r="Q1164" t="n">
-        <v>108000</v>
+        <v>94500</v>
       </c>
     </row>
     <row r="1165">
@@ -53161,22 +53161,22 @@
         <v>0</v>
       </c>
       <c r="L1165" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1165" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N1165" t="n">
-        <v>970.63153846154</v>
+        <v>970.63162162162</v>
       </c>
       <c r="O1165" t="n">
-        <v>7765.05230769232</v>
+        <v>5823.78972972972</v>
       </c>
       <c r="P1165" t="n">
         <v>7200</v>
       </c>
       <c r="Q1165" t="n">
-        <v>57600</v>
+        <v>43200</v>
       </c>
     </row>
     <row r="1166">
@@ -53881,22 +53881,22 @@
         <v>0</v>
       </c>
       <c r="L1180" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1180" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N1180" t="n">
-        <v>2432.1345544554</v>
+        <v>2432.1346</v>
       </c>
       <c r="O1180" t="n">
-        <v>46210.55653465261</v>
+        <v>43778.4228</v>
       </c>
       <c r="P1180" t="n">
         <v>4500</v>
       </c>
       <c r="Q1180" t="n">
-        <v>85500</v>
+        <v>81000</v>
       </c>
     </row>
     <row r="1181">
@@ -55903,22 +55903,22 @@
         <v>0</v>
       </c>
       <c r="L1224" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M1224" t="n">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="N1224" t="n">
         <v>4550</v>
       </c>
       <c r="O1224" t="n">
-        <v>459550</v>
+        <v>409500</v>
       </c>
       <c r="P1224" t="n">
         <v>5500</v>
       </c>
       <c r="Q1224" t="n">
-        <v>555500</v>
+        <v>495000</v>
       </c>
     </row>
     <row r="1225">
@@ -58074,10 +58074,10 @@
         <v>27</v>
       </c>
       <c r="N1271" t="n">
-        <v>2402.6744966443</v>
+        <v>2402.6744594595</v>
       </c>
       <c r="O1271" t="n">
-        <v>64872.21140939609</v>
+        <v>64872.21040540651</v>
       </c>
       <c r="P1271" t="n">
         <v>3000</v>

--- a/bodegas/LJ-101.xlsx
+++ b/bodegas/LJ-101.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-16</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-17</t>
         </is>
       </c>
     </row>

--- a/bodegas/LJ-101.xlsx
+++ b/bodegas/LJ-101.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-17</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-18</t>
         </is>
       </c>
     </row>
@@ -11360,22 +11360,22 @@
         <v>0</v>
       </c>
       <c r="L253" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M253" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="N253" t="n">
         <v>10716.34</v>
       </c>
       <c r="O253" t="n">
-        <v>96447.06</v>
+        <v>21432.68</v>
       </c>
       <c r="P253" t="n">
         <v>39000</v>
       </c>
       <c r="Q253" t="n">
-        <v>351000</v>
+        <v>78000</v>
       </c>
     </row>
     <row r="254">
@@ -35748,22 +35748,22 @@
         <v>0</v>
       </c>
       <c r="L793" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M793" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N793" t="n">
         <v>10732.241904762</v>
       </c>
       <c r="O793" t="n">
-        <v>171715.870476192</v>
+        <v>160983.62857143</v>
       </c>
       <c r="P793" t="n">
         <v>25900</v>
       </c>
       <c r="Q793" t="n">
-        <v>414400</v>
+        <v>388500</v>
       </c>
     </row>
     <row r="794">
@@ -49989,22 +49989,22 @@
         <v>0</v>
       </c>
       <c r="L1096" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M1096" t="n">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="N1096" t="n">
         <v>220.00713026296</v>
       </c>
       <c r="O1096" t="n">
-        <v>77002.49559203601</v>
+        <v>55001.78256574</v>
       </c>
       <c r="P1096" t="n">
         <v>260</v>
       </c>
       <c r="Q1096" t="n">
-        <v>91000</v>
+        <v>65000</v>
       </c>
     </row>
     <row r="1097">

--- a/bodegas/LJ-101.xlsx
+++ b/bodegas/LJ-101.xlsx
@@ -944,10 +944,10 @@
         <v>71</v>
       </c>
       <c r="N13" t="n">
-        <v>1811.3053012048</v>
+        <v>1811.3053333333</v>
       </c>
       <c r="O13" t="n">
-        <v>128602.6763855408</v>
+        <v>128602.6786666643</v>
       </c>
       <c r="P13" t="n">
         <v>2600</v>
@@ -1331,22 +1331,22 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N23" t="n">
         <v>15238.01</v>
       </c>
       <c r="O23" t="n">
-        <v>304760.2</v>
+        <v>289522.19</v>
       </c>
       <c r="P23" t="n">
         <v>40400</v>
       </c>
       <c r="Q23" t="n">
-        <v>808000</v>
+        <v>767600</v>
       </c>
     </row>
     <row r="24">
@@ -1615,22 +1615,22 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M30" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="N30" t="n">
         <v>2812</v>
       </c>
       <c r="O30" t="n">
-        <v>64676</v>
+        <v>47804</v>
       </c>
       <c r="P30" t="n">
         <v>5000</v>
       </c>
       <c r="Q30" t="n">
-        <v>115000</v>
+        <v>85000</v>
       </c>
     </row>
     <row r="31">
@@ -1698,22 +1698,22 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M32" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="N32" t="n">
         <v>2445.67</v>
       </c>
       <c r="O32" t="n">
-        <v>51359.07</v>
+        <v>39130.72</v>
       </c>
       <c r="P32" t="n">
         <v>4600</v>
       </c>
       <c r="Q32" t="n">
-        <v>96600</v>
+        <v>73600</v>
       </c>
     </row>
     <row r="33">
@@ -2177,22 +2177,22 @@
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M44" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="N44" t="n">
-        <v>3716.3301923077</v>
+        <v>3716.3301935484</v>
       </c>
       <c r="O44" t="n">
-        <v>89191.92461538481</v>
+        <v>74326.603870968</v>
       </c>
       <c r="P44" t="n">
         <v>9500</v>
       </c>
       <c r="Q44" t="n">
-        <v>228000</v>
+        <v>190000</v>
       </c>
     </row>
     <row r="45">
@@ -2216,22 +2216,22 @@
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M45" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N45" t="n">
         <v>4113.75</v>
       </c>
       <c r="O45" t="n">
-        <v>12341.25</v>
+        <v>4113.75</v>
       </c>
       <c r="P45" t="n">
         <v>9900</v>
       </c>
       <c r="Q45" t="n">
-        <v>29700</v>
+        <v>9900</v>
       </c>
     </row>
     <row r="46">
@@ -3409,10 +3409,10 @@
         <v>1</v>
       </c>
       <c r="N72" t="n">
-        <v>30708.862857143</v>
+        <v>30708.856153846</v>
       </c>
       <c r="O72" t="n">
-        <v>30708.862857143</v>
+        <v>30708.856153846</v>
       </c>
       <c r="P72" t="n">
         <v>53500</v>
@@ -3576,22 +3576,22 @@
         <v>0</v>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M76" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N76" t="n">
-        <v>17085.518571429</v>
+        <v>17085.49</v>
       </c>
       <c r="O76" t="n">
-        <v>119598.630000003</v>
+        <v>102512.94</v>
       </c>
       <c r="P76" t="n">
         <v>29200</v>
       </c>
       <c r="Q76" t="n">
-        <v>204400</v>
+        <v>175200</v>
       </c>
     </row>
     <row r="77">
@@ -3919,10 +3919,10 @@
         <v>1</v>
       </c>
       <c r="N84" t="n">
-        <v>7407.7300526316</v>
+        <v>7407.7300533333</v>
       </c>
       <c r="O84" t="n">
-        <v>7407.7300526316</v>
+        <v>7407.7300533333</v>
       </c>
       <c r="P84" t="n">
         <v>10900</v>
@@ -4377,10 +4377,10 @@
         <v>11</v>
       </c>
       <c r="N95" t="n">
-        <v>36574.852142857</v>
+        <v>36574.852195122</v>
       </c>
       <c r="O95" t="n">
-        <v>402323.373571427</v>
+        <v>402323.374146342</v>
       </c>
       <c r="P95" t="n">
         <v>65900</v>
@@ -4656,10 +4656,10 @@
         <v>6</v>
       </c>
       <c r="N101" t="n">
-        <v>141416.88454545</v>
+        <v>141416.88456026</v>
       </c>
       <c r="O101" t="n">
-        <v>848501.3072727001</v>
+        <v>848501.3073615599</v>
       </c>
       <c r="P101" t="n">
         <v>251900</v>
@@ -5017,22 +5017,22 @@
         <v>0</v>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M110" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N110" t="n">
         <v>20961.76</v>
       </c>
       <c r="O110" t="n">
-        <v>251541.12</v>
+        <v>230579.36</v>
       </c>
       <c r="P110" t="n">
         <v>38300</v>
       </c>
       <c r="Q110" t="n">
-        <v>459600</v>
+        <v>421300</v>
       </c>
     </row>
     <row r="111">
@@ -5644,22 +5644,22 @@
         <v>0</v>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M124" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N124" t="n">
-        <v>580.36600536193</v>
+        <v>580.36599462366</v>
       </c>
       <c r="O124" t="n">
-        <v>10446.58809651474</v>
+        <v>9866.22190860222</v>
       </c>
       <c r="P124" t="n">
         <v>6800</v>
       </c>
       <c r="Q124" t="n">
-        <v>122400</v>
+        <v>115600</v>
       </c>
     </row>
     <row r="125">
@@ -5736,22 +5736,22 @@
         <v>0</v>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M126" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N126" t="n">
-        <v>28.165539906103</v>
+        <v>28.165518867925</v>
       </c>
       <c r="O126" t="n">
-        <v>704.138497652575</v>
+        <v>675.9724528302</v>
       </c>
       <c r="P126" t="n">
         <v>6800</v>
       </c>
       <c r="Q126" t="n">
-        <v>170000</v>
+        <v>163200</v>
       </c>
     </row>
     <row r="127">
@@ -6687,10 +6687,10 @@
         <v>1</v>
       </c>
       <c r="N148" t="n">
-        <v>4333.6046666667</v>
+        <v>4333.6116666667</v>
       </c>
       <c r="O148" t="n">
-        <v>4333.6046666667</v>
+        <v>4333.6116666667</v>
       </c>
       <c r="P148" t="n">
         <v>7500</v>
@@ -7703,10 +7703,10 @@
         <v>41</v>
       </c>
       <c r="N171" t="n">
-        <v>1950.2147103275</v>
+        <v>1950.21469429</v>
       </c>
       <c r="O171" t="n">
-        <v>79958.8031234275</v>
+        <v>79958.80246589</v>
       </c>
       <c r="P171" t="n">
         <v>2900</v>
@@ -8035,22 +8035,22 @@
         <v>0</v>
       </c>
       <c r="L179" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M179" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N179" t="n">
         <v>39171.85</v>
       </c>
       <c r="O179" t="n">
-        <v>391718.5</v>
+        <v>313374.8</v>
       </c>
       <c r="P179" t="n">
         <v>68900</v>
       </c>
       <c r="Q179" t="n">
-        <v>689000</v>
+        <v>551200</v>
       </c>
     </row>
     <row r="180">
@@ -8117,22 +8117,22 @@
         <v>0</v>
       </c>
       <c r="L181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M181" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N181" t="n">
         <v>14233.54</v>
       </c>
       <c r="O181" t="n">
-        <v>370072.04</v>
+        <v>355838.5</v>
       </c>
       <c r="P181" t="n">
         <v>10000</v>
       </c>
       <c r="Q181" t="n">
-        <v>260000</v>
+        <v>250000</v>
       </c>
     </row>
     <row r="182">
@@ -8161,22 +8161,22 @@
         <v>0</v>
       </c>
       <c r="L182" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M182" t="n">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="N182" t="n">
-        <v>1098.0561100153</v>
+        <v>1098.0566124294</v>
       </c>
       <c r="O182" t="n">
-        <v>592950.299408262</v>
+        <v>586362.2310372996</v>
       </c>
       <c r="P182" t="n">
         <v>1500</v>
       </c>
       <c r="Q182" t="n">
-        <v>810000</v>
+        <v>801000</v>
       </c>
     </row>
     <row r="183">
@@ -8248,22 +8248,22 @@
         <v>0</v>
       </c>
       <c r="L184" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M184" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N184" t="n">
         <v>6295.2</v>
       </c>
       <c r="O184" t="n">
-        <v>62952</v>
+        <v>50361.6</v>
       </c>
       <c r="P184" t="n">
         <v>10500</v>
       </c>
       <c r="Q184" t="n">
-        <v>105000</v>
+        <v>84000</v>
       </c>
     </row>
     <row r="185">
@@ -8607,22 +8607,22 @@
         <v>0</v>
       </c>
       <c r="L192" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M192" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N192" t="n">
         <v>13593.35</v>
       </c>
       <c r="O192" t="n">
-        <v>312647.05</v>
+        <v>285460.35</v>
       </c>
       <c r="P192" t="n">
         <v>25500</v>
       </c>
       <c r="Q192" t="n">
-        <v>586500</v>
+        <v>535500</v>
       </c>
     </row>
     <row r="193">
@@ -9182,10 +9182,10 @@
         <v>62</v>
       </c>
       <c r="N205" t="n">
-        <v>2582.2559749444</v>
+        <v>2582.255965161</v>
       </c>
       <c r="O205" t="n">
-        <v>160099.8704465528</v>
+        <v>160099.869839982</v>
       </c>
       <c r="P205" t="n">
         <v>4500</v>
@@ -9360,22 +9360,22 @@
         <v>0</v>
       </c>
       <c r="L209" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M209" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="N209" t="n">
-        <v>2033.5658041958</v>
+        <v>2033.56088</v>
       </c>
       <c r="O209" t="n">
-        <v>65074.1057342656</v>
+        <v>40671.2176</v>
       </c>
       <c r="P209" t="n">
         <v>4100</v>
       </c>
       <c r="Q209" t="n">
-        <v>131200</v>
+        <v>82000</v>
       </c>
     </row>
     <row r="210">
@@ -9638,10 +9638,10 @@
         <v>388</v>
       </c>
       <c r="N215" t="n">
-        <v>3158.8608230874</v>
+        <v>3158.86082365</v>
       </c>
       <c r="O215" t="n">
-        <v>1225637.999357911</v>
+        <v>1225637.9995762</v>
       </c>
       <c r="P215" t="n">
         <v>5600</v>
@@ -9730,10 +9730,10 @@
         <v>140</v>
       </c>
       <c r="N217" t="n">
-        <v>3841.6247414634</v>
+        <v>3841.6247693817</v>
       </c>
       <c r="O217" t="n">
-        <v>537827.463804876</v>
+        <v>537827.467713438</v>
       </c>
       <c r="P217" t="n">
         <v>6900</v>
@@ -9860,22 +9860,22 @@
         <v>0</v>
       </c>
       <c r="L220" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M220" t="n">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="N220" t="n">
-        <v>3230.0675874126</v>
+        <v>3230.0675313059</v>
       </c>
       <c r="O220" t="n">
-        <v>268095.6097552458</v>
+        <v>245485.1323792484</v>
       </c>
       <c r="P220" t="n">
         <v>6200</v>
       </c>
       <c r="Q220" t="n">
-        <v>514600</v>
+        <v>471200</v>
       </c>
     </row>
     <row r="221">
@@ -10044,22 +10044,22 @@
         <v>0</v>
       </c>
       <c r="L224" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M224" t="n">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="N224" t="n">
-        <v>2694.8233333333</v>
+        <v>2694.8232839963</v>
       </c>
       <c r="O224" t="n">
-        <v>512016.433333327</v>
+        <v>468899.2514153562</v>
       </c>
       <c r="P224" t="n">
         <v>4900</v>
       </c>
       <c r="Q224" t="n">
-        <v>931000</v>
+        <v>852600</v>
       </c>
     </row>
     <row r="225">
@@ -10136,22 +10136,22 @@
         <v>0</v>
       </c>
       <c r="L226" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M226" t="n">
-        <v>1032</v>
+        <v>942</v>
       </c>
       <c r="N226" t="n">
         <v>156.25</v>
       </c>
       <c r="O226" t="n">
-        <v>161250</v>
+        <v>147187.5</v>
       </c>
       <c r="P226" t="n">
         <v>250</v>
       </c>
       <c r="Q226" t="n">
-        <v>258000</v>
+        <v>235500</v>
       </c>
     </row>
     <row r="227">
@@ -10416,10 +10416,10 @@
         <v>24</v>
       </c>
       <c r="N232" t="n">
-        <v>3795.7100070822</v>
+        <v>3795.7100070872</v>
       </c>
       <c r="O232" t="n">
-        <v>91097.0401699728</v>
+        <v>91097.04017009281</v>
       </c>
       <c r="P232" t="n">
         <v>6200</v>
@@ -10641,10 +10641,10 @@
         <v>10</v>
       </c>
       <c r="N237" t="n">
-        <v>4890.9300467563</v>
+        <v>4890.9300468384</v>
       </c>
       <c r="O237" t="n">
-        <v>48909.300467563</v>
+        <v>48909.300468384</v>
       </c>
       <c r="P237" t="n">
         <v>8200</v>
@@ -10730,22 +10730,22 @@
         <v>0</v>
       </c>
       <c r="L239" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M239" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="N239" t="n">
         <v>468</v>
       </c>
       <c r="O239" t="n">
-        <v>4680</v>
+        <v>2808</v>
       </c>
       <c r="P239" t="n">
         <v>900</v>
       </c>
       <c r="Q239" t="n">
-        <v>9000</v>
+        <v>5400</v>
       </c>
     </row>
     <row r="240">
@@ -10825,22 +10825,22 @@
         <v>0</v>
       </c>
       <c r="L241" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M241" t="n">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="N241" t="n">
         <v>1203.38</v>
       </c>
       <c r="O241" t="n">
-        <v>64982.52</v>
+        <v>50541.96000000001</v>
       </c>
       <c r="P241" t="n">
         <v>1900</v>
       </c>
       <c r="Q241" t="n">
-        <v>102600</v>
+        <v>79800</v>
       </c>
     </row>
     <row r="242">
@@ -11318,25 +11318,25 @@
         <v>3</v>
       </c>
       <c r="K252" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L252" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M252" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="N252" t="n">
         <v>10716.34</v>
       </c>
       <c r="O252" t="n">
-        <v>32149.02</v>
+        <v>139312.42</v>
       </c>
       <c r="P252" t="n">
         <v>39000</v>
       </c>
       <c r="Q252" t="n">
-        <v>117000</v>
+        <v>507000</v>
       </c>
     </row>
     <row r="253">
@@ -11501,22 +11501,22 @@
         <v>0</v>
       </c>
       <c r="L256" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="M256" t="n">
-        <v>301</v>
+        <v>274</v>
       </c>
       <c r="N256" t="n">
         <v>489.88</v>
       </c>
       <c r="O256" t="n">
-        <v>147453.88</v>
+        <v>134227.12</v>
       </c>
       <c r="P256" t="n">
         <v>700</v>
       </c>
       <c r="Q256" t="n">
-        <v>210700</v>
+        <v>191800</v>
       </c>
     </row>
     <row r="257">
@@ -11630,10 +11630,10 @@
         <v>134</v>
       </c>
       <c r="N259" t="n">
-        <v>3240.8500303951</v>
+        <v>3240.8500305344</v>
       </c>
       <c r="O259" t="n">
-        <v>434273.9040729434</v>
+        <v>434273.9040916096</v>
       </c>
       <c r="P259" t="n">
         <v>5200</v>
@@ -11814,10 +11814,10 @@
         <v>12</v>
       </c>
       <c r="N263" t="n">
-        <v>14822.378861885</v>
+        <v>14822.378858502</v>
       </c>
       <c r="O263" t="n">
-        <v>177868.54634262</v>
+        <v>177868.546302024</v>
       </c>
       <c r="P263" t="n">
         <v>24900</v>
@@ -11898,25 +11898,25 @@
         <v>224</v>
       </c>
       <c r="K265" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L265" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="M265" t="n">
-        <v>224</v>
+        <v>301</v>
       </c>
       <c r="N265" t="n">
         <v>2090.85</v>
       </c>
       <c r="O265" t="n">
-        <v>468350.4</v>
+        <v>629345.85</v>
       </c>
       <c r="P265" t="n">
         <v>2900</v>
       </c>
       <c r="Q265" t="n">
-        <v>649600</v>
+        <v>872900</v>
       </c>
     </row>
     <row r="266">
@@ -12851,10 +12851,10 @@
         <v>25</v>
       </c>
       <c r="N286" t="n">
-        <v>3041.6600128617</v>
+        <v>3041.660012945</v>
       </c>
       <c r="O286" t="n">
-        <v>76041.50032154251</v>
+        <v>76041.50032362499</v>
       </c>
       <c r="P286" t="n">
         <v>5500</v>
@@ -13115,10 +13115,10 @@
         <v>85</v>
       </c>
       <c r="N292" t="n">
-        <v>1592.5673455845</v>
+        <v>1592.5672645976</v>
       </c>
       <c r="O292" t="n">
-        <v>135368.2243746825</v>
+        <v>135368.217490796</v>
       </c>
       <c r="P292" t="n">
         <v>3900</v>
@@ -13324,22 +13324,22 @@
         <v>0</v>
       </c>
       <c r="L297" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M297" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="N297" t="n">
         <v>4717</v>
       </c>
       <c r="O297" t="n">
-        <v>221699</v>
+        <v>202831</v>
       </c>
       <c r="P297" t="n">
         <v>7900</v>
       </c>
       <c r="Q297" t="n">
-        <v>371300</v>
+        <v>339700</v>
       </c>
     </row>
     <row r="298">
@@ -13550,22 +13550,22 @@
         <v>0</v>
       </c>
       <c r="L302" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M302" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="N302" t="n">
         <v>4648.6</v>
       </c>
       <c r="O302" t="n">
-        <v>232430</v>
+        <v>213835.6</v>
       </c>
       <c r="P302" t="n">
         <v>8900</v>
       </c>
       <c r="Q302" t="n">
-        <v>445000</v>
+        <v>409400</v>
       </c>
     </row>
     <row r="303">
@@ -13950,22 +13950,22 @@
         <v>0</v>
       </c>
       <c r="L311" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M311" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N311" t="n">
         <v>9414.309999999999</v>
       </c>
       <c r="O311" t="n">
-        <v>56485.86</v>
+        <v>47071.55</v>
       </c>
       <c r="P311" t="n">
         <v>16900</v>
       </c>
       <c r="Q311" t="n">
-        <v>101400</v>
+        <v>84500</v>
       </c>
     </row>
     <row r="312">
@@ -14138,22 +14138,22 @@
         <v>0</v>
       </c>
       <c r="L315" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M315" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="N315" t="n">
         <v>4635.49</v>
       </c>
       <c r="O315" t="n">
-        <v>55625.88</v>
+        <v>13906.47</v>
       </c>
       <c r="P315" t="n">
         <v>7500</v>
       </c>
       <c r="Q315" t="n">
-        <v>90000</v>
+        <v>22500</v>
       </c>
     </row>
     <row r="316">
@@ -14237,10 +14237,10 @@
         <v>23</v>
       </c>
       <c r="N317" t="n">
-        <v>2021.7211225106</v>
+        <v>2021.7211231884</v>
       </c>
       <c r="O317" t="n">
-        <v>46499.5858177438</v>
+        <v>46499.5858333332</v>
       </c>
       <c r="P317" t="n">
         <v>2400</v>
@@ -14324,22 +14324,22 @@
         <v>0</v>
       </c>
       <c r="L319" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M319" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N319" t="n">
         <v>16897</v>
       </c>
       <c r="O319" t="n">
-        <v>135176</v>
+        <v>101382</v>
       </c>
       <c r="P319" t="n">
         <v>27900</v>
       </c>
       <c r="Q319" t="n">
-        <v>223200</v>
+        <v>167400</v>
       </c>
     </row>
     <row r="320">
@@ -14556,22 +14556,22 @@
         <v>0</v>
       </c>
       <c r="L324" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M324" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="N324" t="n">
         <v>5853</v>
       </c>
       <c r="O324" t="n">
-        <v>64383</v>
+        <v>46824</v>
       </c>
       <c r="P324" t="n">
         <v>9900</v>
       </c>
       <c r="Q324" t="n">
-        <v>108900</v>
+        <v>79200</v>
       </c>
     </row>
     <row r="325">
@@ -14741,22 +14741,22 @@
         <v>0</v>
       </c>
       <c r="L328" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M328" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="N328" t="n">
         <v>11921.4</v>
       </c>
       <c r="O328" t="n">
-        <v>238428</v>
+        <v>214585.2</v>
       </c>
       <c r="P328" t="n">
         <v>19900</v>
       </c>
       <c r="Q328" t="n">
-        <v>398000</v>
+        <v>358200</v>
       </c>
     </row>
     <row r="329">
@@ -15105,22 +15105,22 @@
         <v>0</v>
       </c>
       <c r="L336" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M336" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N336" t="n">
         <v>3751</v>
       </c>
       <c r="O336" t="n">
-        <v>476377</v>
+        <v>472626</v>
       </c>
       <c r="P336" t="n">
         <v>6400</v>
       </c>
       <c r="Q336" t="n">
-        <v>812800</v>
+        <v>806400</v>
       </c>
     </row>
     <row r="337">
@@ -15292,22 +15292,22 @@
         <v>0</v>
       </c>
       <c r="L340" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M340" t="n">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="N340" t="n">
-        <v>1630.9233118002</v>
+        <v>1630.9233376736</v>
       </c>
       <c r="O340" t="n">
-        <v>215281.8771576264</v>
+        <v>200603.5705338528</v>
       </c>
       <c r="P340" t="n">
         <v>2500</v>
       </c>
       <c r="Q340" t="n">
-        <v>330000</v>
+        <v>307500</v>
       </c>
     </row>
     <row r="341">
@@ -15344,10 +15344,10 @@
         <v>1</v>
       </c>
       <c r="N341" t="n">
-        <v>1467.3264227642</v>
+        <v>1467.3258333333</v>
       </c>
       <c r="O341" t="n">
-        <v>1467.3264227642</v>
+        <v>1467.3258333333</v>
       </c>
       <c r="P341" t="n">
         <v>2500</v>
@@ -15384,22 +15384,22 @@
         <v>0</v>
       </c>
       <c r="L342" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="M342" t="n">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="N342" t="n">
-        <v>1690.6006518987</v>
+        <v>1690.6000587084</v>
       </c>
       <c r="O342" t="n">
-        <v>189347.2730126544</v>
+        <v>157225.8054598812</v>
       </c>
       <c r="P342" t="n">
         <v>2900</v>
       </c>
       <c r="Q342" t="n">
-        <v>324800</v>
+        <v>269700</v>
       </c>
     </row>
     <row r="343">
@@ -15430,22 +15430,22 @@
         <v>0</v>
       </c>
       <c r="L343" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M343" t="n">
-        <v>474</v>
+        <v>458</v>
       </c>
       <c r="N343" t="n">
-        <v>1550.1933219945</v>
+        <v>1550.1933547279</v>
       </c>
       <c r="O343" t="n">
-        <v>734791.634625393</v>
+        <v>709988.5564653781</v>
       </c>
       <c r="P343" t="n">
         <v>2500</v>
       </c>
       <c r="Q343" t="n">
-        <v>1185000</v>
+        <v>1145000</v>
       </c>
     </row>
     <row r="344">
@@ -15482,10 +15482,10 @@
         <v>1</v>
       </c>
       <c r="N344" t="n">
-        <v>1579.3908883249</v>
+        <v>1579.3908418367</v>
       </c>
       <c r="O344" t="n">
-        <v>1579.3908883249</v>
+        <v>1579.3908418367</v>
       </c>
       <c r="P344" t="n">
         <v>2900</v>
@@ -15528,10 +15528,10 @@
         <v>293</v>
       </c>
       <c r="N345" t="n">
-        <v>2403.5107961064</v>
+        <v>2403.5109560769</v>
       </c>
       <c r="O345" t="n">
-        <v>704228.6632591751</v>
+        <v>704228.7101305317</v>
       </c>
       <c r="P345" t="n">
         <v>3500</v>
@@ -15568,22 +15568,22 @@
         <v>0</v>
       </c>
       <c r="L346" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M346" t="n">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="N346" t="n">
-        <v>2521.5415942029</v>
+        <v>2521.5405895197</v>
       </c>
       <c r="O346" t="n">
-        <v>257197.2426086958</v>
+        <v>231981.7342358124</v>
       </c>
       <c r="P346" t="n">
         <v>3900</v>
       </c>
       <c r="Q346" t="n">
-        <v>397800</v>
+        <v>358800</v>
       </c>
     </row>
     <row r="347">
@@ -15651,10 +15651,10 @@
         <v>64</v>
       </c>
       <c r="N348" t="n">
-        <v>1232.8080088496</v>
+        <v>1232.8076255708</v>
       </c>
       <c r="O348" t="n">
-        <v>78899.71256637439</v>
+        <v>78899.6880365312</v>
       </c>
       <c r="P348" t="n">
         <v>2400</v>
@@ -18658,10 +18658,10 @@
         <v>201</v>
       </c>
       <c r="N416" t="n">
-        <v>2029.8737091988</v>
+        <v>2029.8737110341</v>
       </c>
       <c r="O416" t="n">
-        <v>408004.6155489588</v>
+        <v>408004.6159178541</v>
       </c>
       <c r="P416" t="n">
         <v>3600</v>
@@ -19502,22 +19502,22 @@
         <v>0</v>
       </c>
       <c r="L436" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M436" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N436" t="n">
         <v>3877.89</v>
       </c>
       <c r="O436" t="n">
-        <v>116336.7</v>
+        <v>96947.25</v>
       </c>
       <c r="P436" t="n">
         <v>6500</v>
       </c>
       <c r="Q436" t="n">
-        <v>195000</v>
+        <v>162500</v>
       </c>
     </row>
     <row r="437">
@@ -20195,10 +20195,10 @@
         <v>15</v>
       </c>
       <c r="N452" t="n">
-        <v>11562.038526316</v>
+        <v>11562.038522427</v>
       </c>
       <c r="O452" t="n">
-        <v>173430.57789474</v>
+        <v>173430.577836405</v>
       </c>
       <c r="P452" t="n">
         <v>18500</v>
@@ -20619,22 +20619,22 @@
         <v>0</v>
       </c>
       <c r="L462" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M462" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="N462" t="n">
         <v>4793.53</v>
       </c>
       <c r="O462" t="n">
-        <v>182154.14</v>
+        <v>148599.43</v>
       </c>
       <c r="P462" t="n">
         <v>7900</v>
       </c>
       <c r="Q462" t="n">
-        <v>300200</v>
+        <v>244900</v>
       </c>
     </row>
     <row r="463">
@@ -20921,22 +20921,22 @@
         <v>0</v>
       </c>
       <c r="L469" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M469" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="N469" t="n">
-        <v>1466.8807100592</v>
+        <v>1466.8807185629</v>
       </c>
       <c r="O469" t="n">
-        <v>44006.421301776</v>
+        <v>41072.6601197612</v>
       </c>
       <c r="P469" t="n">
         <v>3400</v>
       </c>
       <c r="Q469" t="n">
-        <v>102000</v>
+        <v>95200</v>
       </c>
     </row>
     <row r="470">
@@ -21147,10 +21147,10 @@
         <v>76</v>
       </c>
       <c r="N474" t="n">
-        <v>1560.9995548961</v>
+        <v>1560.9996939288</v>
       </c>
       <c r="O474" t="n">
-        <v>118635.9661721036</v>
+        <v>118635.9767385888</v>
       </c>
       <c r="P474" t="n">
         <v>2900</v>
@@ -21838,22 +21838,22 @@
         <v>0</v>
       </c>
       <c r="L490" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M490" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="N490" t="n">
         <v>9627.34</v>
       </c>
       <c r="O490" t="n">
-        <v>125155.42</v>
+        <v>96273.39999999999</v>
       </c>
       <c r="P490" t="n">
         <v>15900</v>
       </c>
       <c r="Q490" t="n">
-        <v>206700</v>
+        <v>159000</v>
       </c>
     </row>
     <row r="491">
@@ -22731,22 +22731,22 @@
         <v>0</v>
       </c>
       <c r="L510" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M510" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="N510" t="n">
         <v>6232.24</v>
       </c>
       <c r="O510" t="n">
-        <v>62322.39999999999</v>
+        <v>37393.44</v>
       </c>
       <c r="P510" t="n">
         <v>7900</v>
       </c>
       <c r="Q510" t="n">
-        <v>79000</v>
+        <v>47400</v>
       </c>
     </row>
     <row r="511">
@@ -23254,22 +23254,22 @@
         <v>0</v>
       </c>
       <c r="L522" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M522" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="N522" t="n">
         <v>4437</v>
       </c>
       <c r="O522" t="n">
-        <v>70992</v>
+        <v>57681</v>
       </c>
       <c r="P522" t="n">
         <v>4900</v>
       </c>
       <c r="Q522" t="n">
-        <v>78400</v>
+        <v>63700</v>
       </c>
     </row>
     <row r="523">
@@ -23525,22 +23525,22 @@
         <v>0</v>
       </c>
       <c r="L528" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M528" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="N528" t="n">
         <v>2634.61</v>
       </c>
       <c r="O528" t="n">
-        <v>102749.79</v>
+        <v>84307.52</v>
       </c>
       <c r="P528" t="n">
         <v>4200</v>
       </c>
       <c r="Q528" t="n">
-        <v>163800</v>
+        <v>134400</v>
       </c>
     </row>
     <row r="529">
@@ -23577,10 +23577,10 @@
         <v>35</v>
       </c>
       <c r="N529" t="n">
-        <v>3113.8900265957</v>
+        <v>3113.890027137</v>
       </c>
       <c r="O529" t="n">
-        <v>108986.1509308495</v>
+        <v>108986.150949795</v>
       </c>
       <c r="P529" t="n">
         <v>5000</v>
@@ -23663,22 +23663,22 @@
         <v>0</v>
       </c>
       <c r="L531" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M531" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="N531" t="n">
         <v>4690.64</v>
       </c>
       <c r="O531" t="n">
-        <v>206388.16</v>
+        <v>150100.48</v>
       </c>
       <c r="P531" t="n">
         <v>7500</v>
       </c>
       <c r="Q531" t="n">
-        <v>330000</v>
+        <v>240000</v>
       </c>
     </row>
     <row r="532">
@@ -23945,10 +23945,10 @@
         <v>13</v>
       </c>
       <c r="N537" t="n">
-        <v>5218.1705238095</v>
+        <v>5218.1705269461</v>
       </c>
       <c r="O537" t="n">
-        <v>67836.2168095235</v>
+        <v>67836.2168502993</v>
       </c>
       <c r="P537" t="n">
         <v>8500</v>
@@ -23991,10 +23991,10 @@
         <v>15</v>
       </c>
       <c r="N538" t="n">
-        <v>3610.6500252207</v>
+        <v>3610.6500253807</v>
       </c>
       <c r="O538" t="n">
-        <v>54159.75037831051</v>
+        <v>54159.75038071049</v>
       </c>
       <c r="P538" t="n">
         <v>5800</v>
@@ -24175,22 +24175,22 @@
         <v>0</v>
       </c>
       <c r="L542" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M542" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N542" t="n">
         <v>3920</v>
       </c>
       <c r="O542" t="n">
-        <v>50960</v>
+        <v>47040</v>
       </c>
       <c r="P542" t="n">
         <v>4900</v>
       </c>
       <c r="Q542" t="n">
-        <v>63700</v>
+        <v>58800</v>
       </c>
     </row>
     <row r="543">
@@ -24270,22 +24270,22 @@
         <v>0</v>
       </c>
       <c r="L544" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M544" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="N544" t="n">
         <v>4227.77</v>
       </c>
       <c r="O544" t="n">
-        <v>169110.8</v>
+        <v>152199.72</v>
       </c>
       <c r="P544" t="n">
         <v>6900</v>
       </c>
       <c r="Q544" t="n">
-        <v>276000</v>
+        <v>248400</v>
       </c>
     </row>
     <row r="545">
@@ -24365,22 +24365,22 @@
         <v>0</v>
       </c>
       <c r="L546" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M546" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="N546" t="n">
         <v>3965.02</v>
       </c>
       <c r="O546" t="n">
-        <v>174460.88</v>
+        <v>162565.82</v>
       </c>
       <c r="P546" t="n">
         <v>6500</v>
       </c>
       <c r="Q546" t="n">
-        <v>286000</v>
+        <v>266500</v>
       </c>
     </row>
     <row r="547">
@@ -24411,22 +24411,22 @@
         <v>0</v>
       </c>
       <c r="L547" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M547" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="N547" t="n">
         <v>5791.05</v>
       </c>
       <c r="O547" t="n">
-        <v>121612.05</v>
+        <v>86865.75</v>
       </c>
       <c r="P547" t="n">
         <v>9300</v>
       </c>
       <c r="Q547" t="n">
-        <v>195300</v>
+        <v>139500</v>
       </c>
     </row>
     <row r="548">
@@ -24647,10 +24647,10 @@
         <v>150</v>
       </c>
       <c r="N552" t="n">
-        <v>1664.3585273632</v>
+        <v>1664.3584236948</v>
       </c>
       <c r="O552" t="n">
-        <v>249653.77910448</v>
+        <v>249653.76355422</v>
       </c>
       <c r="P552" t="n">
         <v>2900</v>
@@ -25205,22 +25205,22 @@
         <v>0</v>
       </c>
       <c r="L564" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M564" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N564" t="n">
         <v>34546</v>
       </c>
       <c r="O564" t="n">
-        <v>138184</v>
+        <v>103638</v>
       </c>
       <c r="P564" t="n">
         <v>57900</v>
       </c>
       <c r="Q564" t="n">
-        <v>231600</v>
+        <v>173700</v>
       </c>
     </row>
     <row r="565">
@@ -25297,22 +25297,22 @@
         <v>0</v>
       </c>
       <c r="L566" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M566" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N566" t="n">
-        <v>23521.62453125</v>
+        <v>23521.624354839</v>
       </c>
       <c r="O566" t="n">
-        <v>235216.2453125</v>
+        <v>188172.994838712</v>
       </c>
       <c r="P566" t="n">
         <v>39000</v>
       </c>
       <c r="Q566" t="n">
-        <v>390000</v>
+        <v>312000</v>
       </c>
     </row>
     <row r="567">
@@ -25441,10 +25441,10 @@
         <v>29</v>
       </c>
       <c r="N569" t="n">
-        <v>1778.4725740823</v>
+        <v>1778.4725809313</v>
       </c>
       <c r="O569" t="n">
-        <v>51575.7046483867</v>
+        <v>51575.7048470077</v>
       </c>
       <c r="P569" t="n">
         <v>4900</v>
@@ -26733,22 +26733,22 @@
         <v>0</v>
       </c>
       <c r="L597" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M597" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N597" t="n">
         <v>13687</v>
       </c>
       <c r="O597" t="n">
-        <v>369549</v>
+        <v>355862</v>
       </c>
       <c r="P597" t="n">
         <v>21900</v>
       </c>
       <c r="Q597" t="n">
-        <v>591300</v>
+        <v>569400</v>
       </c>
     </row>
     <row r="598">
@@ -28172,10 +28172,10 @@
         <v>125</v>
       </c>
       <c r="N628" t="n">
-        <v>2328.1187488882</v>
+        <v>2328.118739546</v>
       </c>
       <c r="O628" t="n">
-        <v>291014.843611025</v>
+        <v>291014.84244325</v>
       </c>
       <c r="P628" t="n">
         <v>4500</v>
@@ -28902,22 +28902,22 @@
         <v>0</v>
       </c>
       <c r="L644" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M644" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="N644" t="n">
         <v>13210</v>
       </c>
       <c r="O644" t="n">
-        <v>250990</v>
+        <v>184940</v>
       </c>
       <c r="P644" t="n">
         <v>23900</v>
       </c>
       <c r="Q644" t="n">
-        <v>454100</v>
+        <v>334600</v>
       </c>
     </row>
     <row r="645">
@@ -28948,22 +28948,22 @@
         <v>0</v>
       </c>
       <c r="L645" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M645" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N645" t="n">
         <v>76839</v>
       </c>
       <c r="O645" t="n">
-        <v>76839</v>
+        <v>0</v>
       </c>
       <c r="P645" t="n">
         <v>122900</v>
       </c>
       <c r="Q645" t="n">
-        <v>122900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="646">
@@ -29046,10 +29046,10 @@
         <v>88</v>
       </c>
       <c r="N647" t="n">
-        <v>3903.7362017804</v>
+        <v>3903.736812933</v>
       </c>
       <c r="O647" t="n">
-        <v>343528.7857566752</v>
+        <v>343528.839538104</v>
       </c>
       <c r="P647" t="n">
         <v>7500</v>
@@ -29449,22 +29449,22 @@
         <v>0</v>
       </c>
       <c r="L656" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M656" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N656" t="n">
         <v>9839</v>
       </c>
       <c r="O656" t="n">
-        <v>78712</v>
+        <v>68873</v>
       </c>
       <c r="P656" t="n">
         <v>16900</v>
       </c>
       <c r="Q656" t="n">
-        <v>135200</v>
+        <v>118300</v>
       </c>
     </row>
     <row r="657">
@@ -29547,10 +29547,10 @@
         <v>65</v>
       </c>
       <c r="N658" t="n">
-        <v>5869.1727464789</v>
+        <v>5869.1727391742</v>
       </c>
       <c r="O658" t="n">
-        <v>381496.2285211285</v>
+        <v>381496.228046323</v>
       </c>
       <c r="P658" t="n">
         <v>9500</v>
@@ -29771,22 +29771,22 @@
         <v>0</v>
       </c>
       <c r="L663" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M663" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N663" t="n">
         <v>8637</v>
       </c>
       <c r="O663" t="n">
-        <v>69096</v>
+        <v>51822</v>
       </c>
       <c r="P663" t="n">
         <v>14500</v>
       </c>
       <c r="Q663" t="n">
-        <v>116000</v>
+        <v>87000</v>
       </c>
     </row>
     <row r="664">
@@ -29955,22 +29955,22 @@
         <v>0</v>
       </c>
       <c r="L667" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M667" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="N667" t="n">
         <v>3898</v>
       </c>
       <c r="O667" t="n">
-        <v>81858</v>
+        <v>70164</v>
       </c>
       <c r="P667" t="n">
         <v>6900</v>
       </c>
       <c r="Q667" t="n">
-        <v>144900</v>
+        <v>124200</v>
       </c>
     </row>
     <row r="668">
@@ -30093,22 +30093,22 @@
         <v>0</v>
       </c>
       <c r="L670" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M670" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N670" t="n">
         <v>5682</v>
       </c>
       <c r="O670" t="n">
-        <v>56820</v>
+        <v>45456</v>
       </c>
       <c r="P670" t="n">
         <v>9900</v>
       </c>
       <c r="Q670" t="n">
-        <v>99000</v>
+        <v>79200</v>
       </c>
     </row>
     <row r="671">
@@ -30139,22 +30139,22 @@
         <v>0</v>
       </c>
       <c r="L671" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M671" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N671" t="n">
         <v>5438</v>
       </c>
       <c r="O671" t="n">
-        <v>70694</v>
+        <v>59818</v>
       </c>
       <c r="P671" t="n">
         <v>8900</v>
       </c>
       <c r="Q671" t="n">
-        <v>115700</v>
+        <v>97900</v>
       </c>
     </row>
     <row r="672">
@@ -30231,22 +30231,22 @@
         <v>0</v>
       </c>
       <c r="L673" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M673" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="N673" t="n">
         <v>8806</v>
       </c>
       <c r="O673" t="n">
-        <v>193732</v>
+        <v>176120</v>
       </c>
       <c r="P673" t="n">
         <v>14900</v>
       </c>
       <c r="Q673" t="n">
-        <v>327800</v>
+        <v>298000</v>
       </c>
     </row>
     <row r="674">
@@ -30277,22 +30277,22 @@
         <v>0</v>
       </c>
       <c r="L674" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M674" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N674" t="n">
         <v>23439</v>
       </c>
       <c r="O674" t="n">
-        <v>468780</v>
+        <v>445341</v>
       </c>
       <c r="P674" t="n">
         <v>37900</v>
       </c>
       <c r="Q674" t="n">
-        <v>758000</v>
+        <v>720100</v>
       </c>
     </row>
     <row r="675">
@@ -30323,22 +30323,22 @@
         <v>0</v>
       </c>
       <c r="L675" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M675" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N675" t="n">
         <v>19008</v>
       </c>
       <c r="O675" t="n">
-        <v>570240</v>
+        <v>551232</v>
       </c>
       <c r="P675" t="n">
         <v>30900</v>
       </c>
       <c r="Q675" t="n">
-        <v>927000</v>
+        <v>896100</v>
       </c>
     </row>
     <row r="676">
@@ -30372,22 +30372,22 @@
         <v>0</v>
       </c>
       <c r="L676" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M676" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N676" t="n">
         <v>753</v>
       </c>
       <c r="O676" t="n">
-        <v>90360</v>
+        <v>75300</v>
       </c>
       <c r="P676" t="n">
         <v>1600</v>
       </c>
       <c r="Q676" t="n">
-        <v>192000</v>
+        <v>160000</v>
       </c>
     </row>
     <row r="677">
@@ -30510,22 +30510,22 @@
         <v>0</v>
       </c>
       <c r="L679" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M679" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N679" t="n">
         <v>11348</v>
       </c>
       <c r="O679" t="n">
-        <v>34044</v>
+        <v>22696</v>
       </c>
       <c r="P679" t="n">
         <v>19900</v>
       </c>
       <c r="Q679" t="n">
-        <v>59700</v>
+        <v>39800</v>
       </c>
     </row>
     <row r="680">
@@ -31204,10 +31204,10 @@
         <v>25</v>
       </c>
       <c r="N694" t="n">
-        <v>4268.7047257384</v>
+        <v>4268.7051082251</v>
       </c>
       <c r="O694" t="n">
-        <v>106717.61814346</v>
+        <v>106717.6277056275</v>
       </c>
       <c r="P694" t="n">
         <v>6900</v>
@@ -31382,22 +31382,22 @@
         <v>0</v>
       </c>
       <c r="L698" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M698" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="N698" t="n">
         <v>40073</v>
       </c>
       <c r="O698" t="n">
-        <v>1242263</v>
+        <v>1162117</v>
       </c>
       <c r="P698" t="n">
         <v>64900</v>
       </c>
       <c r="Q698" t="n">
-        <v>2011900</v>
+        <v>1882100</v>
       </c>
     </row>
     <row r="699">
@@ -31428,22 +31428,22 @@
         <v>0</v>
       </c>
       <c r="L699" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M699" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="N699" t="n">
         <v>4303</v>
       </c>
       <c r="O699" t="n">
-        <v>262483</v>
+        <v>245271</v>
       </c>
       <c r="P699" t="n">
         <v>7900</v>
       </c>
       <c r="Q699" t="n">
-        <v>481900</v>
+        <v>450300</v>
       </c>
     </row>
     <row r="700">
@@ -31612,22 +31612,22 @@
         <v>0</v>
       </c>
       <c r="L703" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M703" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="N703" t="n">
         <v>1326</v>
       </c>
       <c r="O703" t="n">
-        <v>49062</v>
+        <v>43758</v>
       </c>
       <c r="P703" t="n">
         <v>2500</v>
       </c>
       <c r="Q703" t="n">
-        <v>92500</v>
+        <v>82500</v>
       </c>
     </row>
     <row r="704">
@@ -31796,22 +31796,22 @@
         <v>0</v>
       </c>
       <c r="L707" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M707" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="N707" t="n">
         <v>2458</v>
       </c>
       <c r="O707" t="n">
-        <v>31954</v>
+        <v>19664</v>
       </c>
       <c r="P707" t="n">
         <v>3500</v>
       </c>
       <c r="Q707" t="n">
-        <v>45500</v>
+        <v>28000</v>
       </c>
     </row>
     <row r="708">
@@ -32072,22 +32072,22 @@
         <v>0</v>
       </c>
       <c r="L713" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M713" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="N713" t="n">
         <v>7253</v>
       </c>
       <c r="O713" t="n">
-        <v>435180</v>
+        <v>413421</v>
       </c>
       <c r="P713" t="n">
         <v>11900</v>
       </c>
       <c r="Q713" t="n">
-        <v>714000</v>
+        <v>678300</v>
       </c>
     </row>
     <row r="714">
@@ -32256,22 +32256,22 @@
         <v>0</v>
       </c>
       <c r="L717" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M717" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N717" t="n">
         <v>64612</v>
       </c>
       <c r="O717" t="n">
-        <v>258448</v>
+        <v>193836</v>
       </c>
       <c r="P717" t="n">
         <v>103900</v>
       </c>
       <c r="Q717" t="n">
-        <v>415600</v>
+        <v>311700</v>
       </c>
     </row>
     <row r="718">
@@ -32398,10 +32398,10 @@
         <v>46</v>
       </c>
       <c r="N720" t="n">
-        <v>4248.6401470588</v>
+        <v>4248.6496363636</v>
       </c>
       <c r="O720" t="n">
-        <v>195437.4467647048</v>
+        <v>195437.8832727256</v>
       </c>
       <c r="P720" t="n">
         <v>5900</v>
@@ -32582,10 +32582,10 @@
         <v>124</v>
       </c>
       <c r="N724" t="n">
-        <v>2079.3841354372</v>
+        <v>2079.384121911</v>
       </c>
       <c r="O724" t="n">
-        <v>257843.6327942128</v>
+        <v>257843.631116964</v>
       </c>
       <c r="P724" t="n">
         <v>2900</v>
@@ -32628,10 +32628,10 @@
         <v>170</v>
       </c>
       <c r="N725" t="n">
-        <v>1803.0152234206</v>
+        <v>1803.0152282542</v>
       </c>
       <c r="O725" t="n">
-        <v>306512.587981502</v>
+        <v>306512.588803214</v>
       </c>
       <c r="P725" t="n">
         <v>2500</v>
@@ -32674,10 +32674,10 @@
         <v>53</v>
       </c>
       <c r="N726" t="n">
-        <v>3306.5953246753</v>
+        <v>3306.5952380952</v>
       </c>
       <c r="O726" t="n">
-        <v>175249.5522077909</v>
+        <v>175249.5476190456</v>
       </c>
       <c r="P726" t="n">
         <v>4900</v>
@@ -32720,10 +32720,10 @@
         <v>64</v>
       </c>
       <c r="N727" t="n">
-        <v>2122.164</v>
+        <v>2122.1639833897</v>
       </c>
       <c r="O727" t="n">
-        <v>135818.496</v>
+        <v>135818.4949369408</v>
       </c>
       <c r="P727" t="n">
         <v>2900</v>
@@ -32766,10 +32766,10 @@
         <v>86</v>
       </c>
       <c r="N728" t="n">
-        <v>2108.7900692042</v>
+        <v>2108.7902645503</v>
       </c>
       <c r="O728" t="n">
-        <v>181355.9459515612</v>
+        <v>181355.9627513258</v>
       </c>
       <c r="P728" t="n">
         <v>2900</v>
@@ -32812,10 +32812,10 @@
         <v>269</v>
       </c>
       <c r="N729" t="n">
-        <v>2056.0837111517</v>
+        <v>2056.0836725935</v>
       </c>
       <c r="O729" t="n">
-        <v>553086.5182998072</v>
+        <v>553086.5079276515</v>
       </c>
       <c r="P729" t="n">
         <v>2900</v>
@@ -33177,22 +33177,22 @@
         <v>0</v>
       </c>
       <c r="L737" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M737" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="N737" t="n">
-        <v>1592.27610957</v>
+        <v>1592.2763108883</v>
       </c>
       <c r="O737" t="n">
-        <v>90759.73824549001</v>
+        <v>85982.92078796821</v>
       </c>
       <c r="P737" t="n">
         <v>2500</v>
       </c>
       <c r="Q737" t="n">
-        <v>142500</v>
+        <v>135000</v>
       </c>
     </row>
     <row r="738">
@@ -33354,22 +33354,22 @@
         <v>0</v>
       </c>
       <c r="L741" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M741" t="n">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="N741" t="n">
-        <v>2311.9221535181</v>
+        <v>2311.9216849015</v>
       </c>
       <c r="O741" t="n">
-        <v>238127.9818123643</v>
+        <v>210384.8733260365</v>
       </c>
       <c r="P741" t="n">
         <v>3500</v>
       </c>
       <c r="Q741" t="n">
-        <v>360500</v>
+        <v>318500</v>
       </c>
     </row>
     <row r="742">
@@ -33400,22 +33400,22 @@
         <v>0</v>
       </c>
       <c r="L742" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M742" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="N742" t="n">
-        <v>1906.1853846154</v>
+        <v>1906.1853271028</v>
       </c>
       <c r="O742" t="n">
-        <v>131526.7915384626</v>
+        <v>127714.4169158876</v>
       </c>
       <c r="P742" t="n">
         <v>2900</v>
       </c>
       <c r="Q742" t="n">
-        <v>200100</v>
+        <v>194300</v>
       </c>
     </row>
     <row r="743">
@@ -33446,22 +33446,22 @@
         <v>0</v>
       </c>
       <c r="L743" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="M743" t="n">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="N743" t="n">
-        <v>3033.7269651741</v>
+        <v>3033.724972973</v>
       </c>
       <c r="O743" t="n">
-        <v>373148.4167164143</v>
+        <v>294271.322378381</v>
       </c>
       <c r="P743" t="n">
         <v>4500</v>
       </c>
       <c r="Q743" t="n">
-        <v>553500</v>
+        <v>436500</v>
       </c>
     </row>
     <row r="744">
@@ -33492,22 +33492,22 @@
         <v>0</v>
       </c>
       <c r="L744" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M744" t="n">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="N744" t="n">
-        <v>2060.1604635762</v>
+        <v>2060.1603355705</v>
       </c>
       <c r="O744" t="n">
-        <v>220437.1696026534</v>
+        <v>203955.8732214795</v>
       </c>
       <c r="P744" t="n">
         <v>2900</v>
       </c>
       <c r="Q744" t="n">
-        <v>310300</v>
+        <v>287100</v>
       </c>
     </row>
     <row r="745">
@@ -33544,10 +33544,10 @@
         <v>101</v>
       </c>
       <c r="N745" t="n">
-        <v>1668.6236893204</v>
+        <v>1668.6240987654</v>
       </c>
       <c r="O745" t="n">
-        <v>168530.9926213604</v>
+        <v>168531.0339753054</v>
       </c>
       <c r="P745" t="n">
         <v>2500</v>
@@ -33590,10 +33590,10 @@
         <v>161</v>
       </c>
       <c r="N746" t="n">
-        <v>2546.9846915888</v>
+        <v>2546.9846816479</v>
       </c>
       <c r="O746" t="n">
-        <v>410064.5353457968</v>
+        <v>410064.5337453119</v>
       </c>
       <c r="P746" t="n">
         <v>3900</v>
@@ -33630,22 +33630,22 @@
         <v>0</v>
       </c>
       <c r="L747" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M747" t="n">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="N747" t="n">
-        <v>1259.2744638514</v>
+        <v>1259.2745016722</v>
       </c>
       <c r="O747" t="n">
-        <v>259410.5395533884</v>
+        <v>251854.90033444</v>
       </c>
       <c r="P747" t="n">
         <v>1900</v>
       </c>
       <c r="Q747" t="n">
-        <v>391400</v>
+        <v>380000</v>
       </c>
     </row>
     <row r="748">
@@ -33859,10 +33859,10 @@
         <v>350</v>
       </c>
       <c r="N752" t="n">
-        <v>692.15211662075</v>
+        <v>692.1521205151799</v>
       </c>
       <c r="O752" t="n">
-        <v>242253.2408172625</v>
+        <v>242253.242180313</v>
       </c>
       <c r="P752" t="n">
         <v>1200</v>
@@ -34596,22 +34596,22 @@
         <v>0</v>
       </c>
       <c r="L768" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M768" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="N768" t="n">
         <v>8945.379999999999</v>
       </c>
       <c r="O768" t="n">
-        <v>590395.08</v>
+        <v>518832.04</v>
       </c>
       <c r="P768" t="n">
         <v>14900</v>
       </c>
       <c r="Q768" t="n">
-        <v>983400</v>
+        <v>864200</v>
       </c>
     </row>
     <row r="769">
@@ -35709,22 +35709,22 @@
         <v>0</v>
       </c>
       <c r="L792" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M792" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N792" t="n">
-        <v>10732.241904762</v>
+        <v>10732.24195122</v>
       </c>
       <c r="O792" t="n">
-        <v>160983.62857143</v>
+        <v>150251.38731708</v>
       </c>
       <c r="P792" t="n">
         <v>25900</v>
       </c>
       <c r="Q792" t="n">
-        <v>388500</v>
+        <v>362600</v>
       </c>
     </row>
     <row r="793">
@@ -35804,22 +35804,22 @@
         <v>0</v>
       </c>
       <c r="L794" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M794" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="N794" t="n">
         <v>7103.81</v>
       </c>
       <c r="O794" t="n">
-        <v>277048.59</v>
+        <v>248633.35</v>
       </c>
       <c r="P794" t="n">
         <v>8900</v>
       </c>
       <c r="Q794" t="n">
-        <v>347100</v>
+        <v>311500</v>
       </c>
     </row>
     <row r="795">
@@ -36084,10 +36084,10 @@
         <v>52</v>
       </c>
       <c r="N800" t="n">
-        <v>1690.8700089847</v>
+        <v>1690.870009009</v>
       </c>
       <c r="O800" t="n">
-        <v>87925.24046720441</v>
+        <v>87925.24046846799</v>
       </c>
       <c r="P800" t="n">
         <v>3000</v>
@@ -36974,25 +36974,25 @@
         <v>14</v>
       </c>
       <c r="K819" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L819" t="n">
         <v>0</v>
       </c>
       <c r="M819" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="N819" t="n">
         <v>1684.79</v>
       </c>
       <c r="O819" t="n">
-        <v>23587.06</v>
+        <v>26956.64</v>
       </c>
       <c r="P819" t="n">
         <v>2900</v>
       </c>
       <c r="Q819" t="n">
-        <v>40600</v>
+        <v>46400</v>
       </c>
     </row>
     <row r="820">
@@ -37109,22 +37109,22 @@
         <v>0</v>
       </c>
       <c r="L822" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M822" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N822" t="n">
-        <v>1283.653986711</v>
+        <v>1283.6539464883</v>
       </c>
       <c r="O822" t="n">
-        <v>23105.771760798</v>
+        <v>20538.4631438128</v>
       </c>
       <c r="P822" t="n">
         <v>1900</v>
       </c>
       <c r="Q822" t="n">
-        <v>34200</v>
+        <v>30400</v>
       </c>
     </row>
     <row r="823">
@@ -37697,22 +37697,22 @@
         <v>0</v>
       </c>
       <c r="L835" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M835" t="n">
-        <v>1438</v>
+        <v>1388</v>
       </c>
       <c r="N835" t="n">
-        <v>517.28836312001</v>
+        <v>517.2884408203601</v>
       </c>
       <c r="O835" t="n">
-        <v>743860.6661665743</v>
+        <v>717996.3558586597</v>
       </c>
       <c r="P835" t="n">
         <v>900</v>
       </c>
       <c r="Q835" t="n">
-        <v>1294200</v>
+        <v>1249200</v>
       </c>
     </row>
     <row r="836">
@@ -38212,22 +38212,22 @@
         <v>0</v>
       </c>
       <c r="L846" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M846" t="n">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="N846" t="n">
-        <v>3110.8426185007</v>
+        <v>3110.8425641565</v>
       </c>
       <c r="O846" t="n">
-        <v>1011023.851012728</v>
+        <v>992358.7779659235</v>
       </c>
       <c r="P846" t="n">
         <v>4500</v>
       </c>
       <c r="Q846" t="n">
-        <v>1462500</v>
+        <v>1435500</v>
       </c>
     </row>
     <row r="847">
@@ -38395,22 +38395,22 @@
         <v>0</v>
       </c>
       <c r="L850" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M850" t="n">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="N850" t="n">
         <v>2030.02</v>
       </c>
       <c r="O850" t="n">
-        <v>308563.04</v>
+        <v>284202.8</v>
       </c>
       <c r="P850" t="n">
         <v>3600</v>
       </c>
       <c r="Q850" t="n">
-        <v>547200</v>
+        <v>504000</v>
       </c>
     </row>
     <row r="851">
@@ -38487,22 +38487,22 @@
         <v>0</v>
       </c>
       <c r="L852" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M852" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N852" t="n">
         <v>6990.56</v>
       </c>
       <c r="O852" t="n">
-        <v>34952.8</v>
+        <v>20971.68</v>
       </c>
       <c r="P852" t="n">
         <v>8900</v>
       </c>
       <c r="Q852" t="n">
-        <v>44500</v>
+        <v>26700</v>
       </c>
     </row>
     <row r="853">
@@ -38621,25 +38621,25 @@
         <v>183</v>
       </c>
       <c r="K855" t="n">
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="L855" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M855" t="n">
-        <v>183</v>
+        <v>459</v>
       </c>
       <c r="N855" t="n">
-        <v>703.79529676406</v>
+        <v>703.79526826968</v>
       </c>
       <c r="O855" t="n">
-        <v>128794.539307823</v>
+        <v>323042.0281357832</v>
       </c>
       <c r="P855" t="n">
         <v>900</v>
       </c>
       <c r="Q855" t="n">
-        <v>164700</v>
+        <v>413100</v>
       </c>
     </row>
     <row r="856">
@@ -38998,22 +38998,22 @@
         <v>0</v>
       </c>
       <c r="L863" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M863" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N863" t="n">
-        <v>2501.3851351351</v>
+        <v>2501.3850684932</v>
       </c>
       <c r="O863" t="n">
-        <v>15008.3108108106</v>
+        <v>7504.155205479599</v>
       </c>
       <c r="P863" t="n">
         <v>4100</v>
       </c>
       <c r="Q863" t="n">
-        <v>24600</v>
+        <v>12300</v>
       </c>
     </row>
     <row r="864">
@@ -39188,22 +39188,22 @@
         <v>0</v>
       </c>
       <c r="L867" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M867" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N867" t="n">
         <v>14260.14</v>
       </c>
       <c r="O867" t="n">
-        <v>342243.36</v>
+        <v>327983.22</v>
       </c>
       <c r="P867" t="n">
         <v>15900</v>
       </c>
       <c r="Q867" t="n">
-        <v>381600</v>
+        <v>365700</v>
       </c>
     </row>
     <row r="868">
@@ -39321,22 +39321,22 @@
         <v>0</v>
       </c>
       <c r="L870" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M870" t="n">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="N870" t="n">
         <v>2362.86</v>
       </c>
       <c r="O870" t="n">
-        <v>217383.12</v>
+        <v>205568.82</v>
       </c>
       <c r="P870" t="n">
         <v>2900</v>
       </c>
       <c r="Q870" t="n">
-        <v>266800</v>
+        <v>252300</v>
       </c>
     </row>
     <row r="871">
@@ -39687,22 +39687,22 @@
         <v>0</v>
       </c>
       <c r="L878" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M878" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="N878" t="n">
-        <v>1595.5153131828</v>
+        <v>1595.5151400147</v>
       </c>
       <c r="O878" t="n">
-        <v>81371.2809723228</v>
+        <v>71798.1813006615</v>
       </c>
       <c r="P878" t="n">
         <v>2500</v>
       </c>
       <c r="Q878" t="n">
-        <v>127500</v>
+        <v>112500</v>
       </c>
     </row>
     <row r="879">
@@ -41370,22 +41370,22 @@
         <v>0</v>
       </c>
       <c r="L913" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M913" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N913" t="n">
         <v>9874.620000000001</v>
       </c>
       <c r="O913" t="n">
-        <v>59247.72</v>
+        <v>39498.48</v>
       </c>
       <c r="P913" t="n">
         <v>14700</v>
       </c>
       <c r="Q913" t="n">
-        <v>88200</v>
+        <v>58800</v>
       </c>
     </row>
     <row r="914">
@@ -42197,22 +42197,22 @@
         <v>0</v>
       </c>
       <c r="L930" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M930" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N930" t="n">
         <v>6773.85</v>
       </c>
       <c r="O930" t="n">
-        <v>40643.10000000001</v>
+        <v>33869.25</v>
       </c>
       <c r="P930" t="n">
         <v>9500</v>
       </c>
       <c r="Q930" t="n">
-        <v>57000</v>
+        <v>47500</v>
       </c>
     </row>
     <row r="931">
@@ -42246,22 +42246,22 @@
         <v>0</v>
       </c>
       <c r="L931" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M931" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N931" t="n">
         <v>11352.65</v>
       </c>
       <c r="O931" t="n">
-        <v>68115.89999999999</v>
+        <v>34057.95</v>
       </c>
       <c r="P931" t="n">
         <v>14900</v>
       </c>
       <c r="Q931" t="n">
-        <v>89400</v>
+        <v>44700</v>
       </c>
     </row>
     <row r="932">
@@ -43781,22 +43781,22 @@
         <v>0</v>
       </c>
       <c r="L963" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M963" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N963" t="n">
         <v>26630.86</v>
       </c>
       <c r="O963" t="n">
-        <v>79892.58</v>
+        <v>53261.72</v>
       </c>
       <c r="P963" t="n">
         <v>56000</v>
       </c>
       <c r="Q963" t="n">
-        <v>168000</v>
+        <v>112000</v>
       </c>
     </row>
     <row r="964">
@@ -43977,22 +43977,22 @@
         <v>0</v>
       </c>
       <c r="L967" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M967" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="N967" t="n">
-        <v>4697.3811428571</v>
+        <v>4697.38125</v>
       </c>
       <c r="O967" t="n">
-        <v>84552.86057142779</v>
+        <v>70460.71875</v>
       </c>
       <c r="P967" t="n">
         <v>10900</v>
       </c>
       <c r="Q967" t="n">
-        <v>196200</v>
+        <v>163500</v>
       </c>
     </row>
     <row r="968">
@@ -44306,22 +44306,22 @@
         <v>0</v>
       </c>
       <c r="L974" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M974" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N974" t="n">
-        <v>10737.5264</v>
+        <v>10737.526326531</v>
       </c>
       <c r="O974" t="n">
-        <v>118112.7904</v>
+        <v>107375.26326531</v>
       </c>
       <c r="P974" t="n">
         <v>18900</v>
       </c>
       <c r="Q974" t="n">
-        <v>207900</v>
+        <v>189000</v>
       </c>
     </row>
     <row r="975">
@@ -44592,22 +44592,22 @@
         <v>0</v>
       </c>
       <c r="L980" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M980" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N980" t="n">
         <v>14590.52</v>
       </c>
       <c r="O980" t="n">
-        <v>43771.56</v>
+        <v>29181.04</v>
       </c>
       <c r="P980" t="n">
         <v>26500</v>
       </c>
       <c r="Q980" t="n">
-        <v>79500</v>
+        <v>53000</v>
       </c>
     </row>
     <row r="981">
@@ -44926,22 +44926,22 @@
         <v>0</v>
       </c>
       <c r="L987" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M987" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N987" t="n">
         <v>13168.16</v>
       </c>
       <c r="O987" t="n">
-        <v>210690.56</v>
+        <v>184354.24</v>
       </c>
       <c r="P987" t="n">
         <v>49000</v>
       </c>
       <c r="Q987" t="n">
-        <v>784000</v>
+        <v>686000</v>
       </c>
     </row>
     <row r="988">
@@ -45024,22 +45024,22 @@
         <v>0</v>
       </c>
       <c r="L989" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M989" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N989" t="n">
         <v>9526.51</v>
       </c>
       <c r="O989" t="n">
-        <v>114318.12</v>
+        <v>104791.61</v>
       </c>
       <c r="P989" t="n">
         <v>45000</v>
       </c>
       <c r="Q989" t="n">
-        <v>540000</v>
+        <v>495000</v>
       </c>
     </row>
     <row r="990">
@@ -45073,22 +45073,22 @@
         <v>0</v>
       </c>
       <c r="L990" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M990" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N990" t="n">
         <v>10798.03</v>
       </c>
       <c r="O990" t="n">
-        <v>107980.3</v>
+        <v>97182.27</v>
       </c>
       <c r="P990" t="n">
         <v>45000</v>
       </c>
       <c r="Q990" t="n">
-        <v>450000</v>
+        <v>405000</v>
       </c>
     </row>
     <row r="991">
@@ -45165,22 +45165,22 @@
         <v>0</v>
       </c>
       <c r="L992" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M992" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N992" t="n">
         <v>10541.34</v>
       </c>
       <c r="O992" t="n">
-        <v>73789.38</v>
+        <v>63248.04</v>
       </c>
       <c r="P992" t="n">
         <v>49000</v>
       </c>
       <c r="Q992" t="n">
-        <v>343000</v>
+        <v>294000</v>
       </c>
     </row>
     <row r="993">
@@ -45303,22 +45303,22 @@
         <v>0</v>
       </c>
       <c r="L995" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M995" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N995" t="n">
         <v>9031.370000000001</v>
       </c>
       <c r="O995" t="n">
-        <v>27094.11</v>
+        <v>9031.370000000001</v>
       </c>
       <c r="P995" t="n">
         <v>49000</v>
       </c>
       <c r="Q995" t="n">
-        <v>147000</v>
+        <v>49000</v>
       </c>
     </row>
     <row r="996">
@@ -45395,22 +45395,22 @@
         <v>0</v>
       </c>
       <c r="L997" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M997" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="N997" t="n">
         <v>6529.54</v>
       </c>
       <c r="O997" t="n">
-        <v>117531.72</v>
+        <v>91413.56</v>
       </c>
       <c r="P997" t="n">
         <v>45000</v>
       </c>
       <c r="Q997" t="n">
-        <v>810000</v>
+        <v>630000</v>
       </c>
     </row>
     <row r="998">
@@ -45970,22 +45970,22 @@
         <v>0</v>
       </c>
       <c r="L1009" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M1009" t="n">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="N1009" t="n">
         <v>509.69</v>
       </c>
       <c r="O1009" t="n">
-        <v>259941.9</v>
+        <v>254845</v>
       </c>
       <c r="P1009" t="n">
         <v>750</v>
       </c>
       <c r="Q1009" t="n">
-        <v>382500</v>
+        <v>375000</v>
       </c>
     </row>
     <row r="1010">
@@ -46212,22 +46212,22 @@
         <v>0</v>
       </c>
       <c r="L1014" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1014" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N1014" t="n">
         <v>28076.23</v>
       </c>
       <c r="O1014" t="n">
-        <v>56152.46</v>
+        <v>28076.23</v>
       </c>
       <c r="P1014" t="n">
         <v>36500</v>
       </c>
       <c r="Q1014" t="n">
-        <v>73000</v>
+        <v>36500</v>
       </c>
     </row>
     <row r="1015">
@@ -46650,22 +46650,22 @@
         <v>0</v>
       </c>
       <c r="L1023" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M1023" t="n">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="N1023" t="n">
-        <v>665.32347555556</v>
+        <v>665.32351302785</v>
       </c>
       <c r="O1023" t="n">
-        <v>157016.3402311121</v>
+        <v>149032.4669182384</v>
       </c>
       <c r="P1023" t="n">
         <v>2900</v>
       </c>
       <c r="Q1023" t="n">
-        <v>684400</v>
+        <v>649600</v>
       </c>
     </row>
     <row r="1024">
@@ -46987,22 +46987,22 @@
         <v>0</v>
       </c>
       <c r="L1030" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1030" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N1030" t="n">
         <v>4581.84</v>
       </c>
       <c r="O1030" t="n">
-        <v>132873.36</v>
+        <v>128291.52</v>
       </c>
       <c r="P1030" t="n">
         <v>7900</v>
       </c>
       <c r="Q1030" t="n">
-        <v>229100</v>
+        <v>221200</v>
       </c>
     </row>
     <row r="1031">
@@ -47284,10 +47284,10 @@
         <v>64</v>
       </c>
       <c r="N1036" t="n">
-        <v>430.60997668998</v>
+        <v>430.6099765808</v>
       </c>
       <c r="O1036" t="n">
-        <v>27559.03850815872</v>
+        <v>27559.0385011712</v>
       </c>
       <c r="P1036" t="n">
         <v>2200</v>
@@ -47382,10 +47382,10 @@
         <v>28</v>
       </c>
       <c r="N1038" t="n">
-        <v>315.02679218968</v>
+        <v>315.02685915493</v>
       </c>
       <c r="O1038" t="n">
-        <v>8820.750181311039</v>
+        <v>8820.752056338039</v>
       </c>
       <c r="P1038" t="n">
         <v>2200</v>
@@ -48158,22 +48158,22 @@
         <v>0</v>
       </c>
       <c r="L1056" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M1056" t="n">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="N1056" t="n">
         <v>1176.57</v>
       </c>
       <c r="O1056" t="n">
-        <v>749475.09</v>
+        <v>744768.8099999999</v>
       </c>
       <c r="P1056" t="n">
         <v>1900</v>
       </c>
       <c r="Q1056" t="n">
-        <v>1210300</v>
+        <v>1202700</v>
       </c>
     </row>
     <row r="1057">
@@ -48518,10 +48518,10 @@
         <v>17</v>
       </c>
       <c r="N1064" t="n">
-        <v>8922.214942528701</v>
+        <v>8922.215</v>
       </c>
       <c r="O1064" t="n">
-        <v>151677.6540229879</v>
+        <v>151677.655</v>
       </c>
       <c r="P1064" t="n">
         <v>8200</v>
@@ -48703,10 +48703,10 @@
         <v>7</v>
       </c>
       <c r="N1068" t="n">
-        <v>22951.704962406</v>
+        <v>22951.704956085</v>
       </c>
       <c r="O1068" t="n">
-        <v>160661.934736842</v>
+        <v>160661.934692595</v>
       </c>
       <c r="P1068" t="n">
         <v>37900</v>
@@ -48833,22 +48833,22 @@
         <v>0</v>
       </c>
       <c r="L1071" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M1071" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="N1071" t="n">
-        <v>4985.4047808765</v>
+        <v>4985.4050632911</v>
       </c>
       <c r="O1071" t="n">
-        <v>184459.9768924305</v>
+        <v>139591.3417721508</v>
       </c>
       <c r="P1071" t="n">
         <v>7900</v>
       </c>
       <c r="Q1071" t="n">
-        <v>292300</v>
+        <v>221200</v>
       </c>
     </row>
     <row r="1072">
@@ -48941,10 +48941,10 @@
         <v>52</v>
       </c>
       <c r="N1073" t="n">
-        <v>1757.3205416667</v>
+        <v>1757.3205462185</v>
       </c>
       <c r="O1073" t="n">
-        <v>91380.6681666684</v>
+        <v>91380.66840336201</v>
       </c>
       <c r="P1073" t="n">
         <v>2000</v>
@@ -49947,19 +49947,19 @@
         <v>150</v>
       </c>
       <c r="K1095" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="L1095" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="M1095" t="n">
         <v>150</v>
       </c>
       <c r="N1095" t="n">
-        <v>220.00693162525</v>
+        <v>220.00651536869</v>
       </c>
       <c r="O1095" t="n">
-        <v>33001.0397437875</v>
+        <v>33000.9773053035</v>
       </c>
       <c r="P1095" t="n">
         <v>260</v>
@@ -50318,22 +50318,22 @@
         <v>0</v>
       </c>
       <c r="L1103" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M1103" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="N1103" t="n">
         <v>3504.16</v>
       </c>
       <c r="O1103" t="n">
-        <v>49058.24</v>
+        <v>35041.6</v>
       </c>
       <c r="P1103" t="n">
         <v>3900</v>
       </c>
       <c r="Q1103" t="n">
-        <v>54600</v>
+        <v>39000</v>
       </c>
     </row>
     <row r="1104">
@@ -50594,22 +50594,22 @@
         <v>0</v>
       </c>
       <c r="L1109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1109" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="N1109" t="n">
         <v>1952.66</v>
       </c>
       <c r="O1109" t="n">
-        <v>101538.32</v>
+        <v>99585.66</v>
       </c>
       <c r="P1109" t="n">
         <v>3500</v>
       </c>
       <c r="Q1109" t="n">
-        <v>182000</v>
+        <v>178500</v>
       </c>
     </row>
     <row r="1110">
@@ -50778,22 +50778,22 @@
         <v>0</v>
       </c>
       <c r="L1113" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M1113" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="N1113" t="n">
         <v>6270.21</v>
       </c>
       <c r="O1113" t="n">
-        <v>56431.89</v>
+        <v>37621.26</v>
       </c>
       <c r="P1113" t="n">
         <v>8900</v>
       </c>
       <c r="Q1113" t="n">
-        <v>80100</v>
+        <v>53400</v>
       </c>
     </row>
     <row r="1114">
@@ -50916,22 +50916,22 @@
         <v>0</v>
       </c>
       <c r="L1116" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1116" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="N1116" t="n">
         <v>1952.41</v>
       </c>
       <c r="O1116" t="n">
-        <v>70286.76000000001</v>
+        <v>66381.94</v>
       </c>
       <c r="P1116" t="n">
         <v>2700</v>
       </c>
       <c r="Q1116" t="n">
-        <v>97200</v>
+        <v>91800</v>
       </c>
     </row>
     <row r="1117">
@@ -51330,22 +51330,22 @@
         <v>0</v>
       </c>
       <c r="L1125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1125" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N1125" t="n">
         <v>7740</v>
       </c>
       <c r="O1125" t="n">
-        <v>348300</v>
+        <v>340560</v>
       </c>
       <c r="P1125" t="n">
         <v>9500</v>
       </c>
       <c r="Q1125" t="n">
-        <v>427500</v>
+        <v>418000</v>
       </c>
     </row>
     <row r="1126">
@@ -51376,22 +51376,22 @@
         <v>0</v>
       </c>
       <c r="L1126" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M1126" t="n">
-        <v>280</v>
+        <v>269</v>
       </c>
       <c r="N1126" t="n">
         <v>7480</v>
       </c>
       <c r="O1126" t="n">
-        <v>2094400</v>
+        <v>2012120</v>
       </c>
       <c r="P1126" t="n">
         <v>9500</v>
       </c>
       <c r="Q1126" t="n">
-        <v>2660000</v>
+        <v>2555500</v>
       </c>
     </row>
     <row r="1127">
@@ -51514,22 +51514,22 @@
         <v>0</v>
       </c>
       <c r="L1129" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="M1129" t="n">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="N1129" t="n">
         <v>9240</v>
       </c>
       <c r="O1129" t="n">
-        <v>4952640</v>
+        <v>4897200</v>
       </c>
       <c r="P1129" t="n">
         <v>11500</v>
       </c>
       <c r="Q1129" t="n">
-        <v>6164000</v>
+        <v>6095000</v>
       </c>
     </row>
     <row r="1130">
@@ -53134,22 +53134,22 @@
         <v>0</v>
       </c>
       <c r="L1164" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M1164" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="N1164" t="n">
         <v>1236.3</v>
       </c>
       <c r="O1164" t="n">
-        <v>60578.7</v>
+        <v>56869.8</v>
       </c>
       <c r="P1164" t="n">
         <v>2300</v>
       </c>
       <c r="Q1164" t="n">
-        <v>112700</v>
+        <v>105800</v>
       </c>
     </row>
     <row r="1165">
@@ -53660,22 +53660,22 @@
         <v>0</v>
       </c>
       <c r="L1175" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1175" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N1175" t="n">
-        <v>2432.1346</v>
+        <v>2432.1346938776</v>
       </c>
       <c r="O1175" t="n">
-        <v>43778.4228</v>
+        <v>38914.1551020416</v>
       </c>
       <c r="P1175" t="n">
         <v>4500</v>
       </c>
       <c r="Q1175" t="n">
-        <v>81000</v>
+        <v>72000</v>
       </c>
     </row>
     <row r="1176">
@@ -55590,22 +55590,22 @@
         <v>0</v>
       </c>
       <c r="L1217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1217" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N1217" t="n">
         <v>24780.39</v>
       </c>
       <c r="O1217" t="n">
-        <v>396486.24</v>
+        <v>371705.85</v>
       </c>
       <c r="P1217" t="n">
         <v>31500</v>
       </c>
       <c r="Q1217" t="n">
-        <v>504000</v>
+        <v>472500</v>
       </c>
     </row>
     <row r="1218">
@@ -55682,22 +55682,22 @@
         <v>0</v>
       </c>
       <c r="L1219" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1219" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N1219" t="n">
         <v>4550</v>
       </c>
       <c r="O1219" t="n">
-        <v>382200</v>
+        <v>377650</v>
       </c>
       <c r="P1219" t="n">
         <v>5500</v>
       </c>
       <c r="Q1219" t="n">
-        <v>462000</v>
+        <v>456500</v>
       </c>
     </row>
     <row r="1220">

--- a/bodegas/LJ-101.xlsx
+++ b/bodegas/LJ-101.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1271"/>
+  <dimension ref="A1:Q1272"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -944,10 +944,10 @@
         <v>28</v>
       </c>
       <c r="N13" t="n">
-        <v>1811.3058666667</v>
+        <v>1811.3059701493</v>
       </c>
       <c r="O13" t="n">
-        <v>50716.5642666676</v>
+        <v>50716.5671641804</v>
       </c>
       <c r="P13" t="n">
         <v>2600</v>
@@ -1022,10 +1022,10 @@
         <v>50</v>
       </c>
       <c r="N15" t="n">
-        <v>3376.7464891304</v>
+        <v>3376.7464843537</v>
       </c>
       <c r="O15" t="n">
-        <v>168837.32445652</v>
+        <v>168837.324217685</v>
       </c>
       <c r="P15" t="n">
         <v>4500</v>
@@ -1133,22 +1133,22 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N18" t="n">
-        <v>5758.9597787611</v>
+        <v>5758.9597782705</v>
       </c>
       <c r="O18" t="n">
-        <v>40312.7184513277</v>
+        <v>34553.758669623</v>
       </c>
       <c r="P18" t="n">
         <v>16900</v>
       </c>
       <c r="Q18" t="n">
-        <v>118300</v>
+        <v>101400</v>
       </c>
     </row>
     <row r="19">
@@ -2027,10 +2027,10 @@
         <v>11</v>
       </c>
       <c r="N40" t="n">
-        <v>2413.0010683761</v>
+        <v>2413.0010706638</v>
       </c>
       <c r="O40" t="n">
-        <v>26543.0117521371</v>
+        <v>26543.0117773018</v>
       </c>
       <c r="P40" t="n">
         <v>4700</v>
@@ -3409,10 +3409,10 @@
         <v>1</v>
       </c>
       <c r="N72" t="n">
-        <v>30708.856153846</v>
+        <v>30708.848333333</v>
       </c>
       <c r="O72" t="n">
-        <v>30708.856153846</v>
+        <v>30708.848333333</v>
       </c>
       <c r="P72" t="n">
         <v>53500</v>
@@ -3451,10 +3451,10 @@
         <v>14</v>
       </c>
       <c r="N73" t="n">
-        <v>12837.966461538</v>
+        <v>12837.967258065</v>
       </c>
       <c r="O73" t="n">
-        <v>179731.530461532</v>
+        <v>179731.54161291</v>
       </c>
       <c r="P73" t="n">
         <v>22900</v>
@@ -3540,10 +3540,10 @@
         <v>5</v>
       </c>
       <c r="N75" t="n">
-        <v>10994.360689655</v>
+        <v>10994.361428571</v>
       </c>
       <c r="O75" t="n">
-        <v>54971.80344827501</v>
+        <v>54971.807142855</v>
       </c>
       <c r="P75" t="n">
         <v>16900</v>
@@ -3699,22 +3699,22 @@
         <v>0</v>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M79" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N79" t="n">
         <v>36762.36</v>
       </c>
       <c r="O79" t="n">
-        <v>551435.4</v>
+        <v>514673.04</v>
       </c>
       <c r="P79" t="n">
         <v>57100</v>
       </c>
       <c r="Q79" t="n">
-        <v>856500</v>
+        <v>799400</v>
       </c>
     </row>
     <row r="80">
@@ -3747,10 +3747,10 @@
         <v>10</v>
       </c>
       <c r="N80" t="n">
-        <v>15711.966041667</v>
+        <v>15711.966008403</v>
       </c>
       <c r="O80" t="n">
-        <v>157119.66041667</v>
+        <v>157119.66008403</v>
       </c>
       <c r="P80" t="n">
         <v>28500</v>
@@ -4562,10 +4562,10 @@
         <v>3</v>
       </c>
       <c r="N99" t="n">
-        <v>56906.802542373</v>
+        <v>56906.802982456</v>
       </c>
       <c r="O99" t="n">
-        <v>170720.407627119</v>
+        <v>170720.408947368</v>
       </c>
       <c r="P99" t="n">
         <v>95900</v>
@@ -4603,22 +4603,22 @@
         <v>0</v>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M100" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N100" t="n">
-        <v>62349.658857143</v>
+        <v>62349.657575758</v>
       </c>
       <c r="O100" t="n">
-        <v>249398.635428572</v>
+        <v>124699.315151516</v>
       </c>
       <c r="P100" t="n">
         <v>109900</v>
       </c>
       <c r="Q100" t="n">
-        <v>439600</v>
+        <v>219800</v>
       </c>
     </row>
     <row r="101">
@@ -4698,10 +4698,10 @@
         <v>4</v>
       </c>
       <c r="N102" t="n">
-        <v>200072.2004878</v>
+        <v>200072.20057377</v>
       </c>
       <c r="O102" t="n">
-        <v>800288.8019512</v>
+        <v>800288.80229508</v>
       </c>
       <c r="P102" t="n">
         <v>312000</v>
@@ -7703,10 +7703,10 @@
         <v>41</v>
       </c>
       <c r="N171" t="n">
-        <v>1950.2146835443</v>
+        <v>1950.2146537678</v>
       </c>
       <c r="O171" t="n">
-        <v>79958.8020253163</v>
+        <v>79958.8008044798</v>
       </c>
       <c r="P171" t="n">
         <v>2900</v>
@@ -7779,22 +7779,22 @@
         <v>0</v>
       </c>
       <c r="L173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M173" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N173" t="n">
         <v>1726.32</v>
       </c>
       <c r="O173" t="n">
-        <v>1726.32</v>
+        <v>0</v>
       </c>
       <c r="P173" t="n">
         <v>1500</v>
       </c>
       <c r="Q173" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="174">
@@ -7872,10 +7872,10 @@
         <v>108</v>
       </c>
       <c r="N175" t="n">
-        <v>4937.3101616458</v>
+        <v>4937.3101623616</v>
       </c>
       <c r="O175" t="n">
-        <v>533229.4974577464</v>
+        <v>533229.4975350528</v>
       </c>
       <c r="P175" t="n">
         <v>7500</v>
@@ -8167,10 +8167,10 @@
         <v>482</v>
       </c>
       <c r="N182" t="n">
-        <v>1098.0574483741</v>
+        <v>1098.0580436917</v>
       </c>
       <c r="O182" t="n">
-        <v>529263.6901163162</v>
+        <v>529263.9770593995</v>
       </c>
       <c r="P182" t="n">
         <v>1500</v>
@@ -8248,22 +8248,22 @@
         <v>0</v>
       </c>
       <c r="L184" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M184" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N184" t="n">
         <v>6295.2</v>
       </c>
       <c r="O184" t="n">
-        <v>37771.2</v>
+        <v>12590.4</v>
       </c>
       <c r="P184" t="n">
         <v>10500</v>
       </c>
       <c r="Q184" t="n">
-        <v>63000</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="185">
@@ -8333,22 +8333,22 @@
         <v>0</v>
       </c>
       <c r="L186" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M186" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N186" t="n">
         <v>5879</v>
       </c>
       <c r="O186" t="n">
-        <v>170491</v>
+        <v>164612</v>
       </c>
       <c r="P186" t="n">
         <v>10050</v>
       </c>
       <c r="Q186" t="n">
-        <v>291450</v>
+        <v>281400</v>
       </c>
     </row>
     <row r="187">
@@ -8561,22 +8561,22 @@
         <v>0</v>
       </c>
       <c r="L191" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M191" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N191" t="n">
         <v>12587</v>
       </c>
       <c r="O191" t="n">
-        <v>125870</v>
+        <v>113283</v>
       </c>
       <c r="P191" t="n">
         <v>18900</v>
       </c>
       <c r="Q191" t="n">
-        <v>189000</v>
+        <v>170100</v>
       </c>
     </row>
     <row r="192">
@@ -8820,22 +8820,22 @@
         <v>0</v>
       </c>
       <c r="L197" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M197" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="N197" t="n">
         <v>4065.61</v>
       </c>
       <c r="O197" t="n">
-        <v>130099.52</v>
+        <v>113837.08</v>
       </c>
       <c r="P197" t="n">
         <v>5000</v>
       </c>
       <c r="Q197" t="n">
-        <v>160000</v>
+        <v>140000</v>
       </c>
     </row>
     <row r="198">
@@ -9035,22 +9035,22 @@
         <v>0</v>
       </c>
       <c r="L202" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M202" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="N202" t="n">
         <v>2745.81</v>
       </c>
       <c r="O202" t="n">
-        <v>101594.97</v>
+        <v>98849.16</v>
       </c>
       <c r="P202" t="n">
         <v>5600</v>
       </c>
       <c r="Q202" t="n">
-        <v>207200</v>
+        <v>201600</v>
       </c>
     </row>
     <row r="203">
@@ -9176,22 +9176,22 @@
         <v>0</v>
       </c>
       <c r="L205" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M205" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N205" t="n">
-        <v>2582.2558919365</v>
+        <v>2582.2558569052</v>
       </c>
       <c r="O205" t="n">
-        <v>61974.141406476</v>
+        <v>54227.37299500919</v>
       </c>
       <c r="P205" t="n">
         <v>4500</v>
       </c>
       <c r="Q205" t="n">
-        <v>108000</v>
+        <v>94500</v>
       </c>
     </row>
     <row r="206">
@@ -9320,10 +9320,10 @@
         <v>2</v>
       </c>
       <c r="N208" t="n">
-        <v>5216.8961798703</v>
+        <v>5216.8961652752</v>
       </c>
       <c r="O208" t="n">
-        <v>10433.7923597406</v>
+        <v>10433.7923305504</v>
       </c>
       <c r="P208" t="n">
         <v>8500</v>
@@ -9366,10 +9366,10 @@
         <v>6</v>
       </c>
       <c r="N209" t="n">
-        <v>2033.5538679245</v>
+        <v>2033.5525242718</v>
       </c>
       <c r="O209" t="n">
-        <v>12201.323207547</v>
+        <v>12201.3151456308</v>
       </c>
       <c r="P209" t="n">
         <v>4100</v>
@@ -9496,22 +9496,22 @@
         <v>0</v>
       </c>
       <c r="L212" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M212" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N212" t="n">
         <v>1844.18</v>
       </c>
       <c r="O212" t="n">
-        <v>38727.78</v>
+        <v>35039.42</v>
       </c>
       <c r="P212" t="n">
         <v>3200</v>
       </c>
       <c r="Q212" t="n">
-        <v>67200</v>
+        <v>60800</v>
       </c>
     </row>
     <row r="213">
@@ -9638,10 +9638,10 @@
         <v>387</v>
       </c>
       <c r="N215" t="n">
-        <v>3158.8608246566</v>
+        <v>3158.8608249792</v>
       </c>
       <c r="O215" t="n">
-        <v>1222479.139142104</v>
+        <v>1222479.13926695</v>
       </c>
       <c r="P215" t="n">
         <v>5600</v>
@@ -9866,10 +9866,10 @@
         <v>74</v>
       </c>
       <c r="N220" t="n">
-        <v>3230.0674725275</v>
+        <v>3230.0674157303</v>
       </c>
       <c r="O220" t="n">
-        <v>239024.992967035</v>
+        <v>239024.9887640422</v>
       </c>
       <c r="P220" t="n">
         <v>6200</v>
@@ -10050,10 +10050,10 @@
         <v>174</v>
       </c>
       <c r="N224" t="n">
-        <v>2694.8232527881</v>
+        <v>2694.823243369</v>
       </c>
       <c r="O224" t="n">
-        <v>468899.2459851294</v>
+        <v>468899.244346206</v>
       </c>
       <c r="P224" t="n">
         <v>4900</v>
@@ -10136,22 +10136,22 @@
         <v>0</v>
       </c>
       <c r="L226" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M226" t="n">
-        <v>1942</v>
+        <v>1922</v>
       </c>
       <c r="N226" t="n">
         <v>156.25</v>
       </c>
       <c r="O226" t="n">
-        <v>303437.5</v>
+        <v>300312.5</v>
       </c>
       <c r="P226" t="n">
         <v>250</v>
       </c>
       <c r="Q226" t="n">
-        <v>485500</v>
+        <v>480500</v>
       </c>
     </row>
     <row r="227">
@@ -10641,10 +10641,10 @@
         <v>12</v>
       </c>
       <c r="N237" t="n">
-        <v>4890.9300476474</v>
+        <v>4890.9300481348</v>
       </c>
       <c r="O237" t="n">
-        <v>58691.1605717688</v>
+        <v>58691.1605776176</v>
       </c>
       <c r="P237" t="n">
         <v>8200</v>
@@ -10825,22 +10825,22 @@
         <v>0</v>
       </c>
       <c r="L241" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M241" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="N241" t="n">
         <v>1203.38</v>
       </c>
       <c r="O241" t="n">
-        <v>50541.96000000001</v>
+        <v>28881.12</v>
       </c>
       <c r="P241" t="n">
         <v>1900</v>
       </c>
       <c r="Q241" t="n">
-        <v>79800</v>
+        <v>45600</v>
       </c>
     </row>
     <row r="242">
@@ -11318,25 +11318,25 @@
         <v>12</v>
       </c>
       <c r="K252" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L252" t="n">
+        <v>11</v>
+      </c>
+      <c r="M252" t="n">
         <v>7</v>
-      </c>
-      <c r="M252" t="n">
-        <v>5</v>
       </c>
       <c r="N252" t="n">
         <v>10716.34</v>
       </c>
       <c r="O252" t="n">
-        <v>53581.7</v>
+        <v>75014.38</v>
       </c>
       <c r="P252" t="n">
         <v>39000</v>
       </c>
       <c r="Q252" t="n">
-        <v>195000</v>
+        <v>273000</v>
       </c>
     </row>
     <row r="253">
@@ -11411,22 +11411,22 @@
         <v>0</v>
       </c>
       <c r="L254" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M254" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N254" t="n">
-        <v>3594.25408867</v>
+        <v>3594.2540740741</v>
       </c>
       <c r="O254" t="n">
-        <v>57508.06541872</v>
+        <v>53913.8111111115</v>
       </c>
       <c r="P254" t="n">
         <v>6500</v>
       </c>
       <c r="Q254" t="n">
-        <v>104000</v>
+        <v>97500</v>
       </c>
     </row>
     <row r="255">
@@ -11501,22 +11501,22 @@
         <v>0</v>
       </c>
       <c r="L256" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M256" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="N256" t="n">
         <v>489.88</v>
       </c>
       <c r="O256" t="n">
-        <v>36741</v>
+        <v>34781.48</v>
       </c>
       <c r="P256" t="n">
         <v>700</v>
       </c>
       <c r="Q256" t="n">
-        <v>52500</v>
+        <v>49700</v>
       </c>
     </row>
     <row r="257">
@@ -11630,10 +11630,10 @@
         <v>134</v>
       </c>
       <c r="N259" t="n">
-        <v>3240.8500313972</v>
+        <v>3240.8500314961</v>
       </c>
       <c r="O259" t="n">
-        <v>434273.9042072248</v>
+        <v>434273.9042204774</v>
       </c>
       <c r="P259" t="n">
         <v>5200</v>
@@ -11814,10 +11814,10 @@
         <v>11</v>
       </c>
       <c r="N263" t="n">
-        <v>14822.378855098</v>
+        <v>14822.378854415</v>
       </c>
       <c r="O263" t="n">
-        <v>163046.167406078</v>
+        <v>163046.167398565</v>
       </c>
       <c r="P263" t="n">
         <v>24900</v>
@@ -11901,22 +11901,22 @@
         <v>0</v>
       </c>
       <c r="L265" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M265" t="n">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="N265" t="n">
         <v>2090.85</v>
       </c>
       <c r="O265" t="n">
-        <v>723434.1</v>
+        <v>706707.2999999999</v>
       </c>
       <c r="P265" t="n">
         <v>2900</v>
       </c>
       <c r="Q265" t="n">
-        <v>1003400</v>
+        <v>980200</v>
       </c>
     </row>
     <row r="266">
@@ -12032,22 +12032,22 @@
         <v>0</v>
       </c>
       <c r="L268" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M268" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="N268" t="n">
-        <v>5191.4800275862</v>
+        <v>5191.4800277778</v>
       </c>
       <c r="O268" t="n">
-        <v>166127.3608827584</v>
+        <v>140169.9607500006</v>
       </c>
       <c r="P268" t="n">
         <v>9100</v>
       </c>
       <c r="Q268" t="n">
-        <v>291200</v>
+        <v>245700</v>
       </c>
     </row>
     <row r="269">
@@ -12120,22 +12120,22 @@
         <v>0</v>
       </c>
       <c r="L270" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M270" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="N270" t="n">
         <v>2769.98</v>
       </c>
       <c r="O270" t="n">
-        <v>55399.6</v>
+        <v>44319.68</v>
       </c>
       <c r="P270" t="n">
         <v>3500</v>
       </c>
       <c r="Q270" t="n">
-        <v>70000</v>
+        <v>56000</v>
       </c>
     </row>
     <row r="271">
@@ -12441,22 +12441,22 @@
         <v>0</v>
       </c>
       <c r="L277" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M277" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="N277" t="n">
         <v>1381.75</v>
       </c>
       <c r="O277" t="n">
-        <v>42834.25</v>
+        <v>35925.5</v>
       </c>
       <c r="P277" t="n">
         <v>2500</v>
       </c>
       <c r="Q277" t="n">
-        <v>77500</v>
+        <v>65000</v>
       </c>
     </row>
     <row r="278">
@@ -12845,22 +12845,22 @@
         <v>0</v>
       </c>
       <c r="L286" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M286" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="N286" t="n">
-        <v>3041.6600129618</v>
+        <v>3041.6600129786</v>
       </c>
       <c r="O286" t="n">
-        <v>76041.500324045</v>
+        <v>69958.18029850781</v>
       </c>
       <c r="P286" t="n">
         <v>5500</v>
       </c>
       <c r="Q286" t="n">
-        <v>137500</v>
+        <v>126500</v>
       </c>
     </row>
     <row r="287">
@@ -12938,10 +12938,10 @@
         <v>1</v>
       </c>
       <c r="N288" t="n">
-        <v>4372.210788556</v>
+        <v>4372.2107886682</v>
       </c>
       <c r="O288" t="n">
-        <v>4372.210788556</v>
+        <v>4372.2107886682</v>
       </c>
       <c r="P288" t="n">
         <v>7500</v>
@@ -13022,22 +13022,22 @@
         <v>0</v>
       </c>
       <c r="L290" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M290" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="N290" t="n">
         <v>6441.03</v>
       </c>
       <c r="O290" t="n">
-        <v>483077.25</v>
+        <v>437990.04</v>
       </c>
       <c r="P290" t="n">
         <v>10500</v>
       </c>
       <c r="Q290" t="n">
-        <v>787500</v>
+        <v>714000</v>
       </c>
     </row>
     <row r="291">
@@ -13109,22 +13109,22 @@
         <v>0</v>
       </c>
       <c r="L292" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M292" t="n">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="N292" t="n">
-        <v>1592.5670028818</v>
+        <v>1592.5669608416</v>
       </c>
       <c r="O292" t="n">
-        <v>117849.9582132532</v>
+        <v>79628.34804207999</v>
       </c>
       <c r="P292" t="n">
         <v>3900</v>
       </c>
       <c r="Q292" t="n">
-        <v>288600</v>
+        <v>195000</v>
       </c>
     </row>
     <row r="293">
@@ -13191,22 +13191,22 @@
         <v>0</v>
       </c>
       <c r="L294" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M294" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="N294" t="n">
         <v>2224.56</v>
       </c>
       <c r="O294" t="n">
-        <v>37817.52</v>
+        <v>28919.28</v>
       </c>
       <c r="P294" t="n">
         <v>3900</v>
       </c>
       <c r="Q294" t="n">
-        <v>66300</v>
+        <v>50700</v>
       </c>
     </row>
     <row r="295">
@@ -13324,22 +13324,22 @@
         <v>0</v>
       </c>
       <c r="L297" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M297" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="N297" t="n">
         <v>4717</v>
       </c>
       <c r="O297" t="n">
-        <v>188680</v>
+        <v>174529</v>
       </c>
       <c r="P297" t="n">
         <v>7900</v>
       </c>
       <c r="Q297" t="n">
-        <v>316000</v>
+        <v>292300</v>
       </c>
     </row>
     <row r="298">
@@ -13368,22 +13368,22 @@
         <v>0</v>
       </c>
       <c r="L298" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M298" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N298" t="n">
         <v>6446.04</v>
       </c>
       <c r="O298" t="n">
-        <v>148258.92</v>
+        <v>141812.88</v>
       </c>
       <c r="P298" t="n">
         <v>5300</v>
       </c>
       <c r="Q298" t="n">
-        <v>121900</v>
+        <v>116600</v>
       </c>
     </row>
     <row r="299">
@@ -13594,22 +13594,22 @@
         <v>0</v>
       </c>
       <c r="L303" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M303" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="N303" t="n">
         <v>2230.77</v>
       </c>
       <c r="O303" t="n">
-        <v>142769.28</v>
+        <v>131615.43</v>
       </c>
       <c r="P303" t="n">
         <v>2900</v>
       </c>
       <c r="Q303" t="n">
-        <v>185600</v>
+        <v>171100</v>
       </c>
     </row>
     <row r="304">
@@ -13690,10 +13690,10 @@
         <v>51</v>
       </c>
       <c r="N305" t="n">
-        <v>1532.6290283636</v>
+        <v>1532.6290281516</v>
       </c>
       <c r="O305" t="n">
-        <v>78164.08044654359</v>
+        <v>78164.08043573161</v>
       </c>
       <c r="P305" t="n">
         <v>1200</v>
@@ -13774,22 +13774,22 @@
         <v>0</v>
       </c>
       <c r="L307" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M307" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="N307" t="n">
         <v>17472.91</v>
       </c>
       <c r="O307" t="n">
-        <v>192202.01</v>
+        <v>157256.19</v>
       </c>
       <c r="P307" t="n">
         <v>2900</v>
       </c>
       <c r="Q307" t="n">
-        <v>31900</v>
+        <v>26100</v>
       </c>
     </row>
     <row r="308">
@@ -13994,22 +13994,22 @@
         <v>0</v>
       </c>
       <c r="L312" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M312" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="N312" t="n">
         <v>1387.55</v>
       </c>
       <c r="O312" t="n">
-        <v>181769.05</v>
+        <v>178993.95</v>
       </c>
       <c r="P312" t="n">
         <v>2300</v>
       </c>
       <c r="Q312" t="n">
-        <v>301300</v>
+        <v>296700</v>
       </c>
     </row>
     <row r="313">
@@ -14278,22 +14278,22 @@
         <v>0</v>
       </c>
       <c r="L318" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M318" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N318" t="n">
         <v>16897</v>
       </c>
       <c r="O318" t="n">
-        <v>101382</v>
+        <v>84485</v>
       </c>
       <c r="P318" t="n">
         <v>27900</v>
       </c>
       <c r="Q318" t="n">
-        <v>167400</v>
+        <v>139500</v>
       </c>
     </row>
     <row r="319">
@@ -15154,22 +15154,22 @@
         <v>0</v>
       </c>
       <c r="L337" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M337" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N337" t="n">
         <v>9903</v>
       </c>
       <c r="O337" t="n">
-        <v>79224</v>
+        <v>49515</v>
       </c>
       <c r="P337" t="n">
         <v>15900</v>
       </c>
       <c r="Q337" t="n">
-        <v>127200</v>
+        <v>79500</v>
       </c>
     </row>
     <row r="338">
@@ -15246,22 +15246,22 @@
         <v>0</v>
       </c>
       <c r="L339" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M339" t="n">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="N339" t="n">
-        <v>1630.9234162594</v>
+        <v>1630.9234624043</v>
       </c>
       <c r="O339" t="n">
-        <v>187556.192869831</v>
+        <v>159830.4993156214</v>
       </c>
       <c r="P339" t="n">
         <v>2500</v>
       </c>
       <c r="Q339" t="n">
-        <v>287500</v>
+        <v>245000</v>
       </c>
     </row>
     <row r="340">
@@ -15298,10 +15298,10 @@
         <v>1</v>
       </c>
       <c r="N340" t="n">
-        <v>1467.3247826087</v>
+        <v>1467.3243362832</v>
       </c>
       <c r="O340" t="n">
-        <v>1467.3247826087</v>
+        <v>1467.3243362832</v>
       </c>
       <c r="P340" t="n">
         <v>2500</v>
@@ -15338,22 +15338,22 @@
         <v>0</v>
       </c>
       <c r="L341" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M341" t="n">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="N341" t="n">
-        <v>1690.5995518395</v>
+        <v>1690.5992886179</v>
       </c>
       <c r="O341" t="n">
-        <v>152153.959665555</v>
+        <v>140319.7409552857</v>
       </c>
       <c r="P341" t="n">
         <v>2900</v>
       </c>
       <c r="Q341" t="n">
-        <v>261000</v>
+        <v>240700</v>
       </c>
     </row>
     <row r="342">
@@ -15384,22 +15384,22 @@
         <v>0</v>
       </c>
       <c r="L342" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="M342" t="n">
-        <v>396</v>
+        <v>362</v>
       </c>
       <c r="N342" t="n">
-        <v>1550.1934418475</v>
+        <v>1550.1935205388</v>
       </c>
       <c r="O342" t="n">
-        <v>613876.60297161</v>
+        <v>561170.0544350456</v>
       </c>
       <c r="P342" t="n">
         <v>2500</v>
       </c>
       <c r="Q342" t="n">
-        <v>990000</v>
+        <v>905000</v>
       </c>
     </row>
     <row r="343">
@@ -15436,10 +15436,10 @@
         <v>1</v>
       </c>
       <c r="N343" t="n">
-        <v>1579.3908418367</v>
+        <v>1579.3907948718</v>
       </c>
       <c r="O343" t="n">
-        <v>1579.3908418367</v>
+        <v>1579.3907948718</v>
       </c>
       <c r="P343" t="n">
         <v>2900</v>
@@ -15476,22 +15476,22 @@
         <v>0</v>
       </c>
       <c r="L344" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="M344" t="n">
-        <v>276</v>
+        <v>244</v>
       </c>
       <c r="N344" t="n">
-        <v>2403.5113112366</v>
+        <v>2403.5114869613</v>
       </c>
       <c r="O344" t="n">
-        <v>663369.1219013016</v>
+        <v>586456.8028185571</v>
       </c>
       <c r="P344" t="n">
         <v>3500</v>
       </c>
       <c r="Q344" t="n">
-        <v>966000</v>
+        <v>854000</v>
       </c>
     </row>
     <row r="345">
@@ -15522,22 +15522,22 @@
         <v>0</v>
       </c>
       <c r="L345" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M345" t="n">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="N345" t="n">
-        <v>2521.5378855721</v>
+        <v>2521.5362299465</v>
       </c>
       <c r="O345" t="n">
-        <v>206766.1066169122</v>
+        <v>186593.681016041</v>
       </c>
       <c r="P345" t="n">
         <v>3900</v>
       </c>
       <c r="Q345" t="n">
-        <v>319800</v>
+        <v>288600</v>
       </c>
     </row>
     <row r="346">
@@ -15686,22 +15686,22 @@
         <v>0</v>
       </c>
       <c r="L349" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M349" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N349" t="n">
         <v>14778</v>
       </c>
       <c r="O349" t="n">
-        <v>103446</v>
+        <v>73890</v>
       </c>
       <c r="P349" t="n">
         <v>24900</v>
       </c>
       <c r="Q349" t="n">
-        <v>174300</v>
+        <v>124500</v>
       </c>
     </row>
     <row r="350">
@@ -16506,22 +16506,22 @@
         <v>0</v>
       </c>
       <c r="L367" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M367" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="N367" t="n">
         <v>17328</v>
       </c>
       <c r="O367" t="n">
-        <v>450528</v>
+        <v>415872</v>
       </c>
       <c r="P367" t="n">
         <v>32900</v>
       </c>
       <c r="Q367" t="n">
-        <v>855400</v>
+        <v>789600</v>
       </c>
     </row>
     <row r="368">
@@ -17937,22 +17937,22 @@
         <v>0</v>
       </c>
       <c r="L399" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M399" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="N399" t="n">
         <v>9338</v>
       </c>
       <c r="O399" t="n">
-        <v>354844</v>
+        <v>336168</v>
       </c>
       <c r="P399" t="n">
         <v>15500</v>
       </c>
       <c r="Q399" t="n">
-        <v>589000</v>
+        <v>558000</v>
       </c>
     </row>
     <row r="400">
@@ -18314,22 +18314,22 @@
         <v>0</v>
       </c>
       <c r="L408" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M408" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="N408" t="n">
         <v>1969</v>
       </c>
       <c r="O408" t="n">
-        <v>23628</v>
+        <v>17721</v>
       </c>
       <c r="P408" t="n">
         <v>1500</v>
       </c>
       <c r="Q408" t="n">
-        <v>18000</v>
+        <v>13500</v>
       </c>
     </row>
     <row r="409">
@@ -18612,10 +18612,10 @@
         <v>201</v>
       </c>
       <c r="N415" t="n">
-        <v>2029.8737332006</v>
+        <v>2029.8737350598</v>
       </c>
       <c r="O415" t="n">
-        <v>408004.6203733206</v>
+        <v>408004.6207470198</v>
       </c>
       <c r="P415" t="n">
         <v>3600</v>
@@ -18817,10 +18817,10 @@
         <v>45</v>
       </c>
       <c r="N420" t="n">
-        <v>2680.7396999388</v>
+        <v>2680.7396995708</v>
       </c>
       <c r="O420" t="n">
-        <v>120633.286497246</v>
+        <v>120633.286480686</v>
       </c>
       <c r="P420" t="n">
         <v>4900</v>
@@ -18858,10 +18858,10 @@
         <v>531</v>
       </c>
       <c r="N421" t="n">
-        <v>880.32945034206</v>
+        <v>880.3295131797699</v>
       </c>
       <c r="O421" t="n">
-        <v>467454.9381316339</v>
+        <v>467454.9714984578</v>
       </c>
       <c r="P421" t="n">
         <v>1200</v>
@@ -19318,22 +19318,22 @@
         <v>0</v>
       </c>
       <c r="L432" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M432" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N432" t="n">
         <v>14371.45</v>
       </c>
       <c r="O432" t="n">
-        <v>100600.15</v>
+        <v>86228.70000000001</v>
       </c>
       <c r="P432" t="n">
         <v>23300</v>
       </c>
       <c r="Q432" t="n">
-        <v>163100</v>
+        <v>139800</v>
       </c>
     </row>
     <row r="433">
@@ -19364,22 +19364,22 @@
         <v>0</v>
       </c>
       <c r="L433" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M433" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N433" t="n">
         <v>30611</v>
       </c>
       <c r="O433" t="n">
-        <v>367332</v>
+        <v>336721</v>
       </c>
       <c r="P433" t="n">
         <v>38900</v>
       </c>
       <c r="Q433" t="n">
-        <v>466800</v>
+        <v>427900</v>
       </c>
     </row>
     <row r="434">
@@ -19587,22 +19587,22 @@
         <v>0</v>
       </c>
       <c r="L438" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M438" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N438" t="n">
-        <v>4285.1953927813</v>
+        <v>4285.1954215582</v>
       </c>
       <c r="O438" t="n">
-        <v>59992.7354989382</v>
+        <v>55707.5404802566</v>
       </c>
       <c r="P438" t="n">
         <v>6900</v>
       </c>
       <c r="Q438" t="n">
-        <v>96600</v>
+        <v>89700</v>
       </c>
     </row>
     <row r="439">
@@ -20010,22 +20010,22 @@
         <v>0</v>
       </c>
       <c r="L448" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M448" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N448" t="n">
         <v>8987</v>
       </c>
       <c r="O448" t="n">
-        <v>53922</v>
+        <v>35948</v>
       </c>
       <c r="P448" t="n">
         <v>15200</v>
       </c>
       <c r="Q448" t="n">
-        <v>91200</v>
+        <v>60800</v>
       </c>
     </row>
     <row r="449">
@@ -20062,10 +20062,10 @@
         <v>14</v>
       </c>
       <c r="N449" t="n">
-        <v>4605.2146617238</v>
+        <v>4605.2146660482</v>
       </c>
       <c r="O449" t="n">
-        <v>64473.00526413321</v>
+        <v>64473.00532467481</v>
       </c>
       <c r="P449" t="n">
         <v>7600</v>
@@ -20149,10 +20149,10 @@
         <v>15</v>
       </c>
       <c r="N451" t="n">
-        <v>11562.038522427</v>
+        <v>11562.038518519</v>
       </c>
       <c r="O451" t="n">
-        <v>173430.577836405</v>
+        <v>173430.577777785</v>
       </c>
       <c r="P451" t="n">
         <v>18500</v>
@@ -20241,10 +20241,10 @@
         <v>3</v>
       </c>
       <c r="N453" t="n">
-        <v>12005.159831224</v>
+        <v>12005.159830508</v>
       </c>
       <c r="O453" t="n">
-        <v>36015.479493672</v>
+        <v>36015.47949152401</v>
       </c>
       <c r="P453" t="n">
         <v>19500</v>
@@ -20573,22 +20573,22 @@
         <v>0</v>
       </c>
       <c r="L461" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M461" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="N461" t="n">
         <v>4793.53</v>
       </c>
       <c r="O461" t="n">
-        <v>139012.37</v>
+        <v>129425.31</v>
       </c>
       <c r="P461" t="n">
         <v>7900</v>
       </c>
       <c r="Q461" t="n">
-        <v>229100</v>
+        <v>213300</v>
       </c>
     </row>
     <row r="462">
@@ -21095,22 +21095,22 @@
         <v>0</v>
       </c>
       <c r="L473" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M473" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="N473" t="n">
-        <v>1561</v>
+        <v>1561.0000887728</v>
       </c>
       <c r="O473" t="n">
-        <v>118636</v>
+        <v>106148.0060365504</v>
       </c>
       <c r="P473" t="n">
         <v>2900</v>
       </c>
       <c r="Q473" t="n">
-        <v>220400</v>
+        <v>197200</v>
       </c>
     </row>
     <row r="474">
@@ -21233,22 +21233,22 @@
         <v>0</v>
       </c>
       <c r="L476" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M476" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N476" t="n">
         <v>26854</v>
       </c>
       <c r="O476" t="n">
-        <v>349102</v>
+        <v>322248</v>
       </c>
       <c r="P476" t="n">
         <v>43900</v>
       </c>
       <c r="Q476" t="n">
-        <v>570700</v>
+        <v>526800</v>
       </c>
     </row>
     <row r="477">
@@ -21479,22 +21479,22 @@
         <v>0</v>
       </c>
       <c r="L482" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M482" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N482" t="n">
         <v>11662.4</v>
       </c>
       <c r="O482" t="n">
-        <v>34987.2</v>
+        <v>0</v>
       </c>
       <c r="P482" t="n">
         <v>19900</v>
       </c>
       <c r="Q482" t="n">
-        <v>59700</v>
+        <v>0</v>
       </c>
     </row>
     <row r="483">
@@ -21580,10 +21580,10 @@
         <v>6</v>
       </c>
       <c r="N484" t="n">
-        <v>7969.9501660377</v>
+        <v>7969.9501665405</v>
       </c>
       <c r="O484" t="n">
-        <v>47819.7009962262</v>
+        <v>47819.700999243</v>
       </c>
       <c r="P484" t="n">
         <v>12900</v>
@@ -23346,22 +23346,22 @@
         <v>0</v>
       </c>
       <c r="L524" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M524" t="n">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="N524" t="n">
         <v>7700</v>
       </c>
       <c r="O524" t="n">
-        <v>746900</v>
+        <v>708400</v>
       </c>
       <c r="P524" t="n">
         <v>13900</v>
       </c>
       <c r="Q524" t="n">
-        <v>1348300</v>
+        <v>1278800</v>
       </c>
     </row>
     <row r="525">
@@ -23444,10 +23444,10 @@
         <v>33</v>
       </c>
       <c r="N526" t="n">
-        <v>3113.8900273598</v>
+        <v>3113.8900274725</v>
       </c>
       <c r="O526" t="n">
-        <v>102758.3709028734</v>
+        <v>102758.3709065925</v>
       </c>
       <c r="P526" t="n">
         <v>5000</v>
@@ -23530,22 +23530,22 @@
         <v>0</v>
       </c>
       <c r="L528" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M528" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N528" t="n">
         <v>4690.64</v>
       </c>
       <c r="O528" t="n">
-        <v>32834.48</v>
+        <v>14071.92</v>
       </c>
       <c r="P528" t="n">
         <v>7500</v>
       </c>
       <c r="Q528" t="n">
-        <v>52500</v>
+        <v>22500</v>
       </c>
     </row>
     <row r="529">
@@ -23622,22 +23622,22 @@
         <v>0</v>
       </c>
       <c r="L530" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M530" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N530" t="n">
         <v>10911.29</v>
       </c>
       <c r="O530" t="n">
-        <v>10911.29</v>
+        <v>0</v>
       </c>
       <c r="P530" t="n">
         <v>17400</v>
       </c>
       <c r="Q530" t="n">
-        <v>17400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="531">
@@ -23812,10 +23812,10 @@
         <v>13</v>
       </c>
       <c r="N534" t="n">
-        <v>5218.1705346294</v>
+        <v>5218.1705412054</v>
       </c>
       <c r="O534" t="n">
-        <v>67836.21695018221</v>
+        <v>67836.2170356702</v>
       </c>
       <c r="P534" t="n">
         <v>8500</v>
@@ -24137,22 +24137,22 @@
         <v>0</v>
       </c>
       <c r="L541" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M541" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="N541" t="n">
         <v>4227.77</v>
       </c>
       <c r="O541" t="n">
-        <v>147971.95</v>
+        <v>139516.41</v>
       </c>
       <c r="P541" t="n">
         <v>6900</v>
       </c>
       <c r="Q541" t="n">
-        <v>241500</v>
+        <v>227700</v>
       </c>
     </row>
     <row r="542">
@@ -24278,22 +24278,22 @@
         <v>0</v>
       </c>
       <c r="L544" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M544" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N544" t="n">
         <v>5791.05</v>
       </c>
       <c r="O544" t="n">
-        <v>86865.75</v>
+        <v>81074.7</v>
       </c>
       <c r="P544" t="n">
         <v>9300</v>
       </c>
       <c r="Q544" t="n">
-        <v>139500</v>
+        <v>130200</v>
       </c>
     </row>
     <row r="545">
@@ -24416,22 +24416,22 @@
         <v>0</v>
       </c>
       <c r="L547" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M547" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="N547" t="n">
         <v>10977.27</v>
       </c>
       <c r="O547" t="n">
-        <v>164659.05</v>
+        <v>120749.97</v>
       </c>
       <c r="P547" t="n">
         <v>17900</v>
       </c>
       <c r="Q547" t="n">
-        <v>268500</v>
+        <v>196900</v>
       </c>
     </row>
     <row r="548">
@@ -24508,22 +24508,22 @@
         <v>0</v>
       </c>
       <c r="L549" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M549" t="n">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="N549" t="n">
-        <v>1664.3579393305</v>
+        <v>1664.3571460424</v>
       </c>
       <c r="O549" t="n">
-        <v>246324.975020914</v>
+        <v>228016.9290078088</v>
       </c>
       <c r="P549" t="n">
         <v>2900</v>
       </c>
       <c r="Q549" t="n">
-        <v>429200</v>
+        <v>397300</v>
       </c>
     </row>
     <row r="550">
@@ -24652,22 +24652,22 @@
         <v>0</v>
       </c>
       <c r="L552" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M552" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="N552" t="n">
         <v>3079.84</v>
       </c>
       <c r="O552" t="n">
-        <v>163231.52</v>
+        <v>153992</v>
       </c>
       <c r="P552" t="n">
         <v>2900</v>
       </c>
       <c r="Q552" t="n">
-        <v>153700</v>
+        <v>145000</v>
       </c>
     </row>
     <row r="553">
@@ -25308,10 +25308,10 @@
         <v>27</v>
       </c>
       <c r="N566" t="n">
-        <v>1778.4725974412</v>
+        <v>1778.4725978277</v>
       </c>
       <c r="O566" t="n">
-        <v>48018.7601309124</v>
+        <v>48018.7601413479</v>
       </c>
       <c r="P566" t="n">
         <v>4900</v>
@@ -25486,22 +25486,22 @@
         <v>0</v>
       </c>
       <c r="L570" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M570" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N570" t="n">
         <v>10571</v>
       </c>
       <c r="O570" t="n">
-        <v>147994</v>
+        <v>137423</v>
       </c>
       <c r="P570" t="n">
         <v>18900</v>
       </c>
       <c r="Q570" t="n">
-        <v>264600</v>
+        <v>245700</v>
       </c>
     </row>
     <row r="571">
@@ -25624,22 +25624,22 @@
         <v>0</v>
       </c>
       <c r="L573" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M573" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N573" t="n">
         <v>16058</v>
       </c>
       <c r="O573" t="n">
-        <v>128464</v>
+        <v>80290</v>
       </c>
       <c r="P573" t="n">
         <v>25900</v>
       </c>
       <c r="Q573" t="n">
-        <v>207200</v>
+        <v>129500</v>
       </c>
     </row>
     <row r="574">
@@ -26223,25 +26223,25 @@
         <v>1</v>
       </c>
       <c r="K586" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L586" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M586" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="N586" t="n">
         <v>7108.85</v>
       </c>
       <c r="O586" t="n">
-        <v>7108.85</v>
+        <v>156394.7</v>
       </c>
       <c r="P586" t="n">
         <v>7900</v>
       </c>
       <c r="Q586" t="n">
-        <v>7900</v>
+        <v>173800</v>
       </c>
     </row>
     <row r="587">
@@ -26600,22 +26600,22 @@
         <v>0</v>
       </c>
       <c r="L594" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M594" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N594" t="n">
         <v>13687</v>
       </c>
       <c r="O594" t="n">
-        <v>355862</v>
+        <v>314801</v>
       </c>
       <c r="P594" t="n">
         <v>21900</v>
       </c>
       <c r="Q594" t="n">
-        <v>569400</v>
+        <v>503700</v>
       </c>
     </row>
     <row r="595">
@@ -26784,22 +26784,22 @@
         <v>0</v>
       </c>
       <c r="L598" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M598" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N598" t="n">
         <v>3938.66</v>
       </c>
       <c r="O598" t="n">
-        <v>59079.89999999999</v>
+        <v>51202.58</v>
       </c>
       <c r="P598" t="n">
         <v>4500</v>
       </c>
       <c r="Q598" t="n">
-        <v>67500</v>
+        <v>58500</v>
       </c>
     </row>
     <row r="599">
@@ -28079,22 +28079,22 @@
         <v>0</v>
       </c>
       <c r="L626" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M626" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N626" t="n">
         <v>21676</v>
       </c>
       <c r="O626" t="n">
-        <v>888716</v>
+        <v>867040</v>
       </c>
       <c r="P626" t="n">
         <v>34900</v>
       </c>
       <c r="Q626" t="n">
-        <v>1430900</v>
+        <v>1396000</v>
       </c>
     </row>
     <row r="627">
@@ -28401,22 +28401,22 @@
         <v>0</v>
       </c>
       <c r="L633" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M633" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="N633" t="n">
         <v>4544</v>
       </c>
       <c r="O633" t="n">
-        <v>358976</v>
+        <v>327168</v>
       </c>
       <c r="P633" t="n">
         <v>7900</v>
       </c>
       <c r="Q633" t="n">
-        <v>624100</v>
+        <v>568800</v>
       </c>
     </row>
     <row r="634">
@@ -28677,22 +28677,22 @@
         <v>0</v>
       </c>
       <c r="L639" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M639" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="N639" t="n">
-        <v>4907.8220483871</v>
+        <v>4907.8220583468</v>
       </c>
       <c r="O639" t="n">
-        <v>181589.4157903227</v>
+        <v>171773.772042138</v>
       </c>
       <c r="P639" t="n">
         <v>8200</v>
       </c>
       <c r="Q639" t="n">
-        <v>303400</v>
+        <v>287000</v>
       </c>
     </row>
     <row r="640">
@@ -28907,22 +28907,22 @@
         <v>0</v>
       </c>
       <c r="L644" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M644" t="n">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="N644" t="n">
-        <v>3903.7363106796</v>
+        <v>3903.7364457831</v>
       </c>
       <c r="O644" t="n">
-        <v>343528.7953398048</v>
+        <v>324010.1249999973</v>
       </c>
       <c r="P644" t="n">
         <v>7500</v>
       </c>
       <c r="Q644" t="n">
-        <v>660000</v>
+        <v>622500</v>
       </c>
     </row>
     <row r="645">
@@ -28948,22 +28948,22 @@
         <v>0</v>
       </c>
       <c r="L645" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M645" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N645" t="n">
         <v>20726</v>
       </c>
       <c r="O645" t="n">
-        <v>227986</v>
+        <v>207260</v>
       </c>
       <c r="P645" t="n">
         <v>33900</v>
       </c>
       <c r="Q645" t="n">
-        <v>372900</v>
+        <v>339000</v>
       </c>
     </row>
     <row r="646">
@@ -29037,25 +29037,25 @@
         <v>1</v>
       </c>
       <c r="K647" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="L647" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M647" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="N647" t="n">
         <v>12113</v>
       </c>
       <c r="O647" t="n">
-        <v>12113</v>
+        <v>193808</v>
       </c>
       <c r="P647" t="n">
         <v>19900</v>
       </c>
       <c r="Q647" t="n">
-        <v>19900</v>
+        <v>318400</v>
       </c>
     </row>
     <row r="648">
@@ -29730,22 +29730,22 @@
         <v>0</v>
       </c>
       <c r="L662" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M662" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N662" t="n">
         <v>27186</v>
       </c>
       <c r="O662" t="n">
-        <v>217488</v>
+        <v>135930</v>
       </c>
       <c r="P662" t="n">
         <v>43900</v>
       </c>
       <c r="Q662" t="n">
-        <v>351200</v>
+        <v>219500</v>
       </c>
     </row>
     <row r="663">
@@ -30429,10 +30429,10 @@
         <v>36</v>
       </c>
       <c r="N677" t="n">
-        <v>17075.98952381</v>
+        <v>17075.989523481</v>
       </c>
       <c r="O677" t="n">
-        <v>614735.6228571599</v>
+        <v>614735.622845316</v>
       </c>
       <c r="P677" t="n">
         <v>27500</v>
@@ -30786,22 +30786,22 @@
         <v>0</v>
       </c>
       <c r="L685" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M685" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N685" t="n">
         <v>18001</v>
       </c>
       <c r="O685" t="n">
-        <v>108006</v>
+        <v>90005</v>
       </c>
       <c r="P685" t="n">
         <v>28900</v>
       </c>
       <c r="Q685" t="n">
-        <v>173400</v>
+        <v>144500</v>
       </c>
     </row>
     <row r="686">
@@ -31663,22 +31663,22 @@
         <v>0</v>
       </c>
       <c r="L704" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M704" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N704" t="n">
         <v>2458</v>
       </c>
       <c r="O704" t="n">
-        <v>34412</v>
+        <v>29496</v>
       </c>
       <c r="P704" t="n">
         <v>3500</v>
       </c>
       <c r="Q704" t="n">
-        <v>49000</v>
+        <v>42000</v>
       </c>
     </row>
     <row r="705">
@@ -31985,22 +31985,22 @@
         <v>0</v>
       </c>
       <c r="L711" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M711" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N711" t="n">
         <v>5476</v>
       </c>
       <c r="O711" t="n">
-        <v>27380</v>
+        <v>21904</v>
       </c>
       <c r="P711" t="n">
         <v>8900</v>
       </c>
       <c r="Q711" t="n">
-        <v>44500</v>
+        <v>35600</v>
       </c>
     </row>
     <row r="712">
@@ -32169,22 +32169,22 @@
         <v>0</v>
       </c>
       <c r="L715" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M715" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="N715" t="n">
-        <v>1516.0388031113</v>
+        <v>1516.0388018299</v>
       </c>
       <c r="O715" t="n">
-        <v>27288.6984560034</v>
+        <v>15160.388018299</v>
       </c>
       <c r="P715" t="n">
         <v>2300</v>
       </c>
       <c r="Q715" t="n">
-        <v>41400</v>
+        <v>23000</v>
       </c>
     </row>
     <row r="716">
@@ -32265,10 +32265,10 @@
         <v>45</v>
       </c>
       <c r="N717" t="n">
-        <v>4248.652</v>
+        <v>4248.6728</v>
       </c>
       <c r="O717" t="n">
-        <v>191189.34</v>
+        <v>191190.276</v>
       </c>
       <c r="P717" t="n">
         <v>5900</v>
@@ -32305,22 +32305,22 @@
         <v>0</v>
       </c>
       <c r="L718" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M718" t="n">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="N718" t="n">
-        <v>2458.5132807977</v>
+        <v>2458.5132504039</v>
       </c>
       <c r="O718" t="n">
-        <v>565458.054583471</v>
+        <v>560541.0210920892</v>
       </c>
       <c r="P718" t="n">
         <v>3500</v>
       </c>
       <c r="Q718" t="n">
-        <v>805000</v>
+        <v>798000</v>
       </c>
     </row>
     <row r="719">
@@ -32351,22 +32351,22 @@
         <v>0</v>
       </c>
       <c r="L719" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M719" t="n">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="N719" t="n">
-        <v>1907.3938243626</v>
+        <v>1907.3938009479</v>
       </c>
       <c r="O719" t="n">
-        <v>286109.07365439</v>
+        <v>282294.2825402892</v>
       </c>
       <c r="P719" t="n">
         <v>2500</v>
       </c>
       <c r="Q719" t="n">
-        <v>375000</v>
+        <v>370000</v>
       </c>
     </row>
     <row r="720">
@@ -32397,22 +32397,22 @@
         <v>0</v>
       </c>
       <c r="L720" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M720" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="N720" t="n">
-        <v>1771.0906468305</v>
+        <v>1771.0905981795</v>
       </c>
       <c r="O720" t="n">
-        <v>76156.8978137115</v>
+        <v>70843.62392718</v>
       </c>
       <c r="P720" t="n">
         <v>2500</v>
       </c>
       <c r="Q720" t="n">
-        <v>107500</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="721">
@@ -32443,22 +32443,22 @@
         <v>0</v>
       </c>
       <c r="L721" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M721" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="N721" t="n">
-        <v>2079.3840533333</v>
+        <v>2079.3840473807</v>
       </c>
       <c r="O721" t="n">
-        <v>257843.6226133292</v>
+        <v>253684.8537804454</v>
       </c>
       <c r="P721" t="n">
         <v>2900</v>
       </c>
       <c r="Q721" t="n">
-        <v>359600</v>
+        <v>353800</v>
       </c>
     </row>
     <row r="722">
@@ -32495,10 +32495,10 @@
         <v>144</v>
       </c>
       <c r="N722" t="n">
-        <v>1803.0155537353</v>
+        <v>1803.0155591997</v>
       </c>
       <c r="O722" t="n">
-        <v>259634.2397378832</v>
+        <v>259634.2405247568</v>
       </c>
       <c r="P722" t="n">
         <v>2500</v>
@@ -32535,22 +32535,22 @@
         <v>0</v>
       </c>
       <c r="L723" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M723" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="N723" t="n">
-        <v>3306.5952380952</v>
+        <v>3306.5951935915</v>
       </c>
       <c r="O723" t="n">
-        <v>175249.5476190456</v>
+        <v>168636.3548731665</v>
       </c>
       <c r="P723" t="n">
         <v>4900</v>
       </c>
       <c r="Q723" t="n">
-        <v>259700</v>
+        <v>249900</v>
       </c>
     </row>
     <row r="724">
@@ -32587,10 +32587,10 @@
         <v>40</v>
       </c>
       <c r="N724" t="n">
-        <v>2122.1639235788</v>
+        <v>2122.1639198011</v>
       </c>
       <c r="O724" t="n">
-        <v>84886.55694315201</v>
+        <v>84886.55679204399</v>
       </c>
       <c r="P724" t="n">
         <v>2900</v>
@@ -32627,22 +32627,22 @@
         <v>0</v>
       </c>
       <c r="L725" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M725" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="N725" t="n">
-        <v>2108.7910927573</v>
+        <v>2108.7914267016</v>
       </c>
       <c r="O725" t="n">
-        <v>181356.0339771278</v>
+        <v>168703.314136128</v>
       </c>
       <c r="P725" t="n">
         <v>2900</v>
       </c>
       <c r="Q725" t="n">
-        <v>249400</v>
+        <v>232000</v>
       </c>
     </row>
     <row r="726">
@@ -32673,22 +32673,22 @@
         <v>0</v>
       </c>
       <c r="L726" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M726" t="n">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="N726" t="n">
-        <v>2056.0834704208</v>
+        <v>2056.0834183673</v>
       </c>
       <c r="O726" t="n">
-        <v>540749.9527206704</v>
+        <v>536637.7721938653</v>
       </c>
       <c r="P726" t="n">
         <v>2900</v>
       </c>
       <c r="Q726" t="n">
-        <v>762700</v>
+        <v>756900</v>
       </c>
     </row>
     <row r="727">
@@ -32719,22 +32719,22 @@
         <v>0</v>
       </c>
       <c r="L727" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M727" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="N727" t="n">
-        <v>3224.5685035629</v>
+        <v>3224.5685238095</v>
       </c>
       <c r="O727" t="n">
-        <v>254740.9117814691</v>
+        <v>238618.070761903</v>
       </c>
       <c r="P727" t="n">
         <v>4500</v>
       </c>
       <c r="Q727" t="n">
-        <v>355500</v>
+        <v>333000</v>
       </c>
     </row>
     <row r="728">
@@ -32765,22 +32765,22 @@
         <v>0</v>
       </c>
       <c r="L728" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M728" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="N728" t="n">
-        <v>1655.9309755302</v>
+        <v>1655.9309666884</v>
       </c>
       <c r="O728" t="n">
-        <v>259981.1631582414</v>
+        <v>256669.299836702</v>
       </c>
       <c r="P728" t="n">
         <v>2500</v>
       </c>
       <c r="Q728" t="n">
-        <v>392500</v>
+        <v>387500</v>
       </c>
     </row>
     <row r="729">
@@ -33044,22 +33044,22 @@
         <v>0</v>
       </c>
       <c r="L734" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M734" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="N734" t="n">
-        <v>1592.276898982</v>
+        <v>1592.2773416667</v>
       </c>
       <c r="O734" t="n">
-        <v>73244.73735317199</v>
+        <v>44583.7655666676</v>
       </c>
       <c r="P734" t="n">
         <v>2500</v>
       </c>
       <c r="Q734" t="n">
-        <v>115000</v>
+        <v>70000</v>
       </c>
     </row>
     <row r="735">
@@ -33221,22 +33221,22 @@
         <v>0</v>
       </c>
       <c r="L738" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M738" t="n">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="N738" t="n">
-        <v>2311.9211486486</v>
+        <v>2311.9204895105</v>
       </c>
       <c r="O738" t="n">
-        <v>182641.7707432394</v>
+        <v>154898.6727972035</v>
       </c>
       <c r="P738" t="n">
         <v>3500</v>
       </c>
       <c r="Q738" t="n">
-        <v>276500</v>
+        <v>234500</v>
       </c>
     </row>
     <row r="739">
@@ -33267,22 +33267,22 @@
         <v>0</v>
       </c>
       <c r="L739" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M739" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="N739" t="n">
-        <v>1906.1850980392</v>
+        <v>1906.1849324324</v>
       </c>
       <c r="O739" t="n">
-        <v>99121.62509803841</v>
+        <v>91496.8767567552</v>
       </c>
       <c r="P739" t="n">
         <v>2900</v>
       </c>
       <c r="Q739" t="n">
-        <v>150800</v>
+        <v>139200</v>
       </c>
     </row>
     <row r="740">
@@ -33313,22 +33313,22 @@
         <v>0</v>
       </c>
       <c r="L740" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M740" t="n">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="N740" t="n">
-        <v>3033.723314121</v>
+        <v>3033.7213312693</v>
       </c>
       <c r="O740" t="n">
-        <v>236630.418501438</v>
+        <v>175955.8372136194</v>
       </c>
       <c r="P740" t="n">
         <v>4500</v>
       </c>
       <c r="Q740" t="n">
-        <v>351000</v>
+        <v>261000</v>
       </c>
     </row>
     <row r="741">
@@ -33359,22 +33359,22 @@
         <v>0</v>
       </c>
       <c r="L741" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M741" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="N741" t="n">
-        <v>2060.1603030303</v>
+        <v>2060.1601200686</v>
       </c>
       <c r="O741" t="n">
-        <v>199835.5493939391</v>
+        <v>193655.0512864484</v>
       </c>
       <c r="P741" t="n">
         <v>2900</v>
       </c>
       <c r="Q741" t="n">
-        <v>281300</v>
+        <v>272600</v>
       </c>
     </row>
     <row r="742">
@@ -33405,22 +33405,22 @@
         <v>0</v>
       </c>
       <c r="L742" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="M742" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="N742" t="n">
-        <v>1668.6274157303</v>
+        <v>1668.628045977</v>
       </c>
       <c r="O742" t="n">
-        <v>125147.0561797725</v>
+        <v>113466.707126436</v>
       </c>
       <c r="P742" t="n">
         <v>2500</v>
       </c>
       <c r="Q742" t="n">
-        <v>187500</v>
+        <v>170000</v>
       </c>
     </row>
     <row r="743">
@@ -33451,22 +33451,22 @@
         <v>0</v>
       </c>
       <c r="L743" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="M743" t="n">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="N743" t="n">
-        <v>2546.9846516008</v>
+        <v>2546.9843873518</v>
       </c>
       <c r="O743" t="n">
-        <v>402423.5749529264</v>
+        <v>387141.6268774736</v>
       </c>
       <c r="P743" t="n">
         <v>3900</v>
       </c>
       <c r="Q743" t="n">
-        <v>616200</v>
+        <v>592800</v>
       </c>
     </row>
     <row r="744">
@@ -33503,10 +33503,10 @@
         <v>200</v>
       </c>
       <c r="N744" t="n">
-        <v>1259.2745137492</v>
+        <v>1259.2745258911</v>
       </c>
       <c r="O744" t="n">
-        <v>251854.90274984</v>
+        <v>251854.90517822</v>
       </c>
       <c r="P744" t="n">
         <v>1900</v>
@@ -33590,10 +33590,10 @@
         <v>20</v>
       </c>
       <c r="N746" t="n">
-        <v>2842.2737539432</v>
+        <v>2842.2737341772</v>
       </c>
       <c r="O746" t="n">
-        <v>56845.475078864</v>
+        <v>56845.474683544</v>
       </c>
       <c r="P746" t="n">
         <v>4900</v>
@@ -33676,22 +33676,22 @@
         <v>0</v>
       </c>
       <c r="L748" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M748" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="N748" t="n">
-        <v>2556.745819398</v>
+        <v>2556.7459385666</v>
       </c>
       <c r="O748" t="n">
-        <v>240334.107023412</v>
+        <v>230107.134470994</v>
       </c>
       <c r="P748" t="n">
         <v>3900</v>
       </c>
       <c r="Q748" t="n">
-        <v>366600</v>
+        <v>351000</v>
       </c>
     </row>
     <row r="749">
@@ -33726,10 +33726,10 @@
         <v>350</v>
       </c>
       <c r="N749" t="n">
-        <v>692.15220363289</v>
+        <v>692.15222061657</v>
       </c>
       <c r="O749" t="n">
-        <v>242253.2712715115</v>
+        <v>242253.2772157995</v>
       </c>
       <c r="P749" t="n">
         <v>1200</v>
@@ -34177,25 +34177,25 @@
         <v>27</v>
       </c>
       <c r="K759" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="L759" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M759" t="n">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="N759" t="n">
         <v>1337.86</v>
       </c>
       <c r="O759" t="n">
-        <v>36122.21999999999</v>
+        <v>82947.31999999999</v>
       </c>
       <c r="P759" t="n">
         <v>3000</v>
       </c>
       <c r="Q759" t="n">
-        <v>81000</v>
+        <v>186000</v>
       </c>
     </row>
     <row r="760">
@@ -35389,22 +35389,22 @@
         <v>0</v>
       </c>
       <c r="L785" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M785" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N785" t="n">
         <v>2312.96</v>
       </c>
       <c r="O785" t="n">
-        <v>53198.08</v>
+        <v>48572.16</v>
       </c>
       <c r="P785" t="n">
         <v>2500</v>
       </c>
       <c r="Q785" t="n">
-        <v>57500</v>
+        <v>52500</v>
       </c>
     </row>
     <row r="786">
@@ -35671,22 +35671,22 @@
         <v>0</v>
       </c>
       <c r="L791" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M791" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="N791" t="n">
         <v>7103.81</v>
       </c>
       <c r="O791" t="n">
-        <v>440436.22</v>
+        <v>397813.36</v>
       </c>
       <c r="P791" t="n">
         <v>8900</v>
       </c>
       <c r="Q791" t="n">
-        <v>551800</v>
+        <v>498400</v>
       </c>
     </row>
     <row r="792">
@@ -35899,22 +35899,22 @@
         <v>0</v>
       </c>
       <c r="L796" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M796" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N796" t="n">
-        <v>2296.5708333333</v>
+        <v>2296.5708695652</v>
       </c>
       <c r="O796" t="n">
-        <v>110235.3999999984</v>
+        <v>105642.2599999992</v>
       </c>
       <c r="P796" t="n">
         <v>1900</v>
       </c>
       <c r="Q796" t="n">
-        <v>91200</v>
+        <v>87400</v>
       </c>
     </row>
     <row r="797">
@@ -35945,22 +35945,22 @@
         <v>0</v>
       </c>
       <c r="L797" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M797" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N797" t="n">
-        <v>1690.870009058</v>
+        <v>1690.8700090909</v>
       </c>
       <c r="O797" t="n">
-        <v>84543.5004529</v>
+        <v>82852.63044545411</v>
       </c>
       <c r="P797" t="n">
         <v>3000</v>
       </c>
       <c r="Q797" t="n">
-        <v>150000</v>
+        <v>147000</v>
       </c>
     </row>
     <row r="798">
@@ -36982,10 +36982,10 @@
         <v>16</v>
       </c>
       <c r="N819" t="n">
-        <v>1283.6539261745</v>
+        <v>1283.6538013699</v>
       </c>
       <c r="O819" t="n">
-        <v>20538.462818792</v>
+        <v>20538.4608219184</v>
       </c>
       <c r="P819" t="n">
         <v>1900</v>
@@ -37564,22 +37564,22 @@
         <v>0</v>
       </c>
       <c r="L832" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M832" t="n">
-        <v>1194</v>
+        <v>1180</v>
       </c>
       <c r="N832" t="n">
-        <v>517.28896164542</v>
+        <v>517.28908220781</v>
       </c>
       <c r="O832" t="n">
-        <v>617643.0202046315</v>
+        <v>610401.1170052158</v>
       </c>
       <c r="P832" t="n">
         <v>900</v>
       </c>
       <c r="Q832" t="n">
-        <v>1074600</v>
+        <v>1062000</v>
       </c>
     </row>
     <row r="833">
@@ -38085,10 +38085,10 @@
         <v>316</v>
       </c>
       <c r="N843" t="n">
-        <v>3110.8423302235</v>
+        <v>3110.842321894</v>
       </c>
       <c r="O843" t="n">
-        <v>983026.176350626</v>
+        <v>983026.173718504</v>
       </c>
       <c r="P843" t="n">
         <v>4500</v>
@@ -38262,22 +38262,22 @@
         <v>0</v>
       </c>
       <c r="L847" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M847" t="n">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="N847" t="n">
         <v>2030.02</v>
       </c>
       <c r="O847" t="n">
-        <v>294352.9</v>
+        <v>265932.62</v>
       </c>
       <c r="P847" t="n">
         <v>3600</v>
       </c>
       <c r="Q847" t="n">
-        <v>522000</v>
+        <v>471600</v>
       </c>
     </row>
     <row r="848">
@@ -38308,22 +38308,22 @@
         <v>0</v>
       </c>
       <c r="L848" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M848" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N848" t="n">
         <v>7120</v>
       </c>
       <c r="O848" t="n">
-        <v>128160</v>
+        <v>113920</v>
       </c>
       <c r="P848" t="n">
         <v>8900</v>
       </c>
       <c r="Q848" t="n">
-        <v>160200</v>
+        <v>142400</v>
       </c>
     </row>
     <row r="849">
@@ -38491,22 +38491,22 @@
         <v>0</v>
       </c>
       <c r="L852" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="M852" t="n">
-        <v>438</v>
+        <v>367</v>
       </c>
       <c r="N852" t="n">
-        <v>703.79522697548</v>
+        <v>703.79521051815</v>
       </c>
       <c r="O852" t="n">
-        <v>308262.3094152602</v>
+        <v>258292.8422601611</v>
       </c>
       <c r="P852" t="n">
         <v>900</v>
       </c>
       <c r="Q852" t="n">
-        <v>394200</v>
+        <v>330300</v>
       </c>
     </row>
     <row r="853">
@@ -38546,10 +38546,10 @@
         <v>24</v>
       </c>
       <c r="N853" t="n">
-        <v>3182.2511070111</v>
+        <v>3182.2511214953</v>
       </c>
       <c r="O853" t="n">
-        <v>76374.0265682664</v>
+        <v>76374.0269158872</v>
       </c>
       <c r="P853" t="n">
         <v>6900</v>
@@ -38773,22 +38773,22 @@
         <v>0</v>
       </c>
       <c r="L858" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M858" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="N858" t="n">
         <v>7570.87</v>
       </c>
       <c r="O858" t="n">
-        <v>181700.88</v>
+        <v>136275.66</v>
       </c>
       <c r="P858" t="n">
         <v>9500</v>
       </c>
       <c r="Q858" t="n">
-        <v>228000</v>
+        <v>171000</v>
       </c>
     </row>
     <row r="859">
@@ -39006,22 +39006,22 @@
         <v>0</v>
       </c>
       <c r="L863" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M863" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="N863" t="n">
-        <v>3006.0208695652</v>
+        <v>3006.0208780488</v>
       </c>
       <c r="O863" t="n">
-        <v>396794.7547826064</v>
+        <v>390782.714146344</v>
       </c>
       <c r="P863" t="n">
         <v>3900</v>
       </c>
       <c r="Q863" t="n">
-        <v>514800</v>
+        <v>507000</v>
       </c>
     </row>
     <row r="864">
@@ -39324,22 +39324,22 @@
         <v>0</v>
       </c>
       <c r="L870" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M870" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="N870" t="n">
         <v>1300</v>
       </c>
       <c r="O870" t="n">
-        <v>27300</v>
+        <v>23400</v>
       </c>
       <c r="P870" t="n">
         <v>2200</v>
       </c>
       <c r="Q870" t="n">
-        <v>46200</v>
+        <v>39600</v>
       </c>
     </row>
     <row r="871">
@@ -39417,22 +39417,22 @@
         <v>0</v>
       </c>
       <c r="L872" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M872" t="n">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="N872" t="n">
         <v>2525.02</v>
       </c>
       <c r="O872" t="n">
-        <v>217151.72</v>
+        <v>194426.54</v>
       </c>
       <c r="P872" t="n">
         <v>3000</v>
       </c>
       <c r="Q872" t="n">
-        <v>258000</v>
+        <v>231000</v>
       </c>
     </row>
     <row r="873">
@@ -39554,22 +39554,22 @@
         <v>0</v>
       </c>
       <c r="L875" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M875" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="N875" t="n">
-        <v>1595.5132863655</v>
+        <v>1595.513125523</v>
       </c>
       <c r="O875" t="n">
-        <v>70202.584600082</v>
+        <v>57438.47251882801</v>
       </c>
       <c r="P875" t="n">
         <v>2500</v>
       </c>
       <c r="Q875" t="n">
-        <v>110000</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="876">
@@ -41237,22 +41237,22 @@
         <v>0</v>
       </c>
       <c r="L910" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M910" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N910" t="n">
         <v>9874.620000000001</v>
       </c>
       <c r="O910" t="n">
-        <v>39498.48</v>
+        <v>9874.620000000001</v>
       </c>
       <c r="P910" t="n">
         <v>14700</v>
       </c>
       <c r="Q910" t="n">
-        <v>58800</v>
+        <v>14700</v>
       </c>
     </row>
     <row r="911">
@@ -41335,22 +41335,22 @@
         <v>0</v>
       </c>
       <c r="L912" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M912" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N912" t="n">
         <v>12837.03</v>
       </c>
       <c r="O912" t="n">
-        <v>179718.42</v>
+        <v>154044.36</v>
       </c>
       <c r="P912" t="n">
         <v>15500</v>
       </c>
       <c r="Q912" t="n">
-        <v>217000</v>
+        <v>186000</v>
       </c>
     </row>
     <row r="913">
@@ -41675,22 +41675,22 @@
         <v>0</v>
       </c>
       <c r="L919" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M919" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="N919" t="n">
-        <v>5796.3343478261</v>
+        <v>5796.3347619048</v>
       </c>
       <c r="O919" t="n">
-        <v>115926.686956522</v>
+        <v>104334.0257142864</v>
       </c>
       <c r="P919" t="n">
         <v>15900</v>
       </c>
       <c r="Q919" t="n">
-        <v>318000</v>
+        <v>286200</v>
       </c>
     </row>
     <row r="920">
@@ -41724,22 +41724,22 @@
         <v>0</v>
       </c>
       <c r="L920" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M920" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="N920" t="n">
         <v>2286.48</v>
       </c>
       <c r="O920" t="n">
-        <v>50302.56</v>
+        <v>27437.76</v>
       </c>
       <c r="P920" t="n">
         <v>3500</v>
       </c>
       <c r="Q920" t="n">
-        <v>77000</v>
+        <v>42000</v>
       </c>
     </row>
     <row r="921">
@@ -42113,22 +42113,22 @@
         <v>0</v>
       </c>
       <c r="L928" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M928" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N928" t="n">
-        <v>11352.65</v>
+        <v>0</v>
       </c>
       <c r="O928" t="n">
-        <v>34057.95</v>
+        <v>0</v>
       </c>
       <c r="P928" t="n">
         <v>14900</v>
       </c>
       <c r="Q928" t="n">
-        <v>44700</v>
+        <v>0</v>
       </c>
     </row>
     <row r="929">
@@ -42589,22 +42589,22 @@
         <v>0</v>
       </c>
       <c r="L938" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M938" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="N938" t="n">
         <v>19632.66</v>
       </c>
       <c r="O938" t="n">
-        <v>3474980.82</v>
+        <v>3455348.16</v>
       </c>
       <c r="P938" t="n">
         <v>2800</v>
       </c>
       <c r="Q938" t="n">
-        <v>495600</v>
+        <v>492800</v>
       </c>
     </row>
     <row r="939">
@@ -43019,22 +43019,22 @@
         <v>0</v>
       </c>
       <c r="L947" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M947" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="N947" t="n">
         <v>4190.77</v>
       </c>
       <c r="O947" t="n">
-        <v>150867.72</v>
+        <v>138295.41</v>
       </c>
       <c r="P947" t="n">
         <v>5900</v>
       </c>
       <c r="Q947" t="n">
-        <v>212400</v>
+        <v>194700</v>
       </c>
     </row>
     <row r="948">
@@ -45360,22 +45360,22 @@
         <v>0</v>
       </c>
       <c r="L996" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M996" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N996" t="n">
-        <v>14327.781818182</v>
+        <v>14327.782</v>
       </c>
       <c r="O996" t="n">
-        <v>157605.600000002</v>
+        <v>143277.82</v>
       </c>
       <c r="P996" t="n">
         <v>29900</v>
       </c>
       <c r="Q996" t="n">
-        <v>328900</v>
+        <v>299000</v>
       </c>
     </row>
     <row r="997">
@@ -45404,22 +45404,22 @@
         <v>0</v>
       </c>
       <c r="L997" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M997" t="n">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="N997" t="n">
-        <v>2000.6734965035</v>
+        <v>2000.6767625899</v>
       </c>
       <c r="O997" t="n">
-        <v>280094.28951049</v>
+        <v>272092.0397122264</v>
       </c>
       <c r="P997" t="n">
         <v>2000</v>
       </c>
       <c r="Q997" t="n">
-        <v>280000</v>
+        <v>272000</v>
       </c>
     </row>
     <row r="998">
@@ -45499,22 +45499,22 @@
         <v>0</v>
       </c>
       <c r="L999" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M999" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="N999" t="n">
         <v>1024.29</v>
       </c>
       <c r="O999" t="n">
-        <v>29704.41</v>
+        <v>26631.54</v>
       </c>
       <c r="P999" t="n">
         <v>2900</v>
       </c>
       <c r="Q999" t="n">
-        <v>84100</v>
+        <v>75400</v>
       </c>
     </row>
     <row r="1000">
@@ -45548,22 +45548,22 @@
         <v>0</v>
       </c>
       <c r="L1000" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M1000" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="N1000" t="n">
         <v>711.48</v>
       </c>
       <c r="O1000" t="n">
-        <v>31305.12</v>
+        <v>27036.24</v>
       </c>
       <c r="P1000" t="n">
         <v>2500</v>
       </c>
       <c r="Q1000" t="n">
-        <v>110000</v>
+        <v>95000</v>
       </c>
     </row>
     <row r="1001">
@@ -46425,10 +46425,10 @@
         <v>224</v>
       </c>
       <c r="N1018" t="n">
-        <v>665.32351302785</v>
+        <v>665.32352410996</v>
       </c>
       <c r="O1018" t="n">
-        <v>149032.4669182384</v>
+        <v>149032.469400631</v>
       </c>
       <c r="P1018" t="n">
         <v>2900</v>
@@ -46658,22 +46658,22 @@
         <v>0</v>
       </c>
       <c r="L1023" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1023" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="N1023" t="n">
         <v>1911</v>
       </c>
       <c r="O1023" t="n">
-        <v>42042</v>
+        <v>38220</v>
       </c>
       <c r="P1023" t="n">
         <v>4500</v>
       </c>
       <c r="Q1023" t="n">
-        <v>99000</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="1024">
@@ -46998,22 +46998,22 @@
         <v>0</v>
       </c>
       <c r="L1030" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1030" t="n">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="N1030" t="n">
         <v>426.1</v>
       </c>
       <c r="O1030" t="n">
-        <v>76271.90000000001</v>
+        <v>75419.7</v>
       </c>
       <c r="P1030" t="n">
         <v>2900</v>
       </c>
       <c r="Q1030" t="n">
-        <v>519100</v>
+        <v>513300</v>
       </c>
     </row>
     <row r="1031">
@@ -47047,22 +47047,22 @@
         <v>0</v>
       </c>
       <c r="L1031" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M1031" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="N1031" t="n">
-        <v>430.60997630332</v>
+        <v>430.60997624703</v>
       </c>
       <c r="O1031" t="n">
-        <v>23252.93872037928</v>
+        <v>21530.4988123515</v>
       </c>
       <c r="P1031" t="n">
         <v>2200</v>
       </c>
       <c r="Q1031" t="n">
-        <v>118800</v>
+        <v>110000</v>
       </c>
     </row>
     <row r="1032">
@@ -47145,22 +47145,22 @@
         <v>0</v>
       </c>
       <c r="L1033" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M1033" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="N1033" t="n">
-        <v>315.02694721826</v>
+        <v>315.02697707736</v>
       </c>
       <c r="O1033" t="n">
-        <v>8820.75452211128</v>
+        <v>7875.674426934001</v>
       </c>
       <c r="P1033" t="n">
         <v>2200</v>
       </c>
       <c r="Q1033" t="n">
-        <v>61600</v>
+        <v>55000</v>
       </c>
     </row>
     <row r="1034">
@@ -47625,10 +47625,10 @@
         <v>9</v>
       </c>
       <c r="N1044" t="n">
-        <v>6243.3531428571</v>
+        <v>6243.3531578947</v>
       </c>
       <c r="O1044" t="n">
-        <v>56190.1782857139</v>
+        <v>56190.1784210523</v>
       </c>
       <c r="P1044" t="n">
         <v>9900</v>
@@ -47851,10 +47851,10 @@
         <v>29</v>
       </c>
       <c r="N1049" t="n">
-        <v>2129.8331598174</v>
+        <v>2129.8331627057</v>
       </c>
       <c r="O1049" t="n">
-        <v>61765.1616347046</v>
+        <v>61765.1617184653</v>
       </c>
       <c r="P1049" t="n">
         <v>2700</v>
@@ -47971,22 +47971,22 @@
         <v>0</v>
       </c>
       <c r="L1052" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M1052" t="n">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="N1052" t="n">
         <v>3181.9</v>
       </c>
       <c r="O1052" t="n">
-        <v>315008.1</v>
+        <v>295916.7</v>
       </c>
       <c r="P1052" t="n">
         <v>5100</v>
       </c>
       <c r="Q1052" t="n">
-        <v>504900</v>
+        <v>474300</v>
       </c>
     </row>
     <row r="1053">
@@ -48150,10 +48150,10 @@
         <v>12</v>
       </c>
       <c r="N1056" t="n">
-        <v>15219.155232558</v>
+        <v>15219.155176471</v>
       </c>
       <c r="O1056" t="n">
-        <v>182629.862790696</v>
+        <v>182629.862117652</v>
       </c>
       <c r="P1056" t="n">
         <v>16000</v>
@@ -48472,10 +48472,10 @@
         <v>6</v>
       </c>
       <c r="N1063" t="n">
-        <v>22951.704911392</v>
+        <v>22951.704904943</v>
       </c>
       <c r="O1063" t="n">
-        <v>137710.229468352</v>
+        <v>137710.229429658</v>
       </c>
       <c r="P1063" t="n">
         <v>37900</v>
@@ -48567,10 +48567,10 @@
         <v>140</v>
       </c>
       <c r="N1065" t="n">
-        <v>705.52801204819</v>
+        <v>705.52800453515</v>
       </c>
       <c r="O1065" t="n">
-        <v>98773.9216867466</v>
+        <v>98773.920634921</v>
       </c>
       <c r="P1065" t="n">
         <v>1500</v>
@@ -48608,10 +48608,10 @@
         <v>28</v>
       </c>
       <c r="N1066" t="n">
-        <v>4985.4051948052</v>
+        <v>4985.4053097345</v>
       </c>
       <c r="O1066" t="n">
-        <v>139591.3454545456</v>
+        <v>139591.348672566</v>
       </c>
       <c r="P1066" t="n">
         <v>7900</v>
@@ -48710,10 +48710,10 @@
         <v>52</v>
       </c>
       <c r="N1068" t="n">
-        <v>1757.3205567452</v>
+        <v>1757.3205591398</v>
       </c>
       <c r="O1068" t="n">
-        <v>91380.66895075041</v>
+        <v>91380.6690752696</v>
       </c>
       <c r="P1068" t="n">
         <v>2000</v>
@@ -48750,22 +48750,22 @@
         <v>0</v>
       </c>
       <c r="L1069" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M1069" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="N1069" t="n">
         <v>1561.33</v>
       </c>
       <c r="O1069" t="n">
-        <v>49962.56</v>
+        <v>45278.57</v>
       </c>
       <c r="P1069" t="n">
         <v>2000</v>
       </c>
       <c r="Q1069" t="n">
-        <v>64000</v>
+        <v>58000</v>
       </c>
     </row>
     <row r="1070">
@@ -49673,22 +49673,22 @@
         <v>0</v>
       </c>
       <c r="L1089" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1089" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N1089" t="n">
         <v>3000</v>
       </c>
       <c r="O1089" t="n">
-        <v>36000</v>
+        <v>33000</v>
       </c>
       <c r="P1089" t="n">
         <v>3900</v>
       </c>
       <c r="Q1089" t="n">
-        <v>46800</v>
+        <v>42900</v>
       </c>
     </row>
     <row r="1090">
@@ -49719,22 +49719,22 @@
         <v>0</v>
       </c>
       <c r="L1090" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="M1090" t="n">
-        <v>350</v>
+        <v>150</v>
       </c>
       <c r="N1090" t="n">
-        <v>220.00629713546</v>
+        <v>220.00534867624</v>
       </c>
       <c r="O1090" t="n">
-        <v>77002.20399741099</v>
+        <v>33000.802301436</v>
       </c>
       <c r="P1090" t="n">
         <v>260</v>
       </c>
       <c r="Q1090" t="n">
-        <v>91000</v>
+        <v>39000</v>
       </c>
     </row>
     <row r="1091">
@@ -50685,22 +50685,22 @@
         <v>0</v>
       </c>
       <c r="L1111" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M1111" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="N1111" t="n">
         <v>1952.41</v>
       </c>
       <c r="O1111" t="n">
-        <v>66381.94</v>
+        <v>54667.48</v>
       </c>
       <c r="P1111" t="n">
         <v>2700</v>
       </c>
       <c r="Q1111" t="n">
-        <v>91800</v>
+        <v>75600</v>
       </c>
     </row>
     <row r="1112">
@@ -51145,22 +51145,22 @@
         <v>0</v>
       </c>
       <c r="L1121" t="n">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="M1121" t="n">
-        <v>264</v>
+        <v>115</v>
       </c>
       <c r="N1121" t="n">
         <v>7480</v>
       </c>
       <c r="O1121" t="n">
-        <v>1974720</v>
+        <v>860200</v>
       </c>
       <c r="P1121" t="n">
         <v>9500</v>
       </c>
       <c r="Q1121" t="n">
-        <v>2508000</v>
+        <v>1092500</v>
       </c>
     </row>
     <row r="1122">
@@ -51191,22 +51191,22 @@
         <v>0</v>
       </c>
       <c r="L1122" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M1122" t="n">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="N1122" t="n">
         <v>6336</v>
       </c>
       <c r="O1122" t="n">
-        <v>912384</v>
+        <v>893376</v>
       </c>
       <c r="P1122" t="n">
         <v>7500</v>
       </c>
       <c r="Q1122" t="n">
-        <v>1080000</v>
+        <v>1057500</v>
       </c>
     </row>
     <row r="1123">
@@ -51237,22 +51237,22 @@
         <v>0</v>
       </c>
       <c r="L1123" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M1123" t="n">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="N1123" t="n">
         <v>5280</v>
       </c>
       <c r="O1123" t="n">
-        <v>781440</v>
+        <v>686400</v>
       </c>
       <c r="P1123" t="n">
         <v>6900</v>
       </c>
       <c r="Q1123" t="n">
-        <v>1021200</v>
+        <v>897000</v>
       </c>
     </row>
     <row r="1124">
@@ -51283,22 +51283,22 @@
         <v>0</v>
       </c>
       <c r="L1124" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M1124" t="n">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="N1124" t="n">
         <v>5280</v>
       </c>
       <c r="O1124" t="n">
-        <v>792000</v>
+        <v>749760</v>
       </c>
       <c r="P1124" t="n">
         <v>6900</v>
       </c>
       <c r="Q1124" t="n">
-        <v>1035000</v>
+        <v>979800</v>
       </c>
     </row>
     <row r="1125">
@@ -51329,22 +51329,22 @@
         <v>0</v>
       </c>
       <c r="L1125" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M1125" t="n">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="N1125" t="n">
         <v>1584</v>
       </c>
       <c r="O1125" t="n">
-        <v>456192</v>
+        <v>451440</v>
       </c>
       <c r="P1125" t="n">
         <v>2000</v>
       </c>
       <c r="Q1125" t="n">
-        <v>576000</v>
+        <v>570000</v>
       </c>
     </row>
     <row r="1126">
@@ -51375,22 +51375,22 @@
         <v>0</v>
       </c>
       <c r="L1126" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M1126" t="n">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="N1126" t="n">
         <v>3872</v>
       </c>
       <c r="O1126" t="n">
-        <v>650496</v>
+        <v>638880</v>
       </c>
       <c r="P1126" t="n">
         <v>4900</v>
       </c>
       <c r="Q1126" t="n">
-        <v>823200</v>
+        <v>808500</v>
       </c>
     </row>
     <row r="1127">
@@ -51467,22 +51467,22 @@
         <v>0</v>
       </c>
       <c r="L1128" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1128" t="n">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="N1128" t="n">
         <v>4400</v>
       </c>
       <c r="O1128" t="n">
-        <v>739200</v>
+        <v>730400</v>
       </c>
       <c r="P1128" t="n">
         <v>5900</v>
       </c>
       <c r="Q1128" t="n">
-        <v>991200</v>
+        <v>979400</v>
       </c>
     </row>
     <row r="1129">
@@ -51513,22 +51513,22 @@
         <v>0</v>
       </c>
       <c r="L1129" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M1129" t="n">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="N1129" t="n">
         <v>3520</v>
       </c>
       <c r="O1129" t="n">
-        <v>675840</v>
+        <v>640640</v>
       </c>
       <c r="P1129" t="n">
         <v>4500</v>
       </c>
       <c r="Q1129" t="n">
-        <v>864000</v>
+        <v>819000</v>
       </c>
     </row>
     <row r="1130">
@@ -51651,22 +51651,22 @@
         <v>0</v>
       </c>
       <c r="L1132" t="n">
-        <v>0</v>
+        <v>489</v>
       </c>
       <c r="M1132" t="n">
-        <v>523</v>
+        <v>34</v>
       </c>
       <c r="N1132" t="n">
         <v>9240</v>
       </c>
       <c r="O1132" t="n">
-        <v>4832520</v>
+        <v>314160</v>
       </c>
       <c r="P1132" t="n">
         <v>11500</v>
       </c>
       <c r="Q1132" t="n">
-        <v>6014500</v>
+        <v>391000</v>
       </c>
     </row>
     <row r="1133">
@@ -51743,22 +51743,22 @@
         <v>0</v>
       </c>
       <c r="L1134" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M1134" t="n">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="N1134" t="n">
         <v>4576</v>
       </c>
       <c r="O1134" t="n">
-        <v>878592</v>
+        <v>837408</v>
       </c>
       <c r="P1134" t="n">
         <v>5900</v>
       </c>
       <c r="Q1134" t="n">
-        <v>1132800</v>
+        <v>1079700</v>
       </c>
     </row>
     <row r="1135">
@@ -51789,22 +51789,22 @@
         <v>0</v>
       </c>
       <c r="L1135" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M1135" t="n">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="N1135" t="n">
         <v>5280</v>
       </c>
       <c r="O1135" t="n">
-        <v>1578720</v>
+        <v>1547040</v>
       </c>
       <c r="P1135" t="n">
         <v>6900</v>
       </c>
       <c r="Q1135" t="n">
-        <v>2063100</v>
+        <v>2021700</v>
       </c>
     </row>
     <row r="1136">
@@ -52019,22 +52019,22 @@
         <v>0</v>
       </c>
       <c r="L1140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1140" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N1140" t="n">
         <v>25000</v>
       </c>
       <c r="O1140" t="n">
-        <v>225000</v>
+        <v>200000</v>
       </c>
       <c r="P1140" t="n">
         <v>30000</v>
       </c>
       <c r="Q1140" t="n">
-        <v>270000</v>
+        <v>240000</v>
       </c>
     </row>
     <row r="1141">
@@ -53052,17 +53052,17 @@
     <row r="1163">
       <c r="A1163" t="inlineStr">
         <is>
-          <t>MG16420</t>
+          <t>MG16348</t>
         </is>
       </c>
       <c r="C1163" t="inlineStr">
         <is>
-          <t>CAMION EXCAVADORA CON OPERARIO BOLSA MG16420</t>
+          <t>SET DE COCINA FOGON GDE MG16348</t>
         </is>
       </c>
       <c r="E1163" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I1163" t="inlineStr">
@@ -53071,39 +53071,39 @@
         </is>
       </c>
       <c r="J1163" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K1163" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L1163" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M1163" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="N1163" t="n">
-        <v>1043.65</v>
+        <v>910.85</v>
       </c>
       <c r="O1163" t="n">
-        <v>12523.8</v>
+        <v>6375.95</v>
       </c>
       <c r="P1163" t="n">
-        <v>12500</v>
+        <v>7900</v>
       </c>
       <c r="Q1163" t="n">
-        <v>150000</v>
+        <v>55300</v>
       </c>
     </row>
     <row r="1164">
       <c r="A1164" t="inlineStr">
         <is>
-          <t>MG16422</t>
+          <t>MG16420</t>
         </is>
       </c>
       <c r="C1164" t="inlineStr">
         <is>
-          <t>CAMION VOLQUETA BOLSA MG16422</t>
+          <t>CAMION EXCAVADORA CON OPERARIO BOLSA MG16420</t>
         </is>
       </c>
       <c r="E1164" t="inlineStr">
@@ -53117,7 +53117,7 @@
         </is>
       </c>
       <c r="J1164" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="K1164" t="n">
         <v>0</v>
@@ -53126,35 +53126,35 @@
         <v>0</v>
       </c>
       <c r="M1164" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="N1164" t="n">
-        <v>3949.25</v>
+        <v>1043.65</v>
       </c>
       <c r="O1164" t="n">
-        <v>15797</v>
+        <v>12523.8</v>
       </c>
       <c r="P1164" t="n">
         <v>12500</v>
       </c>
       <c r="Q1164" t="n">
-        <v>50000</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="1165">
       <c r="A1165" t="inlineStr">
         <is>
-          <t>MG19023</t>
+          <t>MG16422</t>
         </is>
       </c>
       <c r="C1165" t="inlineStr">
         <is>
-          <t>SET DE BELLEZA PARA NIÑAS CON SECADOR EN  BLISTER MG19023</t>
+          <t>CAMION VOLQUETA BOLSA MG16422</t>
         </is>
       </c>
       <c r="E1165" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I1165" t="inlineStr">
@@ -53163,7 +53163,7 @@
         </is>
       </c>
       <c r="J1165" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K1165" t="n">
         <v>0</v>
@@ -53172,35 +53172,35 @@
         <v>0</v>
       </c>
       <c r="M1165" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N1165" t="n">
-        <v>32.41</v>
+        <v>3949.25</v>
       </c>
       <c r="O1165" t="n">
-        <v>226.87</v>
+        <v>15797</v>
       </c>
       <c r="P1165" t="n">
-        <v>13500</v>
+        <v>12500</v>
       </c>
       <c r="Q1165" t="n">
-        <v>94500</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="1166">
       <c r="A1166" t="inlineStr">
         <is>
-          <t>MG20669</t>
+          <t>MG19023</t>
         </is>
       </c>
       <c r="C1166" t="inlineStr">
         <is>
-          <t>SET DE PLASTILINA PARA MOLDEAR EN BLISTER MG20669</t>
+          <t>SET DE BELLEZA PARA NIÑAS CON SECADOR EN  BLISTER MG19023</t>
         </is>
       </c>
       <c r="E1166" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I1166" t="inlineStr">
@@ -53209,7 +53209,7 @@
         </is>
       </c>
       <c r="J1166" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K1166" t="n">
         <v>0</v>
@@ -53218,30 +53218,30 @@
         <v>0</v>
       </c>
       <c r="M1166" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N1166" t="n">
-        <v>970.63171428571</v>
+        <v>32.41</v>
       </c>
       <c r="O1166" t="n">
-        <v>3882.52685714284</v>
+        <v>226.87</v>
       </c>
       <c r="P1166" t="n">
-        <v>7200</v>
+        <v>13500</v>
       </c>
       <c r="Q1166" t="n">
-        <v>28800</v>
+        <v>94500</v>
       </c>
     </row>
     <row r="1167">
       <c r="A1167" t="inlineStr">
         <is>
-          <t>MG20906</t>
+          <t>MG20669</t>
         </is>
       </c>
       <c r="C1167" t="inlineStr">
         <is>
-          <t>DINOSAURIO DIDACTICO EN BOLSA MG20906</t>
+          <t>SET DE PLASTILINA PARA MOLDEAR EN BLISTER MG20669</t>
         </is>
       </c>
       <c r="E1167" t="inlineStr">
@@ -53255,49 +53255,44 @@
         </is>
       </c>
       <c r="J1167" t="n">
+        <v>4</v>
+      </c>
+      <c r="K1167" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1167" t="n">
         <v>3</v>
       </c>
-      <c r="K1167" t="n">
-        <v>0</v>
-      </c>
-      <c r="L1167" t="n">
-        <v>0</v>
-      </c>
       <c r="M1167" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N1167" t="n">
-        <v>1482.84</v>
+        <v>970.631875</v>
       </c>
       <c r="O1167" t="n">
-        <v>4448.52</v>
+        <v>970.631875</v>
       </c>
       <c r="P1167" t="n">
-        <v>6500</v>
+        <v>7200</v>
       </c>
       <c r="Q1167" t="n">
-        <v>19500</v>
+        <v>7200</v>
       </c>
     </row>
     <row r="1168">
       <c r="A1168" t="inlineStr">
         <is>
-          <t>MG22220</t>
-        </is>
-      </c>
-      <c r="B1168" t="inlineStr">
-        <is>
-          <t>MG22220</t>
+          <t>MG20906</t>
         </is>
       </c>
       <c r="C1168" t="inlineStr">
         <is>
-          <t>DINOSAURIO CON SOMBRERO MG22220</t>
+          <t>DINOSAURIO DIDACTICO EN BOLSA MG20906</t>
         </is>
       </c>
       <c r="E1168" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I1168" t="inlineStr">
@@ -53306,7 +53301,7 @@
         </is>
       </c>
       <c r="J1168" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K1168" t="n">
         <v>0</v>
@@ -53315,35 +53310,40 @@
         <v>0</v>
       </c>
       <c r="M1168" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N1168" t="n">
-        <v>4662.9</v>
+        <v>1482.84</v>
       </c>
       <c r="O1168" t="n">
-        <v>4662.9</v>
+        <v>4448.52</v>
       </c>
       <c r="P1168" t="n">
-        <v>22900</v>
+        <v>6500</v>
       </c>
       <c r="Q1168" t="n">
-        <v>22900</v>
+        <v>19500</v>
       </c>
     </row>
     <row r="1169">
       <c r="A1169" t="inlineStr">
         <is>
-          <t>MG22320</t>
+          <t>MG22220</t>
+        </is>
+      </c>
+      <c r="B1169" t="inlineStr">
+        <is>
+          <t>MG22220</t>
         </is>
       </c>
       <c r="C1169" t="inlineStr">
         <is>
-          <t>CABALLO DIDACTICO DESARMABLE PQÑ MG22320</t>
+          <t>DINOSAURIO CON SOMBRERO MG22220</t>
         </is>
       </c>
       <c r="E1169" t="inlineStr">
         <is>
-          <t>DIDACTICOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I1169" t="inlineStr">
@@ -53352,7 +53352,7 @@
         </is>
       </c>
       <c r="J1169" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="K1169" t="n">
         <v>0</v>
@@ -53361,40 +53361,35 @@
         <v>0</v>
       </c>
       <c r="M1169" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="N1169" t="n">
-        <v>1129.14</v>
+        <v>4662.9</v>
       </c>
       <c r="O1169" t="n">
-        <v>31615.92</v>
+        <v>4662.9</v>
       </c>
       <c r="P1169" t="n">
-        <v>6900</v>
+        <v>22900</v>
       </c>
       <c r="Q1169" t="n">
-        <v>193200</v>
+        <v>22900</v>
       </c>
     </row>
     <row r="1170">
       <c r="A1170" t="inlineStr">
         <is>
-          <t>MG22435</t>
-        </is>
-      </c>
-      <c r="B1170" t="inlineStr">
-        <is>
-          <t>MG22435</t>
+          <t>MG22320</t>
         </is>
       </c>
       <c r="C1170" t="inlineStr">
         <is>
-          <t>SONAJERO PERRITO BOLSA PQÑ MG22435</t>
+          <t>CABALLO DIDACTICO DESARMABLE PQÑ MG22320</t>
         </is>
       </c>
       <c r="E1170" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>DIDACTICOS</t>
         </is>
       </c>
       <c r="I1170" t="inlineStr">
@@ -53403,7 +53398,7 @@
         </is>
       </c>
       <c r="J1170" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="K1170" t="n">
         <v>0</v>
@@ -53412,35 +53407,40 @@
         <v>0</v>
       </c>
       <c r="M1170" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="N1170" t="n">
-        <v>1236.3</v>
+        <v>1129.14</v>
       </c>
       <c r="O1170" t="n">
-        <v>56869.8</v>
+        <v>31615.92</v>
       </c>
       <c r="P1170" t="n">
-        <v>2300</v>
+        <v>6900</v>
       </c>
       <c r="Q1170" t="n">
-        <v>105800</v>
+        <v>193200</v>
       </c>
     </row>
     <row r="1171">
       <c r="A1171" t="inlineStr">
         <is>
-          <t>MG22440</t>
+          <t>MG22435</t>
+        </is>
+      </c>
+      <c r="B1171" t="inlineStr">
+        <is>
+          <t>MG22435</t>
         </is>
       </c>
       <c r="C1171" t="inlineStr">
         <is>
-          <t>SONAJERO CON CUERDA DISEÑO PEZ EN BLISTER MG22440</t>
+          <t>SONAJERO PERRITO BOLSA PQÑ MG22435</t>
         </is>
       </c>
       <c r="E1171" t="inlineStr">
         <is>
-          <t>MUSICALES</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I1171" t="inlineStr">
@@ -53449,7 +53449,7 @@
         </is>
       </c>
       <c r="J1171" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="K1171" t="n">
         <v>0</v>
@@ -53458,35 +53458,35 @@
         <v>0</v>
       </c>
       <c r="M1171" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="N1171" t="n">
-        <v>8174.05</v>
+        <v>1236.3</v>
       </c>
       <c r="O1171" t="n">
-        <v>8174.05</v>
+        <v>56869.8</v>
       </c>
       <c r="P1171" t="n">
-        <v>8900</v>
+        <v>2300</v>
       </c>
       <c r="Q1171" t="n">
-        <v>8900</v>
+        <v>105800</v>
       </c>
     </row>
     <row r="1172">
       <c r="A1172" t="inlineStr">
         <is>
-          <t>MG26010</t>
+          <t>MG22440</t>
         </is>
       </c>
       <c r="C1172" t="inlineStr">
         <is>
-          <t>SET BELLEZA CON ACCESORIOS EMPAQUE BOLSO MG26010</t>
+          <t>SONAJERO CON CUERDA DISEÑO PEZ EN BLISTER MG22440</t>
         </is>
       </c>
       <c r="E1172" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>MUSICALES</t>
         </is>
       </c>
       <c r="I1172" t="inlineStr">
@@ -53495,7 +53495,7 @@
         </is>
       </c>
       <c r="J1172" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K1172" t="n">
         <v>0</v>
@@ -53504,35 +53504,35 @@
         <v>0</v>
       </c>
       <c r="M1172" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N1172" t="n">
-        <v>11433.53</v>
+        <v>8174.05</v>
       </c>
       <c r="O1172" t="n">
-        <v>68601.18000000001</v>
+        <v>8174.05</v>
       </c>
       <c r="P1172" t="n">
-        <v>15000</v>
+        <v>8900</v>
       </c>
       <c r="Q1172" t="n">
-        <v>90000</v>
+        <v>8900</v>
       </c>
     </row>
     <row r="1173">
       <c r="A1173" t="inlineStr">
         <is>
-          <t>MG26196</t>
+          <t>MG26010</t>
         </is>
       </c>
       <c r="C1173" t="inlineStr">
         <is>
-          <t>SET PISTA DE CONSTRUCCION Y CARROS MG26196</t>
+          <t>SET BELLEZA CON ACCESORIOS EMPAQUE BOLSO MG26010</t>
         </is>
       </c>
       <c r="E1173" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I1173" t="inlineStr">
@@ -53541,7 +53541,7 @@
         </is>
       </c>
       <c r="J1173" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K1173" t="n">
         <v>0</v>
@@ -53550,35 +53550,35 @@
         <v>0</v>
       </c>
       <c r="M1173" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N1173" t="n">
-        <v>6272.36</v>
+        <v>11433.53</v>
       </c>
       <c r="O1173" t="n">
-        <v>31361.8</v>
+        <v>68601.18000000001</v>
       </c>
       <c r="P1173" t="n">
-        <v>10500</v>
+        <v>15000</v>
       </c>
       <c r="Q1173" t="n">
-        <v>52500</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="1174">
       <c r="A1174" t="inlineStr">
         <is>
-          <t>MG27667</t>
+          <t>MG26196</t>
         </is>
       </c>
       <c r="C1174" t="inlineStr">
         <is>
-          <t>MUÑECA ARTICULADA VESTIDO GALA CON BOLSO MG27667</t>
+          <t>SET PISTA DE CONSTRUCCION Y CARROS MG26196</t>
         </is>
       </c>
       <c r="E1174" t="inlineStr">
         <is>
-          <t>MUÑECA</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I1174" t="inlineStr">
@@ -53587,7 +53587,7 @@
         </is>
       </c>
       <c r="J1174" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K1174" t="n">
         <v>0</v>
@@ -53596,30 +53596,30 @@
         <v>0</v>
       </c>
       <c r="M1174" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N1174" t="n">
-        <v>17846.15</v>
+        <v>6272.36</v>
       </c>
       <c r="O1174" t="n">
-        <v>17846.15</v>
+        <v>31361.8</v>
       </c>
       <c r="P1174" t="n">
-        <v>23200</v>
+        <v>10500</v>
       </c>
       <c r="Q1174" t="n">
-        <v>23200</v>
+        <v>52500</v>
       </c>
     </row>
     <row r="1175">
       <c r="A1175" t="inlineStr">
         <is>
-          <t>MG27682</t>
+          <t>MG27667</t>
         </is>
       </c>
       <c r="C1175" t="inlineStr">
         <is>
-          <t>MUÑECA ARTICULADA CORONA VESTIDO GALA MG27682</t>
+          <t>MUÑECA ARTICULADA VESTIDO GALA CON BOLSO MG27667</t>
         </is>
       </c>
       <c r="E1175" t="inlineStr">
@@ -53633,7 +53633,7 @@
         </is>
       </c>
       <c r="J1175" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K1175" t="n">
         <v>0</v>
@@ -53642,40 +53642,35 @@
         <v>0</v>
       </c>
       <c r="M1175" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N1175" t="n">
-        <v>19230.86</v>
+        <v>17846.15</v>
       </c>
       <c r="O1175" t="n">
-        <v>76923.44</v>
+        <v>17846.15</v>
       </c>
       <c r="P1175" t="n">
         <v>23200</v>
       </c>
       <c r="Q1175" t="n">
-        <v>92800</v>
+        <v>23200</v>
       </c>
     </row>
     <row r="1176">
       <c r="A1176" t="inlineStr">
         <is>
-          <t>MG29806</t>
-        </is>
-      </c>
-      <c r="B1176" t="inlineStr">
-        <is>
-          <t>MG29806</t>
+          <t>MG27682</t>
         </is>
       </c>
       <c r="C1176" t="inlineStr">
         <is>
-          <t>DINOSAURIO CON HUEVO MG29806</t>
+          <t>MUÑECA ARTICULADA CORONA VESTIDO GALA MG27682</t>
         </is>
       </c>
       <c r="E1176" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>MUÑECA</t>
         </is>
       </c>
       <c r="I1176" t="inlineStr">
@@ -53684,7 +53679,7 @@
         </is>
       </c>
       <c r="J1176" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K1176" t="n">
         <v>0</v>
@@ -53693,40 +53688,40 @@
         <v>0</v>
       </c>
       <c r="M1176" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="N1176" t="n">
-        <v>10667.9</v>
+        <v>19230.86</v>
       </c>
       <c r="O1176" t="n">
-        <v>96011.09999999999</v>
+        <v>76923.44</v>
       </c>
       <c r="P1176" t="n">
-        <v>29900</v>
+        <v>23200</v>
       </c>
       <c r="Q1176" t="n">
-        <v>269100</v>
+        <v>92800</v>
       </c>
     </row>
     <row r="1177">
       <c r="A1177" t="inlineStr">
         <is>
-          <t>MG30151</t>
+          <t>MG29806</t>
         </is>
       </c>
       <c r="B1177" t="inlineStr">
         <is>
-          <t>MG30151</t>
+          <t>MG29806</t>
         </is>
       </c>
       <c r="C1177" t="inlineStr">
         <is>
-          <t>DIDACTICO PIANO MUSICAL CARRITO MG30151</t>
+          <t>DINOSAURIO CON HUEVO MG29806</t>
         </is>
       </c>
       <c r="E1177" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I1177" t="inlineStr">
@@ -53735,7 +53730,7 @@
         </is>
       </c>
       <c r="J1177" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K1177" t="n">
         <v>0</v>
@@ -53744,35 +53739,40 @@
         <v>0</v>
       </c>
       <c r="M1177" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N1177" t="n">
-        <v>15452.21</v>
+        <v>10667.9</v>
       </c>
       <c r="O1177" t="n">
-        <v>108165.47</v>
+        <v>96011.09999999999</v>
       </c>
       <c r="P1177" t="n">
-        <v>36500</v>
+        <v>29900</v>
       </c>
       <c r="Q1177" t="n">
-        <v>255500</v>
+        <v>269100</v>
       </c>
     </row>
     <row r="1178">
       <c r="A1178" t="inlineStr">
         <is>
-          <t>MG32390</t>
+          <t>MG30151</t>
+        </is>
+      </c>
+      <c r="B1178" t="inlineStr">
+        <is>
+          <t>MG30151</t>
         </is>
       </c>
       <c r="C1178" t="inlineStr">
         <is>
-          <t>CARRO PATRULLA RECARGABLE MG32390</t>
+          <t>DIDACTICO PIANO MUSICAL CARRITO MG30151</t>
         </is>
       </c>
       <c r="E1178" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I1178" t="inlineStr">
@@ -53781,7 +53781,7 @@
         </is>
       </c>
       <c r="J1178" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K1178" t="n">
         <v>0</v>
@@ -53790,40 +53790,35 @@
         <v>0</v>
       </c>
       <c r="M1178" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="N1178" t="n">
-        <v>17399.33</v>
+        <v>15452.21</v>
       </c>
       <c r="O1178" t="n">
-        <v>17399.33</v>
+        <v>108165.47</v>
       </c>
       <c r="P1178" t="n">
-        <v>39000</v>
+        <v>36500</v>
       </c>
       <c r="Q1178" t="n">
-        <v>39000</v>
+        <v>255500</v>
       </c>
     </row>
     <row r="1179">
       <c r="A1179" t="inlineStr">
         <is>
-          <t>MG33219</t>
-        </is>
-      </c>
-      <c r="B1179" t="inlineStr">
-        <is>
-          <t>MG33219</t>
+          <t>MG32390</t>
         </is>
       </c>
       <c r="C1179" t="inlineStr">
         <is>
-          <t>BINOCULARES CAMUFLADOS MG33219</t>
+          <t>CARRO PATRULLA RECARGABLE MG32390</t>
         </is>
       </c>
       <c r="E1179" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I1179" t="inlineStr">
@@ -53832,7 +53827,7 @@
         </is>
       </c>
       <c r="J1179" t="n">
-        <v>77</v>
+        <v>1</v>
       </c>
       <c r="K1179" t="n">
         <v>0</v>
@@ -53841,35 +53836,40 @@
         <v>0</v>
       </c>
       <c r="M1179" t="n">
-        <v>77</v>
+        <v>1</v>
       </c>
       <c r="N1179" t="n">
-        <v>751.45</v>
+        <v>17399.33</v>
       </c>
       <c r="O1179" t="n">
-        <v>57861.65</v>
+        <v>17399.33</v>
       </c>
       <c r="P1179" t="n">
-        <v>2500</v>
+        <v>39000</v>
       </c>
       <c r="Q1179" t="n">
-        <v>192500</v>
+        <v>39000</v>
       </c>
     </row>
     <row r="1180">
       <c r="A1180" t="inlineStr">
         <is>
-          <t>MG40210</t>
+          <t>MG33219</t>
+        </is>
+      </c>
+      <c r="B1180" t="inlineStr">
+        <is>
+          <t>MG33219</t>
         </is>
       </c>
       <c r="C1180" t="inlineStr">
         <is>
-          <t>SONAJERO OSO MG40210</t>
+          <t>BINOCULARES CAMUFLADOS MG33219</t>
         </is>
       </c>
       <c r="E1180" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I1180" t="inlineStr">
@@ -53878,7 +53878,7 @@
         </is>
       </c>
       <c r="J1180" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K1180" t="n">
         <v>0</v>
@@ -53887,40 +53887,35 @@
         <v>0</v>
       </c>
       <c r="M1180" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="N1180" t="n">
-        <v>571.87</v>
+        <v>751.45</v>
       </c>
       <c r="O1180" t="n">
-        <v>43462.12</v>
+        <v>57861.65</v>
       </c>
       <c r="P1180" t="n">
         <v>2500</v>
       </c>
       <c r="Q1180" t="n">
-        <v>190000</v>
+        <v>192500</v>
       </c>
     </row>
     <row r="1181">
       <c r="A1181" t="inlineStr">
         <is>
-          <t>MG40269</t>
-        </is>
-      </c>
-      <c r="B1181" t="inlineStr">
-        <is>
-          <t>MG40269</t>
+          <t>MG40210</t>
         </is>
       </c>
       <c r="C1181" t="inlineStr">
         <is>
-          <t>SONAJERO BOLSA ELEFANTE MG40269</t>
+          <t>SONAJERO OSO MG40210</t>
         </is>
       </c>
       <c r="E1181" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I1181" t="inlineStr">
@@ -53929,44 +53924,49 @@
         </is>
       </c>
       <c r="J1181" t="n">
-        <v>34</v>
+        <v>76</v>
       </c>
       <c r="K1181" t="n">
         <v>0</v>
       </c>
       <c r="L1181" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M1181" t="n">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="N1181" t="n">
-        <v>2432.1346938776</v>
+        <v>571.87</v>
       </c>
       <c r="O1181" t="n">
-        <v>82692.5795918384</v>
+        <v>40030.9</v>
       </c>
       <c r="P1181" t="n">
-        <v>4500</v>
+        <v>2500</v>
       </c>
       <c r="Q1181" t="n">
-        <v>153000</v>
+        <v>175000</v>
       </c>
     </row>
     <row r="1182">
       <c r="A1182" t="inlineStr">
         <is>
-          <t>MG40334</t>
+          <t>MG40269</t>
+        </is>
+      </c>
+      <c r="B1182" t="inlineStr">
+        <is>
+          <t>MG40269</t>
         </is>
       </c>
       <c r="C1182" t="inlineStr">
         <is>
-          <t>MARIMBA 4 NOTAS MG40334</t>
+          <t>SONAJERO BOLSA ELEFANTE MG40269</t>
         </is>
       </c>
       <c r="E1182" t="inlineStr">
         <is>
-          <t>MUSICALES</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I1182" t="inlineStr">
@@ -53975,7 +53975,7 @@
         </is>
       </c>
       <c r="J1182" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="K1182" t="n">
         <v>0</v>
@@ -53984,30 +53984,30 @@
         <v>0</v>
       </c>
       <c r="M1182" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="N1182" t="n">
-        <v>227.41601620029</v>
+        <v>2432.1346938776</v>
       </c>
       <c r="O1182" t="n">
-        <v>4093.48829160522</v>
+        <v>82692.5795918384</v>
       </c>
       <c r="P1182" t="n">
-        <v>1200</v>
+        <v>4500</v>
       </c>
       <c r="Q1182" t="n">
-        <v>21600</v>
+        <v>153000</v>
       </c>
     </row>
     <row r="1183">
       <c r="A1183" t="inlineStr">
         <is>
-          <t>MG40415</t>
+          <t>MG40334</t>
         </is>
       </c>
       <c r="C1183" t="inlineStr">
         <is>
-          <t>TELEFONO AVION MG40415</t>
+          <t>MARIMBA 4 NOTAS MG40334</t>
         </is>
       </c>
       <c r="E1183" t="inlineStr">
@@ -54021,7 +54021,7 @@
         </is>
       </c>
       <c r="J1183" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="K1183" t="n">
         <v>0</v>
@@ -54030,35 +54030,35 @@
         <v>0</v>
       </c>
       <c r="M1183" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="N1183" t="n">
-        <v>13308.19</v>
+        <v>227.41601620029</v>
       </c>
       <c r="O1183" t="n">
-        <v>13308.19</v>
+        <v>4093.48829160522</v>
       </c>
       <c r="P1183" t="n">
-        <v>34600</v>
+        <v>1200</v>
       </c>
       <c r="Q1183" t="n">
-        <v>34600</v>
+        <v>21600</v>
       </c>
     </row>
     <row r="1184">
       <c r="A1184" t="inlineStr">
         <is>
-          <t>MG40717</t>
+          <t>MG40415</t>
         </is>
       </c>
       <c r="C1184" t="inlineStr">
         <is>
-          <t>COMPUTADOR PORTATIL GAME MG40717</t>
+          <t>TELEFONO AVION MG40415</t>
         </is>
       </c>
       <c r="E1184" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>MUSICALES</t>
         </is>
       </c>
       <c r="I1184" t="inlineStr">
@@ -54079,32 +54079,27 @@
         <v>1</v>
       </c>
       <c r="N1184" t="n">
-        <v>16115.88</v>
+        <v>13308.19</v>
       </c>
       <c r="O1184" t="n">
-        <v>16115.88</v>
+        <v>13308.19</v>
       </c>
       <c r="P1184" t="n">
-        <v>41900</v>
+        <v>34600</v>
       </c>
       <c r="Q1184" t="n">
-        <v>41900</v>
+        <v>34600</v>
       </c>
     </row>
     <row r="1185">
       <c r="A1185" t="inlineStr">
         <is>
-          <t>MG40720</t>
-        </is>
-      </c>
-      <c r="B1185" t="inlineStr">
-        <is>
-          <t>MG40720</t>
+          <t>MG40717</t>
         </is>
       </c>
       <c r="C1185" t="inlineStr">
         <is>
-          <t>MAQUINA DE COSER MINI MG40720</t>
+          <t>COMPUTADOR PORTATIL GAME MG40717</t>
         </is>
       </c>
       <c r="E1185" t="inlineStr">
@@ -54118,7 +54113,7 @@
         </is>
       </c>
       <c r="J1185" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K1185" t="n">
         <v>0</v>
@@ -54127,40 +54122,40 @@
         <v>0</v>
       </c>
       <c r="M1185" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N1185" t="n">
-        <v>9917.040000000001</v>
+        <v>16115.88</v>
       </c>
       <c r="O1185" t="n">
-        <v>99170.40000000001</v>
+        <v>16115.88</v>
       </c>
       <c r="P1185" t="n">
-        <v>15900</v>
+        <v>41900</v>
       </c>
       <c r="Q1185" t="n">
-        <v>159000</v>
+        <v>41900</v>
       </c>
     </row>
     <row r="1186">
       <c r="A1186" t="inlineStr">
         <is>
-          <t>MG40952</t>
+          <t>MG40720</t>
         </is>
       </c>
       <c r="B1186" t="inlineStr">
         <is>
-          <t>MG40952</t>
+          <t>MG40720</t>
         </is>
       </c>
       <c r="C1186" t="inlineStr">
         <is>
-          <t>CAMIONETA BLACK MG40952</t>
+          <t>MAQUINA DE COSER MINI MG40720</t>
         </is>
       </c>
       <c r="E1186" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I1186" t="inlineStr">
@@ -54169,7 +54164,7 @@
         </is>
       </c>
       <c r="J1186" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="K1186" t="n">
         <v>0</v>
@@ -54178,35 +54173,40 @@
         <v>0</v>
       </c>
       <c r="M1186" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="N1186" t="n">
-        <v>38043.57</v>
+        <v>9917.040000000001</v>
       </c>
       <c r="O1186" t="n">
-        <v>38043.57</v>
+        <v>99170.40000000001</v>
       </c>
       <c r="P1186" t="n">
-        <v>70900</v>
+        <v>15900</v>
       </c>
       <c r="Q1186" t="n">
-        <v>70900</v>
+        <v>159000</v>
       </c>
     </row>
     <row r="1187">
       <c r="A1187" t="inlineStr">
         <is>
-          <t>MG41589</t>
+          <t>MG40952</t>
+        </is>
+      </c>
+      <c r="B1187" t="inlineStr">
+        <is>
+          <t>MG40952</t>
         </is>
       </c>
       <c r="C1187" t="inlineStr">
         <is>
-          <t>MUÑECA ODONTOLOGA MG41589</t>
+          <t>CAMIONETA BLACK MG40952</t>
         </is>
       </c>
       <c r="E1187" t="inlineStr">
         <is>
-          <t>MUÑECA</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I1187" t="inlineStr">
@@ -54227,32 +54227,32 @@
         <v>1</v>
       </c>
       <c r="N1187" t="n">
-        <v>5103.23</v>
+        <v>38043.57</v>
       </c>
       <c r="O1187" t="n">
-        <v>5103.23</v>
+        <v>38043.57</v>
       </c>
       <c r="P1187" t="n">
-        <v>19900</v>
+        <v>70900</v>
       </c>
       <c r="Q1187" t="n">
-        <v>19900</v>
+        <v>70900</v>
       </c>
     </row>
     <row r="1188">
       <c r="A1188" t="inlineStr">
         <is>
-          <t>MGB024</t>
+          <t>MG41589</t>
         </is>
       </c>
       <c r="C1188" t="inlineStr">
         <is>
-          <t>DINOSAURIO LUZ Y SONIDO HUEVO MG22277</t>
+          <t>MUÑECA ODONTOLOGA MG41589</t>
         </is>
       </c>
       <c r="E1188" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>MUÑECA</t>
         </is>
       </c>
       <c r="I1188" t="inlineStr">
@@ -54273,27 +54273,27 @@
         <v>1</v>
       </c>
       <c r="N1188" t="n">
-        <v>45769.23</v>
+        <v>5103.23</v>
       </c>
       <c r="O1188" t="n">
-        <v>45769.23</v>
+        <v>5103.23</v>
       </c>
       <c r="P1188" t="n">
-        <v>59500</v>
+        <v>19900</v>
       </c>
       <c r="Q1188" t="n">
-        <v>59500</v>
+        <v>19900</v>
       </c>
     </row>
     <row r="1189">
       <c r="A1189" t="inlineStr">
         <is>
-          <t>MGB028</t>
+          <t>MGB024</t>
         </is>
       </c>
       <c r="C1189" t="inlineStr">
         <is>
-          <t>CARRO DE BASURA BOLSA MG26016</t>
+          <t>DINOSAURIO LUZ Y SONIDO HUEVO MG22277</t>
         </is>
       </c>
       <c r="E1189" t="inlineStr">
@@ -54319,27 +54319,27 @@
         <v>1</v>
       </c>
       <c r="N1189" t="n">
-        <v>14320</v>
+        <v>45769.23</v>
       </c>
       <c r="O1189" t="n">
-        <v>14320</v>
+        <v>45769.23</v>
       </c>
       <c r="P1189" t="n">
-        <v>17900</v>
+        <v>59500</v>
       </c>
       <c r="Q1189" t="n">
-        <v>17900</v>
+        <v>59500</v>
       </c>
     </row>
     <row r="1190">
       <c r="A1190" t="inlineStr">
         <is>
-          <t>MGB033</t>
+          <t>MGB028</t>
         </is>
       </c>
       <c r="C1190" t="inlineStr">
         <is>
-          <t>VARA LUZ DEDITOS PT21040</t>
+          <t>CARRO DE BASURA BOLSA MG26016</t>
         </is>
       </c>
       <c r="E1190" t="inlineStr">
@@ -54353,7 +54353,7 @@
         </is>
       </c>
       <c r="J1190" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K1190" t="n">
         <v>0</v>
@@ -54362,30 +54362,30 @@
         <v>0</v>
       </c>
       <c r="M1190" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N1190" t="n">
-        <v>2400</v>
+        <v>14320</v>
       </c>
       <c r="O1190" t="n">
-        <v>4800</v>
+        <v>14320</v>
       </c>
       <c r="P1190" t="n">
-        <v>3000</v>
+        <v>17900</v>
       </c>
       <c r="Q1190" t="n">
-        <v>6000</v>
+        <v>17900</v>
       </c>
     </row>
     <row r="1191">
       <c r="A1191" t="inlineStr">
         <is>
-          <t>MGB035</t>
+          <t>MGB033</t>
         </is>
       </c>
       <c r="C1191" t="inlineStr">
         <is>
-          <t>SOMBRILLA FRUTAS CON FILTRO PT21531SK</t>
+          <t>VARA LUZ DEDITOS PT21040</t>
         </is>
       </c>
       <c r="E1191" t="inlineStr">
@@ -54399,7 +54399,7 @@
         </is>
       </c>
       <c r="J1191" t="n">
-        <v>74</v>
+        <v>2</v>
       </c>
       <c r="K1191" t="n">
         <v>0</v>
@@ -54408,30 +54408,30 @@
         <v>0</v>
       </c>
       <c r="M1191" t="n">
-        <v>74</v>
+        <v>2</v>
       </c>
       <c r="N1191" t="n">
-        <v>11600</v>
+        <v>2400</v>
       </c>
       <c r="O1191" t="n">
-        <v>858400</v>
+        <v>4800</v>
       </c>
       <c r="P1191" t="n">
-        <v>11700</v>
+        <v>3000</v>
       </c>
       <c r="Q1191" t="n">
-        <v>865800</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="1192">
       <c r="A1192" t="inlineStr">
         <is>
-          <t>MJC-558</t>
+          <t>MGB035</t>
         </is>
       </c>
       <c r="C1192" t="inlineStr">
         <is>
-          <t>MOORAL ESCOLAR TONOS PASTELES 20cm MJC-558</t>
+          <t>SOMBRILLA FRUTAS CON FILTRO PT21531SK</t>
         </is>
       </c>
       <c r="E1192" t="inlineStr">
@@ -54445,7 +54445,7 @@
         </is>
       </c>
       <c r="J1192" t="n">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="K1192" t="n">
         <v>0</v>
@@ -54454,30 +54454,30 @@
         <v>0</v>
       </c>
       <c r="M1192" t="n">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="N1192" t="n">
-        <v>40500</v>
+        <v>11600</v>
       </c>
       <c r="O1192" t="n">
-        <v>729000</v>
+        <v>858400</v>
       </c>
       <c r="P1192" t="n">
-        <v>48600</v>
+        <v>11700</v>
       </c>
       <c r="Q1192" t="n">
-        <v>874800</v>
+        <v>865800</v>
       </c>
     </row>
     <row r="1193">
       <c r="A1193" t="inlineStr">
         <is>
-          <t>MJC-558-1</t>
+          <t>MJC-558</t>
         </is>
       </c>
       <c r="C1193" t="inlineStr">
         <is>
-          <t>MORRAL ESCOLAR 20cm MOTIVO ESPACIAL DEPORTE MJ-558-1</t>
+          <t>MOORAL ESCOLAR TONOS PASTELES 20cm MJC-558</t>
         </is>
       </c>
       <c r="E1193" t="inlineStr">
@@ -54491,7 +54491,7 @@
         </is>
       </c>
       <c r="J1193" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K1193" t="n">
         <v>0</v>
@@ -54500,30 +54500,30 @@
         <v>0</v>
       </c>
       <c r="M1193" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="N1193" t="n">
         <v>40500</v>
       </c>
       <c r="O1193" t="n">
-        <v>607500</v>
+        <v>729000</v>
       </c>
       <c r="P1193" t="n">
         <v>48600</v>
       </c>
       <c r="Q1193" t="n">
-        <v>729000</v>
+        <v>874800</v>
       </c>
     </row>
     <row r="1194">
       <c r="A1194" t="inlineStr">
         <is>
-          <t>MR020-LJ</t>
+          <t>MJC-558-1</t>
         </is>
       </c>
       <c r="C1194" t="inlineStr">
         <is>
-          <t>MORRAL ZOOLOGICO PELUCHE 5190</t>
+          <t>MORRAL ESCOLAR 20cm MOTIVO ESPACIAL DEPORTE MJ-558-1</t>
         </is>
       </c>
       <c r="E1194" t="inlineStr">
@@ -54537,7 +54537,7 @@
         </is>
       </c>
       <c r="J1194" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K1194" t="n">
         <v>0</v>
@@ -54546,30 +54546,30 @@
         <v>0</v>
       </c>
       <c r="M1194" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N1194" t="n">
-        <v>407.61125</v>
+        <v>40500</v>
       </c>
       <c r="O1194" t="n">
-        <v>6521.78</v>
+        <v>607500</v>
       </c>
       <c r="P1194" t="n">
-        <v>22900</v>
+        <v>48600</v>
       </c>
       <c r="Q1194" t="n">
-        <v>366400</v>
+        <v>729000</v>
       </c>
     </row>
     <row r="1195">
       <c r="A1195" t="inlineStr">
         <is>
-          <t>MR042</t>
+          <t>MR020-LJ</t>
         </is>
       </c>
       <c r="C1195" t="inlineStr">
         <is>
-          <t>MORRAL ANIMALES STD 002-003-02-0230-</t>
+          <t>MORRAL ZOOLOGICO PELUCHE 5190</t>
         </is>
       </c>
       <c r="E1195" t="inlineStr">
@@ -54583,7 +54583,7 @@
         </is>
       </c>
       <c r="J1195" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="K1195" t="n">
         <v>0</v>
@@ -54592,39 +54592,44 @@
         <v>0</v>
       </c>
       <c r="M1195" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="N1195" t="n">
-        <v>23920</v>
+        <v>407.61125</v>
       </c>
       <c r="O1195" t="n">
-        <v>47840</v>
+        <v>6521.78</v>
       </c>
       <c r="P1195" t="n">
-        <v>29900</v>
+        <v>22900</v>
       </c>
       <c r="Q1195" t="n">
-        <v>59800</v>
+        <v>366400</v>
       </c>
     </row>
     <row r="1196">
       <c r="A1196" t="inlineStr">
         <is>
-          <t>MT4004</t>
+          <t>MR042</t>
         </is>
       </c>
       <c r="C1196" t="inlineStr">
         <is>
-          <t>MT4004 BLADE PLAYA JUEGO</t>
+          <t>MORRAL ANIMALES STD 002-003-02-0230-</t>
+        </is>
+      </c>
+      <c r="E1196" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I1196" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J1196" t="n">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="K1196" t="n">
         <v>0</v>
@@ -54633,76 +54638,71 @@
         <v>0</v>
       </c>
       <c r="M1196" t="n">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="N1196" t="n">
-        <v>2058.92</v>
+        <v>23920</v>
       </c>
       <c r="O1196" t="n">
-        <v>111181.68</v>
+        <v>47840</v>
       </c>
       <c r="P1196" t="n">
-        <v>2500</v>
+        <v>29900</v>
       </c>
       <c r="Q1196" t="n">
-        <v>135000</v>
+        <v>59800</v>
       </c>
     </row>
     <row r="1197">
       <c r="A1197" t="inlineStr">
         <is>
-          <t>MT4691</t>
+          <t>MT4004</t>
         </is>
       </c>
       <c r="C1197" t="inlineStr">
         <is>
-          <t>BALDE TORRE MARINO</t>
-        </is>
-      </c>
-      <c r="E1197" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>MT4004 BLADE PLAYA JUEGO</t>
         </is>
       </c>
       <c r="I1197" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J1197" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K1197" t="n">
         <v>0</v>
       </c>
       <c r="L1197" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1197" t="n">
         <v>52</v>
       </c>
       <c r="N1197" t="n">
-        <v>3306.0098306773</v>
+        <v>2058.92</v>
       </c>
       <c r="O1197" t="n">
-        <v>171912.5111952196</v>
+        <v>107063.84</v>
       </c>
       <c r="P1197" t="n">
-        <v>4200</v>
+        <v>2500</v>
       </c>
       <c r="Q1197" t="n">
-        <v>218400</v>
+        <v>130000</v>
       </c>
     </row>
     <row r="1198">
       <c r="A1198" t="inlineStr">
         <is>
-          <t>PC011</t>
+          <t>MT4691</t>
         </is>
       </c>
       <c r="C1198" t="inlineStr">
         <is>
-          <t>KIT DE LAPIZ BASKETBALL</t>
+          <t>BALDE TORRE MARINO</t>
         </is>
       </c>
       <c r="E1198" t="inlineStr">
@@ -54716,44 +54716,44 @@
         </is>
       </c>
       <c r="J1198" t="n">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="K1198" t="n">
         <v>0</v>
       </c>
       <c r="L1198" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M1198" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="N1198" t="n">
-        <v>7500</v>
+        <v>3306.00983</v>
       </c>
       <c r="O1198" t="n">
-        <v>15000</v>
+        <v>158688.47184</v>
       </c>
       <c r="P1198" t="n">
-        <v>8900</v>
+        <v>4200</v>
       </c>
       <c r="Q1198" t="n">
-        <v>17800</v>
+        <v>201600</v>
       </c>
     </row>
     <row r="1199">
       <c r="A1199" t="inlineStr">
         <is>
-          <t>PT14026</t>
+          <t>PC011</t>
         </is>
       </c>
       <c r="C1199" t="inlineStr">
         <is>
-          <t>JIRAFA CON DESTORNILLADOR DIDACTICA PT14026</t>
+          <t>KIT DE LAPIZ BASKETBALL</t>
         </is>
       </c>
       <c r="E1199" t="inlineStr">
         <is>
-          <t>DIDACTICOS</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I1199" t="inlineStr">
@@ -54762,7 +54762,7 @@
         </is>
       </c>
       <c r="J1199" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K1199" t="n">
         <v>0</v>
@@ -54771,35 +54771,35 @@
         <v>0</v>
       </c>
       <c r="M1199" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="N1199" t="n">
-        <v>2690.69</v>
+        <v>7500</v>
       </c>
       <c r="O1199" t="n">
-        <v>18834.83</v>
+        <v>15000</v>
       </c>
       <c r="P1199" t="n">
-        <v>5900</v>
+        <v>8900</v>
       </c>
       <c r="Q1199" t="n">
-        <v>41300</v>
+        <v>17800</v>
       </c>
     </row>
     <row r="1200">
       <c r="A1200" t="inlineStr">
         <is>
-          <t>PT25419</t>
+          <t>PT14026</t>
         </is>
       </c>
       <c r="C1200" t="inlineStr">
         <is>
-          <t>MONOPATIN CAJA LUCES PT25419</t>
+          <t>JIRAFA CON DESTORNILLADOR DIDACTICA PT14026</t>
         </is>
       </c>
       <c r="E1200" t="inlineStr">
         <is>
-          <t>MONTABLES</t>
+          <t>DIDACTICOS</t>
         </is>
       </c>
       <c r="I1200" t="inlineStr">
@@ -54808,7 +54808,7 @@
         </is>
       </c>
       <c r="J1200" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K1200" t="n">
         <v>0</v>
@@ -54817,35 +54817,35 @@
         <v>0</v>
       </c>
       <c r="M1200" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N1200" t="n">
-        <v>87920</v>
+        <v>2690.69</v>
       </c>
       <c r="O1200" t="n">
-        <v>263760</v>
+        <v>18834.83</v>
       </c>
       <c r="P1200" t="n">
-        <v>109900</v>
+        <v>5900</v>
       </c>
       <c r="Q1200" t="n">
-        <v>329700</v>
+        <v>41300</v>
       </c>
     </row>
     <row r="1201">
       <c r="A1201" t="inlineStr">
         <is>
-          <t>QH-8308</t>
+          <t>PT25419</t>
         </is>
       </c>
       <c r="C1201" t="inlineStr">
         <is>
-          <t>SET BORRADORES FANTASIA ESPACIAL QH-8308</t>
+          <t>MONOPATIN CAJA LUCES PT25419</t>
         </is>
       </c>
       <c r="E1201" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>MONTABLES</t>
         </is>
       </c>
       <c r="I1201" t="inlineStr">
@@ -54854,7 +54854,7 @@
         </is>
       </c>
       <c r="J1201" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1201" t="n">
         <v>0</v>
@@ -54863,30 +54863,30 @@
         <v>0</v>
       </c>
       <c r="M1201" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N1201" t="n">
-        <v>2200</v>
+        <v>87920</v>
       </c>
       <c r="O1201" t="n">
-        <v>4400</v>
+        <v>263760</v>
       </c>
       <c r="P1201" t="n">
-        <v>2700</v>
+        <v>109900</v>
       </c>
       <c r="Q1201" t="n">
-        <v>5400</v>
+        <v>329700</v>
       </c>
     </row>
     <row r="1202">
       <c r="A1202" t="inlineStr">
         <is>
-          <t>QH-8311</t>
+          <t>QH-8308</t>
         </is>
       </c>
       <c r="C1202" t="inlineStr">
         <is>
-          <t>SET BORRADORES ANIMALES QH-8311</t>
+          <t>SET BORRADORES FANTASIA ESPACIAL QH-8308</t>
         </is>
       </c>
       <c r="E1202" t="inlineStr">
@@ -54927,12 +54927,12 @@
     <row r="1203">
       <c r="A1203" t="inlineStr">
         <is>
-          <t>QH-8314</t>
+          <t>QH-8311</t>
         </is>
       </c>
       <c r="C1203" t="inlineStr">
         <is>
-          <t>SET BORRADORES DEPORTES QH-8314</t>
+          <t>SET BORRADORES ANIMALES QH-8311</t>
         </is>
       </c>
       <c r="E1203" t="inlineStr">
@@ -54946,7 +54946,7 @@
         </is>
       </c>
       <c r="J1203" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K1203" t="n">
         <v>0</v>
@@ -54955,30 +54955,30 @@
         <v>0</v>
       </c>
       <c r="M1203" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N1203" t="n">
         <v>2200</v>
       </c>
       <c r="O1203" t="n">
-        <v>13200</v>
+        <v>4400</v>
       </c>
       <c r="P1203" t="n">
         <v>2700</v>
       </c>
       <c r="Q1203" t="n">
-        <v>16200</v>
+        <v>5400</v>
       </c>
     </row>
     <row r="1204">
       <c r="A1204" t="inlineStr">
         <is>
-          <t>QQ-1502</t>
+          <t>QH-8314</t>
         </is>
       </c>
       <c r="C1204" t="inlineStr">
         <is>
-          <t>LAPIZ INFINITO REYRACTIL DEPORTES QQ-1502</t>
+          <t>SET BORRADORES DEPORTES QH-8314</t>
         </is>
       </c>
       <c r="E1204" t="inlineStr">
@@ -54992,7 +54992,7 @@
         </is>
       </c>
       <c r="J1204" t="n">
-        <v>58</v>
+        <v>6</v>
       </c>
       <c r="K1204" t="n">
         <v>0</v>
@@ -55001,30 +55001,30 @@
         <v>0</v>
       </c>
       <c r="M1204" t="n">
-        <v>58</v>
+        <v>6</v>
       </c>
       <c r="N1204" t="n">
         <v>2200</v>
       </c>
       <c r="O1204" t="n">
-        <v>127600</v>
+        <v>13200</v>
       </c>
       <c r="P1204" t="n">
         <v>2700</v>
       </c>
       <c r="Q1204" t="n">
-        <v>156600</v>
+        <v>16200</v>
       </c>
     </row>
     <row r="1205">
       <c r="A1205" t="inlineStr">
         <is>
-          <t>QQ-827</t>
+          <t>QQ-1502</t>
         </is>
       </c>
       <c r="C1205" t="inlineStr">
         <is>
-          <t>ESFERO CON LUZ BALONES QQ-827</t>
+          <t>LAPIZ INFINITO REYRACTIL DEPORTES QQ-1502</t>
         </is>
       </c>
       <c r="E1205" t="inlineStr">
@@ -55038,7 +55038,7 @@
         </is>
       </c>
       <c r="J1205" t="n">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="K1205" t="n">
         <v>0</v>
@@ -55047,30 +55047,30 @@
         <v>0</v>
       </c>
       <c r="M1205" t="n">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="N1205" t="n">
-        <v>2100</v>
+        <v>2200</v>
       </c>
       <c r="O1205" t="n">
-        <v>90300</v>
+        <v>127600</v>
       </c>
       <c r="P1205" t="n">
-        <v>2600</v>
+        <v>2700</v>
       </c>
       <c r="Q1205" t="n">
-        <v>111800</v>
+        <v>156600</v>
       </c>
     </row>
     <row r="1206">
       <c r="A1206" t="inlineStr">
         <is>
-          <t>QT511252-E</t>
+          <t>QQ-827</t>
         </is>
       </c>
       <c r="C1206" t="inlineStr">
         <is>
-          <t>COLORES DE ALTA GAMA CARRITOS X12PCS QT511252-E</t>
+          <t>ESFERO CON LUZ BALONES QQ-827</t>
         </is>
       </c>
       <c r="E1206" t="inlineStr">
@@ -55084,7 +55084,7 @@
         </is>
       </c>
       <c r="J1206" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="K1206" t="n">
         <v>0</v>
@@ -55093,30 +55093,30 @@
         <v>0</v>
       </c>
       <c r="M1206" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="N1206" t="n">
-        <v>5026.6659322034</v>
+        <v>2100</v>
       </c>
       <c r="O1206" t="n">
-        <v>180959.9735593224</v>
+        <v>90300</v>
       </c>
       <c r="P1206" t="n">
-        <v>6300</v>
+        <v>2600</v>
       </c>
       <c r="Q1206" t="n">
-        <v>226800</v>
+        <v>111800</v>
       </c>
     </row>
     <row r="1207">
       <c r="A1207" t="inlineStr">
         <is>
-          <t>QT511253-E</t>
+          <t>QT511252-E</t>
         </is>
       </c>
       <c r="C1207" t="inlineStr">
         <is>
-          <t>COLORES DE ALTA GAMA PRINCESAS X12 PCS QT511253-E</t>
+          <t>COLORES DE ALTA GAMA CARRITOS X12PCS QT511252-E</t>
         </is>
       </c>
       <c r="E1207" t="inlineStr">
@@ -55130,7 +55130,7 @@
         </is>
       </c>
       <c r="J1207" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="K1207" t="n">
         <v>0</v>
@@ -55139,30 +55139,30 @@
         <v>0</v>
       </c>
       <c r="M1207" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="N1207" t="n">
-        <v>5200</v>
+        <v>5026.6659322034</v>
       </c>
       <c r="O1207" t="n">
-        <v>57200</v>
+        <v>180959.9735593224</v>
       </c>
       <c r="P1207" t="n">
         <v>6300</v>
       </c>
       <c r="Q1207" t="n">
-        <v>69300</v>
+        <v>226800</v>
       </c>
     </row>
     <row r="1208">
       <c r="A1208" t="inlineStr">
         <is>
-          <t>QT512452-E</t>
+          <t>QT511253-E</t>
         </is>
       </c>
       <c r="C1208" t="inlineStr">
         <is>
-          <t>COLORES DE ALTA GAMA CARRITOS X 24PCS QT512452-E</t>
+          <t>COLORES DE ALTA GAMA PRINCESAS X12 PCS QT511253-E</t>
         </is>
       </c>
       <c r="E1208" t="inlineStr">
@@ -55176,7 +55176,7 @@
         </is>
       </c>
       <c r="J1208" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="K1208" t="n">
         <v>0</v>
@@ -55185,30 +55185,30 @@
         <v>0</v>
       </c>
       <c r="M1208" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="N1208" t="n">
-        <v>8800</v>
+        <v>5200</v>
       </c>
       <c r="O1208" t="n">
-        <v>264000</v>
+        <v>57200</v>
       </c>
       <c r="P1208" t="n">
-        <v>10600</v>
+        <v>6300</v>
       </c>
       <c r="Q1208" t="n">
-        <v>318000</v>
+        <v>69300</v>
       </c>
     </row>
     <row r="1209">
       <c r="A1209" t="inlineStr">
         <is>
-          <t>QT512453-E</t>
+          <t>QT512452-E</t>
         </is>
       </c>
       <c r="C1209" t="inlineStr">
         <is>
-          <t>COLORES DE ALTA GAMA PRINCESA X24 PCS QT512453-E</t>
+          <t>COLORES DE ALTA GAMA CARRITOS X 24PCS QT512452-E</t>
         </is>
       </c>
       <c r="E1209" t="inlineStr">
@@ -55222,7 +55222,7 @@
         </is>
       </c>
       <c r="J1209" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K1209" t="n">
         <v>0</v>
@@ -55231,33 +55231,30 @@
         <v>0</v>
       </c>
       <c r="M1209" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="N1209" t="n">
         <v>8800</v>
       </c>
       <c r="O1209" t="n">
-        <v>176000</v>
+        <v>264000</v>
       </c>
       <c r="P1209" t="n">
         <v>10600</v>
       </c>
       <c r="Q1209" t="n">
-        <v>212000</v>
+        <v>318000</v>
       </c>
     </row>
     <row r="1210">
       <c r="A1210" t="inlineStr">
         <is>
-          <t>SE1410</t>
-        </is>
-      </c>
-      <c r="B1210" t="n">
-        <v>2019892166532</v>
+          <t>QT512453-E</t>
+        </is>
       </c>
       <c r="C1210" t="inlineStr">
         <is>
-          <t>ESPERIAL PQÑ PQT X12</t>
+          <t>COLORES DE ALTA GAMA PRINCESA X24 PCS QT512453-E</t>
         </is>
       </c>
       <c r="E1210" t="inlineStr">
@@ -55271,7 +55268,7 @@
         </is>
       </c>
       <c r="J1210" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="K1210" t="n">
         <v>0</v>
@@ -55280,35 +55277,38 @@
         <v>0</v>
       </c>
       <c r="M1210" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="N1210" t="n">
-        <v>9900</v>
+        <v>8800</v>
       </c>
       <c r="O1210" t="n">
-        <v>9900</v>
+        <v>176000</v>
       </c>
       <c r="P1210" t="n">
-        <v>14400</v>
+        <v>10600</v>
       </c>
       <c r="Q1210" t="n">
-        <v>14400</v>
+        <v>212000</v>
       </c>
     </row>
     <row r="1211">
       <c r="A1211" t="inlineStr">
         <is>
-          <t>SEB01</t>
-        </is>
+          <t>SE1410</t>
+        </is>
+      </c>
+      <c r="B1211" t="n">
+        <v>2019892166532</v>
       </c>
       <c r="C1211" t="inlineStr">
         <is>
-          <t>ROMPECABEZAS CON TABLERO SE1408</t>
+          <t>ESPERIAL PQÑ PQT X12</t>
         </is>
       </c>
       <c r="E1211" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I1211" t="inlineStr">
@@ -55329,32 +55329,32 @@
         <v>1</v>
       </c>
       <c r="N1211" t="n">
-        <v>1200</v>
+        <v>9900</v>
       </c>
       <c r="O1211" t="n">
-        <v>1200</v>
+        <v>9900</v>
       </c>
       <c r="P1211" t="n">
-        <v>1500</v>
+        <v>14400</v>
       </c>
       <c r="Q1211" t="n">
-        <v>1500</v>
+        <v>14400</v>
       </c>
     </row>
     <row r="1212">
       <c r="A1212" t="inlineStr">
         <is>
-          <t>SEB010</t>
+          <t>SEB01</t>
         </is>
       </c>
       <c r="C1212" t="inlineStr">
         <is>
-          <t>ABACO CON RELOJ ANIMALES SE1420</t>
+          <t>ROMPECABEZAS CON TABLERO SE1408</t>
         </is>
       </c>
       <c r="E1212" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I1212" t="inlineStr">
@@ -55363,7 +55363,7 @@
         </is>
       </c>
       <c r="J1212" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="K1212" t="n">
         <v>0</v>
@@ -55372,35 +55372,35 @@
         <v>0</v>
       </c>
       <c r="M1212" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="N1212" t="n">
-        <v>7600</v>
+        <v>1200</v>
       </c>
       <c r="O1212" t="n">
-        <v>106400</v>
+        <v>1200</v>
       </c>
       <c r="P1212" t="n">
-        <v>9500</v>
+        <v>1500</v>
       </c>
       <c r="Q1212" t="n">
-        <v>133000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="1213">
       <c r="A1213" t="inlineStr">
         <is>
-          <t>SEB02</t>
+          <t>SEB010</t>
         </is>
       </c>
       <c r="C1213" t="inlineStr">
         <is>
-          <t>NUMERO Y LETRAS DIDACTICAS SE1413</t>
+          <t>ABACO CON RELOJ ANIMALES SE1420</t>
         </is>
       </c>
       <c r="E1213" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I1213" t="inlineStr">
@@ -55409,7 +55409,7 @@
         </is>
       </c>
       <c r="J1213" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="K1213" t="n">
         <v>0</v>
@@ -55418,30 +55418,30 @@
         <v>0</v>
       </c>
       <c r="M1213" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="N1213" t="n">
-        <v>9520</v>
+        <v>7600</v>
       </c>
       <c r="O1213" t="n">
-        <v>57120</v>
+        <v>106400</v>
       </c>
       <c r="P1213" t="n">
-        <v>11900</v>
+        <v>9500</v>
       </c>
       <c r="Q1213" t="n">
-        <v>71400</v>
+        <v>133000</v>
       </c>
     </row>
     <row r="1214">
       <c r="A1214" t="inlineStr">
         <is>
-          <t>SEB03</t>
+          <t>SEB02</t>
         </is>
       </c>
       <c r="C1214" t="inlineStr">
         <is>
-          <t>TORRES DE ABACO SE1428/SEB03</t>
+          <t>NUMERO Y LETRAS DIDACTICAS SE1413</t>
         </is>
       </c>
       <c r="E1214" t="inlineStr">
@@ -55455,7 +55455,7 @@
         </is>
       </c>
       <c r="J1214" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="K1214" t="n">
         <v>0</v>
@@ -55464,30 +55464,30 @@
         <v>0</v>
       </c>
       <c r="M1214" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="N1214" t="n">
-        <v>7920</v>
+        <v>9520</v>
       </c>
       <c r="O1214" t="n">
-        <v>150480</v>
+        <v>57120</v>
       </c>
       <c r="P1214" t="n">
-        <v>9900</v>
+        <v>11900</v>
       </c>
       <c r="Q1214" t="n">
-        <v>188100</v>
+        <v>71400</v>
       </c>
     </row>
     <row r="1215">
       <c r="A1215" t="inlineStr">
         <is>
-          <t>SEB04</t>
+          <t>SEB03</t>
         </is>
       </c>
       <c r="C1215" t="inlineStr">
         <is>
-          <t>XILOFONO DE COLORES SE1432</t>
+          <t>TORRES DE ABACO SE1428/SEB03</t>
         </is>
       </c>
       <c r="E1215" t="inlineStr">
@@ -55501,7 +55501,7 @@
         </is>
       </c>
       <c r="J1215" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="K1215" t="n">
         <v>0</v>
@@ -55510,35 +55510,35 @@
         <v>0</v>
       </c>
       <c r="M1215" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="N1215" t="n">
-        <v>5520</v>
+        <v>7920</v>
       </c>
       <c r="O1215" t="n">
-        <v>60720</v>
+        <v>150480</v>
       </c>
       <c r="P1215" t="n">
-        <v>6900</v>
+        <v>9900</v>
       </c>
       <c r="Q1215" t="n">
-        <v>75900</v>
+        <v>188100</v>
       </c>
     </row>
     <row r="1216">
       <c r="A1216" t="inlineStr">
         <is>
-          <t>SEB08</t>
+          <t>SEB04</t>
         </is>
       </c>
       <c r="C1216" t="inlineStr">
         <is>
-          <t>JENGA COLORES BLOQUES DIDACTICOS SE1955</t>
+          <t>XILOFONO DE COLORES SE1432</t>
         </is>
       </c>
       <c r="E1216" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I1216" t="inlineStr">
@@ -55547,7 +55547,7 @@
         </is>
       </c>
       <c r="J1216" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="K1216" t="n">
         <v>0</v>
@@ -55556,35 +55556,35 @@
         <v>0</v>
       </c>
       <c r="M1216" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="N1216" t="n">
-        <v>3600</v>
+        <v>5520</v>
       </c>
       <c r="O1216" t="n">
-        <v>14400</v>
+        <v>60720</v>
       </c>
       <c r="P1216" t="n">
-        <v>4500</v>
+        <v>6900</v>
       </c>
       <c r="Q1216" t="n">
-        <v>18000</v>
+        <v>75900</v>
       </c>
     </row>
     <row r="1217">
       <c r="A1217" t="inlineStr">
         <is>
-          <t>SEB09</t>
+          <t>SEB08</t>
         </is>
       </c>
       <c r="C1217" t="inlineStr">
         <is>
-          <t>SET ESCOLAR PARA PINTAR PQÑ SE1984</t>
+          <t>JENGA COLORES BLOQUES DIDACTICOS SE1955</t>
         </is>
       </c>
       <c r="E1217" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I1217" t="inlineStr">
@@ -55593,7 +55593,7 @@
         </is>
       </c>
       <c r="J1217" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="K1217" t="n">
         <v>0</v>
@@ -55602,34 +55602,44 @@
         <v>0</v>
       </c>
       <c r="M1217" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="N1217" t="n">
-        <v>1600</v>
+        <v>3600</v>
       </c>
       <c r="O1217" t="n">
-        <v>40000</v>
+        <v>14400</v>
       </c>
       <c r="P1217" t="n">
-        <v>2000</v>
+        <v>4500</v>
       </c>
       <c r="Q1217" t="n">
-        <v>50000</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="1218">
       <c r="A1218" t="inlineStr">
         <is>
-          <t>SEBQ08</t>
+          <t>SEB09</t>
         </is>
       </c>
       <c r="C1218" t="inlineStr">
         <is>
-          <t>SLIME TARRO CON TAPA CACHO DE RENO SE1223</t>
+          <t>SET ESCOLAR PARA PINTAR PQÑ SE1984</t>
+        </is>
+      </c>
+      <c r="E1218" t="inlineStr">
+        <is>
+          <t>PIÑATERIA</t>
+        </is>
+      </c>
+      <c r="I1218" t="inlineStr">
+        <is>
+          <t>Und</t>
         </is>
       </c>
       <c r="J1218" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="K1218" t="n">
         <v>0</v>
@@ -55638,40 +55648,30 @@
         <v>0</v>
       </c>
       <c r="M1218" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="N1218" t="n">
-        <v>3000</v>
+        <v>1600</v>
       </c>
       <c r="O1218" t="n">
-        <v>3000</v>
+        <v>40000</v>
       </c>
       <c r="P1218" t="n">
-        <v>3500</v>
+        <v>2000</v>
       </c>
       <c r="Q1218" t="n">
-        <v>3500</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="1219">
       <c r="A1219" t="inlineStr">
         <is>
-          <t>SEBQ17</t>
+          <t>SEBQ08</t>
         </is>
       </c>
       <c r="C1219" t="inlineStr">
         <is>
-          <t>CUBO MAGICO COLORES X5 SE-19126</t>
-        </is>
-      </c>
-      <c r="E1219" t="inlineStr">
-        <is>
-          <t>DIDACTICO</t>
-        </is>
-      </c>
-      <c r="I1219" t="inlineStr">
-        <is>
-          <t>Und</t>
+          <t>SLIME TARRO CON TAPA CACHO DE RENO SE1223</t>
         </is>
       </c>
       <c r="J1219" t="n">
@@ -55687,32 +55687,32 @@
         <v>1</v>
       </c>
       <c r="N1219" t="n">
-        <v>5148.77</v>
+        <v>3000</v>
       </c>
       <c r="O1219" t="n">
-        <v>5148.77</v>
+        <v>3000</v>
       </c>
       <c r="P1219" t="n">
-        <v>10500</v>
+        <v>3500</v>
       </c>
       <c r="Q1219" t="n">
-        <v>10500</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="1220">
       <c r="A1220" t="inlineStr">
         <is>
-          <t>SLT027</t>
+          <t>SEBQ17</t>
         </is>
       </c>
       <c r="C1220" t="inlineStr">
         <is>
-          <t>JUGUETE  DRAGON   AB-02 / 082</t>
+          <t>CUBO MAGICO COLORES X5 SE-19126</t>
         </is>
       </c>
       <c r="E1220" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I1220" t="inlineStr">
@@ -55721,7 +55721,7 @@
         </is>
       </c>
       <c r="J1220" t="n">
-        <v>53</v>
+        <v>1</v>
       </c>
       <c r="K1220" t="n">
         <v>0</v>
@@ -55730,30 +55730,30 @@
         <v>0</v>
       </c>
       <c r="M1220" t="n">
-        <v>53</v>
+        <v>1</v>
       </c>
       <c r="N1220" t="n">
-        <v>3732.8773611111</v>
+        <v>5148.77</v>
       </c>
       <c r="O1220" t="n">
-        <v>197842.5001388883</v>
+        <v>5148.77</v>
       </c>
       <c r="P1220" t="n">
-        <v>4500</v>
+        <v>10500</v>
       </c>
       <c r="Q1220" t="n">
-        <v>238500</v>
+        <v>10500</v>
       </c>
     </row>
     <row r="1221">
       <c r="A1221" t="inlineStr">
         <is>
-          <t>SLT033-LJ</t>
+          <t>SLT027</t>
         </is>
       </c>
       <c r="C1221" t="inlineStr">
         <is>
-          <t>JUGUETE DINOSAURIO  Q301A</t>
+          <t>JUGUETE  DRAGON   AB-02 / 082</t>
         </is>
       </c>
       <c r="E1221" t="inlineStr">
@@ -55767,7 +55767,7 @@
         </is>
       </c>
       <c r="J1221" t="n">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="K1221" t="n">
         <v>0</v>
@@ -55776,30 +55776,30 @@
         <v>0</v>
       </c>
       <c r="M1221" t="n">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="N1221" t="n">
-        <v>54000</v>
+        <v>3732.8773611111</v>
       </c>
       <c r="O1221" t="n">
-        <v>54000</v>
+        <v>197842.5001388883</v>
       </c>
       <c r="P1221" t="n">
-        <v>67500</v>
+        <v>4500</v>
       </c>
       <c r="Q1221" t="n">
-        <v>67500</v>
+        <v>238500</v>
       </c>
     </row>
     <row r="1222">
       <c r="A1222" t="inlineStr">
         <is>
-          <t>SLT034-LJ</t>
+          <t>SLT033-LJ</t>
         </is>
       </c>
       <c r="C1222" t="inlineStr">
         <is>
-          <t>JUGUETE DINOSAURIO  053-1-12</t>
+          <t>JUGUETE DINOSAURIO  Q301A</t>
         </is>
       </c>
       <c r="E1222" t="inlineStr">
@@ -55825,27 +55825,27 @@
         <v>1</v>
       </c>
       <c r="N1222" t="n">
-        <v>45200</v>
+        <v>54000</v>
       </c>
       <c r="O1222" t="n">
-        <v>45200</v>
+        <v>54000</v>
       </c>
       <c r="P1222" t="n">
-        <v>56500</v>
+        <v>67500</v>
       </c>
       <c r="Q1222" t="n">
-        <v>56500</v>
+        <v>67500</v>
       </c>
     </row>
     <row r="1223">
       <c r="A1223" t="inlineStr">
         <is>
-          <t>SLT043-LJ</t>
+          <t>SLT034-LJ</t>
         </is>
       </c>
       <c r="C1223" t="inlineStr">
         <is>
-          <t>JUGUETE  DINOSAURIO  5861</t>
+          <t>JUGUETE DINOSAURIO  053-1-12</t>
         </is>
       </c>
       <c r="E1223" t="inlineStr">
@@ -55859,7 +55859,7 @@
         </is>
       </c>
       <c r="J1223" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K1223" t="n">
         <v>0</v>
@@ -55868,30 +55868,30 @@
         <v>0</v>
       </c>
       <c r="M1223" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N1223" t="n">
-        <v>24780.39</v>
+        <v>45200</v>
       </c>
       <c r="O1223" t="n">
-        <v>247803.9</v>
+        <v>45200</v>
       </c>
       <c r="P1223" t="n">
-        <v>31500</v>
+        <v>56500</v>
       </c>
       <c r="Q1223" t="n">
-        <v>315000</v>
+        <v>56500</v>
       </c>
     </row>
     <row r="1224">
       <c r="A1224" t="inlineStr">
         <is>
-          <t>SLT056</t>
+          <t>SLT043-LJ</t>
         </is>
       </c>
       <c r="C1224" t="inlineStr">
         <is>
-          <t>JUGUETE SET DINOSAURIO  KL-18012</t>
+          <t>JUGUETE  DINOSAURIO  5861</t>
         </is>
       </c>
       <c r="E1224" t="inlineStr">
@@ -55905,7 +55905,7 @@
         </is>
       </c>
       <c r="J1224" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K1224" t="n">
         <v>0</v>
@@ -55914,35 +55914,35 @@
         <v>0</v>
       </c>
       <c r="M1224" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="N1224" t="n">
-        <v>8392.59</v>
+        <v>24780.39</v>
       </c>
       <c r="O1224" t="n">
-        <v>58748.13</v>
+        <v>247803.9</v>
       </c>
       <c r="P1224" t="n">
-        <v>8900</v>
+        <v>31500</v>
       </c>
       <c r="Q1224" t="n">
-        <v>62300</v>
+        <v>315000</v>
       </c>
     </row>
     <row r="1225">
       <c r="A1225" t="inlineStr">
         <is>
-          <t>SLT1934</t>
+          <t>SLT056</t>
         </is>
       </c>
       <c r="C1225" t="inlineStr">
         <is>
-          <t>BROMA DE FIESTA CARTON X 40 PCS</t>
+          <t>JUGUETE SET DINOSAURIO  KL-18012</t>
         </is>
       </c>
       <c r="E1225" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I1225" t="inlineStr">
@@ -55951,7 +55951,7 @@
         </is>
       </c>
       <c r="J1225" t="n">
-        <v>78</v>
+        <v>7</v>
       </c>
       <c r="K1225" t="n">
         <v>0</v>
@@ -55960,30 +55960,30 @@
         <v>0</v>
       </c>
       <c r="M1225" t="n">
-        <v>78</v>
+        <v>7</v>
       </c>
       <c r="N1225" t="n">
-        <v>4550</v>
+        <v>8392.59</v>
       </c>
       <c r="O1225" t="n">
-        <v>354900</v>
+        <v>58748.13</v>
       </c>
       <c r="P1225" t="n">
-        <v>5500</v>
+        <v>8900</v>
       </c>
       <c r="Q1225" t="n">
-        <v>429000</v>
+        <v>62300</v>
       </c>
     </row>
     <row r="1226">
       <c r="A1226" t="inlineStr">
         <is>
-          <t>SLT2640</t>
+          <t>SLT1934</t>
         </is>
       </c>
       <c r="C1226" t="inlineStr">
         <is>
-          <t>BALON BASQUEBOL # 3 SLT2640</t>
+          <t>BROMA DE FIESTA CARTON X 40 PCS</t>
         </is>
       </c>
       <c r="E1226" t="inlineStr">
@@ -55997,7 +55997,7 @@
         </is>
       </c>
       <c r="J1226" t="n">
-        <v>5</v>
+        <v>78</v>
       </c>
       <c r="K1226" t="n">
         <v>0</v>
@@ -56006,30 +56006,30 @@
         <v>0</v>
       </c>
       <c r="M1226" t="n">
-        <v>5</v>
+        <v>78</v>
       </c>
       <c r="N1226" t="n">
-        <v>1059.1847727273</v>
+        <v>4550</v>
       </c>
       <c r="O1226" t="n">
-        <v>5295.9238636365</v>
+        <v>354900</v>
       </c>
       <c r="P1226" t="n">
-        <v>9500</v>
+        <v>5500</v>
       </c>
       <c r="Q1226" t="n">
-        <v>47500</v>
+        <v>429000</v>
       </c>
     </row>
     <row r="1227">
       <c r="A1227" t="inlineStr">
         <is>
-          <t>SLT2641</t>
+          <t>SLT2640</t>
         </is>
       </c>
       <c r="C1227" t="inlineStr">
         <is>
-          <t>BALON BASQUEBOL # 5 SLT2641</t>
+          <t>BALON BASQUEBOL # 3 SLT2640</t>
         </is>
       </c>
       <c r="E1227" t="inlineStr">
@@ -56043,7 +56043,7 @@
         </is>
       </c>
       <c r="J1227" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K1227" t="n">
         <v>0</v>
@@ -56052,30 +56052,30 @@
         <v>0</v>
       </c>
       <c r="M1227" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N1227" t="n">
-        <v>422.91</v>
+        <v>1059.1847727273</v>
       </c>
       <c r="O1227" t="n">
-        <v>422.91</v>
+        <v>5295.9238636365</v>
       </c>
       <c r="P1227" t="n">
-        <v>12500</v>
+        <v>9500</v>
       </c>
       <c r="Q1227" t="n">
-        <v>12500</v>
+        <v>47500</v>
       </c>
     </row>
     <row r="1228">
       <c r="A1228" t="inlineStr">
         <is>
-          <t>SLT2642</t>
+          <t>SLT2641</t>
         </is>
       </c>
       <c r="C1228" t="inlineStr">
         <is>
-          <t>BALON BASQUEBOL # 7 ST2642</t>
+          <t>BALON BASQUEBOL # 5 SLT2641</t>
         </is>
       </c>
       <c r="E1228" t="inlineStr">
@@ -56089,7 +56089,7 @@
         </is>
       </c>
       <c r="J1228" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K1228" t="n">
         <v>0</v>
@@ -56098,35 +56098,35 @@
         <v>0</v>
       </c>
       <c r="M1228" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N1228" t="n">
-        <v>341.02143442623</v>
+        <v>422.91</v>
       </c>
       <c r="O1228" t="n">
-        <v>1023.06430327869</v>
+        <v>422.91</v>
       </c>
       <c r="P1228" t="n">
-        <v>14500</v>
+        <v>12500</v>
       </c>
       <c r="Q1228" t="n">
-        <v>43500</v>
+        <v>12500</v>
       </c>
     </row>
     <row r="1229">
       <c r="A1229" t="inlineStr">
         <is>
-          <t>T032-LJ</t>
+          <t>SLT2642</t>
         </is>
       </c>
       <c r="C1229" t="inlineStr">
         <is>
-          <t>PELUCHE GATA MERIE 35CM CAT-35</t>
+          <t>BALON BASQUEBOL # 7 ST2642</t>
         </is>
       </c>
       <c r="E1229" t="inlineStr">
         <is>
-          <t>PELUCHES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I1229" t="inlineStr">
@@ -56135,7 +56135,7 @@
         </is>
       </c>
       <c r="J1229" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K1229" t="n">
         <v>0</v>
@@ -56144,35 +56144,35 @@
         <v>0</v>
       </c>
       <c r="M1229" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N1229" t="n">
-        <v>30000</v>
+        <v>341.02143442623</v>
       </c>
       <c r="O1229" t="n">
-        <v>30000</v>
+        <v>1023.06430327869</v>
       </c>
       <c r="P1229" t="n">
-        <v>37500</v>
+        <v>14500</v>
       </c>
       <c r="Q1229" t="n">
-        <v>37500</v>
+        <v>43500</v>
       </c>
     </row>
     <row r="1230">
       <c r="A1230" t="inlineStr">
         <is>
-          <t>T040-LJ</t>
+          <t>T032-LJ</t>
         </is>
       </c>
       <c r="C1230" t="inlineStr">
         <is>
-          <t>CHAQUETA COJIN REVERSIBLE CYQ-20</t>
+          <t>PELUCHE GATA MERIE 35CM CAT-35</t>
         </is>
       </c>
       <c r="E1230" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PELUCHES</t>
         </is>
       </c>
       <c r="I1230" t="inlineStr">
@@ -56181,7 +56181,7 @@
         </is>
       </c>
       <c r="J1230" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="K1230" t="n">
         <v>0</v>
@@ -56190,30 +56190,30 @@
         <v>0</v>
       </c>
       <c r="M1230" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="N1230" t="n">
-        <v>3661.88</v>
+        <v>30000</v>
       </c>
       <c r="O1230" t="n">
-        <v>80561.36</v>
+        <v>30000</v>
       </c>
       <c r="P1230" t="n">
-        <v>38900</v>
+        <v>37500</v>
       </c>
       <c r="Q1230" t="n">
-        <v>855800</v>
+        <v>37500</v>
       </c>
     </row>
     <row r="1231">
       <c r="A1231" t="inlineStr">
         <is>
-          <t>T041-LJ</t>
+          <t>T040-LJ</t>
         </is>
       </c>
       <c r="C1231" t="inlineStr">
         <is>
-          <t>PELUCHE ELMO COSQUILLAS A-88/T041-LJ</t>
+          <t>CHAQUETA COJIN REVERSIBLE CYQ-20</t>
         </is>
       </c>
       <c r="E1231" t="inlineStr">
@@ -56227,7 +56227,7 @@
         </is>
       </c>
       <c r="J1231" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="K1231" t="n">
         <v>0</v>
@@ -56236,30 +56236,30 @@
         <v>0</v>
       </c>
       <c r="M1231" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="N1231" t="n">
-        <v>2797.08</v>
+        <v>3661.88</v>
       </c>
       <c r="O1231" t="n">
-        <v>5594.16</v>
+        <v>80561.36</v>
       </c>
       <c r="P1231" t="n">
-        <v>30900</v>
+        <v>38900</v>
       </c>
       <c r="Q1231" t="n">
-        <v>61800</v>
+        <v>855800</v>
       </c>
     </row>
     <row r="1232">
       <c r="A1232" t="inlineStr">
         <is>
-          <t>T048-LJ</t>
+          <t>T041-LJ</t>
         </is>
       </c>
       <c r="C1232" t="inlineStr">
         <is>
-          <t>PELUCHE DINOSAURIO 60CM SWK-60</t>
+          <t>PELUCHE ELMO COSQUILLAS A-88/T041-LJ</t>
         </is>
       </c>
       <c r="E1232" t="inlineStr">
@@ -56273,7 +56273,7 @@
         </is>
       </c>
       <c r="J1232" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K1232" t="n">
         <v>0</v>
@@ -56282,35 +56282,35 @@
         <v>0</v>
       </c>
       <c r="M1232" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N1232" t="n">
-        <v>3462.255</v>
+        <v>2797.08</v>
       </c>
       <c r="O1232" t="n">
-        <v>10386.765</v>
+        <v>5594.16</v>
       </c>
       <c r="P1232" t="n">
-        <v>42000</v>
+        <v>30900</v>
       </c>
       <c r="Q1232" t="n">
-        <v>126000</v>
+        <v>61800</v>
       </c>
     </row>
     <row r="1233">
       <c r="A1233" t="inlineStr">
         <is>
-          <t>T061-LJ</t>
+          <t>T048-LJ</t>
         </is>
       </c>
       <c r="C1233" t="inlineStr">
         <is>
-          <t>PELUCHE ZOOLOGICO MED SUR05-30</t>
+          <t>PELUCHE DINOSAURIO 60CM SWK-60</t>
         </is>
       </c>
       <c r="E1233" t="inlineStr">
         <is>
-          <t>PELUCHES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I1233" t="inlineStr">
@@ -56319,7 +56319,7 @@
         </is>
       </c>
       <c r="J1233" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K1233" t="n">
         <v>0</v>
@@ -56328,35 +56328,35 @@
         <v>0</v>
       </c>
       <c r="M1233" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="N1233" t="n">
-        <v>12392.16</v>
+        <v>3462.255</v>
       </c>
       <c r="O1233" t="n">
-        <v>111529.44</v>
+        <v>10386.765</v>
       </c>
       <c r="P1233" t="n">
-        <v>15900</v>
+        <v>42000</v>
       </c>
       <c r="Q1233" t="n">
-        <v>143100</v>
+        <v>126000</v>
       </c>
     </row>
     <row r="1234">
       <c r="A1234" t="inlineStr">
         <is>
-          <t>T062-LJ</t>
+          <t>T061-LJ</t>
         </is>
       </c>
       <c r="C1234" t="inlineStr">
         <is>
-          <t>PELUCHE ZOOLOGICO STD 40CM SUR05-40</t>
+          <t>PELUCHE ZOOLOGICO MED SUR05-30</t>
         </is>
       </c>
       <c r="E1234" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PELUCHES</t>
         </is>
       </c>
       <c r="I1234" t="inlineStr">
@@ -56365,7 +56365,7 @@
         </is>
       </c>
       <c r="J1234" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K1234" t="n">
         <v>0</v>
@@ -56374,35 +56374,35 @@
         <v>0</v>
       </c>
       <c r="M1234" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N1234" t="n">
-        <v>24882.58</v>
+        <v>12392.16</v>
       </c>
       <c r="O1234" t="n">
-        <v>248825.8</v>
+        <v>111529.44</v>
       </c>
       <c r="P1234" t="n">
-        <v>31500</v>
+        <v>15900</v>
       </c>
       <c r="Q1234" t="n">
-        <v>315000</v>
+        <v>143100</v>
       </c>
     </row>
     <row r="1235">
       <c r="A1235" t="inlineStr">
         <is>
-          <t>T089</t>
+          <t>T062-LJ</t>
         </is>
       </c>
       <c r="C1235" t="inlineStr">
         <is>
-          <t>PELUCHE ZOOLOGICO STD SUR05-40-60</t>
+          <t>PELUCHE ZOOLOGICO STD 40CM SUR05-40</t>
         </is>
       </c>
       <c r="E1235" t="inlineStr">
         <is>
-          <t>PELUCHES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I1235" t="inlineStr">
@@ -56411,7 +56411,7 @@
         </is>
       </c>
       <c r="J1235" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K1235" t="n">
         <v>0</v>
@@ -56420,35 +56420,35 @@
         <v>0</v>
       </c>
       <c r="M1235" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="N1235" t="n">
-        <v>8580.75</v>
+        <v>24882.58</v>
       </c>
       <c r="O1235" t="n">
-        <v>51484.5</v>
+        <v>248825.8</v>
       </c>
       <c r="P1235" t="n">
-        <v>42900</v>
+        <v>31500</v>
       </c>
       <c r="Q1235" t="n">
-        <v>257400</v>
+        <v>315000</v>
       </c>
     </row>
     <row r="1236">
       <c r="A1236" t="inlineStr">
         <is>
-          <t>T124-LJ</t>
+          <t>T089</t>
         </is>
       </c>
       <c r="C1236" t="inlineStr">
         <is>
-          <t>COBIJA PERSONAJES TZ-1-5-7</t>
+          <t>PELUCHE ZOOLOGICO STD SUR05-40-60</t>
         </is>
       </c>
       <c r="E1236" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PELUCHES</t>
         </is>
       </c>
       <c r="I1236" t="inlineStr">
@@ -56457,7 +56457,7 @@
         </is>
       </c>
       <c r="J1236" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K1236" t="n">
         <v>0</v>
@@ -56466,35 +56466,35 @@
         <v>0</v>
       </c>
       <c r="M1236" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N1236" t="n">
-        <v>0.8</v>
+        <v>8580.75</v>
       </c>
       <c r="O1236" t="n">
-        <v>1.6</v>
+        <v>51484.5</v>
       </c>
       <c r="P1236" t="n">
-        <v>24900</v>
+        <v>42900</v>
       </c>
       <c r="Q1236" t="n">
-        <v>49800</v>
+        <v>257400</v>
       </c>
     </row>
     <row r="1237">
       <c r="A1237" t="inlineStr">
         <is>
-          <t>T156</t>
+          <t>T124-LJ</t>
         </is>
       </c>
       <c r="C1237" t="inlineStr">
         <is>
-          <t>PELUCHE UNICORNIO ALAS 80CM DJS-80</t>
+          <t>COBIJA PERSONAJES TZ-1-5-7</t>
         </is>
       </c>
       <c r="E1237" t="inlineStr">
         <is>
-          <t>PELUCHES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I1237" t="inlineStr">
@@ -56503,7 +56503,7 @@
         </is>
       </c>
       <c r="J1237" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1237" t="n">
         <v>0</v>
@@ -56512,30 +56512,30 @@
         <v>0</v>
       </c>
       <c r="M1237" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N1237" t="n">
-        <v>88000</v>
+        <v>0.8</v>
       </c>
       <c r="O1237" t="n">
-        <v>88000</v>
+        <v>1.6</v>
       </c>
       <c r="P1237" t="n">
-        <v>110000</v>
+        <v>24900</v>
       </c>
       <c r="Q1237" t="n">
-        <v>110000</v>
+        <v>49800</v>
       </c>
     </row>
     <row r="1238">
       <c r="A1238" t="inlineStr">
         <is>
-          <t>T166-LJ</t>
+          <t>T156</t>
         </is>
       </c>
       <c r="C1238" t="inlineStr">
         <is>
-          <t>PELUCHE STD 20CM ECOSUR-PER</t>
+          <t>PELUCHE UNICORNIO ALAS 80CM DJS-80</t>
         </is>
       </c>
       <c r="E1238" t="inlineStr">
@@ -56549,7 +56549,7 @@
         </is>
       </c>
       <c r="J1238" t="n">
-        <v>55</v>
+        <v>1</v>
       </c>
       <c r="K1238" t="n">
         <v>0</v>
@@ -56558,35 +56558,35 @@
         <v>0</v>
       </c>
       <c r="M1238" t="n">
-        <v>55</v>
+        <v>1</v>
       </c>
       <c r="N1238" t="n">
-        <v>5186.45</v>
+        <v>88000</v>
       </c>
       <c r="O1238" t="n">
-        <v>285254.75</v>
+        <v>88000</v>
       </c>
       <c r="P1238" t="n">
-        <v>7200</v>
+        <v>110000</v>
       </c>
       <c r="Q1238" t="n">
-        <v>396000</v>
+        <v>110000</v>
       </c>
     </row>
     <row r="1239">
       <c r="A1239" t="inlineStr">
         <is>
-          <t>T178-LJ</t>
+          <t>T166-LJ</t>
         </is>
       </c>
       <c r="C1239" t="inlineStr">
         <is>
-          <t>COJIN HAMBURGUESA HBS-20</t>
+          <t>PELUCHE STD 20CM ECOSUR-PER</t>
         </is>
       </c>
       <c r="E1239" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PELUCHES</t>
         </is>
       </c>
       <c r="I1239" t="inlineStr">
@@ -56595,7 +56595,7 @@
         </is>
       </c>
       <c r="J1239" t="n">
-        <v>2</v>
+        <v>55</v>
       </c>
       <c r="K1239" t="n">
         <v>0</v>
@@ -56604,35 +56604,35 @@
         <v>0</v>
       </c>
       <c r="M1239" t="n">
-        <v>2</v>
+        <v>55</v>
       </c>
       <c r="N1239" t="n">
-        <v>6115.78</v>
+        <v>5186.45</v>
       </c>
       <c r="O1239" t="n">
-        <v>12231.56</v>
+        <v>285254.75</v>
       </c>
       <c r="P1239" t="n">
-        <v>15900</v>
+        <v>7200</v>
       </c>
       <c r="Q1239" t="n">
-        <v>31800</v>
+        <v>396000</v>
       </c>
     </row>
     <row r="1240">
       <c r="A1240" t="inlineStr">
         <is>
-          <t>T182</t>
+          <t>T178-LJ</t>
         </is>
       </c>
       <c r="C1240" t="inlineStr">
         <is>
-          <t>PELUCHE POKEMON X12 MOTIVOS 20CM COLG-8</t>
+          <t>COJIN HAMBURGUESA HBS-20</t>
         </is>
       </c>
       <c r="E1240" t="inlineStr">
         <is>
-          <t>PELUCHES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I1240" t="inlineStr">
@@ -56641,7 +56641,7 @@
         </is>
       </c>
       <c r="J1240" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1240" t="n">
         <v>0</v>
@@ -56650,30 +56650,30 @@
         <v>0</v>
       </c>
       <c r="M1240" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N1240" t="n">
-        <v>5600.5</v>
+        <v>6115.78</v>
       </c>
       <c r="O1240" t="n">
-        <v>5600.5</v>
+        <v>12231.56</v>
       </c>
       <c r="P1240" t="n">
-        <v>14000</v>
+        <v>15900</v>
       </c>
       <c r="Q1240" t="n">
-        <v>14000</v>
+        <v>31800</v>
       </c>
     </row>
     <row r="1241">
       <c r="A1241" t="inlineStr">
         <is>
-          <t>T183-LJ</t>
+          <t>T182</t>
         </is>
       </c>
       <c r="C1241" t="inlineStr">
         <is>
-          <t>ALCANCIA PELUCHE LUCES 25CM 9901-3</t>
+          <t>PELUCHE POKEMON X12 MOTIVOS 20CM COLG-8</t>
         </is>
       </c>
       <c r="E1241" t="inlineStr">
@@ -56699,27 +56699,27 @@
         <v>1</v>
       </c>
       <c r="N1241" t="n">
-        <v>23076.92</v>
+        <v>5600.5</v>
       </c>
       <c r="O1241" t="n">
-        <v>23076.92</v>
+        <v>5600.5</v>
       </c>
       <c r="P1241" t="n">
-        <v>30000</v>
+        <v>14000</v>
       </c>
       <c r="Q1241" t="n">
-        <v>30000</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="1242">
       <c r="A1242" t="inlineStr">
         <is>
-          <t>T209-LJ</t>
+          <t>T183-LJ</t>
         </is>
       </c>
       <c r="C1242" t="inlineStr">
         <is>
-          <t>PELUCHE POKEMON 20CM GPOM-20</t>
+          <t>ALCANCIA PELUCHE LUCES 25CM 9901-3</t>
         </is>
       </c>
       <c r="E1242" t="inlineStr">
@@ -56745,27 +56745,27 @@
         <v>1</v>
       </c>
       <c r="N1242" t="n">
-        <v>10320</v>
+        <v>23076.92</v>
       </c>
       <c r="O1242" t="n">
-        <v>10320</v>
+        <v>23076.92</v>
       </c>
       <c r="P1242" t="n">
-        <v>12900</v>
+        <v>30000</v>
       </c>
       <c r="Q1242" t="n">
-        <v>12900</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="1243">
       <c r="A1243" t="inlineStr">
         <is>
-          <t>T210-LJ</t>
+          <t>T209-LJ</t>
         </is>
       </c>
       <c r="C1243" t="inlineStr">
         <is>
-          <t>PELUCHE SURTIDOS 25CM ECO-SUR25PER</t>
+          <t>PELUCHE POKEMON 20CM GPOM-20</t>
         </is>
       </c>
       <c r="E1243" t="inlineStr">
@@ -56779,7 +56779,7 @@
         </is>
       </c>
       <c r="J1243" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K1243" t="n">
         <v>0</v>
@@ -56788,30 +56788,30 @@
         <v>0</v>
       </c>
       <c r="M1243" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N1243" t="n">
-        <v>7920</v>
+        <v>10320</v>
       </c>
       <c r="O1243" t="n">
-        <v>47520</v>
+        <v>10320</v>
       </c>
       <c r="P1243" t="n">
-        <v>9900</v>
+        <v>12900</v>
       </c>
       <c r="Q1243" t="n">
-        <v>59400</v>
+        <v>12900</v>
       </c>
     </row>
     <row r="1244">
       <c r="A1244" t="inlineStr">
         <is>
-          <t>T219</t>
+          <t>T210-LJ</t>
         </is>
       </c>
       <c r="C1244" t="inlineStr">
         <is>
-          <t>PELUCHE ZOOLOGICO PQÑ SUR05-25</t>
+          <t>PELUCHE SURTIDOS 25CM ECO-SUR25PER</t>
         </is>
       </c>
       <c r="E1244" t="inlineStr">
@@ -56825,7 +56825,7 @@
         </is>
       </c>
       <c r="J1244" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="K1244" t="n">
         <v>0</v>
@@ -56834,30 +56834,30 @@
         <v>0</v>
       </c>
       <c r="M1244" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="N1244" t="n">
-        <v>8746.92</v>
+        <v>7920</v>
       </c>
       <c r="O1244" t="n">
-        <v>236166.84</v>
+        <v>47520</v>
       </c>
       <c r="P1244" t="n">
-        <v>11000</v>
+        <v>9900</v>
       </c>
       <c r="Q1244" t="n">
-        <v>297000</v>
+        <v>59400</v>
       </c>
     </row>
     <row r="1245">
       <c r="A1245" t="inlineStr">
         <is>
-          <t>T229-LJ</t>
+          <t>T219</t>
         </is>
       </c>
       <c r="C1245" t="inlineStr">
         <is>
-          <t>TAPA OJOS  ANIMALES 20CM TAP-ANI</t>
+          <t>PELUCHE ZOOLOGICO PQÑ SUR05-25</t>
         </is>
       </c>
       <c r="E1245" t="inlineStr">
@@ -56871,7 +56871,7 @@
         </is>
       </c>
       <c r="J1245" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="K1245" t="n">
         <v>0</v>
@@ -56880,30 +56880,30 @@
         <v>0</v>
       </c>
       <c r="M1245" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="N1245" t="n">
-        <v>14400</v>
+        <v>8746.92</v>
       </c>
       <c r="O1245" t="n">
-        <v>14400</v>
+        <v>236166.84</v>
       </c>
       <c r="P1245" t="n">
-        <v>18000</v>
+        <v>11000</v>
       </c>
       <c r="Q1245" t="n">
-        <v>18000</v>
+        <v>297000</v>
       </c>
     </row>
     <row r="1246">
       <c r="A1246" t="inlineStr">
         <is>
-          <t>T301</t>
+          <t>T229-LJ</t>
         </is>
       </c>
       <c r="C1246" t="inlineStr">
         <is>
-          <t>PANTUFLAS MOSNTER INC M578</t>
+          <t>TAPA OJOS  ANIMALES 20CM TAP-ANI</t>
         </is>
       </c>
       <c r="E1246" t="inlineStr">
@@ -56929,27 +56929,27 @@
         <v>1</v>
       </c>
       <c r="N1246" t="n">
+        <v>14400</v>
+      </c>
+      <c r="O1246" t="n">
+        <v>14400</v>
+      </c>
+      <c r="P1246" t="n">
         <v>18000</v>
       </c>
-      <c r="O1246" t="n">
+      <c r="Q1246" t="n">
         <v>18000</v>
-      </c>
-      <c r="P1246" t="n">
-        <v>10000</v>
-      </c>
-      <c r="Q1246" t="n">
-        <v>10000</v>
       </c>
     </row>
     <row r="1247">
       <c r="A1247" t="inlineStr">
         <is>
-          <t>TB017</t>
+          <t>T301</t>
         </is>
       </c>
       <c r="C1247" t="inlineStr">
         <is>
-          <t>COJIN BARRIL PQ COJ-BAR-PP</t>
+          <t>PANTUFLAS MOSNTER INC M578</t>
         </is>
       </c>
       <c r="E1247" t="inlineStr">
@@ -56963,7 +56963,7 @@
         </is>
       </c>
       <c r="J1247" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K1247" t="n">
         <v>0</v>
@@ -56972,30 +56972,30 @@
         <v>0</v>
       </c>
       <c r="M1247" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N1247" t="n">
-        <v>21600</v>
+        <v>18000</v>
       </c>
       <c r="O1247" t="n">
-        <v>64800</v>
+        <v>18000</v>
       </c>
       <c r="P1247" t="n">
-        <v>27000</v>
+        <v>10000</v>
       </c>
       <c r="Q1247" t="n">
-        <v>81000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="1248">
       <c r="A1248" t="inlineStr">
         <is>
-          <t>TB018</t>
+          <t>TB017</t>
         </is>
       </c>
       <c r="C1248" t="inlineStr">
         <is>
-          <t>COJIN FRASES MED COJ-ANI-M</t>
+          <t>COJIN BARRIL PQ COJ-BAR-PP</t>
         </is>
       </c>
       <c r="E1248" t="inlineStr">
@@ -57009,7 +57009,7 @@
         </is>
       </c>
       <c r="J1248" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1248" t="n">
         <v>0</v>
@@ -57018,30 +57018,30 @@
         <v>0</v>
       </c>
       <c r="M1248" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N1248" t="n">
-        <v>22800</v>
+        <v>21600</v>
       </c>
       <c r="O1248" t="n">
-        <v>45600</v>
+        <v>64800</v>
       </c>
       <c r="P1248" t="n">
-        <v>28500</v>
+        <v>27000</v>
       </c>
       <c r="Q1248" t="n">
-        <v>57000</v>
+        <v>81000</v>
       </c>
     </row>
     <row r="1249">
       <c r="A1249" t="inlineStr">
         <is>
-          <t>TB019</t>
+          <t>TB018</t>
         </is>
       </c>
       <c r="C1249" t="inlineStr">
         <is>
-          <t>COJIN PELUCHE KUROMI KL-35</t>
+          <t>COJIN FRASES MED COJ-ANI-M</t>
         </is>
       </c>
       <c r="E1249" t="inlineStr">
@@ -57055,7 +57055,7 @@
         </is>
       </c>
       <c r="J1249" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1249" t="n">
         <v>0</v>
@@ -57064,30 +57064,30 @@
         <v>0</v>
       </c>
       <c r="M1249" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N1249" t="n">
-        <v>0</v>
+        <v>22800</v>
       </c>
       <c r="O1249" t="n">
-        <v>0</v>
+        <v>45600</v>
       </c>
       <c r="P1249" t="n">
-        <v>43900</v>
+        <v>28500</v>
       </c>
       <c r="Q1249" t="n">
-        <v>43900</v>
+        <v>57000</v>
       </c>
     </row>
     <row r="1250">
       <c r="A1250" t="inlineStr">
         <is>
-          <t>TB027</t>
+          <t>TB019</t>
         </is>
       </c>
       <c r="C1250" t="inlineStr">
         <is>
-          <t>PELUCHE PATO SOMBRERO 30CM SYL-24</t>
+          <t>COJIN PELUCHE KUROMI KL-35</t>
         </is>
       </c>
       <c r="E1250" t="inlineStr">
@@ -57113,27 +57113,27 @@
         <v>1</v>
       </c>
       <c r="N1250" t="n">
-        <v>14400</v>
+        <v>0</v>
       </c>
       <c r="O1250" t="n">
-        <v>14400</v>
+        <v>0</v>
       </c>
       <c r="P1250" t="n">
-        <v>18000</v>
+        <v>43900</v>
       </c>
       <c r="Q1250" t="n">
-        <v>18000</v>
+        <v>43900</v>
       </c>
     </row>
     <row r="1251">
       <c r="A1251" t="inlineStr">
         <is>
-          <t>TB028</t>
+          <t>TB027</t>
         </is>
       </c>
       <c r="C1251" t="inlineStr">
         <is>
-          <t>COJIN COBIJA ELEFANTE LUMINOSO 821-1L</t>
+          <t>PELUCHE PATO SOMBRERO 30CM SYL-24</t>
         </is>
       </c>
       <c r="E1251" t="inlineStr">
@@ -57147,7 +57147,7 @@
         </is>
       </c>
       <c r="J1251" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K1251" t="n">
         <v>0</v>
@@ -57156,30 +57156,30 @@
         <v>0</v>
       </c>
       <c r="M1251" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N1251" t="n">
-        <v>47796.1625</v>
+        <v>14400</v>
       </c>
       <c r="O1251" t="n">
-        <v>95592.325</v>
+        <v>14400</v>
       </c>
       <c r="P1251" t="n">
-        <v>54000</v>
+        <v>18000</v>
       </c>
       <c r="Q1251" t="n">
-        <v>108000</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="1252">
       <c r="A1252" t="inlineStr">
         <is>
-          <t>TB029</t>
+          <t>TB028</t>
         </is>
       </c>
       <c r="C1252" t="inlineStr">
         <is>
-          <t>CANGURO PELUCHE STD CAN-ANI-01</t>
+          <t>COJIN COBIJA ELEFANTE LUMINOSO 821-1L</t>
         </is>
       </c>
       <c r="E1252" t="inlineStr">
@@ -57205,27 +57205,27 @@
         <v>2</v>
       </c>
       <c r="N1252" t="n">
-        <v>10000</v>
+        <v>47796.1625</v>
       </c>
       <c r="O1252" t="n">
-        <v>20000</v>
+        <v>95592.325</v>
       </c>
       <c r="P1252" t="n">
-        <v>12500</v>
+        <v>54000</v>
       </c>
       <c r="Q1252" t="n">
-        <v>25000</v>
+        <v>108000</v>
       </c>
     </row>
     <row r="1253">
       <c r="A1253" t="inlineStr">
         <is>
-          <t>TB032</t>
+          <t>TB029</t>
         </is>
       </c>
       <c r="C1253" t="inlineStr">
         <is>
-          <t>BOLSO STICH BOL-ST</t>
+          <t>CANGURO PELUCHE STD CAN-ANI-01</t>
         </is>
       </c>
       <c r="E1253" t="inlineStr">
@@ -57239,7 +57239,7 @@
         </is>
       </c>
       <c r="J1253" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1253" t="n">
         <v>0</v>
@@ -57248,30 +57248,30 @@
         <v>0</v>
       </c>
       <c r="M1253" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N1253" t="n">
-        <v>19920</v>
+        <v>10000</v>
       </c>
       <c r="O1253" t="n">
-        <v>19920</v>
+        <v>20000</v>
       </c>
       <c r="P1253" t="n">
-        <v>24900</v>
+        <v>12500</v>
       </c>
       <c r="Q1253" t="n">
-        <v>24900</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="1254">
       <c r="A1254" t="inlineStr">
         <is>
-          <t>TB036</t>
+          <t>TB032</t>
         </is>
       </c>
       <c r="C1254" t="inlineStr">
         <is>
-          <t>PELUCHE PRINCESA MARIO 30CM PRI-528</t>
+          <t>BOLSO STICH BOL-ST</t>
         </is>
       </c>
       <c r="E1254" t="inlineStr">
@@ -57285,7 +57285,7 @@
         </is>
       </c>
       <c r="J1254" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K1254" t="n">
         <v>0</v>
@@ -57294,30 +57294,30 @@
         <v>0</v>
       </c>
       <c r="M1254" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N1254" t="n">
-        <v>11400.5</v>
+        <v>19920</v>
       </c>
       <c r="O1254" t="n">
-        <v>45602</v>
+        <v>19920</v>
       </c>
       <c r="P1254" t="n">
-        <v>28500</v>
+        <v>24900</v>
       </c>
       <c r="Q1254" t="n">
-        <v>114000</v>
+        <v>24900</v>
       </c>
     </row>
     <row r="1255">
       <c r="A1255" t="inlineStr">
         <is>
-          <t>TB037</t>
+          <t>TB036</t>
         </is>
       </c>
       <c r="C1255" t="inlineStr">
         <is>
-          <t>PELUCHE DIGIMON 20CM MD-20</t>
+          <t>PELUCHE PRINCESA MARIO 30CM PRI-528</t>
         </is>
       </c>
       <c r="E1255" t="inlineStr">
@@ -57331,7 +57331,7 @@
         </is>
       </c>
       <c r="J1255" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="K1255" t="n">
         <v>0</v>
@@ -57340,30 +57340,30 @@
         <v>0</v>
       </c>
       <c r="M1255" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="N1255" t="n">
-        <v>12720</v>
+        <v>11400.5</v>
       </c>
       <c r="O1255" t="n">
-        <v>165360</v>
+        <v>45602</v>
       </c>
       <c r="P1255" t="n">
-        <v>15900</v>
+        <v>28500</v>
       </c>
       <c r="Q1255" t="n">
-        <v>206700</v>
+        <v>114000</v>
       </c>
     </row>
     <row r="1256">
       <c r="A1256" t="inlineStr">
         <is>
-          <t>TB039</t>
+          <t>TB037</t>
         </is>
       </c>
       <c r="C1256" t="inlineStr">
         <is>
-          <t>LLAVERO PELUCHE GDE 11A-PEL/GRND</t>
+          <t>PELUCHE DIGIMON 20CM MD-20</t>
         </is>
       </c>
       <c r="E1256" t="inlineStr">
@@ -57377,7 +57377,7 @@
         </is>
       </c>
       <c r="J1256" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="K1256" t="n">
         <v>0</v>
@@ -57386,30 +57386,30 @@
         <v>0</v>
       </c>
       <c r="M1256" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="N1256" t="n">
-        <v>9520</v>
+        <v>12720</v>
       </c>
       <c r="O1256" t="n">
-        <v>47600</v>
+        <v>165360</v>
       </c>
       <c r="P1256" t="n">
-        <v>11900</v>
+        <v>15900</v>
       </c>
       <c r="Q1256" t="n">
-        <v>59500</v>
+        <v>206700</v>
       </c>
     </row>
     <row r="1257">
       <c r="A1257" t="inlineStr">
         <is>
-          <t>TB040</t>
+          <t>TB039</t>
         </is>
       </c>
       <c r="C1257" t="inlineStr">
         <is>
-          <t>PELUCHE ECO ZOOLOGICO 40CM 774-2</t>
+          <t>LLAVERO PELUCHE GDE 11A-PEL/GRND</t>
         </is>
       </c>
       <c r="E1257" t="inlineStr">
@@ -57435,32 +57435,32 @@
         <v>5</v>
       </c>
       <c r="N1257" t="n">
-        <v>7547.98</v>
+        <v>9520</v>
       </c>
       <c r="O1257" t="n">
-        <v>37739.89999999999</v>
+        <v>47600</v>
       </c>
       <c r="P1257" t="n">
-        <v>23900</v>
+        <v>11900</v>
       </c>
       <c r="Q1257" t="n">
-        <v>119500</v>
+        <v>59500</v>
       </c>
     </row>
     <row r="1258">
       <c r="A1258" t="inlineStr">
         <is>
-          <t>TB045</t>
+          <t>TB040</t>
         </is>
       </c>
       <c r="C1258" t="inlineStr">
         <is>
-          <t>PELUCHE ZOOLOGICO GDE SUR05-40</t>
+          <t>PELUCHE ECO ZOOLOGICO 40CM 774-2</t>
         </is>
       </c>
       <c r="E1258" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PELUCHES</t>
         </is>
       </c>
       <c r="I1258" t="inlineStr">
@@ -57469,7 +57469,7 @@
         </is>
       </c>
       <c r="J1258" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K1258" t="n">
         <v>0</v>
@@ -57478,35 +57478,35 @@
         <v>0</v>
       </c>
       <c r="M1258" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N1258" t="n">
-        <v>24230.77</v>
+        <v>7547.98</v>
       </c>
       <c r="O1258" t="n">
-        <v>24230.77</v>
+        <v>37739.89999999999</v>
       </c>
       <c r="P1258" t="n">
-        <v>31500</v>
+        <v>23900</v>
       </c>
       <c r="Q1258" t="n">
-        <v>31500</v>
+        <v>119500</v>
       </c>
     </row>
     <row r="1259">
       <c r="A1259" t="inlineStr">
         <is>
-          <t>TB050</t>
+          <t>TB045</t>
         </is>
       </c>
       <c r="C1259" t="inlineStr">
         <is>
-          <t>PELUCHE ANIMALES PELUSA 20CM ANI01-20</t>
+          <t>PELUCHE ZOOLOGICO GDE SUR05-40</t>
         </is>
       </c>
       <c r="E1259" t="inlineStr">
         <is>
-          <t>PELUCHES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I1259" t="inlineStr">
@@ -57515,7 +57515,7 @@
         </is>
       </c>
       <c r="J1259" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K1259" t="n">
         <v>0</v>
@@ -57524,30 +57524,30 @@
         <v>0</v>
       </c>
       <c r="M1259" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N1259" t="n">
-        <v>13520</v>
+        <v>24230.77</v>
       </c>
       <c r="O1259" t="n">
-        <v>40560</v>
+        <v>24230.77</v>
       </c>
       <c r="P1259" t="n">
-        <v>16900</v>
+        <v>31500</v>
       </c>
       <c r="Q1259" t="n">
-        <v>50700</v>
+        <v>31500</v>
       </c>
     </row>
     <row r="1260">
       <c r="A1260" t="inlineStr">
         <is>
-          <t>TB057</t>
+          <t>TB050</t>
         </is>
       </c>
       <c r="C1260" t="inlineStr">
         <is>
-          <t>LLAVERO OSO FLOR PELUCHE LLA-FLO</t>
+          <t>PELUCHE ANIMALES PELUSA 20CM ANI01-20</t>
         </is>
       </c>
       <c r="E1260" t="inlineStr">
@@ -57561,7 +57561,7 @@
         </is>
       </c>
       <c r="J1260" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K1260" t="n">
         <v>0</v>
@@ -57570,30 +57570,30 @@
         <v>0</v>
       </c>
       <c r="M1260" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N1260" t="n">
-        <v>5520</v>
+        <v>13520</v>
       </c>
       <c r="O1260" t="n">
-        <v>5520</v>
+        <v>40560</v>
       </c>
       <c r="P1260" t="n">
-        <v>6900</v>
+        <v>16900</v>
       </c>
       <c r="Q1260" t="n">
-        <v>6900</v>
+        <v>50700</v>
       </c>
     </row>
     <row r="1261">
       <c r="A1261" t="inlineStr">
         <is>
-          <t>TB060</t>
+          <t>TB057</t>
         </is>
       </c>
       <c r="C1261" t="inlineStr">
         <is>
-          <t>PELUCHE OSO BUSO CARROS 20CM CYX-20</t>
+          <t>LLAVERO OSO FLOR PELUCHE LLA-FLO</t>
         </is>
       </c>
       <c r="E1261" t="inlineStr">
@@ -57607,7 +57607,7 @@
         </is>
       </c>
       <c r="J1261" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K1261" t="n">
         <v>0</v>
@@ -57616,30 +57616,30 @@
         <v>0</v>
       </c>
       <c r="M1261" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N1261" t="n">
-        <v>17200</v>
+        <v>5520</v>
       </c>
       <c r="O1261" t="n">
-        <v>34400</v>
+        <v>5520</v>
       </c>
       <c r="P1261" t="n">
-        <v>21500</v>
+        <v>6900</v>
       </c>
       <c r="Q1261" t="n">
-        <v>43000</v>
+        <v>6900</v>
       </c>
     </row>
     <row r="1262">
       <c r="A1262" t="inlineStr">
         <is>
-          <t>TB072</t>
+          <t>TB060</t>
         </is>
       </c>
       <c r="C1262" t="inlineStr">
         <is>
-          <t>PELUCHE PEREZOSO 30CM 4390-30</t>
+          <t>PELUCHE OSO BUSO CARROS 20CM CYX-20</t>
         </is>
       </c>
       <c r="E1262" t="inlineStr">
@@ -57653,7 +57653,7 @@
         </is>
       </c>
       <c r="J1262" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1262" t="n">
         <v>0</v>
@@ -57662,30 +57662,30 @@
         <v>0</v>
       </c>
       <c r="M1262" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N1262" t="n">
-        <v>26320</v>
+        <v>17200</v>
       </c>
       <c r="O1262" t="n">
-        <v>26320</v>
+        <v>34400</v>
       </c>
       <c r="P1262" t="n">
-        <v>32900</v>
+        <v>21500</v>
       </c>
       <c r="Q1262" t="n">
-        <v>32900</v>
+        <v>43000</v>
       </c>
     </row>
     <row r="1263">
       <c r="A1263" t="inlineStr">
         <is>
-          <t>TB074</t>
+          <t>TB072</t>
         </is>
       </c>
       <c r="C1263" t="inlineStr">
         <is>
-          <t>PELUCHE PATO COMUNISTA 50CM PCG-50</t>
+          <t>PELUCHE PEREZOSO 30CM 4390-30</t>
         </is>
       </c>
       <c r="E1263" t="inlineStr">
@@ -57711,27 +57711,27 @@
         <v>1</v>
       </c>
       <c r="N1263" t="n">
-        <v>38000</v>
+        <v>26320</v>
       </c>
       <c r="O1263" t="n">
-        <v>38000</v>
+        <v>26320</v>
       </c>
       <c r="P1263" t="n">
-        <v>47500</v>
+        <v>32900</v>
       </c>
       <c r="Q1263" t="n">
-        <v>47500</v>
+        <v>32900</v>
       </c>
     </row>
     <row r="1264">
       <c r="A1264" t="inlineStr">
         <is>
-          <t>TB076</t>
+          <t>TB074</t>
         </is>
       </c>
       <c r="C1264" t="inlineStr">
         <is>
-          <t>PELUCHE TIGER 60CM YDD-2211-65</t>
+          <t>PELUCHE PATO COMUNISTA 50CM PCG-50</t>
         </is>
       </c>
       <c r="E1264" t="inlineStr">
@@ -57745,7 +57745,7 @@
         </is>
       </c>
       <c r="J1264" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K1264" t="n">
         <v>0</v>
@@ -57754,30 +57754,30 @@
         <v>0</v>
       </c>
       <c r="M1264" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N1264" t="n">
-        <v>53200</v>
+        <v>38000</v>
       </c>
       <c r="O1264" t="n">
-        <v>106400</v>
+        <v>38000</v>
       </c>
       <c r="P1264" t="n">
-        <v>66500</v>
+        <v>47500</v>
       </c>
       <c r="Q1264" t="n">
-        <v>133000</v>
+        <v>47500</v>
       </c>
     </row>
     <row r="1265">
       <c r="A1265" t="inlineStr">
         <is>
-          <t>TB077</t>
+          <t>TB076</t>
         </is>
       </c>
       <c r="C1265" t="inlineStr">
         <is>
-          <t>COJIN PELUCHE KUROMI COL-KCI</t>
+          <t>PELUCHE TIGER 60CM YDD-2211-65</t>
         </is>
       </c>
       <c r="E1265" t="inlineStr">
@@ -57803,27 +57803,27 @@
         <v>2</v>
       </c>
       <c r="N1265" t="n">
-        <v>27120</v>
+        <v>53200</v>
       </c>
       <c r="O1265" t="n">
-        <v>54240</v>
+        <v>106400</v>
       </c>
       <c r="P1265" t="n">
-        <v>33900</v>
+        <v>66500</v>
       </c>
       <c r="Q1265" t="n">
-        <v>67800</v>
+        <v>133000</v>
       </c>
     </row>
     <row r="1266">
       <c r="A1266" t="inlineStr">
         <is>
-          <t>TB100</t>
+          <t>TB077</t>
         </is>
       </c>
       <c r="C1266" t="inlineStr">
         <is>
-          <t>PELUCHE ADV NUEVA TEMPORADA 20 CM</t>
+          <t>COJIN PELUCHE KUROMI COL-KCI</t>
         </is>
       </c>
       <c r="E1266" t="inlineStr">
@@ -57837,7 +57837,7 @@
         </is>
       </c>
       <c r="J1266" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K1266" t="n">
         <v>0</v>
@@ -57846,30 +57846,30 @@
         <v>0</v>
       </c>
       <c r="M1266" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N1266" t="n">
-        <v>5192.71</v>
+        <v>27120</v>
       </c>
       <c r="O1266" t="n">
-        <v>5192.71</v>
+        <v>54240</v>
       </c>
       <c r="P1266" t="n">
-        <v>13500</v>
+        <v>33900</v>
       </c>
       <c r="Q1266" t="n">
-        <v>13500</v>
+        <v>67800</v>
       </c>
     </row>
     <row r="1267">
       <c r="A1267" t="inlineStr">
         <is>
-          <t>TB114</t>
+          <t>TB100</t>
         </is>
       </c>
       <c r="C1267" t="inlineStr">
         <is>
-          <t>COJIN FRASES PQÑ PAGO-22</t>
+          <t>PELUCHE ADV NUEVA TEMPORADA 20 CM</t>
         </is>
       </c>
       <c r="E1267" t="inlineStr">
@@ -57883,7 +57883,7 @@
         </is>
       </c>
       <c r="J1267" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K1267" t="n">
         <v>0</v>
@@ -57892,30 +57892,30 @@
         <v>0</v>
       </c>
       <c r="M1267" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N1267" t="n">
-        <v>8000</v>
+        <v>5192.71</v>
       </c>
       <c r="O1267" t="n">
-        <v>32000</v>
+        <v>5192.71</v>
       </c>
       <c r="P1267" t="n">
-        <v>10000</v>
+        <v>13500</v>
       </c>
       <c r="Q1267" t="n">
-        <v>40000</v>
+        <v>13500</v>
       </c>
     </row>
     <row r="1268">
       <c r="A1268" t="inlineStr">
         <is>
-          <t>TB115</t>
+          <t>TB114</t>
         </is>
       </c>
       <c r="C1268" t="inlineStr">
         <is>
-          <t>COJIN FRASES PQÑ BZ22-22</t>
+          <t>COJIN FRASES PQÑ PAGO-22</t>
         </is>
       </c>
       <c r="E1268" t="inlineStr">
@@ -57929,7 +57929,7 @@
         </is>
       </c>
       <c r="J1268" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K1268" t="n">
         <v>0</v>
@@ -57938,30 +57938,30 @@
         <v>0</v>
       </c>
       <c r="M1268" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N1268" t="n">
-        <v>8006.3731111111</v>
+        <v>8000</v>
       </c>
       <c r="O1268" t="n">
-        <v>16012.7462222222</v>
+        <v>32000</v>
       </c>
       <c r="P1268" t="n">
         <v>10000</v>
       </c>
       <c r="Q1268" t="n">
-        <v>20000</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="1269">
       <c r="A1269" t="inlineStr">
         <is>
-          <t>TB122</t>
+          <t>TB115</t>
         </is>
       </c>
       <c r="C1269" t="inlineStr">
         <is>
-          <t>PELUCHE DRAGON 50CM DRAG-50</t>
+          <t>COJIN FRASES PQÑ BZ22-22</t>
         </is>
       </c>
       <c r="E1269" t="inlineStr">
@@ -57975,7 +57975,7 @@
         </is>
       </c>
       <c r="J1269" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K1269" t="n">
         <v>0</v>
@@ -57984,38 +57984,35 @@
         <v>0</v>
       </c>
       <c r="M1269" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N1269" t="n">
-        <v>47920</v>
+        <v>8006.3731111111</v>
       </c>
       <c r="O1269" t="n">
-        <v>143760</v>
+        <v>16012.7462222222</v>
       </c>
       <c r="P1269" t="n">
-        <v>59900</v>
+        <v>10000</v>
       </c>
       <c r="Q1269" t="n">
-        <v>179700</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="1270">
       <c r="A1270" t="inlineStr">
         <is>
-          <t>X1499</t>
-        </is>
-      </c>
-      <c r="B1270" t="n">
-        <v>6901353020520</v>
+          <t>TB122</t>
+        </is>
       </c>
       <c r="C1270" t="inlineStr">
         <is>
-          <t>ESPADA LUZ LASER X1499</t>
+          <t>PELUCHE DRAGON 50CM DRAG-50</t>
         </is>
       </c>
       <c r="E1270" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>PELUCHES</t>
         </is>
       </c>
       <c r="I1270" t="inlineStr">
@@ -58024,7 +58021,7 @@
         </is>
       </c>
       <c r="J1270" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="K1270" t="n">
         <v>0</v>
@@ -58033,64 +58030,113 @@
         <v>0</v>
       </c>
       <c r="M1270" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="N1270" t="n">
-        <v>4538.35</v>
+        <v>47920</v>
       </c>
       <c r="O1270" t="n">
-        <v>58998.55</v>
+        <v>143760</v>
       </c>
       <c r="P1270" t="n">
-        <v>5500</v>
+        <v>59900</v>
       </c>
       <c r="Q1270" t="n">
-        <v>71500</v>
+        <v>179700</v>
       </c>
     </row>
     <row r="1271">
       <c r="A1271" t="inlineStr">
         <is>
+          <t>X1499</t>
+        </is>
+      </c>
+      <c r="B1271" t="n">
+        <v>6901353020520</v>
+      </c>
+      <c r="C1271" t="inlineStr">
+        <is>
+          <t>ESPADA LUZ LASER X1499</t>
+        </is>
+      </c>
+      <c r="E1271" t="inlineStr">
+        <is>
+          <t>PIÑATERIA</t>
+        </is>
+      </c>
+      <c r="I1271" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="J1271" t="n">
+        <v>13</v>
+      </c>
+      <c r="K1271" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1271" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1271" t="n">
+        <v>13</v>
+      </c>
+      <c r="N1271" t="n">
+        <v>4538.35</v>
+      </c>
+      <c r="O1271" t="n">
+        <v>58998.55</v>
+      </c>
+      <c r="P1271" t="n">
+        <v>5500</v>
+      </c>
+      <c r="Q1271" t="n">
+        <v>71500</v>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" t="inlineStr">
+        <is>
           <t>XP-2986</t>
         </is>
       </c>
-      <c r="C1271" t="inlineStr">
+      <c r="C1272" t="inlineStr">
         <is>
           <t>BORRADOR RETRACTIL COHETE XP-2986</t>
         </is>
       </c>
-      <c r="E1271" t="inlineStr">
+      <c r="E1272" t="inlineStr">
         <is>
           <t>JUGUETERIA</t>
         </is>
       </c>
-      <c r="I1271" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="J1271" t="n">
+      <c r="I1272" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="J1272" t="n">
         <v>19</v>
       </c>
-      <c r="K1271" t="n">
-        <v>0</v>
-      </c>
-      <c r="L1271" t="n">
-        <v>0</v>
-      </c>
-      <c r="M1271" t="n">
+      <c r="K1272" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1272" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1272" t="n">
         <v>19</v>
       </c>
-      <c r="N1271" t="n">
+      <c r="N1272" t="n">
         <v>2402.6741428571</v>
       </c>
-      <c r="O1271" t="n">
+      <c r="O1272" t="n">
         <v>45650.8087142849</v>
       </c>
-      <c r="P1271" t="n">
+      <c r="P1272" t="n">
         <v>3000</v>
       </c>
-      <c r="Q1271" t="n">
+      <c r="Q1272" t="n">
         <v>57000</v>
       </c>
     </row>

--- a/bodegas/LJ-101.xlsx
+++ b/bodegas/LJ-101.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-23</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-24</t>
         </is>
       </c>
     </row>
@@ -21094,13 +21094,13 @@
         </is>
       </c>
       <c r="J473" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K473" t="n">
         <v>0</v>
       </c>
       <c r="L473" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M473" t="n">
         <v>3</v>
@@ -31989,13 +31989,13 @@
         </is>
       </c>
       <c r="J711" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K711" t="n">
         <v>0</v>
       </c>
       <c r="L711" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M711" t="n">
         <v>2</v>
@@ -37436,22 +37436,22 @@
         <v>0</v>
       </c>
       <c r="L829" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M829" t="n">
-        <v>1180</v>
+        <v>1156</v>
       </c>
       <c r="N829" t="n">
         <v>517.28908220781</v>
       </c>
       <c r="O829" t="n">
-        <v>610401.1170052158</v>
+        <v>597986.1790322283</v>
       </c>
       <c r="P829" t="n">
         <v>900</v>
       </c>
       <c r="Q829" t="n">
-        <v>1062000</v>
+        <v>1040400</v>
       </c>
     </row>
     <row r="830">
@@ -38363,22 +38363,22 @@
         <v>0</v>
       </c>
       <c r="L849" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="M849" t="n">
-        <v>367</v>
+        <v>331</v>
       </c>
       <c r="N849" t="n">
         <v>703.79521051815</v>
       </c>
       <c r="O849" t="n">
-        <v>258292.8422601611</v>
+        <v>232956.2146815077</v>
       </c>
       <c r="P849" t="n">
         <v>900</v>
       </c>
       <c r="Q849" t="n">
-        <v>330300</v>
+        <v>297900</v>
       </c>
     </row>
     <row r="850">
@@ -49536,13 +49536,13 @@
         </is>
       </c>
       <c r="J1086" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="K1086" t="n">
         <v>0</v>
       </c>
       <c r="L1086" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M1086" t="n">
         <v>50</v>

--- a/bodegas/LJ-101.xlsx
+++ b/bodegas/LJ-101.xlsx
@@ -944,10 +944,10 @@
         <v>26</v>
       </c>
       <c r="N13" t="n">
-        <v>1811.3069785884</v>
+        <v>1811.307219032</v>
       </c>
       <c r="O13" t="n">
-        <v>47093.9814432984</v>
+        <v>47093.987694832</v>
       </c>
       <c r="P13" t="n">
         <v>2600</v>
@@ -1022,10 +1022,10 @@
         <v>50</v>
       </c>
       <c r="N15" t="n">
-        <v>3376.7464699454</v>
+        <v>3376.7464660832</v>
       </c>
       <c r="O15" t="n">
-        <v>168837.32349727</v>
+        <v>168837.32330416</v>
       </c>
       <c r="P15" t="n">
         <v>4500</v>
@@ -1495,22 +1495,22 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N27" t="n">
         <v>27000</v>
       </c>
       <c r="O27" t="n">
-        <v>324000</v>
+        <v>297000</v>
       </c>
       <c r="P27" t="n">
         <v>20000</v>
       </c>
       <c r="Q27" t="n">
-        <v>240000</v>
+        <v>220000</v>
       </c>
     </row>
     <row r="28">
@@ -4962,22 +4962,22 @@
         <v>0</v>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M109" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N109" t="n">
         <v>26280.41</v>
       </c>
       <c r="O109" t="n">
-        <v>578169.02</v>
+        <v>551888.61</v>
       </c>
       <c r="P109" t="n">
         <v>46500</v>
       </c>
       <c r="Q109" t="n">
-        <v>1023000</v>
+        <v>976500</v>
       </c>
     </row>
     <row r="110">
@@ -8026,22 +8026,22 @@
         <v>0</v>
       </c>
       <c r="L179" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M179" t="n">
-        <v>458</v>
+        <v>451</v>
       </c>
       <c r="N179" t="n">
-        <v>1098.0593600211</v>
+        <v>1098.059452236</v>
       </c>
       <c r="O179" t="n">
-        <v>502911.1868896638</v>
+        <v>495224.812958436</v>
       </c>
       <c r="P179" t="n">
         <v>1500</v>
       </c>
       <c r="Q179" t="n">
-        <v>687000</v>
+        <v>676500</v>
       </c>
     </row>
     <row r="180">
@@ -8472,22 +8472,22 @@
         <v>0</v>
       </c>
       <c r="L189" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M189" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N189" t="n">
         <v>13593.35</v>
       </c>
       <c r="O189" t="n">
-        <v>244680.3</v>
+        <v>231086.95</v>
       </c>
       <c r="P189" t="n">
         <v>25500</v>
       </c>
       <c r="Q189" t="n">
-        <v>459000</v>
+        <v>433500</v>
       </c>
     </row>
     <row r="190">
@@ -8685,22 +8685,22 @@
         <v>0</v>
       </c>
       <c r="L194" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M194" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N194" t="n">
         <v>4065.61</v>
       </c>
       <c r="O194" t="n">
-        <v>113837.08</v>
+        <v>105705.86</v>
       </c>
       <c r="P194" t="n">
         <v>5000</v>
       </c>
       <c r="Q194" t="n">
-        <v>140000</v>
+        <v>130000</v>
       </c>
     </row>
     <row r="195">
@@ -9041,22 +9041,22 @@
         <v>0</v>
       </c>
       <c r="L202" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M202" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N202" t="n">
-        <v>2582.2557508532</v>
+        <v>2582.2557353886</v>
       </c>
       <c r="O202" t="n">
-        <v>72303.1610238896</v>
+        <v>69720.9048554922</v>
       </c>
       <c r="P202" t="n">
         <v>4500</v>
       </c>
       <c r="Q202" t="n">
-        <v>126000</v>
+        <v>121500</v>
       </c>
     </row>
     <row r="203">
@@ -9185,10 +9185,10 @@
         <v>2</v>
       </c>
       <c r="N205" t="n">
-        <v>5216.8961296772</v>
+        <v>5216.8961258041</v>
       </c>
       <c r="O205" t="n">
-        <v>10433.7922593544</v>
+        <v>10433.7922516082</v>
       </c>
       <c r="P205" t="n">
         <v>8500</v>
@@ -9231,10 +9231,10 @@
         <v>6</v>
       </c>
       <c r="N206" t="n">
-        <v>2033.5487958115</v>
+        <v>2033.5474193548</v>
       </c>
       <c r="O206" t="n">
-        <v>12201.292774869</v>
+        <v>12201.2845161288</v>
       </c>
       <c r="P206" t="n">
         <v>4100</v>
@@ -9676,22 +9676,22 @@
         <v>0</v>
       </c>
       <c r="L216" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M216" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N216" t="n">
         <v>8214</v>
       </c>
       <c r="O216" t="n">
-        <v>410700</v>
+        <v>402486</v>
       </c>
       <c r="P216" t="n">
         <v>7900</v>
       </c>
       <c r="Q216" t="n">
-        <v>395000</v>
+        <v>387100</v>
       </c>
     </row>
     <row r="217">
@@ -9731,10 +9731,10 @@
         <v>85</v>
       </c>
       <c r="N217" t="n">
-        <v>3230.0672564612</v>
+        <v>3230.067250996</v>
       </c>
       <c r="O217" t="n">
-        <v>274555.716799202</v>
+        <v>274555.71633466</v>
       </c>
       <c r="P217" t="n">
         <v>6200</v>
@@ -10001,22 +10001,22 @@
         <v>0</v>
       </c>
       <c r="L223" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M223" t="n">
-        <v>1852</v>
+        <v>1842</v>
       </c>
       <c r="N223" t="n">
         <v>156.25</v>
       </c>
       <c r="O223" t="n">
-        <v>289375</v>
+        <v>287812.5</v>
       </c>
       <c r="P223" t="n">
         <v>250</v>
       </c>
       <c r="Q223" t="n">
-        <v>463000</v>
+        <v>460500</v>
       </c>
     </row>
     <row r="224">
@@ -10188,22 +10188,22 @@
         <v>0</v>
       </c>
       <c r="L227" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M227" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="N227" t="n">
         <v>6507</v>
       </c>
       <c r="O227" t="n">
-        <v>182196</v>
+        <v>162675</v>
       </c>
       <c r="P227" t="n">
         <v>9900</v>
       </c>
       <c r="Q227" t="n">
-        <v>277200</v>
+        <v>247500</v>
       </c>
     </row>
     <row r="228">
@@ -10281,10 +10281,10 @@
         <v>36</v>
       </c>
       <c r="N229" t="n">
-        <v>3795.7100075514</v>
+        <v>3795.7100075529</v>
       </c>
       <c r="O229" t="n">
-        <v>136645.5602718504</v>
+        <v>136645.5602719044</v>
       </c>
       <c r="P229" t="n">
         <v>6200</v>
@@ -10408,22 +10408,22 @@
         <v>0</v>
       </c>
       <c r="L232" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M232" t="n">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="N232" t="n">
         <v>4357.55</v>
       </c>
       <c r="O232" t="n">
-        <v>806146.75</v>
+        <v>788716.55</v>
       </c>
       <c r="P232" t="n">
         <v>7500</v>
       </c>
       <c r="Q232" t="n">
-        <v>1387500</v>
+        <v>1357500</v>
       </c>
     </row>
     <row r="233">
@@ -10506,10 +10506,10 @@
         <v>12</v>
       </c>
       <c r="N234" t="n">
-        <v>4890.9300486322</v>
+        <v>4890.9300487805</v>
       </c>
       <c r="O234" t="n">
-        <v>58691.1605835864</v>
+        <v>58691.160585366</v>
       </c>
       <c r="P234" t="n">
         <v>8200</v>
@@ -10647,10 +10647,10 @@
         <v>36</v>
       </c>
       <c r="N237" t="n">
-        <v>5484.9492105263</v>
+        <v>5484.9500917431</v>
       </c>
       <c r="O237" t="n">
-        <v>197458.1715789468</v>
+        <v>197458.2033027516</v>
       </c>
       <c r="P237" t="n">
         <v>8500</v>
@@ -10736,22 +10736,22 @@
         <v>0</v>
       </c>
       <c r="L239" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M239" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N239" t="n">
         <v>5888</v>
       </c>
       <c r="O239" t="n">
-        <v>41216</v>
+        <v>29440</v>
       </c>
       <c r="P239" t="n">
         <v>9500</v>
       </c>
       <c r="Q239" t="n">
-        <v>66500</v>
+        <v>47500</v>
       </c>
     </row>
     <row r="240">
@@ -10869,22 +10869,22 @@
         <v>0</v>
       </c>
       <c r="L242" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M242" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="N242" t="n">
-        <v>2267.0481451951</v>
+        <v>2267.0481436371</v>
       </c>
       <c r="O242" t="n">
-        <v>188164.9960511933</v>
+        <v>183630.8996346051</v>
       </c>
       <c r="P242" t="n">
         <v>3900</v>
       </c>
       <c r="Q242" t="n">
-        <v>323700</v>
+        <v>315900</v>
       </c>
     </row>
     <row r="243">
@@ -10915,22 +10915,22 @@
         <v>0</v>
       </c>
       <c r="L243" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M243" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N243" t="n">
         <v>7041</v>
       </c>
       <c r="O243" t="n">
-        <v>63369</v>
+        <v>56328</v>
       </c>
       <c r="P243" t="n">
         <v>11500</v>
       </c>
       <c r="Q243" t="n">
-        <v>103500</v>
+        <v>92000</v>
       </c>
     </row>
     <row r="244">
@@ -11099,22 +11099,22 @@
         <v>0</v>
       </c>
       <c r="L247" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M247" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="N247" t="n">
         <v>8662</v>
       </c>
       <c r="O247" t="n">
-        <v>77958</v>
+        <v>51972</v>
       </c>
       <c r="P247" t="n">
         <v>14200</v>
       </c>
       <c r="Q247" t="n">
-        <v>127800</v>
+        <v>85200</v>
       </c>
     </row>
     <row r="248">
@@ -11186,22 +11186,22 @@
         <v>0</v>
       </c>
       <c r="L249" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M249" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N249" t="n">
         <v>10716.34</v>
       </c>
       <c r="O249" t="n">
-        <v>64298.04</v>
+        <v>53581.7</v>
       </c>
       <c r="P249" t="n">
         <v>39000</v>
       </c>
       <c r="Q249" t="n">
-        <v>234000</v>
+        <v>195000</v>
       </c>
     </row>
     <row r="250">
@@ -11495,10 +11495,10 @@
         <v>134</v>
       </c>
       <c r="N256" t="n">
-        <v>3240.8500325733</v>
+        <v>3240.8500369004</v>
       </c>
       <c r="O256" t="n">
-        <v>434273.9043648222</v>
+        <v>434273.9049446536</v>
       </c>
       <c r="P256" t="n">
         <v>5200</v>
@@ -11627,22 +11627,22 @@
         <v>0</v>
       </c>
       <c r="L259" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M259" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="N259" t="n">
         <v>8154</v>
       </c>
       <c r="O259" t="n">
-        <v>130464</v>
+        <v>97848</v>
       </c>
       <c r="P259" t="n">
         <v>13500</v>
       </c>
       <c r="Q259" t="n">
-        <v>216000</v>
+        <v>162000</v>
       </c>
     </row>
     <row r="260">
@@ -11679,10 +11679,10 @@
         <v>11</v>
       </c>
       <c r="N260" t="n">
-        <v>14822.378850987</v>
+        <v>14822.378849611</v>
       </c>
       <c r="O260" t="n">
-        <v>163046.167360857</v>
+        <v>163046.167345721</v>
       </c>
       <c r="P260" t="n">
         <v>24900</v>
@@ -11766,22 +11766,22 @@
         <v>0</v>
       </c>
       <c r="L262" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="M262" t="n">
-        <v>338</v>
+        <v>312</v>
       </c>
       <c r="N262" t="n">
         <v>2090.85</v>
       </c>
       <c r="O262" t="n">
-        <v>706707.2999999999</v>
+        <v>652345.2</v>
       </c>
       <c r="P262" t="n">
         <v>2900</v>
       </c>
       <c r="Q262" t="n">
-        <v>980200</v>
+        <v>904800</v>
       </c>
     </row>
     <row r="263">
@@ -12677,10 +12677,10 @@
         <v>6</v>
       </c>
       <c r="N282" t="n">
-        <v>4242.5421445221</v>
+        <v>4242.5421749409</v>
       </c>
       <c r="O282" t="n">
-        <v>25455.2528671326</v>
+        <v>25455.2530496454</v>
       </c>
       <c r="P282" t="n">
         <v>5900</v>
@@ -12767,10 +12767,10 @@
         <v>20</v>
       </c>
       <c r="N284" t="n">
-        <v>3041.6600131579</v>
+        <v>3041.660013245</v>
       </c>
       <c r="O284" t="n">
-        <v>60833.200263158</v>
+        <v>60833.2002649</v>
       </c>
       <c r="P284" t="n">
         <v>5500</v>
@@ -12895,10 +12895,10 @@
         <v>1</v>
       </c>
       <c r="N287" t="n">
-        <v>4372.2107896237</v>
+        <v>4372.2107901305</v>
       </c>
       <c r="O287" t="n">
-        <v>4372.2107896237</v>
+        <v>4372.2107901305</v>
       </c>
       <c r="P287" t="n">
         <v>7500</v>
@@ -13066,22 +13066,22 @@
         <v>0</v>
       </c>
       <c r="L291" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M291" t="n">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="N291" t="n">
-        <v>1592.5668693558</v>
+        <v>1592.5667761934</v>
       </c>
       <c r="O291" t="n">
-        <v>351957.2781276318</v>
+        <v>347179.5572101612</v>
       </c>
       <c r="P291" t="n">
         <v>3900</v>
       </c>
       <c r="Q291" t="n">
-        <v>861900</v>
+        <v>850200</v>
       </c>
     </row>
     <row r="292">
@@ -13194,22 +13194,22 @@
         <v>0</v>
       </c>
       <c r="L294" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M294" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="N294" t="n">
         <v>3655.96</v>
       </c>
       <c r="O294" t="n">
-        <v>212045.68</v>
+        <v>204733.76</v>
       </c>
       <c r="P294" t="n">
         <v>5500</v>
       </c>
       <c r="Q294" t="n">
-        <v>319000</v>
+        <v>308000</v>
       </c>
     </row>
     <row r="295">
@@ -13504,25 +13504,25 @@
         <v>79</v>
       </c>
       <c r="K301" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L301" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M301" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="N301" t="n">
         <v>4648.6</v>
       </c>
       <c r="O301" t="n">
-        <v>367239.4</v>
+        <v>348645</v>
       </c>
       <c r="P301" t="n">
         <v>8900</v>
       </c>
       <c r="Q301" t="n">
-        <v>703100</v>
+        <v>667500</v>
       </c>
     </row>
     <row r="302">
@@ -13951,22 +13951,22 @@
         <v>0</v>
       </c>
       <c r="L311" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M311" t="n">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="N311" t="n">
         <v>1387.55</v>
       </c>
       <c r="O311" t="n">
-        <v>449566.2</v>
+        <v>444016</v>
       </c>
       <c r="P311" t="n">
         <v>2300</v>
       </c>
       <c r="Q311" t="n">
-        <v>745200</v>
+        <v>736000</v>
       </c>
     </row>
     <row r="312">
@@ -14281,22 +14281,22 @@
         <v>0</v>
       </c>
       <c r="L318" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M318" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N318" t="n">
         <v>16897</v>
       </c>
       <c r="O318" t="n">
-        <v>33794</v>
+        <v>16897</v>
       </c>
       <c r="P318" t="n">
         <v>27900</v>
       </c>
       <c r="Q318" t="n">
-        <v>55800</v>
+        <v>27900</v>
       </c>
     </row>
     <row r="319">
@@ -14562,22 +14562,22 @@
         <v>0</v>
       </c>
       <c r="L324" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M324" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="N324" t="n">
         <v>3761.6</v>
       </c>
       <c r="O324" t="n">
-        <v>244504</v>
+        <v>233219.2</v>
       </c>
       <c r="P324" t="n">
         <v>6900</v>
       </c>
       <c r="Q324" t="n">
-        <v>448500</v>
+        <v>427800</v>
       </c>
     </row>
     <row r="325">
@@ -14887,10 +14887,10 @@
         <v>4</v>
       </c>
       <c r="N331" t="n">
-        <v>8296.642647058799</v>
+        <v>8296.6427272727</v>
       </c>
       <c r="O331" t="n">
-        <v>33186.5705882352</v>
+        <v>33186.5709090908</v>
       </c>
       <c r="P331" t="n">
         <v>15900</v>
@@ -15295,22 +15295,22 @@
         <v>0</v>
       </c>
       <c r="L340" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M340" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="N340" t="n">
-        <v>1630.9235742505</v>
+        <v>1630.9236077879</v>
       </c>
       <c r="O340" t="n">
-        <v>151675.8924052965</v>
+        <v>148414.0483086989</v>
       </c>
       <c r="P340" t="n">
         <v>2500</v>
       </c>
       <c r="Q340" t="n">
-        <v>232500</v>
+        <v>227500</v>
       </c>
     </row>
     <row r="341">
@@ -15387,22 +15387,22 @@
         <v>0</v>
       </c>
       <c r="L342" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M342" t="n">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="N342" t="n">
-        <v>1690.5974723655</v>
+        <v>1690.5973219585</v>
       </c>
       <c r="O342" t="n">
-        <v>96364.05592483349</v>
+        <v>86220.4634198835</v>
       </c>
       <c r="P342" t="n">
         <v>2900</v>
       </c>
       <c r="Q342" t="n">
-        <v>165300</v>
+        <v>147900</v>
       </c>
     </row>
     <row r="343">
@@ -15433,22 +15433,22 @@
         <v>0</v>
       </c>
       <c r="L343" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M343" t="n">
-        <v>411</v>
+        <v>398</v>
       </c>
       <c r="N343" t="n">
-        <v>1550.1936350279</v>
+        <v>1550.1936746212</v>
       </c>
       <c r="O343" t="n">
-        <v>637129.5839964669</v>
+        <v>616977.0824992376</v>
       </c>
       <c r="P343" t="n">
         <v>2500</v>
       </c>
       <c r="Q343" t="n">
-        <v>1027500</v>
+        <v>995000</v>
       </c>
     </row>
     <row r="344">
@@ -15485,10 +15485,10 @@
         <v>1</v>
       </c>
       <c r="N344" t="n">
-        <v>1579.3906753247</v>
+        <v>1579.3905526316</v>
       </c>
       <c r="O344" t="n">
-        <v>1579.3906753247</v>
+        <v>1579.3905526316</v>
       </c>
       <c r="P344" t="n">
         <v>2900</v>
@@ -15525,22 +15525,22 @@
         <v>0</v>
       </c>
       <c r="L345" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M345" t="n">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="N345" t="n">
-        <v>2403.5118666412</v>
+        <v>2403.5119649393</v>
       </c>
       <c r="O345" t="n">
-        <v>584053.3835938115</v>
+        <v>574439.3596204927</v>
       </c>
       <c r="P345" t="n">
         <v>3500</v>
       </c>
       <c r="Q345" t="n">
-        <v>850500</v>
+        <v>836500</v>
       </c>
     </row>
     <row r="346">
@@ -15577,10 +15577,10 @@
         <v>69</v>
       </c>
       <c r="N346" t="n">
-        <v>2521.5305629139</v>
+        <v>2521.5288070175</v>
       </c>
       <c r="O346" t="n">
-        <v>173985.6088410591</v>
+        <v>173985.4876842075</v>
       </c>
       <c r="P346" t="n">
         <v>3900</v>
@@ -16509,22 +16509,22 @@
         <v>0</v>
       </c>
       <c r="L367" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M367" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N367" t="n">
         <v>17328</v>
       </c>
       <c r="O367" t="n">
-        <v>415872</v>
+        <v>398544</v>
       </c>
       <c r="P367" t="n">
         <v>32900</v>
       </c>
       <c r="Q367" t="n">
-        <v>789600</v>
+        <v>756700</v>
       </c>
     </row>
     <row r="368">
@@ -16903,22 +16903,22 @@
         <v>0</v>
       </c>
       <c r="L376" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M376" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="N376" t="n">
         <v>6280.31</v>
       </c>
       <c r="O376" t="n">
-        <v>87924.34000000001</v>
+        <v>69083.41</v>
       </c>
       <c r="P376" t="n">
         <v>10500</v>
       </c>
       <c r="Q376" t="n">
-        <v>147000</v>
+        <v>115500</v>
       </c>
     </row>
     <row r="377">
@@ -16995,22 +16995,22 @@
         <v>0</v>
       </c>
       <c r="L378" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M378" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N378" t="n">
         <v>14118.32</v>
       </c>
       <c r="O378" t="n">
-        <v>112946.56</v>
+        <v>84709.92</v>
       </c>
       <c r="P378" t="n">
         <v>17900</v>
       </c>
       <c r="Q378" t="n">
-        <v>143200</v>
+        <v>107400</v>
       </c>
     </row>
     <row r="379">
@@ -18568,22 +18568,22 @@
         <v>0</v>
       </c>
       <c r="L414" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M414" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="N414" t="n">
         <v>2517.22</v>
       </c>
       <c r="O414" t="n">
-        <v>196343.16</v>
+        <v>183757.06</v>
       </c>
       <c r="P414" t="n">
         <v>4200</v>
       </c>
       <c r="Q414" t="n">
-        <v>327600</v>
+        <v>306600</v>
       </c>
     </row>
     <row r="415">
@@ -18615,10 +18615,10 @@
         <v>198</v>
       </c>
       <c r="N415" t="n">
-        <v>2029.8737669513</v>
+        <v>2029.8738600103</v>
       </c>
       <c r="O415" t="n">
-        <v>401915.0058563574</v>
+        <v>401915.0242820394</v>
       </c>
       <c r="P415" t="n">
         <v>3600</v>
@@ -18820,10 +18820,10 @@
         <v>45</v>
       </c>
       <c r="N420" t="n">
-        <v>2680.7396995708</v>
+        <v>2680.739699202</v>
       </c>
       <c r="O420" t="n">
-        <v>120633.286480686</v>
+        <v>120633.28646409</v>
       </c>
       <c r="P420" t="n">
         <v>4900</v>
@@ -19596,10 +19596,10 @@
         <v>25</v>
       </c>
       <c r="N438" t="n">
-        <v>4285.1954859611</v>
+        <v>4285.1954978355</v>
       </c>
       <c r="O438" t="n">
-        <v>107129.8871490275</v>
+        <v>107129.8874458875</v>
       </c>
       <c r="P438" t="n">
         <v>6900</v>
@@ -20065,10 +20065,10 @@
         <v>12</v>
       </c>
       <c r="N449" t="n">
-        <v>4605.2147274436</v>
+        <v>4605.2147318909</v>
       </c>
       <c r="O449" t="n">
-        <v>55262.57672932321</v>
+        <v>55262.5767826908</v>
       </c>
       <c r="P449" t="n">
         <v>7600</v>
@@ -20146,22 +20146,22 @@
         <v>0</v>
       </c>
       <c r="L451" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M451" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N451" t="n">
-        <v>11562.038478261</v>
+        <v>11562.038474114</v>
       </c>
       <c r="O451" t="n">
-        <v>173430.577173915</v>
+        <v>161868.538637596</v>
       </c>
       <c r="P451" t="n">
         <v>18500</v>
       </c>
       <c r="Q451" t="n">
-        <v>277500</v>
+        <v>259000</v>
       </c>
     </row>
     <row r="452">
@@ -20192,22 +20192,22 @@
         <v>0</v>
       </c>
       <c r="L452" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M452" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N452" t="n">
-        <v>13513.643014706</v>
+        <v>13513.643059701</v>
       </c>
       <c r="O452" t="n">
-        <v>175677.359191178</v>
+        <v>148650.073656711</v>
       </c>
       <c r="P452" t="n">
         <v>21900</v>
       </c>
       <c r="Q452" t="n">
-        <v>284700</v>
+        <v>240900</v>
       </c>
     </row>
     <row r="453">
@@ -20443,22 +20443,22 @@
         <v>0</v>
       </c>
       <c r="L458" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M458" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N458" t="n">
         <v>15700</v>
       </c>
       <c r="O458" t="n">
-        <v>125600</v>
+        <v>109900</v>
       </c>
       <c r="P458" t="n">
         <v>29900</v>
       </c>
       <c r="Q458" t="n">
-        <v>239200</v>
+        <v>209300</v>
       </c>
     </row>
     <row r="459">
@@ -20802,10 +20802,10 @@
         <v>9</v>
       </c>
       <c r="N466" t="n">
-        <v>27123.765223881</v>
+        <v>27123.765205993</v>
       </c>
       <c r="O466" t="n">
-        <v>244113.887014929</v>
+        <v>244113.886853937</v>
       </c>
       <c r="P466" t="n">
         <v>44500</v>
@@ -21104,10 +21104,10 @@
         <v>56</v>
       </c>
       <c r="N473" t="n">
-        <v>1561.0002330508</v>
+        <v>1561.0003094984</v>
       </c>
       <c r="O473" t="n">
-        <v>87416.01305084481</v>
+        <v>87416.01733191039</v>
       </c>
       <c r="P473" t="n">
         <v>2900</v>
@@ -21236,22 +21236,22 @@
         <v>0</v>
       </c>
       <c r="L476" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M476" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N476" t="n">
         <v>26854</v>
       </c>
       <c r="O476" t="n">
-        <v>456518</v>
+        <v>402810</v>
       </c>
       <c r="P476" t="n">
         <v>43900</v>
       </c>
       <c r="Q476" t="n">
-        <v>746300</v>
+        <v>658500</v>
       </c>
     </row>
     <row r="477">
@@ -21542,10 +21542,10 @@
         <v>6</v>
       </c>
       <c r="N483" t="n">
-        <v>7969.9501669196</v>
+        <v>7969.9501671733</v>
       </c>
       <c r="O483" t="n">
-        <v>47819.7010015176</v>
+        <v>47819.70100303979</v>
       </c>
       <c r="P483" t="n">
         <v>12900</v>
@@ -22419,22 +22419,22 @@
         <v>0</v>
       </c>
       <c r="L503" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M503" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="N503" t="n">
         <v>4679.92</v>
       </c>
       <c r="O503" t="n">
-        <v>65518.88</v>
+        <v>32759.44</v>
       </c>
       <c r="P503" t="n">
         <v>2500</v>
       </c>
       <c r="Q503" t="n">
-        <v>35000</v>
+        <v>17500</v>
       </c>
     </row>
     <row r="504">
@@ -23446,22 +23446,22 @@
         <v>0</v>
       </c>
       <c r="L526" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M526" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N526" t="n">
         <v>5569.98</v>
       </c>
       <c r="O526" t="n">
-        <v>194949.3</v>
+        <v>189379.32</v>
       </c>
       <c r="P526" t="n">
         <v>8900</v>
       </c>
       <c r="Q526" t="n">
-        <v>311500</v>
+        <v>302600</v>
       </c>
     </row>
     <row r="527">
@@ -23492,22 +23492,22 @@
         <v>0</v>
       </c>
       <c r="L527" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M527" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N527" t="n">
         <v>4690.64</v>
       </c>
       <c r="O527" t="n">
-        <v>14071.92</v>
+        <v>9381.280000000001</v>
       </c>
       <c r="P527" t="n">
         <v>7500</v>
       </c>
       <c r="Q527" t="n">
-        <v>22500</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="528">
@@ -23722,22 +23722,22 @@
         <v>0</v>
       </c>
       <c r="L532" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M532" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N532" t="n">
-        <v>5218.1705520703</v>
+        <v>5218.1705541562</v>
       </c>
       <c r="O532" t="n">
-        <v>36527.1938644921</v>
+        <v>31309.0233249372</v>
       </c>
       <c r="P532" t="n">
         <v>8500</v>
       </c>
       <c r="Q532" t="n">
-        <v>59500</v>
+        <v>51000</v>
       </c>
     </row>
     <row r="533">
@@ -23768,22 +23768,22 @@
         <v>0</v>
       </c>
       <c r="L533" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M533" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N533" t="n">
-        <v>3610.6500258065</v>
+        <v>3610.6500258732</v>
       </c>
       <c r="O533" t="n">
-        <v>32495.8502322585</v>
+        <v>25274.5501811124</v>
       </c>
       <c r="P533" t="n">
         <v>5800</v>
       </c>
       <c r="Q533" t="n">
-        <v>52200</v>
+        <v>40600</v>
       </c>
     </row>
     <row r="534">
@@ -23814,22 +23814,22 @@
         <v>0</v>
       </c>
       <c r="L534" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M534" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N534" t="n">
         <v>5194</v>
       </c>
       <c r="O534" t="n">
-        <v>41552</v>
+        <v>36358</v>
       </c>
       <c r="P534" t="n">
         <v>9000</v>
       </c>
       <c r="Q534" t="n">
-        <v>72000</v>
+        <v>63000</v>
       </c>
     </row>
     <row r="535">
@@ -23909,22 +23909,22 @@
         <v>0</v>
       </c>
       <c r="L536" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M536" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N536" t="n">
         <v>7863.64</v>
       </c>
       <c r="O536" t="n">
-        <v>684136.6800000001</v>
+        <v>676273.04</v>
       </c>
       <c r="P536" t="n">
         <v>9900</v>
       </c>
       <c r="Q536" t="n">
-        <v>861300</v>
+        <v>851400</v>
       </c>
     </row>
     <row r="537">
@@ -24053,22 +24053,22 @@
         <v>0</v>
       </c>
       <c r="L539" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M539" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="N539" t="n">
         <v>4227.77</v>
       </c>
       <c r="O539" t="n">
-        <v>122605.33</v>
+        <v>114149.79</v>
       </c>
       <c r="P539" t="n">
         <v>6900</v>
       </c>
       <c r="Q539" t="n">
-        <v>200100</v>
+        <v>186300</v>
       </c>
     </row>
     <row r="540">
@@ -24148,22 +24148,22 @@
         <v>0</v>
       </c>
       <c r="L541" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M541" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N541" t="n">
         <v>3965.02</v>
       </c>
       <c r="O541" t="n">
-        <v>154635.78</v>
+        <v>150670.76</v>
       </c>
       <c r="P541" t="n">
         <v>6500</v>
       </c>
       <c r="Q541" t="n">
-        <v>253500</v>
+        <v>247000</v>
       </c>
     </row>
     <row r="542">
@@ -24194,22 +24194,22 @@
         <v>0</v>
       </c>
       <c r="L542" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M542" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N542" t="n">
         <v>5791.05</v>
       </c>
       <c r="O542" t="n">
-        <v>69492.60000000001</v>
+        <v>63701.55</v>
       </c>
       <c r="P542" t="n">
         <v>9300</v>
       </c>
       <c r="Q542" t="n">
-        <v>111600</v>
+        <v>102300</v>
       </c>
     </row>
     <row r="543">
@@ -24332,22 +24332,22 @@
         <v>0</v>
       </c>
       <c r="L545" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M545" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N545" t="n">
         <v>10977.27</v>
       </c>
       <c r="O545" t="n">
-        <v>109772.7</v>
+        <v>98795.43000000001</v>
       </c>
       <c r="P545" t="n">
         <v>17900</v>
       </c>
       <c r="Q545" t="n">
-        <v>179000</v>
+        <v>161100</v>
       </c>
     </row>
     <row r="546">
@@ -24424,22 +24424,22 @@
         <v>0</v>
       </c>
       <c r="L547" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M547" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="N547" t="n">
-        <v>1664.355973236</v>
+        <v>1664.355782984</v>
       </c>
       <c r="O547" t="n">
-        <v>223023.700413624</v>
+        <v>219694.963353888</v>
       </c>
       <c r="P547" t="n">
         <v>2900</v>
       </c>
       <c r="Q547" t="n">
-        <v>388600</v>
+        <v>382800</v>
       </c>
     </row>
     <row r="548">
@@ -25031,25 +25031,25 @@
         <v>3</v>
       </c>
       <c r="K560" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L560" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M560" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N560" t="n">
         <v>3646</v>
       </c>
       <c r="O560" t="n">
-        <v>10938</v>
+        <v>3646</v>
       </c>
       <c r="P560" t="n">
         <v>6900</v>
       </c>
       <c r="Q560" t="n">
-        <v>20700</v>
+        <v>6900</v>
       </c>
     </row>
     <row r="561">
@@ -25172,22 +25172,22 @@
         <v>0</v>
       </c>
       <c r="L563" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M563" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="N563" t="n">
         <v>3486</v>
       </c>
       <c r="O563" t="n">
-        <v>27888</v>
+        <v>6972</v>
       </c>
       <c r="P563" t="n">
         <v>6900</v>
       </c>
       <c r="Q563" t="n">
-        <v>55200</v>
+        <v>13800</v>
       </c>
     </row>
     <row r="564">
@@ -25224,10 +25224,10 @@
         <v>27</v>
       </c>
       <c r="N564" t="n">
-        <v>1778.4726251691</v>
+        <v>1778.4726394558</v>
       </c>
       <c r="O564" t="n">
-        <v>48018.7608795657</v>
+        <v>48018.7612653066</v>
       </c>
       <c r="P564" t="n">
         <v>4900</v>
@@ -25678,22 +25678,22 @@
         <v>0</v>
       </c>
       <c r="L574" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M574" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="N574" t="n">
         <v>5148</v>
       </c>
       <c r="O574" t="n">
-        <v>283140</v>
+        <v>272844</v>
       </c>
       <c r="P574" t="n">
         <v>8600</v>
       </c>
       <c r="Q574" t="n">
-        <v>473000</v>
+        <v>455800</v>
       </c>
     </row>
     <row r="575">
@@ -26654,22 +26654,22 @@
         <v>0</v>
       </c>
       <c r="L595" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M595" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="N595" t="n">
         <v>3938.66</v>
       </c>
       <c r="O595" t="n">
-        <v>153607.74</v>
+        <v>145730.42</v>
       </c>
       <c r="P595" t="n">
         <v>4500</v>
       </c>
       <c r="Q595" t="n">
-        <v>175500</v>
+        <v>166500</v>
       </c>
     </row>
     <row r="596">
@@ -26746,22 +26746,22 @@
         <v>0</v>
       </c>
       <c r="L597" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M597" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="N597" t="n">
         <v>12709</v>
       </c>
       <c r="O597" t="n">
-        <v>139799</v>
+        <v>114381</v>
       </c>
       <c r="P597" t="n">
         <v>20500</v>
       </c>
       <c r="Q597" t="n">
-        <v>225500</v>
+        <v>184500</v>
       </c>
     </row>
     <row r="598">
@@ -26792,22 +26792,22 @@
         <v>0</v>
       </c>
       <c r="L598" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M598" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N598" t="n">
         <v>28116</v>
       </c>
       <c r="O598" t="n">
-        <v>84348</v>
+        <v>56232</v>
       </c>
       <c r="P598" t="n">
         <v>45900</v>
       </c>
       <c r="Q598" t="n">
-        <v>137700</v>
+        <v>91800</v>
       </c>
     </row>
     <row r="599">
@@ -26838,22 +26838,22 @@
         <v>0</v>
       </c>
       <c r="L599" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M599" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N599" t="n">
         <v>3424</v>
       </c>
       <c r="O599" t="n">
-        <v>112992</v>
+        <v>109568</v>
       </c>
       <c r="P599" t="n">
         <v>5900</v>
       </c>
       <c r="Q599" t="n">
-        <v>194700</v>
+        <v>188800</v>
       </c>
     </row>
     <row r="600">
@@ -27253,22 +27253,22 @@
         <v>0</v>
       </c>
       <c r="L608" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M608" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N608" t="n">
         <v>13019</v>
       </c>
       <c r="O608" t="n">
-        <v>78114</v>
+        <v>39057</v>
       </c>
       <c r="P608" t="n">
         <v>20900</v>
       </c>
       <c r="Q608" t="n">
-        <v>125400</v>
+        <v>62700</v>
       </c>
     </row>
     <row r="609">
@@ -27345,22 +27345,22 @@
         <v>0</v>
       </c>
       <c r="L610" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M610" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N610" t="n">
         <v>5858</v>
       </c>
       <c r="O610" t="n">
-        <v>52722</v>
+        <v>46864</v>
       </c>
       <c r="P610" t="n">
         <v>9500</v>
       </c>
       <c r="Q610" t="n">
-        <v>85500</v>
+        <v>76000</v>
       </c>
     </row>
     <row r="611">
@@ -27443,10 +27443,10 @@
         <v>190</v>
       </c>
       <c r="N612" t="n">
-        <v>2252.2968774194</v>
+        <v>2252.2969855832</v>
       </c>
       <c r="O612" t="n">
-        <v>427936.406709686</v>
+        <v>427936.4272608079</v>
       </c>
       <c r="P612" t="n">
         <v>3900</v>
@@ -27909,10 +27909,10 @@
         <v>125</v>
       </c>
       <c r="N622" t="n">
-        <v>2328.1187161545</v>
+        <v>2328.1187114504</v>
       </c>
       <c r="O622" t="n">
-        <v>291014.8395193125</v>
+        <v>291014.8389313</v>
       </c>
       <c r="P622" t="n">
         <v>4500</v>
@@ -28731,22 +28731,22 @@
         <v>0</v>
       </c>
       <c r="L640" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M640" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N640" t="n">
         <v>76839</v>
       </c>
       <c r="O640" t="n">
-        <v>153678</v>
+        <v>230517</v>
       </c>
       <c r="P640" t="n">
         <v>122900</v>
       </c>
       <c r="Q640" t="n">
-        <v>245800</v>
+        <v>368700</v>
       </c>
     </row>
     <row r="641">
@@ -28823,22 +28823,22 @@
         <v>0</v>
       </c>
       <c r="L642" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M642" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="N642" t="n">
-        <v>3903.7365705615</v>
+        <v>3903.736684492</v>
       </c>
       <c r="O642" t="n">
-        <v>327913.871927166</v>
+        <v>312298.93475936</v>
       </c>
       <c r="P642" t="n">
         <v>7500</v>
       </c>
       <c r="Q642" t="n">
-        <v>630000</v>
+        <v>600000</v>
       </c>
     </row>
     <row r="643">
@@ -28956,22 +28956,22 @@
         <v>0</v>
       </c>
       <c r="L645" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M645" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="N645" t="n">
         <v>12113</v>
       </c>
       <c r="O645" t="n">
-        <v>181695</v>
+        <v>145356</v>
       </c>
       <c r="P645" t="n">
         <v>19900</v>
       </c>
       <c r="Q645" t="n">
-        <v>298500</v>
+        <v>238800</v>
       </c>
     </row>
     <row r="646">
@@ -29278,22 +29278,22 @@
         <v>0</v>
       </c>
       <c r="L652" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M652" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="N652" t="n">
         <v>2629</v>
       </c>
       <c r="O652" t="n">
-        <v>433785</v>
+        <v>431156</v>
       </c>
       <c r="P652" t="n">
         <v>4500</v>
       </c>
       <c r="Q652" t="n">
-        <v>742500</v>
+        <v>738000</v>
       </c>
     </row>
     <row r="653">
@@ -29462,22 +29462,22 @@
         <v>0</v>
       </c>
       <c r="L656" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M656" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N656" t="n">
         <v>5772</v>
       </c>
       <c r="O656" t="n">
-        <v>207792</v>
+        <v>202020</v>
       </c>
       <c r="P656" t="n">
         <v>9900</v>
       </c>
       <c r="Q656" t="n">
-        <v>356400</v>
+        <v>346500</v>
       </c>
     </row>
     <row r="657">
@@ -29830,22 +29830,22 @@
         <v>0</v>
       </c>
       <c r="L664" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M664" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N664" t="n">
         <v>7635</v>
       </c>
       <c r="O664" t="n">
-        <v>137430</v>
+        <v>129795</v>
       </c>
       <c r="P664" t="n">
         <v>13900</v>
       </c>
       <c r="Q664" t="n">
-        <v>250200</v>
+        <v>236300</v>
       </c>
     </row>
     <row r="665">
@@ -30345,10 +30345,10 @@
         <v>36</v>
       </c>
       <c r="N675" t="n">
-        <v>17075.989523481</v>
+        <v>17075.989523151</v>
       </c>
       <c r="O675" t="n">
-        <v>614735.622845316</v>
+        <v>614735.6228334361</v>
       </c>
       <c r="P675" t="n">
         <v>27500</v>
@@ -30797,22 +30797,22 @@
         <v>0</v>
       </c>
       <c r="L685" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M685" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="N685" t="n">
         <v>10755</v>
       </c>
       <c r="O685" t="n">
-        <v>408690</v>
+        <v>387180</v>
       </c>
       <c r="P685" t="n">
         <v>17900</v>
       </c>
       <c r="Q685" t="n">
-        <v>680200</v>
+        <v>644400</v>
       </c>
     </row>
     <row r="686">
@@ -30889,22 +30889,22 @@
         <v>0</v>
       </c>
       <c r="L687" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M687" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N687" t="n">
         <v>20014</v>
       </c>
       <c r="O687" t="n">
-        <v>20014</v>
+        <v>0</v>
       </c>
       <c r="P687" t="n">
         <v>33900</v>
       </c>
       <c r="Q687" t="n">
-        <v>33900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="688">
@@ -32137,10 +32137,10 @@
         <v>10</v>
       </c>
       <c r="N714" t="n">
-        <v>1516.0387986728</v>
+        <v>1516.0387953812</v>
       </c>
       <c r="O714" t="n">
-        <v>15160.387986728</v>
+        <v>15160.387953812</v>
       </c>
       <c r="P714" t="n">
         <v>2300</v>
@@ -32273,10 +32273,10 @@
         <v>227</v>
       </c>
       <c r="N717" t="n">
-        <v>2458.5131821149</v>
+        <v>2458.5130781975</v>
       </c>
       <c r="O717" t="n">
-        <v>558082.4923400823</v>
+        <v>558082.4687508325</v>
       </c>
       <c r="P717" t="n">
         <v>3500</v>
@@ -32365,10 +32365,10 @@
         <v>40</v>
       </c>
       <c r="N719" t="n">
-        <v>1771.0904491413</v>
+        <v>1771.0904111406</v>
       </c>
       <c r="O719" t="n">
-        <v>70843.617965652</v>
+        <v>70843.61644562401</v>
       </c>
       <c r="P719" t="n">
         <v>2500</v>
@@ -32411,10 +32411,10 @@
         <v>122</v>
       </c>
       <c r="N720" t="n">
-        <v>2079.3840254521</v>
+        <v>2079.3839770425</v>
       </c>
       <c r="O720" t="n">
-        <v>253684.8511051562</v>
+        <v>253684.845199185</v>
       </c>
       <c r="P720" t="n">
         <v>2900</v>
@@ -32503,10 +32503,10 @@
         <v>51</v>
       </c>
       <c r="N722" t="n">
-        <v>3306.5951351351</v>
+        <v>3306.5946902655</v>
       </c>
       <c r="O722" t="n">
-        <v>168636.3518918901</v>
+        <v>168636.3292035405</v>
       </c>
       <c r="P722" t="n">
         <v>4900</v>
@@ -32595,10 +32595,10 @@
         <v>79</v>
       </c>
       <c r="N724" t="n">
-        <v>2108.7918292683</v>
+        <v>2108.7920330806</v>
       </c>
       <c r="O724" t="n">
-        <v>166594.5545121957</v>
+        <v>166594.5706133674</v>
       </c>
       <c r="P724" t="n">
         <v>2900</v>
@@ -32641,10 +32641,10 @@
         <v>259</v>
       </c>
       <c r="N725" t="n">
-        <v>2056.0833612094</v>
+        <v>2056.0831903662</v>
       </c>
       <c r="O725" t="n">
-        <v>532525.5905532347</v>
+        <v>532525.5463048458</v>
       </c>
       <c r="P725" t="n">
         <v>2900</v>
@@ -32733,10 +32733,10 @@
         <v>155</v>
       </c>
       <c r="N727" t="n">
-        <v>1655.9308652576</v>
+        <v>1655.9308592201</v>
       </c>
       <c r="O727" t="n">
-        <v>256669.284114928</v>
+        <v>256669.2831791155</v>
       </c>
       <c r="P727" t="n">
         <v>2500</v>
@@ -32822,22 +32822,22 @@
         <v>0</v>
       </c>
       <c r="L729" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M729" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="N729" t="n">
         <v>1871</v>
       </c>
       <c r="O729" t="n">
-        <v>155293</v>
+        <v>153422</v>
       </c>
       <c r="P729" t="n">
         <v>3900</v>
       </c>
       <c r="Q729" t="n">
-        <v>323700</v>
+        <v>319800</v>
       </c>
     </row>
     <row r="730">
@@ -33006,22 +33006,22 @@
         <v>0</v>
       </c>
       <c r="L733" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M733" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="N733" t="n">
-        <v>1592.278225957</v>
+        <v>1592.2785867446</v>
       </c>
       <c r="O733" t="n">
-        <v>136935.927432302</v>
+        <v>128974.5655263126</v>
       </c>
       <c r="P733" t="n">
         <v>2500</v>
       </c>
       <c r="Q733" t="n">
-        <v>215000</v>
+        <v>202500</v>
       </c>
     </row>
     <row r="734">
@@ -33281,10 +33281,10 @@
         <v>49</v>
       </c>
       <c r="N739" t="n">
-        <v>3033.7177351916</v>
+        <v>3033.7172791519</v>
       </c>
       <c r="O739" t="n">
-        <v>148652.1690243884</v>
+        <v>148652.1466784431</v>
       </c>
       <c r="P739" t="n">
         <v>4500</v>
@@ -33373,10 +33373,10 @@
         <v>92</v>
       </c>
       <c r="N741" t="n">
-        <v>1668.6302167183</v>
+        <v>1668.6318954248</v>
       </c>
       <c r="O741" t="n">
-        <v>153513.9799380836</v>
+        <v>153514.1343790816</v>
       </c>
       <c r="P741" t="n">
         <v>2500</v>
@@ -33465,10 +33465,10 @@
         <v>200</v>
       </c>
       <c r="N743" t="n">
-        <v>1259.2745452499</v>
+        <v>1259.2745472973</v>
       </c>
       <c r="O743" t="n">
-        <v>251854.90904998</v>
+        <v>251854.90945946</v>
       </c>
       <c r="P743" t="n">
         <v>1900</v>
@@ -33682,22 +33682,22 @@
         <v>0</v>
       </c>
       <c r="L748" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M748" t="n">
-        <v>350</v>
+        <v>326</v>
       </c>
       <c r="N748" t="n">
-        <v>692.15222061657</v>
+        <v>692.15222920696</v>
       </c>
       <c r="O748" t="n">
-        <v>242253.2772157995</v>
+        <v>225641.626721469</v>
       </c>
       <c r="P748" t="n">
         <v>1200</v>
       </c>
       <c r="Q748" t="n">
-        <v>420000</v>
+        <v>391200</v>
       </c>
     </row>
     <row r="749">
@@ -34612,22 +34612,22 @@
         <v>0</v>
       </c>
       <c r="L768" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M768" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N768" t="n">
         <v>2682.71</v>
       </c>
       <c r="O768" t="n">
-        <v>21461.68</v>
+        <v>16096.26</v>
       </c>
       <c r="P768" t="n">
         <v>10900</v>
       </c>
       <c r="Q768" t="n">
-        <v>87200</v>
+        <v>65400</v>
       </c>
     </row>
     <row r="769">
@@ -35079,22 +35079,22 @@
         <v>0</v>
       </c>
       <c r="L778" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M778" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="N778" t="n">
         <v>3629.36</v>
       </c>
       <c r="O778" t="n">
-        <v>47181.68</v>
+        <v>32664.24</v>
       </c>
       <c r="P778" t="n">
         <v>3900</v>
       </c>
       <c r="Q778" t="n">
-        <v>50700</v>
+        <v>35100</v>
       </c>
     </row>
     <row r="779">
@@ -35221,10 +35221,10 @@
         <v>38</v>
       </c>
       <c r="N781" t="n">
-        <v>527.91977777778</v>
+        <v>527.92037313433</v>
       </c>
       <c r="O781" t="n">
-        <v>20060.95155555564</v>
+        <v>20060.97417910454</v>
       </c>
       <c r="P781" t="n">
         <v>1300</v>
@@ -35544,10 +35544,10 @@
         <v>10</v>
       </c>
       <c r="N788" t="n">
-        <v>10732.242162162</v>
+        <v>10732.242222222</v>
       </c>
       <c r="O788" t="n">
-        <v>107322.42162162</v>
+        <v>107322.42222222</v>
       </c>
       <c r="P788" t="n">
         <v>25900</v>
@@ -35725,22 +35725,22 @@
         <v>0</v>
       </c>
       <c r="L792" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M792" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N792" t="n">
         <v>4979.58</v>
       </c>
       <c r="O792" t="n">
-        <v>24897.9</v>
+        <v>9959.16</v>
       </c>
       <c r="P792" t="n">
         <v>6500</v>
       </c>
       <c r="Q792" t="n">
-        <v>32500</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="793">
@@ -37526,22 +37526,22 @@
         <v>0</v>
       </c>
       <c r="L831" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="M831" t="n">
-        <v>1015</v>
+        <v>968</v>
       </c>
       <c r="N831" t="n">
-        <v>517.28943177426</v>
+        <v>517.28978235968</v>
       </c>
       <c r="O831" t="n">
-        <v>525048.7732508739</v>
+        <v>500736.5093241702</v>
       </c>
       <c r="P831" t="n">
         <v>900</v>
       </c>
       <c r="Q831" t="n">
-        <v>913500</v>
+        <v>871200</v>
       </c>
     </row>
     <row r="832">
@@ -38041,22 +38041,22 @@
         <v>0</v>
       </c>
       <c r="L842" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M842" t="n">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="N842" t="n">
-        <v>3110.8416960301</v>
+        <v>3110.8415531661</v>
       </c>
       <c r="O842" t="n">
-        <v>871035.6748884281</v>
+        <v>839927.219354847</v>
       </c>
       <c r="P842" t="n">
         <v>4500</v>
       </c>
       <c r="Q842" t="n">
-        <v>1260000</v>
+        <v>1215000</v>
       </c>
     </row>
     <row r="843">
@@ -38224,22 +38224,22 @@
         <v>0</v>
       </c>
       <c r="L846" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M846" t="n">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="N846" t="n">
         <v>2030.02</v>
       </c>
       <c r="O846" t="n">
-        <v>288262.84</v>
+        <v>276082.72</v>
       </c>
       <c r="P846" t="n">
         <v>3600</v>
       </c>
       <c r="Q846" t="n">
-        <v>511200</v>
+        <v>489600</v>
       </c>
     </row>
     <row r="847">
@@ -38453,22 +38453,22 @@
         <v>0</v>
       </c>
       <c r="L851" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M851" t="n">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="N851" t="n">
-        <v>703.79518287415</v>
+        <v>703.79517569581</v>
       </c>
       <c r="O851" t="n">
-        <v>216065.121142364</v>
+        <v>212546.1430601346</v>
       </c>
       <c r="P851" t="n">
         <v>900</v>
       </c>
       <c r="Q851" t="n">
-        <v>276300</v>
+        <v>271800</v>
       </c>
     </row>
     <row r="852">
@@ -38735,22 +38735,22 @@
         <v>0</v>
       </c>
       <c r="L857" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M857" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N857" t="n">
         <v>7570.87</v>
       </c>
       <c r="O857" t="n">
-        <v>136275.66</v>
+        <v>128704.79</v>
       </c>
       <c r="P857" t="n">
         <v>9500</v>
       </c>
       <c r="Q857" t="n">
-        <v>171000</v>
+        <v>161500</v>
       </c>
     </row>
     <row r="858">
@@ -39522,10 +39522,10 @@
         <v>36</v>
       </c>
       <c r="N874" t="n">
-        <v>1595.5127943686</v>
+        <v>1595.5120596085</v>
       </c>
       <c r="O874" t="n">
-        <v>57438.4605972696</v>
+        <v>57438.434145906</v>
       </c>
       <c r="P874" t="n">
         <v>2500</v>
@@ -40297,10 +40297,10 @@
         <v>8</v>
       </c>
       <c r="N890" t="n">
-        <v>2098.4049712644</v>
+        <v>2098.405</v>
       </c>
       <c r="O890" t="n">
-        <v>16787.2397701152</v>
+        <v>16787.24</v>
       </c>
       <c r="P890" t="n">
         <v>9500</v>
@@ -40389,22 +40389,22 @@
         <v>0</v>
       </c>
       <c r="L892" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M892" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N892" t="n">
         <v>16301</v>
       </c>
       <c r="O892" t="n">
-        <v>114107</v>
+        <v>97806</v>
       </c>
       <c r="P892" t="n">
         <v>22500</v>
       </c>
       <c r="Q892" t="n">
-        <v>157500</v>
+        <v>135000</v>
       </c>
     </row>
     <row r="893">
@@ -40481,22 +40481,22 @@
         <v>0</v>
       </c>
       <c r="L894" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M894" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N894" t="n">
         <v>16064.59</v>
       </c>
       <c r="O894" t="n">
-        <v>80322.95</v>
+        <v>48193.77</v>
       </c>
       <c r="P894" t="n">
         <v>30000</v>
       </c>
       <c r="Q894" t="n">
-        <v>150000</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="895">
@@ -40628,22 +40628,22 @@
         <v>0</v>
       </c>
       <c r="L897" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M897" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N897" t="n">
-        <v>2832.1949275362</v>
+        <v>2832.195</v>
       </c>
       <c r="O897" t="n">
-        <v>16993.1695652172</v>
+        <v>14160.975</v>
       </c>
       <c r="P897" t="n">
         <v>12900</v>
       </c>
       <c r="Q897" t="n">
-        <v>77400</v>
+        <v>64500</v>
       </c>
     </row>
     <row r="898">
@@ -41150,22 +41150,22 @@
         <v>0</v>
       </c>
       <c r="L908" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M908" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N908" t="n">
         <v>12156.79</v>
       </c>
       <c r="O908" t="n">
-        <v>255292.59</v>
+        <v>230979.01</v>
       </c>
       <c r="P908" t="n">
         <v>12000</v>
       </c>
       <c r="Q908" t="n">
-        <v>252000</v>
+        <v>228000</v>
       </c>
     </row>
     <row r="909">
@@ -41637,22 +41637,22 @@
         <v>0</v>
       </c>
       <c r="L918" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M918" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N918" t="n">
-        <v>5796.335</v>
+        <v>5796.3355555556</v>
       </c>
       <c r="O918" t="n">
-        <v>98537.69500000001</v>
+        <v>86945.03333333399</v>
       </c>
       <c r="P918" t="n">
         <v>15900</v>
       </c>
       <c r="Q918" t="n">
-        <v>270300</v>
+        <v>238500</v>
       </c>
     </row>
     <row r="919">
@@ -41833,22 +41833,22 @@
         <v>0</v>
       </c>
       <c r="L922" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M922" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N922" t="n">
         <v>10296.29</v>
       </c>
       <c r="O922" t="n">
-        <v>175036.93</v>
+        <v>164740.64</v>
       </c>
       <c r="P922" t="n">
         <v>16900</v>
       </c>
       <c r="Q922" t="n">
-        <v>287300</v>
+        <v>270400</v>
       </c>
     </row>
     <row r="923">
@@ -42219,22 +42219,22 @@
         <v>0</v>
       </c>
       <c r="L930" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M930" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="N930" t="n">
         <v>6989.34</v>
       </c>
       <c r="O930" t="n">
-        <v>188712.18</v>
+        <v>174733.5</v>
       </c>
       <c r="P930" t="n">
         <v>10900</v>
       </c>
       <c r="Q930" t="n">
-        <v>294300</v>
+        <v>272500</v>
       </c>
     </row>
     <row r="931">
@@ -43896,22 +43896,22 @@
         <v>0</v>
       </c>
       <c r="L965" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M965" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N965" t="n">
         <v>5876.81</v>
       </c>
       <c r="O965" t="n">
-        <v>41137.67000000001</v>
+        <v>35260.86</v>
       </c>
       <c r="P965" t="n">
         <v>22900</v>
       </c>
       <c r="Q965" t="n">
-        <v>160300</v>
+        <v>137400</v>
       </c>
     </row>
     <row r="966">
@@ -44562,22 +44562,22 @@
         <v>0</v>
       </c>
       <c r="L979" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M979" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N979" t="n">
         <v>13377.81</v>
       </c>
       <c r="O979" t="n">
-        <v>26755.62</v>
+        <v>13377.81</v>
       </c>
       <c r="P979" t="n">
         <v>36900</v>
       </c>
       <c r="Q979" t="n">
-        <v>73800</v>
+        <v>36900</v>
       </c>
     </row>
     <row r="980">
@@ -45559,22 +45559,22 @@
         <v>0</v>
       </c>
       <c r="L1000" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1000" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N1000" t="n">
         <v>1278.27</v>
       </c>
       <c r="O1000" t="n">
-        <v>11504.43</v>
+        <v>8947.889999999999</v>
       </c>
       <c r="P1000" t="n">
         <v>5900</v>
       </c>
       <c r="Q1000" t="n">
-        <v>53100</v>
+        <v>41300</v>
       </c>
     </row>
     <row r="1001">
@@ -46289,10 +46289,10 @@
         <v>224</v>
       </c>
       <c r="N1015" t="n">
-        <v>665.32358222629</v>
+        <v>665.32359209922</v>
       </c>
       <c r="O1015" t="n">
-        <v>149032.4824186889</v>
+        <v>149032.4846302253</v>
       </c>
       <c r="P1015" t="n">
         <v>2900</v>
@@ -46917,10 +46917,10 @@
         <v>50</v>
       </c>
       <c r="N1028" t="n">
-        <v>430.60997624703</v>
+        <v>430.6099761621</v>
       </c>
       <c r="O1028" t="n">
-        <v>21530.4988123515</v>
+        <v>21530.498808105</v>
       </c>
       <c r="P1028" t="n">
         <v>2200</v>
@@ -47835,22 +47835,22 @@
         <v>0</v>
       </c>
       <c r="L1049" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M1049" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="N1049" t="n">
         <v>3181.9</v>
       </c>
       <c r="O1049" t="n">
-        <v>238642.5</v>
+        <v>225914.9</v>
       </c>
       <c r="P1049" t="n">
         <v>5100</v>
       </c>
       <c r="Q1049" t="n">
-        <v>382500</v>
+        <v>362100</v>
       </c>
     </row>
     <row r="1050">
@@ -47882,10 +47882,10 @@
         <v>16</v>
       </c>
       <c r="N1050" t="n">
-        <v>1213.6821194605</v>
+        <v>1213.6821359223</v>
       </c>
       <c r="O1050" t="n">
-        <v>19418.913911368</v>
+        <v>19418.9141747568</v>
       </c>
       <c r="P1050" t="n">
         <v>1500</v>
@@ -48151,10 +48151,10 @@
         <v>17</v>
       </c>
       <c r="N1056" t="n">
-        <v>8922.2151190476</v>
+        <v>8922.2151807229</v>
       </c>
       <c r="O1056" t="n">
-        <v>151677.6570238092</v>
+        <v>151677.6580722893</v>
       </c>
       <c r="P1056" t="n">
         <v>8200</v>
@@ -48330,22 +48330,22 @@
         <v>0</v>
       </c>
       <c r="L1060" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1060" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N1060" t="n">
-        <v>22951.704839538</v>
+        <v>22951.704819588</v>
       </c>
       <c r="O1060" t="n">
-        <v>137710.229037228</v>
+        <v>91806.81927835201</v>
       </c>
       <c r="P1060" t="n">
         <v>37900</v>
       </c>
       <c r="Q1060" t="n">
-        <v>227400</v>
+        <v>151600</v>
       </c>
     </row>
     <row r="1061">
@@ -48517,22 +48517,22 @@
         <v>0</v>
       </c>
       <c r="L1064" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1064" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N1064" t="n">
-        <v>1547.8825373134</v>
+        <v>1547.8826153846</v>
       </c>
       <c r="O1064" t="n">
-        <v>20122.4729850742</v>
+        <v>17026.7087692306</v>
       </c>
       <c r="P1064" t="n">
         <v>5500</v>
       </c>
       <c r="Q1064" t="n">
-        <v>71500</v>
+        <v>60500</v>
       </c>
     </row>
     <row r="1065">
@@ -48614,22 +48614,22 @@
         <v>0</v>
       </c>
       <c r="L1066" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1066" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="N1066" t="n">
         <v>1561.33</v>
       </c>
       <c r="O1066" t="n">
-        <v>42155.91</v>
+        <v>39033.25</v>
       </c>
       <c r="P1066" t="n">
         <v>2000</v>
       </c>
       <c r="Q1066" t="n">
-        <v>54000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="1067">
@@ -49583,22 +49583,22 @@
         <v>0</v>
       </c>
       <c r="L1087" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M1087" t="n">
-        <v>550</v>
+        <v>450</v>
       </c>
       <c r="N1087" t="n">
-        <v>220.00534867624</v>
+        <v>220.00509068498</v>
       </c>
       <c r="O1087" t="n">
-        <v>121002.941771932</v>
+        <v>99002.290808241</v>
       </c>
       <c r="P1087" t="n">
         <v>260</v>
       </c>
       <c r="Q1087" t="n">
-        <v>143000</v>
+        <v>117000</v>
       </c>
     </row>
     <row r="1088">
@@ -50227,22 +50227,22 @@
         <v>0</v>
       </c>
       <c r="L1101" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M1101" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="N1101" t="n">
         <v>1952.66</v>
       </c>
       <c r="O1101" t="n">
-        <v>89822.36</v>
+        <v>80059.06</v>
       </c>
       <c r="P1101" t="n">
         <v>3500</v>
       </c>
       <c r="Q1101" t="n">
-        <v>161000</v>
+        <v>143500</v>
       </c>
     </row>
     <row r="1102">
@@ -51055,22 +51055,22 @@
         <v>0</v>
       </c>
       <c r="L1119" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M1119" t="n">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="N1119" t="n">
         <v>6336</v>
       </c>
       <c r="O1119" t="n">
-        <v>792000</v>
+        <v>772992</v>
       </c>
       <c r="P1119" t="n">
         <v>7500</v>
       </c>
       <c r="Q1119" t="n">
-        <v>937500</v>
+        <v>915000</v>
       </c>
     </row>
     <row r="1120">
@@ -51101,22 +51101,22 @@
         <v>0</v>
       </c>
       <c r="L1120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1120" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N1120" t="n">
         <v>5280</v>
       </c>
       <c r="O1120" t="n">
-        <v>116160</v>
+        <v>110880</v>
       </c>
       <c r="P1120" t="n">
         <v>6900</v>
       </c>
       <c r="Q1120" t="n">
-        <v>151800</v>
+        <v>144900</v>
       </c>
     </row>
     <row r="1121">
@@ -51193,22 +51193,22 @@
         <v>0</v>
       </c>
       <c r="L1122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1122" t="n">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N1122" t="n">
         <v>1584</v>
       </c>
       <c r="O1122" t="n">
-        <v>408672</v>
+        <v>407088</v>
       </c>
       <c r="P1122" t="n">
         <v>2000</v>
       </c>
       <c r="Q1122" t="n">
-        <v>516000</v>
+        <v>514000</v>
       </c>
     </row>
     <row r="1123">
@@ -51377,22 +51377,22 @@
         <v>0</v>
       </c>
       <c r="L1126" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M1126" t="n">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="N1126" t="n">
         <v>3520</v>
       </c>
       <c r="O1126" t="n">
-        <v>457600</v>
+        <v>425920</v>
       </c>
       <c r="P1126" t="n">
         <v>4500</v>
       </c>
       <c r="Q1126" t="n">
-        <v>585000</v>
+        <v>544500</v>
       </c>
     </row>
     <row r="1127">
@@ -51515,22 +51515,22 @@
         <v>0</v>
       </c>
       <c r="L1129" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1129" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N1129" t="n">
         <v>9240</v>
       </c>
       <c r="O1129" t="n">
-        <v>498960</v>
+        <v>480480</v>
       </c>
       <c r="P1129" t="n">
         <v>11500</v>
       </c>
       <c r="Q1129" t="n">
-        <v>621000</v>
+        <v>598000</v>
       </c>
     </row>
     <row r="1130">
@@ -51561,22 +51561,22 @@
         <v>0</v>
       </c>
       <c r="L1130" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1130" t="n">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="N1130" t="n">
         <v>2288</v>
       </c>
       <c r="O1130" t="n">
-        <v>1249248</v>
+        <v>1244672</v>
       </c>
       <c r="P1130" t="n">
         <v>2900</v>
       </c>
       <c r="Q1130" t="n">
-        <v>1583400</v>
+        <v>1577600</v>
       </c>
     </row>
     <row r="1131">
@@ -51607,22 +51607,22 @@
         <v>0</v>
       </c>
       <c r="L1131" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M1131" t="n">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="N1131" t="n">
         <v>4576</v>
       </c>
       <c r="O1131" t="n">
-        <v>832832</v>
+        <v>819104</v>
       </c>
       <c r="P1131" t="n">
         <v>5900</v>
       </c>
       <c r="Q1131" t="n">
-        <v>1073800</v>
+        <v>1056100</v>
       </c>
     </row>
     <row r="1132">
@@ -53079,22 +53079,22 @@
         <v>0</v>
       </c>
       <c r="L1163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1163" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N1163" t="n">
         <v>32.41</v>
       </c>
       <c r="O1163" t="n">
-        <v>226.87</v>
+        <v>194.46</v>
       </c>
       <c r="P1163" t="n">
         <v>13500</v>
       </c>
       <c r="Q1163" t="n">
-        <v>94500</v>
+        <v>81000</v>
       </c>
     </row>
     <row r="1164">
@@ -53697,22 +53697,22 @@
         <v>0</v>
       </c>
       <c r="L1176" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1176" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="N1176" t="n">
-        <v>1319.3608823529</v>
+        <v>1319.360887574</v>
       </c>
       <c r="O1176" t="n">
-        <v>31664.6611764696</v>
+        <v>29025.939526628</v>
       </c>
       <c r="P1176" t="n">
         <v>3500</v>
       </c>
       <c r="Q1176" t="n">
-        <v>84000</v>
+        <v>77000</v>
       </c>
     </row>
     <row r="1177">
@@ -53891,22 +53891,22 @@
         <v>0</v>
       </c>
       <c r="L1180" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M1180" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="N1180" t="n">
-        <v>2432.1347916667</v>
+        <v>2432.1351111111</v>
       </c>
       <c r="O1180" t="n">
-        <v>77828.3133333344</v>
+        <v>63235.5128888886</v>
       </c>
       <c r="P1180" t="n">
         <v>4500</v>
       </c>
       <c r="Q1180" t="n">
-        <v>144000</v>
+        <v>117000</v>
       </c>
     </row>
     <row r="1181">
@@ -54080,22 +54080,22 @@
         <v>0</v>
       </c>
       <c r="L1184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1184" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N1184" t="n">
         <v>9917.040000000001</v>
       </c>
       <c r="O1184" t="n">
-        <v>109087.44</v>
+        <v>99170.40000000001</v>
       </c>
       <c r="P1184" t="n">
         <v>15900</v>
       </c>
       <c r="Q1184" t="n">
-        <v>174900</v>
+        <v>159000</v>
       </c>
     </row>
     <row r="1185">

--- a/bodegas/LJ-101.xlsx
+++ b/bodegas/LJ-101.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-27</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-28</t>
         </is>
       </c>
     </row>
@@ -1821,10 +1821,10 @@
         <v>21</v>
       </c>
       <c r="N35" t="n">
-        <v>3926.8371059432</v>
+        <v>3926.8370969414</v>
       </c>
       <c r="O35" t="n">
-        <v>82463.57922480721</v>
+        <v>82463.57903576941</v>
       </c>
       <c r="P35" t="n">
         <v>4800</v>
@@ -2027,10 +2027,10 @@
         <v>11</v>
       </c>
       <c r="N40" t="n">
-        <v>2413.0010706638</v>
+        <v>2413.0010741139</v>
       </c>
       <c r="O40" t="n">
-        <v>26543.0117773018</v>
+        <v>26543.0118152529</v>
       </c>
       <c r="P40" t="n">
         <v>4700</v>
@@ -2066,10 +2066,10 @@
         <v>6</v>
       </c>
       <c r="N41" t="n">
-        <v>2474.7041652614</v>
+        <v>2474.7041355932</v>
       </c>
       <c r="O41" t="n">
-        <v>14848.2249915684</v>
+        <v>14848.2248135592</v>
       </c>
       <c r="P41" t="n">
         <v>4500</v>
@@ -2417,10 +2417,10 @@
         <v>2</v>
       </c>
       <c r="N50" t="n">
-        <v>15403.520914286</v>
+        <v>15403.520977011</v>
       </c>
       <c r="O50" t="n">
-        <v>30807.041828572</v>
+        <v>30807.041954022</v>
       </c>
       <c r="P50" t="n">
         <v>33500</v>
@@ -2456,10 +2456,10 @@
         <v>6</v>
       </c>
       <c r="N51" t="n">
-        <v>14857.623243243</v>
+        <v>14857.623257919</v>
       </c>
       <c r="O51" t="n">
-        <v>89145.73945945801</v>
+        <v>89145.73954751401</v>
       </c>
       <c r="P51" t="n">
         <v>34900</v>
@@ -4956,13 +4956,13 @@
         </is>
       </c>
       <c r="J109" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K109" t="n">
         <v>0</v>
       </c>
       <c r="L109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M109" t="n">
         <v>21</v>
@@ -6678,10 +6678,10 @@
         <v>1</v>
       </c>
       <c r="N148" t="n">
-        <v>3340.6800817996</v>
+        <v>3340.6800821355</v>
       </c>
       <c r="O148" t="n">
-        <v>3340.6800817996</v>
+        <v>3340.6800821355</v>
       </c>
       <c r="P148" t="n">
         <v>7100</v>
@@ -7737,10 +7737,10 @@
         <v>108</v>
       </c>
       <c r="N172" t="n">
-        <v>4937.3101623616</v>
+        <v>4937.3101635688</v>
       </c>
       <c r="O172" t="n">
-        <v>533229.4975350528</v>
+        <v>533229.4976654304</v>
       </c>
       <c r="P172" t="n">
         <v>7500</v>
@@ -8020,22 +8020,22 @@
         </is>
       </c>
       <c r="J179" t="n">
-        <v>458</v>
+        <v>451</v>
       </c>
       <c r="K179" t="n">
         <v>0</v>
       </c>
       <c r="L179" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M179" t="n">
         <v>451</v>
       </c>
       <c r="N179" t="n">
-        <v>1098.059452236</v>
+        <v>1098.0595661432</v>
       </c>
       <c r="O179" t="n">
-        <v>495224.812958436</v>
+        <v>495224.8643305833</v>
       </c>
       <c r="P179" t="n">
         <v>1500</v>
@@ -8679,13 +8679,13 @@
         </is>
       </c>
       <c r="J194" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K194" t="n">
         <v>0</v>
       </c>
       <c r="L194" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M194" t="n">
         <v>26</v>
@@ -9035,13 +9035,13 @@
         </is>
       </c>
       <c r="J202" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K202" t="n">
         <v>0</v>
       </c>
       <c r="L202" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M202" t="n">
         <v>27</v>
@@ -9185,10 +9185,10 @@
         <v>2</v>
       </c>
       <c r="N205" t="n">
-        <v>5216.8961258041</v>
+        <v>5216.8961202577</v>
       </c>
       <c r="O205" t="n">
-        <v>10433.7922516082</v>
+        <v>10433.7922405154</v>
       </c>
       <c r="P205" t="n">
         <v>8500</v>
@@ -9670,13 +9670,13 @@
         </is>
       </c>
       <c r="J216" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K216" t="n">
         <v>0</v>
       </c>
       <c r="L216" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M216" t="n">
         <v>49</v>
@@ -9731,10 +9731,10 @@
         <v>85</v>
       </c>
       <c r="N217" t="n">
-        <v>3230.067250996</v>
+        <v>3230.0672177419</v>
       </c>
       <c r="O217" t="n">
-        <v>274555.71633466</v>
+        <v>274555.7135080615</v>
       </c>
       <c r="P217" t="n">
         <v>6200</v>
@@ -9995,13 +9995,13 @@
         </is>
       </c>
       <c r="J223" t="n">
-        <v>1852</v>
+        <v>1842</v>
       </c>
       <c r="K223" t="n">
         <v>0</v>
       </c>
       <c r="L223" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M223" t="n">
         <v>1842</v>
@@ -10182,13 +10182,13 @@
         </is>
       </c>
       <c r="J227" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K227" t="n">
         <v>0</v>
       </c>
       <c r="L227" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M227" t="n">
         <v>25</v>
@@ -10647,10 +10647,10 @@
         <v>36</v>
       </c>
       <c r="N237" t="n">
-        <v>5484.9500917431</v>
+        <v>5484.9508571429</v>
       </c>
       <c r="O237" t="n">
-        <v>197458.2033027516</v>
+        <v>197458.2308571444</v>
       </c>
       <c r="P237" t="n">
         <v>8500</v>
@@ -10863,13 +10863,13 @@
         </is>
       </c>
       <c r="J242" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K242" t="n">
         <v>0</v>
       </c>
       <c r="L242" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M242" t="n">
         <v>81</v>
@@ -11282,10 +11282,10 @@
         <v>12</v>
       </c>
       <c r="N251" t="n">
-        <v>3594.2540224159</v>
+        <v>3594.2540186916</v>
       </c>
       <c r="O251" t="n">
-        <v>43131.0482689908</v>
+        <v>43131.0482242992</v>
       </c>
       <c r="P251" t="n">
         <v>6500</v>
@@ -11495,10 +11495,10 @@
         <v>134</v>
       </c>
       <c r="N256" t="n">
-        <v>3240.8500369004</v>
+        <v>3240.8500325733</v>
       </c>
       <c r="O256" t="n">
-        <v>434273.9049446536</v>
+        <v>434273.9043648222</v>
       </c>
       <c r="P256" t="n">
         <v>5200</v>
@@ -11760,13 +11760,13 @@
         </is>
       </c>
       <c r="J262" t="n">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="K262" t="n">
         <v>0</v>
       </c>
       <c r="L262" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="M262" t="n">
         <v>312</v>
@@ -12263,10 +12263,10 @@
         <v>9</v>
       </c>
       <c r="N273" t="n">
-        <v>12267.648701299</v>
+        <v>12267.648552632</v>
       </c>
       <c r="O273" t="n">
-        <v>110408.838311691</v>
+        <v>110408.836973688</v>
       </c>
       <c r="P273" t="n">
         <v>19900</v>
@@ -12677,10 +12677,10 @@
         <v>6</v>
       </c>
       <c r="N282" t="n">
-        <v>4242.5421749409</v>
+        <v>4242.5422384428</v>
       </c>
       <c r="O282" t="n">
-        <v>25455.2530496454</v>
+        <v>25455.2534306568</v>
       </c>
       <c r="P282" t="n">
         <v>5900</v>
@@ -12895,10 +12895,10 @@
         <v>1</v>
       </c>
       <c r="N287" t="n">
-        <v>4372.2107901305</v>
+        <v>4372.2107902432</v>
       </c>
       <c r="O287" t="n">
-        <v>4372.2107901305</v>
+        <v>4372.2107902432</v>
       </c>
       <c r="P287" t="n">
         <v>7500</v>
@@ -13060,28 +13060,28 @@
         </is>
       </c>
       <c r="J291" t="n">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="K291" t="n">
         <v>0</v>
       </c>
       <c r="L291" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M291" t="n">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="N291" t="n">
-        <v>1592.5667761934</v>
+        <v>1592.566762142</v>
       </c>
       <c r="O291" t="n">
-        <v>347179.5572101612</v>
+        <v>337624.153574104</v>
       </c>
       <c r="P291" t="n">
         <v>3900</v>
       </c>
       <c r="Q291" t="n">
-        <v>850200</v>
+        <v>826800</v>
       </c>
     </row>
     <row r="292">
@@ -13188,13 +13188,13 @@
         </is>
       </c>
       <c r="J294" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="K294" t="n">
         <v>0</v>
       </c>
       <c r="L294" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M294" t="n">
         <v>56</v>
@@ -13501,28 +13501,28 @@
         </is>
       </c>
       <c r="J301" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="K301" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L301" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M301" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="N301" t="n">
         <v>4648.6</v>
       </c>
       <c r="O301" t="n">
-        <v>348645</v>
+        <v>334699.2</v>
       </c>
       <c r="P301" t="n">
         <v>8900</v>
       </c>
       <c r="Q301" t="n">
-        <v>667500</v>
+        <v>640800</v>
       </c>
     </row>
     <row r="302">
@@ -13945,13 +13945,13 @@
         </is>
       </c>
       <c r="J311" t="n">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="K311" t="n">
         <v>0</v>
       </c>
       <c r="L311" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M311" t="n">
         <v>320</v>
@@ -15289,22 +15289,22 @@
         </is>
       </c>
       <c r="J340" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="K340" t="n">
         <v>0</v>
       </c>
       <c r="L340" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M340" t="n">
         <v>91</v>
       </c>
       <c r="N340" t="n">
-        <v>1630.9236077879</v>
+        <v>1630.9235901027</v>
       </c>
       <c r="O340" t="n">
-        <v>148414.0483086989</v>
+        <v>148414.0466993457</v>
       </c>
       <c r="P340" t="n">
         <v>2500</v>
@@ -15381,28 +15381,28 @@
         </is>
       </c>
       <c r="J342" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="K342" t="n">
         <v>0</v>
       </c>
       <c r="L342" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M342" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="N342" t="n">
-        <v>1690.5973219585</v>
+        <v>1690.5972035794</v>
       </c>
       <c r="O342" t="n">
-        <v>86220.4634198835</v>
+        <v>81148.6657718112</v>
       </c>
       <c r="P342" t="n">
         <v>2900</v>
       </c>
       <c r="Q342" t="n">
-        <v>147900</v>
+        <v>139200</v>
       </c>
     </row>
     <row r="343">
@@ -15427,28 +15427,28 @@
         </is>
       </c>
       <c r="J343" t="n">
-        <v>411</v>
+        <v>392</v>
       </c>
       <c r="K343" t="n">
         <v>0</v>
       </c>
       <c r="L343" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M343" t="n">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="N343" t="n">
-        <v>1550.1936746212</v>
+        <v>1550.1936753491</v>
       </c>
       <c r="O343" t="n">
-        <v>616977.0824992376</v>
+        <v>607675.9207368472</v>
       </c>
       <c r="P343" t="n">
         <v>2500</v>
       </c>
       <c r="Q343" t="n">
-        <v>995000</v>
+        <v>980000</v>
       </c>
     </row>
     <row r="344">
@@ -15519,22 +15519,22 @@
         </is>
       </c>
       <c r="J345" t="n">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="K345" t="n">
         <v>0</v>
       </c>
       <c r="L345" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M345" t="n">
         <v>239</v>
       </c>
       <c r="N345" t="n">
-        <v>2403.5119649393</v>
+        <v>2403.5119996136</v>
       </c>
       <c r="O345" t="n">
-        <v>574439.3596204927</v>
+        <v>574439.3679076504</v>
       </c>
       <c r="P345" t="n">
         <v>3500</v>
@@ -15565,7 +15565,7 @@
         </is>
       </c>
       <c r="J346" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="K346" t="n">
         <v>0</v>
@@ -15574,19 +15574,19 @@
         <v>0</v>
       </c>
       <c r="M346" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="N346" t="n">
-        <v>2521.5288070175</v>
+        <v>2521.52825</v>
       </c>
       <c r="O346" t="n">
-        <v>173985.4876842075</v>
+        <v>161377.808</v>
       </c>
       <c r="P346" t="n">
         <v>3900</v>
       </c>
       <c r="Q346" t="n">
-        <v>269100</v>
+        <v>249600</v>
       </c>
     </row>
     <row r="347">
@@ -16503,13 +16503,13 @@
         </is>
       </c>
       <c r="J367" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K367" t="n">
         <v>0</v>
       </c>
       <c r="L367" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M367" t="n">
         <v>23</v>
@@ -16897,13 +16897,13 @@
         </is>
       </c>
       <c r="J376" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K376" t="n">
         <v>0</v>
       </c>
       <c r="L376" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M376" t="n">
         <v>11</v>
@@ -18615,10 +18615,10 @@
         <v>198</v>
       </c>
       <c r="N415" t="n">
-        <v>2029.8738600103</v>
+        <v>2029.8738129131</v>
       </c>
       <c r="O415" t="n">
-        <v>401915.0242820394</v>
+        <v>401915.0149567938</v>
       </c>
       <c r="P415" t="n">
         <v>3600</v>
@@ -18820,10 +18820,10 @@
         <v>45</v>
       </c>
       <c r="N420" t="n">
-        <v>2680.739699202</v>
+        <v>2680.7396988322</v>
       </c>
       <c r="O420" t="n">
-        <v>120633.28646409</v>
+        <v>120633.286447449</v>
       </c>
       <c r="P420" t="n">
         <v>4900</v>
@@ -19453,7 +19453,7 @@
         </is>
       </c>
       <c r="J435" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="K435" t="n">
         <v>0</v>
@@ -19462,19 +19462,19 @@
         <v>0</v>
       </c>
       <c r="M435" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="N435" t="n">
         <v>3877.89</v>
       </c>
       <c r="O435" t="n">
-        <v>166749.27</v>
+        <v>155115.6</v>
       </c>
       <c r="P435" t="n">
         <v>6500</v>
       </c>
       <c r="Q435" t="n">
-        <v>279500</v>
+        <v>260000</v>
       </c>
     </row>
     <row r="436">
@@ -19596,10 +19596,10 @@
         <v>25</v>
       </c>
       <c r="N438" t="n">
-        <v>4285.1954978355</v>
+        <v>4285.1955097614</v>
       </c>
       <c r="O438" t="n">
-        <v>107129.8874458875</v>
+        <v>107129.887744035</v>
       </c>
       <c r="P438" t="n">
         <v>6900</v>
@@ -21104,10 +21104,10 @@
         <v>56</v>
       </c>
       <c r="N473" t="n">
-        <v>1561.0003094984</v>
+        <v>1561.0003205128</v>
       </c>
       <c r="O473" t="n">
-        <v>87416.01733191039</v>
+        <v>87416.01794871681</v>
       </c>
       <c r="P473" t="n">
         <v>2900</v>
@@ -22413,13 +22413,13 @@
         </is>
       </c>
       <c r="J503" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="K503" t="n">
         <v>0</v>
       </c>
       <c r="L503" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M503" t="n">
         <v>7</v>
@@ -23440,13 +23440,13 @@
         </is>
       </c>
       <c r="J526" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K526" t="n">
         <v>0</v>
       </c>
       <c r="L526" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M526" t="n">
         <v>34</v>
@@ -23486,13 +23486,13 @@
         </is>
       </c>
       <c r="J527" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K527" t="n">
         <v>0</v>
       </c>
       <c r="L527" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M527" t="n">
         <v>2</v>
@@ -23716,22 +23716,22 @@
         </is>
       </c>
       <c r="J532" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K532" t="n">
         <v>0</v>
       </c>
       <c r="L532" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M532" t="n">
         <v>6</v>
       </c>
       <c r="N532" t="n">
-        <v>5218.1705541562</v>
+        <v>5218.170554855</v>
       </c>
       <c r="O532" t="n">
-        <v>31309.0233249372</v>
+        <v>31309.02332913</v>
       </c>
       <c r="P532" t="n">
         <v>8500</v>
@@ -23762,13 +23762,13 @@
         </is>
       </c>
       <c r="J533" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K533" t="n">
         <v>0</v>
       </c>
       <c r="L533" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M533" t="n">
         <v>7</v>
@@ -23808,13 +23808,13 @@
         </is>
       </c>
       <c r="J534" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K534" t="n">
         <v>0</v>
       </c>
       <c r="L534" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M534" t="n">
         <v>7</v>
@@ -23903,13 +23903,13 @@
         </is>
       </c>
       <c r="J536" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K536" t="n">
         <v>0</v>
       </c>
       <c r="L536" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M536" t="n">
         <v>86</v>
@@ -24047,13 +24047,13 @@
         </is>
       </c>
       <c r="J539" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K539" t="n">
         <v>0</v>
       </c>
       <c r="L539" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M539" t="n">
         <v>27</v>
@@ -24142,13 +24142,13 @@
         </is>
       </c>
       <c r="J541" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K541" t="n">
         <v>0</v>
       </c>
       <c r="L541" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M541" t="n">
         <v>38</v>
@@ -24188,13 +24188,13 @@
         </is>
       </c>
       <c r="J542" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K542" t="n">
         <v>0</v>
       </c>
       <c r="L542" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M542" t="n">
         <v>11</v>
@@ -24326,13 +24326,13 @@
         </is>
       </c>
       <c r="J545" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K545" t="n">
         <v>0</v>
       </c>
       <c r="L545" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M545" t="n">
         <v>9</v>
@@ -24418,28 +24418,28 @@
         </is>
       </c>
       <c r="J547" t="n">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="K547" t="n">
         <v>0</v>
       </c>
       <c r="L547" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M547" t="n">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="N547" t="n">
-        <v>1664.355782984</v>
+        <v>1664.355659204</v>
       </c>
       <c r="O547" t="n">
-        <v>219694.963353888</v>
+        <v>213037.524378112</v>
       </c>
       <c r="P547" t="n">
         <v>2900</v>
       </c>
       <c r="Q547" t="n">
-        <v>382800</v>
+        <v>371200</v>
       </c>
     </row>
     <row r="548">
@@ -24758,22 +24758,22 @@
         <v>0</v>
       </c>
       <c r="L554" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M554" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N554" t="n">
         <v>10174</v>
       </c>
       <c r="O554" t="n">
-        <v>71218</v>
+        <v>30522</v>
       </c>
       <c r="P554" t="n">
         <v>16900</v>
       </c>
       <c r="Q554" t="n">
-        <v>118300</v>
+        <v>50700</v>
       </c>
     </row>
     <row r="555">
@@ -25028,13 +25028,13 @@
         </is>
       </c>
       <c r="J560" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K560" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L560" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M560" t="n">
         <v>1</v>
@@ -25166,13 +25166,13 @@
         </is>
       </c>
       <c r="J563" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K563" t="n">
         <v>0</v>
       </c>
       <c r="L563" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M563" t="n">
         <v>2</v>
@@ -25224,10 +25224,10 @@
         <v>27</v>
       </c>
       <c r="N564" t="n">
-        <v>1778.4726394558</v>
+        <v>1778.4726299141</v>
       </c>
       <c r="O564" t="n">
-        <v>48018.7612653066</v>
+        <v>48018.7610076807</v>
       </c>
       <c r="P564" t="n">
         <v>4900</v>
@@ -25534,7 +25534,7 @@
         </is>
       </c>
       <c r="J571" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K571" t="n">
         <v>0</v>
@@ -25543,19 +25543,19 @@
         <v>0</v>
       </c>
       <c r="M571" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N571" t="n">
         <v>16058</v>
       </c>
       <c r="O571" t="n">
-        <v>80290</v>
+        <v>64232</v>
       </c>
       <c r="P571" t="n">
         <v>25900</v>
       </c>
       <c r="Q571" t="n">
-        <v>129500</v>
+        <v>103600</v>
       </c>
     </row>
     <row r="572">
@@ -25672,13 +25672,13 @@
         </is>
       </c>
       <c r="J574" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="K574" t="n">
         <v>0</v>
       </c>
       <c r="L574" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M574" t="n">
         <v>53</v>
@@ -27339,13 +27339,13 @@
         </is>
       </c>
       <c r="J610" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K610" t="n">
         <v>0</v>
       </c>
       <c r="L610" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M610" t="n">
         <v>8</v>
@@ -28265,7 +28265,7 @@
         </is>
       </c>
       <c r="J630" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K630" t="n">
         <v>0</v>
@@ -28274,19 +28274,19 @@
         <v>0</v>
       </c>
       <c r="M630" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="N630" t="n">
         <v>4544</v>
       </c>
       <c r="O630" t="n">
-        <v>327168</v>
+        <v>322624</v>
       </c>
       <c r="P630" t="n">
         <v>7900</v>
       </c>
       <c r="Q630" t="n">
-        <v>568800</v>
+        <v>560900</v>
       </c>
     </row>
     <row r="631">
@@ -28731,22 +28731,22 @@
         <v>0</v>
       </c>
       <c r="L640" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M640" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N640" t="n">
         <v>76839</v>
       </c>
       <c r="O640" t="n">
-        <v>230517</v>
+        <v>153678</v>
       </c>
       <c r="P640" t="n">
         <v>122900</v>
       </c>
       <c r="Q640" t="n">
-        <v>368700</v>
+        <v>245800</v>
       </c>
     </row>
     <row r="641">
@@ -28829,10 +28829,10 @@
         <v>80</v>
       </c>
       <c r="N642" t="n">
-        <v>3903.736684492</v>
+        <v>3903.7366972477</v>
       </c>
       <c r="O642" t="n">
-        <v>312298.93475936</v>
+        <v>312298.935779816</v>
       </c>
       <c r="P642" t="n">
         <v>7500</v>
@@ -29226,28 +29226,28 @@
         </is>
       </c>
       <c r="J651" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K651" t="n">
         <v>0</v>
       </c>
       <c r="L651" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M651" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N651" t="n">
         <v>9839</v>
       </c>
       <c r="O651" t="n">
-        <v>29517</v>
+        <v>68873</v>
       </c>
       <c r="P651" t="n">
         <v>16900</v>
       </c>
       <c r="Q651" t="n">
-        <v>50700</v>
+        <v>118300</v>
       </c>
     </row>
     <row r="652">
@@ -29272,13 +29272,13 @@
         </is>
       </c>
       <c r="J652" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K652" t="n">
         <v>0</v>
       </c>
       <c r="L652" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M652" t="n">
         <v>164</v>
@@ -29456,13 +29456,13 @@
         </is>
       </c>
       <c r="J656" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K656" t="n">
         <v>0</v>
       </c>
       <c r="L656" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M656" t="n">
         <v>35</v>
@@ -29916,7 +29916,7 @@
         </is>
       </c>
       <c r="J666" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K666" t="n">
         <v>0</v>
@@ -29925,19 +29925,19 @@
         <v>0</v>
       </c>
       <c r="M666" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N666" t="n">
         <v>5438</v>
       </c>
       <c r="O666" t="n">
-        <v>59818</v>
+        <v>54380</v>
       </c>
       <c r="P666" t="n">
         <v>8900</v>
       </c>
       <c r="Q666" t="n">
-        <v>97900</v>
+        <v>89000</v>
       </c>
     </row>
     <row r="667">
@@ -30791,13 +30791,13 @@
         </is>
       </c>
       <c r="J685" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K685" t="n">
         <v>0</v>
       </c>
       <c r="L685" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M685" t="n">
         <v>36</v>
@@ -31021,7 +31021,7 @@
         </is>
       </c>
       <c r="J690" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K690" t="n">
         <v>0</v>
@@ -31030,19 +31030,19 @@
         <v>0</v>
       </c>
       <c r="M690" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="N690" t="n">
-        <v>4268.7068599034</v>
+        <v>4268.7071078431</v>
       </c>
       <c r="O690" t="n">
-        <v>106717.671497585</v>
+        <v>93911.55637254819</v>
       </c>
       <c r="P690" t="n">
         <v>6900</v>
       </c>
       <c r="Q690" t="n">
-        <v>172500</v>
+        <v>151800</v>
       </c>
     </row>
     <row r="691">
@@ -32137,10 +32137,10 @@
         <v>10</v>
       </c>
       <c r="N714" t="n">
-        <v>1516.0387953812</v>
+        <v>1516.0387982037</v>
       </c>
       <c r="O714" t="n">
-        <v>15160.387953812</v>
+        <v>15160.387982037</v>
       </c>
       <c r="P714" t="n">
         <v>2300</v>
@@ -32227,10 +32227,10 @@
         <v>45</v>
       </c>
       <c r="N716" t="n">
-        <v>4248.6814925373</v>
+        <v>4248.6880645161</v>
       </c>
       <c r="O716" t="n">
-        <v>191190.6671641785</v>
+        <v>191190.9629032245</v>
       </c>
       <c r="P716" t="n">
         <v>5900</v>
@@ -32273,10 +32273,10 @@
         <v>227</v>
       </c>
       <c r="N717" t="n">
-        <v>2458.5130781975</v>
+        <v>2458.5131328074</v>
       </c>
       <c r="O717" t="n">
-        <v>558082.4687508325</v>
+        <v>558082.4811472797</v>
       </c>
       <c r="P717" t="n">
         <v>3500</v>
@@ -32411,10 +32411,10 @@
         <v>122</v>
       </c>
       <c r="N720" t="n">
-        <v>2079.3839770425</v>
+        <v>2079.3840254521</v>
       </c>
       <c r="O720" t="n">
-        <v>253684.845199185</v>
+        <v>253684.8511051562</v>
       </c>
       <c r="P720" t="n">
         <v>2900</v>
@@ -32503,10 +32503,10 @@
         <v>51</v>
       </c>
       <c r="N722" t="n">
-        <v>3306.5946902655</v>
+        <v>3306.5951153324</v>
       </c>
       <c r="O722" t="n">
-        <v>168636.3292035405</v>
+        <v>168636.3508819524</v>
       </c>
       <c r="P722" t="n">
         <v>4900</v>
@@ -32641,10 +32641,10 @@
         <v>259</v>
       </c>
       <c r="N725" t="n">
-        <v>2056.0831903662</v>
+        <v>2056.0831723454</v>
       </c>
       <c r="O725" t="n">
-        <v>532525.5463048458</v>
+        <v>532525.5416374586</v>
       </c>
       <c r="P725" t="n">
         <v>2900</v>
@@ -32816,13 +32816,13 @@
         </is>
       </c>
       <c r="J729" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K729" t="n">
         <v>0</v>
       </c>
       <c r="L729" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M729" t="n">
         <v>82</v>
@@ -32862,7 +32862,7 @@
         </is>
       </c>
       <c r="J730" t="n">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="K730" t="n">
         <v>0</v>
@@ -32871,19 +32871,19 @@
         <v>0</v>
       </c>
       <c r="M730" t="n">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="N730" t="n">
         <v>1662</v>
       </c>
       <c r="O730" t="n">
-        <v>601644</v>
+        <v>599982</v>
       </c>
       <c r="P730" t="n">
         <v>2900</v>
       </c>
       <c r="Q730" t="n">
-        <v>1049800</v>
+        <v>1046900</v>
       </c>
     </row>
     <row r="731">
@@ -33000,28 +33000,28 @@
         </is>
       </c>
       <c r="J733" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="K733" t="n">
         <v>0</v>
       </c>
       <c r="L733" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M733" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="N733" t="n">
-        <v>1592.2785867446</v>
+        <v>1592.2786119257</v>
       </c>
       <c r="O733" t="n">
-        <v>128974.5655263126</v>
+        <v>127382.288954056</v>
       </c>
       <c r="P733" t="n">
         <v>2500</v>
       </c>
       <c r="Q733" t="n">
-        <v>202500</v>
+        <v>200000</v>
       </c>
     </row>
     <row r="734">
@@ -33419,10 +33419,10 @@
         <v>152</v>
       </c>
       <c r="N742" t="n">
-        <v>2546.9839957717</v>
+        <v>2546.9839186296</v>
       </c>
       <c r="O742" t="n">
-        <v>387141.5673572984</v>
+        <v>387141.5556316992</v>
       </c>
       <c r="P742" t="n">
         <v>3900</v>
@@ -34231,7 +34231,7 @@
         </is>
       </c>
       <c r="J760" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K760" t="n">
         <v>0</v>
@@ -34240,19 +34240,19 @@
         <v>0</v>
       </c>
       <c r="M760" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N760" t="n">
         <v>3597.62</v>
       </c>
       <c r="O760" t="n">
-        <v>122319.08</v>
+        <v>118721.46</v>
       </c>
       <c r="P760" t="n">
         <v>4500</v>
       </c>
       <c r="Q760" t="n">
-        <v>153000</v>
+        <v>148500</v>
       </c>
     </row>
     <row r="761">
@@ -34477,10 +34477,10 @@
         <v>30</v>
       </c>
       <c r="N765" t="n">
-        <v>3026.5152486188</v>
+        <v>3026.5153672316</v>
       </c>
       <c r="O765" t="n">
-        <v>90795.45745856399</v>
+        <v>90795.461016948</v>
       </c>
       <c r="P765" t="n">
         <v>7000</v>
@@ -37520,22 +37520,22 @@
         </is>
       </c>
       <c r="J831" t="n">
-        <v>1015</v>
+        <v>992</v>
       </c>
       <c r="K831" t="n">
         <v>0</v>
       </c>
       <c r="L831" t="n">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="M831" t="n">
         <v>968</v>
       </c>
       <c r="N831" t="n">
-        <v>517.28978235968</v>
+        <v>517.2898138359</v>
       </c>
       <c r="O831" t="n">
-        <v>500736.5093241702</v>
+        <v>500736.5397931511</v>
       </c>
       <c r="P831" t="n">
         <v>900</v>
@@ -38035,22 +38035,22 @@
         </is>
       </c>
       <c r="J842" t="n">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="K842" t="n">
         <v>0</v>
       </c>
       <c r="L842" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M842" t="n">
         <v>270</v>
       </c>
       <c r="N842" t="n">
-        <v>3110.8415531661</v>
+        <v>3110.8415227818</v>
       </c>
       <c r="O842" t="n">
-        <v>839927.219354847</v>
+        <v>839927.211151086</v>
       </c>
       <c r="P842" t="n">
         <v>4500</v>
@@ -38218,13 +38218,13 @@
         </is>
       </c>
       <c r="J846" t="n">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="K846" t="n">
         <v>0</v>
       </c>
       <c r="L846" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M846" t="n">
         <v>136</v>
@@ -38447,22 +38447,22 @@
         </is>
       </c>
       <c r="J851" t="n">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="K851" t="n">
         <v>0</v>
       </c>
       <c r="L851" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M851" t="n">
         <v>302</v>
       </c>
       <c r="N851" t="n">
-        <v>703.79517569581</v>
+        <v>703.795175</v>
       </c>
       <c r="O851" t="n">
-        <v>212546.1430601346</v>
+        <v>212546.14285</v>
       </c>
       <c r="P851" t="n">
         <v>900</v>
@@ -38508,10 +38508,10 @@
         <v>24</v>
       </c>
       <c r="N852" t="n">
-        <v>3182.2511214953</v>
+        <v>3182.2511235955</v>
       </c>
       <c r="O852" t="n">
-        <v>76374.0269158872</v>
+        <v>76374.026966292</v>
       </c>
       <c r="P852" t="n">
         <v>6900</v>
@@ -38729,13 +38729,13 @@
         </is>
       </c>
       <c r="J857" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K857" t="n">
         <v>0</v>
       </c>
       <c r="L857" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M857" t="n">
         <v>17</v>
@@ -39522,10 +39522,10 @@
         <v>36</v>
       </c>
       <c r="N874" t="n">
-        <v>1595.5120596085</v>
+        <v>1595.5123423818</v>
       </c>
       <c r="O874" t="n">
-        <v>57438.434145906</v>
+        <v>57438.4443257448</v>
       </c>
       <c r="P874" t="n">
         <v>2500</v>
@@ -40285,7 +40285,7 @@
         </is>
       </c>
       <c r="J890" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K890" t="n">
         <v>0</v>
@@ -40294,19 +40294,19 @@
         <v>0</v>
       </c>
       <c r="M890" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N890" t="n">
-        <v>2098.405</v>
+        <v>2098.4050144928</v>
       </c>
       <c r="O890" t="n">
-        <v>16787.24</v>
+        <v>14688.8351014496</v>
       </c>
       <c r="P890" t="n">
         <v>9500</v>
       </c>
       <c r="Q890" t="n">
-        <v>76000</v>
+        <v>66500</v>
       </c>
     </row>
     <row r="891">
@@ -40383,13 +40383,13 @@
         </is>
       </c>
       <c r="J892" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K892" t="n">
         <v>0</v>
       </c>
       <c r="L892" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M892" t="n">
         <v>6</v>
@@ -40475,13 +40475,13 @@
         </is>
       </c>
       <c r="J894" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K894" t="n">
         <v>0</v>
       </c>
       <c r="L894" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M894" t="n">
         <v>3</v>
@@ -40622,13 +40622,13 @@
         </is>
       </c>
       <c r="J897" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K897" t="n">
         <v>0</v>
       </c>
       <c r="L897" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M897" t="n">
         <v>5</v>
@@ -41101,22 +41101,22 @@
         <v>0</v>
       </c>
       <c r="L907" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M907" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N907" t="n">
         <v>10536.4</v>
       </c>
       <c r="O907" t="n">
-        <v>42145.6</v>
+        <v>31609.2</v>
       </c>
       <c r="P907" t="n">
         <v>16900</v>
       </c>
       <c r="Q907" t="n">
-        <v>67600</v>
+        <v>50700</v>
       </c>
     </row>
     <row r="908">
@@ -41144,13 +41144,13 @@
         </is>
       </c>
       <c r="J908" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K908" t="n">
         <v>0</v>
       </c>
       <c r="L908" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M908" t="n">
         <v>19</v>
@@ -41827,13 +41827,13 @@
         </is>
       </c>
       <c r="J922" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K922" t="n">
         <v>0</v>
       </c>
       <c r="L922" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M922" t="n">
         <v>16</v>
@@ -45553,13 +45553,13 @@
         </is>
       </c>
       <c r="J1000" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K1000" t="n">
         <v>0</v>
       </c>
       <c r="L1000" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M1000" t="n">
         <v>7</v>
@@ -46516,28 +46516,28 @@
         </is>
       </c>
       <c r="J1020" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K1020" t="n">
         <v>0</v>
       </c>
       <c r="L1020" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M1020" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="N1020" t="n">
         <v>1911</v>
       </c>
       <c r="O1020" t="n">
-        <v>36309</v>
+        <v>22932</v>
       </c>
       <c r="P1020" t="n">
         <v>4500</v>
       </c>
       <c r="Q1020" t="n">
-        <v>85500</v>
+        <v>54000</v>
       </c>
     </row>
     <row r="1021">
@@ -47829,13 +47829,13 @@
         </is>
       </c>
       <c r="J1049" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="K1049" t="n">
         <v>0</v>
       </c>
       <c r="L1049" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M1049" t="n">
         <v>71</v>
@@ -48336,10 +48336,10 @@
         <v>4</v>
       </c>
       <c r="N1060" t="n">
-        <v>22951.704819588</v>
+        <v>22951.704812903</v>
       </c>
       <c r="O1060" t="n">
-        <v>91806.81927835201</v>
+        <v>91806.819251612</v>
       </c>
       <c r="P1060" t="n">
         <v>37900</v>
@@ -48511,13 +48511,13 @@
         </is>
       </c>
       <c r="J1064" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K1064" t="n">
         <v>0</v>
       </c>
       <c r="L1064" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M1064" t="n">
         <v>11</v>
@@ -48608,13 +48608,13 @@
         </is>
       </c>
       <c r="J1066" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="K1066" t="n">
         <v>0</v>
       </c>
       <c r="L1066" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M1066" t="n">
         <v>25</v>
@@ -49577,13 +49577,13 @@
         </is>
       </c>
       <c r="J1087" t="n">
-        <v>550</v>
+        <v>450</v>
       </c>
       <c r="K1087" t="n">
         <v>0</v>
       </c>
       <c r="L1087" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M1087" t="n">
         <v>450</v>
@@ -51049,13 +51049,13 @@
         </is>
       </c>
       <c r="J1119" t="n">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="K1119" t="n">
         <v>0</v>
       </c>
       <c r="L1119" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M1119" t="n">
         <v>122</v>
@@ -51187,13 +51187,13 @@
         </is>
       </c>
       <c r="J1122" t="n">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K1122" t="n">
         <v>0</v>
       </c>
       <c r="L1122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1122" t="n">
         <v>257</v>
@@ -51279,7 +51279,7 @@
         </is>
       </c>
       <c r="J1124" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="K1124" t="n">
         <v>0</v>
@@ -51288,19 +51288,19 @@
         <v>0</v>
       </c>
       <c r="M1124" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="N1124" t="n">
         <v>6160</v>
       </c>
       <c r="O1124" t="n">
-        <v>412720</v>
+        <v>388080</v>
       </c>
       <c r="P1124" t="n">
         <v>7900</v>
       </c>
       <c r="Q1124" t="n">
-        <v>529300</v>
+        <v>497700</v>
       </c>
     </row>
     <row r="1125">
@@ -51371,13 +51371,13 @@
         </is>
       </c>
       <c r="J1126" t="n">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="K1126" t="n">
         <v>0</v>
       </c>
       <c r="L1126" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="M1126" t="n">
         <v>121</v>
@@ -51555,13 +51555,13 @@
         </is>
       </c>
       <c r="J1130" t="n">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="K1130" t="n">
         <v>0</v>
       </c>
       <c r="L1130" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M1130" t="n">
         <v>544</v>
@@ -51601,13 +51601,13 @@
         </is>
       </c>
       <c r="J1131" t="n">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="K1131" t="n">
         <v>0</v>
       </c>
       <c r="L1131" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M1131" t="n">
         <v>179</v>
@@ -53691,13 +53691,13 @@
         </is>
       </c>
       <c r="J1176" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K1176" t="n">
         <v>0</v>
       </c>
       <c r="L1176" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M1176" t="n">
         <v>22</v>
@@ -53885,13 +53885,13 @@
         </is>
       </c>
       <c r="J1180" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="K1180" t="n">
         <v>0</v>
       </c>
       <c r="L1180" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M1180" t="n">
         <v>26</v>
@@ -54600,10 +54600,10 @@
         <v>52</v>
       </c>
       <c r="N1195" t="n">
-        <v>2539.571542461</v>
+        <v>2539.5715559441</v>
       </c>
       <c r="O1195" t="n">
-        <v>132057.720207972</v>
+        <v>132057.7209090932</v>
       </c>
       <c r="P1195" t="n">
         <v>3500</v>

--- a/bodegas/LJ-101.xlsx
+++ b/bodegas/LJ-101.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-28</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-29</t>
         </is>
       </c>
     </row>
@@ -1495,22 +1495,22 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N27" t="n">
         <v>27000</v>
       </c>
       <c r="O27" t="n">
-        <v>324000</v>
+        <v>297000</v>
       </c>
       <c r="P27" t="n">
         <v>20000</v>
       </c>
       <c r="Q27" t="n">
-        <v>240000</v>
+        <v>220000</v>
       </c>
     </row>
     <row r="28">
@@ -1609,13 +1609,13 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
         <v>15</v>
@@ -8020,13 +8020,13 @@
         </is>
       </c>
       <c r="J179" t="n">
-        <v>451</v>
+        <v>409</v>
       </c>
       <c r="K179" t="n">
         <v>0</v>
       </c>
       <c r="L179" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="M179" t="n">
         <v>409</v>
@@ -8472,22 +8472,22 @@
         <v>0</v>
       </c>
       <c r="L189" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M189" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N189" t="n">
         <v>13593.35</v>
       </c>
       <c r="O189" t="n">
-        <v>244680.3</v>
+        <v>231086.95</v>
       </c>
       <c r="P189" t="n">
         <v>25500</v>
       </c>
       <c r="Q189" t="n">
-        <v>459000</v>
+        <v>433500</v>
       </c>
     </row>
     <row r="190">
@@ -9047,10 +9047,10 @@
         <v>27</v>
       </c>
       <c r="N202" t="n">
-        <v>2582.2557142857</v>
+        <v>2582.2556563454</v>
       </c>
       <c r="O202" t="n">
-        <v>69720.9042857139</v>
+        <v>69720.90272132579</v>
       </c>
       <c r="P202" t="n">
         <v>4500</v>
@@ -9185,10 +9185,10 @@
         <v>2</v>
       </c>
       <c r="N205" t="n">
-        <v>5216.8961124659</v>
+        <v>5216.8961063218</v>
       </c>
       <c r="O205" t="n">
-        <v>10433.7922249318</v>
+        <v>10433.7922126436</v>
       </c>
       <c r="P205" t="n">
         <v>8500</v>
@@ -9583,13 +9583,13 @@
         </is>
       </c>
       <c r="J214" t="n">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="K214" t="n">
         <v>0</v>
       </c>
       <c r="L214" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M214" t="n">
         <v>134</v>
@@ -9719,10 +9719,10 @@
         </is>
       </c>
       <c r="J217" t="n">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="K217" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L217" t="n">
         <v>0</v>
@@ -10356,13 +10356,13 @@
         </is>
       </c>
       <c r="J231" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K231" t="n">
         <v>0</v>
       </c>
       <c r="L231" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M231" t="n">
         <v>68</v>
@@ -10402,28 +10402,28 @@
         </is>
       </c>
       <c r="J232" t="n">
-        <v>185</v>
+        <v>349</v>
       </c>
       <c r="K232" t="n">
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="L232" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M232" t="n">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="N232" t="n">
         <v>4357.55</v>
       </c>
       <c r="O232" t="n">
-        <v>1520784.95</v>
+        <v>1503354.75</v>
       </c>
       <c r="P232" t="n">
         <v>7500</v>
       </c>
       <c r="Q232" t="n">
-        <v>2617500</v>
+        <v>2587500</v>
       </c>
     </row>
     <row r="233">
@@ -10506,10 +10506,10 @@
         <v>12</v>
       </c>
       <c r="N234" t="n">
-        <v>4890.93004884</v>
+        <v>4890.9300488998</v>
       </c>
       <c r="O234" t="n">
-        <v>58691.16058608</v>
+        <v>58691.1605867976</v>
       </c>
       <c r="P234" t="n">
         <v>8200</v>
@@ -10736,22 +10736,22 @@
         <v>0</v>
       </c>
       <c r="L239" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M239" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N239" t="n">
         <v>5888</v>
       </c>
       <c r="O239" t="n">
-        <v>41216</v>
+        <v>29440</v>
       </c>
       <c r="P239" t="n">
         <v>9500</v>
       </c>
       <c r="Q239" t="n">
-        <v>66500</v>
+        <v>47500</v>
       </c>
     </row>
     <row r="240">
@@ -10915,22 +10915,22 @@
         <v>0</v>
       </c>
       <c r="L243" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M243" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N243" t="n">
         <v>7041</v>
       </c>
       <c r="O243" t="n">
-        <v>63369</v>
+        <v>56328</v>
       </c>
       <c r="P243" t="n">
         <v>11500</v>
       </c>
       <c r="Q243" t="n">
-        <v>103500</v>
+        <v>92000</v>
       </c>
     </row>
     <row r="244">
@@ -11099,22 +11099,22 @@
         <v>0</v>
       </c>
       <c r="L247" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M247" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="N247" t="n">
         <v>8662</v>
       </c>
       <c r="O247" t="n">
-        <v>77958</v>
+        <v>51972</v>
       </c>
       <c r="P247" t="n">
         <v>14200</v>
       </c>
       <c r="Q247" t="n">
-        <v>127800</v>
+        <v>85200</v>
       </c>
     </row>
     <row r="248">
@@ -11186,22 +11186,22 @@
         <v>0</v>
       </c>
       <c r="L249" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M249" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N249" t="n">
         <v>10716.34</v>
       </c>
       <c r="O249" t="n">
-        <v>64298.04</v>
+        <v>53581.7</v>
       </c>
       <c r="P249" t="n">
         <v>39000</v>
       </c>
       <c r="Q249" t="n">
-        <v>234000</v>
+        <v>195000</v>
       </c>
     </row>
     <row r="250">
@@ -11360,13 +11360,13 @@
         </is>
       </c>
       <c r="J253" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K253" t="n">
         <v>0</v>
       </c>
       <c r="L253" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M253" t="n">
         <v>12</v>
@@ -11495,10 +11495,10 @@
         <v>134</v>
       </c>
       <c r="N256" t="n">
-        <v>3240.850037037</v>
+        <v>3240.8500371058</v>
       </c>
       <c r="O256" t="n">
-        <v>434273.904962958</v>
+        <v>434273.9049721772</v>
       </c>
       <c r="P256" t="n">
         <v>5200</v>
@@ -11627,22 +11627,22 @@
         <v>0</v>
       </c>
       <c r="L259" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M259" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="N259" t="n">
         <v>8154</v>
       </c>
       <c r="O259" t="n">
-        <v>130464</v>
+        <v>97848</v>
       </c>
       <c r="P259" t="n">
         <v>13500</v>
       </c>
       <c r="Q259" t="n">
-        <v>216000</v>
+        <v>162000</v>
       </c>
     </row>
     <row r="260">
@@ -11760,28 +11760,28 @@
         </is>
       </c>
       <c r="J262" t="n">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="K262" t="n">
         <v>0</v>
       </c>
       <c r="L262" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="M262" t="n">
-        <v>316</v>
+        <v>300</v>
       </c>
       <c r="N262" t="n">
         <v>2090.85</v>
       </c>
       <c r="O262" t="n">
-        <v>660708.6</v>
+        <v>627255</v>
       </c>
       <c r="P262" t="n">
         <v>2900</v>
       </c>
       <c r="Q262" t="n">
-        <v>916400</v>
+        <v>870000</v>
       </c>
     </row>
     <row r="263">
@@ -11903,10 +11903,10 @@
         <v>25</v>
       </c>
       <c r="N265" t="n">
-        <v>5191.4800278552</v>
+        <v>5191.4800280899</v>
       </c>
       <c r="O265" t="n">
-        <v>129787.00069638</v>
+        <v>129787.0007022475</v>
       </c>
       <c r="P265" t="n">
         <v>9100</v>
@@ -12883,7 +12883,7 @@
         </is>
       </c>
       <c r="J287" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K287" t="n">
         <v>0</v>
@@ -12892,19 +12892,19 @@
         <v>0</v>
       </c>
       <c r="M287" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="N287" t="n">
-        <v>4372.2107902432</v>
+        <v>4372.2107903559</v>
       </c>
       <c r="O287" t="n">
-        <v>4372.2107902432</v>
+        <v>34977.6863228472</v>
       </c>
       <c r="P287" t="n">
         <v>7500</v>
       </c>
       <c r="Q287" t="n">
-        <v>7500</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="288">
@@ -12973,13 +12973,13 @@
         </is>
       </c>
       <c r="J289" t="n">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="K289" t="n">
         <v>0</v>
       </c>
       <c r="L289" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M289" t="n">
         <v>56</v>
@@ -13014,13 +13014,13 @@
         </is>
       </c>
       <c r="J290" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K290" t="n">
         <v>0</v>
       </c>
       <c r="L290" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M290" t="n">
         <v>1</v>
@@ -13060,13 +13060,13 @@
         </is>
       </c>
       <c r="J291" t="n">
-        <v>212</v>
+        <v>271</v>
       </c>
       <c r="K291" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="L291" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M291" t="n">
         <v>271</v>
@@ -13188,13 +13188,13 @@
         </is>
       </c>
       <c r="J294" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K294" t="n">
         <v>0</v>
       </c>
       <c r="L294" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M294" t="n">
         <v>54</v>
@@ -13275,28 +13275,28 @@
         </is>
       </c>
       <c r="J296" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="K296" t="n">
         <v>0</v>
       </c>
       <c r="L296" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M296" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="N296" t="n">
         <v>4717</v>
       </c>
       <c r="O296" t="n">
-        <v>103774</v>
+        <v>84906</v>
       </c>
       <c r="P296" t="n">
         <v>7900</v>
       </c>
       <c r="Q296" t="n">
-        <v>173800</v>
+        <v>142200</v>
       </c>
     </row>
     <row r="297">
@@ -13501,28 +13501,28 @@
         </is>
       </c>
       <c r="J301" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K301" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L301" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M301" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="N301" t="n">
         <v>4648.6</v>
       </c>
       <c r="O301" t="n">
-        <v>395131.0000000001</v>
+        <v>381185.2</v>
       </c>
       <c r="P301" t="n">
         <v>8900</v>
       </c>
       <c r="Q301" t="n">
-        <v>756500</v>
+        <v>729800</v>
       </c>
     </row>
     <row r="302">
@@ -13594,13 +13594,13 @@
         </is>
       </c>
       <c r="J303" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K303" t="n">
         <v>0</v>
       </c>
       <c r="L303" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M303" t="n">
         <v>120</v>
@@ -13945,13 +13945,13 @@
         </is>
       </c>
       <c r="J311" t="n">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="K311" t="n">
         <v>0</v>
       </c>
       <c r="L311" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M311" t="n">
         <v>315</v>
@@ -14089,13 +14089,13 @@
         </is>
       </c>
       <c r="J314" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K314" t="n">
         <v>0</v>
       </c>
       <c r="L314" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M314" t="n">
         <v>75</v>
@@ -14275,13 +14275,13 @@
         </is>
       </c>
       <c r="J318" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K318" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L318" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M318" t="n">
         <v>12</v>
@@ -14321,13 +14321,13 @@
         </is>
       </c>
       <c r="J319" t="n">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="K319" t="n">
         <v>0</v>
       </c>
       <c r="L319" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M319" t="n">
         <v>265</v>
@@ -14562,22 +14562,22 @@
         <v>0</v>
       </c>
       <c r="L324" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M324" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="N324" t="n">
         <v>3761.6</v>
       </c>
       <c r="O324" t="n">
-        <v>244504</v>
+        <v>233219.2</v>
       </c>
       <c r="P324" t="n">
         <v>6900</v>
       </c>
       <c r="Q324" t="n">
-        <v>448500</v>
+        <v>427800</v>
       </c>
     </row>
     <row r="325">
@@ -15102,28 +15102,28 @@
         </is>
       </c>
       <c r="J336" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K336" t="n">
         <v>0</v>
       </c>
       <c r="L336" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M336" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="N336" t="n">
         <v>3751</v>
       </c>
       <c r="O336" t="n">
-        <v>431365</v>
+        <v>427614</v>
       </c>
       <c r="P336" t="n">
         <v>6400</v>
       </c>
       <c r="Q336" t="n">
-        <v>736000</v>
+        <v>729600</v>
       </c>
     </row>
     <row r="337">
@@ -15197,13 +15197,13 @@
         </is>
       </c>
       <c r="J338" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K338" t="n">
         <v>0</v>
       </c>
       <c r="L338" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M338" t="n">
         <v>6</v>
@@ -15289,22 +15289,22 @@
         </is>
       </c>
       <c r="J340" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="K340" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="L340" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M340" t="n">
         <v>96</v>
       </c>
       <c r="N340" t="n">
-        <v>1630.9236367936</v>
+        <v>1630.9236471425</v>
       </c>
       <c r="O340" t="n">
-        <v>156568.6691321856</v>
+        <v>156568.67012568</v>
       </c>
       <c r="P340" t="n">
         <v>2500</v>
@@ -15381,22 +15381,22 @@
         </is>
       </c>
       <c r="J342" t="n">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="K342" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="L342" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M342" t="n">
         <v>61</v>
       </c>
       <c r="N342" t="n">
-        <v>1690.5971524664</v>
+        <v>1690.5969977427</v>
       </c>
       <c r="O342" t="n">
-        <v>103126.4263004504</v>
+        <v>103126.4168623047</v>
       </c>
       <c r="P342" t="n">
         <v>2900</v>
@@ -15427,22 +15427,22 @@
         </is>
       </c>
       <c r="J343" t="n">
-        <v>392</v>
+        <v>406</v>
       </c>
       <c r="K343" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="L343" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="M343" t="n">
         <v>406</v>
       </c>
       <c r="N343" t="n">
-        <v>1550.1936973199</v>
+        <v>1550.1936995315</v>
       </c>
       <c r="O343" t="n">
-        <v>629378.6411118794</v>
+        <v>629378.642009789</v>
       </c>
       <c r="P343" t="n">
         <v>2500</v>
@@ -15519,22 +15519,22 @@
         </is>
       </c>
       <c r="J345" t="n">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="K345" t="n">
         <v>0</v>
       </c>
       <c r="L345" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M345" t="n">
         <v>228</v>
       </c>
       <c r="N345" t="n">
-        <v>2403.5120742613</v>
+        <v>2403.5121001364</v>
       </c>
       <c r="O345" t="n">
-        <v>548000.7529315763</v>
+        <v>548000.7588310993</v>
       </c>
       <c r="P345" t="n">
         <v>3500</v>
@@ -15565,22 +15565,22 @@
         </is>
       </c>
       <c r="J346" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="K346" t="n">
         <v>0</v>
       </c>
       <c r="L346" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M346" t="n">
         <v>59</v>
       </c>
       <c r="N346" t="n">
-        <v>2530.9356343284</v>
+        <v>2521.5268283582</v>
       </c>
       <c r="O346" t="n">
-        <v>149325.2024253756</v>
+        <v>148770.0828731338</v>
       </c>
       <c r="P346" t="n">
         <v>3900</v>
@@ -16186,13 +16186,13 @@
         </is>
       </c>
       <c r="J360" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K360" t="n">
         <v>0</v>
       </c>
       <c r="L360" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M360" t="n">
         <v>44</v>
@@ -16503,13 +16503,13 @@
         </is>
       </c>
       <c r="J367" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K367" t="n">
         <v>0</v>
       </c>
       <c r="L367" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M367" t="n">
         <v>22</v>
@@ -16903,22 +16903,22 @@
         <v>0</v>
       </c>
       <c r="L376" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M376" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N376" t="n">
         <v>6280.31</v>
       </c>
       <c r="O376" t="n">
-        <v>81644.03</v>
+        <v>69083.41</v>
       </c>
       <c r="P376" t="n">
         <v>10500</v>
       </c>
       <c r="Q376" t="n">
-        <v>136500</v>
+        <v>115500</v>
       </c>
     </row>
     <row r="377">
@@ -16995,22 +16995,22 @@
         <v>0</v>
       </c>
       <c r="L378" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M378" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N378" t="n">
         <v>14118.32</v>
       </c>
       <c r="O378" t="n">
-        <v>112946.56</v>
+        <v>84709.92</v>
       </c>
       <c r="P378" t="n">
         <v>17900</v>
       </c>
       <c r="Q378" t="n">
-        <v>143200</v>
+        <v>107400</v>
       </c>
     </row>
     <row r="379">
@@ -17978,13 +17978,13 @@
         </is>
       </c>
       <c r="J400" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K400" t="n">
         <v>0</v>
       </c>
       <c r="L400" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M400" t="n">
         <v>25</v>
@@ -18480,13 +18480,13 @@
         </is>
       </c>
       <c r="J412" t="n">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="K412" t="n">
         <v>0</v>
       </c>
       <c r="L412" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M412" t="n">
         <v>165</v>
@@ -18568,22 +18568,22 @@
         <v>0</v>
       </c>
       <c r="L414" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M414" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="N414" t="n">
         <v>2517.22</v>
       </c>
       <c r="O414" t="n">
-        <v>196343.16</v>
+        <v>183757.06</v>
       </c>
       <c r="P414" t="n">
         <v>4200</v>
       </c>
       <c r="Q414" t="n">
-        <v>327600</v>
+        <v>306600</v>
       </c>
     </row>
     <row r="415">
@@ -18820,10 +18820,10 @@
         <v>45</v>
       </c>
       <c r="N420" t="n">
-        <v>2680.7396988322</v>
+        <v>2680.739695084</v>
       </c>
       <c r="O420" t="n">
-        <v>120633.286447449</v>
+        <v>120633.28627878</v>
       </c>
       <c r="P420" t="n">
         <v>4900</v>
@@ -19674,7 +19674,7 @@
         </is>
       </c>
       <c r="J440" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K440" t="n">
         <v>0</v>
@@ -19683,19 +19683,19 @@
         <v>0</v>
       </c>
       <c r="M440" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N440" t="n">
         <v>9776.99</v>
       </c>
       <c r="O440" t="n">
-        <v>185762.81</v>
+        <v>175985.82</v>
       </c>
       <c r="P440" t="n">
         <v>15900</v>
       </c>
       <c r="Q440" t="n">
-        <v>302100</v>
+        <v>286200</v>
       </c>
     </row>
     <row r="441">
@@ -20146,22 +20146,22 @@
         <v>0</v>
       </c>
       <c r="L451" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M451" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N451" t="n">
-        <v>11562.038474114</v>
+        <v>11562.038465753</v>
       </c>
       <c r="O451" t="n">
-        <v>173430.57711171</v>
+        <v>161868.538520542</v>
       </c>
       <c r="P451" t="n">
         <v>18500</v>
       </c>
       <c r="Q451" t="n">
-        <v>277500</v>
+        <v>259000</v>
       </c>
     </row>
     <row r="452">
@@ -20192,22 +20192,22 @@
         <v>0</v>
       </c>
       <c r="L452" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M452" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N452" t="n">
-        <v>13513.643059701</v>
+        <v>13513.643082707</v>
       </c>
       <c r="O452" t="n">
-        <v>175677.359776113</v>
+        <v>148650.073909777</v>
       </c>
       <c r="P452" t="n">
         <v>21900</v>
       </c>
       <c r="Q452" t="n">
-        <v>284700</v>
+        <v>240900</v>
       </c>
     </row>
     <row r="453">
@@ -20443,22 +20443,22 @@
         <v>0</v>
       </c>
       <c r="L458" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M458" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N458" t="n">
         <v>15700</v>
       </c>
       <c r="O458" t="n">
-        <v>125600</v>
+        <v>109900</v>
       </c>
       <c r="P458" t="n">
         <v>29900</v>
       </c>
       <c r="Q458" t="n">
-        <v>239200</v>
+        <v>209300</v>
       </c>
     </row>
     <row r="459">
@@ -20570,13 +20570,13 @@
         </is>
       </c>
       <c r="J461" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K461" t="n">
         <v>0</v>
       </c>
       <c r="L461" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M461" t="n">
         <v>24</v>
@@ -21104,10 +21104,10 @@
         <v>56</v>
       </c>
       <c r="N473" t="n">
-        <v>1561.0009152542</v>
+        <v>1561.0009337861</v>
       </c>
       <c r="O473" t="n">
-        <v>87416.05125423519</v>
+        <v>87416.0522920216</v>
       </c>
       <c r="P473" t="n">
         <v>2900</v>
@@ -21236,22 +21236,22 @@
         <v>0</v>
       </c>
       <c r="L476" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M476" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N476" t="n">
         <v>26854</v>
       </c>
       <c r="O476" t="n">
-        <v>456518</v>
+        <v>402810</v>
       </c>
       <c r="P476" t="n">
         <v>43900</v>
       </c>
       <c r="Q476" t="n">
-        <v>746300</v>
+        <v>658500</v>
       </c>
     </row>
     <row r="477">
@@ -22144,13 +22144,13 @@
         </is>
       </c>
       <c r="J497" t="n">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="K497" t="n">
         <v>0</v>
       </c>
       <c r="L497" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M497" t="n">
         <v>149</v>
@@ -22777,13 +22777,13 @@
         </is>
       </c>
       <c r="J511" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K511" t="n">
         <v>0</v>
       </c>
       <c r="L511" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M511" t="n">
         <v>11</v>
@@ -23578,13 +23578,13 @@
         </is>
       </c>
       <c r="J529" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K529" t="n">
         <v>0</v>
       </c>
       <c r="L529" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M529" t="n">
         <v>6</v>
@@ -23728,10 +23728,10 @@
         <v>6</v>
       </c>
       <c r="N532" t="n">
-        <v>5218.170554855</v>
+        <v>5218.1705597964</v>
       </c>
       <c r="O532" t="n">
-        <v>31309.02332913</v>
+        <v>31309.0233587784</v>
       </c>
       <c r="P532" t="n">
         <v>8500</v>
@@ -24418,13 +24418,13 @@
         </is>
       </c>
       <c r="J547" t="n">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="K547" t="n">
         <v>0</v>
       </c>
       <c r="L547" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M547" t="n">
         <v>123</v>
@@ -25534,10 +25534,10 @@
         </is>
       </c>
       <c r="J571" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K571" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L571" t="n">
         <v>0</v>
@@ -26648,28 +26648,28 @@
         </is>
       </c>
       <c r="J595" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K595" t="n">
         <v>0</v>
       </c>
       <c r="L595" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M595" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="N595" t="n">
         <v>3938.66</v>
       </c>
       <c r="O595" t="n">
-        <v>149669.08</v>
+        <v>141791.76</v>
       </c>
       <c r="P595" t="n">
         <v>4500</v>
       </c>
       <c r="Q595" t="n">
-        <v>171000</v>
+        <v>162000</v>
       </c>
     </row>
     <row r="596">
@@ -26746,22 +26746,22 @@
         <v>0</v>
       </c>
       <c r="L597" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M597" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="N597" t="n">
         <v>12709</v>
       </c>
       <c r="O597" t="n">
-        <v>139799</v>
+        <v>114381</v>
       </c>
       <c r="P597" t="n">
         <v>20500</v>
       </c>
       <c r="Q597" t="n">
-        <v>225500</v>
+        <v>184500</v>
       </c>
     </row>
     <row r="598">
@@ -26792,22 +26792,22 @@
         <v>0</v>
       </c>
       <c r="L598" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M598" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N598" t="n">
         <v>28116</v>
       </c>
       <c r="O598" t="n">
-        <v>84348</v>
+        <v>56232</v>
       </c>
       <c r="P598" t="n">
         <v>45900</v>
       </c>
       <c r="Q598" t="n">
-        <v>137700</v>
+        <v>91800</v>
       </c>
     </row>
     <row r="599">
@@ -26832,7 +26832,7 @@
         </is>
       </c>
       <c r="J599" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K599" t="n">
         <v>0</v>
@@ -26841,19 +26841,19 @@
         <v>1</v>
       </c>
       <c r="M599" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="N599" t="n">
         <v>3424</v>
       </c>
       <c r="O599" t="n">
-        <v>109568</v>
+        <v>106144</v>
       </c>
       <c r="P599" t="n">
         <v>5900</v>
       </c>
       <c r="Q599" t="n">
-        <v>188800</v>
+        <v>182900</v>
       </c>
     </row>
     <row r="600">
@@ -27253,22 +27253,22 @@
         <v>0</v>
       </c>
       <c r="L608" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M608" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N608" t="n">
         <v>13019</v>
       </c>
       <c r="O608" t="n">
-        <v>78114</v>
+        <v>39057</v>
       </c>
       <c r="P608" t="n">
         <v>20900</v>
       </c>
       <c r="Q608" t="n">
-        <v>125400</v>
+        <v>62700</v>
       </c>
     </row>
     <row r="609">
@@ -28817,28 +28817,28 @@
         </is>
       </c>
       <c r="J642" t="n">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="K642" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L642" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M642" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="N642" t="n">
         <v>3903.7366972477</v>
       </c>
       <c r="O642" t="n">
-        <v>374758.7229357792</v>
+        <v>359143.7761467884</v>
       </c>
       <c r="P642" t="n">
         <v>7500</v>
       </c>
       <c r="Q642" t="n">
-        <v>720000</v>
+        <v>690000</v>
       </c>
     </row>
     <row r="643">
@@ -28956,22 +28956,22 @@
         <v>0</v>
       </c>
       <c r="L645" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M645" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="N645" t="n">
         <v>12113</v>
       </c>
       <c r="O645" t="n">
-        <v>181695</v>
+        <v>145356</v>
       </c>
       <c r="P645" t="n">
         <v>19900</v>
       </c>
       <c r="Q645" t="n">
-        <v>298500</v>
+        <v>238800</v>
       </c>
     </row>
     <row r="646">
@@ -29318,10 +29318,10 @@
         </is>
       </c>
       <c r="J653" t="n">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="K653" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="L653" t="n">
         <v>0</v>
@@ -29830,22 +29830,22 @@
         <v>0</v>
       </c>
       <c r="L664" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M664" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N664" t="n">
         <v>7635</v>
       </c>
       <c r="O664" t="n">
-        <v>137430</v>
+        <v>129795</v>
       </c>
       <c r="P664" t="n">
         <v>13900</v>
       </c>
       <c r="Q664" t="n">
-        <v>250200</v>
+        <v>236300</v>
       </c>
     </row>
     <row r="665">
@@ -30333,13 +30333,13 @@
         </is>
       </c>
       <c r="J675" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K675" t="n">
         <v>0</v>
       </c>
       <c r="L675" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M675" t="n">
         <v>35</v>
@@ -30889,22 +30889,22 @@
         <v>0</v>
       </c>
       <c r="L687" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M687" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N687" t="n">
         <v>20014</v>
       </c>
       <c r="O687" t="n">
-        <v>20014</v>
+        <v>0</v>
       </c>
       <c r="P687" t="n">
         <v>33900</v>
       </c>
       <c r="Q687" t="n">
-        <v>33900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="688">
@@ -32125,13 +32125,13 @@
         </is>
       </c>
       <c r="J714" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K714" t="n">
         <v>0</v>
       </c>
       <c r="L714" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M714" t="n">
         <v>8</v>
@@ -32261,10 +32261,10 @@
         </is>
       </c>
       <c r="J717" t="n">
-        <v>227</v>
+        <v>299</v>
       </c>
       <c r="K717" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="L717" t="n">
         <v>0</v>
@@ -32273,10 +32273,10 @@
         <v>299</v>
       </c>
       <c r="N717" t="n">
-        <v>2458.5130759032</v>
+        <v>2458.5130690113</v>
       </c>
       <c r="O717" t="n">
-        <v>735095.4096950567</v>
+        <v>735095.4076343788</v>
       </c>
       <c r="P717" t="n">
         <v>3500</v>
@@ -32353,10 +32353,10 @@
         </is>
       </c>
       <c r="J719" t="n">
-        <v>40</v>
+        <v>184</v>
       </c>
       <c r="K719" t="n">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="L719" t="n">
         <v>0</v>
@@ -32399,10 +32399,10 @@
         </is>
       </c>
       <c r="J720" t="n">
-        <v>122</v>
+        <v>218</v>
       </c>
       <c r="K720" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="L720" t="n">
         <v>0</v>
@@ -32491,10 +32491,10 @@
         </is>
       </c>
       <c r="J722" t="n">
-        <v>51</v>
+        <v>111</v>
       </c>
       <c r="K722" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="L722" t="n">
         <v>0</v>
@@ -32537,10 +32537,10 @@
         </is>
       </c>
       <c r="J723" t="n">
-        <v>40</v>
+        <v>232</v>
       </c>
       <c r="K723" t="n">
-        <v>192</v>
+        <v>0</v>
       </c>
       <c r="L723" t="n">
         <v>0</v>
@@ -32583,22 +32583,22 @@
         </is>
       </c>
       <c r="J724" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K724" t="n">
         <v>0</v>
       </c>
       <c r="L724" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M724" t="n">
         <v>78</v>
       </c>
       <c r="N724" t="n">
-        <v>2108.792083045</v>
+        <v>2108.7921081831</v>
       </c>
       <c r="O724" t="n">
-        <v>164485.78247751</v>
+        <v>164485.7844382818</v>
       </c>
       <c r="P724" t="n">
         <v>2900</v>
@@ -32641,10 +32641,10 @@
         <v>259</v>
       </c>
       <c r="N725" t="n">
-        <v>2056.0829891304</v>
+        <v>2056.0829843644</v>
       </c>
       <c r="O725" t="n">
-        <v>532525.4941847736</v>
+        <v>532525.4929503796</v>
       </c>
       <c r="P725" t="n">
         <v>2900</v>
@@ -32675,10 +32675,10 @@
         </is>
       </c>
       <c r="J726" t="n">
-        <v>73</v>
+        <v>199</v>
       </c>
       <c r="K726" t="n">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="L726" t="n">
         <v>0</v>
@@ -33000,22 +33000,22 @@
         </is>
       </c>
       <c r="J733" t="n">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="K733" t="n">
         <v>0</v>
       </c>
       <c r="L733" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M733" t="n">
         <v>68</v>
       </c>
       <c r="N733" t="n">
-        <v>1592.2787749004</v>
+        <v>1592.27881</v>
       </c>
       <c r="O733" t="n">
-        <v>108274.9566932272</v>
+        <v>108274.95908</v>
       </c>
       <c r="P733" t="n">
         <v>2500</v>
@@ -33223,22 +33223,22 @@
         </is>
       </c>
       <c r="J738" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K738" t="n">
         <v>0</v>
       </c>
       <c r="L738" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M738" t="n">
         <v>43</v>
       </c>
       <c r="N738" t="n">
-        <v>1906.1834782609</v>
+        <v>1906.1829245283</v>
       </c>
       <c r="O738" t="n">
-        <v>81965.88956521871</v>
+        <v>81965.8657547169</v>
       </c>
       <c r="P738" t="n">
         <v>2900</v>
@@ -33361,13 +33361,13 @@
         </is>
       </c>
       <c r="J741" t="n">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="K741" t="n">
         <v>0</v>
       </c>
       <c r="L741" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M741" t="n">
         <v>85</v>
@@ -33419,10 +33419,10 @@
         <v>152</v>
       </c>
       <c r="N742" t="n">
-        <v>2546.9838660907</v>
+        <v>2546.9837028825</v>
       </c>
       <c r="O742" t="n">
-        <v>387141.5476457864</v>
+        <v>387141.52283814</v>
       </c>
       <c r="P742" t="n">
         <v>3900</v>
@@ -33453,13 +33453,13 @@
         </is>
       </c>
       <c r="J743" t="n">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="K743" t="n">
         <v>0</v>
       </c>
       <c r="L743" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M743" t="n">
         <v>192</v>
@@ -33632,13 +33632,13 @@
         </is>
       </c>
       <c r="J747" t="n">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="K747" t="n">
         <v>0</v>
       </c>
       <c r="L747" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M747" t="n">
         <v>110</v>
@@ -33676,28 +33676,28 @@
         </is>
       </c>
       <c r="J748" t="n">
+        <v>374</v>
+      </c>
+      <c r="K748" t="n">
+        <v>0</v>
+      </c>
+      <c r="L748" t="n">
+        <v>24</v>
+      </c>
+      <c r="M748" t="n">
         <v>350</v>
-      </c>
-      <c r="K748" t="n">
-        <v>24</v>
-      </c>
-      <c r="L748" t="n">
-        <v>0</v>
-      </c>
-      <c r="M748" t="n">
-        <v>374</v>
       </c>
       <c r="N748" t="n">
         <v>692.15222920696</v>
       </c>
       <c r="O748" t="n">
-        <v>258864.933723403</v>
+        <v>242253.280222436</v>
       </c>
       <c r="P748" t="n">
         <v>1200</v>
       </c>
       <c r="Q748" t="n">
-        <v>448800</v>
+        <v>420000</v>
       </c>
     </row>
     <row r="749">
@@ -33769,10 +33769,10 @@
         </is>
       </c>
       <c r="J750" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K750" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L750" t="n">
         <v>0</v>
@@ -34468,7 +34468,7 @@
         </is>
       </c>
       <c r="J765" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="K765" t="n">
         <v>0</v>
@@ -34477,19 +34477,19 @@
         <v>0</v>
       </c>
       <c r="M765" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="N765" t="n">
         <v>8945.379999999999</v>
       </c>
       <c r="O765" t="n">
-        <v>822974.96</v>
+        <v>805084.2</v>
       </c>
       <c r="P765" t="n">
         <v>14900</v>
       </c>
       <c r="Q765" t="n">
-        <v>1370800</v>
+        <v>1341000</v>
       </c>
     </row>
     <row r="766">
@@ -34661,22 +34661,22 @@
         <v>0</v>
       </c>
       <c r="L769" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M769" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N769" t="n">
         <v>2682.71</v>
       </c>
       <c r="O769" t="n">
-        <v>21461.68</v>
+        <v>16096.26</v>
       </c>
       <c r="P769" t="n">
         <v>10900</v>
       </c>
       <c r="Q769" t="n">
-        <v>87200</v>
+        <v>65400</v>
       </c>
     </row>
     <row r="770">
@@ -35128,22 +35128,22 @@
         <v>0</v>
       </c>
       <c r="L779" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M779" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="N779" t="n">
         <v>3629.36</v>
       </c>
       <c r="O779" t="n">
-        <v>47181.68</v>
+        <v>32664.24</v>
       </c>
       <c r="P779" t="n">
         <v>3900</v>
       </c>
       <c r="Q779" t="n">
-        <v>50700</v>
+        <v>35100</v>
       </c>
     </row>
     <row r="780">
@@ -35774,22 +35774,22 @@
         <v>0</v>
       </c>
       <c r="L793" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M793" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N793" t="n">
         <v>4979.58</v>
       </c>
       <c r="O793" t="n">
-        <v>24897.9</v>
+        <v>9959.16</v>
       </c>
       <c r="P793" t="n">
         <v>6500</v>
       </c>
       <c r="Q793" t="n">
-        <v>32500</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="794">
@@ -36383,13 +36383,13 @@
         </is>
       </c>
       <c r="J806" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K806" t="n">
         <v>0</v>
       </c>
       <c r="L806" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M806" t="n">
         <v>1</v>
@@ -37483,10 +37483,10 @@
         <v>22</v>
       </c>
       <c r="N830" t="n">
-        <v>4032.3968461538</v>
+        <v>4032.3968380463</v>
       </c>
       <c r="O830" t="n">
-        <v>88712.73061538361</v>
+        <v>88712.7304370186</v>
       </c>
       <c r="P830" t="n">
         <v>4200</v>
@@ -37569,28 +37569,28 @@
         </is>
       </c>
       <c r="J832" t="n">
-        <v>992</v>
+        <v>1265</v>
       </c>
       <c r="K832" t="n">
-        <v>312</v>
+        <v>0</v>
       </c>
       <c r="L832" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="M832" t="n">
-        <v>1289</v>
+        <v>1241</v>
       </c>
       <c r="N832" t="n">
-        <v>517.28990087531</v>
+        <v>517.2899423715</v>
       </c>
       <c r="O832" t="n">
-        <v>666786.6822282745</v>
+        <v>641956.8184830316</v>
       </c>
       <c r="P832" t="n">
         <v>900</v>
       </c>
       <c r="Q832" t="n">
-        <v>1160100</v>
+        <v>1116900</v>
       </c>
     </row>
     <row r="833">
@@ -37894,13 +37894,13 @@
         </is>
       </c>
       <c r="J839" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="K839" t="n">
         <v>0</v>
       </c>
       <c r="L839" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M839" t="n">
         <v>23</v>
@@ -38096,10 +38096,10 @@
         <v>270</v>
       </c>
       <c r="N843" t="n">
-        <v>3110.8414032101</v>
+        <v>3110.8413822526</v>
       </c>
       <c r="O843" t="n">
-        <v>839927.178866727</v>
+        <v>839927.173208202</v>
       </c>
       <c r="P843" t="n">
         <v>4500</v>
@@ -38133,10 +38133,10 @@
         </is>
       </c>
       <c r="J844" t="n">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="K844" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="L844" t="n">
         <v>0</v>
@@ -38267,13 +38267,13 @@
         </is>
       </c>
       <c r="J847" t="n">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="K847" t="n">
         <v>0</v>
       </c>
       <c r="L847" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M847" t="n">
         <v>131</v>
@@ -38508,10 +38508,10 @@
         <v>302</v>
       </c>
       <c r="N852" t="n">
-        <v>703.79516919374</v>
+        <v>703.79516599434</v>
       </c>
       <c r="O852" t="n">
-        <v>212546.1410965095</v>
+        <v>212546.1401302907</v>
       </c>
       <c r="P852" t="n">
         <v>900</v>
@@ -39510,13 +39510,13 @@
         </is>
       </c>
       <c r="J874" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="K874" t="n">
         <v>0</v>
       </c>
       <c r="L874" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M874" t="n">
         <v>52</v>
@@ -40715,13 +40715,13 @@
         </is>
       </c>
       <c r="J899" t="n">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="K899" t="n">
         <v>0</v>
       </c>
       <c r="L899" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M899" t="n">
         <v>207</v>
@@ -41144,13 +41144,13 @@
         </is>
       </c>
       <c r="J908" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K908" t="n">
         <v>0</v>
       </c>
       <c r="L908" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M908" t="n">
         <v>3</v>
@@ -41686,22 +41686,22 @@
         <v>0</v>
       </c>
       <c r="L919" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M919" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N919" t="n">
         <v>5796.3355555556</v>
       </c>
       <c r="O919" t="n">
-        <v>98537.7044444452</v>
+        <v>86945.03333333399</v>
       </c>
       <c r="P919" t="n">
         <v>15900</v>
       </c>
       <c r="Q919" t="n">
-        <v>270300</v>
+        <v>238500</v>
       </c>
     </row>
     <row r="920">
@@ -41790,10 +41790,10 @@
         <v>13</v>
       </c>
       <c r="N921" t="n">
-        <v>9746.8801904762</v>
+        <v>9746.880194174801</v>
       </c>
       <c r="O921" t="n">
-        <v>126709.4424761906</v>
+        <v>126709.4425242724</v>
       </c>
       <c r="P921" t="n">
         <v>18500</v>
@@ -42268,22 +42268,22 @@
         <v>0</v>
       </c>
       <c r="L931" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M931" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="N931" t="n">
         <v>6989.34</v>
       </c>
       <c r="O931" t="n">
-        <v>188712.18</v>
+        <v>174733.5</v>
       </c>
       <c r="P931" t="n">
         <v>10900</v>
       </c>
       <c r="Q931" t="n">
-        <v>294300</v>
+        <v>272500</v>
       </c>
     </row>
     <row r="932">
@@ -43945,22 +43945,22 @@
         <v>0</v>
       </c>
       <c r="L966" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M966" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N966" t="n">
         <v>5876.81</v>
       </c>
       <c r="O966" t="n">
-        <v>41137.67000000001</v>
+        <v>35260.86</v>
       </c>
       <c r="P966" t="n">
         <v>22900</v>
       </c>
       <c r="Q966" t="n">
-        <v>160300</v>
+        <v>137400</v>
       </c>
     </row>
     <row r="967">
@@ -44129,10 +44129,10 @@
         </is>
       </c>
       <c r="J970" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K970" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L970" t="n">
         <v>0</v>
@@ -44611,22 +44611,22 @@
         <v>0</v>
       </c>
       <c r="L980" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M980" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N980" t="n">
         <v>13377.81</v>
       </c>
       <c r="O980" t="n">
-        <v>26755.62</v>
+        <v>13377.81</v>
       </c>
       <c r="P980" t="n">
         <v>36900</v>
       </c>
       <c r="Q980" t="n">
-        <v>73800</v>
+        <v>36900</v>
       </c>
     </row>
     <row r="981">
@@ -45406,13 +45406,13 @@
         </is>
       </c>
       <c r="J997" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K997" t="n">
         <v>0</v>
       </c>
       <c r="L997" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M997" t="n">
         <v>8</v>
@@ -45888,13 +45888,13 @@
         </is>
       </c>
       <c r="J1007" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K1007" t="n">
         <v>0</v>
       </c>
       <c r="L1007" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M1007" t="n">
         <v>12</v>
@@ -46565,13 +46565,13 @@
         </is>
       </c>
       <c r="J1021" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="K1021" t="n">
         <v>0</v>
       </c>
       <c r="L1021" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M1021" t="n">
         <v>12</v>
@@ -47878,13 +47878,13 @@
         </is>
       </c>
       <c r="J1050" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="K1050" t="n">
         <v>0</v>
       </c>
       <c r="L1050" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M1050" t="n">
         <v>65</v>
@@ -47975,10 +47975,10 @@
         <v>50</v>
       </c>
       <c r="N1052" t="n">
-        <v>1794.2879692219</v>
+        <v>1794.2879686376</v>
       </c>
       <c r="O1052" t="n">
-        <v>89714.398461095</v>
+        <v>89714.39843187999</v>
       </c>
       <c r="P1052" t="n">
         <v>1600</v>
@@ -48107,10 +48107,10 @@
         <v>9</v>
       </c>
       <c r="N1055" t="n">
-        <v>2523.3377470356</v>
+        <v>2523.3377457627</v>
       </c>
       <c r="O1055" t="n">
-        <v>22710.0397233204</v>
+        <v>22710.0397118643</v>
       </c>
       <c r="P1055" t="n">
         <v>2800</v>
@@ -48373,7 +48373,7 @@
         </is>
       </c>
       <c r="J1061" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K1061" t="n">
         <v>0</v>
@@ -48382,19 +48382,19 @@
         <v>2</v>
       </c>
       <c r="M1061" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N1061" t="n">
         <v>22951.704799483</v>
       </c>
       <c r="O1061" t="n">
-        <v>91806.819197932</v>
+        <v>45903.409598966</v>
       </c>
       <c r="P1061" t="n">
         <v>37900</v>
       </c>
       <c r="Q1061" t="n">
-        <v>151600</v>
+        <v>75800</v>
       </c>
     </row>
     <row r="1062">
@@ -48509,13 +48509,13 @@
         </is>
       </c>
       <c r="J1064" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K1064" t="n">
         <v>0</v>
       </c>
       <c r="L1064" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M1064" t="n">
         <v>76</v>
@@ -50224,13 +50224,13 @@
         </is>
       </c>
       <c r="J1101" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K1101" t="n">
         <v>0</v>
       </c>
       <c r="L1101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1101" t="n">
         <v>7</v>
@@ -50270,28 +50270,28 @@
         </is>
       </c>
       <c r="J1102" t="n">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="K1102" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="L1102" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M1102" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="N1102" t="n">
         <v>1952.66</v>
       </c>
       <c r="O1102" t="n">
-        <v>119112.26</v>
+        <v>109348.96</v>
       </c>
       <c r="P1102" t="n">
         <v>3500</v>
       </c>
       <c r="Q1102" t="n">
-        <v>213500</v>
+        <v>196000</v>
       </c>
     </row>
     <row r="1103">
@@ -51052,13 +51052,13 @@
         </is>
       </c>
       <c r="J1119" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="K1119" t="n">
         <v>0</v>
       </c>
       <c r="L1119" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M1119" t="n">
         <v>62</v>
@@ -51098,13 +51098,13 @@
         </is>
       </c>
       <c r="J1120" t="n">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="K1120" t="n">
         <v>0</v>
       </c>
       <c r="L1120" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M1120" t="n">
         <v>117</v>
@@ -51150,22 +51150,22 @@
         <v>0</v>
       </c>
       <c r="L1121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1121" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N1121" t="n">
         <v>5280</v>
       </c>
       <c r="O1121" t="n">
-        <v>116160</v>
+        <v>110880</v>
       </c>
       <c r="P1121" t="n">
         <v>6900</v>
       </c>
       <c r="Q1121" t="n">
-        <v>151800</v>
+        <v>144900</v>
       </c>
     </row>
     <row r="1122">
@@ -51236,13 +51236,13 @@
         </is>
       </c>
       <c r="J1123" t="n">
-        <v>257</v>
+        <v>242</v>
       </c>
       <c r="K1123" t="n">
         <v>0</v>
       </c>
       <c r="L1123" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M1123" t="n">
         <v>242</v>
@@ -51282,13 +51282,13 @@
         </is>
       </c>
       <c r="J1124" t="n">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="K1124" t="n">
         <v>0</v>
       </c>
       <c r="L1124" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M1124" t="n">
         <v>151</v>
@@ -51426,22 +51426,22 @@
         <v>0</v>
       </c>
       <c r="L1127" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M1127" t="n">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="N1127" t="n">
         <v>3520</v>
       </c>
       <c r="O1127" t="n">
-        <v>440000</v>
+        <v>425920</v>
       </c>
       <c r="P1127" t="n">
         <v>4500</v>
       </c>
       <c r="Q1127" t="n">
-        <v>562500</v>
+        <v>544500</v>
       </c>
     </row>
     <row r="1128">
@@ -51564,22 +51564,22 @@
         <v>0</v>
       </c>
       <c r="L1130" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1130" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N1130" t="n">
         <v>9240</v>
       </c>
       <c r="O1130" t="n">
-        <v>498960</v>
+        <v>480480</v>
       </c>
       <c r="P1130" t="n">
         <v>11500</v>
       </c>
       <c r="Q1130" t="n">
-        <v>621000</v>
+        <v>598000</v>
       </c>
     </row>
     <row r="1131">
@@ -51604,13 +51604,13 @@
         </is>
       </c>
       <c r="J1131" t="n">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="K1131" t="n">
         <v>0</v>
       </c>
       <c r="L1131" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M1131" t="n">
         <v>536</v>
@@ -53128,22 +53128,22 @@
         <v>0</v>
       </c>
       <c r="L1164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1164" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N1164" t="n">
         <v>32.41</v>
       </c>
       <c r="O1164" t="n">
-        <v>226.87</v>
+        <v>194.46</v>
       </c>
       <c r="P1164" t="n">
         <v>13500</v>
       </c>
       <c r="Q1164" t="n">
-        <v>94500</v>
+        <v>81000</v>
       </c>
     </row>
     <row r="1165">
@@ -53746,22 +53746,22 @@
         <v>0</v>
       </c>
       <c r="L1177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1177" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N1177" t="n">
         <v>1319.360887574</v>
       </c>
       <c r="O1177" t="n">
-        <v>30345.300414202</v>
+        <v>29025.939526628</v>
       </c>
       <c r="P1177" t="n">
         <v>3500</v>
       </c>
       <c r="Q1177" t="n">
-        <v>80500</v>
+        <v>77000</v>
       </c>
     </row>
     <row r="1178">
@@ -53940,22 +53940,22 @@
         <v>0</v>
       </c>
       <c r="L1181" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M1181" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="N1181" t="n">
         <v>2432.1351111111</v>
       </c>
       <c r="O1181" t="n">
-        <v>70531.9182222219</v>
+        <v>63235.5128888886</v>
       </c>
       <c r="P1181" t="n">
         <v>4500</v>
       </c>
       <c r="Q1181" t="n">
-        <v>130500</v>
+        <v>117000</v>
       </c>
     </row>
     <row r="1182">
@@ -54129,22 +54129,22 @@
         <v>0</v>
       </c>
       <c r="L1185" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1185" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N1185" t="n">
         <v>9917.040000000001</v>
       </c>
       <c r="O1185" t="n">
-        <v>109087.44</v>
+        <v>99170.40000000001</v>
       </c>
       <c r="P1185" t="n">
         <v>15900</v>
       </c>
       <c r="Q1185" t="n">
-        <v>174900</v>
+        <v>159000</v>
       </c>
     </row>
     <row r="1186">
@@ -55964,28 +55964,28 @@
         </is>
       </c>
       <c r="J1225" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K1225" t="n">
         <v>0</v>
       </c>
       <c r="L1225" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1225" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="N1225" t="n">
         <v>4550</v>
       </c>
       <c r="O1225" t="n">
-        <v>323050</v>
+        <v>318500</v>
       </c>
       <c r="P1225" t="n">
         <v>5500</v>
       </c>
       <c r="Q1225" t="n">
-        <v>390500</v>
+        <v>385000</v>
       </c>
     </row>
     <row r="1226">

--- a/bodegas/LJ-101.xlsx
+++ b/bodegas/LJ-101.xlsx
@@ -944,10 +944,10 @@
         <v>26</v>
       </c>
       <c r="N13" t="n">
-        <v>1811.307345576</v>
+        <v>1811.3074074074</v>
       </c>
       <c r="O13" t="n">
-        <v>47093.990984976</v>
+        <v>47093.9925925924</v>
       </c>
       <c r="P13" t="n">
         <v>2600</v>
@@ -1821,10 +1821,10 @@
         <v>21</v>
       </c>
       <c r="N35" t="n">
-        <v>3926.8370969414</v>
+        <v>3926.8370954357</v>
       </c>
       <c r="O35" t="n">
-        <v>82463.57903576941</v>
+        <v>82463.57900414971</v>
       </c>
       <c r="P35" t="n">
         <v>4800</v>
@@ -3741,22 +3741,22 @@
         <v>0</v>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M80" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N80" t="n">
-        <v>15711.965922747</v>
+        <v>15711.965905172</v>
       </c>
       <c r="O80" t="n">
-        <v>157119.65922747</v>
+        <v>141407.693146548</v>
       </c>
       <c r="P80" t="n">
         <v>28500</v>
       </c>
       <c r="Q80" t="n">
-        <v>285000</v>
+        <v>256500</v>
       </c>
     </row>
     <row r="81">
@@ -8026,22 +8026,22 @@
         <v>0</v>
       </c>
       <c r="L179" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M179" t="n">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="N179" t="n">
-        <v>1098.0597873486</v>
+        <v>1098.0598890693</v>
       </c>
       <c r="O179" t="n">
-        <v>449106.4530255774</v>
+        <v>440322.0155167893</v>
       </c>
       <c r="P179" t="n">
         <v>1500</v>
       </c>
       <c r="Q179" t="n">
-        <v>613500</v>
+        <v>601500</v>
       </c>
     </row>
     <row r="180">
@@ -9497,22 +9497,22 @@
         <v>0</v>
       </c>
       <c r="L212" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M212" t="n">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="N212" t="n">
-        <v>3158.8608262318</v>
+        <v>3160.2538267431</v>
       </c>
       <c r="O212" t="n">
-        <v>1222479.139751707</v>
+        <v>1194575.946508892</v>
       </c>
       <c r="P212" t="n">
         <v>5600</v>
       </c>
       <c r="Q212" t="n">
-        <v>2167200</v>
+        <v>2116800</v>
       </c>
     </row>
     <row r="213">
@@ -9589,22 +9589,22 @@
         <v>0</v>
       </c>
       <c r="L214" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M214" t="n">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="N214" t="n">
-        <v>3841.6248214286</v>
+        <v>3856.9300996016</v>
       </c>
       <c r="O214" t="n">
-        <v>514777.7260714324</v>
+        <v>501400.912948208</v>
       </c>
       <c r="P214" t="n">
         <v>6900</v>
       </c>
       <c r="Q214" t="n">
-        <v>924600</v>
+        <v>897000</v>
       </c>
     </row>
     <row r="215">
@@ -10001,22 +10001,22 @@
         <v>0</v>
       </c>
       <c r="L223" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M223" t="n">
-        <v>1842</v>
+        <v>1832</v>
       </c>
       <c r="N223" t="n">
         <v>156.25</v>
       </c>
       <c r="O223" t="n">
-        <v>287812.5</v>
+        <v>286250</v>
       </c>
       <c r="P223" t="n">
         <v>250</v>
       </c>
       <c r="Q223" t="n">
-        <v>460500</v>
+        <v>458000</v>
       </c>
     </row>
     <row r="224">
@@ -10690,22 +10690,22 @@
         <v>0</v>
       </c>
       <c r="L238" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M238" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="N238" t="n">
         <v>1203.38</v>
       </c>
       <c r="O238" t="n">
-        <v>24067.6</v>
+        <v>16847.32</v>
       </c>
       <c r="P238" t="n">
         <v>1900</v>
       </c>
       <c r="Q238" t="n">
-        <v>38000</v>
+        <v>26600</v>
       </c>
     </row>
     <row r="239">
@@ -11186,22 +11186,22 @@
         <v>0</v>
       </c>
       <c r="L249" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M249" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N249" t="n">
         <v>10716.34</v>
       </c>
       <c r="O249" t="n">
-        <v>53581.7</v>
+        <v>21432.68</v>
       </c>
       <c r="P249" t="n">
         <v>39000</v>
       </c>
       <c r="Q249" t="n">
-        <v>195000</v>
+        <v>78000</v>
       </c>
     </row>
     <row r="250">
@@ -11282,10 +11282,10 @@
         <v>12</v>
       </c>
       <c r="N251" t="n">
-        <v>3594.254</v>
+        <v>3594.2539962477</v>
       </c>
       <c r="O251" t="n">
-        <v>43131.048</v>
+        <v>43131.0479549724</v>
       </c>
       <c r="P251" t="n">
         <v>6500</v>
@@ -11766,22 +11766,22 @@
         <v>0</v>
       </c>
       <c r="L262" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M262" t="n">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="N262" t="n">
-        <v>2090.85</v>
+        <v>2091.1308394896</v>
       </c>
       <c r="O262" t="n">
-        <v>627255</v>
+        <v>623156.9901679008</v>
       </c>
       <c r="P262" t="n">
         <v>2900</v>
       </c>
       <c r="Q262" t="n">
-        <v>870000</v>
+        <v>864200</v>
       </c>
     </row>
     <row r="263">
@@ -12895,10 +12895,10 @@
         <v>8</v>
       </c>
       <c r="N287" t="n">
-        <v>4372.2107903559</v>
+        <v>4372.2107904123</v>
       </c>
       <c r="O287" t="n">
-        <v>34977.6863228472</v>
+        <v>34977.6863232984</v>
       </c>
       <c r="P287" t="n">
         <v>7500</v>
@@ -13066,22 +13066,22 @@
         <v>0</v>
       </c>
       <c r="L291" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M291" t="n">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="N291" t="n">
-        <v>1592.5667254408</v>
+        <v>1600.6713740458</v>
       </c>
       <c r="O291" t="n">
-        <v>431585.5825944568</v>
+        <v>417775.2286259538</v>
       </c>
       <c r="P291" t="n">
         <v>3900</v>
       </c>
       <c r="Q291" t="n">
-        <v>1056900</v>
+        <v>1017900</v>
       </c>
     </row>
     <row r="292">
@@ -13951,22 +13951,22 @@
         <v>0</v>
       </c>
       <c r="L311" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M311" t="n">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="N311" t="n">
         <v>1387.55</v>
       </c>
       <c r="O311" t="n">
-        <v>437078.25</v>
+        <v>430140.5</v>
       </c>
       <c r="P311" t="n">
         <v>2300</v>
       </c>
       <c r="Q311" t="n">
-        <v>724500</v>
+        <v>713000</v>
       </c>
     </row>
     <row r="312">
@@ -14281,22 +14281,22 @@
         <v>0</v>
       </c>
       <c r="L318" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M318" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N318" t="n">
         <v>16897</v>
       </c>
       <c r="O318" t="n">
-        <v>202764</v>
+        <v>185867</v>
       </c>
       <c r="P318" t="n">
         <v>27900</v>
       </c>
       <c r="Q318" t="n">
-        <v>334800</v>
+        <v>306900</v>
       </c>
     </row>
     <row r="319">
@@ -14562,22 +14562,22 @@
         <v>0</v>
       </c>
       <c r="L324" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M324" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="N324" t="n">
-        <v>3761.6</v>
+        <v>3775.3787545788</v>
       </c>
       <c r="O324" t="n">
-        <v>233219.2</v>
+        <v>222747.3465201492</v>
       </c>
       <c r="P324" t="n">
         <v>6900</v>
       </c>
       <c r="Q324" t="n">
-        <v>427800</v>
+        <v>407100</v>
       </c>
     </row>
     <row r="325">
@@ -15301,10 +15301,10 @@
         <v>96</v>
       </c>
       <c r="N340" t="n">
-        <v>1630.9236471425</v>
+        <v>1630.9236566809</v>
       </c>
       <c r="O340" t="n">
-        <v>156568.67012568</v>
+        <v>156568.6710413664</v>
       </c>
       <c r="P340" t="n">
         <v>2500</v>
@@ -15387,22 +15387,22 @@
         <v>0</v>
       </c>
       <c r="L342" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M342" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="N342" t="n">
-        <v>1690.5969977427</v>
+        <v>1690.5969630746</v>
       </c>
       <c r="O342" t="n">
-        <v>103126.4168623047</v>
+        <v>99745.2208214014</v>
       </c>
       <c r="P342" t="n">
         <v>2900</v>
       </c>
       <c r="Q342" t="n">
-        <v>176900</v>
+        <v>171100</v>
       </c>
     </row>
     <row r="343">
@@ -15433,22 +15433,22 @@
         <v>0</v>
       </c>
       <c r="L343" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M343" t="n">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="N343" t="n">
-        <v>1550.1936995315</v>
+        <v>1550.1937050719</v>
       </c>
       <c r="O343" t="n">
-        <v>629378.642009789</v>
+        <v>626278.2568490476</v>
       </c>
       <c r="P343" t="n">
         <v>2500</v>
       </c>
       <c r="Q343" t="n">
-        <v>1015000</v>
+        <v>1010000</v>
       </c>
     </row>
     <row r="344">
@@ -15485,10 +15485,10 @@
         <v>1</v>
       </c>
       <c r="N344" t="n">
-        <v>1579.3904266667</v>
+        <v>1579.3903753351</v>
       </c>
       <c r="O344" t="n">
-        <v>1579.3904266667</v>
+        <v>1579.3903753351</v>
       </c>
       <c r="P344" t="n">
         <v>2900</v>
@@ -15531,10 +15531,10 @@
         <v>228</v>
       </c>
       <c r="N345" t="n">
-        <v>2403.5121001364</v>
+        <v>2403.5121166602</v>
       </c>
       <c r="O345" t="n">
-        <v>548000.7588310993</v>
+        <v>548000.7625985255</v>
       </c>
       <c r="P345" t="n">
         <v>3500</v>
@@ -18820,10 +18820,10 @@
         <v>45</v>
       </c>
       <c r="N420" t="n">
-        <v>2680.739695084</v>
+        <v>2680.7396948941</v>
       </c>
       <c r="O420" t="n">
-        <v>120633.28627878</v>
+        <v>120633.2862702345</v>
       </c>
       <c r="P420" t="n">
         <v>4900</v>
@@ -20878,22 +20878,22 @@
         <v>0</v>
       </c>
       <c r="L468" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M468" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N468" t="n">
-        <v>1466.8807185629</v>
+        <v>1484.6610909091</v>
       </c>
       <c r="O468" t="n">
-        <v>41072.6601197612</v>
+        <v>38601.1883636366</v>
       </c>
       <c r="P468" t="n">
         <v>3400</v>
       </c>
       <c r="Q468" t="n">
-        <v>95200</v>
+        <v>88400</v>
       </c>
     </row>
     <row r="469">
@@ -21104,10 +21104,10 @@
         <v>56</v>
       </c>
       <c r="N473" t="n">
-        <v>1561.0009337861</v>
+        <v>1561.000952381</v>
       </c>
       <c r="O473" t="n">
-        <v>87416.0522920216</v>
+        <v>87416.05333333599</v>
       </c>
       <c r="P473" t="n">
         <v>2900</v>
@@ -23406,10 +23406,10 @@
         <v>33</v>
       </c>
       <c r="N525" t="n">
-        <v>3113.8900274725</v>
+        <v>3113.8900276243</v>
       </c>
       <c r="O525" t="n">
-        <v>102758.3709065925</v>
+        <v>102758.3709116019</v>
       </c>
       <c r="P525" t="n">
         <v>5000</v>
@@ -23774,10 +23774,10 @@
         <v>7</v>
       </c>
       <c r="N533" t="n">
-        <v>3610.6500258732</v>
+        <v>3610.6500261438</v>
       </c>
       <c r="O533" t="n">
-        <v>25274.5501811124</v>
+        <v>25274.5501830066</v>
       </c>
       <c r="P533" t="n">
         <v>5800</v>
@@ -28547,22 +28547,22 @@
         <v>0</v>
       </c>
       <c r="L636" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M636" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="N636" t="n">
-        <v>4907.822092257</v>
+        <v>4956.8186522463</v>
       </c>
       <c r="O636" t="n">
-        <v>186497.239505766</v>
+        <v>158618.1968718816</v>
       </c>
       <c r="P636" t="n">
         <v>8200</v>
       </c>
       <c r="Q636" t="n">
-        <v>311600</v>
+        <v>262400</v>
       </c>
     </row>
     <row r="637">
@@ -29876,22 +29876,22 @@
         <v>0</v>
       </c>
       <c r="L665" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M665" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N665" t="n">
         <v>5682</v>
       </c>
       <c r="O665" t="n">
-        <v>96594</v>
+        <v>90912</v>
       </c>
       <c r="P665" t="n">
         <v>9900</v>
       </c>
       <c r="Q665" t="n">
-        <v>168300</v>
+        <v>158400</v>
       </c>
     </row>
     <row r="666">
@@ -31625,22 +31625,22 @@
         <v>0</v>
       </c>
       <c r="L703" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M703" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N703" t="n">
         <v>2458</v>
       </c>
       <c r="O703" t="n">
-        <v>14748</v>
+        <v>4916</v>
       </c>
       <c r="P703" t="n">
         <v>3500</v>
       </c>
       <c r="Q703" t="n">
-        <v>21000</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="704">
@@ -32451,22 +32451,22 @@
         <v>0</v>
       </c>
       <c r="L721" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M721" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="N721" t="n">
-        <v>1803.0156237558</v>
+        <v>1803.0156368474</v>
       </c>
       <c r="O721" t="n">
-        <v>257831.2341970794</v>
+        <v>256028.2204323308</v>
       </c>
       <c r="P721" t="n">
         <v>2500</v>
       </c>
       <c r="Q721" t="n">
-        <v>357500</v>
+        <v>355000</v>
       </c>
     </row>
     <row r="722">
@@ -32497,22 +32497,22 @@
         <v>0</v>
       </c>
       <c r="L722" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M722" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="N722" t="n">
-        <v>3306.5946745562</v>
+        <v>3306.5946666667</v>
       </c>
       <c r="O722" t="n">
-        <v>367032.0088757382</v>
+        <v>363725.413333337</v>
       </c>
       <c r="P722" t="n">
         <v>4900</v>
       </c>
       <c r="Q722" t="n">
-        <v>543900</v>
+        <v>539000</v>
       </c>
     </row>
     <row r="723">
@@ -32635,22 +32635,22 @@
         <v>0</v>
       </c>
       <c r="L725" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M725" t="n">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="N725" t="n">
-        <v>2056.0829843644</v>
+        <v>2056.0829819789</v>
       </c>
       <c r="O725" t="n">
-        <v>532525.4929503796</v>
+        <v>530469.4093505562</v>
       </c>
       <c r="P725" t="n">
         <v>2900</v>
       </c>
       <c r="Q725" t="n">
-        <v>751100</v>
+        <v>748200</v>
       </c>
     </row>
     <row r="726">
@@ -32733,10 +32733,10 @@
         <v>155</v>
       </c>
       <c r="N727" t="n">
-        <v>1655.9308045213</v>
+        <v>1655.9307861426</v>
       </c>
       <c r="O727" t="n">
-        <v>256669.2747008015</v>
+        <v>256669.271852103</v>
       </c>
       <c r="P727" t="n">
         <v>2500</v>
@@ -33012,10 +33012,10 @@
         <v>68</v>
       </c>
       <c r="N733" t="n">
-        <v>1592.27881</v>
+        <v>1592.2788188188</v>
       </c>
       <c r="O733" t="n">
-        <v>108274.95908</v>
+        <v>108274.9596796784</v>
       </c>
       <c r="P733" t="n">
         <v>2500</v>
@@ -33229,22 +33229,22 @@
         <v>0</v>
       </c>
       <c r="L738" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M738" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="N738" t="n">
-        <v>1906.1829245283</v>
+        <v>1906.1827536232</v>
       </c>
       <c r="O738" t="n">
-        <v>81965.8657547169</v>
+        <v>72434.94463768159</v>
       </c>
       <c r="P738" t="n">
         <v>2900</v>
       </c>
       <c r="Q738" t="n">
-        <v>124700</v>
+        <v>110200</v>
       </c>
     </row>
     <row r="739">
@@ -33281,10 +33281,10 @@
         <v>49</v>
       </c>
       <c r="N739" t="n">
-        <v>3033.7169285714</v>
+        <v>3033.7165703971</v>
       </c>
       <c r="O739" t="n">
-        <v>148652.1294999986</v>
+        <v>148652.1119494579</v>
       </c>
       <c r="P739" t="n">
         <v>4500</v>
@@ -35128,22 +35128,22 @@
         <v>0</v>
       </c>
       <c r="L779" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M779" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N779" t="n">
-        <v>3629.36</v>
+        <v>3642.7032352941</v>
       </c>
       <c r="O779" t="n">
-        <v>32664.24</v>
+        <v>25498.9226470587</v>
       </c>
       <c r="P779" t="n">
         <v>3900</v>
       </c>
       <c r="Q779" t="n">
-        <v>35100</v>
+        <v>27300</v>
       </c>
     </row>
     <row r="780">
@@ -35864,22 +35864,22 @@
         <v>0</v>
       </c>
       <c r="L795" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M795" t="n">
-        <v>257</v>
+        <v>227</v>
       </c>
       <c r="N795" t="n">
         <v>628</v>
       </c>
       <c r="O795" t="n">
-        <v>161396</v>
+        <v>142556</v>
       </c>
       <c r="P795" t="n">
         <v>1400</v>
       </c>
       <c r="Q795" t="n">
-        <v>359800</v>
+        <v>317800</v>
       </c>
     </row>
     <row r="796">
@@ -36054,22 +36054,22 @@
         <v>0</v>
       </c>
       <c r="L799" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M799" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N799" t="n">
-        <v>6090.22</v>
+        <v>6160.2225287356</v>
       </c>
       <c r="O799" t="n">
-        <v>42631.54</v>
+        <v>30801.112643678</v>
       </c>
       <c r="P799" t="n">
         <v>8500</v>
       </c>
       <c r="Q799" t="n">
-        <v>59500</v>
+        <v>42500</v>
       </c>
     </row>
     <row r="800">
@@ -37581,10 +37581,10 @@
         <v>1241</v>
       </c>
       <c r="N832" t="n">
-        <v>517.2899423715</v>
+        <v>517.28997081144</v>
       </c>
       <c r="O832" t="n">
-        <v>641956.8184830316</v>
+        <v>641956.853776997</v>
       </c>
       <c r="P832" t="n">
         <v>900</v>
@@ -38090,22 +38090,22 @@
         <v>0</v>
       </c>
       <c r="L843" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M843" t="n">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="N843" t="n">
-        <v>3110.8413822526</v>
+        <v>3110.8413717354</v>
       </c>
       <c r="O843" t="n">
-        <v>839927.173208202</v>
+        <v>824372.9635098811</v>
       </c>
       <c r="P843" t="n">
         <v>4500</v>
       </c>
       <c r="Q843" t="n">
-        <v>1215000</v>
+        <v>1192500</v>
       </c>
     </row>
     <row r="844">
@@ -38502,22 +38502,22 @@
         <v>0</v>
       </c>
       <c r="L852" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M852" t="n">
-        <v>302</v>
+        <v>278</v>
       </c>
       <c r="N852" t="n">
-        <v>703.79516599434</v>
+        <v>703.79516401441</v>
       </c>
       <c r="O852" t="n">
-        <v>212546.1401302907</v>
+        <v>195655.055596006</v>
       </c>
       <c r="P852" t="n">
         <v>900</v>
       </c>
       <c r="Q852" t="n">
-        <v>271800</v>
+        <v>250200</v>
       </c>
     </row>
     <row r="853">
@@ -38876,22 +38876,22 @@
         <v>0</v>
       </c>
       <c r="L860" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M860" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N860" t="n">
-        <v>2501.3849767442</v>
+        <v>2501.384953271</v>
       </c>
       <c r="O860" t="n">
-        <v>30016.6197209304</v>
+        <v>27515.234485981</v>
       </c>
       <c r="P860" t="n">
         <v>4100</v>
       </c>
       <c r="Q860" t="n">
-        <v>49200</v>
+        <v>45100</v>
       </c>
     </row>
     <row r="861">
@@ -40340,22 +40340,22 @@
         <v>0</v>
       </c>
       <c r="L891" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M891" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N891" t="n">
-        <v>2098.4050144928</v>
+        <v>2110.6406122449</v>
       </c>
       <c r="O891" t="n">
-        <v>14688.8351014496</v>
+        <v>10553.2030612245</v>
       </c>
       <c r="P891" t="n">
         <v>9500</v>
       </c>
       <c r="Q891" t="n">
-        <v>66500</v>
+        <v>47500</v>
       </c>
     </row>
     <row r="892">
@@ -42124,22 +42124,22 @@
         <v>0</v>
       </c>
       <c r="L928" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M928" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N928" t="n">
-        <v>2992.5689285714</v>
+        <v>3065.5584146341</v>
       </c>
       <c r="O928" t="n">
-        <v>50873.67178571381</v>
+        <v>45983.3762195115</v>
       </c>
       <c r="P928" t="n">
         <v>6000</v>
       </c>
       <c r="Q928" t="n">
-        <v>102000</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="929">
@@ -42170,22 +42170,22 @@
         <v>0</v>
       </c>
       <c r="L929" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M929" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N929" t="n">
-        <v>875.69016806723</v>
+        <v>883.11127118644</v>
       </c>
       <c r="O929" t="n">
-        <v>8756.901680672301</v>
+        <v>7064.89016949152</v>
       </c>
       <c r="P929" t="n">
         <v>4500</v>
       </c>
       <c r="Q929" t="n">
-        <v>45000</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="930">
@@ -46332,22 +46332,22 @@
         <v>0</v>
       </c>
       <c r="L1016" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M1016" t="n">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="N1016" t="n">
-        <v>665.32359209922</v>
+        <v>665.32360534809</v>
       </c>
       <c r="O1016" t="n">
-        <v>149032.4846302253</v>
+        <v>143709.8987551875</v>
       </c>
       <c r="P1016" t="n">
         <v>2900</v>
       </c>
       <c r="Q1016" t="n">
-        <v>649600</v>
+        <v>626400</v>
       </c>
     </row>
     <row r="1017">
@@ -48761,10 +48761,10 @@
         <v>7</v>
       </c>
       <c r="N1069" t="n">
-        <v>2367.1669565217</v>
+        <v>2367.1668181818</v>
       </c>
       <c r="O1069" t="n">
-        <v>16570.1686956519</v>
+        <v>16570.1677272726</v>
       </c>
       <c r="P1069" t="n">
         <v>2900</v>
@@ -51150,22 +51150,22 @@
         <v>0</v>
       </c>
       <c r="L1121" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M1121" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N1121" t="n">
-        <v>5280</v>
+        <v>5305.2631578947</v>
       </c>
       <c r="O1121" t="n">
-        <v>110880</v>
+        <v>100799.9999999993</v>
       </c>
       <c r="P1121" t="n">
         <v>6900</v>
       </c>
       <c r="Q1121" t="n">
-        <v>144900</v>
+        <v>131100</v>
       </c>
     </row>
     <row r="1122">
@@ -51196,22 +51196,22 @@
         <v>0</v>
       </c>
       <c r="L1122" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1122" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="N1122" t="n">
-        <v>5280</v>
+        <v>5301.8181818182</v>
       </c>
       <c r="O1122" t="n">
-        <v>691680</v>
+        <v>683934.5454545479</v>
       </c>
       <c r="P1122" t="n">
         <v>6900</v>
       </c>
       <c r="Q1122" t="n">
-        <v>903900</v>
+        <v>890100</v>
       </c>
     </row>
     <row r="1123">
@@ -51380,22 +51380,22 @@
         <v>0</v>
       </c>
       <c r="L1126" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1126" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="N1126" t="n">
         <v>4400</v>
       </c>
       <c r="O1126" t="n">
-        <v>730400</v>
+        <v>721600</v>
       </c>
       <c r="P1126" t="n">
         <v>5900</v>
       </c>
       <c r="Q1126" t="n">
-        <v>979400</v>
+        <v>967600</v>
       </c>
     </row>
     <row r="1127">
@@ -51426,22 +51426,22 @@
         <v>0</v>
       </c>
       <c r="L1127" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M1127" t="n">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="N1127" t="n">
         <v>3520</v>
       </c>
       <c r="O1127" t="n">
-        <v>425920</v>
+        <v>404800</v>
       </c>
       <c r="P1127" t="n">
         <v>4500</v>
       </c>
       <c r="Q1127" t="n">
-        <v>544500</v>
+        <v>517500</v>
       </c>
     </row>
     <row r="1128">
@@ -51610,22 +51610,22 @@
         <v>0</v>
       </c>
       <c r="L1131" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M1131" t="n">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="N1131" t="n">
         <v>2288</v>
       </c>
       <c r="O1131" t="n">
-        <v>1226368</v>
+        <v>1214928</v>
       </c>
       <c r="P1131" t="n">
         <v>2900</v>
       </c>
       <c r="Q1131" t="n">
-        <v>1554400</v>
+        <v>1539900</v>
       </c>
     </row>
     <row r="1132">
@@ -53746,22 +53746,22 @@
         <v>0</v>
       </c>
       <c r="L1177" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M1177" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="N1177" t="n">
-        <v>1319.360887574</v>
+        <v>1327.2142261905</v>
       </c>
       <c r="O1177" t="n">
-        <v>29025.939526628</v>
+        <v>26544.28452381</v>
       </c>
       <c r="P1177" t="n">
         <v>3500</v>
       </c>
       <c r="Q1177" t="n">
-        <v>77000</v>
+        <v>70000</v>
       </c>
     </row>
     <row r="1178">
@@ -54649,10 +54649,10 @@
         <v>52</v>
       </c>
       <c r="N1196" t="n">
-        <v>2539.5715559441</v>
+        <v>2539.5715696649</v>
       </c>
       <c r="O1196" t="n">
-        <v>132057.7209090932</v>
+        <v>132057.7216225748</v>
       </c>
       <c r="P1196" t="n">
         <v>3500</v>
@@ -54695,10 +54695,10 @@
         <v>48</v>
       </c>
       <c r="N1197" t="n">
-        <v>4171.6686912752</v>
+        <v>4171.6686824324</v>
       </c>
       <c r="O1197" t="n">
-        <v>200240.0971812096</v>
+        <v>200240.0967567552</v>
       </c>
       <c r="P1197" t="n">
         <v>5500</v>
@@ -55970,22 +55970,22 @@
         <v>0</v>
       </c>
       <c r="L1225" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1225" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="N1225" t="n">
         <v>4550</v>
       </c>
       <c r="O1225" t="n">
-        <v>318500</v>
+        <v>309400</v>
       </c>
       <c r="P1225" t="n">
         <v>5500</v>
       </c>
       <c r="Q1225" t="n">
-        <v>385000</v>
+        <v>374000</v>
       </c>
     </row>
     <row r="1226">

--- a/bodegas/LJ-101.xlsx
+++ b/bodegas/LJ-101.xlsx
@@ -20843,10 +20843,10 @@
         <v>26</v>
       </c>
       <c r="N467" t="n">
-        <v>1484.6610909091</v>
+        <v>1466.8807272727</v>
       </c>
       <c r="O467" t="n">
-        <v>38601.1883636366</v>
+        <v>38138.8989090902</v>
       </c>
       <c r="P467" t="n">
         <v>3400</v>
@@ -28466,10 +28466,10 @@
         <v>32</v>
       </c>
       <c r="N634" t="n">
-        <v>4956.8186522463</v>
+        <v>4907.8221131448</v>
       </c>
       <c r="O634" t="n">
-        <v>158618.1968718816</v>
+        <v>157050.3076206336</v>
       </c>
       <c r="P634" t="n">
         <v>8200</v>
@@ -34955,10 +34955,10 @@
         <v>7</v>
       </c>
       <c r="N775" t="n">
-        <v>3642.7032352941</v>
+        <v>3629.36</v>
       </c>
       <c r="O775" t="n">
-        <v>25498.9226470587</v>
+        <v>25405.52</v>
       </c>
       <c r="P775" t="n">
         <v>3900</v>
@@ -35881,10 +35881,10 @@
         <v>5</v>
       </c>
       <c r="N795" t="n">
-        <v>6160.2225287356</v>
+        <v>6090.22</v>
       </c>
       <c r="O795" t="n">
-        <v>30801.112643678</v>
+        <v>30451.1</v>
       </c>
       <c r="P795" t="n">
         <v>8500</v>
@@ -41997,10 +41997,10 @@
         <v>8</v>
       </c>
       <c r="N925" t="n">
-        <v>883.11127118644</v>
+        <v>875.69016949153</v>
       </c>
       <c r="O925" t="n">
-        <v>7064.89016949152</v>
+        <v>7005.52135593224</v>
       </c>
       <c r="P925" t="n">
         <v>4500</v>
@@ -43535,10 +43535,10 @@
         <v>10</v>
       </c>
       <c r="N957" t="n">
-        <v>33063.39</v>
+        <v>22042.26</v>
       </c>
       <c r="O957" t="n">
-        <v>330633.9</v>
+        <v>220422.6</v>
       </c>
       <c r="P957" t="n">
         <v>56000</v>
@@ -53573,10 +53573,10 @@
         <v>20</v>
       </c>
       <c r="N1173" t="n">
-        <v>1327.2142261905</v>
+        <v>1319.3608928571</v>
       </c>
       <c r="O1173" t="n">
-        <v>26544.28452381</v>
+        <v>26387.217857142</v>
       </c>
       <c r="P1173" t="n">
         <v>3500</v>

--- a/bodegas/LJ-101.xlsx
+++ b/bodegas/LJ-101.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-30</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-31</t>
         </is>
       </c>
     </row>
@@ -4923,22 +4923,22 @@
         <v>0</v>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M108" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N108" t="n">
         <v>20961.76</v>
       </c>
       <c r="O108" t="n">
-        <v>230579.36</v>
+        <v>209617.6</v>
       </c>
       <c r="P108" t="n">
         <v>38300</v>
       </c>
       <c r="Q108" t="n">
-        <v>421300</v>
+        <v>383000</v>
       </c>
     </row>
     <row r="109">
@@ -4962,22 +4962,22 @@
         <v>0</v>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M109" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N109" t="n">
         <v>26280.41</v>
       </c>
       <c r="O109" t="n">
-        <v>551888.61</v>
+        <v>525608.2</v>
       </c>
       <c r="P109" t="n">
         <v>46500</v>
       </c>
       <c r="Q109" t="n">
-        <v>976500</v>
+        <v>930000</v>
       </c>
     </row>
     <row r="110">
@@ -22511,22 +22511,22 @@
         <v>0</v>
       </c>
       <c r="L505" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M505" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N505" t="n">
         <v>20907</v>
       </c>
       <c r="O505" t="n">
-        <v>20907</v>
+        <v>0</v>
       </c>
       <c r="P505" t="n">
         <v>35600</v>
       </c>
       <c r="Q505" t="n">
-        <v>35600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="506">
@@ -51063,22 +51063,22 @@
         <v>0</v>
       </c>
       <c r="L1119" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M1119" t="n">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="N1119" t="n">
         <v>1584</v>
       </c>
       <c r="O1119" t="n">
-        <v>370656</v>
+        <v>351648</v>
       </c>
       <c r="P1119" t="n">
         <v>2000</v>
       </c>
       <c r="Q1119" t="n">
-        <v>468000</v>
+        <v>444000</v>
       </c>
     </row>
     <row r="1120">
@@ -51109,22 +51109,22 @@
         <v>0</v>
       </c>
       <c r="L1120" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M1120" t="n">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="N1120" t="n">
         <v>3872</v>
       </c>
       <c r="O1120" t="n">
-        <v>584672</v>
+        <v>538208</v>
       </c>
       <c r="P1120" t="n">
         <v>4900</v>
       </c>
       <c r="Q1120" t="n">
-        <v>739900</v>
+        <v>681100</v>
       </c>
     </row>
     <row r="1121">
@@ -51155,22 +51155,22 @@
         <v>0</v>
       </c>
       <c r="L1121" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M1121" t="n">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="N1121" t="n">
         <v>6160</v>
       </c>
       <c r="O1121" t="n">
-        <v>388080</v>
+        <v>314160</v>
       </c>
       <c r="P1121" t="n">
         <v>7900</v>
       </c>
       <c r="Q1121" t="n">
-        <v>497700</v>
+        <v>402900</v>
       </c>
     </row>
     <row r="1122">
@@ -51201,22 +51201,22 @@
         <v>0</v>
       </c>
       <c r="L1122" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M1122" t="n">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="N1122" t="n">
         <v>4400</v>
       </c>
       <c r="O1122" t="n">
-        <v>721600</v>
+        <v>668800</v>
       </c>
       <c r="P1122" t="n">
         <v>5900</v>
       </c>
       <c r="Q1122" t="n">
-        <v>967600</v>
+        <v>896800</v>
       </c>
     </row>
     <row r="1123">

--- a/bodegas/LJ-101.xlsx
+++ b/bodegas/LJ-101.xlsx
@@ -3747,10 +3747,10 @@
         <v>9</v>
       </c>
       <c r="N80" t="n">
-        <v>15711.965869565</v>
+        <v>15711.965851528</v>
       </c>
       <c r="O80" t="n">
-        <v>141407.692826085</v>
+        <v>141407.692663752</v>
       </c>
       <c r="P80" t="n">
         <v>28500</v>
@@ -9544,22 +9544,22 @@
         <v>0</v>
       </c>
       <c r="L213" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M213" t="n">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="N213" t="n">
-        <v>3158.8608271635</v>
+        <v>3158.8608272041</v>
       </c>
       <c r="O213" t="n">
-        <v>1194049.392667803</v>
+        <v>1190890.531855946</v>
       </c>
       <c r="P213" t="n">
         <v>5600</v>
       </c>
       <c r="Q213" t="n">
-        <v>2116800</v>
+        <v>2111200</v>
       </c>
     </row>
     <row r="214">
@@ -11329,10 +11329,10 @@
         <v>9</v>
       </c>
       <c r="N252" t="n">
-        <v>3594.2539622642</v>
+        <v>3594.2539546599</v>
       </c>
       <c r="O252" t="n">
-        <v>32348.2856603778</v>
+        <v>32348.2855919391</v>
       </c>
       <c r="P252" t="n">
         <v>6500</v>
@@ -11542,10 +11542,10 @@
         <v>134</v>
       </c>
       <c r="N257" t="n">
-        <v>3240.850037594</v>
+        <v>3240.8500375235</v>
       </c>
       <c r="O257" t="n">
-        <v>434273.9050375959</v>
+        <v>434273.905028149</v>
       </c>
       <c r="P257" t="n">
         <v>5200</v>
@@ -12119,25 +12119,25 @@
         <v>29</v>
       </c>
       <c r="K270" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="L270" t="n">
         <v>0</v>
       </c>
       <c r="M270" t="n">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="N270" t="n">
         <v>2665.4</v>
       </c>
       <c r="O270" t="n">
-        <v>77296.60000000001</v>
+        <v>138600.8</v>
       </c>
       <c r="P270" t="n">
         <v>20900</v>
       </c>
       <c r="Q270" t="n">
-        <v>606100</v>
+        <v>1086800</v>
       </c>
     </row>
     <row r="271">
@@ -15786,10 +15786,10 @@
         <v>405</v>
       </c>
       <c r="N351" t="n">
-        <v>893.67886945501</v>
+        <v>893.67886888156</v>
       </c>
       <c r="O351" t="n">
-        <v>361939.9421292791</v>
+        <v>361939.9418970318</v>
       </c>
       <c r="P351" t="n">
         <v>1200</v>
@@ -32243,10 +32243,10 @@
         <v>148</v>
       </c>
       <c r="N716" t="n">
-        <v>1907.3929677419</v>
+        <v>1907.3929220779</v>
       </c>
       <c r="O716" t="n">
-        <v>282294.1592258012</v>
+        <v>282294.1524675292</v>
       </c>
       <c r="P716" t="n">
         <v>2500</v>
@@ -32381,10 +32381,10 @@
         <v>142</v>
       </c>
       <c r="N719" t="n">
-        <v>1803.0157013118</v>
+        <v>1803.0157128413</v>
       </c>
       <c r="O719" t="n">
-        <v>256028.2295862756</v>
+        <v>256028.2312234646</v>
       </c>
       <c r="P719" t="n">
         <v>2500</v>
@@ -32519,10 +32519,10 @@
         <v>78</v>
       </c>
       <c r="N722" t="n">
-        <v>2108.7924270463</v>
+        <v>2108.7924803431</v>
       </c>
       <c r="O722" t="n">
-        <v>164485.8093096114</v>
+        <v>164485.8134667618</v>
       </c>
       <c r="P722" t="n">
         <v>2900</v>
@@ -32565,10 +32565,10 @@
         <v>255</v>
       </c>
       <c r="N723" t="n">
-        <v>2056.0829120879</v>
+        <v>2056.0828974535</v>
       </c>
       <c r="O723" t="n">
-        <v>524301.1425824144</v>
+        <v>524301.1388506426</v>
       </c>
       <c r="P723" t="n">
         <v>2900</v>
@@ -32936,10 +32936,10 @@
         <v>54</v>
       </c>
       <c r="N731" t="n">
-        <v>1592.2799548023</v>
+        <v>1592.2799660633</v>
       </c>
       <c r="O731" t="n">
-        <v>85983.11755932419</v>
+        <v>85983.1181674182</v>
       </c>
       <c r="P731" t="n">
         <v>2500</v>
@@ -38432,10 +38432,10 @@
         <v>1325</v>
       </c>
       <c r="N850" t="n">
-        <v>703.79511760843</v>
+        <v>703.79511689575</v>
       </c>
       <c r="O850" t="n">
-        <v>932528.5308311698</v>
+        <v>932528.5298868687</v>
       </c>
       <c r="P850" t="n">
         <v>900</v>
@@ -46734,22 +46734,22 @@
         <v>0</v>
       </c>
       <c r="L1024" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1024" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N1024" t="n">
         <v>1262.07</v>
       </c>
       <c r="O1024" t="n">
-        <v>159020.82</v>
+        <v>157758.75</v>
       </c>
       <c r="P1024" t="n">
         <v>8900</v>
       </c>
       <c r="Q1024" t="n">
-        <v>1121400</v>
+        <v>1112500</v>
       </c>
     </row>
     <row r="1025">
@@ -48355,10 +48355,10 @@
         <v>7</v>
       </c>
       <c r="N1060" t="n">
-        <v>22951.704792746</v>
+        <v>22951.704785992</v>
       </c>
       <c r="O1060" t="n">
-        <v>160661.933549222</v>
+        <v>160661.933501944</v>
       </c>
       <c r="P1060" t="n">
         <v>37900</v>

--- a/bodegas/LJ-101.xlsx
+++ b/bodegas/LJ-101.xlsx
@@ -3660,22 +3660,22 @@
         <v>0</v>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M78" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N78" t="n">
-        <v>16486.408661417</v>
+        <v>16486.408571429</v>
       </c>
       <c r="O78" t="n">
-        <v>181350.495275587</v>
+        <v>164864.08571429</v>
       </c>
       <c r="P78" t="n">
         <v>30500</v>
       </c>
       <c r="Q78" t="n">
-        <v>335500</v>
+        <v>305000</v>
       </c>
     </row>
     <row r="79">
@@ -3741,22 +3741,22 @@
         <v>0</v>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M80" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N80" t="n">
-        <v>15711.965814978</v>
+        <v>15711.96579646</v>
       </c>
       <c r="O80" t="n">
-        <v>109983.760704846</v>
+        <v>94271.79477876</v>
       </c>
       <c r="P80" t="n">
         <v>28500</v>
       </c>
       <c r="Q80" t="n">
-        <v>199500</v>
+        <v>171000</v>
       </c>
     </row>
     <row r="81">
@@ -3788,22 +3788,22 @@
         <v>0</v>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M81" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N81" t="n">
-        <v>9392.075000000001</v>
+        <v>9392.0750746269</v>
       </c>
       <c r="O81" t="n">
-        <v>112704.9</v>
+        <v>103312.8258208959</v>
       </c>
       <c r="P81" t="n">
         <v>18500</v>
       </c>
       <c r="Q81" t="n">
-        <v>222000</v>
+        <v>203500</v>
       </c>
     </row>
     <row r="82">
@@ -9094,10 +9094,10 @@
         <v>27</v>
       </c>
       <c r="N203" t="n">
-        <v>2582.2555555556</v>
+        <v>2582.2555535714</v>
       </c>
       <c r="O203" t="n">
-        <v>69720.9000000012</v>
+        <v>69720.8999464278</v>
       </c>
       <c r="P203" t="n">
         <v>4500</v>
@@ -32706,10 +32706,10 @@
         <v>141</v>
       </c>
       <c r="N726" t="n">
-        <v>1655.9307118872</v>
+        <v>1655.9306993948</v>
       </c>
       <c r="O726" t="n">
-        <v>233486.2303760952</v>
+        <v>233486.2286146668</v>
       </c>
       <c r="P726" t="n">
         <v>2500</v>
@@ -32985,10 +32985,10 @@
         <v>48</v>
       </c>
       <c r="N732" t="n">
-        <v>1592.2805889423</v>
+        <v>1592.2806787879</v>
       </c>
       <c r="O732" t="n">
-        <v>76429.4682692304</v>
+        <v>76429.47258181919</v>
       </c>
       <c r="P732" t="n">
         <v>2500</v>
@@ -33156,22 +33156,22 @@
         <v>0</v>
       </c>
       <c r="L736" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M736" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="N736" t="n">
-        <v>2311.9153823529</v>
+        <v>2311.9150892857</v>
       </c>
       <c r="O736" t="n">
-        <v>60109.7999411754</v>
+        <v>50862.1319642854</v>
       </c>
       <c r="P736" t="n">
         <v>3500</v>
       </c>
       <c r="Q736" t="n">
-        <v>91000</v>
+        <v>77000</v>
       </c>
     </row>
     <row r="737">
@@ -33202,22 +33202,22 @@
         <v>0</v>
       </c>
       <c r="L737" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M737" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="N737" t="n">
-        <v>1906.1813793103</v>
+        <v>1906.1812280702</v>
       </c>
       <c r="O737" t="n">
-        <v>43842.1717241369</v>
+        <v>38123.624561404</v>
       </c>
       <c r="P737" t="n">
         <v>2900</v>
       </c>
       <c r="Q737" t="n">
-        <v>66700</v>
+        <v>58000</v>
       </c>
     </row>
     <row r="738">
@@ -33438,10 +33438,10 @@
         <v>190</v>
       </c>
       <c r="N742" t="n">
-        <v>1259.2746360505</v>
+        <v>1259.2746413793</v>
       </c>
       <c r="O742" t="n">
-        <v>239262.180849595</v>
+        <v>239262.181862067</v>
       </c>
       <c r="P742" t="n">
         <v>1900</v>
@@ -38069,10 +38069,10 @@
         <v>242</v>
       </c>
       <c r="N842" t="n">
-        <v>3110.8404252438</v>
+        <v>3110.840414859</v>
       </c>
       <c r="O842" t="n">
-        <v>752823.3829089996</v>
+        <v>752823.380395878</v>
       </c>
       <c r="P842" t="n">
         <v>4500</v>
@@ -39544,10 +39544,10 @@
         <v>36</v>
       </c>
       <c r="N874" t="n">
-        <v>1595.5116515014</v>
+        <v>1595.5116012774</v>
       </c>
       <c r="O874" t="n">
-        <v>57438.4194540504</v>
+        <v>57438.4176459864</v>
       </c>
       <c r="P874" t="n">
         <v>2500</v>

--- a/bodegas/LJ-101.xlsx
+++ b/bodegas/LJ-101.xlsx
@@ -9094,10 +9094,10 @@
         <v>87</v>
       </c>
       <c r="N203" t="n">
-        <v>2582.255546613</v>
+        <v>2582.2555436242</v>
       </c>
       <c r="O203" t="n">
-        <v>224656.232555331</v>
+        <v>224656.2322953054</v>
       </c>
       <c r="P203" t="n">
         <v>4500</v>
@@ -11810,25 +11810,25 @@
         <v>252</v>
       </c>
       <c r="K263" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L263" t="n">
         <v>0</v>
       </c>
       <c r="M263" t="n">
-        <v>252</v>
+        <v>348</v>
       </c>
       <c r="N263" t="n">
         <v>2090.85</v>
       </c>
       <c r="O263" t="n">
-        <v>526894.2</v>
+        <v>727615.7999999999</v>
       </c>
       <c r="P263" t="n">
         <v>2900</v>
       </c>
       <c r="Q263" t="n">
-        <v>730800</v>
+        <v>1009200</v>
       </c>
     </row>
     <row r="264">
@@ -14852,10 +14852,10 @@
         <v>4</v>
       </c>
       <c r="N330" t="n">
-        <v>8296.6427272727</v>
+        <v>8296.6429032258</v>
       </c>
       <c r="O330" t="n">
-        <v>33186.5709090908</v>
+        <v>33186.5716129032</v>
       </c>
       <c r="P330" t="n">
         <v>15900</v>
@@ -15404,10 +15404,10 @@
         <v>337</v>
       </c>
       <c r="N342" t="n">
-        <v>1550.1938919769</v>
+        <v>1550.1938936103</v>
       </c>
       <c r="O342" t="n">
-        <v>522415.3415962153</v>
+        <v>522415.3421466711</v>
       </c>
       <c r="P342" t="n">
         <v>2500</v>
@@ -21022,22 +21022,22 @@
         <v>0</v>
       </c>
       <c r="L471" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M471" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N471" t="n">
-        <v>8332.779621212099</v>
+        <v>8332.779620253201</v>
       </c>
       <c r="O471" t="n">
-        <v>66662.23696969679</v>
+        <v>58329.4573417724</v>
       </c>
       <c r="P471" t="n">
         <v>14900</v>
       </c>
       <c r="Q471" t="n">
-        <v>119200</v>
+        <v>104300</v>
       </c>
     </row>
     <row r="472">
@@ -30410,10 +30410,10 @@
         <v>35</v>
       </c>
       <c r="N676" t="n">
-        <v>17075.989522491</v>
+        <v>17075.989522161</v>
       </c>
       <c r="O676" t="n">
-        <v>597659.633287185</v>
+        <v>597659.633275635</v>
       </c>
       <c r="P676" t="n">
         <v>27500</v>
@@ -33031,10 +33031,10 @@
         <v>46</v>
       </c>
       <c r="N733" t="n">
-        <v>1592.2810401003</v>
+        <v>1592.2811378003</v>
       </c>
       <c r="O733" t="n">
-        <v>73244.92784461381</v>
+        <v>73244.9323388138</v>
       </c>
       <c r="P733" t="n">
         <v>2500</v>
@@ -37600,10 +37600,10 @@
         <v>1075</v>
       </c>
       <c r="N832" t="n">
-        <v>517.29096206919</v>
+        <v>517.29097263266</v>
       </c>
       <c r="O832" t="n">
-        <v>556087.7842243792</v>
+        <v>556087.7955801095</v>
       </c>
       <c r="P832" t="n">
         <v>900</v>

--- a/bodegas/LJ-101.xlsx
+++ b/bodegas/LJ-101.xlsx
@@ -9778,10 +9778,10 @@
         <v>95</v>
       </c>
       <c r="N218" t="n">
-        <v>3230.0670575693</v>
+        <v>3230.0670386266</v>
       </c>
       <c r="O218" t="n">
-        <v>306856.3704690835</v>
+        <v>306856.368669527</v>
       </c>
       <c r="P218" t="n">
         <v>6200</v>
@@ -10195,10 +10195,10 @@
         <v>45</v>
       </c>
       <c r="N227" t="n">
-        <v>5002</v>
+        <v>5013.3940774487</v>
       </c>
       <c r="O227" t="n">
-        <v>225090</v>
+        <v>225602.7334851915</v>
       </c>
       <c r="P227" t="n">
         <v>8400</v>
@@ -10553,10 +10553,10 @@
         <v>10</v>
       </c>
       <c r="N235" t="n">
-        <v>4890.9300493218</v>
+        <v>4890.9300493827</v>
       </c>
       <c r="O235" t="n">
-        <v>48909.300493218</v>
+        <v>48909.300493827</v>
       </c>
       <c r="P235" t="n">
         <v>8200</v>
@@ -11233,22 +11233,22 @@
         <v>0</v>
       </c>
       <c r="L250" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M250" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N250" t="n">
         <v>10716.34</v>
       </c>
       <c r="O250" t="n">
-        <v>64298.04</v>
+        <v>32149.02</v>
       </c>
       <c r="P250" t="n">
         <v>39000</v>
       </c>
       <c r="Q250" t="n">
-        <v>234000</v>
+        <v>117000</v>
       </c>
     </row>
     <row r="251">
@@ -11819,10 +11819,10 @@
         <v>348</v>
       </c>
       <c r="N263" t="n">
-        <v>2090.85</v>
+        <v>2092.643951094</v>
       </c>
       <c r="O263" t="n">
-        <v>727615.7999999999</v>
+        <v>728240.0949807119</v>
       </c>
       <c r="P263" t="n">
         <v>2900</v>
@@ -12942,10 +12942,10 @@
         <v>4</v>
       </c>
       <c r="N288" t="n">
-        <v>4372.2107917679</v>
+        <v>4372.2107918811</v>
       </c>
       <c r="O288" t="n">
-        <v>17488.8431670716</v>
+        <v>17488.8431675244</v>
       </c>
       <c r="P288" t="n">
         <v>7500</v>
@@ -13078,10 +13078,10 @@
         <v>231</v>
       </c>
       <c r="N291" t="n">
-        <v>1592.5662209302</v>
+        <v>1617.3578206079</v>
       </c>
       <c r="O291" t="n">
-        <v>367882.7970348762</v>
+        <v>373609.6565604249</v>
       </c>
       <c r="P291" t="n">
         <v>3900</v>
@@ -15266,10 +15266,10 @@
         <v>79</v>
       </c>
       <c r="N339" t="n">
-        <v>1630.9238760081</v>
+        <v>1630.9238867829</v>
       </c>
       <c r="O339" t="n">
-        <v>128842.9862046399</v>
+        <v>128842.9870558491</v>
       </c>
       <c r="P339" t="n">
         <v>2500</v>
@@ -15404,10 +15404,10 @@
         <v>337</v>
       </c>
       <c r="N342" t="n">
-        <v>1550.1939063158</v>
+        <v>1550.1939133186</v>
       </c>
       <c r="O342" t="n">
-        <v>522415.3464284246</v>
+        <v>522415.3487883682</v>
       </c>
       <c r="P342" t="n">
         <v>2500</v>
@@ -15496,10 +15496,10 @@
         <v>192</v>
       </c>
       <c r="N344" t="n">
-        <v>2403.5134379057</v>
+        <v>2403.513461205</v>
       </c>
       <c r="O344" t="n">
-        <v>461474.5800778944</v>
+        <v>461474.58455136</v>
       </c>
       <c r="P344" t="n">
         <v>3500</v>
@@ -15542,10 +15542,10 @@
         <v>5</v>
       </c>
       <c r="N345" t="n">
-        <v>2521.5033757962</v>
+        <v>2521.5026451613</v>
       </c>
       <c r="O345" t="n">
-        <v>12607.516878981</v>
+        <v>12607.5132258065</v>
       </c>
       <c r="P345" t="n">
         <v>3900</v>
@@ -18539,10 +18539,10 @@
         <v>73</v>
       </c>
       <c r="N413" t="n">
-        <v>2517.22</v>
+        <v>2541.6788178138</v>
       </c>
       <c r="O413" t="n">
-        <v>183757.06</v>
+        <v>185542.5537004074</v>
       </c>
       <c r="P413" t="n">
         <v>4200</v>
@@ -23744,10 +23744,10 @@
         <v>4</v>
       </c>
       <c r="N532" t="n">
-        <v>5218.1705692109</v>
+        <v>5218.1705706874</v>
       </c>
       <c r="O532" t="n">
-        <v>20872.6822768436</v>
+        <v>20872.6822827496</v>
       </c>
       <c r="P532" t="n">
         <v>8500</v>
@@ -24446,10 +24446,10 @@
         <v>84</v>
       </c>
       <c r="N547" t="n">
-        <v>1664.3525567322</v>
+        <v>1664.3525037936</v>
       </c>
       <c r="O547" t="n">
-        <v>139805.6147655048</v>
+        <v>139805.6103186624</v>
       </c>
       <c r="P547" t="n">
         <v>2900</v>
@@ -32110,10 +32110,10 @@
         <v>8</v>
       </c>
       <c r="N713" t="n">
-        <v>1516.0387891009</v>
+        <v>1517.8304441599</v>
       </c>
       <c r="O713" t="n">
-        <v>12128.3103128072</v>
+        <v>12142.6435532792</v>
       </c>
       <c r="P713" t="n">
         <v>2300</v>
@@ -32430,10 +32430,10 @@
         <v>122</v>
       </c>
       <c r="N720" t="n">
-        <v>1803.0158874609</v>
+        <v>1803.0158936022</v>
       </c>
       <c r="O720" t="n">
-        <v>219967.9382702298</v>
+        <v>219967.9390194684</v>
       </c>
       <c r="P720" t="n">
         <v>2500</v>
@@ -32985,10 +32985,10 @@
         <v>45</v>
       </c>
       <c r="N732" t="n">
-        <v>1592.2815314136</v>
+        <v>1592.2816534392</v>
       </c>
       <c r="O732" t="n">
-        <v>71652.668913612</v>
+        <v>71652.67440476399</v>
       </c>
       <c r="P732" t="n">
         <v>2500</v>
@@ -36313,22 +36313,22 @@
         <v>0</v>
       </c>
       <c r="L804" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M804" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N804" t="n">
         <v>1621.2</v>
       </c>
       <c r="O804" t="n">
-        <v>100514.4</v>
+        <v>98893.2</v>
       </c>
       <c r="P804" t="n">
         <v>2500</v>
       </c>
       <c r="Q804" t="n">
-        <v>155000</v>
+        <v>152500</v>
       </c>
     </row>
     <row r="805">
@@ -37554,10 +37554,10 @@
         <v>1024</v>
       </c>
       <c r="N831" t="n">
-        <v>517.29128286432</v>
+        <v>518.11303680169</v>
       </c>
       <c r="O831" t="n">
-        <v>529706.2736530637</v>
+        <v>530547.7496849305</v>
       </c>
       <c r="P831" t="n">
         <v>900</v>
@@ -38481,10 +38481,10 @@
         <v>1223</v>
       </c>
       <c r="N851" t="n">
-        <v>703.79502188713</v>
+        <v>703.79501848956</v>
       </c>
       <c r="O851" t="n">
-        <v>860741.31176796</v>
+        <v>860741.3076127318</v>
       </c>
       <c r="P851" t="n">
         <v>900</v>
@@ -51451,10 +51451,10 @@
         <v>79</v>
       </c>
       <c r="N1127" t="n">
-        <v>3520</v>
+        <v>3571.512195122</v>
       </c>
       <c r="O1127" t="n">
-        <v>278080</v>
+        <v>282149.463414638</v>
       </c>
       <c r="P1127" t="n">
         <v>4500</v>

--- a/bodegas/LJ-101.xlsx
+++ b/bodegas/LJ-101.xlsx
@@ -9013,10 +9013,10 @@
         <v>83</v>
       </c>
       <c r="N201" t="n">
-        <v>2582.2555145238</v>
+        <v>2582.2555084555</v>
       </c>
       <c r="O201" t="n">
-        <v>214327.2077054754</v>
+        <v>214327.2072018065</v>
       </c>
       <c r="P201" t="n">
         <v>4500</v>
@@ -9561,10 +9561,10 @@
         <v>130</v>
       </c>
       <c r="N213" t="n">
-        <v>3841.62486</v>
+        <v>3841.6248746239</v>
       </c>
       <c r="O213" t="n">
-        <v>499411.2318</v>
+        <v>499411.233701107</v>
       </c>
       <c r="P213" t="n">
         <v>6900</v>
@@ -15185,10 +15185,10 @@
         <v>76</v>
       </c>
       <c r="N337" t="n">
-        <v>1630.9239095069</v>
+        <v>1630.9239154786</v>
       </c>
       <c r="O337" t="n">
-        <v>123950.2171225244</v>
+        <v>123950.2175763736</v>
       </c>
       <c r="P337" t="n">
         <v>2500</v>
@@ -15415,10 +15415,10 @@
         <v>188</v>
       </c>
       <c r="N342" t="n">
-        <v>2403.5136926808</v>
+        <v>2403.513738111</v>
       </c>
       <c r="O342" t="n">
-        <v>451860.5742239904</v>
+        <v>451860.582764868</v>
       </c>
       <c r="P342" t="n">
         <v>3500</v>
@@ -15461,10 +15461,10 @@
         <v>5</v>
       </c>
       <c r="N343" t="n">
-        <v>2521.499109589</v>
+        <v>2521.4955797101</v>
       </c>
       <c r="O343" t="n">
-        <v>12607.495547945</v>
+        <v>12607.4778985505</v>
       </c>
       <c r="P343" t="n">
         <v>3900</v>
@@ -24365,10 +24365,10 @@
         <v>79</v>
       </c>
       <c r="N545" t="n">
-        <v>1664.3520684292</v>
+        <v>1664.351984375</v>
       </c>
       <c r="O545" t="n">
-        <v>131483.8134059068</v>
+        <v>131483.806765625</v>
       </c>
       <c r="P545" t="n">
         <v>2900</v>
@@ -33369,10 +33369,10 @@
         <v>39</v>
       </c>
       <c r="N740" t="n">
-        <v>1592.2817466667</v>
+        <v>1592.281793842</v>
       </c>
       <c r="O740" t="n">
-        <v>62098.9881200013</v>
+        <v>62098.989959838</v>
       </c>
       <c r="P740" t="n">
         <v>2500</v>
@@ -33592,10 +33592,10 @@
         <v>13</v>
       </c>
       <c r="N745" t="n">
-        <v>3033.7037</v>
+        <v>3033.7022680412</v>
       </c>
       <c r="O745" t="n">
-        <v>39438.1481</v>
+        <v>39438.1294845356</v>
       </c>
       <c r="P745" t="n">
         <v>4500</v>
@@ -38819,10 +38819,10 @@
         <v>1173</v>
       </c>
       <c r="N858" t="n">
-        <v>703.79500857932</v>
+        <v>703.79500789654</v>
       </c>
       <c r="O858" t="n">
-        <v>825551.5450635423</v>
+        <v>825551.5442626415</v>
       </c>
       <c r="P858" t="n">
         <v>900</v>

--- a/bodegas/LJ-101.xlsx
+++ b/bodegas/LJ-101.xlsx
@@ -771,10 +771,10 @@
         <v>17</v>
       </c>
       <c r="N9" t="n">
-        <v>27035.809018568</v>
+        <v>27000</v>
       </c>
       <c r="O9" t="n">
-        <v>459608.753315656</v>
+        <v>459000</v>
       </c>
       <c r="P9" t="n">
         <v>20000</v>
@@ -2999,10 +2999,10 @@
         <v>5</v>
       </c>
       <c r="N63" t="n">
-        <v>30074.074074074</v>
+        <v>29000</v>
       </c>
       <c r="O63" t="n">
-        <v>150370.37037037</v>
+        <v>145000</v>
       </c>
       <c r="P63" t="n">
         <v>34800</v>
@@ -8485,10 +8485,10 @@
         <v>14</v>
       </c>
       <c r="N189" t="n">
-        <v>17234.854035088</v>
+        <v>17207.41</v>
       </c>
       <c r="O189" t="n">
-        <v>241287.956491232</v>
+        <v>240903.74</v>
       </c>
       <c r="P189" t="n">
         <v>20000</v>
@@ -10068,10 +10068,10 @@
         <v>53</v>
       </c>
       <c r="N224" t="n">
-        <v>8807.6968085106</v>
+        <v>8796</v>
       </c>
       <c r="O224" t="n">
-        <v>466807.9308510618</v>
+        <v>466188</v>
       </c>
       <c r="P224" t="n">
         <v>14900</v>
@@ -10708,10 +10708,10 @@
         <v>11</v>
       </c>
       <c r="N238" t="n">
-        <v>5946.1052631579</v>
+        <v>5888</v>
       </c>
       <c r="O238" t="n">
-        <v>65407.1578947369</v>
+        <v>64768</v>
       </c>
       <c r="P238" t="n">
         <v>9500</v>
@@ -12047,10 +12047,10 @@
         <v>52</v>
       </c>
       <c r="N268" t="n">
-        <v>2667.0463248919</v>
+        <v>2665.4</v>
       </c>
       <c r="O268" t="n">
-        <v>138686.4088943788</v>
+        <v>138600.8</v>
       </c>
       <c r="P268" t="n">
         <v>20900</v>
@@ -12861,10 +12861,10 @@
         <v>4</v>
       </c>
       <c r="N286" t="n">
-        <v>4372.5234503719</v>
+        <v>4372.2107923341</v>
       </c>
       <c r="O286" t="n">
-        <v>17490.0938014876</v>
+        <v>17488.8431693364</v>
       </c>
       <c r="P286" t="n">
         <v>7500</v>
@@ -13621,10 +13621,10 @@
         <v>29</v>
       </c>
       <c r="N303" t="n">
-        <v>17473.953844316</v>
+        <v>17472.91</v>
       </c>
       <c r="O303" t="n">
-        <v>506744.6614851641</v>
+        <v>506714.39</v>
       </c>
       <c r="P303" t="n">
         <v>2900</v>
@@ -13709,10 +13709,10 @@
         <v>40</v>
       </c>
       <c r="N305" t="n">
-        <v>1530.7162764218</v>
+        <v>1530.63</v>
       </c>
       <c r="O305" t="n">
-        <v>61228.651056872</v>
+        <v>61225.2</v>
       </c>
       <c r="P305" t="n">
         <v>2900</v>
@@ -18376,10 +18376,10 @@
         <v>140</v>
       </c>
       <c r="N409" t="n">
-        <v>2569.7269830028</v>
+        <v>2567</v>
       </c>
       <c r="O409" t="n">
-        <v>359761.777620392</v>
+        <v>359380</v>
       </c>
       <c r="P409" t="n">
         <v>4500</v>
@@ -21477,10 +21477,10 @@
         <v>6</v>
       </c>
       <c r="N481" t="n">
-        <v>7982.1180305344</v>
+        <v>7969.9501679389</v>
       </c>
       <c r="O481" t="n">
-        <v>47892.7081832064</v>
+        <v>47819.7010076334</v>
       </c>
       <c r="P481" t="n">
         <v>12900</v>
@@ -21785,10 +21785,10 @@
         <v>5</v>
       </c>
       <c r="N488" t="n">
-        <v>10148.474923077</v>
+        <v>9994.710153846199</v>
       </c>
       <c r="O488" t="n">
-        <v>50742.37461538499</v>
+        <v>49973.550769231</v>
       </c>
       <c r="P488" t="n">
         <v>20800</v>
@@ -24278,10 +24278,10 @@
         <v>22</v>
       </c>
       <c r="N543" t="n">
-        <v>14447.670588235</v>
+        <v>14380</v>
       </c>
       <c r="O543" t="n">
-        <v>317848.75294117</v>
+        <v>316360</v>
       </c>
       <c r="P543" t="n">
         <v>23000</v>
@@ -28038,10 +28038,10 @@
         <v>3</v>
       </c>
       <c r="N624" t="n">
-        <v>23400.84</v>
+        <v>22942</v>
       </c>
       <c r="O624" t="n">
-        <v>70202.52</v>
+        <v>68826</v>
       </c>
       <c r="P624" t="n">
         <v>36900</v>
@@ -28501,10 +28501,10 @@
         <v>10</v>
       </c>
       <c r="N634" t="n">
-        <v>50584.365236051</v>
+        <v>50153.86</v>
       </c>
       <c r="O634" t="n">
-        <v>505843.65236051</v>
+        <v>501538.6</v>
       </c>
       <c r="P634" t="n">
         <v>11500</v>
@@ -29600,10 +29600,10 @@
         <v>4</v>
       </c>
       <c r="N658" t="n">
-        <v>9952.091954023001</v>
+        <v>9839</v>
       </c>
       <c r="O658" t="n">
-        <v>39808.367816092</v>
+        <v>39356</v>
       </c>
       <c r="P658" t="n">
         <v>16900</v>
@@ -30886,10 +30886,10 @@
         <v>135</v>
       </c>
       <c r="N686" t="n">
-        <v>59958.524453694</v>
+        <v>59834</v>
       </c>
       <c r="O686" t="n">
-        <v>8094400.80124869</v>
+        <v>8077590</v>
       </c>
       <c r="P686" t="n">
         <v>7900</v>
@@ -31070,10 +31070,10 @@
         <v>1</v>
       </c>
       <c r="N690" t="n">
-        <v>10270.481108312</v>
+        <v>10219</v>
       </c>
       <c r="O690" t="n">
-        <v>10270.481108312</v>
+        <v>10219</v>
       </c>
       <c r="P690" t="n">
         <v>16900</v>
@@ -32039,10 +32039,10 @@
         <v>95</v>
       </c>
       <c r="N711" t="n">
-        <v>3821.6520477816</v>
+        <v>3821</v>
       </c>
       <c r="O711" t="n">
-        <v>363056.944539252</v>
+        <v>362995</v>
       </c>
       <c r="P711" t="n">
         <v>5900</v>
@@ -32085,10 +32085,10 @@
         <v>2</v>
       </c>
       <c r="N712" t="n">
-        <v>15512.291666667</v>
+        <v>15472</v>
       </c>
       <c r="O712" t="n">
-        <v>31024.583333334</v>
+        <v>30944</v>
       </c>
       <c r="P712" t="n">
         <v>25900</v>
@@ -32223,10 +32223,10 @@
         <v>4</v>
       </c>
       <c r="N715" t="n">
-        <v>5486.9301397206</v>
+        <v>5476</v>
       </c>
       <c r="O715" t="n">
-        <v>21947.7205588824</v>
+        <v>21904</v>
       </c>
       <c r="P715" t="n">
         <v>8900</v>
@@ -33413,10 +33413,10 @@
         <v>28</v>
       </c>
       <c r="N741" t="n">
-        <v>5372.836713615</v>
+        <v>5347.73</v>
       </c>
       <c r="O741" t="n">
-        <v>150439.42798122</v>
+        <v>149736.44</v>
       </c>
       <c r="P741" t="n">
         <v>9500</v>
@@ -34005,10 +34005,10 @@
         <v>11</v>
       </c>
       <c r="N754" t="n">
-        <v>18654.637168142</v>
+        <v>18491</v>
       </c>
       <c r="O754" t="n">
-        <v>205201.008849562</v>
+        <v>203401</v>
       </c>
       <c r="P754" t="n">
         <v>13500</v>
@@ -35958,10 +35958,10 @@
         <v>37</v>
       </c>
       <c r="N796" t="n">
-        <v>2407.2030769231</v>
+        <v>2357.74</v>
       </c>
       <c r="O796" t="n">
-        <v>89066.5138461547</v>
+        <v>87236.37999999999</v>
       </c>
       <c r="P796" t="n">
         <v>3000</v>
@@ -45593,10 +45593,10 @@
         <v>8</v>
       </c>
       <c r="N1000" t="n">
-        <v>5235.0773519164</v>
+        <v>5216.9</v>
       </c>
       <c r="O1000" t="n">
-        <v>41880.6188153312</v>
+        <v>41735.2</v>
       </c>
       <c r="P1000" t="n">
         <v>20500</v>
@@ -46075,10 +46075,10 @@
         <v>65</v>
       </c>
       <c r="N1010" t="n">
-        <v>7049.9805782093</v>
+        <v>7046.9398274002</v>
       </c>
       <c r="O1010" t="n">
-        <v>458248.7375836045</v>
+        <v>458051.088781013</v>
       </c>
       <c r="P1010" t="n">
         <v>9900</v>

--- a/bodegas/LJ-101.xlsx
+++ b/bodegas/LJ-101.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-06</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-07</t>
         </is>
       </c>
     </row>

--- a/bodegas/LJ-101.xlsx
+++ b/bodegas/LJ-101.xlsx
@@ -6247,22 +6247,22 @@
         <v>0</v>
       </c>
       <c r="L138" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M138" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="N138" t="n">
         <v>2791.02</v>
       </c>
       <c r="O138" t="n">
-        <v>66984.48</v>
+        <v>33492.24</v>
       </c>
       <c r="P138" t="n">
         <v>3900</v>
       </c>
       <c r="Q138" t="n">
-        <v>93600</v>
+        <v>46800</v>
       </c>
     </row>
     <row r="139">
@@ -6286,22 +6286,22 @@
         <v>0</v>
       </c>
       <c r="L139" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M139" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="N139" t="n">
         <v>3564.14</v>
       </c>
       <c r="O139" t="n">
-        <v>35641.4</v>
+        <v>10692.42</v>
       </c>
       <c r="P139" t="n">
         <v>5500</v>
       </c>
       <c r="Q139" t="n">
-        <v>55000</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="140">
@@ -7652,22 +7652,22 @@
         <v>0</v>
       </c>
       <c r="L170" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M170" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N170" t="n">
-        <v>33815</v>
+        <v>35594.736842105</v>
       </c>
       <c r="O170" t="n">
-        <v>270520</v>
+        <v>249163.157894735</v>
       </c>
       <c r="P170" t="n">
         <v>47900</v>
       </c>
       <c r="Q170" t="n">
-        <v>383200</v>
+        <v>335300</v>
       </c>
     </row>
     <row r="171">
@@ -9055,10 +9055,10 @@
         <v>83</v>
       </c>
       <c r="N202" t="n">
-        <v>2582.2554675768</v>
+        <v>2582.2554613807</v>
       </c>
       <c r="O202" t="n">
-        <v>214327.2038088744</v>
+        <v>214327.2032945981</v>
       </c>
       <c r="P202" t="n">
         <v>4500</v>
@@ -9239,10 +9239,10 @@
         <v>6</v>
       </c>
       <c r="N206" t="n">
-        <v>2033.522992126</v>
+        <v>2033.5191735537</v>
       </c>
       <c r="O206" t="n">
-        <v>12201.137952756</v>
+        <v>12201.1150413222</v>
       </c>
       <c r="P206" t="n">
         <v>4100</v>
@@ -10055,22 +10055,22 @@
         <v>0</v>
       </c>
       <c r="L224" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M224" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N224" t="n">
-        <v>7507.39</v>
+        <v>7518.1997768179</v>
       </c>
       <c r="O224" t="n">
-        <v>345339.94</v>
+        <v>330800.7901799876</v>
       </c>
       <c r="P224" t="n">
         <v>13500</v>
       </c>
       <c r="Q224" t="n">
-        <v>621000</v>
+        <v>594000</v>
       </c>
     </row>
     <row r="225">
@@ -10104,22 +10104,22 @@
         <v>0</v>
       </c>
       <c r="L225" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M225" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="N225" t="n">
-        <v>8796</v>
+        <v>8831.230974632799</v>
       </c>
       <c r="O225" t="n">
-        <v>466188</v>
+        <v>441561.54873164</v>
       </c>
       <c r="P225" t="n">
         <v>14900</v>
       </c>
       <c r="Q225" t="n">
-        <v>789700</v>
+        <v>745000</v>
       </c>
     </row>
     <row r="226">
@@ -12494,22 +12494,22 @@
         <v>0</v>
       </c>
       <c r="L278" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M278" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N278" t="n">
-        <v>15851.61</v>
+        <v>15976.425826772</v>
       </c>
       <c r="O278" t="n">
-        <v>15851.61</v>
+        <v>0</v>
       </c>
       <c r="P278" t="n">
         <v>23900</v>
       </c>
       <c r="Q278" t="n">
-        <v>23900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="279">
@@ -15365,10 +15365,10 @@
         <v>292</v>
       </c>
       <c r="N341" t="n">
-        <v>1550.1940686328</v>
+        <v>1550.1940704179</v>
       </c>
       <c r="O341" t="n">
-        <v>452656.6680407776</v>
+        <v>452656.6685620268</v>
       </c>
       <c r="P341" t="n">
         <v>2500</v>
@@ -15457,10 +15457,10 @@
         <v>172</v>
       </c>
       <c r="N343" t="n">
-        <v>2403.5142945915</v>
+        <v>2403.514304468</v>
       </c>
       <c r="O343" t="n">
-        <v>413404.458669738</v>
+        <v>413404.460368496</v>
       </c>
       <c r="P343" t="n">
         <v>3500</v>
@@ -24406,22 +24406,22 @@
         <v>0</v>
       </c>
       <c r="L546" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M546" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N546" t="n">
-        <v>15502</v>
+        <v>15634.495726496</v>
       </c>
       <c r="O546" t="n">
-        <v>46506</v>
+        <v>31268.991452992</v>
       </c>
       <c r="P546" t="n">
         <v>25900</v>
       </c>
       <c r="Q546" t="n">
-        <v>77700</v>
+        <v>51800</v>
       </c>
     </row>
     <row r="547">
@@ -25114,10 +25114,10 @@
         <v>62</v>
       </c>
       <c r="N561" t="n">
-        <v>1778.4727006961</v>
+        <v>1778.4727011139</v>
       </c>
       <c r="O561" t="n">
-        <v>110265.3074431582</v>
+        <v>110265.3074690618</v>
       </c>
       <c r="P561" t="n">
         <v>4900</v>
@@ -27196,22 +27196,22 @@
         <v>0</v>
       </c>
       <c r="L606" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M606" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N606" t="n">
-        <v>28116</v>
+        <v>28613.628318584</v>
       </c>
       <c r="O606" t="n">
-        <v>196812</v>
+        <v>143068.14159292</v>
       </c>
       <c r="P606" t="n">
         <v>45900</v>
       </c>
       <c r="Q606" t="n">
-        <v>321300</v>
+        <v>229500</v>
       </c>
     </row>
     <row r="607">
@@ -30004,22 +30004,22 @@
         <v>0</v>
       </c>
       <c r="L667" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M667" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N667" t="n">
-        <v>27186</v>
+        <v>27309.572727273</v>
       </c>
       <c r="O667" t="n">
-        <v>81558</v>
+        <v>54619.145454546</v>
       </c>
       <c r="P667" t="n">
         <v>43900</v>
       </c>
       <c r="Q667" t="n">
-        <v>131700</v>
+        <v>87800</v>
       </c>
     </row>
     <row r="668">
@@ -31155,22 +31155,22 @@
         <v>0</v>
       </c>
       <c r="L692" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M692" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="N692" t="n">
-        <v>10755</v>
+        <v>10792.803163445</v>
       </c>
       <c r="O692" t="n">
-        <v>333405</v>
+        <v>291405.685413015</v>
       </c>
       <c r="P692" t="n">
         <v>17900</v>
       </c>
       <c r="Q692" t="n">
-        <v>554900</v>
+        <v>483300</v>
       </c>
     </row>
     <row r="693">
@@ -31845,22 +31845,22 @@
         <v>0</v>
       </c>
       <c r="L707" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M707" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="N707" t="n">
-        <v>10713.21</v>
+        <v>10792.371650246</v>
       </c>
       <c r="O707" t="n">
-        <v>117845.31</v>
+        <v>86338.97320196799</v>
       </c>
       <c r="P707" t="n">
         <v>20900</v>
       </c>
       <c r="Q707" t="n">
-        <v>229900</v>
+        <v>167200</v>
       </c>
     </row>
     <row r="708">
@@ -32769,10 +32769,10 @@
         <v>122</v>
       </c>
       <c r="N727" t="n">
-        <v>1803.0159286464</v>
+        <v>1803.0159327966</v>
       </c>
       <c r="O727" t="n">
-        <v>219967.9432948608</v>
+        <v>219967.9438011852</v>
       </c>
       <c r="P727" t="n">
         <v>2500</v>
@@ -33501,10 +33501,10 @@
         <v>19</v>
       </c>
       <c r="N743" t="n">
-        <v>1906.180625</v>
+        <v>1906.1803846154</v>
       </c>
       <c r="O743" t="n">
-        <v>36217.431875</v>
+        <v>36217.4273076926</v>
       </c>
       <c r="P743" t="n">
         <v>2900</v>
@@ -38768,22 +38768,22 @@
         <v>0</v>
       </c>
       <c r="L857" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M857" t="n">
-        <v>1172</v>
+        <v>1163</v>
       </c>
       <c r="N857" t="n">
-        <v>703.79497049501</v>
+        <v>703.79496992783</v>
       </c>
       <c r="O857" t="n">
-        <v>824847.7054201517</v>
+        <v>818513.5500260664</v>
       </c>
       <c r="P857" t="n">
         <v>900</v>
       </c>
       <c r="Q857" t="n">
-        <v>1054800</v>
+        <v>1046700</v>
       </c>
     </row>
     <row r="858">
@@ -46932,22 +46932,22 @@
         <v>0</v>
       </c>
       <c r="L1028" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M1028" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="N1028" t="n">
         <v>4581.84</v>
       </c>
       <c r="O1028" t="n">
-        <v>178691.76</v>
+        <v>146618.88</v>
       </c>
       <c r="P1028" t="n">
         <v>7900</v>
       </c>
       <c r="Q1028" t="n">
-        <v>308100</v>
+        <v>252800</v>
       </c>
     </row>
     <row r="1029">
@@ -51275,22 +51275,22 @@
         <v>0</v>
       </c>
       <c r="L1123" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M1123" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="N1123" t="n">
-        <v>7480</v>
+        <v>7524.8351648352</v>
       </c>
       <c r="O1123" t="n">
-        <v>478720</v>
+        <v>436440.4395604416</v>
       </c>
       <c r="P1123" t="n">
         <v>9500</v>
       </c>
       <c r="Q1123" t="n">
-        <v>608000</v>
+        <v>551000</v>
       </c>
     </row>
     <row r="1124">

--- a/bodegas/LJ-101.xlsx
+++ b/bodegas/LJ-101.xlsx
@@ -2677,10 +2677,10 @@
         <v>1</v>
       </c>
       <c r="N56" t="n">
-        <v>2053.9877300613</v>
+        <v>1800</v>
       </c>
       <c r="O56" t="n">
-        <v>2053.9877300613</v>
+        <v>1800</v>
       </c>
       <c r="P56" t="n">
         <v>2200</v>
@@ -4244,10 +4244,10 @@
         <v>1</v>
       </c>
       <c r="N92" t="n">
-        <v>23504.638888889</v>
+        <v>22267.552777778</v>
       </c>
       <c r="O92" t="n">
-        <v>23504.638888889</v>
+        <v>22267.552777778</v>
       </c>
       <c r="P92" t="n">
         <v>46300</v>
@@ -8034,22 +8034,22 @@
         <v>0</v>
       </c>
       <c r="L179" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M179" t="n">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="N179" t="n">
-        <v>1098.0627514701</v>
+        <v>1098.0628221049</v>
       </c>
       <c r="O179" t="n">
-        <v>375537.4610027742</v>
+        <v>364556.8569388269</v>
       </c>
       <c r="P179" t="n">
         <v>1500</v>
       </c>
       <c r="Q179" t="n">
-        <v>513000</v>
+        <v>498000</v>
       </c>
     </row>
     <row r="180">
@@ -8486,10 +8486,10 @@
         <v>11</v>
       </c>
       <c r="N189" t="n">
-        <v>13642.54185766</v>
+        <v>13593.35</v>
       </c>
       <c r="O189" t="n">
-        <v>150067.96043426</v>
+        <v>149526.85</v>
       </c>
       <c r="P189" t="n">
         <v>25500</v>
@@ -8791,10 +8791,10 @@
         <v>10</v>
       </c>
       <c r="N196" t="n">
-        <v>2808.3040151157</v>
+        <v>2804.33</v>
       </c>
       <c r="O196" t="n">
-        <v>28083.040151157</v>
+        <v>28043.3</v>
       </c>
       <c r="P196" t="n">
         <v>4900</v>
@@ -9055,10 +9055,10 @@
         <v>82</v>
       </c>
       <c r="N202" t="n">
-        <v>2584.0407928094</v>
+        <v>2582.2554090804</v>
       </c>
       <c r="O202" t="n">
-        <v>211891.3450103708</v>
+        <v>211744.9435445928</v>
       </c>
       <c r="P202" t="n">
         <v>4500</v>
@@ -9193,10 +9193,10 @@
         <v>42</v>
       </c>
       <c r="N205" t="n">
-        <v>5216.8960111863</v>
+        <v>5216.8960094242</v>
       </c>
       <c r="O205" t="n">
-        <v>219109.6324698246</v>
+        <v>219109.6323958164</v>
       </c>
       <c r="P205" t="n">
         <v>8500</v>
@@ -9416,10 +9416,10 @@
         <v>35</v>
       </c>
       <c r="N210" t="n">
-        <v>6754.0134146341</v>
+        <v>6713.08</v>
       </c>
       <c r="O210" t="n">
-        <v>236390.4695121935</v>
+        <v>234957.8</v>
       </c>
       <c r="P210" t="n">
         <v>9900</v>
@@ -9511,10 +9511,10 @@
         <v>377</v>
       </c>
       <c r="N212" t="n">
-        <v>3161.3542590035</v>
+        <v>3158.8608322644</v>
       </c>
       <c r="O212" t="n">
-        <v>1191830.555644319</v>
+        <v>1190890.533763679</v>
       </c>
       <c r="P212" t="n">
         <v>5600</v>
@@ -9785,10 +9785,10 @@
         <v>95</v>
       </c>
       <c r="N218" t="n">
-        <v>1482.16796875</v>
+        <v>1480</v>
       </c>
       <c r="O218" t="n">
-        <v>140805.95703125</v>
+        <v>140600</v>
       </c>
       <c r="P218" t="n">
         <v>2600</v>
@@ -10110,10 +10110,10 @@
         <v>50</v>
       </c>
       <c r="N225" t="n">
-        <v>8807.775100401601</v>
+        <v>8796</v>
       </c>
       <c r="O225" t="n">
-        <v>440388.75502008</v>
+        <v>439800</v>
       </c>
       <c r="P225" t="n">
         <v>14900</v>
@@ -10376,10 +10376,10 @@
         <v>128</v>
       </c>
       <c r="N231" t="n">
-        <v>2619.5155335628</v>
+        <v>2612.77</v>
       </c>
       <c r="O231" t="n">
-        <v>335297.9882960384</v>
+        <v>334434.56</v>
       </c>
       <c r="P231" t="n">
         <v>4900</v>
@@ -10422,10 +10422,10 @@
         <v>327</v>
       </c>
       <c r="N232" t="n">
-        <v>4362.7231895528</v>
+        <v>4357.55</v>
       </c>
       <c r="O232" t="n">
-        <v>1426610.482983766</v>
+        <v>1424918.85</v>
       </c>
       <c r="P232" t="n">
         <v>7500</v>
@@ -10514,10 +10514,10 @@
         <v>12</v>
       </c>
       <c r="N234" t="n">
-        <v>4890.9300496586</v>
+        <v>4890.9300497203</v>
       </c>
       <c r="O234" t="n">
-        <v>58691.1605959032</v>
+        <v>58691.1605966436</v>
       </c>
       <c r="P234" t="n">
         <v>8200</v>
@@ -11113,10 +11113,10 @@
         <v>6</v>
       </c>
       <c r="N247" t="n">
-        <v>8670.9576008273</v>
+        <v>8662</v>
       </c>
       <c r="O247" t="n">
-        <v>52025.7456049638</v>
+        <v>51972</v>
       </c>
       <c r="P247" t="n">
         <v>14200</v>
@@ -11290,10 +11290,10 @@
         <v>23</v>
       </c>
       <c r="N251" t="n">
-        <v>3594.2535785953</v>
+        <v>3594.2535742972</v>
       </c>
       <c r="O251" t="n">
-        <v>82667.8323076919</v>
+        <v>82667.83220883559</v>
       </c>
       <c r="P251" t="n">
         <v>6500</v>
@@ -11380,10 +11380,10 @@
         <v>1</v>
       </c>
       <c r="N253" t="n">
-        <v>500.91436884092</v>
+        <v>489.88</v>
       </c>
       <c r="O253" t="n">
-        <v>500.91436884092</v>
+        <v>489.88</v>
       </c>
       <c r="P253" t="n">
         <v>700</v>
@@ -11687,10 +11687,10 @@
         <v>11</v>
       </c>
       <c r="N260" t="n">
-        <v>14849.377704918</v>
+        <v>14822.378834244</v>
       </c>
       <c r="O260" t="n">
-        <v>163343.154754098</v>
+        <v>163046.167176684</v>
       </c>
       <c r="P260" t="n">
         <v>24900</v>
@@ -12089,10 +12089,10 @@
         <v>52</v>
       </c>
       <c r="N269" t="n">
-        <v>2672.0057001239</v>
+        <v>2665.4</v>
       </c>
       <c r="O269" t="n">
-        <v>138944.2964064428</v>
+        <v>138600.8</v>
       </c>
       <c r="P269" t="n">
         <v>20900</v>
@@ -12271,10 +12271,10 @@
         <v>9</v>
       </c>
       <c r="N273" t="n">
-        <v>12618.152142857</v>
+        <v>12267.647571429</v>
       </c>
       <c r="O273" t="n">
-        <v>113563.369285713</v>
+        <v>110408.828142861</v>
       </c>
       <c r="P273" t="n">
         <v>19900</v>
@@ -12731,10 +12731,10 @@
         <v>7</v>
       </c>
       <c r="N283" t="n">
-        <v>3041.6600137268</v>
+        <v>3041.6600137646</v>
       </c>
       <c r="O283" t="n">
-        <v>21291.6200960876</v>
+        <v>21291.6200963522</v>
       </c>
       <c r="P283" t="n">
         <v>5500</v>
@@ -12859,10 +12859,10 @@
         <v>3</v>
       </c>
       <c r="N286" t="n">
-        <v>4372.2107926742</v>
+        <v>4374.7145640659</v>
       </c>
       <c r="O286" t="n">
-        <v>13116.6323780226</v>
+        <v>13124.1436921977</v>
       </c>
       <c r="P286" t="n">
         <v>7500</v>
@@ -13795,10 +13795,10 @@
         <v>1</v>
       </c>
       <c r="N307" t="n">
-        <v>9422.619187996501</v>
+        <v>9414.309999999999</v>
       </c>
       <c r="O307" t="n">
-        <v>9422.619187996501</v>
+        <v>9414.309999999999</v>
       </c>
       <c r="P307" t="n">
         <v>16900</v>
@@ -13983,10 +13983,10 @@
         <v>61</v>
       </c>
       <c r="N311" t="n">
-        <v>4673.2793206522</v>
+        <v>4635.49</v>
       </c>
       <c r="O311" t="n">
-        <v>285070.0385597842</v>
+        <v>282764.89</v>
       </c>
       <c r="P311" t="n">
         <v>7500</v>
@@ -14169,10 +14169,10 @@
         <v>5</v>
       </c>
       <c r="N315" t="n">
-        <v>16960.16635514</v>
+        <v>16897</v>
       </c>
       <c r="O315" t="n">
-        <v>84800.8317757</v>
+        <v>84485</v>
       </c>
       <c r="P315" t="n">
         <v>27900</v>
@@ -14586,10 +14586,10 @@
         <v>14</v>
       </c>
       <c r="N324" t="n">
-        <v>11939.712442396</v>
+        <v>11921.4</v>
       </c>
       <c r="O324" t="n">
-        <v>167155.974193544</v>
+        <v>166899.6</v>
       </c>
       <c r="P324" t="n">
         <v>19900</v>
@@ -15091,10 +15091,10 @@
         <v>7</v>
       </c>
       <c r="N335" t="n">
-        <v>9926.065993788799</v>
+        <v>9903</v>
       </c>
       <c r="O335" t="n">
-        <v>69482.4619565216</v>
+        <v>69321</v>
       </c>
       <c r="P335" t="n">
         <v>15900</v>
@@ -15275,10 +15275,10 @@
         <v>11</v>
       </c>
       <c r="N339" t="n">
-        <v>1690.5907183908</v>
+        <v>1830.8887033195</v>
       </c>
       <c r="O339" t="n">
-        <v>18596.4979022988</v>
+        <v>20139.7757365145</v>
       </c>
       <c r="P339" t="n">
         <v>2900</v>
@@ -15321,10 +15321,10 @@
         <v>292</v>
       </c>
       <c r="N340" t="n">
-        <v>1550.194110545</v>
+        <v>1550.1942738685</v>
       </c>
       <c r="O340" t="n">
-        <v>452656.68027914</v>
+        <v>452656.727969602</v>
       </c>
       <c r="P340" t="n">
         <v>2500</v>
@@ -15413,10 +15413,10 @@
         <v>172</v>
       </c>
       <c r="N342" t="n">
-        <v>2403.5145969448</v>
+        <v>2549.7269035153</v>
       </c>
       <c r="O342" t="n">
-        <v>413404.5106745056</v>
+        <v>438553.0274046316</v>
       </c>
       <c r="P342" t="n">
         <v>3500</v>
@@ -16785,22 +16785,22 @@
         <v>0</v>
       </c>
       <c r="L373" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M373" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N373" t="n">
         <v>6280.31</v>
       </c>
       <c r="O373" t="n">
-        <v>43962.17000000001</v>
+        <v>31401.55</v>
       </c>
       <c r="P373" t="n">
         <v>10500</v>
       </c>
       <c r="Q373" t="n">
-        <v>73500</v>
+        <v>52500</v>
       </c>
     </row>
     <row r="374">
@@ -17822,22 +17822,22 @@
         <v>0</v>
       </c>
       <c r="L396" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M396" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="N396" t="n">
-        <v>9396.9148264984</v>
+        <v>9338</v>
       </c>
       <c r="O396" t="n">
-        <v>319495.1041009456</v>
+        <v>298816</v>
       </c>
       <c r="P396" t="n">
         <v>15500</v>
       </c>
       <c r="Q396" t="n">
-        <v>527000</v>
+        <v>496000</v>
       </c>
     </row>
     <row r="397">
@@ -18287,10 +18287,10 @@
         <v>53</v>
       </c>
       <c r="N407" t="n">
-        <v>8799.4430248307</v>
+        <v>8794.48</v>
       </c>
       <c r="O407" t="n">
-        <v>466370.4803160271</v>
+        <v>466107.44</v>
       </c>
       <c r="P407" t="n">
         <v>14500</v>
@@ -18456,10 +18456,10 @@
         <v>73</v>
       </c>
       <c r="N411" t="n">
-        <v>2523.5712699748</v>
+        <v>2517.22</v>
       </c>
       <c r="O411" t="n">
-        <v>184220.7027081604</v>
+        <v>183757.06</v>
       </c>
       <c r="P411" t="n">
         <v>4200</v>
@@ -18958,10 +18958,10 @@
         <v>15</v>
       </c>
       <c r="N423" t="n">
-        <v>14161.073142857</v>
+        <v>14060.64</v>
       </c>
       <c r="O423" t="n">
-        <v>212416.097142855</v>
+        <v>210909.6</v>
       </c>
       <c r="P423" t="n">
         <v>22900</v>
@@ -19524,10 +19524,10 @@
         <v>16</v>
       </c>
       <c r="N436" t="n">
-        <v>4285.1958660508</v>
+        <v>4285.1959694477</v>
       </c>
       <c r="O436" t="n">
-        <v>68563.1338568128</v>
+        <v>68563.1355111632</v>
       </c>
       <c r="P436" t="n">
         <v>6900</v>
@@ -20080,10 +20080,10 @@
         <v>12</v>
       </c>
       <c r="N449" t="n">
-        <v>11594.607549296</v>
+        <v>11562.038422535</v>
       </c>
       <c r="O449" t="n">
-        <v>139135.290591552</v>
+        <v>138744.46107042</v>
       </c>
       <c r="P449" t="n">
         <v>18500</v>
@@ -20126,10 +20126,10 @@
         <v>12</v>
       </c>
       <c r="N450" t="n">
-        <v>13621.7524</v>
+        <v>13513.64328</v>
       </c>
       <c r="O450" t="n">
-        <v>163461.0288</v>
+        <v>162163.71936</v>
       </c>
       <c r="P450" t="n">
         <v>21900</v>
@@ -20336,10 +20336,10 @@
         <v>7</v>
       </c>
       <c r="N455" t="n">
-        <v>22428.571428571</v>
+        <v>15700</v>
       </c>
       <c r="O455" t="n">
-        <v>156999.999999997</v>
+        <v>109900</v>
       </c>
       <c r="P455" t="n">
         <v>29900</v>
@@ -20689,10 +20689,10 @@
         <v>9</v>
       </c>
       <c r="N463" t="n">
-        <v>27871.270433071</v>
+        <v>27123.76496063</v>
       </c>
       <c r="O463" t="n">
-        <v>250841.433897639</v>
+        <v>244113.88464567</v>
       </c>
       <c r="P463" t="n">
         <v>44500</v>
@@ -20817,10 +20817,10 @@
         <v>21</v>
       </c>
       <c r="N466" t="n">
-        <v>17070.322056338</v>
+        <v>16974.69</v>
       </c>
       <c r="O466" t="n">
-        <v>358476.7631830979</v>
+        <v>356468.49</v>
       </c>
       <c r="P466" t="n">
         <v>26900</v>
@@ -20858,10 +20858,10 @@
         <v>3</v>
       </c>
       <c r="N467" t="n">
-        <v>4110.4025485437</v>
+        <v>4100.45</v>
       </c>
       <c r="O467" t="n">
-        <v>12331.2076456311</v>
+        <v>12301.35</v>
       </c>
       <c r="P467" t="n">
         <v>26900</v>
@@ -21693,10 +21693,10 @@
         <v>2</v>
       </c>
       <c r="N486" t="n">
-        <v>9681.731751412401</v>
+        <v>9627.34</v>
       </c>
       <c r="O486" t="n">
-        <v>19363.4635028248</v>
+        <v>19254.68</v>
       </c>
       <c r="P486" t="n">
         <v>15900</v>
@@ -24316,22 +24316,22 @@
         <v>0</v>
       </c>
       <c r="L544" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M544" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="N544" t="n">
-        <v>1664.3476116505</v>
+        <v>1664.3474804688</v>
       </c>
       <c r="O544" t="n">
-        <v>118168.6804271855</v>
+        <v>113175.6286718784</v>
       </c>
       <c r="P544" t="n">
         <v>2900</v>
       </c>
       <c r="Q544" t="n">
-        <v>205900</v>
+        <v>197200</v>
       </c>
     </row>
     <row r="545">
@@ -25070,10 +25070,10 @@
         <v>2</v>
       </c>
       <c r="N560" t="n">
-        <v>3494.4765957447</v>
+        <v>3486</v>
       </c>
       <c r="O560" t="n">
-        <v>6988.9531914894</v>
+        <v>6972</v>
       </c>
       <c r="P560" t="n">
         <v>6900</v>
@@ -25116,10 +25116,10 @@
         <v>62</v>
       </c>
       <c r="N561" t="n">
-        <v>1778.4727221703</v>
+        <v>1778.4727234441</v>
       </c>
       <c r="O561" t="n">
-        <v>110265.3087745586</v>
+        <v>110265.3088535342</v>
       </c>
       <c r="P561" t="n">
         <v>4900</v>
@@ -27573,10 +27573,10 @@
         <v>20</v>
       </c>
       <c r="N614" t="n">
-        <v>8872.340618996799</v>
+        <v>8858.16</v>
       </c>
       <c r="O614" t="n">
-        <v>177446.812379936</v>
+        <v>177163.2</v>
       </c>
       <c r="P614" t="n">
         <v>15500</v>
@@ -28361,10 +28361,10 @@
         <v>121</v>
       </c>
       <c r="N631" t="n">
-        <v>2336.84913125</v>
+        <v>2328.11868125</v>
       </c>
       <c r="O631" t="n">
-        <v>282758.74488125</v>
+        <v>281702.36043125</v>
       </c>
       <c r="P631" t="n">
         <v>4500</v>
@@ -29281,10 +29281,10 @@
         <v>88</v>
       </c>
       <c r="N651" t="n">
-        <v>3922.9680788177</v>
+        <v>3903.7379310345</v>
       </c>
       <c r="O651" t="n">
-        <v>345221.1909359576</v>
+        <v>343528.937931036</v>
       </c>
       <c r="P651" t="n">
         <v>7500</v>
@@ -29460,10 +29460,10 @@
         <v>6</v>
       </c>
       <c r="N655" t="n">
-        <v>33317.307692308</v>
+        <v>33000</v>
       </c>
       <c r="O655" t="n">
-        <v>199903.846153848</v>
+        <v>198000</v>
       </c>
       <c r="P655" t="n">
         <v>52900</v>
@@ -30104,10 +30104,10 @@
         <v>1</v>
       </c>
       <c r="N669" t="n">
-        <v>7668.5070422535</v>
+        <v>7562</v>
       </c>
       <c r="O669" t="n">
-        <v>7668.5070422535</v>
+        <v>7562</v>
       </c>
       <c r="P669" t="n">
         <v>12900</v>
@@ -30150,10 +30150,10 @@
         <v>18</v>
       </c>
       <c r="N670" t="n">
-        <v>3901.1562753036</v>
+        <v>3898</v>
       </c>
       <c r="O670" t="n">
-        <v>70220.8129554648</v>
+        <v>70164</v>
       </c>
       <c r="P670" t="n">
         <v>6900</v>
@@ -30196,10 +30196,10 @@
         <v>7</v>
       </c>
       <c r="N671" t="n">
-        <v>13606.546707504</v>
+        <v>13565</v>
       </c>
       <c r="O671" t="n">
-        <v>95245.826952528</v>
+        <v>94955</v>
       </c>
       <c r="P671" t="n">
         <v>22500</v>
@@ -30242,10 +30242,10 @@
         <v>12</v>
       </c>
       <c r="N672" t="n">
-        <v>7647.7960893855</v>
+        <v>7635</v>
       </c>
       <c r="O672" t="n">
-        <v>91773.553072626</v>
+        <v>91620</v>
       </c>
       <c r="P672" t="n">
         <v>13900</v>
@@ -30288,10 +30288,10 @@
         <v>13</v>
       </c>
       <c r="N673" t="n">
-        <v>5690.8504672897</v>
+        <v>5682</v>
       </c>
       <c r="O673" t="n">
-        <v>73981.05607476609</v>
+        <v>73866</v>
       </c>
       <c r="P673" t="n">
         <v>9900</v>
@@ -30334,10 +30334,10 @@
         <v>9</v>
       </c>
       <c r="N674" t="n">
-        <v>5465.19</v>
+        <v>5438</v>
       </c>
       <c r="O674" t="n">
-        <v>49186.71</v>
+        <v>48942</v>
       </c>
       <c r="P674" t="n">
         <v>8900</v>
@@ -31439,10 +31439,10 @@
         <v>83</v>
       </c>
       <c r="N698" t="n">
-        <v>5319.824120603</v>
+        <v>5215</v>
       </c>
       <c r="O698" t="n">
-        <v>441545.402010049</v>
+        <v>432845</v>
       </c>
       <c r="P698" t="n">
         <v>8900</v>
@@ -31715,10 +31715,10 @@
         <v>21</v>
       </c>
       <c r="N704" t="n">
-        <v>8721.0653753027</v>
+        <v>8700</v>
       </c>
       <c r="O704" t="n">
-        <v>183142.3728813567</v>
+        <v>182700</v>
       </c>
       <c r="P704" t="n">
         <v>14900</v>
@@ -32083,10 +32083,10 @@
         <v>8</v>
       </c>
       <c r="N712" t="n">
-        <v>21822.282548476</v>
+        <v>21762</v>
       </c>
       <c r="O712" t="n">
-        <v>174578.260387808</v>
+        <v>174096</v>
       </c>
       <c r="P712" t="n">
         <v>35900</v>
@@ -32175,10 +32175,10 @@
         <v>2</v>
       </c>
       <c r="N714" t="n">
-        <v>15512.396866841</v>
+        <v>15472</v>
       </c>
       <c r="O714" t="n">
-        <v>31024.793733682</v>
+        <v>30944</v>
       </c>
       <c r="P714" t="n">
         <v>25900</v>
@@ -32313,10 +32313,10 @@
         <v>4</v>
       </c>
       <c r="N717" t="n">
-        <v>5483.2964690207</v>
+        <v>5476</v>
       </c>
       <c r="O717" t="n">
-        <v>21933.1858760828</v>
+        <v>21904</v>
       </c>
       <c r="P717" t="n">
         <v>8900</v>
@@ -33372,10 +33372,10 @@
         <v>33</v>
       </c>
       <c r="N740" t="n">
-        <v>1592.2821517241</v>
+        <v>1789.7745116279</v>
       </c>
       <c r="O740" t="n">
-        <v>52545.3110068953</v>
+        <v>59062.5588837207</v>
       </c>
       <c r="P740" t="n">
         <v>2500</v>
@@ -34465,10 +34465,10 @@
         <v>9</v>
       </c>
       <c r="N764" t="n">
-        <v>15733.897449664</v>
+        <v>15423.36</v>
       </c>
       <c r="O764" t="n">
-        <v>141605.077046976</v>
+        <v>138810.24</v>
       </c>
       <c r="P764" t="n">
         <v>24900</v>
@@ -35901,22 +35901,22 @@
         <v>0</v>
       </c>
       <c r="L795" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M795" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N795" t="n">
-        <v>10732.242580645</v>
+        <v>10732.242857143</v>
       </c>
       <c r="O795" t="n">
-        <v>53661.21290322499</v>
+        <v>21464.485714286</v>
       </c>
       <c r="P795" t="n">
         <v>25900</v>
       </c>
       <c r="Q795" t="n">
-        <v>129500</v>
+        <v>51800</v>
       </c>
     </row>
     <row r="796">
@@ -38410,10 +38410,10 @@
         <v>205</v>
       </c>
       <c r="N849" t="n">
-        <v>3110.839841954</v>
+        <v>3110.8397979798</v>
       </c>
       <c r="O849" t="n">
-        <v>637722.16760057</v>
+        <v>637722.158585859</v>
       </c>
       <c r="P849" t="n">
         <v>4500</v>
@@ -40372,10 +40372,10 @@
         <v>24</v>
       </c>
       <c r="N891" t="n">
-        <v>18621.814408602</v>
+        <v>18423.71</v>
       </c>
       <c r="O891" t="n">
-        <v>446923.545806448</v>
+        <v>442169.04</v>
       </c>
       <c r="P891" t="n">
         <v>10000</v>
@@ -43010,10 +43010,10 @@
         <v>14</v>
       </c>
       <c r="N946" t="n">
-        <v>3098.3874489796</v>
+        <v>3067.0906122449</v>
       </c>
       <c r="O946" t="n">
-        <v>43377.4242857144</v>
+        <v>42939.2685714286</v>
       </c>
       <c r="P946" t="n">
         <v>7200</v>
@@ -44406,10 +44406,10 @@
         <v>11</v>
       </c>
       <c r="N975" t="n">
-        <v>10993.181190476</v>
+        <v>10737.525714286</v>
       </c>
       <c r="O975" t="n">
-        <v>120924.993095236</v>
+        <v>118112.782857146</v>
       </c>
       <c r="P975" t="n">
         <v>18900</v>
@@ -46211,10 +46211,10 @@
         <v>11</v>
       </c>
       <c r="N1013" t="n">
-        <v>24490.111557632</v>
+        <v>24338.47</v>
       </c>
       <c r="O1013" t="n">
-        <v>269391.227133952</v>
+        <v>267723.17</v>
       </c>
       <c r="P1013" t="n">
         <v>27900</v>
@@ -51277,22 +51277,22 @@
         <v>0</v>
       </c>
       <c r="L1123" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M1123" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="N1123" t="n">
         <v>7480</v>
       </c>
       <c r="O1123" t="n">
-        <v>433840</v>
+        <v>411400</v>
       </c>
       <c r="P1123" t="n">
         <v>9500</v>
       </c>
       <c r="Q1123" t="n">
-        <v>551000</v>
+        <v>522500</v>
       </c>
     </row>
     <row r="1124">
@@ -51881,10 +51881,10 @@
         <v>24</v>
       </c>
       <c r="N1136" t="n">
-        <v>4598.7284768212</v>
+        <v>4576</v>
       </c>
       <c r="O1136" t="n">
-        <v>110369.4834437088</v>
+        <v>109824</v>
       </c>
       <c r="P1136" t="n">
         <v>5900</v>
@@ -55919,10 +55919,10 @@
         <v>50</v>
       </c>
       <c r="N1223" t="n">
-        <v>3732.8768115942</v>
+        <v>4365.5677966102</v>
       </c>
       <c r="O1223" t="n">
-        <v>186643.84057971</v>
+        <v>218278.38983051</v>
       </c>
       <c r="P1223" t="n">
         <v>4500</v>
@@ -56103,10 +56103,10 @@
         <v>61</v>
       </c>
       <c r="N1227" t="n">
-        <v>4566.0211267606</v>
+        <v>4550</v>
       </c>
       <c r="O1227" t="n">
-        <v>278527.2887323966</v>
+        <v>277550</v>
       </c>
       <c r="P1227" t="n">
         <v>5500</v>

--- a/bodegas/LJ-101.xlsx
+++ b/bodegas/LJ-101.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-09</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-10</t>
         </is>
       </c>
     </row>
@@ -2066,10 +2066,10 @@
         <v>42</v>
       </c>
       <c r="N41" t="n">
-        <v>2474.7040138408</v>
+        <v>2474.7039930556</v>
       </c>
       <c r="O41" t="n">
-        <v>103937.5685813136</v>
+        <v>103937.5677083352</v>
       </c>
       <c r="P41" t="n">
         <v>4500</v>
@@ -3654,7 +3654,7 @@
         </is>
       </c>
       <c r="J78" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K78" t="n">
         <v>0</v>
@@ -3663,19 +3663,19 @@
         <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N78" t="n">
-        <v>16486.408196721</v>
+        <v>16486.408099174</v>
       </c>
       <c r="O78" t="n">
-        <v>131891.265573768</v>
+        <v>115404.856694218</v>
       </c>
       <c r="P78" t="n">
         <v>30500</v>
       </c>
       <c r="Q78" t="n">
-        <v>244000</v>
+        <v>213500</v>
       </c>
     </row>
     <row r="79">
@@ -3696,7 +3696,7 @@
         </is>
       </c>
       <c r="J79" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K79" t="n">
         <v>0</v>
@@ -3705,19 +3705,19 @@
         <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N79" t="n">
-        <v>15711.96478022</v>
+        <v>15711.964751381</v>
       </c>
       <c r="O79" t="n">
-        <v>219967.50692308</v>
+        <v>204255.541767953</v>
       </c>
       <c r="P79" t="n">
         <v>28500</v>
       </c>
       <c r="Q79" t="n">
-        <v>399000</v>
+        <v>370500</v>
       </c>
     </row>
     <row r="80">
@@ -3743,7 +3743,7 @@
         </is>
       </c>
       <c r="J80" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K80" t="n">
         <v>0</v>
@@ -3752,19 +3752,19 @@
         <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N80" t="n">
-        <v>9392.0755737705</v>
+        <v>9392.0756666667</v>
       </c>
       <c r="O80" t="n">
-        <v>75136.604590164</v>
+        <v>65744.5296666669</v>
       </c>
       <c r="P80" t="n">
         <v>18500</v>
       </c>
       <c r="Q80" t="n">
-        <v>148000</v>
+        <v>129500</v>
       </c>
     </row>
     <row r="81">
@@ -4464,7 +4464,7 @@
         </is>
       </c>
       <c r="J97" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K97" t="n">
         <v>0</v>
@@ -4473,19 +4473,19 @@
         <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N97" t="n">
-        <v>56906.805744681</v>
+        <v>56906.806444444</v>
       </c>
       <c r="O97" t="n">
-        <v>227627.222978724</v>
+        <v>170720.419333332</v>
       </c>
       <c r="P97" t="n">
         <v>95900</v>
       </c>
       <c r="Q97" t="n">
-        <v>383600</v>
+        <v>287700</v>
       </c>
     </row>
     <row r="98">
@@ -4570,10 +4570,10 @@
         <v>6</v>
       </c>
       <c r="N99" t="n">
-        <v>141416.88460526</v>
+        <v>141416.88462046</v>
       </c>
       <c r="O99" t="n">
-        <v>848501.3076315601</v>
+        <v>848501.3077227601</v>
       </c>
       <c r="P99" t="n">
         <v>251900</v>
@@ -4612,10 +4612,10 @@
         <v>5</v>
       </c>
       <c r="N100" t="n">
-        <v>200072.20205607</v>
+        <v>200072.20216981</v>
       </c>
       <c r="O100" t="n">
-        <v>1000361.01028035</v>
+        <v>1000361.01084905</v>
       </c>
       <c r="P100" t="n">
         <v>312000</v>
@@ -6601,10 +6601,10 @@
         <v>1</v>
       </c>
       <c r="N146" t="n">
-        <v>4333.614</v>
+        <v>4333.6175</v>
       </c>
       <c r="O146" t="n">
-        <v>4333.614</v>
+        <v>4333.6175</v>
       </c>
       <c r="P146" t="n">
         <v>7500</v>
@@ -7300,7 +7300,7 @@
         </is>
       </c>
       <c r="J162" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="K162" t="n">
         <v>0</v>
@@ -7309,19 +7309,19 @@
         <v>0</v>
       </c>
       <c r="M162" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="N162" t="n">
         <v>1368.1</v>
       </c>
       <c r="O162" t="n">
-        <v>62932.6</v>
+        <v>58828.3</v>
       </c>
       <c r="P162" t="n">
         <v>1900</v>
       </c>
       <c r="Q162" t="n">
-        <v>87400</v>
+        <v>81700</v>
       </c>
     </row>
     <row r="163">
@@ -7617,10 +7617,10 @@
         <v>41</v>
       </c>
       <c r="N169" t="n">
-        <v>1950.2145369407</v>
+        <v>1950.214488189</v>
       </c>
       <c r="O169" t="n">
-        <v>79958.79601456871</v>
+        <v>79958.79401574899</v>
       </c>
       <c r="P169" t="n">
         <v>2900</v>
@@ -8028,28 +8028,28 @@
         </is>
       </c>
       <c r="J179" t="n">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="K179" t="n">
         <v>0</v>
       </c>
       <c r="L179" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M179" t="n">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="N179" t="n">
-        <v>1098.0628221049</v>
+        <v>1098.062979056</v>
       </c>
       <c r="O179" t="n">
-        <v>364556.8569388269</v>
+        <v>357968.531172256</v>
       </c>
       <c r="P179" t="n">
         <v>1500</v>
       </c>
       <c r="Q179" t="n">
-        <v>498000</v>
+        <v>489000</v>
       </c>
     </row>
     <row r="180">
@@ -8428,7 +8428,7 @@
         </is>
       </c>
       <c r="J188" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K188" t="n">
         <v>0</v>
@@ -8437,19 +8437,19 @@
         <v>0</v>
       </c>
       <c r="M188" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N188" t="n">
         <v>12587</v>
       </c>
       <c r="O188" t="n">
-        <v>113283</v>
+        <v>100696</v>
       </c>
       <c r="P188" t="n">
         <v>18900</v>
       </c>
       <c r="Q188" t="n">
-        <v>170100</v>
+        <v>151200</v>
       </c>
     </row>
     <row r="189">
@@ -8861,7 +8861,7 @@
         </is>
       </c>
       <c r="J198" t="n">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="K198" t="n">
         <v>0</v>
@@ -8870,19 +8870,19 @@
         <v>0</v>
       </c>
       <c r="M198" t="n">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="N198" t="n">
         <v>1194.83</v>
       </c>
       <c r="O198" t="n">
-        <v>123067.49</v>
+        <v>112314.02</v>
       </c>
       <c r="P198" t="n">
         <v>2500</v>
       </c>
       <c r="Q198" t="n">
-        <v>257500</v>
+        <v>235000</v>
       </c>
     </row>
     <row r="199">
@@ -9055,10 +9055,10 @@
         <v>82</v>
       </c>
       <c r="N202" t="n">
-        <v>2582.2554090804</v>
+        <v>2582.2554027233</v>
       </c>
       <c r="O202" t="n">
-        <v>211744.9435445928</v>
+        <v>211744.9430233106</v>
       </c>
       <c r="P202" t="n">
         <v>4500</v>
@@ -9193,10 +9193,10 @@
         <v>42</v>
       </c>
       <c r="N205" t="n">
-        <v>5216.8960094242</v>
+        <v>5216.8960047177</v>
       </c>
       <c r="O205" t="n">
-        <v>219109.6323958164</v>
+        <v>219109.6321981434</v>
       </c>
       <c r="P205" t="n">
         <v>8500</v>
@@ -9239,10 +9239,10 @@
         <v>6</v>
       </c>
       <c r="N206" t="n">
-        <v>2033.5191735537</v>
+        <v>2033.5178151261</v>
       </c>
       <c r="O206" t="n">
-        <v>12201.1150413222</v>
+        <v>12201.1068907566</v>
       </c>
       <c r="P206" t="n">
         <v>4100</v>
@@ -9363,7 +9363,7 @@
         </is>
       </c>
       <c r="J209" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="K209" t="n">
         <v>0</v>
@@ -9372,19 +9372,19 @@
         <v>0</v>
       </c>
       <c r="M209" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="N209" t="n">
         <v>1844.18</v>
       </c>
       <c r="O209" t="n">
-        <v>20285.98</v>
+        <v>12909.26</v>
       </c>
       <c r="P209" t="n">
         <v>3200</v>
       </c>
       <c r="Q209" t="n">
-        <v>35200</v>
+        <v>22400</v>
       </c>
     </row>
     <row r="210">
@@ -9404,7 +9404,7 @@
         </is>
       </c>
       <c r="J210" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K210" t="n">
         <v>0</v>
@@ -9413,19 +9413,19 @@
         <v>0</v>
       </c>
       <c r="M210" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="N210" t="n">
         <v>6713.08</v>
       </c>
       <c r="O210" t="n">
-        <v>234957.8</v>
+        <v>221531.64</v>
       </c>
       <c r="P210" t="n">
         <v>9900</v>
       </c>
       <c r="Q210" t="n">
-        <v>346500</v>
+        <v>326700</v>
       </c>
     </row>
     <row r="211">
@@ -9499,7 +9499,7 @@
         </is>
       </c>
       <c r="J212" t="n">
-        <v>377</v>
+        <v>355</v>
       </c>
       <c r="K212" t="n">
         <v>0</v>
@@ -9508,19 +9508,19 @@
         <v>0</v>
       </c>
       <c r="M212" t="n">
-        <v>377</v>
+        <v>355</v>
       </c>
       <c r="N212" t="n">
-        <v>3158.8608322644</v>
+        <v>3158.8608345701</v>
       </c>
       <c r="O212" t="n">
-        <v>1190890.533763679</v>
+        <v>1121395.596272385</v>
       </c>
       <c r="P212" t="n">
         <v>5600</v>
       </c>
       <c r="Q212" t="n">
-        <v>2111200</v>
+        <v>1988000</v>
       </c>
     </row>
     <row r="213">
@@ -9591,7 +9591,7 @@
         </is>
       </c>
       <c r="J214" t="n">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="K214" t="n">
         <v>0</v>
@@ -9600,19 +9600,19 @@
         <v>0</v>
       </c>
       <c r="M214" t="n">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="N214" t="n">
-        <v>3841.6249390244</v>
+        <v>3841.6250103093</v>
       </c>
       <c r="O214" t="n">
-        <v>495569.6171341476</v>
+        <v>445628.5011958788</v>
       </c>
       <c r="P214" t="n">
         <v>6900</v>
       </c>
       <c r="Q214" t="n">
-        <v>890100</v>
+        <v>800400</v>
       </c>
     </row>
     <row r="215">
@@ -9678,28 +9678,28 @@
         </is>
       </c>
       <c r="J216" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="K216" t="n">
         <v>0</v>
       </c>
       <c r="L216" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M216" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="N216" t="n">
         <v>8214</v>
       </c>
       <c r="O216" t="n">
-        <v>353202</v>
+        <v>435342</v>
       </c>
       <c r="P216" t="n">
         <v>7900</v>
       </c>
       <c r="Q216" t="n">
-        <v>339700</v>
+        <v>418700</v>
       </c>
     </row>
     <row r="217">
@@ -9727,7 +9727,7 @@
         </is>
       </c>
       <c r="J217" t="n">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="K217" t="n">
         <v>0</v>
@@ -9736,19 +9736,19 @@
         <v>0</v>
       </c>
       <c r="M217" t="n">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="N217" t="n">
-        <v>3230.0666985646</v>
+        <v>3230.0666176471</v>
       </c>
       <c r="O217" t="n">
-        <v>300396.2029665078</v>
+        <v>281015.7957352977</v>
       </c>
       <c r="P217" t="n">
         <v>6200</v>
       </c>
       <c r="Q217" t="n">
-        <v>576600</v>
+        <v>539400</v>
       </c>
     </row>
     <row r="218">
@@ -9911,7 +9911,7 @@
         </is>
       </c>
       <c r="J221" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K221" t="n">
         <v>0</v>
@@ -9920,19 +9920,19 @@
         <v>0</v>
       </c>
       <c r="M221" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="N221" t="n">
-        <v>2694.8231444759</v>
+        <v>2694.8231379962</v>
       </c>
       <c r="O221" t="n">
-        <v>468899.2271388066</v>
+        <v>466204.4028733426</v>
       </c>
       <c r="P221" t="n">
         <v>4900</v>
       </c>
       <c r="Q221" t="n">
-        <v>852600</v>
+        <v>847700</v>
       </c>
     </row>
     <row r="222">
@@ -10003,13 +10003,13 @@
         </is>
       </c>
       <c r="J223" t="n">
-        <v>1752</v>
+        <v>1692</v>
       </c>
       <c r="K223" t="n">
         <v>0</v>
       </c>
       <c r="L223" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="M223" t="n">
         <v>1692</v>
@@ -10098,7 +10098,7 @@
         </is>
       </c>
       <c r="J225" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="K225" t="n">
         <v>0</v>
@@ -10107,19 +10107,19 @@
         <v>0</v>
       </c>
       <c r="M225" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="N225" t="n">
         <v>8796</v>
       </c>
       <c r="O225" t="n">
-        <v>439800</v>
+        <v>422208</v>
       </c>
       <c r="P225" t="n">
         <v>14900</v>
       </c>
       <c r="Q225" t="n">
-        <v>745000</v>
+        <v>715200</v>
       </c>
     </row>
     <row r="226">
@@ -10364,28 +10364,28 @@
         </is>
       </c>
       <c r="J231" t="n">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="K231" t="n">
         <v>0</v>
       </c>
       <c r="L231" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M231" t="n">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="N231" t="n">
         <v>2612.77</v>
       </c>
       <c r="O231" t="n">
-        <v>334434.56</v>
+        <v>316145.17</v>
       </c>
       <c r="P231" t="n">
         <v>4900</v>
       </c>
       <c r="Q231" t="n">
-        <v>627200</v>
+        <v>592900</v>
       </c>
     </row>
     <row r="232">
@@ -10514,10 +10514,10 @@
         <v>12</v>
       </c>
       <c r="N234" t="n">
-        <v>4890.9300497203</v>
+        <v>4890.9300498132</v>
       </c>
       <c r="O234" t="n">
-        <v>58691.1605966436</v>
+        <v>58691.1605977584</v>
       </c>
       <c r="P234" t="n">
         <v>8200</v>
@@ -10692,7 +10692,7 @@
         </is>
       </c>
       <c r="J238" t="n">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="K238" t="n">
         <v>0</v>
@@ -10701,19 +10701,19 @@
         <v>0</v>
       </c>
       <c r="M238" t="n">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="N238" t="n">
         <v>1203.38</v>
       </c>
       <c r="O238" t="n">
-        <v>8423.66</v>
+        <v>57762.24000000001</v>
       </c>
       <c r="P238" t="n">
         <v>1900</v>
       </c>
       <c r="Q238" t="n">
-        <v>13300</v>
+        <v>91200</v>
       </c>
     </row>
     <row r="239">
@@ -10883,10 +10883,10 @@
         <v>81</v>
       </c>
       <c r="N242" t="n">
-        <v>2267.0481239389</v>
+        <v>2267.0481103035</v>
       </c>
       <c r="O242" t="n">
-        <v>183630.8980390509</v>
+        <v>183630.8969345835</v>
       </c>
       <c r="P242" t="n">
         <v>3900</v>
@@ -11188,7 +11188,7 @@
         </is>
       </c>
       <c r="J249" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K249" t="n">
         <v>0</v>
@@ -11197,19 +11197,19 @@
         <v>0</v>
       </c>
       <c r="M249" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N249" t="n">
         <v>10716.34</v>
       </c>
       <c r="O249" t="n">
-        <v>85730.72</v>
+        <v>53581.7</v>
       </c>
       <c r="P249" t="n">
         <v>39000</v>
       </c>
       <c r="Q249" t="n">
-        <v>312000</v>
+        <v>195000</v>
       </c>
     </row>
     <row r="250">
@@ -11278,7 +11278,7 @@
         </is>
       </c>
       <c r="J251" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K251" t="n">
         <v>0</v>
@@ -11287,19 +11287,19 @@
         <v>0</v>
       </c>
       <c r="M251" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N251" t="n">
-        <v>3594.2535742972</v>
+        <v>3594.2535483871</v>
       </c>
       <c r="O251" t="n">
-        <v>82667.83220883559</v>
+        <v>75479.3245161291</v>
       </c>
       <c r="P251" t="n">
         <v>6500</v>
       </c>
       <c r="Q251" t="n">
-        <v>149500</v>
+        <v>136500</v>
       </c>
     </row>
     <row r="252">
@@ -11368,7 +11368,7 @@
         </is>
       </c>
       <c r="J253" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K253" t="n">
         <v>0</v>
@@ -11377,19 +11377,19 @@
         <v>0</v>
       </c>
       <c r="M253" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N253" t="n">
         <v>489.88</v>
       </c>
       <c r="O253" t="n">
-        <v>489.88</v>
+        <v>1469.64</v>
       </c>
       <c r="P253" t="n">
         <v>700</v>
       </c>
       <c r="Q253" t="n">
-        <v>700</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="254">
@@ -11415,22 +11415,22 @@
         <v>0</v>
       </c>
       <c r="L254" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M254" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N254" t="n">
         <v>2917.02</v>
       </c>
       <c r="O254" t="n">
-        <v>5834.04</v>
+        <v>0</v>
       </c>
       <c r="P254" t="n">
         <v>5200</v>
       </c>
       <c r="Q254" t="n">
-        <v>10400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="255">
@@ -11491,28 +11491,28 @@
         </is>
       </c>
       <c r="J256" t="n">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="K256" t="n">
         <v>0</v>
       </c>
       <c r="L256" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M256" t="n">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="N256" t="n">
-        <v>3240.8500422833</v>
+        <v>3240.8500449438</v>
       </c>
       <c r="O256" t="n">
-        <v>395383.7051585626</v>
+        <v>369456.9051235932</v>
       </c>
       <c r="P256" t="n">
         <v>5200</v>
       </c>
       <c r="Q256" t="n">
-        <v>634400</v>
+        <v>592800</v>
       </c>
     </row>
     <row r="257">
@@ -11687,10 +11687,10 @@
         <v>11</v>
       </c>
       <c r="N260" t="n">
-        <v>14822.378834244</v>
+        <v>14822.378831406</v>
       </c>
       <c r="O260" t="n">
-        <v>163046.167176684</v>
+        <v>163046.167145466</v>
       </c>
       <c r="P260" t="n">
         <v>24900</v>
@@ -11768,7 +11768,7 @@
         </is>
       </c>
       <c r="J262" t="n">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="K262" t="n">
         <v>0</v>
@@ -11777,19 +11777,19 @@
         <v>0</v>
       </c>
       <c r="M262" t="n">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="N262" t="n">
         <v>2090.85</v>
       </c>
       <c r="O262" t="n">
-        <v>648163.5</v>
+        <v>643981.7999999999</v>
       </c>
       <c r="P262" t="n">
         <v>2900</v>
       </c>
       <c r="Q262" t="n">
-        <v>899000</v>
+        <v>893200</v>
       </c>
     </row>
     <row r="263">
@@ -11987,7 +11987,7 @@
         </is>
       </c>
       <c r="J267" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="K267" t="n">
         <v>0</v>
@@ -11996,19 +11996,19 @@
         <v>0</v>
       </c>
       <c r="M267" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="N267" t="n">
         <v>2769.98</v>
       </c>
       <c r="O267" t="n">
-        <v>155118.88</v>
+        <v>144038.96</v>
       </c>
       <c r="P267" t="n">
         <v>3500</v>
       </c>
       <c r="Q267" t="n">
-        <v>196000</v>
+        <v>182000</v>
       </c>
     </row>
     <row r="268">
@@ -12259,7 +12259,7 @@
         </is>
       </c>
       <c r="J273" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K273" t="n">
         <v>0</v>
@@ -12268,19 +12268,19 @@
         <v>0</v>
       </c>
       <c r="M273" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N273" t="n">
-        <v>12267.647571429</v>
+        <v>12267.647205882</v>
       </c>
       <c r="O273" t="n">
-        <v>110408.828142861</v>
+        <v>85873.53044117399</v>
       </c>
       <c r="P273" t="n">
         <v>19900</v>
       </c>
       <c r="Q273" t="n">
-        <v>179100</v>
+        <v>139300</v>
       </c>
     </row>
     <row r="274">
@@ -12488,7 +12488,7 @@
         </is>
       </c>
       <c r="J278" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K278" t="n">
         <v>0</v>
@@ -12497,19 +12497,19 @@
         <v>0</v>
       </c>
       <c r="M278" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="N278" t="n">
         <v>1441.01</v>
       </c>
       <c r="O278" t="n">
-        <v>172921.2</v>
+        <v>170039.18</v>
       </c>
       <c r="P278" t="n">
         <v>2100</v>
       </c>
       <c r="Q278" t="n">
-        <v>252000</v>
+        <v>247800</v>
       </c>
     </row>
     <row r="279">
@@ -12641,10 +12641,10 @@
         <v>6</v>
       </c>
       <c r="N281" t="n">
-        <v>4242.5422384428</v>
+        <v>4242.5422439024</v>
       </c>
       <c r="O281" t="n">
-        <v>25455.2534306568</v>
+        <v>25455.2534634144</v>
       </c>
       <c r="P281" t="n">
         <v>5900</v>
@@ -12731,10 +12731,10 @@
         <v>7</v>
       </c>
       <c r="N283" t="n">
-        <v>3041.6600137646</v>
+        <v>3041.6600137931</v>
       </c>
       <c r="O283" t="n">
-        <v>21291.6200963522</v>
+        <v>21291.6200965517</v>
       </c>
       <c r="P283" t="n">
         <v>5500</v>
@@ -12847,7 +12847,7 @@
         </is>
       </c>
       <c r="J286" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="K286" t="n">
         <v>0</v>
@@ -12856,19 +12856,19 @@
         <v>0</v>
       </c>
       <c r="M286" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="N286" t="n">
-        <v>4374.7145640659</v>
+        <v>4372.2107930714</v>
       </c>
       <c r="O286" t="n">
-        <v>13124.1436921977</v>
+        <v>48094.3187237854</v>
       </c>
       <c r="P286" t="n">
         <v>7500</v>
       </c>
       <c r="Q286" t="n">
-        <v>22500</v>
+        <v>82500</v>
       </c>
     </row>
     <row r="287">
@@ -12937,7 +12937,7 @@
         </is>
       </c>
       <c r="J288" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K288" t="n">
         <v>0</v>
@@ -12946,19 +12946,19 @@
         <v>0</v>
       </c>
       <c r="M288" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="N288" t="n">
         <v>6441.03</v>
       </c>
       <c r="O288" t="n">
-        <v>380020.77</v>
+        <v>418666.95</v>
       </c>
       <c r="P288" t="n">
         <v>10500</v>
       </c>
       <c r="Q288" t="n">
-        <v>619500</v>
+        <v>682500</v>
       </c>
     </row>
     <row r="289">
@@ -12983,7 +12983,7 @@
         </is>
       </c>
       <c r="J289" t="n">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="K289" t="n">
         <v>0</v>
@@ -12992,19 +12992,19 @@
         <v>0</v>
       </c>
       <c r="M289" t="n">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="N289" t="n">
-        <v>1592.5657792208</v>
+        <v>1592.565713108</v>
       </c>
       <c r="O289" t="n">
-        <v>437955.58928572</v>
+        <v>426807.611112944</v>
       </c>
       <c r="P289" t="n">
         <v>3900</v>
       </c>
       <c r="Q289" t="n">
-        <v>1072500</v>
+        <v>1045200</v>
       </c>
     </row>
     <row r="290">
@@ -13024,7 +13024,7 @@
         </is>
       </c>
       <c r="J290" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="K290" t="n">
         <v>0</v>
@@ -13033,19 +13033,19 @@
         <v>0</v>
       </c>
       <c r="M290" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="N290" t="n">
         <v>4513.76</v>
       </c>
       <c r="O290" t="n">
-        <v>311449.44</v>
+        <v>297908.16</v>
       </c>
       <c r="P290" t="n">
         <v>8900</v>
       </c>
       <c r="Q290" t="n">
-        <v>614100</v>
+        <v>587400</v>
       </c>
     </row>
     <row r="291">
@@ -13201,7 +13201,7 @@
         </is>
       </c>
       <c r="J294" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K294" t="n">
         <v>0</v>
@@ -13210,19 +13210,19 @@
         <v>0</v>
       </c>
       <c r="M294" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="N294" t="n">
         <v>6446.04</v>
       </c>
       <c r="O294" t="n">
-        <v>135366.84</v>
+        <v>116028.72</v>
       </c>
       <c r="P294" t="n">
         <v>5300</v>
       </c>
       <c r="Q294" t="n">
-        <v>111300</v>
+        <v>95400</v>
       </c>
     </row>
     <row r="295">
@@ -13476,7 +13476,7 @@
         </is>
       </c>
       <c r="J300" t="n">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="K300" t="n">
         <v>0</v>
@@ -13485,19 +13485,19 @@
         <v>0</v>
       </c>
       <c r="M300" t="n">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="N300" t="n">
         <v>1770.37</v>
       </c>
       <c r="O300" t="n">
-        <v>203592.55</v>
+        <v>192970.33</v>
       </c>
       <c r="P300" t="n">
         <v>3900</v>
       </c>
       <c r="Q300" t="n">
-        <v>448500</v>
+        <v>425100</v>
       </c>
     </row>
     <row r="301">
@@ -13529,10 +13529,10 @@
         <v>50</v>
       </c>
       <c r="N301" t="n">
-        <v>1532.6290265229</v>
+        <v>1532.6290255288</v>
       </c>
       <c r="O301" t="n">
-        <v>76631.451326145</v>
+        <v>76631.45127644</v>
       </c>
       <c r="P301" t="n">
         <v>1200</v>
@@ -13833,22 +13833,22 @@
         <v>0</v>
       </c>
       <c r="L308" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M308" t="n">
-        <v>201</v>
+        <v>187</v>
       </c>
       <c r="N308" t="n">
         <v>1387.55</v>
       </c>
       <c r="O308" t="n">
-        <v>278897.55</v>
+        <v>259471.85</v>
       </c>
       <c r="P308" t="n">
         <v>2300</v>
       </c>
       <c r="Q308" t="n">
-        <v>462300</v>
+        <v>430100</v>
       </c>
     </row>
     <row r="309">
@@ -14574,7 +14574,7 @@
         </is>
       </c>
       <c r="J324" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K324" t="n">
         <v>0</v>
@@ -14583,19 +14583,19 @@
         <v>0</v>
       </c>
       <c r="M324" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N324" t="n">
         <v>11921.4</v>
       </c>
       <c r="O324" t="n">
-        <v>166899.6</v>
+        <v>143056.8</v>
       </c>
       <c r="P324" t="n">
         <v>19900</v>
       </c>
       <c r="Q324" t="n">
-        <v>278600</v>
+        <v>238800</v>
       </c>
     </row>
     <row r="325">
@@ -14990,22 +14990,22 @@
         <v>0</v>
       </c>
       <c r="L333" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M333" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N333" t="n">
         <v>3751</v>
       </c>
       <c r="O333" t="n">
-        <v>476377</v>
+        <v>472626</v>
       </c>
       <c r="P333" t="n">
         <v>6400</v>
       </c>
       <c r="Q333" t="n">
-        <v>812800</v>
+        <v>806400</v>
       </c>
     </row>
     <row r="334">
@@ -15183,10 +15183,10 @@
         <v>146</v>
       </c>
       <c r="N337" t="n">
-        <v>1630.9239968815</v>
+        <v>1630.9240698598</v>
       </c>
       <c r="O337" t="n">
-        <v>238114.903544699</v>
+        <v>238114.9141995308</v>
       </c>
       <c r="P337" t="n">
         <v>2500</v>
@@ -15263,7 +15263,7 @@
         </is>
       </c>
       <c r="J339" t="n">
-        <v>11</v>
+        <v>80</v>
       </c>
       <c r="K339" t="n">
         <v>0</v>
@@ -15272,19 +15272,19 @@
         <v>0</v>
       </c>
       <c r="M339" t="n">
-        <v>11</v>
+        <v>80</v>
       </c>
       <c r="N339" t="n">
-        <v>1830.8887033195</v>
+        <v>1690.5903203883</v>
       </c>
       <c r="O339" t="n">
-        <v>20139.7757365145</v>
+        <v>135247.225631064</v>
       </c>
       <c r="P339" t="n">
         <v>2900</v>
       </c>
       <c r="Q339" t="n">
-        <v>31900</v>
+        <v>232000</v>
       </c>
     </row>
     <row r="340">
@@ -15309,7 +15309,7 @@
         </is>
       </c>
       <c r="J340" t="n">
-        <v>292</v>
+        <v>623</v>
       </c>
       <c r="K340" t="n">
         <v>0</v>
@@ -15318,19 +15318,19 @@
         <v>0</v>
       </c>
       <c r="M340" t="n">
-        <v>292</v>
+        <v>623</v>
       </c>
       <c r="N340" t="n">
-        <v>1550.1942738685</v>
+        <v>1550.1941645158</v>
       </c>
       <c r="O340" t="n">
-        <v>452656.727969602</v>
+        <v>965770.9644933434</v>
       </c>
       <c r="P340" t="n">
         <v>2500</v>
       </c>
       <c r="Q340" t="n">
-        <v>730000</v>
+        <v>1557500</v>
       </c>
     </row>
     <row r="341">
@@ -15367,10 +15367,10 @@
         <v>1</v>
       </c>
       <c r="N341" t="n">
-        <v>1579.3881518152</v>
+        <v>1579.3874912892</v>
       </c>
       <c r="O341" t="n">
-        <v>1579.3881518152</v>
+        <v>1579.3874912892</v>
       </c>
       <c r="P341" t="n">
         <v>2900</v>
@@ -15401,7 +15401,7 @@
         </is>
       </c>
       <c r="J342" t="n">
-        <v>172</v>
+        <v>409</v>
       </c>
       <c r="K342" t="n">
         <v>0</v>
@@ -15410,19 +15410,19 @@
         <v>0</v>
       </c>
       <c r="M342" t="n">
-        <v>172</v>
+        <v>409</v>
       </c>
       <c r="N342" t="n">
-        <v>2549.7269035153</v>
+        <v>2403.5147075539</v>
       </c>
       <c r="O342" t="n">
-        <v>438553.0274046316</v>
+        <v>983037.515389545</v>
       </c>
       <c r="P342" t="n">
         <v>3500</v>
       </c>
       <c r="Q342" t="n">
-        <v>602000</v>
+        <v>1431500</v>
       </c>
     </row>
     <row r="343">
@@ -15459,10 +15459,10 @@
         <v>5</v>
       </c>
       <c r="N343" t="n">
-        <v>2521.4820175439</v>
+        <v>2521.4791818182</v>
       </c>
       <c r="O343" t="n">
-        <v>12607.4100877195</v>
+        <v>12607.395909091</v>
       </c>
       <c r="P343" t="n">
         <v>3900</v>
@@ -16779,13 +16779,13 @@
         </is>
       </c>
       <c r="J373" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K373" t="n">
         <v>0</v>
       </c>
       <c r="L373" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M373" t="n">
         <v>5</v>
@@ -17816,13 +17816,13 @@
         </is>
       </c>
       <c r="J396" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="K396" t="n">
         <v>0</v>
       </c>
       <c r="L396" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M396" t="n">
         <v>32</v>
@@ -17872,10 +17872,10 @@
         <v>25</v>
       </c>
       <c r="N397" t="n">
-        <v>4196.8725389755</v>
+        <v>4196.8725410978</v>
       </c>
       <c r="O397" t="n">
-        <v>104921.8134743875</v>
+        <v>104921.813527445</v>
       </c>
       <c r="P397" t="n">
         <v>5900</v>
@@ -18234,7 +18234,7 @@
         </is>
       </c>
       <c r="J406" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="K406" t="n">
         <v>0</v>
@@ -18243,19 +18243,19 @@
         <v>0</v>
       </c>
       <c r="M406" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="N406" t="n">
         <v>1958.73</v>
       </c>
       <c r="O406" t="n">
-        <v>72473.00999999999</v>
+        <v>66596.82000000001</v>
       </c>
       <c r="P406" t="n">
         <v>3400</v>
       </c>
       <c r="Q406" t="n">
-        <v>125800</v>
+        <v>115600</v>
       </c>
     </row>
     <row r="407">
@@ -18743,10 +18743,10 @@
         <v>521</v>
       </c>
       <c r="N418" t="n">
-        <v>880.32965533864</v>
+        <v>880.32968334542</v>
       </c>
       <c r="O418" t="n">
-        <v>458651.7504314315</v>
+        <v>458651.7650229638</v>
       </c>
       <c r="P418" t="n">
         <v>1200</v>
@@ -19524,10 +19524,10 @@
         <v>16</v>
       </c>
       <c r="N436" t="n">
-        <v>4285.1959694477</v>
+        <v>4285.1960260973</v>
       </c>
       <c r="O436" t="n">
-        <v>68563.1355111632</v>
+        <v>68563.1364175568</v>
       </c>
       <c r="P436" t="n">
         <v>6900</v>
@@ -19894,7 +19894,7 @@
         </is>
       </c>
       <c r="J445" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K445" t="n">
         <v>0</v>
@@ -19903,19 +19903,19 @@
         <v>0</v>
       </c>
       <c r="M445" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="N445" t="n">
         <v>1430.38</v>
       </c>
       <c r="O445" t="n">
-        <v>27177.22</v>
+        <v>22886.08</v>
       </c>
       <c r="P445" t="n">
         <v>4000</v>
       </c>
       <c r="Q445" t="n">
-        <v>76000</v>
+        <v>64000</v>
       </c>
     </row>
     <row r="446">
@@ -20126,10 +20126,10 @@
         <v>12</v>
       </c>
       <c r="N450" t="n">
-        <v>13513.64328</v>
+        <v>13513.643306452</v>
       </c>
       <c r="O450" t="n">
-        <v>162163.71936</v>
+        <v>162163.719677424</v>
       </c>
       <c r="P450" t="n">
         <v>21900</v>
@@ -20805,7 +20805,7 @@
         </is>
       </c>
       <c r="J466" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K466" t="n">
         <v>0</v>
@@ -20814,19 +20814,19 @@
         <v>0</v>
       </c>
       <c r="M466" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N466" t="n">
         <v>16974.69</v>
       </c>
       <c r="O466" t="n">
-        <v>356468.49</v>
+        <v>322519.11</v>
       </c>
       <c r="P466" t="n">
         <v>26900</v>
       </c>
       <c r="Q466" t="n">
-        <v>564900</v>
+        <v>511100</v>
       </c>
     </row>
     <row r="467">
@@ -21037,10 +21037,10 @@
         <v>80</v>
       </c>
       <c r="N471" t="n">
-        <v>1561.0030188679</v>
+        <v>1561.003125</v>
       </c>
       <c r="O471" t="n">
-        <v>124880.241509432</v>
+        <v>124880.25</v>
       </c>
       <c r="P471" t="n">
         <v>2900</v>
@@ -21681,7 +21681,7 @@
         </is>
       </c>
       <c r="J486" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K486" t="n">
         <v>0</v>
@@ -21690,19 +21690,19 @@
         <v>0</v>
       </c>
       <c r="M486" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="N486" t="n">
         <v>9627.34</v>
       </c>
       <c r="O486" t="n">
-        <v>19254.68</v>
+        <v>86646.06</v>
       </c>
       <c r="P486" t="n">
         <v>15900</v>
       </c>
       <c r="Q486" t="n">
-        <v>31800</v>
+        <v>143100</v>
       </c>
     </row>
     <row r="487">
@@ -21730,28 +21730,28 @@
         </is>
       </c>
       <c r="J487" t="n">
-        <v>300</v>
+        <v>282</v>
       </c>
       <c r="K487" t="n">
         <v>0</v>
       </c>
       <c r="L487" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M487" t="n">
-        <v>300</v>
+        <v>269</v>
       </c>
       <c r="N487" t="n">
         <v>1200</v>
       </c>
       <c r="O487" t="n">
-        <v>360000</v>
+        <v>322800</v>
       </c>
       <c r="P487" t="n">
         <v>1500</v>
       </c>
       <c r="Q487" t="n">
-        <v>450000</v>
+        <v>403500</v>
       </c>
     </row>
     <row r="488">
@@ -22089,10 +22089,10 @@
         <v>133</v>
       </c>
       <c r="N495" t="n">
-        <v>548.1471442590801</v>
+        <v>548.14712450593</v>
       </c>
       <c r="O495" t="n">
-        <v>72903.57018645764</v>
+        <v>72903.5675592887</v>
       </c>
       <c r="P495" t="n">
         <v>2000</v>
@@ -22484,7 +22484,7 @@
         </is>
       </c>
       <c r="J504" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K504" t="n">
         <v>0</v>
@@ -22493,19 +22493,19 @@
         <v>0</v>
       </c>
       <c r="M504" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N504" t="n">
         <v>4720</v>
       </c>
       <c r="O504" t="n">
-        <v>108560</v>
+        <v>99120</v>
       </c>
       <c r="P504" t="n">
         <v>5900</v>
       </c>
       <c r="Q504" t="n">
-        <v>135700</v>
+        <v>123900</v>
       </c>
     </row>
     <row r="505">
@@ -24310,28 +24310,28 @@
         </is>
       </c>
       <c r="J544" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="K544" t="n">
         <v>0</v>
       </c>
       <c r="L544" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M544" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="N544" t="n">
-        <v>1664.3474804688</v>
+        <v>1664.3470318725</v>
       </c>
       <c r="O544" t="n">
-        <v>113175.6286718784</v>
+        <v>108182.5570717125</v>
       </c>
       <c r="P544" t="n">
         <v>2900</v>
       </c>
       <c r="Q544" t="n">
-        <v>197200</v>
+        <v>188500</v>
       </c>
     </row>
     <row r="545">
@@ -25104,7 +25104,7 @@
         </is>
       </c>
       <c r="J561" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K561" t="n">
         <v>0</v>
@@ -25113,19 +25113,19 @@
         <v>0</v>
       </c>
       <c r="M561" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="N561" t="n">
-        <v>1778.4727234441</v>
+        <v>1778.4727448514</v>
       </c>
       <c r="O561" t="n">
-        <v>110265.3088535342</v>
+        <v>106708.364691084</v>
       </c>
       <c r="P561" t="n">
         <v>4900</v>
       </c>
       <c r="Q561" t="n">
-        <v>303800</v>
+        <v>294000</v>
       </c>
     </row>
     <row r="562">
@@ -25613,7 +25613,7 @@
         </is>
       </c>
       <c r="J572" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="K572" t="n">
         <v>0</v>
@@ -25622,19 +25622,19 @@
         <v>0</v>
       </c>
       <c r="M572" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="N572" t="n">
         <v>5148</v>
       </c>
       <c r="O572" t="n">
-        <v>267696</v>
+        <v>247104</v>
       </c>
       <c r="P572" t="n">
         <v>8600</v>
       </c>
       <c r="Q572" t="n">
-        <v>447200</v>
+        <v>412800</v>
       </c>
     </row>
     <row r="573">
@@ -26214,7 +26214,7 @@
         </is>
       </c>
       <c r="J585" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="K585" t="n">
         <v>0</v>
@@ -26223,19 +26223,19 @@
         <v>0</v>
       </c>
       <c r="M585" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="N585" t="n">
         <v>1860</v>
       </c>
       <c r="O585" t="n">
-        <v>215760</v>
+        <v>210180</v>
       </c>
       <c r="P585" t="n">
         <v>3000</v>
       </c>
       <c r="Q585" t="n">
-        <v>348000</v>
+        <v>339000</v>
       </c>
     </row>
     <row r="586">
@@ -27192,7 +27192,7 @@
         </is>
       </c>
       <c r="J606" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K606" t="n">
         <v>0</v>
@@ -27201,19 +27201,19 @@
         <v>0</v>
       </c>
       <c r="M606" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N606" t="n">
         <v>12709</v>
       </c>
       <c r="O606" t="n">
-        <v>88963</v>
+        <v>76254</v>
       </c>
       <c r="P606" t="n">
         <v>20500</v>
       </c>
       <c r="Q606" t="n">
-        <v>143500</v>
+        <v>123000</v>
       </c>
     </row>
     <row r="607">
@@ -27284,7 +27284,7 @@
         </is>
       </c>
       <c r="J608" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="K608" t="n">
         <v>0</v>
@@ -27293,19 +27293,19 @@
         <v>0</v>
       </c>
       <c r="M608" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="N608" t="n">
         <v>3424</v>
       </c>
       <c r="O608" t="n">
-        <v>102720</v>
+        <v>116416</v>
       </c>
       <c r="P608" t="n">
         <v>5900</v>
       </c>
       <c r="Q608" t="n">
-        <v>177000</v>
+        <v>200600</v>
       </c>
     </row>
     <row r="609">
@@ -27561,7 +27561,7 @@
         </is>
       </c>
       <c r="J614" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K614" t="n">
         <v>0</v>
@@ -27570,19 +27570,19 @@
         <v>0</v>
       </c>
       <c r="M614" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N614" t="n">
         <v>8858.16</v>
       </c>
       <c r="O614" t="n">
-        <v>177163.2</v>
+        <v>203737.68</v>
       </c>
       <c r="P614" t="n">
         <v>15500</v>
       </c>
       <c r="Q614" t="n">
-        <v>310000</v>
+        <v>356500</v>
       </c>
     </row>
     <row r="615">
@@ -27745,7 +27745,7 @@
         </is>
       </c>
       <c r="J618" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="K618" t="n">
         <v>0</v>
@@ -27754,19 +27754,19 @@
         <v>0</v>
       </c>
       <c r="M618" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="N618" t="n">
         <v>17644.653166667</v>
       </c>
       <c r="O618" t="n">
-        <v>35289.306333334</v>
+        <v>194091.184833337</v>
       </c>
       <c r="P618" t="n">
         <v>28200</v>
       </c>
       <c r="Q618" t="n">
-        <v>56400</v>
+        <v>310200</v>
       </c>
     </row>
     <row r="619">
@@ -28422,12 +28422,12 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>C4475</t>
+          <t>C4468</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>LANZADORAS BIOGEL MODELOS STD C4475</t>
+          <t>MAQUINA PARA HACER PULSERAS C4468</t>
         </is>
       </c>
       <c r="E633" t="inlineStr">
@@ -28441,7 +28441,7 @@
         </is>
       </c>
       <c r="J633" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K633" t="n">
         <v>0</v>
@@ -28450,30 +28450,30 @@
         <v>0</v>
       </c>
       <c r="M633" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N633" t="n">
-        <v>32332</v>
+        <v>9384</v>
       </c>
       <c r="O633" t="n">
-        <v>161660</v>
+        <v>93840</v>
       </c>
       <c r="P633" t="n">
-        <v>55900</v>
+        <v>15900</v>
       </c>
       <c r="Q633" t="n">
-        <v>279500</v>
+        <v>159000</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>C4478</t>
+          <t>C4475</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>FICHAS DE ARMAR FOOTBALL STD C4478</t>
+          <t>LANZADORAS BIOGEL MODELOS STD C4475</t>
         </is>
       </c>
       <c r="E634" t="inlineStr">
@@ -28487,7 +28487,7 @@
         </is>
       </c>
       <c r="J634" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K634" t="n">
         <v>0</v>
@@ -28496,35 +28496,35 @@
         <v>0</v>
       </c>
       <c r="M634" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N634" t="n">
-        <v>7732</v>
+        <v>32332</v>
       </c>
       <c r="O634" t="n">
-        <v>7732</v>
+        <v>161660</v>
       </c>
       <c r="P634" t="n">
-        <v>12700</v>
+        <v>55900</v>
       </c>
       <c r="Q634" t="n">
-        <v>12700</v>
+        <v>279500</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>C4481</t>
+          <t>C4478</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>SCOOTER METALICA C4481</t>
+          <t>FICHAS DE ARMAR FOOTBALL STD C4478</t>
         </is>
       </c>
       <c r="E635" t="inlineStr">
         <is>
-          <t>SCOOTER</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I635" t="inlineStr">
@@ -28533,7 +28533,7 @@
         </is>
       </c>
       <c r="J635" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K635" t="n">
         <v>0</v>
@@ -28542,35 +28542,35 @@
         <v>0</v>
       </c>
       <c r="M635" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N635" t="n">
-        <v>29105.23</v>
+        <v>7732</v>
       </c>
       <c r="O635" t="n">
-        <v>58210.46</v>
+        <v>7732</v>
       </c>
       <c r="P635" t="n">
-        <v>39900</v>
+        <v>12700</v>
       </c>
       <c r="Q635" t="n">
-        <v>79800</v>
+        <v>12700</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>C4483</t>
+          <t>C4481</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>LANZADORA BLEY BLEY C4483</t>
+          <t>SCOOTER METALICA C4481</t>
         </is>
       </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>SCOOTER</t>
         </is>
       </c>
       <c r="I636" t="inlineStr">
@@ -28579,7 +28579,7 @@
         </is>
       </c>
       <c r="J636" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="K636" t="n">
         <v>0</v>
@@ -28588,30 +28588,30 @@
         <v>0</v>
       </c>
       <c r="M636" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="N636" t="n">
-        <v>50153.86</v>
+        <v>29105.23</v>
       </c>
       <c r="O636" t="n">
-        <v>501538.6</v>
+        <v>58210.46</v>
       </c>
       <c r="P636" t="n">
-        <v>11500</v>
+        <v>39900</v>
       </c>
       <c r="Q636" t="n">
-        <v>115000</v>
+        <v>79800</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>C4488</t>
+          <t>C4483</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>RANITA LUZ Y SONIDO C4488</t>
+          <t>LANZADORA BLEY BLEY C4483</t>
         </is>
       </c>
       <c r="E637" t="inlineStr">
@@ -28625,7 +28625,7 @@
         </is>
       </c>
       <c r="J637" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K637" t="n">
         <v>0</v>
@@ -28634,30 +28634,30 @@
         <v>0</v>
       </c>
       <c r="M637" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N637" t="n">
-        <v>9003</v>
+        <v>50153.86</v>
       </c>
       <c r="O637" t="n">
-        <v>72024</v>
+        <v>501538.6</v>
       </c>
       <c r="P637" t="n">
-        <v>14900</v>
+        <v>11500</v>
       </c>
       <c r="Q637" t="n">
-        <v>119200</v>
+        <v>115000</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>C4489</t>
+          <t>C4488</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
         <is>
-          <t>PATO LUZ Y SONIDO C4489</t>
+          <t>RANITA LUZ Y SONIDO C4488</t>
         </is>
       </c>
       <c r="E638" t="inlineStr">
@@ -28671,7 +28671,7 @@
         </is>
       </c>
       <c r="J638" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K638" t="n">
         <v>0</v>
@@ -28680,30 +28680,30 @@
         <v>0</v>
       </c>
       <c r="M638" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="N638" t="n">
-        <v>9178</v>
+        <v>9003</v>
       </c>
       <c r="O638" t="n">
-        <v>36712</v>
+        <v>72024</v>
       </c>
       <c r="P638" t="n">
         <v>14900</v>
       </c>
       <c r="Q638" t="n">
-        <v>59600</v>
+        <v>119200</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>C4490</t>
+          <t>C4489</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
         <is>
-          <t>TELEFONO DIDACTICO DINO/ UNICORNIO C4490</t>
+          <t>PATO LUZ Y SONIDO C4489</t>
         </is>
       </c>
       <c r="E639" t="inlineStr">
@@ -28717,7 +28717,7 @@
         </is>
       </c>
       <c r="J639" t="n">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="K639" t="n">
         <v>0</v>
@@ -28726,30 +28726,30 @@
         <v>0</v>
       </c>
       <c r="M639" t="n">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="N639" t="n">
-        <v>4544</v>
+        <v>9178</v>
       </c>
       <c r="O639" t="n">
-        <v>272640</v>
+        <v>36712</v>
       </c>
       <c r="P639" t="n">
-        <v>7900</v>
+        <v>14900</v>
       </c>
       <c r="Q639" t="n">
-        <v>474000</v>
+        <v>59600</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>C4492</t>
+          <t>C4490</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>LANZADORA AGUA  PALA C4492</t>
+          <t>TELEFONO DIDACTICO DINO/ UNICORNIO C4490</t>
         </is>
       </c>
       <c r="E640" t="inlineStr">
@@ -28763,7 +28763,7 @@
         </is>
       </c>
       <c r="J640" t="n">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="K640" t="n">
         <v>0</v>
@@ -28772,30 +28772,30 @@
         <v>0</v>
       </c>
       <c r="M640" t="n">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="N640" t="n">
-        <v>3196</v>
+        <v>4544</v>
       </c>
       <c r="O640" t="n">
-        <v>131036</v>
+        <v>272640</v>
       </c>
       <c r="P640" t="n">
-        <v>6400</v>
+        <v>7900</v>
       </c>
       <c r="Q640" t="n">
-        <v>262400</v>
+        <v>474000</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>C4493</t>
+          <t>C4492</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>ARCO STD NIÑO Y NIÑA LASER C4493</t>
+          <t>LANZADORA AGUA  PALA C4492</t>
         </is>
       </c>
       <c r="E641" t="inlineStr">
@@ -28809,7 +28809,7 @@
         </is>
       </c>
       <c r="J641" t="n">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="K641" t="n">
         <v>0</v>
@@ -28818,30 +28818,30 @@
         <v>0</v>
       </c>
       <c r="M641" t="n">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="N641" t="n">
-        <v>13922</v>
+        <v>3196</v>
       </c>
       <c r="O641" t="n">
-        <v>180986</v>
+        <v>131036</v>
       </c>
       <c r="P641" t="n">
-        <v>22900</v>
+        <v>6400</v>
       </c>
       <c r="Q641" t="n">
-        <v>297700</v>
+        <v>262400</v>
       </c>
     </row>
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>C4494</t>
+          <t>C4493</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>JUEGO PLASTILINA PULPO C4494</t>
+          <t>ARCO STD NIÑO Y NIÑA LASER C4493</t>
         </is>
       </c>
       <c r="E642" t="inlineStr">
@@ -28855,7 +28855,7 @@
         </is>
       </c>
       <c r="J642" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K642" t="n">
         <v>0</v>
@@ -28864,30 +28864,30 @@
         <v>0</v>
       </c>
       <c r="M642" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N642" t="n">
-        <v>16285.911125</v>
+        <v>13922</v>
       </c>
       <c r="O642" t="n">
-        <v>179145.022375</v>
+        <v>180986</v>
       </c>
       <c r="P642" t="n">
-        <v>29900</v>
+        <v>22900</v>
       </c>
       <c r="Q642" t="n">
-        <v>328900</v>
+        <v>297700</v>
       </c>
     </row>
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>C4495</t>
+          <t>C4494</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
         <is>
-          <t>JUEGO PLASTILINA PERRO C4495</t>
+          <t>JUEGO PLASTILINA PULPO C4494</t>
         </is>
       </c>
       <c r="E643" t="inlineStr">
@@ -28901,7 +28901,7 @@
         </is>
       </c>
       <c r="J643" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K643" t="n">
         <v>0</v>
@@ -28910,30 +28910,30 @@
         <v>0</v>
       </c>
       <c r="M643" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="N643" t="n">
-        <v>17981</v>
+        <v>16285.911125</v>
       </c>
       <c r="O643" t="n">
-        <v>251734</v>
+        <v>179145.022375</v>
       </c>
       <c r="P643" t="n">
         <v>29900</v>
       </c>
       <c r="Q643" t="n">
-        <v>418600</v>
+        <v>328900</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>C4496</t>
+          <t>C4495</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>MARIMBA VIOLIN C4496</t>
+          <t>JUEGO PLASTILINA PERRO C4495</t>
         </is>
       </c>
       <c r="E644" t="inlineStr">
@@ -28947,7 +28947,7 @@
         </is>
       </c>
       <c r="J644" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K644" t="n">
         <v>0</v>
@@ -28956,30 +28956,30 @@
         <v>0</v>
       </c>
       <c r="M644" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N644" t="n">
-        <v>3396.38</v>
+        <v>17981</v>
       </c>
       <c r="O644" t="n">
-        <v>54342.08</v>
+        <v>251734</v>
       </c>
       <c r="P644" t="n">
-        <v>6500</v>
+        <v>29900</v>
       </c>
       <c r="Q644" t="n">
-        <v>104000</v>
+        <v>418600</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>C4498</t>
+          <t>C4496</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>RELOJ PROYECTOR STD C4498</t>
+          <t>MARIMBA VIOLIN C4496</t>
         </is>
       </c>
       <c r="E645" t="inlineStr">
@@ -28993,7 +28993,7 @@
         </is>
       </c>
       <c r="J645" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="K645" t="n">
         <v>0</v>
@@ -29002,30 +29002,30 @@
         <v>0</v>
       </c>
       <c r="M645" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="N645" t="n">
-        <v>4907.8224423077</v>
+        <v>3396.38</v>
       </c>
       <c r="O645" t="n">
-        <v>147234.673269231</v>
+        <v>54342.08</v>
       </c>
       <c r="P645" t="n">
-        <v>8200</v>
+        <v>6500</v>
       </c>
       <c r="Q645" t="n">
-        <v>246000</v>
+        <v>104000</v>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>C4499</t>
+          <t>C4498</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>PIANO ELEFANTE PQÑ C4499</t>
+          <t>RELOJ PROYECTOR STD C4498</t>
         </is>
       </c>
       <c r="E646" t="inlineStr">
@@ -29039,7 +29039,7 @@
         </is>
       </c>
       <c r="J646" t="n">
-        <v>81</v>
+        <v>27</v>
       </c>
       <c r="K646" t="n">
         <v>0</v>
@@ -29048,30 +29048,30 @@
         <v>0</v>
       </c>
       <c r="M646" t="n">
-        <v>81</v>
+        <v>27</v>
       </c>
       <c r="N646" t="n">
-        <v>6414</v>
+        <v>4907.822504931</v>
       </c>
       <c r="O646" t="n">
-        <v>519534</v>
+        <v>132511.207633137</v>
       </c>
       <c r="P646" t="n">
-        <v>10900</v>
+        <v>8200</v>
       </c>
       <c r="Q646" t="n">
-        <v>882900</v>
+        <v>221400</v>
       </c>
     </row>
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>C4500</t>
+          <t>C4499</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
         <is>
-          <t>SET AEROPUETO ACCESORIOS C4500</t>
+          <t>PIANO ELEFANTE PQÑ C4499</t>
         </is>
       </c>
       <c r="E647" t="inlineStr">
@@ -29085,7 +29085,7 @@
         </is>
       </c>
       <c r="J647" t="n">
-        <v>1</v>
+        <v>81</v>
       </c>
       <c r="K647" t="n">
         <v>0</v>
@@ -29094,30 +29094,30 @@
         <v>0</v>
       </c>
       <c r="M647" t="n">
-        <v>1</v>
+        <v>81</v>
       </c>
       <c r="N647" t="n">
-        <v>4771.01</v>
+        <v>6414</v>
       </c>
       <c r="O647" t="n">
-        <v>4771.01</v>
+        <v>519534</v>
       </c>
       <c r="P647" t="n">
-        <v>8900</v>
+        <v>10900</v>
       </c>
       <c r="Q647" t="n">
-        <v>8900</v>
+        <v>882900</v>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>C4505</t>
+          <t>C4500</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
         <is>
-          <t>PESCADITO Y TIBURON  LUZ Y SONIDO C4505</t>
+          <t>SET AEROPUETO ACCESORIOS C4500</t>
         </is>
       </c>
       <c r="E648" t="inlineStr">
@@ -29131,7 +29131,7 @@
         </is>
       </c>
       <c r="J648" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="K648" t="n">
         <v>0</v>
@@ -29140,30 +29140,30 @@
         <v>0</v>
       </c>
       <c r="M648" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="N648" t="n">
-        <v>13210</v>
+        <v>4771.01</v>
       </c>
       <c r="O648" t="n">
-        <v>184940</v>
+        <v>4771.01</v>
       </c>
       <c r="P648" t="n">
-        <v>23900</v>
+        <v>8900</v>
       </c>
       <c r="Q648" t="n">
-        <v>334600</v>
+        <v>8900</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>C4507</t>
+          <t>C4505</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>COCINA HORNO C4507</t>
+          <t>PESCADITO Y TIBURON  LUZ Y SONIDO C4505</t>
         </is>
       </c>
       <c r="E649" t="inlineStr">
@@ -29177,7 +29177,7 @@
         </is>
       </c>
       <c r="J649" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="K649" t="n">
         <v>0</v>
@@ -29186,30 +29186,30 @@
         <v>0</v>
       </c>
       <c r="M649" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="N649" t="n">
-        <v>76839</v>
+        <v>13210</v>
       </c>
       <c r="O649" t="n">
-        <v>307356</v>
+        <v>184940</v>
       </c>
       <c r="P649" t="n">
-        <v>122900</v>
+        <v>23900</v>
       </c>
       <c r="Q649" t="n">
-        <v>491600</v>
+        <v>334600</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>C4510</t>
+          <t>C4507</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
         <is>
-          <t>TOCADOR CASTILLO MUSICA Y LUZ C4510</t>
+          <t>COCINA HORNO C4507</t>
         </is>
       </c>
       <c r="E650" t="inlineStr">
@@ -29223,7 +29223,7 @@
         </is>
       </c>
       <c r="J650" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="K650" t="n">
         <v>0</v>
@@ -29232,30 +29232,30 @@
         <v>0</v>
       </c>
       <c r="M650" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="N650" t="n">
-        <v>52443</v>
+        <v>76839</v>
       </c>
       <c r="O650" t="n">
-        <v>943974</v>
+        <v>307356</v>
       </c>
       <c r="P650" t="n">
-        <v>83900</v>
+        <v>122900</v>
       </c>
       <c r="Q650" t="n">
-        <v>1510200</v>
+        <v>491600</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>C4511</t>
+          <t>C4510</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>BURBUJERO MODELOS STDS C4511</t>
+          <t>TOCADOR CASTILLO MUSICA Y LUZ C4510</t>
         </is>
       </c>
       <c r="E651" t="inlineStr">
@@ -29269,7 +29269,7 @@
         </is>
       </c>
       <c r="J651" t="n">
-        <v>88</v>
+        <v>18</v>
       </c>
       <c r="K651" t="n">
         <v>0</v>
@@ -29278,30 +29278,35 @@
         <v>0</v>
       </c>
       <c r="M651" t="n">
-        <v>88</v>
+        <v>18</v>
       </c>
       <c r="N651" t="n">
-        <v>3903.7379310345</v>
+        <v>52443</v>
       </c>
       <c r="O651" t="n">
-        <v>343528.937931036</v>
+        <v>943974</v>
       </c>
       <c r="P651" t="n">
-        <v>7500</v>
+        <v>83900</v>
       </c>
       <c r="Q651" t="n">
-        <v>660000</v>
+        <v>1510200</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>C4512</t>
+          <t>C4511</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
         <is>
-          <t>MAQUILLAJE ESTUCHE UNICORNIO C4512</t>
+          <t>BURBUJERO MODELOS STDS C4511</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I652" t="inlineStr">
@@ -29310,7 +29315,7 @@
         </is>
       </c>
       <c r="J652" t="n">
-        <v>10</v>
+        <v>88</v>
       </c>
       <c r="K652" t="n">
         <v>0</v>
@@ -29319,35 +29324,30 @@
         <v>0</v>
       </c>
       <c r="M652" t="n">
-        <v>10</v>
+        <v>88</v>
       </c>
       <c r="N652" t="n">
-        <v>20726</v>
+        <v>3903.7383067896</v>
       </c>
       <c r="O652" t="n">
-        <v>207260</v>
+        <v>343528.9709974848</v>
       </c>
       <c r="P652" t="n">
-        <v>33900</v>
+        <v>7500</v>
       </c>
       <c r="Q652" t="n">
-        <v>339000</v>
+        <v>660000</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>C4514</t>
+          <t>C4512</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>ESTUCHE MAQUILLAJE PARA UÑAS C4514</t>
-        </is>
-      </c>
-      <c r="E653" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
+          <t>MAQUILLAJE ESTUCHE UNICORNIO C4512</t>
         </is>
       </c>
       <c r="I653" t="inlineStr">
@@ -29356,7 +29356,7 @@
         </is>
       </c>
       <c r="J653" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="K653" t="n">
         <v>0</v>
@@ -29365,30 +29365,30 @@
         <v>0</v>
       </c>
       <c r="M653" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="N653" t="n">
-        <v>20731</v>
+        <v>20726</v>
       </c>
       <c r="O653" t="n">
-        <v>539006</v>
+        <v>207260</v>
       </c>
       <c r="P653" t="n">
         <v>33900</v>
       </c>
       <c r="Q653" t="n">
-        <v>881400</v>
+        <v>339000</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>C4516</t>
+          <t>C4514</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
         <is>
-          <t>COCHE EN CAJA C4516</t>
+          <t>ESTUCHE MAQUILLAJE PARA UÑAS C4514</t>
         </is>
       </c>
       <c r="E654" t="inlineStr">
@@ -29402,7 +29402,7 @@
         </is>
       </c>
       <c r="J654" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="K654" t="n">
         <v>0</v>
@@ -29411,30 +29411,30 @@
         <v>0</v>
       </c>
       <c r="M654" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="N654" t="n">
-        <v>12113</v>
+        <v>20731</v>
       </c>
       <c r="O654" t="n">
-        <v>48452</v>
+        <v>539006</v>
       </c>
       <c r="P654" t="n">
-        <v>19900</v>
+        <v>33900</v>
       </c>
       <c r="Q654" t="n">
-        <v>79600</v>
+        <v>881400</v>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>C4517</t>
+          <t>C4516</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>SET COCINA</t>
+          <t>COCHE EN CAJA C4516</t>
         </is>
       </c>
       <c r="E655" t="inlineStr">
@@ -29448,7 +29448,7 @@
         </is>
       </c>
       <c r="J655" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K655" t="n">
         <v>0</v>
@@ -29457,30 +29457,30 @@
         <v>0</v>
       </c>
       <c r="M655" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N655" t="n">
-        <v>33000</v>
+        <v>12113</v>
       </c>
       <c r="O655" t="n">
-        <v>198000</v>
+        <v>48452</v>
       </c>
       <c r="P655" t="n">
-        <v>52900</v>
+        <v>19900</v>
       </c>
       <c r="Q655" t="n">
-        <v>317400</v>
+        <v>79600</v>
       </c>
     </row>
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>C4521</t>
+          <t>C4517</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>JUEGO DE AJEDREZ 3EN1</t>
+          <t>SET COCINA</t>
         </is>
       </c>
       <c r="E656" t="inlineStr">
@@ -29494,7 +29494,7 @@
         </is>
       </c>
       <c r="J656" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K656" t="n">
         <v>0</v>
@@ -29503,30 +29503,30 @@
         <v>0</v>
       </c>
       <c r="M656" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N656" t="n">
-        <v>4202</v>
+        <v>33000</v>
       </c>
       <c r="O656" t="n">
-        <v>12606</v>
+        <v>198000</v>
       </c>
       <c r="P656" t="n">
-        <v>7900</v>
+        <v>52900</v>
       </c>
       <c r="Q656" t="n">
-        <v>23700</v>
+        <v>317400</v>
       </c>
     </row>
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>C4522</t>
+          <t>C4521</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>CARRO RECARGABLE LAMBO Y BUGATTI C4522</t>
+          <t>JUEGO DE AJEDREZ 3EN1</t>
         </is>
       </c>
       <c r="E657" t="inlineStr">
@@ -29540,7 +29540,7 @@
         </is>
       </c>
       <c r="J657" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K657" t="n">
         <v>0</v>
@@ -29549,30 +29549,30 @@
         <v>0</v>
       </c>
       <c r="M657" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N657" t="n">
-        <v>14703</v>
+        <v>4202</v>
       </c>
       <c r="O657" t="n">
-        <v>14703</v>
+        <v>12606</v>
       </c>
       <c r="P657" t="n">
-        <v>24900</v>
+        <v>7900</v>
       </c>
       <c r="Q657" t="n">
-        <v>24900</v>
+        <v>23700</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>C4523</t>
+          <t>C4522</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>PIANO TAPETE MUSICAL C4523</t>
+          <t>CARRO RECARGABLE LAMBO Y BUGATTI C4522</t>
         </is>
       </c>
       <c r="E658" t="inlineStr">
@@ -29586,7 +29586,7 @@
         </is>
       </c>
       <c r="J658" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="K658" t="n">
         <v>0</v>
@@ -29595,30 +29595,30 @@
         <v>0</v>
       </c>
       <c r="M658" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="N658" t="n">
-        <v>16469</v>
+        <v>14703</v>
       </c>
       <c r="O658" t="n">
-        <v>609353</v>
+        <v>14703</v>
       </c>
       <c r="P658" t="n">
-        <v>26900</v>
+        <v>24900</v>
       </c>
       <c r="Q658" t="n">
-        <v>995300</v>
+        <v>24900</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>C4527</t>
+          <t>C4523</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>MINI PIANO C4527</t>
+          <t>PIANO TAPETE MUSICAL C4523</t>
         </is>
       </c>
       <c r="E659" t="inlineStr">
@@ -29632,7 +29632,7 @@
         </is>
       </c>
       <c r="J659" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K659" t="n">
         <v>0</v>
@@ -29641,30 +29641,30 @@
         <v>0</v>
       </c>
       <c r="M659" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N659" t="n">
-        <v>12556</v>
+        <v>16469</v>
       </c>
       <c r="O659" t="n">
-        <v>452016</v>
+        <v>609353</v>
       </c>
       <c r="P659" t="n">
-        <v>21900</v>
+        <v>26900</v>
       </c>
       <c r="Q659" t="n">
-        <v>788400</v>
+        <v>995300</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>C4528</t>
+          <t>C4527</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>JUEGO MAGNETICO DIDACTICO</t>
+          <t>MINI PIANO C4527</t>
         </is>
       </c>
       <c r="E660" t="inlineStr">
@@ -29678,7 +29678,7 @@
         </is>
       </c>
       <c r="J660" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="K660" t="n">
         <v>0</v>
@@ -29687,30 +29687,30 @@
         <v>0</v>
       </c>
       <c r="M660" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="N660" t="n">
-        <v>9839</v>
+        <v>12556</v>
       </c>
       <c r="O660" t="n">
-        <v>39356</v>
+        <v>452016</v>
       </c>
       <c r="P660" t="n">
-        <v>16900</v>
+        <v>21900</v>
       </c>
       <c r="Q660" t="n">
-        <v>67600</v>
+        <v>788400</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>C4529</t>
+          <t>C4528</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
         <is>
-          <t>PATO BAÑERA C4529</t>
+          <t>JUEGO MAGNETICO DIDACTICO</t>
         </is>
       </c>
       <c r="E661" t="inlineStr">
@@ -29724,7 +29724,7 @@
         </is>
       </c>
       <c r="J661" t="n">
-        <v>157</v>
+        <v>4</v>
       </c>
       <c r="K661" t="n">
         <v>0</v>
@@ -29733,30 +29733,30 @@
         <v>0</v>
       </c>
       <c r="M661" t="n">
-        <v>157</v>
+        <v>4</v>
       </c>
       <c r="N661" t="n">
-        <v>2629</v>
+        <v>9839</v>
       </c>
       <c r="O661" t="n">
-        <v>412753</v>
+        <v>39356</v>
       </c>
       <c r="P661" t="n">
-        <v>4500</v>
+        <v>16900</v>
       </c>
       <c r="Q661" t="n">
-        <v>706500</v>
+        <v>67600</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>C4530</t>
+          <t>C4529</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>CARRO FORMULAY DINO BURBUJERA C4530</t>
+          <t>PATO BAÑERA C4529</t>
         </is>
       </c>
       <c r="E662" t="inlineStr">
@@ -29770,7 +29770,7 @@
         </is>
       </c>
       <c r="J662" t="n">
-        <v>86</v>
+        <v>157</v>
       </c>
       <c r="K662" t="n">
         <v>0</v>
@@ -29779,30 +29779,30 @@
         <v>0</v>
       </c>
       <c r="M662" t="n">
-        <v>86</v>
+        <v>157</v>
       </c>
       <c r="N662" t="n">
-        <v>5869.1725746653</v>
+        <v>2629</v>
       </c>
       <c r="O662" t="n">
-        <v>504748.8414212158</v>
+        <v>412753</v>
       </c>
       <c r="P662" t="n">
-        <v>9500</v>
+        <v>4500</v>
       </c>
       <c r="Q662" t="n">
-        <v>817000</v>
+        <v>706500</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>C4531</t>
+          <t>C4530</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>CARROS RETRO/GRUA STD BOLSA PVC C4531</t>
+          <t>CARRO FORMULAY DINO BURBUJERA C4530</t>
         </is>
       </c>
       <c r="E663" t="inlineStr">
@@ -29816,39 +29816,39 @@
         </is>
       </c>
       <c r="J663" t="n">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="K663" t="n">
         <v>0</v>
       </c>
       <c r="L663" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M663" t="n">
-        <v>22</v>
+        <v>86</v>
       </c>
       <c r="N663" t="n">
-        <v>6849.2</v>
+        <v>5869.1725746653</v>
       </c>
       <c r="O663" t="n">
-        <v>150682.4</v>
+        <v>504748.8414212158</v>
       </c>
       <c r="P663" t="n">
-        <v>11500</v>
+        <v>9500</v>
       </c>
       <c r="Q663" t="n">
-        <v>253000</v>
+        <v>817000</v>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>C4532</t>
+          <t>C4531</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>BURBUJERO SIRENA CON LUZ C4532</t>
+          <t>CARROS RETRO/GRUA STD BOLSA PVC C4531</t>
         </is>
       </c>
       <c r="E664" t="inlineStr">
@@ -29862,7 +29862,7 @@
         </is>
       </c>
       <c r="J664" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="K664" t="n">
         <v>0</v>
@@ -29871,30 +29871,30 @@
         <v>0</v>
       </c>
       <c r="M664" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="N664" t="n">
-        <v>4984</v>
+        <v>6849.2</v>
       </c>
       <c r="O664" t="n">
-        <v>99680</v>
+        <v>273968</v>
       </c>
       <c r="P664" t="n">
-        <v>7900</v>
+        <v>11500</v>
       </c>
       <c r="Q664" t="n">
-        <v>158000</v>
+        <v>460000</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>C4534</t>
+          <t>C4532</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>CARROS RETROS STD CAJA X 12 C4534</t>
+          <t>BURBUJERO SIRENA CON LUZ C4532</t>
         </is>
       </c>
       <c r="E665" t="inlineStr">
@@ -29908,7 +29908,7 @@
         </is>
       </c>
       <c r="J665" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="K665" t="n">
         <v>0</v>
@@ -29917,30 +29917,30 @@
         <v>0</v>
       </c>
       <c r="M665" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="N665" t="n">
-        <v>5772</v>
+        <v>4984</v>
       </c>
       <c r="O665" t="n">
-        <v>202020</v>
+        <v>99680</v>
       </c>
       <c r="P665" t="n">
-        <v>9900</v>
+        <v>7900</v>
       </c>
       <c r="Q665" t="n">
-        <v>346500</v>
+        <v>158000</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>C4535</t>
+          <t>C4534</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>CARROLLANTON DINO STD C4535</t>
+          <t>CARROS RETROS STD CAJA X 12 C4534</t>
         </is>
       </c>
       <c r="E666" t="inlineStr">
@@ -29954,7 +29954,7 @@
         </is>
       </c>
       <c r="J666" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="K666" t="n">
         <v>0</v>
@@ -29963,30 +29963,30 @@
         <v>0</v>
       </c>
       <c r="M666" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="N666" t="n">
-        <v>6268</v>
+        <v>5772</v>
       </c>
       <c r="O666" t="n">
-        <v>50144</v>
+        <v>202020</v>
       </c>
       <c r="P666" t="n">
-        <v>10900</v>
+        <v>9900</v>
       </c>
       <c r="Q666" t="n">
-        <v>87200</v>
+        <v>346500</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>C4541</t>
+          <t>C4535</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>LANZADORADARDOS MED C4541</t>
+          <t>CARROLLANTON DINO STD C4535</t>
         </is>
       </c>
       <c r="E667" t="inlineStr">
@@ -30000,7 +30000,7 @@
         </is>
       </c>
       <c r="J667" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="K667" t="n">
         <v>0</v>
@@ -30009,30 +30009,30 @@
         <v>0</v>
       </c>
       <c r="M667" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="N667" t="n">
-        <v>6645</v>
+        <v>6268</v>
       </c>
       <c r="O667" t="n">
-        <v>205995</v>
+        <v>50144</v>
       </c>
       <c r="P667" t="n">
         <v>10900</v>
       </c>
       <c r="Q667" t="n">
-        <v>337900</v>
+        <v>87200</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>C4545</t>
+          <t>C4541</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>TAPETE PIANO PARA BEBE C4545</t>
+          <t>LANZADORADARDOS MED C4541</t>
         </is>
       </c>
       <c r="E668" t="inlineStr">
@@ -30046,7 +30046,7 @@
         </is>
       </c>
       <c r="J668" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="K668" t="n">
         <v>0</v>
@@ -30055,30 +30055,30 @@
         <v>0</v>
       </c>
       <c r="M668" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="N668" t="n">
-        <v>27186</v>
+        <v>6645</v>
       </c>
       <c r="O668" t="n">
-        <v>217488</v>
+        <v>205995</v>
       </c>
       <c r="P668" t="n">
-        <v>43900</v>
+        <v>10900</v>
       </c>
       <c r="Q668" t="n">
-        <v>351200</v>
+        <v>337900</v>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>C4548</t>
+          <t>C4545</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>CARRO DIDACTICO X4 BEBE</t>
+          <t>TAPETE PIANO PARA BEBE C4545</t>
         </is>
       </c>
       <c r="E669" t="inlineStr">
@@ -30092,7 +30092,7 @@
         </is>
       </c>
       <c r="J669" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K669" t="n">
         <v>0</v>
@@ -30101,30 +30101,30 @@
         <v>0</v>
       </c>
       <c r="M669" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="N669" t="n">
-        <v>7562</v>
+        <v>27186</v>
       </c>
       <c r="O669" t="n">
-        <v>7562</v>
+        <v>217488</v>
       </c>
       <c r="P669" t="n">
-        <v>12900</v>
+        <v>43900</v>
       </c>
       <c r="Q669" t="n">
-        <v>12900</v>
+        <v>351200</v>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>C4549</t>
+          <t>C4548</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>CARRO DIDCTICO PVC C4549</t>
+          <t>CARRO DIDACTICO X4 BEBE</t>
         </is>
       </c>
       <c r="E670" t="inlineStr">
@@ -30138,7 +30138,7 @@
         </is>
       </c>
       <c r="J670" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="K670" t="n">
         <v>0</v>
@@ -30147,30 +30147,30 @@
         <v>0</v>
       </c>
       <c r="M670" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="N670" t="n">
-        <v>3898</v>
+        <v>7562</v>
       </c>
       <c r="O670" t="n">
-        <v>70164</v>
+        <v>7562</v>
       </c>
       <c r="P670" t="n">
-        <v>6900</v>
+        <v>12900</v>
       </c>
       <c r="Q670" t="n">
-        <v>124200</v>
+        <v>12900</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>C4550</t>
+          <t>C4549</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>HELICOPTERO  FASHION C4550</t>
+          <t>CARRO DIDCTICO PVC C4549</t>
         </is>
       </c>
       <c r="E671" t="inlineStr">
@@ -30184,7 +30184,7 @@
         </is>
       </c>
       <c r="J671" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="K671" t="n">
         <v>0</v>
@@ -30193,30 +30193,30 @@
         <v>0</v>
       </c>
       <c r="M671" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="N671" t="n">
-        <v>13565</v>
+        <v>3898</v>
       </c>
       <c r="O671" t="n">
-        <v>94955</v>
+        <v>70164</v>
       </c>
       <c r="P671" t="n">
-        <v>22500</v>
+        <v>6900</v>
       </c>
       <c r="Q671" t="n">
-        <v>157500</v>
+        <v>124200</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>C4551</t>
+          <t>C4550</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>PRINCESS EN CASTILLO Y CARRUAJE C4551</t>
+          <t>HELICOPTERO  FASHION C4550</t>
         </is>
       </c>
       <c r="E672" t="inlineStr">
@@ -30230,7 +30230,7 @@
         </is>
       </c>
       <c r="J672" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="K672" t="n">
         <v>0</v>
@@ -30239,30 +30239,30 @@
         <v>0</v>
       </c>
       <c r="M672" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="N672" t="n">
-        <v>7635</v>
+        <v>13565</v>
       </c>
       <c r="O672" t="n">
-        <v>91620</v>
+        <v>94955</v>
       </c>
       <c r="P672" t="n">
-        <v>13900</v>
+        <v>22500</v>
       </c>
       <c r="Q672" t="n">
-        <v>166800</v>
+        <v>157500</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>C4553</t>
+          <t>C4551</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
         <is>
-          <t>BOLSA CHILLONES X 12 PCS</t>
+          <t>PRINCESS EN CASTILLO Y CARRUAJE C4551</t>
         </is>
       </c>
       <c r="E673" t="inlineStr">
@@ -30276,7 +30276,7 @@
         </is>
       </c>
       <c r="J673" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K673" t="n">
         <v>0</v>
@@ -30285,30 +30285,30 @@
         <v>0</v>
       </c>
       <c r="M673" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N673" t="n">
-        <v>5682</v>
+        <v>7635</v>
       </c>
       <c r="O673" t="n">
-        <v>73866</v>
+        <v>91620</v>
       </c>
       <c r="P673" t="n">
-        <v>9900</v>
+        <v>13900</v>
       </c>
       <c r="Q673" t="n">
-        <v>128700</v>
+        <v>166800</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>C4555</t>
+          <t>C4553</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
         <is>
-          <t>SONAJERO EN BOLSA 5 PCS C4555</t>
+          <t>BOLSA CHILLONES X 12 PCS</t>
         </is>
       </c>
       <c r="E674" t="inlineStr">
@@ -30322,7 +30322,7 @@
         </is>
       </c>
       <c r="J674" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="K674" t="n">
         <v>0</v>
@@ -30331,30 +30331,30 @@
         <v>0</v>
       </c>
       <c r="M674" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="N674" t="n">
-        <v>5438</v>
+        <v>5682</v>
       </c>
       <c r="O674" t="n">
-        <v>48942</v>
+        <v>73866</v>
       </c>
       <c r="P674" t="n">
-        <v>8900</v>
+        <v>9900</v>
       </c>
       <c r="Q674" t="n">
-        <v>80100</v>
+        <v>128700</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>C4556</t>
+          <t>C4555</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
         <is>
-          <t>SONAJERO EN CAJA 8PCS C4556</t>
+          <t>SONAJERO EN BOLSA 5 PCS C4555</t>
         </is>
       </c>
       <c r="E675" t="inlineStr">
@@ -30368,7 +30368,7 @@
         </is>
       </c>
       <c r="J675" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K675" t="n">
         <v>0</v>
@@ -30377,30 +30377,30 @@
         <v>0</v>
       </c>
       <c r="M675" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N675" t="n">
-        <v>16086</v>
+        <v>5438</v>
       </c>
       <c r="O675" t="n">
-        <v>112602</v>
+        <v>48942</v>
       </c>
       <c r="P675" t="n">
-        <v>25900</v>
+        <v>8900</v>
       </c>
       <c r="Q675" t="n">
-        <v>181300</v>
+        <v>80100</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>C4557</t>
+          <t>C4556</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
         <is>
-          <t>JUEGO DE UÑAS Y MAQUILLAJE C4557</t>
+          <t>SONAJERO EN CAJA 8PCS C4556</t>
         </is>
       </c>
       <c r="E676" t="inlineStr">
@@ -30414,7 +30414,7 @@
         </is>
       </c>
       <c r="J676" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="K676" t="n">
         <v>0</v>
@@ -30423,30 +30423,30 @@
         <v>0</v>
       </c>
       <c r="M676" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="N676" t="n">
-        <v>8806</v>
+        <v>16086</v>
       </c>
       <c r="O676" t="n">
-        <v>158508</v>
+        <v>112602</v>
       </c>
       <c r="P676" t="n">
-        <v>14900</v>
+        <v>25900</v>
       </c>
       <c r="Q676" t="n">
-        <v>268200</v>
+        <v>181300</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>C4558</t>
+          <t>C4557</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>LIBRO DIDACTICO INGLES/ESPAÑOL C4558</t>
+          <t>JUEGO DE UÑAS Y MAQUILLAJE C4557</t>
         </is>
       </c>
       <c r="E677" t="inlineStr">
@@ -30460,7 +30460,7 @@
         </is>
       </c>
       <c r="J677" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K677" t="n">
         <v>0</v>
@@ -30469,30 +30469,30 @@
         <v>0</v>
       </c>
       <c r="M677" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N677" t="n">
-        <v>23439</v>
+        <v>8806</v>
       </c>
       <c r="O677" t="n">
-        <v>398463</v>
+        <v>158508</v>
       </c>
       <c r="P677" t="n">
-        <v>37900</v>
+        <v>14900</v>
       </c>
       <c r="Q677" t="n">
-        <v>644300</v>
+        <v>268200</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>C4559</t>
+          <t>C4558</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
         <is>
-          <t>PIANO DIDACTICO 3en1 C4559</t>
+          <t>LIBRO DIDACTICO INGLES/ESPAÑOL C4558</t>
         </is>
       </c>
       <c r="E678" t="inlineStr">
@@ -30506,7 +30506,7 @@
         </is>
       </c>
       <c r="J678" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="K678" t="n">
         <v>0</v>
@@ -30515,33 +30515,30 @@
         <v>0</v>
       </c>
       <c r="M678" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="N678" t="n">
-        <v>19008</v>
+        <v>23439</v>
       </c>
       <c r="O678" t="n">
-        <v>551232</v>
+        <v>398463</v>
       </c>
       <c r="P678" t="n">
-        <v>30900</v>
+        <v>37900</v>
       </c>
       <c r="Q678" t="n">
-        <v>896100</v>
+        <v>644300</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>C456</t>
-        </is>
-      </c>
-      <c r="B679" t="n">
-        <v>6920190230411</v>
+          <t>C4559</t>
+        </is>
       </c>
       <c r="C679" t="inlineStr">
         <is>
-          <t>BALON PLAYERO SURTIDO</t>
+          <t>PIANO DIDACTICO 3en1 C4559</t>
         </is>
       </c>
       <c r="E679" t="inlineStr">
@@ -30551,11 +30548,11 @@
       </c>
       <c r="I679" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J679" t="n">
-        <v>77</v>
+        <v>29</v>
       </c>
       <c r="K679" t="n">
         <v>0</v>
@@ -30564,30 +30561,33 @@
         <v>0</v>
       </c>
       <c r="M679" t="n">
-        <v>77</v>
+        <v>29</v>
       </c>
       <c r="N679" t="n">
-        <v>753</v>
+        <v>19008</v>
       </c>
       <c r="O679" t="n">
-        <v>57981</v>
+        <v>551232</v>
       </c>
       <c r="P679" t="n">
-        <v>1600</v>
+        <v>30900</v>
       </c>
       <c r="Q679" t="n">
-        <v>123200</v>
+        <v>896100</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>C4560</t>
-        </is>
+          <t>C456</t>
+        </is>
+      </c>
+      <c r="B680" t="n">
+        <v>6920190230411</v>
       </c>
       <c r="C680" t="inlineStr">
         <is>
-          <t>PIANO TAPETE C4560</t>
+          <t>BALON PLAYERO SURTIDO</t>
         </is>
       </c>
       <c r="E680" t="inlineStr">
@@ -30597,11 +30597,11 @@
       </c>
       <c r="I680" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J680" t="n">
-        <v>33</v>
+        <v>77</v>
       </c>
       <c r="K680" t="n">
         <v>0</v>
@@ -30610,30 +30610,30 @@
         <v>0</v>
       </c>
       <c r="M680" t="n">
-        <v>33</v>
+        <v>77</v>
       </c>
       <c r="N680" t="n">
-        <v>11302</v>
+        <v>753</v>
       </c>
       <c r="O680" t="n">
-        <v>372966</v>
+        <v>57981</v>
       </c>
       <c r="P680" t="n">
-        <v>18900</v>
+        <v>1600</v>
       </c>
       <c r="Q680" t="n">
-        <v>623700</v>
+        <v>123200</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>C4561</t>
+          <t>C4560</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
         <is>
-          <t>ABECEDARIO INGLES MUSICAL C4561</t>
+          <t>PIANO TAPETE C4560</t>
         </is>
       </c>
       <c r="E681" t="inlineStr">
@@ -30647,7 +30647,7 @@
         </is>
       </c>
       <c r="J681" t="n">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="K681" t="n">
         <v>0</v>
@@ -30656,30 +30656,30 @@
         <v>0</v>
       </c>
       <c r="M681" t="n">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="N681" t="n">
-        <v>17992</v>
+        <v>11302</v>
       </c>
       <c r="O681" t="n">
-        <v>881608</v>
+        <v>372966</v>
       </c>
       <c r="P681" t="n">
-        <v>28900</v>
+        <v>18900</v>
       </c>
       <c r="Q681" t="n">
-        <v>1416100</v>
+        <v>623700</v>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>C4566</t>
+          <t>C4561</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
         <is>
-          <t>CARRO MINI CONTROL MODELOS STDS C4566</t>
+          <t>ABECEDARIO INGLES MUSICAL C4561</t>
         </is>
       </c>
       <c r="E682" t="inlineStr">
@@ -30693,7 +30693,7 @@
         </is>
       </c>
       <c r="J682" t="n">
-        <v>2</v>
+        <v>49</v>
       </c>
       <c r="K682" t="n">
         <v>0</v>
@@ -30702,30 +30702,30 @@
         <v>0</v>
       </c>
       <c r="M682" t="n">
-        <v>2</v>
+        <v>49</v>
       </c>
       <c r="N682" t="n">
-        <v>11348</v>
+        <v>17992</v>
       </c>
       <c r="O682" t="n">
-        <v>22696</v>
+        <v>881608</v>
       </c>
       <c r="P682" t="n">
-        <v>19900</v>
+        <v>28900</v>
       </c>
       <c r="Q682" t="n">
-        <v>39800</v>
+        <v>1416100</v>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>C4567</t>
+          <t>C4566</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>JUEGO MESA FORMA DE ANIMALES C4567</t>
+          <t>CARRO MINI CONTROL MODELOS STDS C4566</t>
         </is>
       </c>
       <c r="E683" t="inlineStr">
@@ -30739,7 +30739,7 @@
         </is>
       </c>
       <c r="J683" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="K683" t="n">
         <v>0</v>
@@ -30748,30 +30748,30 @@
         <v>0</v>
       </c>
       <c r="M683" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="N683" t="n">
-        <v>17075.989520833</v>
+        <v>11348</v>
       </c>
       <c r="O683" t="n">
-        <v>563507.6541874891</v>
+        <v>22696</v>
       </c>
       <c r="P683" t="n">
-        <v>27500</v>
+        <v>19900</v>
       </c>
       <c r="Q683" t="n">
-        <v>907500</v>
+        <v>39800</v>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>C4570</t>
+          <t>C4567</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
         <is>
-          <t>CUBO MAGICO C4570 EQY766</t>
+          <t>JUEGO MESA FORMA DE ANIMALES C4567</t>
         </is>
       </c>
       <c r="E684" t="inlineStr">
@@ -30785,7 +30785,7 @@
         </is>
       </c>
       <c r="J684" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="K684" t="n">
         <v>0</v>
@@ -30794,30 +30794,30 @@
         <v>0</v>
       </c>
       <c r="M684" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="N684" t="n">
-        <v>10398</v>
+        <v>17075.989520833</v>
       </c>
       <c r="O684" t="n">
-        <v>270348</v>
+        <v>563507.6541874891</v>
       </c>
       <c r="P684" t="n">
-        <v>16900</v>
+        <v>27500</v>
       </c>
       <c r="Q684" t="n">
-        <v>439400</v>
+        <v>907500</v>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>C4571</t>
+          <t>C4570</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
         <is>
-          <t>CUBO MAGIOC C4571 EQY825</t>
+          <t>CUBO MAGICO C4570 EQY766</t>
         </is>
       </c>
       <c r="E685" t="inlineStr">
@@ -30831,7 +30831,7 @@
         </is>
       </c>
       <c r="J685" t="n">
-        <v>69</v>
+        <v>26</v>
       </c>
       <c r="K685" t="n">
         <v>0</v>
@@ -30840,30 +30840,30 @@
         <v>0</v>
       </c>
       <c r="M685" t="n">
-        <v>69</v>
+        <v>26</v>
       </c>
       <c r="N685" t="n">
-        <v>5922</v>
+        <v>10398</v>
       </c>
       <c r="O685" t="n">
-        <v>408618</v>
+        <v>270348</v>
       </c>
       <c r="P685" t="n">
-        <v>9900</v>
+        <v>16900</v>
       </c>
       <c r="Q685" t="n">
-        <v>683100</v>
+        <v>439400</v>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>C4572</t>
+          <t>C4571</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>CUBO MAGICO C4572 EQY10130</t>
+          <t>CUBO MAGIOC C4571 EQY825</t>
         </is>
       </c>
       <c r="E686" t="inlineStr">
@@ -30877,7 +30877,7 @@
         </is>
       </c>
       <c r="J686" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="K686" t="n">
         <v>0</v>
@@ -30886,30 +30886,35 @@
         <v>0</v>
       </c>
       <c r="M686" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="N686" t="n">
-        <v>4518</v>
+        <v>5922</v>
       </c>
       <c r="O686" t="n">
-        <v>271080</v>
+        <v>408618</v>
       </c>
       <c r="P686" t="n">
-        <v>7900</v>
+        <v>9900</v>
       </c>
       <c r="Q686" t="n">
-        <v>474000</v>
+        <v>683100</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>C4573</t>
+          <t>C4572</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
         <is>
-          <t>CUBO MAGICO C4573 EQY 807</t>
+          <t>CUBO MAGICO C4572 EQY10130</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I687" t="inlineStr">
@@ -30918,7 +30923,7 @@
         </is>
       </c>
       <c r="J687" t="n">
-        <v>4</v>
+        <v>57</v>
       </c>
       <c r="K687" t="n">
         <v>0</v>
@@ -30927,19 +30932,19 @@
         <v>0</v>
       </c>
       <c r="M687" t="n">
-        <v>4</v>
+        <v>57</v>
       </c>
       <c r="N687" t="n">
-        <v>11015</v>
+        <v>4518</v>
       </c>
       <c r="O687" t="n">
-        <v>44060</v>
+        <v>257526</v>
       </c>
       <c r="P687" t="n">
-        <v>17900</v>
+        <v>7900</v>
       </c>
       <c r="Q687" t="n">
-        <v>71600</v>
+        <v>450300</v>
       </c>
     </row>
     <row r="688">
@@ -32163,7 +32168,7 @@
         </is>
       </c>
       <c r="J714" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K714" t="n">
         <v>0</v>
@@ -32172,19 +32177,19 @@
         <v>0</v>
       </c>
       <c r="M714" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="N714" t="n">
         <v>15472</v>
       </c>
       <c r="O714" t="n">
-        <v>30944</v>
+        <v>123776</v>
       </c>
       <c r="P714" t="n">
         <v>25900</v>
       </c>
       <c r="Q714" t="n">
-        <v>51800</v>
+        <v>207200</v>
       </c>
     </row>
     <row r="715">
@@ -32255,7 +32260,7 @@
         </is>
       </c>
       <c r="J716" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="K716" t="n">
         <v>0</v>
@@ -32264,19 +32269,19 @@
         <v>0</v>
       </c>
       <c r="M716" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="N716" t="n">
         <v>7253</v>
       </c>
       <c r="O716" t="n">
-        <v>398915</v>
+        <v>456939</v>
       </c>
       <c r="P716" t="n">
         <v>11900</v>
       </c>
       <c r="Q716" t="n">
-        <v>654500</v>
+        <v>749700</v>
       </c>
     </row>
     <row r="717">
@@ -32497,10 +32502,10 @@
         <v>80</v>
       </c>
       <c r="N721" t="n">
-        <v>1516.0387724372</v>
+        <v>1516.0387635597</v>
       </c>
       <c r="O721" t="n">
-        <v>121283.101794976</v>
+        <v>121283.101084776</v>
       </c>
       <c r="P721" t="n">
         <v>2300</v>
@@ -32633,10 +32638,10 @@
         <v>283</v>
       </c>
       <c r="N724" t="n">
-        <v>2458.5128114246</v>
+        <v>2458.5127187173</v>
       </c>
       <c r="O724" t="n">
-        <v>695759.1256331617</v>
+        <v>695759.0993969959</v>
       </c>
       <c r="P724" t="n">
         <v>3500</v>
@@ -32679,10 +32684,10 @@
         <v>148</v>
       </c>
       <c r="N725" t="n">
-        <v>1907.3928289474</v>
+        <v>1907.3928131868</v>
       </c>
       <c r="O725" t="n">
-        <v>282294.1386842152</v>
+        <v>282294.1363516464</v>
       </c>
       <c r="P725" t="n">
         <v>2500</v>
@@ -32771,10 +32776,10 @@
         <v>212</v>
       </c>
       <c r="N727" t="n">
-        <v>2079.3837709497</v>
+        <v>2079.3836916549</v>
       </c>
       <c r="O727" t="n">
-        <v>440829.3594413364</v>
+        <v>440829.3426308387</v>
       </c>
       <c r="P727" t="n">
         <v>2900</v>
@@ -32817,10 +32822,10 @@
         <v>122</v>
       </c>
       <c r="N728" t="n">
-        <v>1803.0159704121</v>
+        <v>1803.0161346363</v>
       </c>
       <c r="O728" t="n">
-        <v>219967.9483902762</v>
+        <v>219967.9684256286</v>
       </c>
       <c r="P728" t="n">
         <v>2500</v>
@@ -32863,10 +32868,10 @@
         <v>108</v>
       </c>
       <c r="N729" t="n">
-        <v>3306.5944954128</v>
+        <v>3306.5944785276</v>
       </c>
       <c r="O729" t="n">
-        <v>357112.2055045824</v>
+        <v>357112.2036809808</v>
       </c>
       <c r="P729" t="n">
         <v>4900</v>
@@ -32909,10 +32914,10 @@
         <v>199</v>
       </c>
       <c r="N730" t="n">
-        <v>2122.1637267479</v>
+        <v>2122.1636203523</v>
       </c>
       <c r="O730" t="n">
-        <v>422310.5816228321</v>
+        <v>422310.5604501077</v>
       </c>
       <c r="P730" t="n">
         <v>2900</v>
@@ -32943,7 +32948,7 @@
         </is>
       </c>
       <c r="J731" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K731" t="n">
         <v>0</v>
@@ -32952,19 +32957,19 @@
         <v>0</v>
       </c>
       <c r="M731" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N731" t="n">
-        <v>2108.7941491086</v>
+        <v>2108.7945137157</v>
       </c>
       <c r="O731" t="n">
-        <v>156050.7670340364</v>
+        <v>153941.9995012461</v>
       </c>
       <c r="P731" t="n">
         <v>2900</v>
       </c>
       <c r="Q731" t="n">
-        <v>214600</v>
+        <v>211700</v>
       </c>
     </row>
     <row r="732">
@@ -33001,10 +33006,10 @@
         <v>234</v>
       </c>
       <c r="N732" t="n">
-        <v>2056.0826834456</v>
+        <v>2056.0824863487</v>
       </c>
       <c r="O732" t="n">
-        <v>481123.3479262704</v>
+        <v>481123.3018055958</v>
       </c>
       <c r="P732" t="n">
         <v>2900</v>
@@ -33047,10 +33052,10 @@
         <v>196</v>
       </c>
       <c r="N733" t="n">
-        <v>3224.5691001525</v>
+        <v>3224.5693083723</v>
       </c>
       <c r="O733" t="n">
-        <v>632015.5436298901</v>
+        <v>632015.5844409708</v>
       </c>
       <c r="P733" t="n">
         <v>4500</v>
@@ -33093,10 +33098,10 @@
         <v>113</v>
       </c>
       <c r="N734" t="n">
-        <v>1655.9302708407</v>
+        <v>1655.9298420859</v>
       </c>
       <c r="O734" t="n">
-        <v>187120.1206049991</v>
+        <v>187120.0721557067</v>
       </c>
       <c r="P734" t="n">
         <v>2500</v>
@@ -33360,7 +33365,7 @@
         </is>
       </c>
       <c r="J740" t="n">
-        <v>33</v>
+        <v>113</v>
       </c>
       <c r="K740" t="n">
         <v>0</v>
@@ -33369,19 +33374,19 @@
         <v>0</v>
       </c>
       <c r="M740" t="n">
-        <v>33</v>
+        <v>113</v>
       </c>
       <c r="N740" t="n">
-        <v>1789.7745116279</v>
+        <v>1592.2821517241</v>
       </c>
       <c r="O740" t="n">
-        <v>59062.5588837207</v>
+        <v>179927.8831448233</v>
       </c>
       <c r="P740" t="n">
         <v>2500</v>
       </c>
       <c r="Q740" t="n">
-        <v>82500</v>
+        <v>282500</v>
       </c>
     </row>
     <row r="741">
@@ -33549,10 +33554,10 @@
         <v>19</v>
       </c>
       <c r="N744" t="n">
-        <v>1906.1803846154</v>
+        <v>1906.1797959184</v>
       </c>
       <c r="O744" t="n">
-        <v>36217.4273076926</v>
+        <v>36217.4161224496</v>
       </c>
       <c r="P744" t="n">
         <v>2900</v>
@@ -33595,10 +33600,10 @@
         <v>13</v>
       </c>
       <c r="N745" t="n">
-        <v>3033.701005291</v>
+        <v>3033.6993989071</v>
       </c>
       <c r="O745" t="n">
-        <v>39438.113068783</v>
+        <v>39438.0921857923</v>
       </c>
       <c r="P745" t="n">
         <v>4500</v>
@@ -33635,22 +33640,22 @@
         <v>0</v>
       </c>
       <c r="L746" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M746" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="N746" t="n">
-        <v>2060.1591932458</v>
+        <v>2060.1589866157</v>
       </c>
       <c r="O746" t="n">
-        <v>111248.5964352732</v>
+        <v>98887.6313575536</v>
       </c>
       <c r="P746" t="n">
         <v>2900</v>
       </c>
       <c r="Q746" t="n">
-        <v>156600</v>
+        <v>139200</v>
       </c>
     </row>
     <row r="747">
@@ -33687,10 +33692,10 @@
         <v>55</v>
       </c>
       <c r="N747" t="n">
-        <v>1668.6382745098</v>
+        <v>1668.6384251969</v>
       </c>
       <c r="O747" t="n">
-        <v>91775.105098039</v>
+        <v>91775.11338582951</v>
       </c>
       <c r="P747" t="n">
         <v>2500</v>
@@ -33767,28 +33772,28 @@
         </is>
       </c>
       <c r="J749" t="n">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="K749" t="n">
         <v>0</v>
       </c>
       <c r="L749" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M749" t="n">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="N749" t="n">
-        <v>1259.2746942571</v>
+        <v>1259.2747051969</v>
       </c>
       <c r="O749" t="n">
-        <v>353856.1890862451</v>
+        <v>341263.4451083599</v>
       </c>
       <c r="P749" t="n">
         <v>1900</v>
       </c>
       <c r="Q749" t="n">
-        <v>533900</v>
+        <v>514900</v>
       </c>
     </row>
     <row r="750">
@@ -33946,7 +33951,7 @@
         </is>
       </c>
       <c r="J753" t="n">
-        <v>94</v>
+        <v>142</v>
       </c>
       <c r="K753" t="n">
         <v>0</v>
@@ -33955,19 +33960,19 @@
         <v>0</v>
       </c>
       <c r="M753" t="n">
-        <v>94</v>
+        <v>142</v>
       </c>
       <c r="N753" t="n">
-        <v>2556.7471311475</v>
+        <v>2556.747219917</v>
       </c>
       <c r="O753" t="n">
-        <v>240334.230327865</v>
+        <v>363058.105228214</v>
       </c>
       <c r="P753" t="n">
         <v>3900</v>
       </c>
       <c r="Q753" t="n">
-        <v>366600</v>
+        <v>553800</v>
       </c>
     </row>
     <row r="754">
@@ -34002,10 +34007,10 @@
         <v>283</v>
       </c>
       <c r="N754" t="n">
-        <v>692.15228029678</v>
+        <v>692.15231697102</v>
       </c>
       <c r="O754" t="n">
-        <v>195879.0953239887</v>
+        <v>195879.1057027987</v>
       </c>
       <c r="P754" t="n">
         <v>1200</v>
@@ -35895,13 +35900,13 @@
         </is>
       </c>
       <c r="J795" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K795" t="n">
         <v>0</v>
       </c>
       <c r="L795" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M795" t="n">
         <v>2</v>
@@ -37609,7 +37614,7 @@
         </is>
       </c>
       <c r="J832" t="n">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="K832" t="n">
         <v>0</v>
@@ -37618,19 +37623,19 @@
         <v>0</v>
       </c>
       <c r="M832" t="n">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="N832" t="n">
         <v>1326</v>
       </c>
       <c r="O832" t="n">
-        <v>123318</v>
+        <v>115362</v>
       </c>
       <c r="P832" t="n">
         <v>2900</v>
       </c>
       <c r="Q832" t="n">
-        <v>269700</v>
+        <v>252300</v>
       </c>
     </row>
     <row r="833">
@@ -37883,28 +37888,28 @@
         </is>
       </c>
       <c r="J838" t="n">
-        <v>1109</v>
+        <v>1085</v>
       </c>
       <c r="K838" t="n">
         <v>0</v>
       </c>
       <c r="L838" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M838" t="n">
-        <v>1109</v>
+        <v>1079</v>
       </c>
       <c r="N838" t="n">
-        <v>517.29272348033</v>
+        <v>517.29287307808</v>
       </c>
       <c r="O838" t="n">
-        <v>573677.6303396859</v>
+        <v>558159.0100512484</v>
       </c>
       <c r="P838" t="n">
         <v>900</v>
       </c>
       <c r="Q838" t="n">
-        <v>998100</v>
+        <v>971100</v>
       </c>
     </row>
     <row r="839">
@@ -38398,7 +38403,7 @@
         </is>
       </c>
       <c r="J849" t="n">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="K849" t="n">
         <v>0</v>
@@ -38407,19 +38412,19 @@
         <v>0</v>
       </c>
       <c r="M849" t="n">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="N849" t="n">
-        <v>3110.8397979798</v>
+        <v>3110.8397028838</v>
       </c>
       <c r="O849" t="n">
-        <v>637722.158585859</v>
+        <v>628389.6199825276</v>
       </c>
       <c r="P849" t="n">
         <v>4500</v>
       </c>
       <c r="Q849" t="n">
-        <v>922500</v>
+        <v>909000</v>
       </c>
     </row>
     <row r="850">
@@ -38816,22 +38821,22 @@
         <v>0</v>
       </c>
       <c r="L858" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M858" t="n">
-        <v>1160</v>
+        <v>1148</v>
       </c>
       <c r="N858" t="n">
-        <v>703.7949437622</v>
+        <v>703.79492130965</v>
       </c>
       <c r="O858" t="n">
-        <v>816402.134764152</v>
+        <v>807956.5696634782</v>
       </c>
       <c r="P858" t="n">
         <v>900</v>
       </c>
       <c r="Q858" t="n">
-        <v>1044000</v>
+        <v>1033200</v>
       </c>
     </row>
     <row r="859">
@@ -39184,7 +39189,7 @@
         </is>
       </c>
       <c r="J866" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K866" t="n">
         <v>0</v>
@@ -39193,19 +39198,19 @@
         <v>0</v>
       </c>
       <c r="M866" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="N866" t="n">
-        <v>2501.3847058824</v>
+        <v>2501.3846268657</v>
       </c>
       <c r="O866" t="n">
-        <v>32518.0011764712</v>
+        <v>25013.846268657</v>
       </c>
       <c r="P866" t="n">
         <v>4100</v>
       </c>
       <c r="Q866" t="n">
-        <v>53300</v>
+        <v>41000</v>
       </c>
     </row>
     <row r="867">
@@ -39337,10 +39342,10 @@
         <v>113</v>
       </c>
       <c r="N869" t="n">
-        <v>3006.0209574468</v>
+        <v>3006.0209677419</v>
       </c>
       <c r="O869" t="n">
-        <v>339680.3681914884</v>
+        <v>339680.3693548347</v>
       </c>
       <c r="P869" t="n">
         <v>3900</v>
@@ -39374,7 +39379,7 @@
         </is>
       </c>
       <c r="J870" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="K870" t="n">
         <v>0</v>
@@ -39383,19 +39388,19 @@
         <v>0</v>
       </c>
       <c r="M870" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N870" t="n">
         <v>14260.14</v>
       </c>
       <c r="O870" t="n">
-        <v>327983.22</v>
+        <v>256682.52</v>
       </c>
       <c r="P870" t="n">
         <v>15900</v>
       </c>
       <c r="Q870" t="n">
-        <v>365700</v>
+        <v>286200</v>
       </c>
     </row>
     <row r="871">
@@ -39736,7 +39741,7 @@
         </is>
       </c>
       <c r="J878" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="K878" t="n">
         <v>0</v>
@@ -39745,19 +39750,19 @@
         <v>0</v>
       </c>
       <c r="M878" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="N878" t="n">
         <v>2525.02</v>
       </c>
       <c r="O878" t="n">
-        <v>249976.98</v>
+        <v>229776.82</v>
       </c>
       <c r="P878" t="n">
         <v>3000</v>
       </c>
       <c r="Q878" t="n">
-        <v>297000</v>
+        <v>273000</v>
       </c>
     </row>
     <row r="879">
@@ -40213,7 +40218,7 @@
         </is>
       </c>
       <c r="J888" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K888" t="n">
         <v>0</v>
@@ -40222,19 +40227,19 @@
         <v>0</v>
       </c>
       <c r="M888" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N888" t="n">
         <v>6701.05</v>
       </c>
       <c r="O888" t="n">
-        <v>73711.55</v>
+        <v>67010.5</v>
       </c>
       <c r="P888" t="n">
         <v>14500</v>
       </c>
       <c r="Q888" t="n">
-        <v>159500</v>
+        <v>145000</v>
       </c>
     </row>
     <row r="889">
@@ -40660,10 +40665,10 @@
         <v>22</v>
       </c>
       <c r="N897" t="n">
-        <v>2098.4051032448</v>
+        <v>2098.4051183432</v>
       </c>
       <c r="O897" t="n">
-        <v>46164.9122713856</v>
+        <v>46164.91260355039</v>
       </c>
       <c r="P897" t="n">
         <v>9500</v>
@@ -42043,7 +42048,7 @@
         </is>
       </c>
       <c r="J926" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K926" t="n">
         <v>0</v>
@@ -42052,19 +42057,19 @@
         <v>0</v>
       </c>
       <c r="M926" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N926" t="n">
-        <v>9746.880194174801</v>
+        <v>9746.8801960784</v>
       </c>
       <c r="O926" t="n">
-        <v>146203.202912622</v>
+        <v>136456.3227450976</v>
       </c>
       <c r="P926" t="n">
         <v>18500</v>
       </c>
       <c r="Q926" t="n">
-        <v>277500</v>
+        <v>259000</v>
       </c>
     </row>
     <row r="927">
@@ -42395,10 +42400,10 @@
         <v>28</v>
       </c>
       <c r="N933" t="n">
-        <v>2992.5705633803</v>
+        <v>2992.5708695652</v>
       </c>
       <c r="O933" t="n">
-        <v>83791.9757746484</v>
+        <v>83791.98434782561</v>
       </c>
       <c r="P933" t="n">
         <v>6000</v>
@@ -42441,10 +42446,10 @@
         <v>4</v>
       </c>
       <c r="N934" t="n">
-        <v>875.69017699115</v>
+        <v>875.69017777778</v>
       </c>
       <c r="O934" t="n">
-        <v>3502.7607079646</v>
+        <v>3502.76071111112</v>
       </c>
       <c r="P934" t="n">
         <v>4500</v>
@@ -42527,28 +42532,28 @@
         </is>
       </c>
       <c r="J936" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="K936" t="n">
         <v>0</v>
       </c>
       <c r="L936" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M936" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="N936" t="n">
         <v>6989.34</v>
       </c>
       <c r="O936" t="n">
-        <v>111829.44</v>
+        <v>181722.84</v>
       </c>
       <c r="P936" t="n">
         <v>10900</v>
       </c>
       <c r="Q936" t="n">
-        <v>174400</v>
+        <v>283400</v>
       </c>
     </row>
     <row r="937">
@@ -44065,7 +44070,7 @@
         </is>
       </c>
       <c r="J968" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="K968" t="n">
         <v>0</v>
@@ -44074,19 +44079,19 @@
         <v>0</v>
       </c>
       <c r="M968" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="N968" t="n">
         <v>4697.3812903226</v>
       </c>
       <c r="O968" t="n">
-        <v>84552.8632258068</v>
+        <v>108039.7696774198</v>
       </c>
       <c r="P968" t="n">
         <v>10900</v>
       </c>
       <c r="Q968" t="n">
-        <v>196200</v>
+        <v>250700</v>
       </c>
     </row>
     <row r="969">
@@ -45625,7 +45630,7 @@
         </is>
       </c>
       <c r="J1001" t="n">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="K1001" t="n">
         <v>0</v>
@@ -45634,19 +45639,19 @@
         <v>0</v>
       </c>
       <c r="M1001" t="n">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="N1001" t="n">
-        <v>2000.6941322314</v>
+        <v>2000.6987179487</v>
       </c>
       <c r="O1001" t="n">
-        <v>236081.9076033052</v>
+        <v>228079.6538461518</v>
       </c>
       <c r="P1001" t="n">
         <v>2000</v>
       </c>
       <c r="Q1001" t="n">
-        <v>236000</v>
+        <v>228000</v>
       </c>
     </row>
     <row r="1002">
@@ -45766,7 +45771,7 @@
         </is>
       </c>
       <c r="J1004" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="K1004" t="n">
         <v>0</v>
@@ -45775,19 +45780,19 @@
         <v>0</v>
       </c>
       <c r="M1004" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="N1004" t="n">
         <v>1024.29</v>
       </c>
       <c r="O1004" t="n">
-        <v>26631.54</v>
+        <v>31752.99</v>
       </c>
       <c r="P1004" t="n">
         <v>2900</v>
       </c>
       <c r="Q1004" t="n">
-        <v>75400</v>
+        <v>89900</v>
       </c>
     </row>
     <row r="1005">
@@ -45815,7 +45820,7 @@
         </is>
       </c>
       <c r="J1005" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="K1005" t="n">
         <v>0</v>
@@ -45824,19 +45829,19 @@
         <v>0</v>
       </c>
       <c r="M1005" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="N1005" t="n">
         <v>711.48</v>
       </c>
       <c r="O1005" t="n">
-        <v>25613.28</v>
+        <v>31305.12</v>
       </c>
       <c r="P1005" t="n">
         <v>2500</v>
       </c>
       <c r="Q1005" t="n">
-        <v>90000</v>
+        <v>110000</v>
       </c>
     </row>
     <row r="1006">
@@ -46153,7 +46158,7 @@
         </is>
       </c>
       <c r="J1012" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="K1012" t="n">
         <v>0</v>
@@ -46162,19 +46167,19 @@
         <v>0</v>
       </c>
       <c r="M1012" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="N1012" t="n">
         <v>7046.939827363</v>
       </c>
       <c r="O1012" t="n">
-        <v>458051.088778595</v>
+        <v>598989.885325855</v>
       </c>
       <c r="P1012" t="n">
         <v>9900</v>
       </c>
       <c r="Q1012" t="n">
-        <v>643500</v>
+        <v>841500</v>
       </c>
     </row>
     <row r="1013">
@@ -46502,10 +46507,10 @@
         <v>1</v>
       </c>
       <c r="N1019" t="n">
-        <v>44113.603953488</v>
+        <v>44113.604096386</v>
       </c>
       <c r="O1019" t="n">
-        <v>44113.603953488</v>
+        <v>44113.604096386</v>
       </c>
       <c r="P1019" t="n">
         <v>71900</v>
@@ -46649,10 +46654,10 @@
         <v>216</v>
       </c>
       <c r="N1022" t="n">
-        <v>665.3237759536501</v>
+        <v>665.3237979601701</v>
       </c>
       <c r="O1022" t="n">
-        <v>143709.9356059884</v>
+        <v>143709.9403593967</v>
       </c>
       <c r="P1022" t="n">
         <v>2900</v>
@@ -48151,22 +48156,22 @@
         <v>0</v>
       </c>
       <c r="L1055" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M1055" t="n">
-        <v>585</v>
+        <v>573</v>
       </c>
       <c r="N1055" t="n">
         <v>1176.57</v>
       </c>
       <c r="O1055" t="n">
-        <v>688293.45</v>
+        <v>674174.61</v>
       </c>
       <c r="P1055" t="n">
         <v>1900</v>
       </c>
       <c r="Q1055" t="n">
-        <v>1111500</v>
+        <v>1088700</v>
       </c>
     </row>
     <row r="1056">
@@ -48189,7 +48194,7 @@
         </is>
       </c>
       <c r="J1056" t="n">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="K1056" t="n">
         <v>0</v>
@@ -48198,19 +48203,19 @@
         <v>0</v>
       </c>
       <c r="M1056" t="n">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="N1056" t="n">
         <v>3181.9</v>
       </c>
       <c r="O1056" t="n">
-        <v>394555.6</v>
+        <v>426374.6</v>
       </c>
       <c r="P1056" t="n">
         <v>5100</v>
       </c>
       <c r="Q1056" t="n">
-        <v>632400</v>
+        <v>683400</v>
       </c>
     </row>
     <row r="1057">
@@ -48774,7 +48779,7 @@
         </is>
       </c>
       <c r="J1069" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="K1069" t="n">
         <v>0</v>
@@ -48783,19 +48788,19 @@
         <v>0</v>
       </c>
       <c r="M1069" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="N1069" t="n">
-        <v>4985.4060913706</v>
+        <v>4985.4063157895</v>
       </c>
       <c r="O1069" t="n">
-        <v>304109.7715736066</v>
+        <v>269211.941052633</v>
       </c>
       <c r="P1069" t="n">
         <v>7900</v>
       </c>
       <c r="Q1069" t="n">
-        <v>481900</v>
+        <v>426600</v>
       </c>
     </row>
     <row r="1070">
@@ -48876,7 +48881,7 @@
         </is>
       </c>
       <c r="J1071" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="K1071" t="n">
         <v>0</v>
@@ -48885,19 +48890,19 @@
         <v>0</v>
       </c>
       <c r="M1071" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="N1071" t="n">
-        <v>1757.3205764967</v>
+        <v>1757.3205829596</v>
       </c>
       <c r="O1071" t="n">
-        <v>105439.234589802</v>
+        <v>96652.63206277799</v>
       </c>
       <c r="P1071" t="n">
         <v>2000</v>
       </c>
       <c r="Q1071" t="n">
-        <v>120000</v>
+        <v>110000</v>
       </c>
     </row>
     <row r="1072">
@@ -48922,7 +48927,7 @@
         </is>
       </c>
       <c r="J1072" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="K1072" t="n">
         <v>0</v>
@@ -48931,19 +48936,19 @@
         <v>0</v>
       </c>
       <c r="M1072" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="N1072" t="n">
         <v>1561.33</v>
       </c>
       <c r="O1072" t="n">
-        <v>32787.93</v>
+        <v>56207.88</v>
       </c>
       <c r="P1072" t="n">
         <v>2000</v>
       </c>
       <c r="Q1072" t="n">
-        <v>42000</v>
+        <v>72000</v>
       </c>
     </row>
     <row r="1073">
@@ -49845,7 +49850,7 @@
         </is>
       </c>
       <c r="J1092" t="n">
-        <v>650</v>
+        <v>450</v>
       </c>
       <c r="K1092" t="n">
         <v>0</v>
@@ -49854,19 +49859,19 @@
         <v>0</v>
       </c>
       <c r="M1092" t="n">
-        <v>650</v>
+        <v>450</v>
       </c>
       <c r="N1092" t="n">
-        <v>220.00364812669</v>
+        <v>220.00299116111</v>
       </c>
       <c r="O1092" t="n">
-        <v>143002.3712823485</v>
+        <v>99001.34602249951</v>
       </c>
       <c r="P1092" t="n">
         <v>260</v>
       </c>
       <c r="Q1092" t="n">
-        <v>169000</v>
+        <v>117000</v>
       </c>
     </row>
     <row r="1093">
@@ -50213,7 +50218,7 @@
         </is>
       </c>
       <c r="J1100" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="K1100" t="n">
         <v>0</v>
@@ -50222,19 +50227,19 @@
         <v>0</v>
       </c>
       <c r="M1100" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="N1100" t="n">
         <v>3504.16</v>
       </c>
       <c r="O1100" t="n">
-        <v>31537.44</v>
+        <v>66579.03999999999</v>
       </c>
       <c r="P1100" t="n">
         <v>3900</v>
       </c>
       <c r="Q1100" t="n">
-        <v>35100</v>
+        <v>74100</v>
       </c>
     </row>
     <row r="1101">
@@ -50811,7 +50816,7 @@
         </is>
       </c>
       <c r="J1113" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="K1113" t="n">
         <v>0</v>
@@ -50820,19 +50825,19 @@
         <v>0</v>
       </c>
       <c r="M1113" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="N1113" t="n">
         <v>1952.41</v>
       </c>
       <c r="O1113" t="n">
-        <v>54667.48</v>
+        <v>74191.58</v>
       </c>
       <c r="P1113" t="n">
         <v>2700</v>
       </c>
       <c r="Q1113" t="n">
-        <v>75600</v>
+        <v>102600</v>
       </c>
     </row>
     <row r="1114">
@@ -51271,28 +51276,28 @@
         </is>
       </c>
       <c r="J1123" t="n">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="K1123" t="n">
         <v>0</v>
       </c>
       <c r="L1123" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M1123" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="N1123" t="n">
         <v>7480</v>
       </c>
       <c r="O1123" t="n">
-        <v>411400</v>
+        <v>224400</v>
       </c>
       <c r="P1123" t="n">
         <v>9500</v>
       </c>
       <c r="Q1123" t="n">
-        <v>522500</v>
+        <v>285000</v>
       </c>
     </row>
     <row r="1124">
@@ -51317,7 +51322,7 @@
         </is>
       </c>
       <c r="J1124" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="K1124" t="n">
         <v>0</v>
@@ -51326,19 +51331,19 @@
         <v>0</v>
       </c>
       <c r="M1124" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="N1124" t="n">
         <v>6336</v>
       </c>
       <c r="O1124" t="n">
-        <v>544896</v>
+        <v>519552</v>
       </c>
       <c r="P1124" t="n">
         <v>7500</v>
       </c>
       <c r="Q1124" t="n">
-        <v>645000</v>
+        <v>615000</v>
       </c>
     </row>
     <row r="1125">
@@ -51363,7 +51368,7 @@
         </is>
       </c>
       <c r="J1125" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K1125" t="n">
         <v>0</v>
@@ -51372,19 +51377,19 @@
         <v>0</v>
       </c>
       <c r="M1125" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="N1125" t="n">
         <v>5280</v>
       </c>
       <c r="O1125" t="n">
-        <v>116160</v>
+        <v>105600</v>
       </c>
       <c r="P1125" t="n">
         <v>6900</v>
       </c>
       <c r="Q1125" t="n">
-        <v>151800</v>
+        <v>138000</v>
       </c>
     </row>
     <row r="1126">
@@ -51409,7 +51414,7 @@
         </is>
       </c>
       <c r="J1126" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K1126" t="n">
         <v>0</v>
@@ -51418,19 +51423,19 @@
         <v>0</v>
       </c>
       <c r="M1126" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="N1126" t="n">
         <v>5280</v>
       </c>
       <c r="O1126" t="n">
-        <v>184800</v>
+        <v>174240</v>
       </c>
       <c r="P1126" t="n">
         <v>6900</v>
       </c>
       <c r="Q1126" t="n">
-        <v>241500</v>
+        <v>227700</v>
       </c>
     </row>
     <row r="1127">
@@ -51455,7 +51460,7 @@
         </is>
       </c>
       <c r="J1127" t="n">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="K1127" t="n">
         <v>0</v>
@@ -51464,19 +51469,19 @@
         <v>0</v>
       </c>
       <c r="M1127" t="n">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="N1127" t="n">
         <v>1584</v>
       </c>
       <c r="O1127" t="n">
-        <v>291456</v>
+        <v>281952</v>
       </c>
       <c r="P1127" t="n">
         <v>2000</v>
       </c>
       <c r="Q1127" t="n">
-        <v>368000</v>
+        <v>356000</v>
       </c>
     </row>
     <row r="1128">
@@ -51547,7 +51552,7 @@
         </is>
       </c>
       <c r="J1129" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K1129" t="n">
         <v>0</v>
@@ -51556,19 +51561,19 @@
         <v>0</v>
       </c>
       <c r="M1129" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="N1129" t="n">
         <v>6160</v>
       </c>
       <c r="O1129" t="n">
-        <v>86240</v>
+        <v>61600</v>
       </c>
       <c r="P1129" t="n">
         <v>7900</v>
       </c>
       <c r="Q1129" t="n">
-        <v>110600</v>
+        <v>79000</v>
       </c>
     </row>
     <row r="1130">
@@ -51593,7 +51598,7 @@
         </is>
       </c>
       <c r="J1130" t="n">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="K1130" t="n">
         <v>0</v>
@@ -51602,19 +51607,19 @@
         <v>0</v>
       </c>
       <c r="M1130" t="n">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="N1130" t="n">
         <v>4400</v>
       </c>
       <c r="O1130" t="n">
-        <v>602800</v>
+        <v>585200</v>
       </c>
       <c r="P1130" t="n">
         <v>5900</v>
       </c>
       <c r="Q1130" t="n">
-        <v>808300</v>
+        <v>784700</v>
       </c>
     </row>
     <row r="1131">
@@ -52559,7 +52564,7 @@
         </is>
       </c>
       <c r="J1151" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K1151" t="n">
         <v>0</v>
@@ -52568,19 +52573,19 @@
         <v>0</v>
       </c>
       <c r="M1151" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N1151" t="n">
         <v>1400</v>
       </c>
       <c r="O1151" t="n">
-        <v>79800</v>
+        <v>78400</v>
       </c>
       <c r="P1151" t="n">
         <v>1700</v>
       </c>
       <c r="Q1151" t="n">
-        <v>96900</v>
+        <v>95200</v>
       </c>
     </row>
     <row r="1152">
@@ -53249,13 +53254,13 @@
         </is>
       </c>
       <c r="J1166" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K1166" t="n">
         <v>0</v>
       </c>
       <c r="L1166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1166" t="n">
         <v>10</v>
@@ -54010,7 +54015,7 @@
         </is>
       </c>
       <c r="J1182" t="n">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="K1182" t="n">
         <v>0</v>
@@ -54019,19 +54024,19 @@
         <v>0</v>
       </c>
       <c r="M1182" t="n">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="N1182" t="n">
         <v>751.45</v>
       </c>
       <c r="O1182" t="n">
-        <v>51098.60000000001</v>
+        <v>66127.60000000001</v>
       </c>
       <c r="P1182" t="n">
         <v>2500</v>
       </c>
       <c r="Q1182" t="n">
-        <v>170000</v>
+        <v>220000</v>
       </c>
     </row>
     <row r="1183">
@@ -54868,10 +54873,10 @@
         <v>48</v>
       </c>
       <c r="N1200" t="n">
-        <v>4171.6686299766</v>
+        <v>4171.6686251469</v>
       </c>
       <c r="O1200" t="n">
-        <v>200240.0942388768</v>
+        <v>200240.0940070512</v>
       </c>
       <c r="P1200" t="n">
         <v>5500</v>
@@ -55224,7 +55229,7 @@
         </is>
       </c>
       <c r="J1208" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K1208" t="n">
         <v>0</v>
@@ -55233,19 +55238,19 @@
         <v>0</v>
       </c>
       <c r="M1208" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N1208" t="n">
         <v>2100</v>
       </c>
       <c r="O1208" t="n">
-        <v>90300</v>
+        <v>86100</v>
       </c>
       <c r="P1208" t="n">
         <v>2600</v>
       </c>
       <c r="Q1208" t="n">
-        <v>111800</v>
+        <v>106600</v>
       </c>
     </row>
     <row r="1209">
@@ -55907,7 +55912,7 @@
         </is>
       </c>
       <c r="J1223" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="K1223" t="n">
         <v>0</v>
@@ -55916,19 +55921,19 @@
         <v>0</v>
       </c>
       <c r="M1223" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="N1223" t="n">
-        <v>4365.5677966102</v>
+        <v>3732.8768115942</v>
       </c>
       <c r="O1223" t="n">
-        <v>218278.38983051</v>
+        <v>223972.608695652</v>
       </c>
       <c r="P1223" t="n">
         <v>4500</v>
       </c>
       <c r="Q1223" t="n">
-        <v>225000</v>
+        <v>270000</v>
       </c>
     </row>
     <row r="1224">
@@ -56097,22 +56102,22 @@
         <v>0</v>
       </c>
       <c r="L1227" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M1227" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="N1227" t="n">
         <v>4550</v>
       </c>
       <c r="O1227" t="n">
-        <v>277550</v>
+        <v>263900</v>
       </c>
       <c r="P1227" t="n">
         <v>5500</v>
       </c>
       <c r="Q1227" t="n">
-        <v>335500</v>
+        <v>319000</v>
       </c>
     </row>
     <row r="1228">

--- a/bodegas/LJ-101.xlsx
+++ b/bodegas/LJ-101.xlsx
@@ -9055,10 +9055,10 @@
         <v>82</v>
       </c>
       <c r="N202" t="n">
-        <v>2582.2554027233</v>
+        <v>2582.2553995381</v>
       </c>
       <c r="O202" t="n">
-        <v>211744.9430233106</v>
+        <v>211744.9427621242</v>
       </c>
       <c r="P202" t="n">
         <v>4500</v>
@@ -9739,10 +9739,10 @@
         <v>87</v>
       </c>
       <c r="N217" t="n">
-        <v>3230.0666176471</v>
+        <v>3230.0665925926</v>
       </c>
       <c r="O217" t="n">
-        <v>281015.7957352977</v>
+        <v>281015.7935555562</v>
       </c>
       <c r="P217" t="n">
         <v>6200</v>
@@ -12943,22 +12943,22 @@
         <v>0</v>
       </c>
       <c r="L288" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M288" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="N288" t="n">
         <v>6441.03</v>
       </c>
       <c r="O288" t="n">
-        <v>418666.95</v>
+        <v>386461.8</v>
       </c>
       <c r="P288" t="n">
         <v>10500</v>
       </c>
       <c r="Q288" t="n">
-        <v>682500</v>
+        <v>630000</v>
       </c>
     </row>
     <row r="289">
@@ -14586,10 +14586,10 @@
         <v>12</v>
       </c>
       <c r="N324" t="n">
-        <v>11921.4</v>
+        <v>11949.297191888</v>
       </c>
       <c r="O324" t="n">
-        <v>143056.8</v>
+        <v>143391.566302656</v>
       </c>
       <c r="P324" t="n">
         <v>19900</v>
@@ -15177,22 +15177,22 @@
         <v>0</v>
       </c>
       <c r="L337" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M337" t="n">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="N337" t="n">
-        <v>1630.9240698598</v>
+        <v>1630.9240720148</v>
       </c>
       <c r="O337" t="n">
-        <v>238114.9141995308</v>
+        <v>234853.0663701312</v>
       </c>
       <c r="P337" t="n">
         <v>2500</v>
       </c>
       <c r="Q337" t="n">
-        <v>365000</v>
+        <v>360000</v>
       </c>
     </row>
     <row r="338">
@@ -15315,22 +15315,22 @@
         <v>0</v>
       </c>
       <c r="L340" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M340" t="n">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="N340" t="n">
-        <v>1550.1941645158</v>
+        <v>1550.1941668538</v>
       </c>
       <c r="O340" t="n">
-        <v>965770.9644933434</v>
+        <v>958019.9951156484</v>
       </c>
       <c r="P340" t="n">
         <v>2500</v>
       </c>
       <c r="Q340" t="n">
-        <v>1557500</v>
+        <v>1545000</v>
       </c>
     </row>
     <row r="341">
@@ -15413,10 +15413,10 @@
         <v>409</v>
       </c>
       <c r="N342" t="n">
-        <v>2403.5147075539</v>
+        <v>2403.51472848</v>
       </c>
       <c r="O342" t="n">
-        <v>983037.515389545</v>
+        <v>983037.52394832</v>
       </c>
       <c r="P342" t="n">
         <v>3500</v>
@@ -20904,10 +20904,10 @@
         <v>7</v>
       </c>
       <c r="N468" t="n">
-        <v>8332.779613402099</v>
+        <v>8397.710363636401</v>
       </c>
       <c r="O468" t="n">
-        <v>58329.4572938147</v>
+        <v>58783.9725454548</v>
       </c>
       <c r="P468" t="n">
         <v>14900</v>
@@ -22985,22 +22985,22 @@
         <v>0</v>
       </c>
       <c r="L515" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M515" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N515" t="n">
         <v>8562.18</v>
       </c>
       <c r="O515" t="n">
-        <v>128432.7</v>
+        <v>111308.34</v>
       </c>
       <c r="P515" t="n">
         <v>9900</v>
       </c>
       <c r="Q515" t="n">
-        <v>148500</v>
+        <v>128700</v>
       </c>
     </row>
     <row r="516">
@@ -23200,22 +23200,22 @@
         <v>0</v>
       </c>
       <c r="L520" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M520" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="N520" t="n">
         <v>7700</v>
       </c>
       <c r="O520" t="n">
-        <v>708400</v>
+        <v>685300</v>
       </c>
       <c r="P520" t="n">
         <v>13900</v>
       </c>
       <c r="Q520" t="n">
-        <v>1278800</v>
+        <v>1237100</v>
       </c>
     </row>
     <row r="521">
@@ -24316,22 +24316,22 @@
         <v>0</v>
       </c>
       <c r="L544" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M544" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="N544" t="n">
-        <v>1664.3470318725</v>
+        <v>1664.3469860279</v>
       </c>
       <c r="O544" t="n">
-        <v>108182.5570717125</v>
+        <v>106518.2071057856</v>
       </c>
       <c r="P544" t="n">
         <v>2900</v>
       </c>
       <c r="Q544" t="n">
-        <v>188500</v>
+        <v>185600</v>
       </c>
     </row>
     <row r="545">
@@ -25533,10 +25533,10 @@
         <v>3</v>
       </c>
       <c r="N570" t="n">
-        <v>26956</v>
+        <v>28079.166666667</v>
       </c>
       <c r="O570" t="n">
-        <v>80868</v>
+        <v>84237.50000000099</v>
       </c>
       <c r="P570" t="n">
         <v>44900</v>
@@ -27475,22 +27475,22 @@
         <v>0</v>
       </c>
       <c r="L612" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M612" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N612" t="n">
-        <v>3960</v>
+        <v>0</v>
       </c>
       <c r="O612" t="n">
-        <v>7920</v>
+        <v>0</v>
       </c>
       <c r="P612" t="n">
         <v>6500</v>
       </c>
       <c r="Q612" t="n">
-        <v>13000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="613">
@@ -29327,10 +29327,10 @@
         <v>88</v>
       </c>
       <c r="N652" t="n">
-        <v>3903.7383067896</v>
+        <v>3903.7383529412</v>
       </c>
       <c r="O652" t="n">
-        <v>343528.9709974848</v>
+        <v>343528.9750588256</v>
       </c>
       <c r="P652" t="n">
         <v>7500</v>
@@ -29546,22 +29546,22 @@
         <v>0</v>
       </c>
       <c r="L657" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M657" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N657" t="n">
         <v>4202</v>
       </c>
       <c r="O657" t="n">
-        <v>12606</v>
+        <v>0</v>
       </c>
       <c r="P657" t="n">
         <v>7900</v>
       </c>
       <c r="Q657" t="n">
-        <v>23700</v>
+        <v>0</v>
       </c>
     </row>
     <row r="658">
@@ -33371,22 +33371,22 @@
         <v>0</v>
       </c>
       <c r="L740" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M740" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="N740" t="n">
-        <v>1592.2821517241</v>
+        <v>1592.2821853389</v>
       </c>
       <c r="O740" t="n">
-        <v>179927.8831448233</v>
+        <v>176743.3225726179</v>
       </c>
       <c r="P740" t="n">
         <v>2500</v>
       </c>
       <c r="Q740" t="n">
-        <v>282500</v>
+        <v>277500</v>
       </c>
     </row>
     <row r="741">
@@ -37900,10 +37900,10 @@
         <v>1079</v>
       </c>
       <c r="N838" t="n">
-        <v>517.29287307808</v>
+        <v>517.2929433161599</v>
       </c>
       <c r="O838" t="n">
-        <v>558159.0100512484</v>
+        <v>558159.0858381366</v>
       </c>
       <c r="P838" t="n">
         <v>900</v>
@@ -38415,10 +38415,10 @@
         <v>202</v>
       </c>
       <c r="N849" t="n">
-        <v>3110.8397028838</v>
+        <v>3110.8396848556</v>
       </c>
       <c r="O849" t="n">
-        <v>628389.6199825276</v>
+        <v>628389.6163408312</v>
       </c>
       <c r="P849" t="n">
         <v>4500</v>
@@ -51926,22 +51926,22 @@
         <v>0</v>
       </c>
       <c r="L1137" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M1137" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="N1137" t="n">
         <v>5280</v>
       </c>
       <c r="O1137" t="n">
-        <v>179520</v>
+        <v>163680</v>
       </c>
       <c r="P1137" t="n">
         <v>6900</v>
       </c>
       <c r="Q1137" t="n">
-        <v>234600</v>
+        <v>213900</v>
       </c>
     </row>
     <row r="1138">

--- a/bodegas/LJ-101.xlsx
+++ b/bodegas/LJ-101.xlsx
@@ -9239,10 +9239,10 @@
         <v>6</v>
       </c>
       <c r="N206" t="n">
-        <v>2033.5164102564</v>
+        <v>2033.5050485437</v>
       </c>
       <c r="O206" t="n">
-        <v>12201.0984615384</v>
+        <v>12201.0302912622</v>
       </c>
       <c r="P206" t="n">
         <v>4100</v>
@@ -15372,10 +15372,10 @@
         <v>390</v>
       </c>
       <c r="N341" t="n">
-        <v>2403.515543043</v>
+        <v>2403.5155820371</v>
       </c>
       <c r="O341" t="n">
-        <v>937371.06178677</v>
+        <v>937371.076994469</v>
       </c>
       <c r="P341" t="n">
         <v>3500</v>
@@ -15418,10 +15418,10 @@
         <v>5</v>
       </c>
       <c r="N342" t="n">
-        <v>2521.4791818182</v>
+        <v>2521.4745192308</v>
       </c>
       <c r="O342" t="n">
-        <v>12607.395909091</v>
+        <v>12607.372596154</v>
       </c>
       <c r="P342" t="n">
         <v>3900</v>
@@ -19254,22 +19254,22 @@
         <v>0</v>
       </c>
       <c r="L430" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M430" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="N430" t="n">
         <v>56503</v>
       </c>
       <c r="O430" t="n">
-        <v>508527</v>
+        <v>339018</v>
       </c>
       <c r="P430" t="n">
         <v>90500</v>
       </c>
       <c r="Q430" t="n">
-        <v>814500</v>
+        <v>543000</v>
       </c>
     </row>
     <row r="431">
@@ -38282,10 +38282,10 @@
         <v>201</v>
       </c>
       <c r="N846" t="n">
-        <v>3110.8396334311</v>
+        <v>3110.8396273474</v>
       </c>
       <c r="O846" t="n">
-        <v>625278.7663196512</v>
+        <v>625278.7650968274</v>
       </c>
       <c r="P846" t="n">
         <v>4500</v>
@@ -38694,10 +38694,10 @@
         <v>1139</v>
       </c>
       <c r="N855" t="n">
-        <v>703.79488487659</v>
+        <v>703.79488357273</v>
       </c>
       <c r="O855" t="n">
-        <v>801622.373874436</v>
+        <v>801622.3723893395</v>
       </c>
       <c r="P855" t="n">
         <v>900</v>

--- a/bodegas/LJ-101.xlsx
+++ b/bodegas/LJ-101.xlsx
@@ -771,10 +771,10 @@
         <v>18</v>
       </c>
       <c r="N9" t="n">
-        <v>27108.144192256</v>
+        <v>27000</v>
       </c>
       <c r="O9" t="n">
-        <v>487946.595460608</v>
+        <v>486000</v>
       </c>
       <c r="P9" t="n">
         <v>20000</v>
@@ -983,10 +983,10 @@
         <v>11</v>
       </c>
       <c r="N14" t="n">
-        <v>27117.391304348</v>
+        <v>27000</v>
       </c>
       <c r="O14" t="n">
-        <v>298291.304347828</v>
+        <v>297000</v>
       </c>
       <c r="P14" t="n">
         <v>30000</v>
@@ -4745,10 +4745,10 @@
         <v>7</v>
       </c>
       <c r="N103" t="n">
-        <v>27229.787234043</v>
+        <v>27000</v>
       </c>
       <c r="O103" t="n">
-        <v>190608.510638301</v>
+        <v>189000</v>
       </c>
       <c r="P103" t="n">
         <v>20000</v>
@@ -9193,10 +9193,10 @@
         <v>42</v>
       </c>
       <c r="N205" t="n">
-        <v>5224.6087374335</v>
+        <v>5216.895993495</v>
       </c>
       <c r="O205" t="n">
-        <v>219433.566972207</v>
+        <v>219109.63172679</v>
       </c>
       <c r="P205" t="n">
         <v>8500</v>
@@ -10514,10 +10514,10 @@
         <v>12</v>
       </c>
       <c r="N234" t="n">
-        <v>4903.3514603175</v>
+        <v>4890.9300507937</v>
       </c>
       <c r="O234" t="n">
-        <v>58840.21752381</v>
+        <v>58691.16060952439</v>
       </c>
       <c r="P234" t="n">
         <v>8200</v>
@@ -10750,10 +10750,10 @@
         <v>7</v>
       </c>
       <c r="N239" t="n">
-        <v>5928.7474048443</v>
+        <v>5888</v>
       </c>
       <c r="O239" t="n">
-        <v>41501.2318339101</v>
+        <v>41216</v>
       </c>
       <c r="P239" t="n">
         <v>9500</v>
@@ -11600,10 +11600,10 @@
         <v>18</v>
       </c>
       <c r="N258" t="n">
-        <v>8184.2747524752</v>
+        <v>8154</v>
       </c>
       <c r="O258" t="n">
-        <v>147316.9455445536</v>
+        <v>146772</v>
       </c>
       <c r="P258" t="n">
         <v>13500</v>
@@ -11646,10 +11646,10 @@
         <v>11</v>
       </c>
       <c r="N259" t="n">
-        <v>14831.411358927</v>
+        <v>14822.378829982</v>
       </c>
       <c r="O259" t="n">
-        <v>163145.524948197</v>
+        <v>163046.167129802</v>
       </c>
       <c r="P259" t="n">
         <v>24900</v>
@@ -12549,10 +12549,10 @@
         <v>15</v>
       </c>
       <c r="N279" t="n">
-        <v>15071.76</v>
+        <v>14386.68</v>
       </c>
       <c r="O279" t="n">
-        <v>226076.4</v>
+        <v>215800.2</v>
       </c>
       <c r="P279" t="n">
         <v>21900</v>
@@ -14545,10 +14545,10 @@
         <v>13</v>
       </c>
       <c r="N323" t="n">
-        <v>11959.066350711</v>
+        <v>11921.4</v>
       </c>
       <c r="O323" t="n">
-        <v>155467.862559243</v>
+        <v>154978.2</v>
       </c>
       <c r="P323" t="n">
         <v>19900</v>
@@ -16571,10 +16571,10 @@
         <v>3</v>
       </c>
       <c r="N368" t="n">
-        <v>10907.343571429</v>
+        <v>10836.973636364</v>
       </c>
       <c r="O368" t="n">
-        <v>32722.030714287</v>
+        <v>32510.920909092</v>
       </c>
       <c r="P368" t="n">
         <v>19900</v>
@@ -17787,10 +17787,10 @@
         <v>34</v>
       </c>
       <c r="N395" t="n">
-        <v>9460.065359477099</v>
+        <v>9338</v>
       </c>
       <c r="O395" t="n">
-        <v>321642.2222222214</v>
+        <v>317492</v>
       </c>
       <c r="P395" t="n">
         <v>15500</v>
@@ -19998,10 +19998,10 @@
         <v>12</v>
       </c>
       <c r="N447" t="n">
-        <v>11594.699548023</v>
+        <v>11562.038418079</v>
       </c>
       <c r="O447" t="n">
-        <v>139136.394576276</v>
+        <v>138744.461016948</v>
       </c>
       <c r="P447" t="n">
         <v>18500</v>
@@ -20090,10 +20090,10 @@
         <v>3</v>
       </c>
       <c r="N449" t="n">
-        <v>12056.245617021</v>
+        <v>12005.159829787</v>
       </c>
       <c r="O449" t="n">
-        <v>36168.736851063</v>
+        <v>36015.479489361</v>
       </c>
       <c r="P449" t="n">
         <v>19500</v>
@@ -20607,10 +20607,10 @@
         <v>9</v>
       </c>
       <c r="N461" t="n">
-        <v>27232.25996</v>
+        <v>27123.76488</v>
       </c>
       <c r="O461" t="n">
-        <v>245090.33964</v>
+        <v>244113.88392</v>
       </c>
       <c r="P461" t="n">
         <v>44500</v>
@@ -21093,10 +21093,10 @@
         <v>16</v>
       </c>
       <c r="N472" t="n">
-        <v>27011.040935673</v>
+        <v>26854</v>
       </c>
       <c r="O472" t="n">
-        <v>432176.654970768</v>
+        <v>429664</v>
       </c>
       <c r="P472" t="n">
         <v>43900</v>
@@ -21701,10 +21701,10 @@
         <v>5</v>
       </c>
       <c r="N486" t="n">
-        <v>10317.12016129</v>
+        <v>9994.710161290301</v>
       </c>
       <c r="O486" t="n">
-        <v>51585.60080645001</v>
+        <v>49973.5508064515</v>
       </c>
       <c r="P486" t="n">
         <v>20800</v>
@@ -22143,10 +22143,10 @@
         <v>36</v>
       </c>
       <c r="N496" t="n">
-        <v>13079.564264151</v>
+        <v>12981.59</v>
       </c>
       <c r="O496" t="n">
-        <v>470864.313509436</v>
+        <v>467337.24</v>
       </c>
       <c r="P496" t="n">
         <v>21900</v>
@@ -22189,10 +22189,10 @@
         <v>47</v>
       </c>
       <c r="N497" t="n">
-        <v>13974.031438356</v>
+        <v>13878.97</v>
       </c>
       <c r="O497" t="n">
-        <v>656779.477602732</v>
+        <v>652311.59</v>
       </c>
       <c r="P497" t="n">
         <v>21900</v>
@@ -27954,10 +27954,10 @@
         <v>18</v>
       </c>
       <c r="N622" t="n">
-        <v>27408.335664336</v>
+        <v>27218</v>
       </c>
       <c r="O622" t="n">
-        <v>493350.041958048</v>
+        <v>489924</v>
       </c>
       <c r="P622" t="n">
         <v>43900</v>
@@ -28000,10 +28000,10 @@
         <v>5</v>
       </c>
       <c r="N623" t="n">
-        <v>21456.861702128</v>
+        <v>21231</v>
       </c>
       <c r="O623" t="n">
-        <v>107284.30851064</v>
+        <v>106155</v>
       </c>
       <c r="P623" t="n">
         <v>34500</v>
@@ -28046,10 +28046,10 @@
         <v>3</v>
       </c>
       <c r="N624" t="n">
-        <v>23419.958333333</v>
+        <v>22942</v>
       </c>
       <c r="O624" t="n">
-        <v>70259.87499999901</v>
+        <v>68826</v>
       </c>
       <c r="P624" t="n">
         <v>36900</v>
@@ -28647,10 +28647,10 @@
         <v>4</v>
       </c>
       <c r="N637" t="n">
-        <v>9198.3277962348</v>
+        <v>9178</v>
       </c>
       <c r="O637" t="n">
-        <v>36793.3111849392</v>
+        <v>36712</v>
       </c>
       <c r="P637" t="n">
         <v>14900</v>
@@ -28693,10 +28693,10 @@
         <v>60</v>
       </c>
       <c r="N638" t="n">
-        <v>4567.8948290973</v>
+        <v>4544</v>
       </c>
       <c r="O638" t="n">
-        <v>274073.689745838</v>
+        <v>272640</v>
       </c>
       <c r="P638" t="n">
         <v>7900</v>
@@ -28785,10 +28785,10 @@
         <v>15</v>
       </c>
       <c r="N640" t="n">
-        <v>13948.467680608</v>
+        <v>13922</v>
       </c>
       <c r="O640" t="n">
-        <v>209227.01520912</v>
+        <v>208830</v>
       </c>
       <c r="P640" t="n">
         <v>22900</v>
@@ -29608,10 +29608,10 @@
         <v>2</v>
       </c>
       <c r="N658" t="n">
-        <v>10198.963414634</v>
+        <v>9839</v>
       </c>
       <c r="O658" t="n">
-        <v>20397.926829268</v>
+        <v>19678</v>
       </c>
       <c r="P658" t="n">
         <v>16900</v>
@@ -30715,10 +30715,10 @@
         <v>34</v>
       </c>
       <c r="N682" t="n">
-        <v>17123.621290098</v>
+        <v>17075.989518828</v>
       </c>
       <c r="O682" t="n">
-        <v>582203.123863332</v>
+        <v>580583.6436401519</v>
       </c>
       <c r="P682" t="n">
         <v>27500</v>
@@ -30991,10 +30991,10 @@
         <v>1</v>
       </c>
       <c r="N688" t="n">
-        <v>21666.992481203</v>
+        <v>21346</v>
       </c>
       <c r="O688" t="n">
-        <v>21666.992481203</v>
+        <v>21346</v>
       </c>
       <c r="P688" t="n">
         <v>34900</v>
@@ -31178,10 +31178,10 @@
         <v>13</v>
       </c>
       <c r="N692" t="n">
-        <v>17325.987730061</v>
+        <v>17168</v>
       </c>
       <c r="O692" t="n">
-        <v>225237.840490793</v>
+        <v>223184</v>
       </c>
       <c r="P692" t="n">
         <v>27900</v>
@@ -31224,10 +31224,10 @@
         <v>20</v>
       </c>
       <c r="N693" t="n">
-        <v>27289.075933076</v>
+        <v>27254</v>
       </c>
       <c r="O693" t="n">
-        <v>545781.51866152</v>
+        <v>545080</v>
       </c>
       <c r="P693" t="n">
         <v>43900</v>
@@ -31500,10 +31500,10 @@
         <v>29</v>
       </c>
       <c r="N699" t="n">
-        <v>40316.604863222</v>
+        <v>40073</v>
       </c>
       <c r="O699" t="n">
-        <v>1169181.541033438</v>
+        <v>1162117</v>
       </c>
       <c r="P699" t="n">
         <v>64900</v>
@@ -31638,10 +31638,10 @@
         <v>20</v>
       </c>
       <c r="N702" t="n">
-        <v>8721.297429620599</v>
+        <v>8700</v>
       </c>
       <c r="O702" t="n">
-        <v>174425.948592412</v>
+        <v>174000</v>
       </c>
       <c r="P702" t="n">
         <v>14900</v>
@@ -42269,10 +42269,10 @@
         <v>5</v>
       </c>
       <c r="N930" t="n">
-        <v>7184.3863636364</v>
+        <v>6773.85</v>
       </c>
       <c r="O930" t="n">
-        <v>35921.931818182</v>
+        <v>33869.25</v>
       </c>
       <c r="P930" t="n">
         <v>9500</v>
@@ -46134,10 +46134,10 @@
         <v>11</v>
       </c>
       <c r="N1011" t="n">
-        <v>24492.510949367</v>
+        <v>24338.47</v>
       </c>
       <c r="O1011" t="n">
-        <v>269417.620443037</v>
+        <v>267723.17</v>
       </c>
       <c r="P1011" t="n">
         <v>27900</v>
